--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm12\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F9D44CC-7703-4B4D-8D0E-7FEFF56BFB36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AAD60B3-27EA-41D2-9209-D6EC749F0A4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5790" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -25,15 +25,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -247,23 +244,23 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -276,7 +273,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -319,7 +316,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -340,27 +337,27 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -368,8 +365,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -387,7 +384,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -847,6 +844,15 @@
                 <c:pt idx="135">
                   <c:v>46114</c:v>
                 </c:pt>
+                <c:pt idx="136">
+                  <c:v>46115</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>46115</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>46115</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1260,6 +1266,9 @@
                 </c:pt>
                 <c:pt idx="134">
                   <c:v>36.832999999999998</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>37</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1714,6 +1723,15 @@
                 <c:pt idx="135">
                   <c:v>46114</c:v>
                 </c:pt>
+                <c:pt idx="136">
+                  <c:v>46115</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>46115</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>46115</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2126,6 +2144,9 @@
                   <c:v>21.3</c:v>
                 </c:pt>
                 <c:pt idx="134">
+                  <c:v>21.3</c:v>
+                </c:pt>
+                <c:pt idx="135">
                   <c:v>21.3</c:v>
                 </c:pt>
               </c:numCache>
@@ -2581,6 +2602,15 @@
                 <c:pt idx="135">
                   <c:v>46114</c:v>
                 </c:pt>
+                <c:pt idx="136">
+                  <c:v>46115</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>46115</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>46115</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2993,6 +3023,9 @@
                   <c:v>73.317999999999998</c:v>
                 </c:pt>
                 <c:pt idx="134">
+                  <c:v>73.317999999999998</c:v>
+                </c:pt>
+                <c:pt idx="135">
                   <c:v>73.317999999999998</c:v>
                 </c:pt>
               </c:numCache>
@@ -3448,6 +3481,15 @@
                 <c:pt idx="135">
                   <c:v>46114</c:v>
                 </c:pt>
+                <c:pt idx="136">
+                  <c:v>46115</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>46115</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>46115</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3860,6 +3902,9 @@
                   <c:v>13.55</c:v>
                 </c:pt>
                 <c:pt idx="134">
+                  <c:v>13.55</c:v>
+                </c:pt>
+                <c:pt idx="135">
                   <c:v>13.55</c:v>
                 </c:pt>
               </c:numCache>
@@ -4315,6 +4360,15 @@
                 <c:pt idx="135">
                   <c:v>46114</c:v>
                 </c:pt>
+                <c:pt idx="136">
+                  <c:v>46115</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>46115</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>46115</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4727,6 +4781,9 @@
                   <c:v>33.659999999999997</c:v>
                 </c:pt>
                 <c:pt idx="134">
+                  <c:v>33.659999999999997</c:v>
+                </c:pt>
+                <c:pt idx="135">
                   <c:v>33.659999999999997</c:v>
                 </c:pt>
               </c:numCache>
@@ -5198,6 +5255,15 @@
                 <c:pt idx="135">
                   <c:v>46114</c:v>
                 </c:pt>
+                <c:pt idx="136">
+                  <c:v>46115</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>46115</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>46115</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5610,6 +5676,9 @@
                   <c:v>6.766</c:v>
                 </c:pt>
                 <c:pt idx="134">
+                  <c:v>6.766</c:v>
+                </c:pt>
+                <c:pt idx="135">
                   <c:v>6.766</c:v>
                 </c:pt>
               </c:numCache>
@@ -6067,6 +6136,15 @@
                 <c:pt idx="135">
                   <c:v>46114</c:v>
                 </c:pt>
+                <c:pt idx="136">
+                  <c:v>46115</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>46115</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>46115</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6479,6 +6557,9 @@
                   <c:v>7.625</c:v>
                 </c:pt>
                 <c:pt idx="134">
+                  <c:v>7.625</c:v>
+                </c:pt>
+                <c:pt idx="135">
                   <c:v>7.625</c:v>
                 </c:pt>
               </c:numCache>
@@ -6714,6 +6795,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -6721,7 +6803,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6757,7 +6838,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7224,6 +7305,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -7231,7 +7313,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -7267,7 +7348,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7639,6 +7720,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -7646,7 +7728,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -9732,18 +9813,18 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y138"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:Y141"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.125" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.26953125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="5" customFormat="1">
       <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
@@ -9820,7 +9901,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -9889,7 +9970,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="12">
         <v>46044</v>
       </c>
@@ -9966,7 +10047,7 @@
         <v>4.9450000000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="12">
         <v>46045</v>
       </c>
@@ -10043,7 +10124,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="12">
         <v>46045</v>
       </c>
@@ -10120,7 +10201,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="12">
         <v>46045</v>
       </c>
@@ -10197,7 +10278,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="12">
         <v>46048</v>
       </c>
@@ -10274,7 +10355,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25">
       <c r="A8" s="12">
         <v>46048</v>
       </c>
@@ -10351,7 +10432,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25">
       <c r="A9" s="12">
         <v>46048</v>
       </c>
@@ -10428,7 +10509,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25">
       <c r="A10" s="12">
         <v>46049</v>
       </c>
@@ -10505,7 +10586,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25">
       <c r="A11" s="12">
         <v>46049</v>
       </c>
@@ -10582,7 +10663,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25">
       <c r="A12" s="12">
         <v>46049</v>
       </c>
@@ -10659,7 +10740,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25">
       <c r="A13" s="12">
         <v>46050</v>
       </c>
@@ -10736,7 +10817,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25">
       <c r="A14" s="12">
         <v>46050</v>
       </c>
@@ -10813,7 +10894,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25">
       <c r="A15" s="12">
         <v>46050</v>
       </c>
@@ -10890,7 +10971,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25">
       <c r="A16" s="12">
         <v>46051</v>
       </c>
@@ -10967,7 +11048,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:25">
       <c r="A17" s="12">
         <v>46051</v>
       </c>
@@ -11044,7 +11125,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:25">
       <c r="A18" s="12">
         <v>46051</v>
       </c>
@@ -11121,7 +11202,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:25">
       <c r="A19" s="12">
         <v>46052</v>
       </c>
@@ -11198,7 +11279,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:25">
       <c r="A20" s="12">
         <v>46052</v>
       </c>
@@ -11275,7 +11356,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:25">
       <c r="A21" s="12">
         <v>46052</v>
       </c>
@@ -11352,7 +11433,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:25">
       <c r="A22" s="12">
         <v>46055</v>
       </c>
@@ -11429,7 +11510,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:25">
       <c r="A23" s="12">
         <v>46055</v>
       </c>
@@ -11506,7 +11587,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:25">
       <c r="A24" s="12">
         <v>46055</v>
       </c>
@@ -11583,7 +11664,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:25">
       <c r="A25" s="12">
         <v>46056</v>
       </c>
@@ -11660,7 +11741,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:25">
       <c r="A26" s="12">
         <v>46056</v>
       </c>
@@ -11737,7 +11818,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:25">
       <c r="A27" s="12">
         <v>46056</v>
       </c>
@@ -11814,7 +11895,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:25">
       <c r="A28" s="12">
         <v>46057</v>
       </c>
@@ -11891,7 +11972,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:25">
       <c r="A29" s="12">
         <v>46057</v>
       </c>
@@ -11968,7 +12049,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:25">
       <c r="A30" s="12">
         <v>46057</v>
       </c>
@@ -12045,7 +12126,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:25">
       <c r="A31" s="12">
         <v>46058</v>
       </c>
@@ -12122,7 +12203,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:25">
       <c r="A32" s="12">
         <v>46058</v>
       </c>
@@ -12199,7 +12280,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:25">
       <c r="A33" s="12">
         <v>46058</v>
       </c>
@@ -12276,7 +12357,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:25">
       <c r="A34" s="12">
         <v>46059</v>
       </c>
@@ -12353,7 +12434,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:25">
       <c r="A35" s="12">
         <v>46059</v>
       </c>
@@ -12430,7 +12511,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:25">
       <c r="A36" s="12">
         <v>46059</v>
       </c>
@@ -12507,7 +12588,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:25">
       <c r="A37" s="12">
         <v>46062</v>
       </c>
@@ -12584,7 +12665,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:25">
       <c r="A38" s="12">
         <v>46062</v>
       </c>
@@ -12661,7 +12742,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:25">
       <c r="A39" s="12">
         <v>46062</v>
       </c>
@@ -12738,7 +12819,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:25">
       <c r="A40" s="12">
         <v>46063</v>
       </c>
@@ -12815,7 +12896,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:25">
       <c r="A41" s="12">
         <v>46063</v>
       </c>
@@ -12892,7 +12973,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:25">
       <c r="A42" s="12">
         <v>46063</v>
       </c>
@@ -12969,7 +13050,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:25">
       <c r="A43" s="12">
         <v>46064</v>
       </c>
@@ -13046,7 +13127,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:25">
       <c r="A44" s="12">
         <v>46064</v>
       </c>
@@ -13123,7 +13204,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:25">
       <c r="A45" s="12">
         <v>46064</v>
       </c>
@@ -13200,7 +13281,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:25">
       <c r="A46" s="12">
         <v>46065</v>
       </c>
@@ -13277,7 +13358,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:25">
       <c r="A47" s="12">
         <v>46065</v>
       </c>
@@ -13354,7 +13435,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:25">
       <c r="A48" s="12">
         <v>46065</v>
       </c>
@@ -13431,7 +13512,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:25">
       <c r="A49" s="12">
         <v>46066</v>
       </c>
@@ -13508,7 +13589,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:25">
       <c r="A50" s="12">
         <v>46066</v>
       </c>
@@ -13585,7 +13666,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:25">
       <c r="A51" s="12">
         <v>46066</v>
       </c>
@@ -13662,7 +13743,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:25">
       <c r="A52" s="12">
         <v>46076</v>
       </c>
@@ -13739,7 +13820,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:25">
       <c r="A53" s="12">
         <v>46076</v>
       </c>
@@ -13816,7 +13897,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:25">
       <c r="A54" s="12">
         <v>46076</v>
       </c>
@@ -13893,7 +13974,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:25">
       <c r="A55" s="12">
         <v>46077</v>
       </c>
@@ -13970,7 +14051,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:25">
       <c r="A56" s="12">
         <v>46077</v>
       </c>
@@ -14047,7 +14128,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:25">
       <c r="A57" s="12">
         <v>46077</v>
       </c>
@@ -14124,7 +14205,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:25">
       <c r="A58" s="12">
         <v>46078</v>
       </c>
@@ -14201,7 +14282,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:25">
       <c r="A59" s="12">
         <v>46078</v>
       </c>
@@ -14278,7 +14359,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:25">
       <c r="A60" s="12">
         <v>46078</v>
       </c>
@@ -14355,7 +14436,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="61" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:25">
       <c r="A61" s="12">
         <v>46079</v>
       </c>
@@ -14432,7 +14513,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="62" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:25">
       <c r="A62" s="12">
         <v>46079</v>
       </c>
@@ -14509,7 +14590,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="63" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:25">
       <c r="A63" s="12">
         <v>46079</v>
       </c>
@@ -14586,7 +14667,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="64" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:25">
       <c r="A64" s="12">
         <v>46080</v>
       </c>
@@ -14663,7 +14744,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="65" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:25">
       <c r="A65" s="12">
         <v>46080</v>
       </c>
@@ -14740,7 +14821,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="66" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:25">
       <c r="A66" s="12">
         <v>46080</v>
       </c>
@@ -14817,7 +14898,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="67" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:25">
       <c r="A67" s="12">
         <v>46083</v>
       </c>
@@ -14894,7 +14975,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="68" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:25">
       <c r="A68" s="12">
         <v>46083</v>
       </c>
@@ -14971,7 +15052,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="69" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:25">
       <c r="A69" s="12">
         <v>46083</v>
       </c>
@@ -15048,7 +15129,7 @@
         <v>5.68</v>
       </c>
     </row>
-    <row r="70" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:25">
       <c r="A70" s="12">
         <v>46084</v>
       </c>
@@ -15125,7 +15206,7 @@
         <v>5.7590000000000003</v>
       </c>
     </row>
-    <row r="71" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:25">
       <c r="A71" s="12">
         <v>46084</v>
       </c>
@@ -15202,7 +15283,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="72" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:25">
       <c r="A72" s="12">
         <v>46084</v>
       </c>
@@ -15279,7 +15360,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="73" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:25">
       <c r="A73" s="12">
         <v>46085</v>
       </c>
@@ -15356,7 +15437,7 @@
         <v>5.8390000000000004</v>
       </c>
     </row>
-    <row r="74" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:25">
       <c r="A74" s="12">
         <v>46085</v>
       </c>
@@ -15433,7 +15514,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:25">
       <c r="A75" s="12">
         <v>46085</v>
       </c>
@@ -15510,7 +15591,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:25">
       <c r="A76" s="12">
         <v>46086</v>
       </c>
@@ -15587,7 +15668,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="77" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:25">
       <c r="A77" s="12">
         <v>46086</v>
       </c>
@@ -15664,7 +15745,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="78" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:25">
       <c r="A78" s="12">
         <v>46086</v>
       </c>
@@ -15741,7 +15822,7 @@
         <v>5.9210000000000003</v>
       </c>
     </row>
-    <row r="79" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:25">
       <c r="A79" s="12">
         <v>46087</v>
       </c>
@@ -15818,7 +15899,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="80" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:25">
       <c r="A80" s="12">
         <v>46087</v>
       </c>
@@ -15895,7 +15976,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="81" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:25">
       <c r="A81" s="12">
         <v>46087</v>
       </c>
@@ -15972,7 +16053,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="82" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:25">
       <c r="A82" s="12">
         <v>46090</v>
       </c>
@@ -16049,7 +16130,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="83" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:25">
       <c r="A83" s="12">
         <v>46090</v>
       </c>
@@ -16126,7 +16207,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="84" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:25">
       <c r="A84" s="12">
         <v>46090</v>
       </c>
@@ -16203,7 +16284,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="85" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:25">
       <c r="A85" s="12">
         <v>46091</v>
       </c>
@@ -16280,7 +16361,7 @@
         <v>6.157</v>
       </c>
     </row>
-    <row r="86" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:25">
       <c r="A86" s="12">
         <v>46091</v>
       </c>
@@ -16357,7 +16438,7 @@
         <v>6.181</v>
       </c>
     </row>
-    <row r="87" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:25">
       <c r="A87" s="12">
         <v>46091</v>
       </c>
@@ -16434,7 +16515,7 @@
         <v>6.181</v>
       </c>
     </row>
-    <row r="88" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:25">
       <c r="A88" s="12">
         <v>46092</v>
       </c>
@@ -16511,7 +16592,7 @@
         <v>6.2430000000000003</v>
       </c>
     </row>
-    <row r="89" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:25">
       <c r="A89" s="12">
         <v>46092</v>
       </c>
@@ -16588,7 +16669,7 @@
         <v>6.29</v>
       </c>
     </row>
-    <row r="90" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:25">
       <c r="A90" s="12">
         <v>46092</v>
       </c>
@@ -16665,7 +16746,7 @@
         <v>6.3049999999999997</v>
       </c>
     </row>
-    <row r="91" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:25">
       <c r="A91" s="12">
         <v>46093</v>
       </c>
@@ -16742,7 +16823,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="92" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:25">
       <c r="A92" s="12">
         <v>46093</v>
       </c>
@@ -16819,7 +16900,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="93" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:25">
       <c r="A93" s="12">
         <v>46093</v>
       </c>
@@ -16896,7 +16977,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="94" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:25">
       <c r="A94" s="12">
         <v>46094</v>
       </c>
@@ -16973,7 +17054,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="95" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:25">
       <c r="A95" s="12">
         <v>46094</v>
       </c>
@@ -17050,7 +17131,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="96" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:25">
       <c r="A96" s="12">
         <v>46094</v>
       </c>
@@ -17127,7 +17208,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="97" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:25">
       <c r="A97" s="12">
         <v>46097</v>
       </c>
@@ -17204,7 +17285,7 @@
         <v>6.5330000000000004</v>
       </c>
     </row>
-    <row r="98" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:25">
       <c r="A98" s="12">
         <v>46097</v>
       </c>
@@ -17281,7 +17362,7 @@
         <v>6.5119999999999996</v>
       </c>
     </row>
-    <row r="99" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:25">
       <c r="A99" s="12">
         <v>46097</v>
       </c>
@@ -17358,7 +17439,7 @@
         <v>6.5119999999999996</v>
       </c>
     </row>
-    <row r="100" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:25">
       <c r="A100" s="12">
         <v>46098</v>
       </c>
@@ -17435,7 +17516,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="101" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:25">
       <c r="A101" s="12">
         <v>46098</v>
       </c>
@@ -17512,7 +17593,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="102" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:25">
       <c r="A102" s="12">
         <v>46098</v>
       </c>
@@ -17589,7 +17670,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="103" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:25">
       <c r="A103" s="12">
         <v>46099</v>
       </c>
@@ -17666,7 +17747,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="104" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:25">
       <c r="A104" s="12">
         <v>46099</v>
       </c>
@@ -17743,7 +17824,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="105" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:25">
       <c r="A105" s="12">
         <v>46099</v>
       </c>
@@ -17820,7 +17901,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="106" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:25">
       <c r="A106" s="12">
         <v>46100</v>
       </c>
@@ -17897,7 +17978,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="107" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:25">
       <c r="A107" s="12">
         <v>46100</v>
       </c>
@@ -17974,7 +18055,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="108" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:25">
       <c r="A108" s="12">
         <v>46100</v>
       </c>
@@ -18051,7 +18132,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="109" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:25">
       <c r="A109" s="12">
         <v>46101</v>
       </c>
@@ -18128,7 +18209,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="110" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:25">
       <c r="A110" s="12">
         <v>46101</v>
       </c>
@@ -18205,7 +18286,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="111" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:25">
       <c r="A111" s="12">
         <v>46101</v>
       </c>
@@ -18282,7 +18363,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="112" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:25">
       <c r="A112" s="12">
         <v>46104</v>
       </c>
@@ -18359,7 +18440,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="113" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:25">
       <c r="A113" s="12">
         <v>46104</v>
       </c>
@@ -18436,7 +18517,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="114" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:25">
       <c r="A114" s="12">
         <v>46104</v>
       </c>
@@ -18513,7 +18594,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="115" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:25">
       <c r="A115" s="12">
         <v>46105</v>
       </c>
@@ -18590,7 +18671,7 @@
         <v>7.0250000000000004</v>
       </c>
     </row>
-    <row r="116" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:25">
       <c r="A116" s="12">
         <v>46105</v>
       </c>
@@ -18667,7 +18748,7 @@
         <v>7.125</v>
       </c>
     </row>
-    <row r="117" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:25">
       <c r="A117" s="12">
         <v>46105</v>
       </c>
@@ -18744,7 +18825,7 @@
         <v>7.125</v>
       </c>
     </row>
-    <row r="118" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:25">
       <c r="A118" s="12">
         <v>46106</v>
       </c>
@@ -18821,7 +18902,7 @@
         <v>7.15</v>
       </c>
     </row>
-    <row r="119" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:25">
       <c r="A119" s="12">
         <v>46106</v>
       </c>
@@ -18898,7 +18979,7 @@
         <v>7.2249999999999996</v>
       </c>
     </row>
-    <row r="120" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:25">
       <c r="A120" s="12">
         <v>46106</v>
       </c>
@@ -18975,7 +19056,7 @@
         <v>7.2249999999999996</v>
       </c>
     </row>
-    <row r="121" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:25">
       <c r="A121" s="12">
         <v>46107</v>
       </c>
@@ -19052,7 +19133,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="122" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:25">
       <c r="A122" s="12">
         <v>46107</v>
       </c>
@@ -19129,7 +19210,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="123" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:25">
       <c r="A123" s="12">
         <v>46107</v>
       </c>
@@ -19206,7 +19287,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="124" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:25">
       <c r="A124" s="12">
         <v>46108</v>
       </c>
@@ -19283,7 +19364,7 @@
         <v>7.375</v>
       </c>
     </row>
-    <row r="125" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:25">
       <c r="A125" s="12">
         <v>46108</v>
       </c>
@@ -19360,7 +19441,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="126" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:25">
       <c r="A126" s="12">
         <v>46108</v>
       </c>
@@ -19437,7 +19518,7 @@
         <v>7.375</v>
       </c>
     </row>
-    <row r="127" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:25">
       <c r="A127" s="12">
         <v>46111</v>
       </c>
@@ -19514,7 +19595,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="128" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:25">
       <c r="A128" s="12">
         <v>46111</v>
       </c>
@@ -19591,7 +19672,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="129" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:25">
       <c r="A129" s="12">
         <v>46111</v>
       </c>
@@ -19668,7 +19749,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="130" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:25">
       <c r="A130" s="12">
         <v>46112</v>
       </c>
@@ -19745,7 +19826,7 @@
         <v>7.5250000000000004</v>
       </c>
     </row>
-    <row r="131" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:25">
       <c r="A131" s="12">
         <v>46112</v>
       </c>
@@ -19822,7 +19903,7 @@
         <v>7.5250000000000004</v>
       </c>
     </row>
-    <row r="132" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:25">
       <c r="A132" s="12">
         <v>46112</v>
       </c>
@@ -19899,7 +19980,7 @@
         <v>7.55</v>
       </c>
     </row>
-    <row r="133" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:25">
       <c r="A133" s="12">
         <v>46113</v>
       </c>
@@ -19976,7 +20057,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="134" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:25">
       <c r="A134" s="12">
         <v>46113</v>
       </c>
@@ -20053,7 +20134,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="135" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:25">
       <c r="A135" s="12">
         <v>46113</v>
       </c>
@@ -20130,7 +20211,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="136" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:25">
       <c r="A136" s="12">
         <v>46114</v>
       </c>
@@ -20207,7 +20288,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="137" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:25">
       <c r="A137" s="12">
         <v>46114</v>
       </c>
@@ -20284,7 +20365,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="138" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:25">
       <c r="A138" s="12">
         <v>46114</v>
       </c>
@@ -20295,6 +20376,111 @@
         <v>0.75694444444444453</v>
       </c>
       <c r="D138" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E138" s="11">
+        <v>48</v>
+      </c>
+      <c r="F138" s="11">
+        <v>25.8</v>
+      </c>
+      <c r="G138" s="11">
+        <v>37</v>
+      </c>
+      <c r="H138" s="11">
+        <v>23.8</v>
+      </c>
+      <c r="I138" s="11">
+        <v>20.6</v>
+      </c>
+      <c r="J138" s="11">
+        <v>21.3</v>
+      </c>
+      <c r="K138" s="11">
+        <v>90</v>
+      </c>
+      <c r="L138" s="11">
+        <v>26.2</v>
+      </c>
+      <c r="M138" s="11">
+        <v>73.317999999999998</v>
+      </c>
+      <c r="N138" s="11">
+        <v>15</v>
+      </c>
+      <c r="O138" s="11">
+        <v>13</v>
+      </c>
+      <c r="P138" s="11">
+        <v>13.55</v>
+      </c>
+      <c r="Q138" s="11">
+        <v>48.5</v>
+      </c>
+      <c r="R138" s="11">
+        <v>12</v>
+      </c>
+      <c r="S138" s="11">
+        <v>33.659999999999997</v>
+      </c>
+      <c r="T138" s="11">
+        <v>7.95</v>
+      </c>
+      <c r="U138" s="11">
+        <v>5.6</v>
+      </c>
+      <c r="V138" s="11">
+        <v>6.766</v>
+      </c>
+      <c r="W138" s="11">
+        <v>9.65</v>
+      </c>
+      <c r="X138" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="Y138" s="11">
+        <v>7.625</v>
+      </c>
+    </row>
+    <row r="139" spans="1:25">
+      <c r="A139" s="12">
+        <v>46115</v>
+      </c>
+      <c r="B139" s="12">
+        <v>46115</v>
+      </c>
+      <c r="C139" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D139" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="140" spans="1:25">
+      <c r="A140" s="12">
+        <v>46115</v>
+      </c>
+      <c r="B140" s="12">
+        <v>46115</v>
+      </c>
+      <c r="C140" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D140" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="141" spans="1:25">
+      <c r="A141" s="12">
+        <v>46115</v>
+      </c>
+      <c r="B141" s="12">
+        <v>46115</v>
+      </c>
+      <c r="C141" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D141" s="7" t="s">
         <v>53</v>
       </c>
     </row>
@@ -20314,17 +20500,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3E2CD10-06F7-40BE-85D8-E29219BBD9A9}">
   <dimension ref="A1:AK5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.36328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:37" s="5" customFormat="1">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -20413,7 +20599,7 @@
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:37">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -20494,7 +20680,7 @@
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:37">
       <c r="A3" s="6">
         <v>45962</v>
       </c>
@@ -20583,7 +20769,7 @@
       <c r="AJ3" s="2"/>
       <c r="AK3" s="2"/>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:37">
       <c r="A4" s="6">
         <v>45992</v>
       </c>
@@ -20672,7 +20858,7 @@
       <c r="AJ4" s="2"/>
       <c r="AK4" s="2"/>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37">
       <c r="A5" s="6"/>
       <c r="B5" s="6"/>
     </row>
@@ -20691,24 +20877,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3556165B-22F0-4AF5-853E-ED25EB5C0B71}">
   <dimension ref="A1:Y11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.125" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="14"/>
-    <col min="7" max="7" width="9.125" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.453125" style="14" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="14"/>
-    <col min="10" max="10" width="9.125" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="9" style="14"/>
-    <col min="13" max="13" width="9.125" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="5" customFormat="1">
       <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
@@ -20761,7 +20947,7 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -20806,7 +20992,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -20859,7 +21045,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -20912,7 +21098,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -20953,7 +21139,7 @@
         <v>118.333</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -20994,7 +21180,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -21035,7 +21221,7 @@
         <v>122.667</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25">
       <c r="A8" s="12">
         <v>46083</v>
       </c>
@@ -21076,7 +21262,7 @@
         <v>123.333</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25">
       <c r="A9" s="12">
         <v>46090</v>
       </c>
@@ -21117,7 +21303,7 @@
         <v>126.667</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25">
       <c r="A10" s="12">
         <v>46097</v>
       </c>
@@ -21158,7 +21344,7 @@
         <v>132.333</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25">
       <c r="A11" s="12">
         <v>46104</v>
       </c>
@@ -21215,18 +21401,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C550C51-95E6-4243-AC05-025707E45857}">
   <dimension ref="A1:Y11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.625" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.6328125" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="5" customFormat="1">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -21273,7 +21459,7 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -21312,7 +21498,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -21359,7 +21545,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -21406,7 +21592,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -21438,7 +21624,7 @@
         <v>9.6539999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -21470,7 +21656,7 @@
         <v>9.8650000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -21502,7 +21688,7 @@
         <v>10.221</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25">
       <c r="A8" s="12">
         <v>46083</v>
       </c>
@@ -21534,7 +21720,7 @@
         <v>10.721</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25">
       <c r="A9" s="12">
         <v>46090</v>
       </c>
@@ -21566,7 +21752,7 @@
         <v>11.462</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25">
       <c r="A10" s="12">
         <v>46097</v>
       </c>
@@ -21598,7 +21784,7 @@
         <v>11.962</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25">
       <c r="A11" s="12">
         <v>46104</v>
       </c>
@@ -21645,7 +21831,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BD8F7D3-2DB0-479E-83DC-4D765C588609}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="16384" width="9" style="3"/>
   </cols>
@@ -21659,15 +21845,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="22.875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.875" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.90625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.90625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.6328125" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>48</v>
       </c>
@@ -21678,7 +21864,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
@@ -21692,7 +21878,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="s">
         <v>29</v>
@@ -21701,7 +21887,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>31</v>
@@ -21710,7 +21896,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
         <v>33</v>
@@ -21719,7 +21905,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4">
       <c r="A6" s="1"/>
       <c r="B6" s="2" t="s">
         <v>35</v>
@@ -21728,7 +21914,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
         <v>37</v>
@@ -21737,7 +21923,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
         <v>39</v>
@@ -21746,7 +21932,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
         <v>41</v>
       </c>
@@ -21755,49 +21941,49 @@
       </c>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4">
       <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4">
       <c r="A12" s="1"/>
       <c r="B12" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4">
       <c r="A14" s="1"/>
       <c r="B14" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4">
       <c r="A15" s="1"/>
       <c r="B15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4">
       <c r="A16" s="1" t="s">
         <v>42</v>
       </c>
@@ -21808,7 +21994,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3">
       <c r="A17" s="1"/>
       <c r="B17" s="2" t="s">
         <v>8</v>
@@ -21817,7 +22003,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3">
       <c r="A18" s="1"/>
       <c r="B18" s="2" t="s">
         <v>9</v>
@@ -21826,7 +22012,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3">
       <c r="A19" s="1" t="s">
         <v>44</v>
       </c>
@@ -21837,7 +22023,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3">
       <c r="A20" s="1"/>
       <c r="B20" s="2" t="s">
         <v>11</v>
@@ -21846,7 +22032,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3">
       <c r="A21" s="1" t="s">
         <v>45</v>
       </c>
@@ -21855,42 +22041,42 @@
       </c>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3">
       <c r="A22" s="1"/>
       <c r="B22" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3">
       <c r="A23" s="1"/>
       <c r="B23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3">
       <c r="A24" s="1"/>
       <c r="B24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3">
       <c r="A25" s="1"/>
       <c r="B25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3">
       <c r="A26" s="1"/>
       <c r="B26" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3">
       <c r="A27" s="1" t="s">
         <v>46</v>
       </c>
@@ -21899,35 +22085,35 @@
       </c>
       <c r="C27" s="2"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3">
       <c r="A28" s="1"/>
       <c r="B28" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C28" s="2"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3">
       <c r="A29" s="1"/>
       <c r="B29" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C29" s="2"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3">
       <c r="A30" s="1"/>
       <c r="B30" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C30" s="2"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3">
       <c r="A31" s="1"/>
       <c r="B31" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C31" s="2"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3">
       <c r="A32" s="1"/>
       <c r="B32" s="2" t="s">
         <v>23</v>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm12\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99837A0A-F2D0-48AC-92BA-47F53B3E84B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDE37BA9-FA98-4236-B7BE-D8705C46B5AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-5790" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -25,12 +25,24 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -244,23 +256,23 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -273,7 +285,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -316,7 +328,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -337,36 +349,36 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -384,7 +396,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -853,6 +865,15 @@
                 <c:pt idx="138">
                   <c:v>46115</c:v>
                 </c:pt>
+                <c:pt idx="139">
+                  <c:v>46119</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>46119</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>46119</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1277,6 +1298,12 @@
                   <c:v>37</c:v>
                 </c:pt>
                 <c:pt idx="138">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="140">
                   <c:v>37</c:v>
                 </c:pt>
               </c:numCache>
@@ -1741,6 +1768,15 @@
                 <c:pt idx="138">
                   <c:v>46115</c:v>
                 </c:pt>
+                <c:pt idx="139">
+                  <c:v>46119</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>46119</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>46119</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2165,6 +2201,12 @@
                   <c:v>21.3</c:v>
                 </c:pt>
                 <c:pt idx="138">
+                  <c:v>21.25</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>21.25</c:v>
+                </c:pt>
+                <c:pt idx="140">
                   <c:v>21.25</c:v>
                 </c:pt>
               </c:numCache>
@@ -2629,6 +2671,15 @@
                 <c:pt idx="138">
                   <c:v>46115</c:v>
                 </c:pt>
+                <c:pt idx="139">
+                  <c:v>46119</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>46119</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>46119</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3054,6 +3105,12 @@
                 </c:pt>
                 <c:pt idx="138">
                   <c:v>73.090999999999994</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>73.090999999999994</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>73.036000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3517,6 +3574,15 @@
                 <c:pt idx="138">
                   <c:v>46115</c:v>
                 </c:pt>
+                <c:pt idx="139">
+                  <c:v>46119</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>46119</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>46119</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3941,6 +4007,12 @@
                   <c:v>13.55</c:v>
                 </c:pt>
                 <c:pt idx="138">
+                  <c:v>13.55</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>13.55</c:v>
+                </c:pt>
+                <c:pt idx="140">
                   <c:v>13.55</c:v>
                 </c:pt>
               </c:numCache>
@@ -4405,6 +4477,15 @@
                 <c:pt idx="138">
                   <c:v>46115</c:v>
                 </c:pt>
+                <c:pt idx="139">
+                  <c:v>46119</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>46119</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>46119</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4830,6 +4911,12 @@
                 </c:pt>
                 <c:pt idx="138">
                   <c:v>33.6</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>33.6</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>33.56</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5309,6 +5396,15 @@
                 <c:pt idx="138">
                   <c:v>46115</c:v>
                 </c:pt>
+                <c:pt idx="139">
+                  <c:v>46119</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>46119</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>46119</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5734,6 +5830,12 @@
                 </c:pt>
                 <c:pt idx="138">
                   <c:v>6.73</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>6.72</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>6.72</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6199,6 +6301,15 @@
                 <c:pt idx="138">
                   <c:v>46115</c:v>
                 </c:pt>
+                <c:pt idx="139">
+                  <c:v>46119</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>46119</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>46119</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6623,6 +6734,12 @@
                   <c:v>7.7</c:v>
                 </c:pt>
                 <c:pt idx="138">
+                  <c:v>7.7</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>7.7</c:v>
+                </c:pt>
+                <c:pt idx="140">
                   <c:v>7.7</c:v>
                 </c:pt>
               </c:numCache>
@@ -6858,7 +6975,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -6866,6 +6982,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6901,7 +7018,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6949,10 +7066,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Module!$B$3:$B$9</c:f>
+              <c:f>Module!$B$3:$B$1119</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="1117"/>
                 <c:pt idx="0">
                   <c:v>46048</c:v>
                 </c:pt>
@@ -6973,16 +7090,25 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46104</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46111</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46118</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Module!$G$3:$G$9</c:f>
+              <c:f>Module!$G$3:$G$1119</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="1117"/>
                 <c:pt idx="0">
                   <c:v>177.5</c:v>
                 </c:pt>
@@ -7003,6 +7129,15 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>230</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>232.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>232.5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>242.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7045,10 +7180,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Module!$B$3:$B$9</c:f>
+              <c:f>Module!$B$3:$B$1119</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="1117"/>
                 <c:pt idx="0">
                   <c:v>46048</c:v>
                 </c:pt>
@@ -7069,16 +7204,25 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46104</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46111</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46118</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Module!$J$3:$J$9</c:f>
+              <c:f>Module!$J$3:$J$1119</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="1117"/>
                 <c:pt idx="0">
                   <c:v>545</c:v>
                 </c:pt>
@@ -7099,6 +7243,15 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>910</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>917.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>925</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>935</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7141,10 +7294,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Module!$B$3:$B$9</c:f>
+              <c:f>Module!$B$3:$B$1119</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="1117"/>
                 <c:pt idx="0">
                   <c:v>46048</c:v>
                 </c:pt>
@@ -7165,16 +7318,25 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46104</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46111</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46118</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Module!$M$3:$M$9</c:f>
+              <c:f>Module!$M$3:$M$1119</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="1117"/>
                 <c:pt idx="0">
                   <c:v>94</c:v>
                 </c:pt>
@@ -7195,6 +7357,15 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>126.667</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>132.333</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>143.333</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>150</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7368,7 +7539,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -7376,6 +7546,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -7411,7 +7582,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7459,10 +7630,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>GDDR!$B$3:$B$9</c:f>
+              <c:f>GDDR!$B$3:$B$1119</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="1117"/>
                 <c:pt idx="0">
                   <c:v>46048</c:v>
                 </c:pt>
@@ -7483,16 +7654,25 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46104</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46111</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46118</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>GDDR!$G$3:$G$9</c:f>
+              <c:f>GDDR!$G$3:$G$1119</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="1117"/>
                 <c:pt idx="0">
                   <c:v>7.0910000000000002</c:v>
                 </c:pt>
@@ -7513,6 +7693,15 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>11.182</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>11.682</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>12.727</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>12.526999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7555,10 +7744,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>GDDR!$B$3:$B$9</c:f>
+              <c:f>GDDR!$B$3:$B$1119</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="1117"/>
                 <c:pt idx="0">
                   <c:v>46048</c:v>
                 </c:pt>
@@ -7579,16 +7768,25 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46104</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46111</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46118</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>GDDR!$J$3:$J$9</c:f>
+              <c:f>GDDR!$J$3:$J$1119</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="1117"/>
                 <c:pt idx="0">
                   <c:v>7.1539999999999999</c:v>
                 </c:pt>
@@ -7609,6 +7807,15 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>11.462</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>11.962</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>12.865</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>12.71</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7783,7 +7990,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -7791,6 +7997,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -9876,28 +10083,28 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y141"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:Y144"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.26953125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.125" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.25" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="15" t="s">
         <v>50</v>
       </c>
       <c r="C1" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="17" t="s">
         <v>52</v>
       </c>
       <c r="E1" s="9" t="s">
@@ -9964,11 +10171,11 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A2" s="15"/>
+      <c r="B2" s="15"/>
       <c r="C2" s="16"/>
-      <c r="D2" s="15"/>
+      <c r="D2" s="17"/>
       <c r="E2" s="10" t="s">
         <v>54</v>
       </c>
@@ -10033,7 +10240,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>46044</v>
       </c>
@@ -10110,7 +10317,7 @@
         <v>4.9450000000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>46045</v>
       </c>
@@ -10187,7 +10394,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <v>46045</v>
       </c>
@@ -10264,7 +10471,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
         <v>46045</v>
       </c>
@@ -10341,7 +10548,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
         <v>46048</v>
       </c>
@@ -10418,7 +10625,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="12">
         <v>46048</v>
       </c>
@@ -10495,7 +10702,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="12">
         <v>46048</v>
       </c>
@@ -10572,7 +10779,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="12">
         <v>46049</v>
       </c>
@@ -10649,7 +10856,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="12">
         <v>46049</v>
       </c>
@@ -10726,7 +10933,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" s="12">
         <v>46049</v>
       </c>
@@ -10803,7 +11010,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" s="12">
         <v>46050</v>
       </c>
@@ -10880,7 +11087,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A14" s="12">
         <v>46050</v>
       </c>
@@ -10957,7 +11164,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A15" s="12">
         <v>46050</v>
       </c>
@@ -11034,7 +11241,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="16" spans="1:25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A16" s="12">
         <v>46051</v>
       </c>
@@ -11111,7 +11318,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:25">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A17" s="12">
         <v>46051</v>
       </c>
@@ -11188,7 +11395,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:25">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A18" s="12">
         <v>46051</v>
       </c>
@@ -11265,7 +11472,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:25">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A19" s="12">
         <v>46052</v>
       </c>
@@ -11342,7 +11549,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="20" spans="1:25">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A20" s="12">
         <v>46052</v>
       </c>
@@ -11419,7 +11626,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="21" spans="1:25">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A21" s="12">
         <v>46052</v>
       </c>
@@ -11496,7 +11703,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="22" spans="1:25">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A22" s="12">
         <v>46055</v>
       </c>
@@ -11573,7 +11780,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="23" spans="1:25">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A23" s="12">
         <v>46055</v>
       </c>
@@ -11650,7 +11857,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="24" spans="1:25">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A24" s="12">
         <v>46055</v>
       </c>
@@ -11727,7 +11934,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="25" spans="1:25">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A25" s="12">
         <v>46056</v>
       </c>
@@ -11804,7 +12011,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="26" spans="1:25">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A26" s="12">
         <v>46056</v>
       </c>
@@ -11881,7 +12088,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="27" spans="1:25">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A27" s="12">
         <v>46056</v>
       </c>
@@ -11958,7 +12165,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="28" spans="1:25">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A28" s="12">
         <v>46057</v>
       </c>
@@ -12035,7 +12242,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="29" spans="1:25">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A29" s="12">
         <v>46057</v>
       </c>
@@ -12112,7 +12319,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="30" spans="1:25">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A30" s="12">
         <v>46057</v>
       </c>
@@ -12189,7 +12396,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="31" spans="1:25">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A31" s="12">
         <v>46058</v>
       </c>
@@ -12266,7 +12473,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="32" spans="1:25">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A32" s="12">
         <v>46058</v>
       </c>
@@ -12343,7 +12550,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="33" spans="1:25">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A33" s="12">
         <v>46058</v>
       </c>
@@ -12420,7 +12627,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="34" spans="1:25">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A34" s="12">
         <v>46059</v>
       </c>
@@ -12497,7 +12704,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:25">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A35" s="12">
         <v>46059</v>
       </c>
@@ -12574,7 +12781,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:25">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A36" s="12">
         <v>46059</v>
       </c>
@@ -12651,7 +12858,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:25">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A37" s="12">
         <v>46062</v>
       </c>
@@ -12728,7 +12935,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="38" spans="1:25">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A38" s="12">
         <v>46062</v>
       </c>
@@ -12805,7 +13012,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="39" spans="1:25">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A39" s="12">
         <v>46062</v>
       </c>
@@ -12882,7 +13089,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="40" spans="1:25">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A40" s="12">
         <v>46063</v>
       </c>
@@ -12959,7 +13166,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="41" spans="1:25">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A41" s="12">
         <v>46063</v>
       </c>
@@ -13036,7 +13243,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="42" spans="1:25">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A42" s="12">
         <v>46063</v>
       </c>
@@ -13113,7 +13320,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="43" spans="1:25">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A43" s="12">
         <v>46064</v>
       </c>
@@ -13190,7 +13397,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="44" spans="1:25">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A44" s="12">
         <v>46064</v>
       </c>
@@ -13267,7 +13474,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="45" spans="1:25">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A45" s="12">
         <v>46064</v>
       </c>
@@ -13344,7 +13551,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="46" spans="1:25">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A46" s="12">
         <v>46065</v>
       </c>
@@ -13421,7 +13628,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:25">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A47" s="12">
         <v>46065</v>
       </c>
@@ -13498,7 +13705,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:25">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A48" s="12">
         <v>46065</v>
       </c>
@@ -13575,7 +13782,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="49" spans="1:25">
+    <row r="49" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A49" s="12">
         <v>46066</v>
       </c>
@@ -13652,7 +13859,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:25">
+    <row r="50" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A50" s="12">
         <v>46066</v>
       </c>
@@ -13729,7 +13936,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:25">
+    <row r="51" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A51" s="12">
         <v>46066</v>
       </c>
@@ -13806,7 +14013,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:25">
+    <row r="52" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A52" s="12">
         <v>46076</v>
       </c>
@@ -13883,7 +14090,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="53" spans="1:25">
+    <row r="53" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A53" s="12">
         <v>46076</v>
       </c>
@@ -13960,7 +14167,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:25">
+    <row r="54" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A54" s="12">
         <v>46076</v>
       </c>
@@ -14037,7 +14244,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="55" spans="1:25">
+    <row r="55" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A55" s="12">
         <v>46077</v>
       </c>
@@ -14114,7 +14321,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="56" spans="1:25">
+    <row r="56" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A56" s="12">
         <v>46077</v>
       </c>
@@ -14191,7 +14398,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="57" spans="1:25">
+    <row r="57" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A57" s="12">
         <v>46077</v>
       </c>
@@ -14268,7 +14475,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="58" spans="1:25">
+    <row r="58" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A58" s="12">
         <v>46078</v>
       </c>
@@ -14345,7 +14552,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="59" spans="1:25">
+    <row r="59" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A59" s="12">
         <v>46078</v>
       </c>
@@ -14422,7 +14629,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="60" spans="1:25">
+    <row r="60" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A60" s="12">
         <v>46078</v>
       </c>
@@ -14499,7 +14706,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="61" spans="1:25">
+    <row r="61" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A61" s="12">
         <v>46079</v>
       </c>
@@ -14576,7 +14783,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="62" spans="1:25">
+    <row r="62" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A62" s="12">
         <v>46079</v>
       </c>
@@ -14653,7 +14860,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="63" spans="1:25">
+    <row r="63" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A63" s="12">
         <v>46079</v>
       </c>
@@ -14730,7 +14937,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="64" spans="1:25">
+    <row r="64" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A64" s="12">
         <v>46080</v>
       </c>
@@ -14807,7 +15014,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="65" spans="1:25">
+    <row r="65" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A65" s="12">
         <v>46080</v>
       </c>
@@ -14884,7 +15091,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="66" spans="1:25">
+    <row r="66" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A66" s="12">
         <v>46080</v>
       </c>
@@ -14961,7 +15168,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="67" spans="1:25">
+    <row r="67" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A67" s="12">
         <v>46083</v>
       </c>
@@ -15038,7 +15245,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="68" spans="1:25">
+    <row r="68" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A68" s="12">
         <v>46083</v>
       </c>
@@ -15115,7 +15322,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="69" spans="1:25">
+    <row r="69" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A69" s="12">
         <v>46083</v>
       </c>
@@ -15192,7 +15399,7 @@
         <v>5.68</v>
       </c>
     </row>
-    <row r="70" spans="1:25">
+    <row r="70" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A70" s="12">
         <v>46084</v>
       </c>
@@ -15269,7 +15476,7 @@
         <v>5.7590000000000003</v>
       </c>
     </row>
-    <row r="71" spans="1:25">
+    <row r="71" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A71" s="12">
         <v>46084</v>
       </c>
@@ -15346,7 +15553,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="72" spans="1:25">
+    <row r="72" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A72" s="12">
         <v>46084</v>
       </c>
@@ -15423,7 +15630,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="73" spans="1:25">
+    <row r="73" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A73" s="12">
         <v>46085</v>
       </c>
@@ -15500,7 +15707,7 @@
         <v>5.8390000000000004</v>
       </c>
     </row>
-    <row r="74" spans="1:25">
+    <row r="74" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A74" s="12">
         <v>46085</v>
       </c>
@@ -15577,7 +15784,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:25">
+    <row r="75" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A75" s="12">
         <v>46085</v>
       </c>
@@ -15654,7 +15861,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:25">
+    <row r="76" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A76" s="12">
         <v>46086</v>
       </c>
@@ -15731,7 +15938,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="77" spans="1:25">
+    <row r="77" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A77" s="12">
         <v>46086</v>
       </c>
@@ -15808,7 +16015,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="78" spans="1:25">
+    <row r="78" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A78" s="12">
         <v>46086</v>
       </c>
@@ -15885,7 +16092,7 @@
         <v>5.9210000000000003</v>
       </c>
     </row>
-    <row r="79" spans="1:25">
+    <row r="79" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A79" s="12">
         <v>46087</v>
       </c>
@@ -15962,7 +16169,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="80" spans="1:25">
+    <row r="80" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A80" s="12">
         <v>46087</v>
       </c>
@@ -16039,7 +16246,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="81" spans="1:25">
+    <row r="81" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A81" s="12">
         <v>46087</v>
       </c>
@@ -16116,7 +16323,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="82" spans="1:25">
+    <row r="82" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A82" s="12">
         <v>46090</v>
       </c>
@@ -16193,7 +16400,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="83" spans="1:25">
+    <row r="83" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A83" s="12">
         <v>46090</v>
       </c>
@@ -16270,7 +16477,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="84" spans="1:25">
+    <row r="84" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A84" s="12">
         <v>46090</v>
       </c>
@@ -16347,7 +16554,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="85" spans="1:25">
+    <row r="85" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A85" s="12">
         <v>46091</v>
       </c>
@@ -16424,7 +16631,7 @@
         <v>6.157</v>
       </c>
     </row>
-    <row r="86" spans="1:25">
+    <row r="86" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A86" s="12">
         <v>46091</v>
       </c>
@@ -16501,7 +16708,7 @@
         <v>6.181</v>
       </c>
     </row>
-    <row r="87" spans="1:25">
+    <row r="87" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A87" s="12">
         <v>46091</v>
       </c>
@@ -16578,7 +16785,7 @@
         <v>6.181</v>
       </c>
     </row>
-    <row r="88" spans="1:25">
+    <row r="88" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A88" s="12">
         <v>46092</v>
       </c>
@@ -16655,7 +16862,7 @@
         <v>6.2430000000000003</v>
       </c>
     </row>
-    <row r="89" spans="1:25">
+    <row r="89" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A89" s="12">
         <v>46092</v>
       </c>
@@ -16732,7 +16939,7 @@
         <v>6.29</v>
       </c>
     </row>
-    <row r="90" spans="1:25">
+    <row r="90" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A90" s="12">
         <v>46092</v>
       </c>
@@ -16809,7 +17016,7 @@
         <v>6.3049999999999997</v>
       </c>
     </row>
-    <row r="91" spans="1:25">
+    <row r="91" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A91" s="12">
         <v>46093</v>
       </c>
@@ -16886,7 +17093,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="92" spans="1:25">
+    <row r="92" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A92" s="12">
         <v>46093</v>
       </c>
@@ -16963,7 +17170,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="93" spans="1:25">
+    <row r="93" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A93" s="12">
         <v>46093</v>
       </c>
@@ -17040,7 +17247,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="94" spans="1:25">
+    <row r="94" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A94" s="12">
         <v>46094</v>
       </c>
@@ -17117,7 +17324,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="95" spans="1:25">
+    <row r="95" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A95" s="12">
         <v>46094</v>
       </c>
@@ -17194,7 +17401,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="96" spans="1:25">
+    <row r="96" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A96" s="12">
         <v>46094</v>
       </c>
@@ -17271,7 +17478,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="97" spans="1:25">
+    <row r="97" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A97" s="12">
         <v>46097</v>
       </c>
@@ -17348,7 +17555,7 @@
         <v>6.5330000000000004</v>
       </c>
     </row>
-    <row r="98" spans="1:25">
+    <row r="98" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A98" s="12">
         <v>46097</v>
       </c>
@@ -17425,7 +17632,7 @@
         <v>6.5119999999999996</v>
       </c>
     </row>
-    <row r="99" spans="1:25">
+    <row r="99" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A99" s="12">
         <v>46097</v>
       </c>
@@ -17502,7 +17709,7 @@
         <v>6.5119999999999996</v>
       </c>
     </row>
-    <row r="100" spans="1:25">
+    <row r="100" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A100" s="12">
         <v>46098</v>
       </c>
@@ -17579,7 +17786,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="101" spans="1:25">
+    <row r="101" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A101" s="12">
         <v>46098</v>
       </c>
@@ -17656,7 +17863,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="102" spans="1:25">
+    <row r="102" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A102" s="12">
         <v>46098</v>
       </c>
@@ -17733,7 +17940,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="103" spans="1:25">
+    <row r="103" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A103" s="12">
         <v>46099</v>
       </c>
@@ -17810,7 +18017,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="104" spans="1:25">
+    <row r="104" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A104" s="12">
         <v>46099</v>
       </c>
@@ -17887,7 +18094,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="105" spans="1:25">
+    <row r="105" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A105" s="12">
         <v>46099</v>
       </c>
@@ -17964,7 +18171,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="106" spans="1:25">
+    <row r="106" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A106" s="12">
         <v>46100</v>
       </c>
@@ -18041,7 +18248,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="107" spans="1:25">
+    <row r="107" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A107" s="12">
         <v>46100</v>
       </c>
@@ -18118,7 +18325,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="108" spans="1:25">
+    <row r="108" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A108" s="12">
         <v>46100</v>
       </c>
@@ -18195,7 +18402,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="109" spans="1:25">
+    <row r="109" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A109" s="12">
         <v>46101</v>
       </c>
@@ -18272,7 +18479,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="110" spans="1:25">
+    <row r="110" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A110" s="12">
         <v>46101</v>
       </c>
@@ -18349,7 +18556,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="111" spans="1:25">
+    <row r="111" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A111" s="12">
         <v>46101</v>
       </c>
@@ -18426,7 +18633,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="112" spans="1:25">
+    <row r="112" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A112" s="12">
         <v>46104</v>
       </c>
@@ -18503,7 +18710,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="113" spans="1:25">
+    <row r="113" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A113" s="12">
         <v>46104</v>
       </c>
@@ -18580,7 +18787,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="114" spans="1:25">
+    <row r="114" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A114" s="12">
         <v>46104</v>
       </c>
@@ -18657,7 +18864,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="115" spans="1:25">
+    <row r="115" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A115" s="12">
         <v>46105</v>
       </c>
@@ -18734,7 +18941,7 @@
         <v>7.0250000000000004</v>
       </c>
     </row>
-    <row r="116" spans="1:25">
+    <row r="116" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A116" s="12">
         <v>46105</v>
       </c>
@@ -18811,7 +19018,7 @@
         <v>7.125</v>
       </c>
     </row>
-    <row r="117" spans="1:25">
+    <row r="117" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A117" s="12">
         <v>46105</v>
       </c>
@@ -18888,7 +19095,7 @@
         <v>7.125</v>
       </c>
     </row>
-    <row r="118" spans="1:25">
+    <row r="118" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A118" s="12">
         <v>46106</v>
       </c>
@@ -18965,7 +19172,7 @@
         <v>7.15</v>
       </c>
     </row>
-    <row r="119" spans="1:25">
+    <row r="119" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A119" s="12">
         <v>46106</v>
       </c>
@@ -19042,7 +19249,7 @@
         <v>7.2249999999999996</v>
       </c>
     </row>
-    <row r="120" spans="1:25">
+    <row r="120" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A120" s="12">
         <v>46106</v>
       </c>
@@ -19119,7 +19326,7 @@
         <v>7.2249999999999996</v>
       </c>
     </row>
-    <row r="121" spans="1:25">
+    <row r="121" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A121" s="12">
         <v>46107</v>
       </c>
@@ -19196,7 +19403,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="122" spans="1:25">
+    <row r="122" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A122" s="12">
         <v>46107</v>
       </c>
@@ -19273,7 +19480,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="123" spans="1:25">
+    <row r="123" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A123" s="12">
         <v>46107</v>
       </c>
@@ -19350,7 +19557,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="124" spans="1:25">
+    <row r="124" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A124" s="12">
         <v>46108</v>
       </c>
@@ -19427,7 +19634,7 @@
         <v>7.375</v>
       </c>
     </row>
-    <row r="125" spans="1:25">
+    <row r="125" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A125" s="12">
         <v>46108</v>
       </c>
@@ -19504,7 +19711,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="126" spans="1:25">
+    <row r="126" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A126" s="12">
         <v>46108</v>
       </c>
@@ -19581,7 +19788,7 @@
         <v>7.375</v>
       </c>
     </row>
-    <row r="127" spans="1:25">
+    <row r="127" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A127" s="12">
         <v>46111</v>
       </c>
@@ -19658,7 +19865,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="128" spans="1:25">
+    <row r="128" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A128" s="12">
         <v>46111</v>
       </c>
@@ -19735,7 +19942,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="129" spans="1:25">
+    <row r="129" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A129" s="12">
         <v>46111</v>
       </c>
@@ -19812,7 +20019,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="130" spans="1:25">
+    <row r="130" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A130" s="12">
         <v>46112</v>
       </c>
@@ -19889,7 +20096,7 @@
         <v>7.5250000000000004</v>
       </c>
     </row>
-    <row r="131" spans="1:25">
+    <row r="131" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A131" s="12">
         <v>46112</v>
       </c>
@@ -19966,7 +20173,7 @@
         <v>7.5250000000000004</v>
       </c>
     </row>
-    <row r="132" spans="1:25">
+    <row r="132" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A132" s="12">
         <v>46112</v>
       </c>
@@ -20043,7 +20250,7 @@
         <v>7.55</v>
       </c>
     </row>
-    <row r="133" spans="1:25">
+    <row r="133" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A133" s="12">
         <v>46113</v>
       </c>
@@ -20120,7 +20327,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="134" spans="1:25">
+    <row r="134" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A134" s="12">
         <v>46113</v>
       </c>
@@ -20197,7 +20404,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="135" spans="1:25">
+    <row r="135" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A135" s="12">
         <v>46113</v>
       </c>
@@ -20274,7 +20481,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="136" spans="1:25">
+    <row r="136" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A136" s="12">
         <v>46114</v>
       </c>
@@ -20351,7 +20558,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="137" spans="1:25">
+    <row r="137" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A137" s="12">
         <v>46114</v>
       </c>
@@ -20428,7 +20635,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="138" spans="1:25">
+    <row r="138" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A138" s="12">
         <v>46114</v>
       </c>
@@ -20505,7 +20712,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="139" spans="1:25">
+    <row r="139" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A139" s="12">
         <v>46115</v>
       </c>
@@ -20582,7 +20789,7 @@
         <v>7.6749999999999998</v>
       </c>
     </row>
-    <row r="140" spans="1:25">
+    <row r="140" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A140" s="12">
         <v>46115</v>
       </c>
@@ -20659,7 +20866,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="141" spans="1:25">
+    <row r="141" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A141" s="12">
         <v>46115</v>
       </c>
@@ -20734,6 +20941,174 @@
       </c>
       <c r="Y141" s="11">
         <v>7.7</v>
+      </c>
+    </row>
+    <row r="142" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A142" s="12">
+        <v>46119</v>
+      </c>
+      <c r="B142" s="12">
+        <v>46119</v>
+      </c>
+      <c r="C142" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D142" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E142" s="11">
+        <v>48.5</v>
+      </c>
+      <c r="F142" s="11">
+        <v>26.2</v>
+      </c>
+      <c r="G142" s="11">
+        <v>37</v>
+      </c>
+      <c r="H142" s="11">
+        <v>24</v>
+      </c>
+      <c r="I142" s="11">
+        <v>20.5</v>
+      </c>
+      <c r="J142" s="11">
+        <v>21.25</v>
+      </c>
+      <c r="K142" s="11">
+        <v>89</v>
+      </c>
+      <c r="L142" s="11">
+        <v>26.5</v>
+      </c>
+      <c r="M142" s="11">
+        <v>73.090999999999994</v>
+      </c>
+      <c r="N142" s="11">
+        <v>14.9</v>
+      </c>
+      <c r="O142" s="11">
+        <v>12.95</v>
+      </c>
+      <c r="P142" s="11">
+        <v>13.55</v>
+      </c>
+      <c r="Q142" s="11">
+        <v>49</v>
+      </c>
+      <c r="R142" s="11">
+        <v>12.5</v>
+      </c>
+      <c r="S142" s="11">
+        <v>33.6</v>
+      </c>
+      <c r="T142" s="11">
+        <v>7.8</v>
+      </c>
+      <c r="U142" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="V142" s="11">
+        <v>6.72</v>
+      </c>
+      <c r="W142" s="11">
+        <v>9.75</v>
+      </c>
+      <c r="X142" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="Y142" s="11">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="143" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A143" s="12">
+        <v>46119</v>
+      </c>
+      <c r="B143" s="12">
+        <v>46119</v>
+      </c>
+      <c r="C143" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D143" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E143" s="11">
+        <v>48.5</v>
+      </c>
+      <c r="F143" s="11">
+        <v>26.2</v>
+      </c>
+      <c r="G143" s="11">
+        <v>37</v>
+      </c>
+      <c r="H143" s="11">
+        <v>24</v>
+      </c>
+      <c r="I143" s="11">
+        <v>20.5</v>
+      </c>
+      <c r="J143" s="11">
+        <v>21.25</v>
+      </c>
+      <c r="K143" s="11">
+        <v>89</v>
+      </c>
+      <c r="L143" s="11">
+        <v>26.5</v>
+      </c>
+      <c r="M143" s="11">
+        <v>73.036000000000001</v>
+      </c>
+      <c r="N143" s="11">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="O143" s="11">
+        <v>12.95</v>
+      </c>
+      <c r="P143" s="11">
+        <v>13.55</v>
+      </c>
+      <c r="Q143" s="11">
+        <v>49</v>
+      </c>
+      <c r="R143" s="11">
+        <v>12.5</v>
+      </c>
+      <c r="S143" s="11">
+        <v>33.56</v>
+      </c>
+      <c r="T143" s="11">
+        <v>7.8</v>
+      </c>
+      <c r="U143" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="V143" s="11">
+        <v>6.72</v>
+      </c>
+      <c r="W143" s="11">
+        <v>9.75</v>
+      </c>
+      <c r="X143" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="Y143" s="11">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="144" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A144" s="12">
+        <v>46119</v>
+      </c>
+      <c r="B144" s="12">
+        <v>46119</v>
+      </c>
+      <c r="C144" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D144" s="7" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -20752,29 +21127,29 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3E2CD10-06F7-40BE-85D8-E29219BBD9A9}">
   <dimension ref="A1:AK6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.36328125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.26953125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.375" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.25" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="9" style="11"/>
-    <col min="8" max="10" width="9.1796875" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="9.125" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="5" customFormat="1">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:37" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="17" t="s">
         <v>50</v>
       </c>
       <c r="C1" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="17" t="s">
         <v>52</v>
       </c>
       <c r="E1" s="10" t="s">
@@ -20853,11 +21228,11 @@
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
     </row>
-    <row r="2" spans="1:37">
-      <c r="A2" s="15"/>
-      <c r="B2" s="15"/>
+    <row r="2" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="A2" s="17"/>
+      <c r="B2" s="17"/>
       <c r="C2" s="16"/>
-      <c r="D2" s="15"/>
+      <c r="D2" s="17"/>
       <c r="E2" s="10" t="s">
         <v>54</v>
       </c>
@@ -20934,7 +21309,7 @@
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
     </row>
-    <row r="3" spans="1:37">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45962</v>
       </c>
@@ -21023,7 +21398,7 @@
       <c r="AJ3" s="2"/>
       <c r="AK3" s="2"/>
     </row>
-    <row r="4" spans="1:37">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45992</v>
       </c>
@@ -21112,7 +21487,7 @@
       <c r="AJ4" s="2"/>
       <c r="AK4" s="2"/>
     </row>
-    <row r="5" spans="1:37">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>46023</v>
       </c>
@@ -21144,7 +21519,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:37">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>46054</v>
       </c>
@@ -21235,35 +21610,35 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3556165B-22F0-4AF5-853E-ED25EB5C0B71}">
-  <dimension ref="A1:Y11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:Y12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.125" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="14"/>
-    <col min="7" max="7" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.453125" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.125" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5" style="14" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="14"/>
-    <col min="10" max="10" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.125" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="9" style="14"/>
-    <col min="13" max="13" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.125" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="15" t="s">
         <v>50</v>
       </c>
       <c r="C1" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="17" t="s">
         <v>52</v>
       </c>
       <c r="E1" s="13" t="s">
@@ -21306,11 +21681,11 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A2" s="15"/>
+      <c r="B2" s="15"/>
       <c r="C2" s="16"/>
-      <c r="D2" s="15"/>
+      <c r="D2" s="17"/>
       <c r="E2" s="13" t="s">
         <v>54</v>
       </c>
@@ -21351,7 +21726,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -21404,7 +21779,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -21457,7 +21832,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -21498,7 +21873,7 @@
         <v>118.333</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -21539,7 +21914,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -21580,7 +21955,7 @@
         <v>122.667</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="12">
         <v>46083</v>
       </c>
@@ -21621,7 +21996,7 @@
         <v>123.333</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="12">
         <v>46090</v>
       </c>
@@ -21662,7 +22037,7 @@
         <v>126.667</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="12">
         <v>46097</v>
       </c>
@@ -21703,7 +22078,7 @@
         <v>132.333</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="12">
         <v>46104</v>
       </c>
@@ -21742,6 +22117,47 @@
       </c>
       <c r="M11" s="11">
         <v>143.333</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A12" s="12">
+        <v>46111</v>
+      </c>
+      <c r="B12" s="12">
+        <v>46118</v>
+      </c>
+      <c r="C12" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E12" s="14">
+        <v>260</v>
+      </c>
+      <c r="F12" s="14">
+        <v>220</v>
+      </c>
+      <c r="G12" s="11">
+        <v>242.5</v>
+      </c>
+      <c r="H12" s="14">
+        <v>1150</v>
+      </c>
+      <c r="I12" s="14">
+        <v>880</v>
+      </c>
+      <c r="J12" s="11">
+        <v>935</v>
+      </c>
+      <c r="K12" s="14">
+        <v>171</v>
+      </c>
+      <c r="L12" s="14">
+        <v>135</v>
+      </c>
+      <c r="M12" s="11">
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -21759,29 +22175,29 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C550C51-95E6-4243-AC05-025707E45857}">
-  <dimension ref="A1:Y11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:Y12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.6328125" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.625" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="17" t="s">
         <v>50</v>
       </c>
       <c r="C1" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="17" t="s">
         <v>52</v>
       </c>
       <c r="E1" s="2" t="s">
@@ -21818,11 +22234,11 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25">
-      <c r="A2" s="15"/>
-      <c r="B2" s="15"/>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A2" s="17"/>
+      <c r="B2" s="17"/>
       <c r="C2" s="16"/>
-      <c r="D2" s="15"/>
+      <c r="D2" s="17"/>
       <c r="E2" s="10" t="s">
         <v>54</v>
       </c>
@@ -21857,7 +22273,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -21904,7 +22320,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -21951,7 +22367,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -21983,7 +22399,7 @@
         <v>9.6539999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -22015,7 +22431,7 @@
         <v>9.8650000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -22047,7 +22463,7 @@
         <v>10.221</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="12">
         <v>46083</v>
       </c>
@@ -22079,7 +22495,7 @@
         <v>10.721</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="12">
         <v>46090</v>
       </c>
@@ -22111,7 +22527,7 @@
         <v>11.462</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="12">
         <v>46097</v>
       </c>
@@ -22143,7 +22559,7 @@
         <v>11.962</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="12">
         <v>46104</v>
       </c>
@@ -22173,6 +22589,38 @@
       </c>
       <c r="J11" s="11">
         <v>12.865</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A12" s="12">
+        <v>46111</v>
+      </c>
+      <c r="B12" s="12">
+        <v>46118</v>
+      </c>
+      <c r="C12" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E12" s="11">
+        <v>20</v>
+      </c>
+      <c r="F12" s="11">
+        <v>10</v>
+      </c>
+      <c r="G12" s="11">
+        <v>12.526999999999999</v>
+      </c>
+      <c r="H12" s="11">
+        <v>20</v>
+      </c>
+      <c r="I12" s="11">
+        <v>10</v>
+      </c>
+      <c r="J12" s="11">
+        <v>12.71</v>
       </c>
     </row>
   </sheetData>
@@ -22190,7 +22638,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BD8F7D3-2DB0-479E-83DC-4D765C588609}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="9" style="3"/>
   </cols>
@@ -22204,15 +22652,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.90625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.90625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.6328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.875" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.625" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>48</v>
       </c>
@@ -22223,7 +22671,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
@@ -22237,7 +22685,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="s">
         <v>29</v>
@@ -22246,7 +22694,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>31</v>
@@ -22255,7 +22703,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
         <v>33</v>
@@ -22264,7 +22712,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="2" t="s">
         <v>35</v>
@@ -22273,7 +22721,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
         <v>37</v>
@@ -22282,7 +22730,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
         <v>39</v>
@@ -22291,7 +22739,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>41</v>
       </c>
@@ -22300,49 +22748,49 @@
       </c>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
       <c r="B12" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
       <c r="B14" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
       <c r="B15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>42</v>
       </c>
@@ -22353,7 +22801,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="1"/>
       <c r="B17" s="2" t="s">
         <v>8</v>
@@ -22362,7 +22810,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
       <c r="B18" s="2" t="s">
         <v>9</v>
@@ -22371,7 +22819,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>44</v>
       </c>
@@ -22382,7 +22830,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
       <c r="B20" s="2" t="s">
         <v>11</v>
@@ -22391,7 +22839,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>45</v>
       </c>
@@ -22400,42 +22848,42 @@
       </c>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="1"/>
       <c r="B22" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C22" s="2"/>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
       <c r="B23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
       <c r="B24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
       <c r="B25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
       <c r="B26" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C26" s="2"/>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>46</v>
       </c>
@@ -22444,35 +22892,35 @@
       </c>
       <c r="C27" s="2"/>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
       <c r="B28" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C28" s="2"/>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
       <c r="B29" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C29" s="2"/>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
       <c r="B30" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C30" s="2"/>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
       <c r="B31" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C31" s="2"/>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" s="1"/>
       <c r="B32" s="2" t="s">
         <v>23</v>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm12\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADE804B8-453D-49BB-8CE6-81827ED49567}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A31EC84-1A00-4DAC-848F-5495E282AF9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5790" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -33,9 +33,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -256,23 +253,23 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -285,7 +282,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -328,7 +325,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -349,27 +346,27 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -377,8 +374,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -396,7 +393,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1324,6 +1321,9 @@
                 <c:pt idx="143">
                   <c:v>37</c:v>
                 </c:pt>
+                <c:pt idx="144">
+                  <c:v>37</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2245,6 +2245,9 @@
                 <c:pt idx="143">
                   <c:v>21.25</c:v>
                 </c:pt>
+                <c:pt idx="144">
+                  <c:v>21.25</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3166,6 +3169,9 @@
                 <c:pt idx="143">
                   <c:v>72.817999999999998</c:v>
                 </c:pt>
+                <c:pt idx="144">
+                  <c:v>72.545000000000002</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4087,6 +4093,9 @@
                 <c:pt idx="143">
                   <c:v>13.55</c:v>
                 </c:pt>
+                <c:pt idx="144">
+                  <c:v>13.55</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -5006,6 +5015,9 @@
                   <c:v>33.56</c:v>
                 </c:pt>
                 <c:pt idx="143">
+                  <c:v>33.56</c:v>
+                </c:pt>
+                <c:pt idx="144">
                   <c:v>33.56</c:v>
                 </c:pt>
               </c:numCache>
@@ -5945,6 +5957,9 @@
                 <c:pt idx="143">
                   <c:v>6.72</c:v>
                 </c:pt>
+                <c:pt idx="144">
+                  <c:v>6.68</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -6866,6 +6881,9 @@
                   <c:v>7.7</c:v>
                 </c:pt>
                 <c:pt idx="143">
+                  <c:v>7.7</c:v>
+                </c:pt>
+                <c:pt idx="144">
                   <c:v>7.7</c:v>
                 </c:pt>
               </c:numCache>
@@ -7101,6 +7119,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -7108,7 +7127,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -7144,7 +7162,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7665,6 +7683,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -7672,7 +7691,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -7708,7 +7726,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -8116,6 +8134,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -8123,7 +8142,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -10210,17 +10228,17 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:Y147"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.125" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.26953125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="5" customFormat="1">
       <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
@@ -10297,7 +10315,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -10366,7 +10384,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="12">
         <v>46044</v>
       </c>
@@ -10443,7 +10461,7 @@
         <v>4.9450000000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="12">
         <v>46045</v>
       </c>
@@ -10520,7 +10538,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="12">
         <v>46045</v>
       </c>
@@ -10597,7 +10615,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="12">
         <v>46045</v>
       </c>
@@ -10674,7 +10692,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="12">
         <v>46048</v>
       </c>
@@ -10751,7 +10769,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25">
       <c r="A8" s="12">
         <v>46048</v>
       </c>
@@ -10828,7 +10846,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25">
       <c r="A9" s="12">
         <v>46048</v>
       </c>
@@ -10905,7 +10923,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25">
       <c r="A10" s="12">
         <v>46049</v>
       </c>
@@ -10982,7 +11000,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25">
       <c r="A11" s="12">
         <v>46049</v>
       </c>
@@ -11059,7 +11077,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25">
       <c r="A12" s="12">
         <v>46049</v>
       </c>
@@ -11136,7 +11154,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25">
       <c r="A13" s="12">
         <v>46050</v>
       </c>
@@ -11213,7 +11231,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25">
       <c r="A14" s="12">
         <v>46050</v>
       </c>
@@ -11290,7 +11308,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25">
       <c r="A15" s="12">
         <v>46050</v>
       </c>
@@ -11367,7 +11385,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25">
       <c r="A16" s="12">
         <v>46051</v>
       </c>
@@ -11444,7 +11462,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:25">
       <c r="A17" s="12">
         <v>46051</v>
       </c>
@@ -11521,7 +11539,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:25">
       <c r="A18" s="12">
         <v>46051</v>
       </c>
@@ -11598,7 +11616,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:25">
       <c r="A19" s="12">
         <v>46052</v>
       </c>
@@ -11675,7 +11693,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:25">
       <c r="A20" s="12">
         <v>46052</v>
       </c>
@@ -11752,7 +11770,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:25">
       <c r="A21" s="12">
         <v>46052</v>
       </c>
@@ -11829,7 +11847,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:25">
       <c r="A22" s="12">
         <v>46055</v>
       </c>
@@ -11906,7 +11924,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:25">
       <c r="A23" s="12">
         <v>46055</v>
       </c>
@@ -11983,7 +12001,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:25">
       <c r="A24" s="12">
         <v>46055</v>
       </c>
@@ -12060,7 +12078,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:25">
       <c r="A25" s="12">
         <v>46056</v>
       </c>
@@ -12137,7 +12155,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:25">
       <c r="A26" s="12">
         <v>46056</v>
       </c>
@@ -12214,7 +12232,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:25">
       <c r="A27" s="12">
         <v>46056</v>
       </c>
@@ -12291,7 +12309,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:25">
       <c r="A28" s="12">
         <v>46057</v>
       </c>
@@ -12368,7 +12386,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:25">
       <c r="A29" s="12">
         <v>46057</v>
       </c>
@@ -12445,7 +12463,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:25">
       <c r="A30" s="12">
         <v>46057</v>
       </c>
@@ -12522,7 +12540,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:25">
       <c r="A31" s="12">
         <v>46058</v>
       </c>
@@ -12599,7 +12617,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:25">
       <c r="A32" s="12">
         <v>46058</v>
       </c>
@@ -12676,7 +12694,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:25">
       <c r="A33" s="12">
         <v>46058</v>
       </c>
@@ -12753,7 +12771,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:25">
       <c r="A34" s="12">
         <v>46059</v>
       </c>
@@ -12830,7 +12848,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:25">
       <c r="A35" s="12">
         <v>46059</v>
       </c>
@@ -12907,7 +12925,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:25">
       <c r="A36" s="12">
         <v>46059</v>
       </c>
@@ -12984,7 +13002,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:25">
       <c r="A37" s="12">
         <v>46062</v>
       </c>
@@ -13061,7 +13079,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:25">
       <c r="A38" s="12">
         <v>46062</v>
       </c>
@@ -13138,7 +13156,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:25">
       <c r="A39" s="12">
         <v>46062</v>
       </c>
@@ -13215,7 +13233,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:25">
       <c r="A40" s="12">
         <v>46063</v>
       </c>
@@ -13292,7 +13310,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:25">
       <c r="A41" s="12">
         <v>46063</v>
       </c>
@@ -13369,7 +13387,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:25">
       <c r="A42" s="12">
         <v>46063</v>
       </c>
@@ -13446,7 +13464,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:25">
       <c r="A43" s="12">
         <v>46064</v>
       </c>
@@ -13523,7 +13541,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:25">
       <c r="A44" s="12">
         <v>46064</v>
       </c>
@@ -13600,7 +13618,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:25">
       <c r="A45" s="12">
         <v>46064</v>
       </c>
@@ -13677,7 +13695,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:25">
       <c r="A46" s="12">
         <v>46065</v>
       </c>
@@ -13754,7 +13772,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:25">
       <c r="A47" s="12">
         <v>46065</v>
       </c>
@@ -13831,7 +13849,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:25">
       <c r="A48" s="12">
         <v>46065</v>
       </c>
@@ -13908,7 +13926,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:25">
       <c r="A49" s="12">
         <v>46066</v>
       </c>
@@ -13985,7 +14003,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:25">
       <c r="A50" s="12">
         <v>46066</v>
       </c>
@@ -14062,7 +14080,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:25">
       <c r="A51" s="12">
         <v>46066</v>
       </c>
@@ -14139,7 +14157,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:25">
       <c r="A52" s="12">
         <v>46076</v>
       </c>
@@ -14216,7 +14234,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:25">
       <c r="A53" s="12">
         <v>46076</v>
       </c>
@@ -14293,7 +14311,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:25">
       <c r="A54" s="12">
         <v>46076</v>
       </c>
@@ -14370,7 +14388,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:25">
       <c r="A55" s="12">
         <v>46077</v>
       </c>
@@ -14447,7 +14465,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:25">
       <c r="A56" s="12">
         <v>46077</v>
       </c>
@@ -14524,7 +14542,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:25">
       <c r="A57" s="12">
         <v>46077</v>
       </c>
@@ -14601,7 +14619,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:25">
       <c r="A58" s="12">
         <v>46078</v>
       </c>
@@ -14678,7 +14696,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:25">
       <c r="A59" s="12">
         <v>46078</v>
       </c>
@@ -14755,7 +14773,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:25">
       <c r="A60" s="12">
         <v>46078</v>
       </c>
@@ -14832,7 +14850,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="61" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:25">
       <c r="A61" s="12">
         <v>46079</v>
       </c>
@@ -14909,7 +14927,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="62" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:25">
       <c r="A62" s="12">
         <v>46079</v>
       </c>
@@ -14986,7 +15004,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="63" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:25">
       <c r="A63" s="12">
         <v>46079</v>
       </c>
@@ -15063,7 +15081,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="64" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:25">
       <c r="A64" s="12">
         <v>46080</v>
       </c>
@@ -15140,7 +15158,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="65" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:25">
       <c r="A65" s="12">
         <v>46080</v>
       </c>
@@ -15217,7 +15235,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="66" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:25">
       <c r="A66" s="12">
         <v>46080</v>
       </c>
@@ -15294,7 +15312,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="67" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:25">
       <c r="A67" s="12">
         <v>46083</v>
       </c>
@@ -15371,7 +15389,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="68" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:25">
       <c r="A68" s="12">
         <v>46083</v>
       </c>
@@ -15448,7 +15466,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="69" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:25">
       <c r="A69" s="12">
         <v>46083</v>
       </c>
@@ -15525,7 +15543,7 @@
         <v>5.68</v>
       </c>
     </row>
-    <row r="70" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:25">
       <c r="A70" s="12">
         <v>46084</v>
       </c>
@@ -15602,7 +15620,7 @@
         <v>5.7590000000000003</v>
       </c>
     </row>
-    <row r="71" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:25">
       <c r="A71" s="12">
         <v>46084</v>
       </c>
@@ -15679,7 +15697,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="72" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:25">
       <c r="A72" s="12">
         <v>46084</v>
       </c>
@@ -15756,7 +15774,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="73" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:25">
       <c r="A73" s="12">
         <v>46085</v>
       </c>
@@ -15833,7 +15851,7 @@
         <v>5.8390000000000004</v>
       </c>
     </row>
-    <row r="74" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:25">
       <c r="A74" s="12">
         <v>46085</v>
       </c>
@@ -15910,7 +15928,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:25">
       <c r="A75" s="12">
         <v>46085</v>
       </c>
@@ -15987,7 +16005,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:25">
       <c r="A76" s="12">
         <v>46086</v>
       </c>
@@ -16064,7 +16082,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="77" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:25">
       <c r="A77" s="12">
         <v>46086</v>
       </c>
@@ -16141,7 +16159,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="78" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:25">
       <c r="A78" s="12">
         <v>46086</v>
       </c>
@@ -16218,7 +16236,7 @@
         <v>5.9210000000000003</v>
       </c>
     </row>
-    <row r="79" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:25">
       <c r="A79" s="12">
         <v>46087</v>
       </c>
@@ -16295,7 +16313,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="80" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:25">
       <c r="A80" s="12">
         <v>46087</v>
       </c>
@@ -16372,7 +16390,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="81" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:25">
       <c r="A81" s="12">
         <v>46087</v>
       </c>
@@ -16449,7 +16467,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="82" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:25">
       <c r="A82" s="12">
         <v>46090</v>
       </c>
@@ -16526,7 +16544,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="83" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:25">
       <c r="A83" s="12">
         <v>46090</v>
       </c>
@@ -16603,7 +16621,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="84" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:25">
       <c r="A84" s="12">
         <v>46090</v>
       </c>
@@ -16680,7 +16698,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="85" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:25">
       <c r="A85" s="12">
         <v>46091</v>
       </c>
@@ -16757,7 +16775,7 @@
         <v>6.157</v>
       </c>
     </row>
-    <row r="86" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:25">
       <c r="A86" s="12">
         <v>46091</v>
       </c>
@@ -16834,7 +16852,7 @@
         <v>6.181</v>
       </c>
     </row>
-    <row r="87" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:25">
       <c r="A87" s="12">
         <v>46091</v>
       </c>
@@ -16911,7 +16929,7 @@
         <v>6.181</v>
       </c>
     </row>
-    <row r="88" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:25">
       <c r="A88" s="12">
         <v>46092</v>
       </c>
@@ -16988,7 +17006,7 @@
         <v>6.2430000000000003</v>
       </c>
     </row>
-    <row r="89" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:25">
       <c r="A89" s="12">
         <v>46092</v>
       </c>
@@ -17065,7 +17083,7 @@
         <v>6.29</v>
       </c>
     </row>
-    <row r="90" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:25">
       <c r="A90" s="12">
         <v>46092</v>
       </c>
@@ -17142,7 +17160,7 @@
         <v>6.3049999999999997</v>
       </c>
     </row>
-    <row r="91" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:25">
       <c r="A91" s="12">
         <v>46093</v>
       </c>
@@ -17219,7 +17237,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="92" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:25">
       <c r="A92" s="12">
         <v>46093</v>
       </c>
@@ -17296,7 +17314,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="93" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:25">
       <c r="A93" s="12">
         <v>46093</v>
       </c>
@@ -17373,7 +17391,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="94" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:25">
       <c r="A94" s="12">
         <v>46094</v>
       </c>
@@ -17450,7 +17468,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="95" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:25">
       <c r="A95" s="12">
         <v>46094</v>
       </c>
@@ -17527,7 +17545,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="96" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:25">
       <c r="A96" s="12">
         <v>46094</v>
       </c>
@@ -17604,7 +17622,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="97" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:25">
       <c r="A97" s="12">
         <v>46097</v>
       </c>
@@ -17681,7 +17699,7 @@
         <v>6.5330000000000004</v>
       </c>
     </row>
-    <row r="98" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:25">
       <c r="A98" s="12">
         <v>46097</v>
       </c>
@@ -17758,7 +17776,7 @@
         <v>6.5119999999999996</v>
       </c>
     </row>
-    <row r="99" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:25">
       <c r="A99" s="12">
         <v>46097</v>
       </c>
@@ -17835,7 +17853,7 @@
         <v>6.5119999999999996</v>
       </c>
     </row>
-    <row r="100" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:25">
       <c r="A100" s="12">
         <v>46098</v>
       </c>
@@ -17912,7 +17930,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="101" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:25">
       <c r="A101" s="12">
         <v>46098</v>
       </c>
@@ -17989,7 +18007,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="102" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:25">
       <c r="A102" s="12">
         <v>46098</v>
       </c>
@@ -18066,7 +18084,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="103" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:25">
       <c r="A103" s="12">
         <v>46099</v>
       </c>
@@ -18143,7 +18161,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="104" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:25">
       <c r="A104" s="12">
         <v>46099</v>
       </c>
@@ -18220,7 +18238,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="105" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:25">
       <c r="A105" s="12">
         <v>46099</v>
       </c>
@@ -18297,7 +18315,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="106" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:25">
       <c r="A106" s="12">
         <v>46100</v>
       </c>
@@ -18374,7 +18392,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="107" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:25">
       <c r="A107" s="12">
         <v>46100</v>
       </c>
@@ -18451,7 +18469,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="108" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:25">
       <c r="A108" s="12">
         <v>46100</v>
       </c>
@@ -18528,7 +18546,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="109" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:25">
       <c r="A109" s="12">
         <v>46101</v>
       </c>
@@ -18605,7 +18623,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="110" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:25">
       <c r="A110" s="12">
         <v>46101</v>
       </c>
@@ -18682,7 +18700,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="111" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:25">
       <c r="A111" s="12">
         <v>46101</v>
       </c>
@@ -18759,7 +18777,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="112" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:25">
       <c r="A112" s="12">
         <v>46104</v>
       </c>
@@ -18836,7 +18854,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="113" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:25">
       <c r="A113" s="12">
         <v>46104</v>
       </c>
@@ -18913,7 +18931,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="114" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:25">
       <c r="A114" s="12">
         <v>46104</v>
       </c>
@@ -18990,7 +19008,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="115" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:25">
       <c r="A115" s="12">
         <v>46105</v>
       </c>
@@ -19067,7 +19085,7 @@
         <v>7.0250000000000004</v>
       </c>
     </row>
-    <row r="116" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:25">
       <c r="A116" s="12">
         <v>46105</v>
       </c>
@@ -19144,7 +19162,7 @@
         <v>7.125</v>
       </c>
     </row>
-    <row r="117" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:25">
       <c r="A117" s="12">
         <v>46105</v>
       </c>
@@ -19221,7 +19239,7 @@
         <v>7.125</v>
       </c>
     </row>
-    <row r="118" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:25">
       <c r="A118" s="12">
         <v>46106</v>
       </c>
@@ -19298,7 +19316,7 @@
         <v>7.15</v>
       </c>
     </row>
-    <row r="119" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:25">
       <c r="A119" s="12">
         <v>46106</v>
       </c>
@@ -19375,7 +19393,7 @@
         <v>7.2249999999999996</v>
       </c>
     </row>
-    <row r="120" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:25">
       <c r="A120" s="12">
         <v>46106</v>
       </c>
@@ -19452,7 +19470,7 @@
         <v>7.2249999999999996</v>
       </c>
     </row>
-    <row r="121" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:25">
       <c r="A121" s="12">
         <v>46107</v>
       </c>
@@ -19529,7 +19547,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="122" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:25">
       <c r="A122" s="12">
         <v>46107</v>
       </c>
@@ -19606,7 +19624,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="123" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:25">
       <c r="A123" s="12">
         <v>46107</v>
       </c>
@@ -19683,7 +19701,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="124" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:25">
       <c r="A124" s="12">
         <v>46108</v>
       </c>
@@ -19760,7 +19778,7 @@
         <v>7.375</v>
       </c>
     </row>
-    <row r="125" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:25">
       <c r="A125" s="12">
         <v>46108</v>
       </c>
@@ -19837,7 +19855,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="126" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:25">
       <c r="A126" s="12">
         <v>46108</v>
       </c>
@@ -19914,7 +19932,7 @@
         <v>7.375</v>
       </c>
     </row>
-    <row r="127" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:25">
       <c r="A127" s="12">
         <v>46111</v>
       </c>
@@ -19991,7 +20009,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="128" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:25">
       <c r="A128" s="12">
         <v>46111</v>
       </c>
@@ -20068,7 +20086,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="129" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:25">
       <c r="A129" s="12">
         <v>46111</v>
       </c>
@@ -20145,7 +20163,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="130" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:25">
       <c r="A130" s="12">
         <v>46112</v>
       </c>
@@ -20222,7 +20240,7 @@
         <v>7.5250000000000004</v>
       </c>
     </row>
-    <row r="131" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:25">
       <c r="A131" s="12">
         <v>46112</v>
       </c>
@@ -20299,7 +20317,7 @@
         <v>7.5250000000000004</v>
       </c>
     </row>
-    <row r="132" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:25">
       <c r="A132" s="12">
         <v>46112</v>
       </c>
@@ -20376,7 +20394,7 @@
         <v>7.55</v>
       </c>
     </row>
-    <row r="133" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:25">
       <c r="A133" s="12">
         <v>46113</v>
       </c>
@@ -20453,7 +20471,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="134" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:25">
       <c r="A134" s="12">
         <v>46113</v>
       </c>
@@ -20530,7 +20548,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="135" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:25">
       <c r="A135" s="12">
         <v>46113</v>
       </c>
@@ -20607,7 +20625,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="136" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:25">
       <c r="A136" s="12">
         <v>46114</v>
       </c>
@@ -20684,7 +20702,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="137" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:25">
       <c r="A137" s="12">
         <v>46114</v>
       </c>
@@ -20761,7 +20779,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="138" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:25">
       <c r="A138" s="12">
         <v>46114</v>
       </c>
@@ -20838,7 +20856,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="139" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:25">
       <c r="A139" s="12">
         <v>46115</v>
       </c>
@@ -20915,7 +20933,7 @@
         <v>7.6749999999999998</v>
       </c>
     </row>
-    <row r="140" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:25">
       <c r="A140" s="12">
         <v>46115</v>
       </c>
@@ -20992,7 +21010,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="141" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:25">
       <c r="A141" s="12">
         <v>46115</v>
       </c>
@@ -21069,7 +21087,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="142" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:25">
       <c r="A142" s="12">
         <v>46119</v>
       </c>
@@ -21146,7 +21164,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="143" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:25">
       <c r="A143" s="12">
         <v>46119</v>
       </c>
@@ -21223,7 +21241,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="144" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:25">
       <c r="A144" s="12">
         <v>46119</v>
       </c>
@@ -21300,7 +21318,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="145" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:25">
       <c r="A145" s="12">
         <v>46120</v>
       </c>
@@ -21377,7 +21395,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="146" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:25">
       <c r="A146" s="12">
         <v>46120</v>
       </c>
@@ -21454,7 +21472,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="147" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:25">
       <c r="A147" s="12">
         <v>46120</v>
       </c>
@@ -21466,6 +21484,69 @@
       </c>
       <c r="D147" s="7" t="s">
         <v>53</v>
+      </c>
+      <c r="E147" s="11">
+        <v>48.5</v>
+      </c>
+      <c r="F147" s="11">
+        <v>26.2</v>
+      </c>
+      <c r="G147" s="11">
+        <v>37</v>
+      </c>
+      <c r="H147" s="11">
+        <v>24</v>
+      </c>
+      <c r="I147" s="11">
+        <v>20.5</v>
+      </c>
+      <c r="J147" s="11">
+        <v>21.25</v>
+      </c>
+      <c r="K147" s="11">
+        <v>89</v>
+      </c>
+      <c r="L147" s="11">
+        <v>26.5</v>
+      </c>
+      <c r="M147" s="11">
+        <v>72.545000000000002</v>
+      </c>
+      <c r="N147" s="11">
+        <v>14.9</v>
+      </c>
+      <c r="O147" s="11">
+        <v>12.95</v>
+      </c>
+      <c r="P147" s="11">
+        <v>13.55</v>
+      </c>
+      <c r="Q147" s="11">
+        <v>49</v>
+      </c>
+      <c r="R147" s="11">
+        <v>12.5</v>
+      </c>
+      <c r="S147" s="11">
+        <v>33.56</v>
+      </c>
+      <c r="T147" s="11">
+        <v>7.6</v>
+      </c>
+      <c r="U147" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="V147" s="11">
+        <v>6.68</v>
+      </c>
+      <c r="W147" s="11">
+        <v>9.75</v>
+      </c>
+      <c r="X147" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="Y147" s="11">
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -21484,19 +21565,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3E2CD10-06F7-40BE-85D8-E29219BBD9A9}">
   <dimension ref="A1:AK6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.36328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.26953125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="9" style="11"/>
-    <col min="8" max="10" width="9.125" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:37" s="5" customFormat="1">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -21585,7 +21666,7 @@
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:37">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -21666,7 +21747,7 @@
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:37">
       <c r="A3" s="6">
         <v>45962</v>
       </c>
@@ -21755,7 +21836,7 @@
       <c r="AJ3" s="2"/>
       <c r="AK3" s="2"/>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:37">
       <c r="A4" s="6">
         <v>45992</v>
       </c>
@@ -21844,7 +21925,7 @@
       <c r="AJ4" s="2"/>
       <c r="AK4" s="2"/>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37">
       <c r="A5" s="6">
         <v>46023</v>
       </c>
@@ -21876,7 +21957,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37">
       <c r="A6" s="6">
         <v>46054</v>
       </c>
@@ -21968,24 +22049,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3556165B-22F0-4AF5-853E-ED25EB5C0B71}">
   <dimension ref="A1:Y12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.125" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="14"/>
-    <col min="7" max="7" width="9.125" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.453125" style="14" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="14"/>
-    <col min="10" max="10" width="9.125" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="9" style="14"/>
-    <col min="13" max="13" width="9.125" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="5" customFormat="1">
       <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
@@ -22038,7 +22119,7 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -22083,7 +22164,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -22136,7 +22217,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -22189,7 +22270,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -22230,7 +22311,7 @@
         <v>118.333</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -22271,7 +22352,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -22312,7 +22393,7 @@
         <v>122.667</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25">
       <c r="A8" s="12">
         <v>46083</v>
       </c>
@@ -22353,7 +22434,7 @@
         <v>123.333</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25">
       <c r="A9" s="12">
         <v>46090</v>
       </c>
@@ -22394,7 +22475,7 @@
         <v>126.667</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25">
       <c r="A10" s="12">
         <v>46097</v>
       </c>
@@ -22435,7 +22516,7 @@
         <v>132.333</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25">
       <c r="A11" s="12">
         <v>46104</v>
       </c>
@@ -22476,7 +22557,7 @@
         <v>143.333</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25">
       <c r="A12" s="12">
         <v>46111</v>
       </c>
@@ -22533,18 +22614,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C550C51-95E6-4243-AC05-025707E45857}">
   <dimension ref="A1:Y12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.625" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.6328125" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="5" customFormat="1">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -22591,7 +22672,7 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -22630,7 +22711,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -22677,7 +22758,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -22724,7 +22805,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -22756,7 +22837,7 @@
         <v>9.6539999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -22788,7 +22869,7 @@
         <v>9.8650000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -22820,7 +22901,7 @@
         <v>10.221</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25">
       <c r="A8" s="12">
         <v>46083</v>
       </c>
@@ -22852,7 +22933,7 @@
         <v>10.721</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25">
       <c r="A9" s="12">
         <v>46090</v>
       </c>
@@ -22884,7 +22965,7 @@
         <v>11.462</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25">
       <c r="A10" s="12">
         <v>46097</v>
       </c>
@@ -22916,7 +22997,7 @@
         <v>11.962</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25">
       <c r="A11" s="12">
         <v>46104</v>
       </c>
@@ -22948,7 +23029,7 @@
         <v>12.865</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25">
       <c r="A12" s="12">
         <v>46111</v>
       </c>
@@ -22995,7 +23076,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BD8F7D3-2DB0-479E-83DC-4D765C588609}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="16384" width="9" style="3"/>
   </cols>
@@ -23009,15 +23090,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="22.875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.875" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.90625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.90625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.6328125" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>48</v>
       </c>
@@ -23028,7 +23109,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
@@ -23042,7 +23123,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="s">
         <v>29</v>
@@ -23051,7 +23132,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>31</v>
@@ -23060,7 +23141,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
         <v>33</v>
@@ -23069,7 +23150,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4">
       <c r="A6" s="1"/>
       <c r="B6" s="2" t="s">
         <v>35</v>
@@ -23078,7 +23159,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
         <v>37</v>
@@ -23087,7 +23168,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
         <v>39</v>
@@ -23096,7 +23177,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
         <v>41</v>
       </c>
@@ -23105,49 +23186,49 @@
       </c>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4">
       <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4">
       <c r="A12" s="1"/>
       <c r="B12" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4">
       <c r="A14" s="1"/>
       <c r="B14" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4">
       <c r="A15" s="1"/>
       <c r="B15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4">
       <c r="A16" s="1" t="s">
         <v>42</v>
       </c>
@@ -23158,7 +23239,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3">
       <c r="A17" s="1"/>
       <c r="B17" s="2" t="s">
         <v>8</v>
@@ -23167,7 +23248,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3">
       <c r="A18" s="1"/>
       <c r="B18" s="2" t="s">
         <v>9</v>
@@ -23176,7 +23257,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3">
       <c r="A19" s="1" t="s">
         <v>44</v>
       </c>
@@ -23187,7 +23268,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3">
       <c r="A20" s="1"/>
       <c r="B20" s="2" t="s">
         <v>11</v>
@@ -23196,7 +23277,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3">
       <c r="A21" s="1" t="s">
         <v>45</v>
       </c>
@@ -23205,42 +23286,42 @@
       </c>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3">
       <c r="A22" s="1"/>
       <c r="B22" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3">
       <c r="A23" s="1"/>
       <c r="B23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3">
       <c r="A24" s="1"/>
       <c r="B24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3">
       <c r="A25" s="1"/>
       <c r="B25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3">
       <c r="A26" s="1"/>
       <c r="B26" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3">
       <c r="A27" s="1" t="s">
         <v>46</v>
       </c>
@@ -23249,35 +23330,35 @@
       </c>
       <c r="C27" s="2"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3">
       <c r="A28" s="1"/>
       <c r="B28" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C28" s="2"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3">
       <c r="A29" s="1"/>
       <c r="B29" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C29" s="2"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3">
       <c r="A30" s="1"/>
       <c r="B30" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C30" s="2"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3">
       <c r="A31" s="1"/>
       <c r="B31" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C31" s="2"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3">
       <c r="A32" s="1"/>
       <c r="B32" s="2" t="s">
         <v>23</v>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm12\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A31EC84-1A00-4DAC-848F-5495E282AF9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9697626-F5D4-4170-B75E-24BDF0AB1E2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-5790" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -34,12 +34,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -253,23 +256,23 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -282,7 +285,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -325,7 +328,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -346,27 +349,27 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -374,8 +377,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -393,7 +396,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -880,6 +883,15 @@
                 <c:pt idx="144">
                   <c:v>46120</c:v>
                 </c:pt>
+                <c:pt idx="145">
+                  <c:v>46121</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>46121</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>46121</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1323,6 +1335,12 @@
                 </c:pt>
                 <c:pt idx="144">
                   <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>36.993000000000002</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>36.993000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1804,6 +1822,15 @@
                 <c:pt idx="144">
                   <c:v>46120</c:v>
                 </c:pt>
+                <c:pt idx="145">
+                  <c:v>46121</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>46121</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>46121</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2246,6 +2273,12 @@
                   <c:v>21.25</c:v>
                 </c:pt>
                 <c:pt idx="144">
+                  <c:v>21.25</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>21.25</c:v>
+                </c:pt>
+                <c:pt idx="146">
                   <c:v>21.25</c:v>
                 </c:pt>
               </c:numCache>
@@ -2728,6 +2761,15 @@
                 <c:pt idx="144">
                   <c:v>46120</c:v>
                 </c:pt>
+                <c:pt idx="145">
+                  <c:v>46121</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>46121</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>46121</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3171,6 +3213,12 @@
                 </c:pt>
                 <c:pt idx="144">
                   <c:v>72.545000000000002</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>72</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3652,6 +3700,15 @@
                 <c:pt idx="144">
                   <c:v>46120</c:v>
                 </c:pt>
+                <c:pt idx="145">
+                  <c:v>46121</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>46121</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>46121</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4095,6 +4152,12 @@
                 </c:pt>
                 <c:pt idx="144">
                   <c:v>13.55</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>13.5</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>13.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4576,6 +4639,15 @@
                 <c:pt idx="144">
                   <c:v>46120</c:v>
                 </c:pt>
+                <c:pt idx="145">
+                  <c:v>46121</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>46121</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>46121</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5019,6 +5091,12 @@
                 </c:pt>
                 <c:pt idx="144">
                   <c:v>33.56</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>33.5</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>33.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5516,6 +5594,15 @@
                 <c:pt idx="144">
                   <c:v>46120</c:v>
                 </c:pt>
+                <c:pt idx="145">
+                  <c:v>46121</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>46121</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>46121</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5959,6 +6046,12 @@
                 </c:pt>
                 <c:pt idx="144">
                   <c:v>6.68</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>6.65</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>6.65</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6442,6 +6535,15 @@
                 <c:pt idx="144">
                   <c:v>46120</c:v>
                 </c:pt>
+                <c:pt idx="145">
+                  <c:v>46121</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>46121</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>46121</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6885,6 +6987,12 @@
                 </c:pt>
                 <c:pt idx="144">
                   <c:v>7.7</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>7.7249999999999996</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>7.7249999999999996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7119,7 +7227,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -7127,6 +7234,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -7162,7 +7270,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7683,7 +7791,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -7691,6 +7798,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -7726,7 +7834,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -8134,7 +8242,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -8142,6 +8249,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -10224,21 +10332,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22904F78-1984-4AE6-95B0-F134CF800348}">
-  <sheetPr>
+  <sheetPr codeName="Sheet1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y147"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:Y150"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.26953125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.125" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.25" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
+    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
@@ -10315,7 +10423,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -10384,7 +10492,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>46044</v>
       </c>
@@ -10461,7 +10569,7 @@
         <v>4.9450000000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>46045</v>
       </c>
@@ -10538,7 +10646,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <v>46045</v>
       </c>
@@ -10615,7 +10723,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
         <v>46045</v>
       </c>
@@ -10692,7 +10800,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
         <v>46048</v>
       </c>
@@ -10769,7 +10877,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="12">
         <v>46048</v>
       </c>
@@ -10846,7 +10954,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="12">
         <v>46048</v>
       </c>
@@ -10923,7 +11031,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="12">
         <v>46049</v>
       </c>
@@ -11000,7 +11108,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="12">
         <v>46049</v>
       </c>
@@ -11077,7 +11185,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" s="12">
         <v>46049</v>
       </c>
@@ -11154,7 +11262,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" s="12">
         <v>46050</v>
       </c>
@@ -11231,7 +11339,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A14" s="12">
         <v>46050</v>
       </c>
@@ -11308,7 +11416,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A15" s="12">
         <v>46050</v>
       </c>
@@ -11385,7 +11493,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="16" spans="1:25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A16" s="12">
         <v>46051</v>
       </c>
@@ -11462,7 +11570,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:25">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A17" s="12">
         <v>46051</v>
       </c>
@@ -11539,7 +11647,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:25">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A18" s="12">
         <v>46051</v>
       </c>
@@ -11616,7 +11724,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:25">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A19" s="12">
         <v>46052</v>
       </c>
@@ -11693,7 +11801,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="20" spans="1:25">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A20" s="12">
         <v>46052</v>
       </c>
@@ -11770,7 +11878,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="21" spans="1:25">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A21" s="12">
         <v>46052</v>
       </c>
@@ -11847,7 +11955,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="22" spans="1:25">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A22" s="12">
         <v>46055</v>
       </c>
@@ -11924,7 +12032,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="23" spans="1:25">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A23" s="12">
         <v>46055</v>
       </c>
@@ -12001,7 +12109,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="24" spans="1:25">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A24" s="12">
         <v>46055</v>
       </c>
@@ -12078,7 +12186,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="25" spans="1:25">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A25" s="12">
         <v>46056</v>
       </c>
@@ -12155,7 +12263,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="26" spans="1:25">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A26" s="12">
         <v>46056</v>
       </c>
@@ -12232,7 +12340,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="27" spans="1:25">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A27" s="12">
         <v>46056</v>
       </c>
@@ -12309,7 +12417,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="28" spans="1:25">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A28" s="12">
         <v>46057</v>
       </c>
@@ -12386,7 +12494,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="29" spans="1:25">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A29" s="12">
         <v>46057</v>
       </c>
@@ -12463,7 +12571,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="30" spans="1:25">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A30" s="12">
         <v>46057</v>
       </c>
@@ -12540,7 +12648,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="31" spans="1:25">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A31" s="12">
         <v>46058</v>
       </c>
@@ -12617,7 +12725,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="32" spans="1:25">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A32" s="12">
         <v>46058</v>
       </c>
@@ -12694,7 +12802,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="33" spans="1:25">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A33" s="12">
         <v>46058</v>
       </c>
@@ -12771,7 +12879,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="34" spans="1:25">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A34" s="12">
         <v>46059</v>
       </c>
@@ -12848,7 +12956,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:25">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A35" s="12">
         <v>46059</v>
       </c>
@@ -12925,7 +13033,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:25">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A36" s="12">
         <v>46059</v>
       </c>
@@ -13002,7 +13110,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:25">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A37" s="12">
         <v>46062</v>
       </c>
@@ -13079,7 +13187,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="38" spans="1:25">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A38" s="12">
         <v>46062</v>
       </c>
@@ -13156,7 +13264,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="39" spans="1:25">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A39" s="12">
         <v>46062</v>
       </c>
@@ -13233,7 +13341,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="40" spans="1:25">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A40" s="12">
         <v>46063</v>
       </c>
@@ -13310,7 +13418,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="41" spans="1:25">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A41" s="12">
         <v>46063</v>
       </c>
@@ -13387,7 +13495,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="42" spans="1:25">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A42" s="12">
         <v>46063</v>
       </c>
@@ -13464,7 +13572,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="43" spans="1:25">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A43" s="12">
         <v>46064</v>
       </c>
@@ -13541,7 +13649,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="44" spans="1:25">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A44" s="12">
         <v>46064</v>
       </c>
@@ -13618,7 +13726,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="45" spans="1:25">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A45" s="12">
         <v>46064</v>
       </c>
@@ -13695,7 +13803,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="46" spans="1:25">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A46" s="12">
         <v>46065</v>
       </c>
@@ -13772,7 +13880,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:25">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A47" s="12">
         <v>46065</v>
       </c>
@@ -13849,7 +13957,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:25">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A48" s="12">
         <v>46065</v>
       </c>
@@ -13926,7 +14034,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="49" spans="1:25">
+    <row r="49" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A49" s="12">
         <v>46066</v>
       </c>
@@ -14003,7 +14111,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:25">
+    <row r="50" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A50" s="12">
         <v>46066</v>
       </c>
@@ -14080,7 +14188,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:25">
+    <row r="51" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A51" s="12">
         <v>46066</v>
       </c>
@@ -14157,7 +14265,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:25">
+    <row r="52" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A52" s="12">
         <v>46076</v>
       </c>
@@ -14234,7 +14342,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="53" spans="1:25">
+    <row r="53" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A53" s="12">
         <v>46076</v>
       </c>
@@ -14311,7 +14419,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:25">
+    <row r="54" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A54" s="12">
         <v>46076</v>
       </c>
@@ -14388,7 +14496,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="55" spans="1:25">
+    <row r="55" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A55" s="12">
         <v>46077</v>
       </c>
@@ -14465,7 +14573,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="56" spans="1:25">
+    <row r="56" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A56" s="12">
         <v>46077</v>
       </c>
@@ -14542,7 +14650,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="57" spans="1:25">
+    <row r="57" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A57" s="12">
         <v>46077</v>
       </c>
@@ -14619,7 +14727,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="58" spans="1:25">
+    <row r="58" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A58" s="12">
         <v>46078</v>
       </c>
@@ -14696,7 +14804,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="59" spans="1:25">
+    <row r="59" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A59" s="12">
         <v>46078</v>
       </c>
@@ -14773,7 +14881,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="60" spans="1:25">
+    <row r="60" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A60" s="12">
         <v>46078</v>
       </c>
@@ -14850,7 +14958,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="61" spans="1:25">
+    <row r="61" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A61" s="12">
         <v>46079</v>
       </c>
@@ -14927,7 +15035,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="62" spans="1:25">
+    <row r="62" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A62" s="12">
         <v>46079</v>
       </c>
@@ -15004,7 +15112,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="63" spans="1:25">
+    <row r="63" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A63" s="12">
         <v>46079</v>
       </c>
@@ -15081,7 +15189,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="64" spans="1:25">
+    <row r="64" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A64" s="12">
         <v>46080</v>
       </c>
@@ -15158,7 +15266,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="65" spans="1:25">
+    <row r="65" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A65" s="12">
         <v>46080</v>
       </c>
@@ -15235,7 +15343,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="66" spans="1:25">
+    <row r="66" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A66" s="12">
         <v>46080</v>
       </c>
@@ -15312,7 +15420,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="67" spans="1:25">
+    <row r="67" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A67" s="12">
         <v>46083</v>
       </c>
@@ -15389,7 +15497,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="68" spans="1:25">
+    <row r="68" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A68" s="12">
         <v>46083</v>
       </c>
@@ -15466,7 +15574,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="69" spans="1:25">
+    <row r="69" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A69" s="12">
         <v>46083</v>
       </c>
@@ -15543,7 +15651,7 @@
         <v>5.68</v>
       </c>
     </row>
-    <row r="70" spans="1:25">
+    <row r="70" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A70" s="12">
         <v>46084</v>
       </c>
@@ -15620,7 +15728,7 @@
         <v>5.7590000000000003</v>
       </c>
     </row>
-    <row r="71" spans="1:25">
+    <row r="71" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A71" s="12">
         <v>46084</v>
       </c>
@@ -15697,7 +15805,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="72" spans="1:25">
+    <row r="72" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A72" s="12">
         <v>46084</v>
       </c>
@@ -15774,7 +15882,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="73" spans="1:25">
+    <row r="73" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A73" s="12">
         <v>46085</v>
       </c>
@@ -15851,7 +15959,7 @@
         <v>5.8390000000000004</v>
       </c>
     </row>
-    <row r="74" spans="1:25">
+    <row r="74" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A74" s="12">
         <v>46085</v>
       </c>
@@ -15928,7 +16036,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:25">
+    <row r="75" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A75" s="12">
         <v>46085</v>
       </c>
@@ -16005,7 +16113,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:25">
+    <row r="76" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A76" s="12">
         <v>46086</v>
       </c>
@@ -16082,7 +16190,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="77" spans="1:25">
+    <row r="77" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A77" s="12">
         <v>46086</v>
       </c>
@@ -16159,7 +16267,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="78" spans="1:25">
+    <row r="78" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A78" s="12">
         <v>46086</v>
       </c>
@@ -16236,7 +16344,7 @@
         <v>5.9210000000000003</v>
       </c>
     </row>
-    <row r="79" spans="1:25">
+    <row r="79" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A79" s="12">
         <v>46087</v>
       </c>
@@ -16313,7 +16421,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="80" spans="1:25">
+    <row r="80" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A80" s="12">
         <v>46087</v>
       </c>
@@ -16390,7 +16498,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="81" spans="1:25">
+    <row r="81" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A81" s="12">
         <v>46087</v>
       </c>
@@ -16467,7 +16575,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="82" spans="1:25">
+    <row r="82" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A82" s="12">
         <v>46090</v>
       </c>
@@ -16544,7 +16652,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="83" spans="1:25">
+    <row r="83" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A83" s="12">
         <v>46090</v>
       </c>
@@ -16621,7 +16729,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="84" spans="1:25">
+    <row r="84" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A84" s="12">
         <v>46090</v>
       </c>
@@ -16698,7 +16806,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="85" spans="1:25">
+    <row r="85" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A85" s="12">
         <v>46091</v>
       </c>
@@ -16775,7 +16883,7 @@
         <v>6.157</v>
       </c>
     </row>
-    <row r="86" spans="1:25">
+    <row r="86" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A86" s="12">
         <v>46091</v>
       </c>
@@ -16852,7 +16960,7 @@
         <v>6.181</v>
       </c>
     </row>
-    <row r="87" spans="1:25">
+    <row r="87" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A87" s="12">
         <v>46091</v>
       </c>
@@ -16929,7 +17037,7 @@
         <v>6.181</v>
       </c>
     </row>
-    <row r="88" spans="1:25">
+    <row r="88" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A88" s="12">
         <v>46092</v>
       </c>
@@ -17006,7 +17114,7 @@
         <v>6.2430000000000003</v>
       </c>
     </row>
-    <row r="89" spans="1:25">
+    <row r="89" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A89" s="12">
         <v>46092</v>
       </c>
@@ -17083,7 +17191,7 @@
         <v>6.29</v>
       </c>
     </row>
-    <row r="90" spans="1:25">
+    <row r="90" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A90" s="12">
         <v>46092</v>
       </c>
@@ -17160,7 +17268,7 @@
         <v>6.3049999999999997</v>
       </c>
     </row>
-    <row r="91" spans="1:25">
+    <row r="91" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A91" s="12">
         <v>46093</v>
       </c>
@@ -17237,7 +17345,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="92" spans="1:25">
+    <row r="92" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A92" s="12">
         <v>46093</v>
       </c>
@@ -17314,7 +17422,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="93" spans="1:25">
+    <row r="93" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A93" s="12">
         <v>46093</v>
       </c>
@@ -17391,7 +17499,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="94" spans="1:25">
+    <row r="94" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A94" s="12">
         <v>46094</v>
       </c>
@@ -17468,7 +17576,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="95" spans="1:25">
+    <row r="95" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A95" s="12">
         <v>46094</v>
       </c>
@@ -17545,7 +17653,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="96" spans="1:25">
+    <row r="96" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A96" s="12">
         <v>46094</v>
       </c>
@@ -17622,7 +17730,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="97" spans="1:25">
+    <row r="97" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A97" s="12">
         <v>46097</v>
       </c>
@@ -17699,7 +17807,7 @@
         <v>6.5330000000000004</v>
       </c>
     </row>
-    <row r="98" spans="1:25">
+    <row r="98" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A98" s="12">
         <v>46097</v>
       </c>
@@ -17776,7 +17884,7 @@
         <v>6.5119999999999996</v>
       </c>
     </row>
-    <row r="99" spans="1:25">
+    <row r="99" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A99" s="12">
         <v>46097</v>
       </c>
@@ -17853,7 +17961,7 @@
         <v>6.5119999999999996</v>
       </c>
     </row>
-    <row r="100" spans="1:25">
+    <row r="100" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A100" s="12">
         <v>46098</v>
       </c>
@@ -17930,7 +18038,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="101" spans="1:25">
+    <row r="101" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A101" s="12">
         <v>46098</v>
       </c>
@@ -18007,7 +18115,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="102" spans="1:25">
+    <row r="102" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A102" s="12">
         <v>46098</v>
       </c>
@@ -18084,7 +18192,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="103" spans="1:25">
+    <row r="103" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A103" s="12">
         <v>46099</v>
       </c>
@@ -18161,7 +18269,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="104" spans="1:25">
+    <row r="104" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A104" s="12">
         <v>46099</v>
       </c>
@@ -18238,7 +18346,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="105" spans="1:25">
+    <row r="105" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A105" s="12">
         <v>46099</v>
       </c>
@@ -18315,7 +18423,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="106" spans="1:25">
+    <row r="106" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A106" s="12">
         <v>46100</v>
       </c>
@@ -18392,7 +18500,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="107" spans="1:25">
+    <row r="107" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A107" s="12">
         <v>46100</v>
       </c>
@@ -18469,7 +18577,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="108" spans="1:25">
+    <row r="108" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A108" s="12">
         <v>46100</v>
       </c>
@@ -18546,7 +18654,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="109" spans="1:25">
+    <row r="109" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A109" s="12">
         <v>46101</v>
       </c>
@@ -18623,7 +18731,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="110" spans="1:25">
+    <row r="110" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A110" s="12">
         <v>46101</v>
       </c>
@@ -18700,7 +18808,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="111" spans="1:25">
+    <row r="111" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A111" s="12">
         <v>46101</v>
       </c>
@@ -18777,7 +18885,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="112" spans="1:25">
+    <row r="112" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A112" s="12">
         <v>46104</v>
       </c>
@@ -18854,7 +18962,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="113" spans="1:25">
+    <row r="113" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A113" s="12">
         <v>46104</v>
       </c>
@@ -18931,7 +19039,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="114" spans="1:25">
+    <row r="114" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A114" s="12">
         <v>46104</v>
       </c>
@@ -19008,7 +19116,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="115" spans="1:25">
+    <row r="115" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A115" s="12">
         <v>46105</v>
       </c>
@@ -19085,7 +19193,7 @@
         <v>7.0250000000000004</v>
       </c>
     </row>
-    <row r="116" spans="1:25">
+    <row r="116" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A116" s="12">
         <v>46105</v>
       </c>
@@ -19162,7 +19270,7 @@
         <v>7.125</v>
       </c>
     </row>
-    <row r="117" spans="1:25">
+    <row r="117" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A117" s="12">
         <v>46105</v>
       </c>
@@ -19239,7 +19347,7 @@
         <v>7.125</v>
       </c>
     </row>
-    <row r="118" spans="1:25">
+    <row r="118" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A118" s="12">
         <v>46106</v>
       </c>
@@ -19316,7 +19424,7 @@
         <v>7.15</v>
       </c>
     </row>
-    <row r="119" spans="1:25">
+    <row r="119" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A119" s="12">
         <v>46106</v>
       </c>
@@ -19393,7 +19501,7 @@
         <v>7.2249999999999996</v>
       </c>
     </row>
-    <row r="120" spans="1:25">
+    <row r="120" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A120" s="12">
         <v>46106</v>
       </c>
@@ -19470,7 +19578,7 @@
         <v>7.2249999999999996</v>
       </c>
     </row>
-    <row r="121" spans="1:25">
+    <row r="121" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A121" s="12">
         <v>46107</v>
       </c>
@@ -19547,7 +19655,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="122" spans="1:25">
+    <row r="122" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A122" s="12">
         <v>46107</v>
       </c>
@@ -19624,7 +19732,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="123" spans="1:25">
+    <row r="123" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A123" s="12">
         <v>46107</v>
       </c>
@@ -19701,7 +19809,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="124" spans="1:25">
+    <row r="124" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A124" s="12">
         <v>46108</v>
       </c>
@@ -19778,7 +19886,7 @@
         <v>7.375</v>
       </c>
     </row>
-    <row r="125" spans="1:25">
+    <row r="125" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A125" s="12">
         <v>46108</v>
       </c>
@@ -19855,7 +19963,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="126" spans="1:25">
+    <row r="126" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A126" s="12">
         <v>46108</v>
       </c>
@@ -19932,7 +20040,7 @@
         <v>7.375</v>
       </c>
     </row>
-    <row r="127" spans="1:25">
+    <row r="127" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A127" s="12">
         <v>46111</v>
       </c>
@@ -20009,7 +20117,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="128" spans="1:25">
+    <row r="128" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A128" s="12">
         <v>46111</v>
       </c>
@@ -20086,7 +20194,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="129" spans="1:25">
+    <row r="129" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A129" s="12">
         <v>46111</v>
       </c>
@@ -20163,7 +20271,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="130" spans="1:25">
+    <row r="130" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A130" s="12">
         <v>46112</v>
       </c>
@@ -20240,7 +20348,7 @@
         <v>7.5250000000000004</v>
       </c>
     </row>
-    <row r="131" spans="1:25">
+    <row r="131" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A131" s="12">
         <v>46112</v>
       </c>
@@ -20317,7 +20425,7 @@
         <v>7.5250000000000004</v>
       </c>
     </row>
-    <row r="132" spans="1:25">
+    <row r="132" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A132" s="12">
         <v>46112</v>
       </c>
@@ -20394,7 +20502,7 @@
         <v>7.55</v>
       </c>
     </row>
-    <row r="133" spans="1:25">
+    <row r="133" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A133" s="12">
         <v>46113</v>
       </c>
@@ -20471,7 +20579,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="134" spans="1:25">
+    <row r="134" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A134" s="12">
         <v>46113</v>
       </c>
@@ -20548,7 +20656,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="135" spans="1:25">
+    <row r="135" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A135" s="12">
         <v>46113</v>
       </c>
@@ -20625,7 +20733,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="136" spans="1:25">
+    <row r="136" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A136" s="12">
         <v>46114</v>
       </c>
@@ -20702,7 +20810,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="137" spans="1:25">
+    <row r="137" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A137" s="12">
         <v>46114</v>
       </c>
@@ -20779,7 +20887,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="138" spans="1:25">
+    <row r="138" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A138" s="12">
         <v>46114</v>
       </c>
@@ -20856,7 +20964,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="139" spans="1:25">
+    <row r="139" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A139" s="12">
         <v>46115</v>
       </c>
@@ -20933,7 +21041,7 @@
         <v>7.6749999999999998</v>
       </c>
     </row>
-    <row r="140" spans="1:25">
+    <row r="140" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A140" s="12">
         <v>46115</v>
       </c>
@@ -21010,7 +21118,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="141" spans="1:25">
+    <row r="141" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A141" s="12">
         <v>46115</v>
       </c>
@@ -21087,7 +21195,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="142" spans="1:25">
+    <row r="142" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A142" s="12">
         <v>46119</v>
       </c>
@@ -21164,7 +21272,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="143" spans="1:25">
+    <row r="143" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A143" s="12">
         <v>46119</v>
       </c>
@@ -21241,7 +21349,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="144" spans="1:25">
+    <row r="144" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A144" s="12">
         <v>46119</v>
       </c>
@@ -21318,7 +21426,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="145" spans="1:25">
+    <row r="145" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A145" s="12">
         <v>46120</v>
       </c>
@@ -21395,7 +21503,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="146" spans="1:25">
+    <row r="146" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A146" s="12">
         <v>46120</v>
       </c>
@@ -21472,7 +21580,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="147" spans="1:25">
+    <row r="147" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A147" s="12">
         <v>46120</v>
       </c>
@@ -21547,6 +21655,174 @@
       </c>
       <c r="Y147" s="11">
         <v>7.7</v>
+      </c>
+    </row>
+    <row r="148" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A148" s="12">
+        <v>46121</v>
+      </c>
+      <c r="B148" s="12">
+        <v>46121</v>
+      </c>
+      <c r="C148" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D148" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E148" s="11">
+        <v>48.5</v>
+      </c>
+      <c r="F148" s="11">
+        <v>26.5</v>
+      </c>
+      <c r="G148" s="11">
+        <v>36.993000000000002</v>
+      </c>
+      <c r="H148" s="11">
+        <v>24</v>
+      </c>
+      <c r="I148" s="11">
+        <v>20.5</v>
+      </c>
+      <c r="J148" s="11">
+        <v>21.25</v>
+      </c>
+      <c r="K148" s="11">
+        <v>89</v>
+      </c>
+      <c r="L148" s="11">
+        <v>27</v>
+      </c>
+      <c r="M148" s="11">
+        <v>72</v>
+      </c>
+      <c r="N148" s="11">
+        <v>14.8</v>
+      </c>
+      <c r="O148" s="11">
+        <v>12.9</v>
+      </c>
+      <c r="P148" s="11">
+        <v>13.5</v>
+      </c>
+      <c r="Q148" s="11">
+        <v>49</v>
+      </c>
+      <c r="R148" s="11">
+        <v>13</v>
+      </c>
+      <c r="S148" s="11">
+        <v>33.5</v>
+      </c>
+      <c r="T148" s="11">
+        <v>7.5</v>
+      </c>
+      <c r="U148" s="11">
+        <v>5.45</v>
+      </c>
+      <c r="V148" s="11">
+        <v>6.65</v>
+      </c>
+      <c r="W148" s="11">
+        <v>9.75</v>
+      </c>
+      <c r="X148" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="Y148" s="11">
+        <v>7.7249999999999996</v>
+      </c>
+    </row>
+    <row r="149" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A149" s="12">
+        <v>46121</v>
+      </c>
+      <c r="B149" s="12">
+        <v>46121</v>
+      </c>
+      <c r="C149" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D149" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E149" s="11">
+        <v>48.5</v>
+      </c>
+      <c r="F149" s="11">
+        <v>26.5</v>
+      </c>
+      <c r="G149" s="11">
+        <v>36.993000000000002</v>
+      </c>
+      <c r="H149" s="11">
+        <v>24</v>
+      </c>
+      <c r="I149" s="11">
+        <v>20.5</v>
+      </c>
+      <c r="J149" s="11">
+        <v>21.25</v>
+      </c>
+      <c r="K149" s="11">
+        <v>89</v>
+      </c>
+      <c r="L149" s="11">
+        <v>27</v>
+      </c>
+      <c r="M149" s="11">
+        <v>72</v>
+      </c>
+      <c r="N149" s="11">
+        <v>14.8</v>
+      </c>
+      <c r="O149" s="11">
+        <v>12.9</v>
+      </c>
+      <c r="P149" s="11">
+        <v>13.5</v>
+      </c>
+      <c r="Q149" s="11">
+        <v>49</v>
+      </c>
+      <c r="R149" s="11">
+        <v>13</v>
+      </c>
+      <c r="S149" s="11">
+        <v>33.5</v>
+      </c>
+      <c r="T149" s="11">
+        <v>7.5</v>
+      </c>
+      <c r="U149" s="11">
+        <v>5.45</v>
+      </c>
+      <c r="V149" s="11">
+        <v>6.65</v>
+      </c>
+      <c r="W149" s="11">
+        <v>9.75</v>
+      </c>
+      <c r="X149" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="Y149" s="11">
+        <v>7.7249999999999996</v>
+      </c>
+    </row>
+    <row r="150" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A150" s="12">
+        <v>46121</v>
+      </c>
+      <c r="B150" s="12">
+        <v>46121</v>
+      </c>
+      <c r="C150" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D150" s="7" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -21564,20 +21840,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3E2CD10-06F7-40BE-85D8-E29219BBD9A9}">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:AK6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.36328125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.26953125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.375" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.25" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="9" style="11"/>
-    <col min="8" max="10" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="9.125" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="5" customFormat="1">
+    <row r="1" spans="1:37" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -21666,7 +21943,7 @@
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
     </row>
-    <row r="2" spans="1:37">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -21747,7 +22024,7 @@
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
     </row>
-    <row r="3" spans="1:37">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45962</v>
       </c>
@@ -21836,7 +22113,7 @@
       <c r="AJ3" s="2"/>
       <c r="AK3" s="2"/>
     </row>
-    <row r="4" spans="1:37">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45992</v>
       </c>
@@ -21925,7 +22202,7 @@
       <c r="AJ4" s="2"/>
       <c r="AK4" s="2"/>
     </row>
-    <row r="5" spans="1:37">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>46023</v>
       </c>
@@ -21957,7 +22234,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:37">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>46054</v>
       </c>
@@ -22048,25 +22325,26 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3556165B-22F0-4AF5-853E-ED25EB5C0B71}">
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:Y12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.125" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="14"/>
-    <col min="7" max="7" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.453125" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.125" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5" style="14" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="14"/>
-    <col min="10" max="10" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.125" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="9" style="14"/>
-    <col min="13" max="13" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.125" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
+    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
@@ -22119,7 +22397,7 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -22164,7 +22442,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -22217,7 +22495,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -22270,7 +22548,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -22311,7 +22589,7 @@
         <v>118.333</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -22352,7 +22630,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -22393,7 +22671,7 @@
         <v>122.667</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="12">
         <v>46083</v>
       </c>
@@ -22434,7 +22712,7 @@
         <v>123.333</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="12">
         <v>46090</v>
       </c>
@@ -22475,7 +22753,7 @@
         <v>126.667</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="12">
         <v>46097</v>
       </c>
@@ -22516,7 +22794,7 @@
         <v>132.333</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="12">
         <v>46104</v>
       </c>
@@ -22557,7 +22835,7 @@
         <v>143.333</v>
       </c>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" s="12">
         <v>46111</v>
       </c>
@@ -22613,19 +22891,20 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C550C51-95E6-4243-AC05-025707E45857}">
+  <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:Y12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.6328125" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.625" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
+    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -22672,7 +22951,7 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -22711,7 +22990,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -22758,7 +23037,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -22805,7 +23084,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -22837,7 +23116,7 @@
         <v>9.6539999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -22869,7 +23148,7 @@
         <v>9.8650000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -22901,7 +23180,7 @@
         <v>10.221</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="12">
         <v>46083</v>
       </c>
@@ -22933,7 +23212,7 @@
         <v>10.721</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="12">
         <v>46090</v>
       </c>
@@ -22965,7 +23244,7 @@
         <v>11.462</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="12">
         <v>46097</v>
       </c>
@@ -22997,7 +23276,7 @@
         <v>11.962</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="12">
         <v>46104</v>
       </c>
@@ -23029,7 +23308,7 @@
         <v>12.865</v>
       </c>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" s="12">
         <v>46111</v>
       </c>
@@ -23075,8 +23354,9 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BD8F7D3-2DB0-479E-83DC-4D765C588609}">
+  <sheetPr codeName="Sheet5"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="9" style="3"/>
   </cols>
@@ -23089,16 +23369,17 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.90625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.90625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.6328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.875" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.625" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>48</v>
       </c>
@@ -23109,7 +23390,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
@@ -23123,7 +23404,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="s">
         <v>29</v>
@@ -23132,7 +23413,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>31</v>
@@ -23141,7 +23422,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
         <v>33</v>
@@ -23150,7 +23431,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="2" t="s">
         <v>35</v>
@@ -23159,7 +23440,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
         <v>37</v>
@@ -23168,7 +23449,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
         <v>39</v>
@@ -23177,7 +23458,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>41</v>
       </c>
@@ -23186,49 +23467,49 @@
       </c>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
       <c r="B12" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
       <c r="B14" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
       <c r="B15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>42</v>
       </c>
@@ -23239,7 +23520,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="1"/>
       <c r="B17" s="2" t="s">
         <v>8</v>
@@ -23248,7 +23529,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
       <c r="B18" s="2" t="s">
         <v>9</v>
@@ -23257,7 +23538,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>44</v>
       </c>
@@ -23268,7 +23549,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
       <c r="B20" s="2" t="s">
         <v>11</v>
@@ -23277,7 +23558,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>45</v>
       </c>
@@ -23286,42 +23567,42 @@
       </c>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="1"/>
       <c r="B22" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C22" s="2"/>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
       <c r="B23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
       <c r="B24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
       <c r="B25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
       <c r="B26" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C26" s="2"/>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>46</v>
       </c>
@@ -23330,35 +23611,35 @@
       </c>
       <c r="C27" s="2"/>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
       <c r="B28" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C28" s="2"/>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
       <c r="B29" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C29" s="2"/>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
       <c r="B30" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C30" s="2"/>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
       <c r="B31" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C31" s="2"/>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" s="1"/>
       <c r="B32" s="2" t="s">
         <v>23</v>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm12\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9697626-F5D4-4170-B75E-24BDF0AB1E2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA95D844-7BFB-4F40-B9CC-C3C6B32D6B84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-5790" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -892,6 +892,15 @@
                 <c:pt idx="147">
                   <c:v>46121</c:v>
                 </c:pt>
+                <c:pt idx="148">
+                  <c:v>46122</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>46122</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>46122</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1341,6 +1350,15 @@
                 </c:pt>
                 <c:pt idx="146">
                   <c:v>36.993000000000002</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>37.027000000000001</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>37.033000000000001</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>37.033000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1831,6 +1849,15 @@
                 <c:pt idx="147">
                   <c:v>46121</c:v>
                 </c:pt>
+                <c:pt idx="148">
+                  <c:v>46122</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>46122</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>46122</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2279,6 +2306,15 @@
                   <c:v>21.25</c:v>
                 </c:pt>
                 <c:pt idx="146">
+                  <c:v>21.25</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>21.25</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>21.25</c:v>
+                </c:pt>
+                <c:pt idx="149">
                   <c:v>21.25</c:v>
                 </c:pt>
               </c:numCache>
@@ -2770,6 +2806,15 @@
                 <c:pt idx="147">
                   <c:v>46121</c:v>
                 </c:pt>
+                <c:pt idx="148">
+                  <c:v>46122</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>46122</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>46122</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3219,6 +3264,15 @@
                 </c:pt>
                 <c:pt idx="146">
                   <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>71.727000000000004</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>71.727000000000004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3709,6 +3763,15 @@
                 <c:pt idx="147">
                   <c:v>46121</c:v>
                 </c:pt>
+                <c:pt idx="148">
+                  <c:v>46122</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>46122</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>46122</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4157,6 +4220,15 @@
                   <c:v>13.5</c:v>
                 </c:pt>
                 <c:pt idx="146">
+                  <c:v>13.5</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>13.5</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>13.5</c:v>
+                </c:pt>
+                <c:pt idx="149">
                   <c:v>13.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -4648,6 +4720,15 @@
                 <c:pt idx="147">
                   <c:v>46121</c:v>
                 </c:pt>
+                <c:pt idx="148">
+                  <c:v>46122</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>46122</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>46122</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5097,6 +5178,15 @@
                 </c:pt>
                 <c:pt idx="146">
                   <c:v>33.5</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>33.5</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>33.4</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>33.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5603,6 +5693,15 @@
                 <c:pt idx="147">
                   <c:v>46121</c:v>
                 </c:pt>
+                <c:pt idx="148">
+                  <c:v>46122</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>46122</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>46122</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6052,6 +6151,15 @@
                 </c:pt>
                 <c:pt idx="146">
                   <c:v>6.65</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>6.65</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>6.63</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>6.63</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6544,6 +6652,15 @@
                 <c:pt idx="147">
                   <c:v>46121</c:v>
                 </c:pt>
+                <c:pt idx="148">
+                  <c:v>46122</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>46122</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>46122</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6993,6 +7110,15 @@
                 </c:pt>
                 <c:pt idx="146">
                   <c:v>7.7249999999999996</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>7.7249999999999996</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>7.75</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>7.75</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10335,7 +10461,7 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y150"/>
+  <dimension ref="A1:Y153"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.125" style="12" bestFit="1" customWidth="1"/>
@@ -21822,6 +21948,237 @@
         <v>0.75694444444444453</v>
       </c>
       <c r="D150" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E150" s="11">
+        <v>48.5</v>
+      </c>
+      <c r="F150" s="11">
+        <v>26.5</v>
+      </c>
+      <c r="G150" s="11">
+        <v>37.027000000000001</v>
+      </c>
+      <c r="H150" s="11">
+        <v>24</v>
+      </c>
+      <c r="I150" s="11">
+        <v>20.5</v>
+      </c>
+      <c r="J150" s="11">
+        <v>21.25</v>
+      </c>
+      <c r="K150" s="11">
+        <v>89</v>
+      </c>
+      <c r="L150" s="11">
+        <v>27</v>
+      </c>
+      <c r="M150" s="11">
+        <v>72</v>
+      </c>
+      <c r="N150" s="11">
+        <v>14.8</v>
+      </c>
+      <c r="O150" s="11">
+        <v>12.9</v>
+      </c>
+      <c r="P150" s="11">
+        <v>13.5</v>
+      </c>
+      <c r="Q150" s="11">
+        <v>49</v>
+      </c>
+      <c r="R150" s="11">
+        <v>13</v>
+      </c>
+      <c r="S150" s="11">
+        <v>33.5</v>
+      </c>
+      <c r="T150" s="11">
+        <v>7.5</v>
+      </c>
+      <c r="U150" s="11">
+        <v>5.45</v>
+      </c>
+      <c r="V150" s="11">
+        <v>6.65</v>
+      </c>
+      <c r="W150" s="11">
+        <v>9.75</v>
+      </c>
+      <c r="X150" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="Y150" s="11">
+        <v>7.7249999999999996</v>
+      </c>
+    </row>
+    <row r="151" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A151" s="12">
+        <v>46122</v>
+      </c>
+      <c r="B151" s="12">
+        <v>46122</v>
+      </c>
+      <c r="C151" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D151" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E151" s="11">
+        <v>48.5</v>
+      </c>
+      <c r="F151" s="11">
+        <v>26.5</v>
+      </c>
+      <c r="G151" s="11">
+        <v>37.033000000000001</v>
+      </c>
+      <c r="H151" s="11">
+        <v>24</v>
+      </c>
+      <c r="I151" s="11">
+        <v>20.5</v>
+      </c>
+      <c r="J151" s="11">
+        <v>21.25</v>
+      </c>
+      <c r="K151" s="11">
+        <v>88</v>
+      </c>
+      <c r="L151" s="11">
+        <v>27</v>
+      </c>
+      <c r="M151" s="11">
+        <v>71.727000000000004</v>
+      </c>
+      <c r="N151" s="11">
+        <v>14.8</v>
+      </c>
+      <c r="O151" s="11">
+        <v>12.9</v>
+      </c>
+      <c r="P151" s="11">
+        <v>13.5</v>
+      </c>
+      <c r="Q151" s="11">
+        <v>49</v>
+      </c>
+      <c r="R151" s="11">
+        <v>13</v>
+      </c>
+      <c r="S151" s="11">
+        <v>33.4</v>
+      </c>
+      <c r="T151" s="11">
+        <v>7.5</v>
+      </c>
+      <c r="U151" s="11">
+        <v>5.45</v>
+      </c>
+      <c r="V151" s="11">
+        <v>6.63</v>
+      </c>
+      <c r="W151" s="11">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="X151" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="Y151" s="11">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="152" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A152" s="12">
+        <v>46122</v>
+      </c>
+      <c r="B152" s="12">
+        <v>46122</v>
+      </c>
+      <c r="C152" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D152" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E152" s="11">
+        <v>48.5</v>
+      </c>
+      <c r="F152" s="11">
+        <v>26.5</v>
+      </c>
+      <c r="G152" s="11">
+        <v>37.033000000000001</v>
+      </c>
+      <c r="H152" s="11">
+        <v>24</v>
+      </c>
+      <c r="I152" s="11">
+        <v>20.5</v>
+      </c>
+      <c r="J152" s="11">
+        <v>21.25</v>
+      </c>
+      <c r="K152" s="11">
+        <v>88</v>
+      </c>
+      <c r="L152" s="11">
+        <v>27</v>
+      </c>
+      <c r="M152" s="11">
+        <v>71.727000000000004</v>
+      </c>
+      <c r="N152" s="11">
+        <v>14.8</v>
+      </c>
+      <c r="O152" s="11">
+        <v>12.9</v>
+      </c>
+      <c r="P152" s="11">
+        <v>13.5</v>
+      </c>
+      <c r="Q152" s="11">
+        <v>49</v>
+      </c>
+      <c r="R152" s="11">
+        <v>13</v>
+      </c>
+      <c r="S152" s="11">
+        <v>33.4</v>
+      </c>
+      <c r="T152" s="11">
+        <v>7.5</v>
+      </c>
+      <c r="U152" s="11">
+        <v>5.45</v>
+      </c>
+      <c r="V152" s="11">
+        <v>6.63</v>
+      </c>
+      <c r="W152" s="11">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="X152" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="Y152" s="11">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="153" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A153" s="12">
+        <v>46122</v>
+      </c>
+      <c r="B153" s="12">
+        <v>46122</v>
+      </c>
+      <c r="C153" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D153" s="7" t="s">
         <v>53</v>
       </c>
     </row>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm12\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA95D844-7BFB-4F40-B9CC-C3C6B32D6B84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFBDD5A9-415C-4036-9C3E-2B1E5F6A8D1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5790" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -33,9 +33,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -256,23 +253,23 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -285,7 +282,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -328,7 +325,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -349,27 +346,27 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -377,8 +374,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -396,7 +393,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1360,6 +1357,9 @@
                 <c:pt idx="149">
                   <c:v>37.033000000000001</c:v>
                 </c:pt>
+                <c:pt idx="150">
+                  <c:v>37.033000000000001</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2317,6 +2317,9 @@
                 <c:pt idx="149">
                   <c:v>21.25</c:v>
                 </c:pt>
+                <c:pt idx="150">
+                  <c:v>21.3</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3274,6 +3277,9 @@
                 <c:pt idx="149">
                   <c:v>71.727000000000004</c:v>
                 </c:pt>
+                <c:pt idx="150">
+                  <c:v>71.5</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4231,6 +4237,9 @@
                 <c:pt idx="149">
                   <c:v>13.5</c:v>
                 </c:pt>
+                <c:pt idx="150">
+                  <c:v>13.5</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -5186,6 +5195,9 @@
                   <c:v>33.4</c:v>
                 </c:pt>
                 <c:pt idx="149">
+                  <c:v>33.4</c:v>
+                </c:pt>
+                <c:pt idx="150">
                   <c:v>33.4</c:v>
                 </c:pt>
               </c:numCache>
@@ -6161,6 +6173,9 @@
                 <c:pt idx="149">
                   <c:v>6.63</c:v>
                 </c:pt>
+                <c:pt idx="150">
+                  <c:v>6.63</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -7118,6 +7133,9 @@
                   <c:v>7.75</c:v>
                 </c:pt>
                 <c:pt idx="149">
+                  <c:v>7.75</c:v>
+                </c:pt>
+                <c:pt idx="150">
                   <c:v>7.75</c:v>
                 </c:pt>
               </c:numCache>
@@ -7353,6 +7371,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -7360,7 +7379,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -7396,7 +7414,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7917,6 +7935,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -7924,7 +7943,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -7960,7 +7978,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -8368,6 +8386,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -8375,7 +8394,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -10462,17 +10480,17 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:Y153"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.125" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.26953125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="5" customFormat="1">
       <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
@@ -10549,7 +10567,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -10618,7 +10636,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="12">
         <v>46044</v>
       </c>
@@ -10695,7 +10713,7 @@
         <v>4.9450000000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="12">
         <v>46045</v>
       </c>
@@ -10772,7 +10790,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="12">
         <v>46045</v>
       </c>
@@ -10849,7 +10867,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="12">
         <v>46045</v>
       </c>
@@ -10926,7 +10944,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="12">
         <v>46048</v>
       </c>
@@ -11003,7 +11021,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25">
       <c r="A8" s="12">
         <v>46048</v>
       </c>
@@ -11080,7 +11098,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25">
       <c r="A9" s="12">
         <v>46048</v>
       </c>
@@ -11157,7 +11175,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25">
       <c r="A10" s="12">
         <v>46049</v>
       </c>
@@ -11234,7 +11252,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25">
       <c r="A11" s="12">
         <v>46049</v>
       </c>
@@ -11311,7 +11329,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25">
       <c r="A12" s="12">
         <v>46049</v>
       </c>
@@ -11388,7 +11406,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25">
       <c r="A13" s="12">
         <v>46050</v>
       </c>
@@ -11465,7 +11483,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25">
       <c r="A14" s="12">
         <v>46050</v>
       </c>
@@ -11542,7 +11560,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25">
       <c r="A15" s="12">
         <v>46050</v>
       </c>
@@ -11619,7 +11637,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25">
       <c r="A16" s="12">
         <v>46051</v>
       </c>
@@ -11696,7 +11714,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:25">
       <c r="A17" s="12">
         <v>46051</v>
       </c>
@@ -11773,7 +11791,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:25">
       <c r="A18" s="12">
         <v>46051</v>
       </c>
@@ -11850,7 +11868,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:25">
       <c r="A19" s="12">
         <v>46052</v>
       </c>
@@ -11927,7 +11945,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:25">
       <c r="A20" s="12">
         <v>46052</v>
       </c>
@@ -12004,7 +12022,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:25">
       <c r="A21" s="12">
         <v>46052</v>
       </c>
@@ -12081,7 +12099,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:25">
       <c r="A22" s="12">
         <v>46055</v>
       </c>
@@ -12158,7 +12176,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:25">
       <c r="A23" s="12">
         <v>46055</v>
       </c>
@@ -12235,7 +12253,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:25">
       <c r="A24" s="12">
         <v>46055</v>
       </c>
@@ -12312,7 +12330,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:25">
       <c r="A25" s="12">
         <v>46056</v>
       </c>
@@ -12389,7 +12407,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:25">
       <c r="A26" s="12">
         <v>46056</v>
       </c>
@@ -12466,7 +12484,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:25">
       <c r="A27" s="12">
         <v>46056</v>
       </c>
@@ -12543,7 +12561,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:25">
       <c r="A28" s="12">
         <v>46057</v>
       </c>
@@ -12620,7 +12638,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:25">
       <c r="A29" s="12">
         <v>46057</v>
       </c>
@@ -12697,7 +12715,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:25">
       <c r="A30" s="12">
         <v>46057</v>
       </c>
@@ -12774,7 +12792,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:25">
       <c r="A31" s="12">
         <v>46058</v>
       </c>
@@ -12851,7 +12869,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:25">
       <c r="A32" s="12">
         <v>46058</v>
       </c>
@@ -12928,7 +12946,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:25">
       <c r="A33" s="12">
         <v>46058</v>
       </c>
@@ -13005,7 +13023,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:25">
       <c r="A34" s="12">
         <v>46059</v>
       </c>
@@ -13082,7 +13100,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:25">
       <c r="A35" s="12">
         <v>46059</v>
       </c>
@@ -13159,7 +13177,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:25">
       <c r="A36" s="12">
         <v>46059</v>
       </c>
@@ -13236,7 +13254,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:25">
       <c r="A37" s="12">
         <v>46062</v>
       </c>
@@ -13313,7 +13331,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:25">
       <c r="A38" s="12">
         <v>46062</v>
       </c>
@@ -13390,7 +13408,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:25">
       <c r="A39" s="12">
         <v>46062</v>
       </c>
@@ -13467,7 +13485,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:25">
       <c r="A40" s="12">
         <v>46063</v>
       </c>
@@ -13544,7 +13562,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:25">
       <c r="A41" s="12">
         <v>46063</v>
       </c>
@@ -13621,7 +13639,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:25">
       <c r="A42" s="12">
         <v>46063</v>
       </c>
@@ -13698,7 +13716,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:25">
       <c r="A43" s="12">
         <v>46064</v>
       </c>
@@ -13775,7 +13793,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:25">
       <c r="A44" s="12">
         <v>46064</v>
       </c>
@@ -13852,7 +13870,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:25">
       <c r="A45" s="12">
         <v>46064</v>
       </c>
@@ -13929,7 +13947,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:25">
       <c r="A46" s="12">
         <v>46065</v>
       </c>
@@ -14006,7 +14024,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:25">
       <c r="A47" s="12">
         <v>46065</v>
       </c>
@@ -14083,7 +14101,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:25">
       <c r="A48" s="12">
         <v>46065</v>
       </c>
@@ -14160,7 +14178,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:25">
       <c r="A49" s="12">
         <v>46066</v>
       </c>
@@ -14237,7 +14255,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:25">
       <c r="A50" s="12">
         <v>46066</v>
       </c>
@@ -14314,7 +14332,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:25">
       <c r="A51" s="12">
         <v>46066</v>
       </c>
@@ -14391,7 +14409,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:25">
       <c r="A52" s="12">
         <v>46076</v>
       </c>
@@ -14468,7 +14486,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:25">
       <c r="A53" s="12">
         <v>46076</v>
       </c>
@@ -14545,7 +14563,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:25">
       <c r="A54" s="12">
         <v>46076</v>
       </c>
@@ -14622,7 +14640,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:25">
       <c r="A55" s="12">
         <v>46077</v>
       </c>
@@ -14699,7 +14717,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:25">
       <c r="A56" s="12">
         <v>46077</v>
       </c>
@@ -14776,7 +14794,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:25">
       <c r="A57" s="12">
         <v>46077</v>
       </c>
@@ -14853,7 +14871,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:25">
       <c r="A58" s="12">
         <v>46078</v>
       </c>
@@ -14930,7 +14948,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:25">
       <c r="A59" s="12">
         <v>46078</v>
       </c>
@@ -15007,7 +15025,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:25">
       <c r="A60" s="12">
         <v>46078</v>
       </c>
@@ -15084,7 +15102,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="61" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:25">
       <c r="A61" s="12">
         <v>46079</v>
       </c>
@@ -15161,7 +15179,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="62" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:25">
       <c r="A62" s="12">
         <v>46079</v>
       </c>
@@ -15238,7 +15256,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="63" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:25">
       <c r="A63" s="12">
         <v>46079</v>
       </c>
@@ -15315,7 +15333,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="64" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:25">
       <c r="A64" s="12">
         <v>46080</v>
       </c>
@@ -15392,7 +15410,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="65" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:25">
       <c r="A65" s="12">
         <v>46080</v>
       </c>
@@ -15469,7 +15487,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="66" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:25">
       <c r="A66" s="12">
         <v>46080</v>
       </c>
@@ -15546,7 +15564,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="67" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:25">
       <c r="A67" s="12">
         <v>46083</v>
       </c>
@@ -15623,7 +15641,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="68" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:25">
       <c r="A68" s="12">
         <v>46083</v>
       </c>
@@ -15700,7 +15718,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="69" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:25">
       <c r="A69" s="12">
         <v>46083</v>
       </c>
@@ -15777,7 +15795,7 @@
         <v>5.68</v>
       </c>
     </row>
-    <row r="70" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:25">
       <c r="A70" s="12">
         <v>46084</v>
       </c>
@@ -15854,7 +15872,7 @@
         <v>5.7590000000000003</v>
       </c>
     </row>
-    <row r="71" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:25">
       <c r="A71" s="12">
         <v>46084</v>
       </c>
@@ -15931,7 +15949,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="72" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:25">
       <c r="A72" s="12">
         <v>46084</v>
       </c>
@@ -16008,7 +16026,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="73" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:25">
       <c r="A73" s="12">
         <v>46085</v>
       </c>
@@ -16085,7 +16103,7 @@
         <v>5.8390000000000004</v>
       </c>
     </row>
-    <row r="74" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:25">
       <c r="A74" s="12">
         <v>46085</v>
       </c>
@@ -16162,7 +16180,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:25">
       <c r="A75" s="12">
         <v>46085</v>
       </c>
@@ -16239,7 +16257,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:25">
       <c r="A76" s="12">
         <v>46086</v>
       </c>
@@ -16316,7 +16334,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="77" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:25">
       <c r="A77" s="12">
         <v>46086</v>
       </c>
@@ -16393,7 +16411,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="78" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:25">
       <c r="A78" s="12">
         <v>46086</v>
       </c>
@@ -16470,7 +16488,7 @@
         <v>5.9210000000000003</v>
       </c>
     </row>
-    <row r="79" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:25">
       <c r="A79" s="12">
         <v>46087</v>
       </c>
@@ -16547,7 +16565,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="80" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:25">
       <c r="A80" s="12">
         <v>46087</v>
       </c>
@@ -16624,7 +16642,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="81" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:25">
       <c r="A81" s="12">
         <v>46087</v>
       </c>
@@ -16701,7 +16719,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="82" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:25">
       <c r="A82" s="12">
         <v>46090</v>
       </c>
@@ -16778,7 +16796,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="83" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:25">
       <c r="A83" s="12">
         <v>46090</v>
       </c>
@@ -16855,7 +16873,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="84" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:25">
       <c r="A84" s="12">
         <v>46090</v>
       </c>
@@ -16932,7 +16950,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="85" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:25">
       <c r="A85" s="12">
         <v>46091</v>
       </c>
@@ -17009,7 +17027,7 @@
         <v>6.157</v>
       </c>
     </row>
-    <row r="86" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:25">
       <c r="A86" s="12">
         <v>46091</v>
       </c>
@@ -17086,7 +17104,7 @@
         <v>6.181</v>
       </c>
     </row>
-    <row r="87" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:25">
       <c r="A87" s="12">
         <v>46091</v>
       </c>
@@ -17163,7 +17181,7 @@
         <v>6.181</v>
       </c>
     </row>
-    <row r="88" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:25">
       <c r="A88" s="12">
         <v>46092</v>
       </c>
@@ -17240,7 +17258,7 @@
         <v>6.2430000000000003</v>
       </c>
     </row>
-    <row r="89" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:25">
       <c r="A89" s="12">
         <v>46092</v>
       </c>
@@ -17317,7 +17335,7 @@
         <v>6.29</v>
       </c>
     </row>
-    <row r="90" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:25">
       <c r="A90" s="12">
         <v>46092</v>
       </c>
@@ -17394,7 +17412,7 @@
         <v>6.3049999999999997</v>
       </c>
     </row>
-    <row r="91" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:25">
       <c r="A91" s="12">
         <v>46093</v>
       </c>
@@ -17471,7 +17489,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="92" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:25">
       <c r="A92" s="12">
         <v>46093</v>
       </c>
@@ -17548,7 +17566,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="93" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:25">
       <c r="A93" s="12">
         <v>46093</v>
       </c>
@@ -17625,7 +17643,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="94" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:25">
       <c r="A94" s="12">
         <v>46094</v>
       </c>
@@ -17702,7 +17720,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="95" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:25">
       <c r="A95" s="12">
         <v>46094</v>
       </c>
@@ -17779,7 +17797,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="96" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:25">
       <c r="A96" s="12">
         <v>46094</v>
       </c>
@@ -17856,7 +17874,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="97" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:25">
       <c r="A97" s="12">
         <v>46097</v>
       </c>
@@ -17933,7 +17951,7 @@
         <v>6.5330000000000004</v>
       </c>
     </row>
-    <row r="98" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:25">
       <c r="A98" s="12">
         <v>46097</v>
       </c>
@@ -18010,7 +18028,7 @@
         <v>6.5119999999999996</v>
       </c>
     </row>
-    <row r="99" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:25">
       <c r="A99" s="12">
         <v>46097</v>
       </c>
@@ -18087,7 +18105,7 @@
         <v>6.5119999999999996</v>
       </c>
     </row>
-    <row r="100" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:25">
       <c r="A100" s="12">
         <v>46098</v>
       </c>
@@ -18164,7 +18182,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="101" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:25">
       <c r="A101" s="12">
         <v>46098</v>
       </c>
@@ -18241,7 +18259,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="102" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:25">
       <c r="A102" s="12">
         <v>46098</v>
       </c>
@@ -18318,7 +18336,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="103" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:25">
       <c r="A103" s="12">
         <v>46099</v>
       </c>
@@ -18395,7 +18413,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="104" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:25">
       <c r="A104" s="12">
         <v>46099</v>
       </c>
@@ -18472,7 +18490,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="105" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:25">
       <c r="A105" s="12">
         <v>46099</v>
       </c>
@@ -18549,7 +18567,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="106" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:25">
       <c r="A106" s="12">
         <v>46100</v>
       </c>
@@ -18626,7 +18644,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="107" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:25">
       <c r="A107" s="12">
         <v>46100</v>
       </c>
@@ -18703,7 +18721,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="108" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:25">
       <c r="A108" s="12">
         <v>46100</v>
       </c>
@@ -18780,7 +18798,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="109" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:25">
       <c r="A109" s="12">
         <v>46101</v>
       </c>
@@ -18857,7 +18875,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="110" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:25">
       <c r="A110" s="12">
         <v>46101</v>
       </c>
@@ -18934,7 +18952,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="111" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:25">
       <c r="A111" s="12">
         <v>46101</v>
       </c>
@@ -19011,7 +19029,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="112" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:25">
       <c r="A112" s="12">
         <v>46104</v>
       </c>
@@ -19088,7 +19106,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="113" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:25">
       <c r="A113" s="12">
         <v>46104</v>
       </c>
@@ -19165,7 +19183,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="114" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:25">
       <c r="A114" s="12">
         <v>46104</v>
       </c>
@@ -19242,7 +19260,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="115" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:25">
       <c r="A115" s="12">
         <v>46105</v>
       </c>
@@ -19319,7 +19337,7 @@
         <v>7.0250000000000004</v>
       </c>
     </row>
-    <row r="116" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:25">
       <c r="A116" s="12">
         <v>46105</v>
       </c>
@@ -19396,7 +19414,7 @@
         <v>7.125</v>
       </c>
     </row>
-    <row r="117" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:25">
       <c r="A117" s="12">
         <v>46105</v>
       </c>
@@ -19473,7 +19491,7 @@
         <v>7.125</v>
       </c>
     </row>
-    <row r="118" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:25">
       <c r="A118" s="12">
         <v>46106</v>
       </c>
@@ -19550,7 +19568,7 @@
         <v>7.15</v>
       </c>
     </row>
-    <row r="119" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:25">
       <c r="A119" s="12">
         <v>46106</v>
       </c>
@@ -19627,7 +19645,7 @@
         <v>7.2249999999999996</v>
       </c>
     </row>
-    <row r="120" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:25">
       <c r="A120" s="12">
         <v>46106</v>
       </c>
@@ -19704,7 +19722,7 @@
         <v>7.2249999999999996</v>
       </c>
     </row>
-    <row r="121" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:25">
       <c r="A121" s="12">
         <v>46107</v>
       </c>
@@ -19781,7 +19799,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="122" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:25">
       <c r="A122" s="12">
         <v>46107</v>
       </c>
@@ -19858,7 +19876,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="123" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:25">
       <c r="A123" s="12">
         <v>46107</v>
       </c>
@@ -19935,7 +19953,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="124" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:25">
       <c r="A124" s="12">
         <v>46108</v>
       </c>
@@ -20012,7 +20030,7 @@
         <v>7.375</v>
       </c>
     </row>
-    <row r="125" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:25">
       <c r="A125" s="12">
         <v>46108</v>
       </c>
@@ -20089,7 +20107,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="126" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:25">
       <c r="A126" s="12">
         <v>46108</v>
       </c>
@@ -20166,7 +20184,7 @@
         <v>7.375</v>
       </c>
     </row>
-    <row r="127" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:25">
       <c r="A127" s="12">
         <v>46111</v>
       </c>
@@ -20243,7 +20261,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="128" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:25">
       <c r="A128" s="12">
         <v>46111</v>
       </c>
@@ -20320,7 +20338,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="129" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:25">
       <c r="A129" s="12">
         <v>46111</v>
       </c>
@@ -20397,7 +20415,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="130" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:25">
       <c r="A130" s="12">
         <v>46112</v>
       </c>
@@ -20474,7 +20492,7 @@
         <v>7.5250000000000004</v>
       </c>
     </row>
-    <row r="131" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:25">
       <c r="A131" s="12">
         <v>46112</v>
       </c>
@@ -20551,7 +20569,7 @@
         <v>7.5250000000000004</v>
       </c>
     </row>
-    <row r="132" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:25">
       <c r="A132" s="12">
         <v>46112</v>
       </c>
@@ -20628,7 +20646,7 @@
         <v>7.55</v>
       </c>
     </row>
-    <row r="133" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:25">
       <c r="A133" s="12">
         <v>46113</v>
       </c>
@@ -20705,7 +20723,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="134" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:25">
       <c r="A134" s="12">
         <v>46113</v>
       </c>
@@ -20782,7 +20800,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="135" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:25">
       <c r="A135" s="12">
         <v>46113</v>
       </c>
@@ -20859,7 +20877,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="136" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:25">
       <c r="A136" s="12">
         <v>46114</v>
       </c>
@@ -20936,7 +20954,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="137" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:25">
       <c r="A137" s="12">
         <v>46114</v>
       </c>
@@ -21013,7 +21031,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="138" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:25">
       <c r="A138" s="12">
         <v>46114</v>
       </c>
@@ -21090,7 +21108,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="139" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:25">
       <c r="A139" s="12">
         <v>46115</v>
       </c>
@@ -21167,7 +21185,7 @@
         <v>7.6749999999999998</v>
       </c>
     </row>
-    <row r="140" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:25">
       <c r="A140" s="12">
         <v>46115</v>
       </c>
@@ -21244,7 +21262,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="141" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:25">
       <c r="A141" s="12">
         <v>46115</v>
       </c>
@@ -21321,7 +21339,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="142" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:25">
       <c r="A142" s="12">
         <v>46119</v>
       </c>
@@ -21398,7 +21416,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="143" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:25">
       <c r="A143" s="12">
         <v>46119</v>
       </c>
@@ -21475,7 +21493,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="144" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:25">
       <c r="A144" s="12">
         <v>46119</v>
       </c>
@@ -21552,7 +21570,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="145" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:25">
       <c r="A145" s="12">
         <v>46120</v>
       </c>
@@ -21629,7 +21647,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="146" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:25">
       <c r="A146" s="12">
         <v>46120</v>
       </c>
@@ -21706,7 +21724,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="147" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:25">
       <c r="A147" s="12">
         <v>46120</v>
       </c>
@@ -21783,7 +21801,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="148" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:25">
       <c r="A148" s="12">
         <v>46121</v>
       </c>
@@ -21860,7 +21878,7 @@
         <v>7.7249999999999996</v>
       </c>
     </row>
-    <row r="149" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:25">
       <c r="A149" s="12">
         <v>46121</v>
       </c>
@@ -21937,7 +21955,7 @@
         <v>7.7249999999999996</v>
       </c>
     </row>
-    <row r="150" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:25">
       <c r="A150" s="12">
         <v>46121</v>
       </c>
@@ -22014,7 +22032,7 @@
         <v>7.7249999999999996</v>
       </c>
     </row>
-    <row r="151" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:25">
       <c r="A151" s="12">
         <v>46122</v>
       </c>
@@ -22091,7 +22109,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="152" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:25">
       <c r="A152" s="12">
         <v>46122</v>
       </c>
@@ -22168,7 +22186,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="153" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:25">
       <c r="A153" s="12">
         <v>46122</v>
       </c>
@@ -22180,6 +22198,69 @@
       </c>
       <c r="D153" s="7" t="s">
         <v>53</v>
+      </c>
+      <c r="E153" s="11">
+        <v>48.5</v>
+      </c>
+      <c r="F153" s="11">
+        <v>26.5</v>
+      </c>
+      <c r="G153" s="11">
+        <v>37.033000000000001</v>
+      </c>
+      <c r="H153" s="11">
+        <v>24</v>
+      </c>
+      <c r="I153" s="11">
+        <v>20.5</v>
+      </c>
+      <c r="J153" s="11">
+        <v>21.3</v>
+      </c>
+      <c r="K153" s="11">
+        <v>88</v>
+      </c>
+      <c r="L153" s="11">
+        <v>27</v>
+      </c>
+      <c r="M153" s="11">
+        <v>71.5</v>
+      </c>
+      <c r="N153" s="11">
+        <v>14.8</v>
+      </c>
+      <c r="O153" s="11">
+        <v>12.9</v>
+      </c>
+      <c r="P153" s="11">
+        <v>13.5</v>
+      </c>
+      <c r="Q153" s="11">
+        <v>49</v>
+      </c>
+      <c r="R153" s="11">
+        <v>13</v>
+      </c>
+      <c r="S153" s="11">
+        <v>33.4</v>
+      </c>
+      <c r="T153" s="11">
+        <v>7.5</v>
+      </c>
+      <c r="U153" s="11">
+        <v>5.45</v>
+      </c>
+      <c r="V153" s="11">
+        <v>6.63</v>
+      </c>
+      <c r="W153" s="11">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="X153" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="Y153" s="11">
+        <v>7.75</v>
       </c>
     </row>
   </sheetData>
@@ -22199,19 +22280,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3E2CD10-06F7-40BE-85D8-E29219BBD9A9}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:AK6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.36328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.26953125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="9" style="11"/>
-    <col min="8" max="10" width="9.125" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:37" s="5" customFormat="1">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -22300,7 +22381,7 @@
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:37">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -22381,7 +22462,7 @@
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:37">
       <c r="A3" s="6">
         <v>45962</v>
       </c>
@@ -22470,7 +22551,7 @@
       <c r="AJ3" s="2"/>
       <c r="AK3" s="2"/>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:37">
       <c r="A4" s="6">
         <v>45992</v>
       </c>
@@ -22559,7 +22640,7 @@
       <c r="AJ4" s="2"/>
       <c r="AK4" s="2"/>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37">
       <c r="A5" s="6">
         <v>46023</v>
       </c>
@@ -22591,7 +22672,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37">
       <c r="A6" s="6">
         <v>46054</v>
       </c>
@@ -22684,24 +22765,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3556165B-22F0-4AF5-853E-ED25EB5C0B71}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:Y12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.125" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="14"/>
-    <col min="7" max="7" width="9.125" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.453125" style="14" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="14"/>
-    <col min="10" max="10" width="9.125" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="9" style="14"/>
-    <col min="13" max="13" width="9.125" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="5" customFormat="1">
       <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
@@ -22754,7 +22835,7 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -22799,7 +22880,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -22852,7 +22933,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -22905,7 +22986,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -22946,7 +23027,7 @@
         <v>118.333</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -22987,7 +23068,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -23028,7 +23109,7 @@
         <v>122.667</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25">
       <c r="A8" s="12">
         <v>46083</v>
       </c>
@@ -23069,7 +23150,7 @@
         <v>123.333</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25">
       <c r="A9" s="12">
         <v>46090</v>
       </c>
@@ -23110,7 +23191,7 @@
         <v>126.667</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25">
       <c r="A10" s="12">
         <v>46097</v>
       </c>
@@ -23151,7 +23232,7 @@
         <v>132.333</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25">
       <c r="A11" s="12">
         <v>46104</v>
       </c>
@@ -23192,7 +23273,7 @@
         <v>143.333</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25">
       <c r="A12" s="12">
         <v>46111</v>
       </c>
@@ -23250,18 +23331,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C550C51-95E6-4243-AC05-025707E45857}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:Y12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.625" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.6328125" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="5" customFormat="1">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -23308,7 +23389,7 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -23347,7 +23428,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -23394,7 +23475,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -23441,7 +23522,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -23473,7 +23554,7 @@
         <v>9.6539999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -23505,7 +23586,7 @@
         <v>9.8650000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -23537,7 +23618,7 @@
         <v>10.221</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25">
       <c r="A8" s="12">
         <v>46083</v>
       </c>
@@ -23569,7 +23650,7 @@
         <v>10.721</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25">
       <c r="A9" s="12">
         <v>46090</v>
       </c>
@@ -23601,7 +23682,7 @@
         <v>11.462</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25">
       <c r="A10" s="12">
         <v>46097</v>
       </c>
@@ -23633,7 +23714,7 @@
         <v>11.962</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25">
       <c r="A11" s="12">
         <v>46104</v>
       </c>
@@ -23665,7 +23746,7 @@
         <v>12.865</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25">
       <c r="A12" s="12">
         <v>46111</v>
       </c>
@@ -23713,7 +23794,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BD8F7D3-2DB0-479E-83DC-4D765C588609}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="16384" width="9" style="3"/>
   </cols>
@@ -23728,15 +23809,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="22.875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.875" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.90625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.90625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.6328125" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>48</v>
       </c>
@@ -23747,7 +23828,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
@@ -23761,7 +23842,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="s">
         <v>29</v>
@@ -23770,7 +23851,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>31</v>
@@ -23779,7 +23860,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
         <v>33</v>
@@ -23788,7 +23869,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4">
       <c r="A6" s="1"/>
       <c r="B6" s="2" t="s">
         <v>35</v>
@@ -23797,7 +23878,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
         <v>37</v>
@@ -23806,7 +23887,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
         <v>39</v>
@@ -23815,7 +23896,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
         <v>41</v>
       </c>
@@ -23824,49 +23905,49 @@
       </c>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4">
       <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4">
       <c r="A12" s="1"/>
       <c r="B12" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4">
       <c r="A14" s="1"/>
       <c r="B14" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4">
       <c r="A15" s="1"/>
       <c r="B15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4">
       <c r="A16" s="1" t="s">
         <v>42</v>
       </c>
@@ -23877,7 +23958,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3">
       <c r="A17" s="1"/>
       <c r="B17" s="2" t="s">
         <v>8</v>
@@ -23886,7 +23967,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3">
       <c r="A18" s="1"/>
       <c r="B18" s="2" t="s">
         <v>9</v>
@@ -23895,7 +23976,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3">
       <c r="A19" s="1" t="s">
         <v>44</v>
       </c>
@@ -23906,7 +23987,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3">
       <c r="A20" s="1"/>
       <c r="B20" s="2" t="s">
         <v>11</v>
@@ -23915,7 +23996,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3">
       <c r="A21" s="1" t="s">
         <v>45</v>
       </c>
@@ -23924,42 +24005,42 @@
       </c>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3">
       <c r="A22" s="1"/>
       <c r="B22" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3">
       <c r="A23" s="1"/>
       <c r="B23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3">
       <c r="A24" s="1"/>
       <c r="B24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3">
       <c r="A25" s="1"/>
       <c r="B25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3">
       <c r="A26" s="1"/>
       <c r="B26" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3">
       <c r="A27" s="1" t="s">
         <v>46</v>
       </c>
@@ -23968,35 +24049,35 @@
       </c>
       <c r="C27" s="2"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3">
       <c r="A28" s="1"/>
       <c r="B28" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C28" s="2"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3">
       <c r="A29" s="1"/>
       <c r="B29" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C29" s="2"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3">
       <c r="A30" s="1"/>
       <c r="B30" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C30" s="2"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3">
       <c r="A31" s="1"/>
       <c r="B31" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C31" s="2"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3">
       <c r="A32" s="1"/>
       <c r="B32" s="2" t="s">
         <v>23</v>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82324EB5-987E-4CE3-A042-F5F822F6681D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D063FFBD-DD72-4C97-939A-9997EE9741A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -898,6 +898,15 @@
                 <c:pt idx="153">
                   <c:v>46125</c:v>
                 </c:pt>
+                <c:pt idx="154">
+                  <c:v>46126</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>46126</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>46126</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1364,6 +1373,15 @@
                   <c:v>37.033000000000001</c:v>
                 </c:pt>
                 <c:pt idx="152">
+                  <c:v>37.1</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>37.1</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>37.1</c:v>
+                </c:pt>
+                <c:pt idx="155">
                   <c:v>37.1</c:v>
                 </c:pt>
               </c:numCache>
@@ -1873,6 +1891,15 @@
                 <c:pt idx="153">
                   <c:v>46125</c:v>
                 </c:pt>
+                <c:pt idx="154">
+                  <c:v>46126</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>46126</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>46126</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2339,6 +2366,15 @@
                   <c:v>21.3</c:v>
                 </c:pt>
                 <c:pt idx="152">
+                  <c:v>21.3</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>21.3</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>21.3</c:v>
+                </c:pt>
+                <c:pt idx="155">
                   <c:v>21.3</c:v>
                 </c:pt>
               </c:numCache>
@@ -2848,6 +2884,15 @@
                 <c:pt idx="153">
                   <c:v>46125</c:v>
                 </c:pt>
+                <c:pt idx="154">
+                  <c:v>46126</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>46126</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>46126</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3315,6 +3360,15 @@
                 </c:pt>
                 <c:pt idx="152">
                   <c:v>71.182000000000002</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>71.182000000000002</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>70.954999999999998</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>70.727000000000004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3823,6 +3877,15 @@
                 <c:pt idx="153">
                   <c:v>46125</c:v>
                 </c:pt>
+                <c:pt idx="154">
+                  <c:v>46126</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>46126</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>46126</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4289,6 +4352,15 @@
                   <c:v>13.475</c:v>
                 </c:pt>
                 <c:pt idx="152">
+                  <c:v>13.475</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>13.475</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>13.475</c:v>
+                </c:pt>
+                <c:pt idx="155">
                   <c:v>13.475</c:v>
                 </c:pt>
               </c:numCache>
@@ -4798,6 +4870,15 @@
                 <c:pt idx="153">
                   <c:v>46125</c:v>
                 </c:pt>
+                <c:pt idx="154">
+                  <c:v>46126</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>46126</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>46126</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5264,6 +5345,15 @@
                   <c:v>33.4</c:v>
                 </c:pt>
                 <c:pt idx="152">
+                  <c:v>33.4</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>33.4</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>33.4</c:v>
+                </c:pt>
+                <c:pt idx="155">
                   <c:v>33.4</c:v>
                 </c:pt>
               </c:numCache>
@@ -5789,6 +5879,15 @@
                 <c:pt idx="153">
                   <c:v>46125</c:v>
                 </c:pt>
+                <c:pt idx="154">
+                  <c:v>46126</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>46126</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>46126</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6256,6 +6355,15 @@
                 </c:pt>
                 <c:pt idx="152">
                   <c:v>6.61</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>6.61</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>6.57</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>6.57</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6766,6 +6874,15 @@
                 <c:pt idx="153">
                   <c:v>46125</c:v>
                 </c:pt>
+                <c:pt idx="154">
+                  <c:v>46126</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>46126</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>46126</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7232,6 +7349,15 @@
                   <c:v>7.8</c:v>
                 </c:pt>
                 <c:pt idx="152">
+                  <c:v>7.8</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>7.8</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>7.8</c:v>
+                </c:pt>
+                <c:pt idx="155">
                   <c:v>7.8</c:v>
                 </c:pt>
               </c:numCache>
@@ -7903,7 +8029,7 @@
         <c:axId val="1526098480"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="46203"/>
+          <c:max val="46387"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -7949,7 +8075,7 @@
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
-        <c:majorUnit val="1"/>
+        <c:majorUnit val="2"/>
         <c:majorTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
@@ -8365,7 +8491,7 @@
         <c:axId val="1668066848"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="46203"/>
+          <c:max val="46387"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -8411,7 +8537,7 @@
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
-        <c:majorUnit val="1"/>
+        <c:majorUnit val="2"/>
         <c:majorTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
@@ -10605,7 +10731,7 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y156"/>
+  <dimension ref="A1:Y159"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="12" bestFit="1" customWidth="1"/>
@@ -22554,6 +22680,237 @@
         <v>0.75694444444444453</v>
       </c>
       <c r="D156" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E156" s="11">
+        <v>49</v>
+      </c>
+      <c r="F156" s="11">
+        <v>26.5</v>
+      </c>
+      <c r="G156" s="11">
+        <v>37.1</v>
+      </c>
+      <c r="H156" s="11">
+        <v>24</v>
+      </c>
+      <c r="I156" s="11">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="J156" s="11">
+        <v>21.3</v>
+      </c>
+      <c r="K156" s="11">
+        <v>87.5</v>
+      </c>
+      <c r="L156" s="11">
+        <v>27.5</v>
+      </c>
+      <c r="M156" s="11">
+        <v>71.182000000000002</v>
+      </c>
+      <c r="N156" s="11">
+        <v>14.7</v>
+      </c>
+      <c r="O156" s="11">
+        <v>12.9</v>
+      </c>
+      <c r="P156" s="11">
+        <v>13.475</v>
+      </c>
+      <c r="Q156" s="11">
+        <v>49.3</v>
+      </c>
+      <c r="R156" s="11">
+        <v>13.2</v>
+      </c>
+      <c r="S156" s="11">
+        <v>33.4</v>
+      </c>
+      <c r="T156" s="11">
+        <v>7.5</v>
+      </c>
+      <c r="U156" s="11">
+        <v>5.4</v>
+      </c>
+      <c r="V156" s="11">
+        <v>6.61</v>
+      </c>
+      <c r="W156" s="11">
+        <v>10</v>
+      </c>
+      <c r="X156" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="Y156" s="11">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="157" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A157" s="12">
+        <v>46126</v>
+      </c>
+      <c r="B157" s="12">
+        <v>46126</v>
+      </c>
+      <c r="C157" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D157" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E157" s="11">
+        <v>49</v>
+      </c>
+      <c r="F157" s="11">
+        <v>26.5</v>
+      </c>
+      <c r="G157" s="11">
+        <v>37.1</v>
+      </c>
+      <c r="H157" s="11">
+        <v>24</v>
+      </c>
+      <c r="I157" s="11">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="J157" s="11">
+        <v>21.3</v>
+      </c>
+      <c r="K157" s="11">
+        <v>87.5</v>
+      </c>
+      <c r="L157" s="11">
+        <v>28</v>
+      </c>
+      <c r="M157" s="11">
+        <v>70.954999999999998</v>
+      </c>
+      <c r="N157" s="11">
+        <v>14.7</v>
+      </c>
+      <c r="O157" s="11">
+        <v>12.9</v>
+      </c>
+      <c r="P157" s="11">
+        <v>13.475</v>
+      </c>
+      <c r="Q157" s="11">
+        <v>49.3</v>
+      </c>
+      <c r="R157" s="11">
+        <v>13.5</v>
+      </c>
+      <c r="S157" s="11">
+        <v>33.4</v>
+      </c>
+      <c r="T157" s="11">
+        <v>7.4</v>
+      </c>
+      <c r="U157" s="11">
+        <v>5.4</v>
+      </c>
+      <c r="V157" s="11">
+        <v>6.57</v>
+      </c>
+      <c r="W157" s="11">
+        <v>10</v>
+      </c>
+      <c r="X157" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="Y157" s="11">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="158" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A158" s="12">
+        <v>46126</v>
+      </c>
+      <c r="B158" s="12">
+        <v>46126</v>
+      </c>
+      <c r="C158" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D158" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E158" s="11">
+        <v>49</v>
+      </c>
+      <c r="F158" s="11">
+        <v>26.5</v>
+      </c>
+      <c r="G158" s="11">
+        <v>37.1</v>
+      </c>
+      <c r="H158" s="11">
+        <v>24</v>
+      </c>
+      <c r="I158" s="11">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="J158" s="11">
+        <v>21.3</v>
+      </c>
+      <c r="K158" s="11">
+        <v>87.5</v>
+      </c>
+      <c r="L158" s="11">
+        <v>28</v>
+      </c>
+      <c r="M158" s="11">
+        <v>70.727000000000004</v>
+      </c>
+      <c r="N158" s="11">
+        <v>14.7</v>
+      </c>
+      <c r="O158" s="11">
+        <v>12.9</v>
+      </c>
+      <c r="P158" s="11">
+        <v>13.475</v>
+      </c>
+      <c r="Q158" s="11">
+        <v>49.3</v>
+      </c>
+      <c r="R158" s="11">
+        <v>13.5</v>
+      </c>
+      <c r="S158" s="11">
+        <v>33.4</v>
+      </c>
+      <c r="T158" s="11">
+        <v>7.4</v>
+      </c>
+      <c r="U158" s="11">
+        <v>5.4</v>
+      </c>
+      <c r="V158" s="11">
+        <v>6.57</v>
+      </c>
+      <c r="W158" s="11">
+        <v>10</v>
+      </c>
+      <c r="X158" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="Y158" s="11">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="159" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A159" s="12">
+        <v>46126</v>
+      </c>
+      <c r="B159" s="12">
+        <v>46126</v>
+      </c>
+      <c r="C159" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D159" s="7" t="s">
         <v>53</v>
       </c>
     </row>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EA62476-1871-4DBA-BFCE-FB62E18C7426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6582E0DD-050C-4C7A-9BDA-387EF56B9AB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -244,23 +244,23 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -273,7 +273,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -316,7 +316,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -337,27 +337,27 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -365,8 +365,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -384,7 +384,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -916,6 +916,15 @@
                 <c:pt idx="159">
                   <c:v>46127</c:v>
                 </c:pt>
+                <c:pt idx="160">
+                  <c:v>46128</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>46128</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>46128</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1401,6 +1410,18 @@
                 </c:pt>
                 <c:pt idx="158">
                   <c:v>37.466999999999999</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>37.433</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>37.700000000000003</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>37.700000000000003</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>37.700000000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1927,6 +1948,15 @@
                 <c:pt idx="159">
                   <c:v>46127</c:v>
                 </c:pt>
+                <c:pt idx="160">
+                  <c:v>46128</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>46128</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>46128</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2411,6 +2441,18 @@
                   <c:v>21.5</c:v>
                 </c:pt>
                 <c:pt idx="158">
+                  <c:v>21.5</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>21.5</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>21.5</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>21.5</c:v>
+                </c:pt>
+                <c:pt idx="162">
                   <c:v>21.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -2938,6 +2980,15 @@
                 <c:pt idx="159">
                   <c:v>46127</c:v>
                 </c:pt>
+                <c:pt idx="160">
+                  <c:v>46128</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>46128</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>46128</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3423,6 +3474,18 @@
                 </c:pt>
                 <c:pt idx="158">
                   <c:v>70.5</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>70.5</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>69.454999999999998</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>69.454999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3949,6 +4012,15 @@
                 <c:pt idx="159">
                   <c:v>46127</c:v>
                 </c:pt>
+                <c:pt idx="160">
+                  <c:v>46128</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>46128</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>46128</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4433,6 +4505,18 @@
                   <c:v>13.475</c:v>
                 </c:pt>
                 <c:pt idx="158">
+                  <c:v>13.475</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>13.475</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>13.475</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>13.475</c:v>
+                </c:pt>
+                <c:pt idx="162">
                   <c:v>13.475</c:v>
                 </c:pt>
               </c:numCache>
@@ -4960,6 +5044,15 @@
                 <c:pt idx="159">
                   <c:v>46127</c:v>
                 </c:pt>
+                <c:pt idx="160">
+                  <c:v>46128</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>46128</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>46128</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5445,6 +5538,18 @@
                 </c:pt>
                 <c:pt idx="158">
                   <c:v>33.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>33.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>33.1</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>33.1</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>33.1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5987,6 +6092,15 @@
                 <c:pt idx="159">
                   <c:v>46127</c:v>
                 </c:pt>
+                <c:pt idx="160">
+                  <c:v>46128</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>46128</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>46128</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6472,6 +6586,18 @@
                 </c:pt>
                 <c:pt idx="158">
                   <c:v>6.53</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>6.53</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>6.49</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>6.49</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>6.49</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7000,6 +7126,15 @@
                 <c:pt idx="159">
                   <c:v>46127</c:v>
                 </c:pt>
+                <c:pt idx="160">
+                  <c:v>46128</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>46128</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>46128</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7485,6 +7620,18 @@
                 </c:pt>
                 <c:pt idx="158">
                   <c:v>7.85</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>7.8630000000000004</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>7.8630000000000004</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>7.9749999999999996</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>7.9749999999999996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7762,7 +7909,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -8344,7 +8491,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -10857,18 +11004,18 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y162"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:Y165"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.09765625" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.09765625" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.296875" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.26953125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="5" customFormat="1">
       <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
@@ -10945,7 +11092,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -11014,7 +11161,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="12">
         <v>46044</v>
       </c>
@@ -11091,7 +11238,7 @@
         <v>4.9450000000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="12">
         <v>46045</v>
       </c>
@@ -11168,7 +11315,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="12">
         <v>46045</v>
       </c>
@@ -11245,7 +11392,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="12">
         <v>46045</v>
       </c>
@@ -11322,7 +11469,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="12">
         <v>46048</v>
       </c>
@@ -11399,7 +11546,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25">
       <c r="A8" s="12">
         <v>46048</v>
       </c>
@@ -11476,7 +11623,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25">
       <c r="A9" s="12">
         <v>46048</v>
       </c>
@@ -11553,7 +11700,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25">
       <c r="A10" s="12">
         <v>46049</v>
       </c>
@@ -11630,7 +11777,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25">
       <c r="A11" s="12">
         <v>46049</v>
       </c>
@@ -11707,7 +11854,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25">
       <c r="A12" s="12">
         <v>46049</v>
       </c>
@@ -11784,7 +11931,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25">
       <c r="A13" s="12">
         <v>46050</v>
       </c>
@@ -11861,7 +12008,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25">
       <c r="A14" s="12">
         <v>46050</v>
       </c>
@@ -11938,7 +12085,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25">
       <c r="A15" s="12">
         <v>46050</v>
       </c>
@@ -12015,7 +12162,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25">
       <c r="A16" s="12">
         <v>46051</v>
       </c>
@@ -12092,7 +12239,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:25">
       <c r="A17" s="12">
         <v>46051</v>
       </c>
@@ -12169,7 +12316,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:25">
       <c r="A18" s="12">
         <v>46051</v>
       </c>
@@ -12246,7 +12393,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:25">
       <c r="A19" s="12">
         <v>46052</v>
       </c>
@@ -12323,7 +12470,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:25">
       <c r="A20" s="12">
         <v>46052</v>
       </c>
@@ -12400,7 +12547,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:25">
       <c r="A21" s="12">
         <v>46052</v>
       </c>
@@ -12477,7 +12624,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:25">
       <c r="A22" s="12">
         <v>46055</v>
       </c>
@@ -12554,7 +12701,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:25">
       <c r="A23" s="12">
         <v>46055</v>
       </c>
@@ -12631,7 +12778,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:25">
       <c r="A24" s="12">
         <v>46055</v>
       </c>
@@ -12708,7 +12855,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:25">
       <c r="A25" s="12">
         <v>46056</v>
       </c>
@@ -12785,7 +12932,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:25">
       <c r="A26" s="12">
         <v>46056</v>
       </c>
@@ -12862,7 +13009,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:25">
       <c r="A27" s="12">
         <v>46056</v>
       </c>
@@ -12939,7 +13086,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:25">
       <c r="A28" s="12">
         <v>46057</v>
       </c>
@@ -13016,7 +13163,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:25">
       <c r="A29" s="12">
         <v>46057</v>
       </c>
@@ -13093,7 +13240,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:25">
       <c r="A30" s="12">
         <v>46057</v>
       </c>
@@ -13170,7 +13317,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:25">
       <c r="A31" s="12">
         <v>46058</v>
       </c>
@@ -13247,7 +13394,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:25">
       <c r="A32" s="12">
         <v>46058</v>
       </c>
@@ -13324,7 +13471,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:25">
       <c r="A33" s="12">
         <v>46058</v>
       </c>
@@ -13401,7 +13548,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:25">
       <c r="A34" s="12">
         <v>46059</v>
       </c>
@@ -13478,7 +13625,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:25">
       <c r="A35" s="12">
         <v>46059</v>
       </c>
@@ -13555,7 +13702,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:25">
       <c r="A36" s="12">
         <v>46059</v>
       </c>
@@ -13632,7 +13779,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:25">
       <c r="A37" s="12">
         <v>46062</v>
       </c>
@@ -13709,7 +13856,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:25">
       <c r="A38" s="12">
         <v>46062</v>
       </c>
@@ -13786,7 +13933,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:25">
       <c r="A39" s="12">
         <v>46062</v>
       </c>
@@ -13863,7 +14010,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:25">
       <c r="A40" s="12">
         <v>46063</v>
       </c>
@@ -13940,7 +14087,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:25">
       <c r="A41" s="12">
         <v>46063</v>
       </c>
@@ -14017,7 +14164,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:25">
       <c r="A42" s="12">
         <v>46063</v>
       </c>
@@ -14094,7 +14241,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:25">
       <c r="A43" s="12">
         <v>46064</v>
       </c>
@@ -14171,7 +14318,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:25">
       <c r="A44" s="12">
         <v>46064</v>
       </c>
@@ -14248,7 +14395,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:25">
       <c r="A45" s="12">
         <v>46064</v>
       </c>
@@ -14325,7 +14472,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:25">
       <c r="A46" s="12">
         <v>46065</v>
       </c>
@@ -14402,7 +14549,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:25">
       <c r="A47" s="12">
         <v>46065</v>
       </c>
@@ -14479,7 +14626,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:25">
       <c r="A48" s="12">
         <v>46065</v>
       </c>
@@ -14556,7 +14703,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:25">
       <c r="A49" s="12">
         <v>46066</v>
       </c>
@@ -14633,7 +14780,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:25">
       <c r="A50" s="12">
         <v>46066</v>
       </c>
@@ -14710,7 +14857,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:25">
       <c r="A51" s="12">
         <v>46066</v>
       </c>
@@ -14787,7 +14934,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:25">
       <c r="A52" s="12">
         <v>46076</v>
       </c>
@@ -14864,7 +15011,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:25">
       <c r="A53" s="12">
         <v>46076</v>
       </c>
@@ -14941,7 +15088,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:25">
       <c r="A54" s="12">
         <v>46076</v>
       </c>
@@ -15018,7 +15165,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:25">
       <c r="A55" s="12">
         <v>46077</v>
       </c>
@@ -15095,7 +15242,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:25">
       <c r="A56" s="12">
         <v>46077</v>
       </c>
@@ -15172,7 +15319,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:25">
       <c r="A57" s="12">
         <v>46077</v>
       </c>
@@ -15249,7 +15396,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:25">
       <c r="A58" s="12">
         <v>46078</v>
       </c>
@@ -15326,7 +15473,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:25">
       <c r="A59" s="12">
         <v>46078</v>
       </c>
@@ -15403,7 +15550,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:25">
       <c r="A60" s="12">
         <v>46078</v>
       </c>
@@ -15480,7 +15627,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="61" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:25">
       <c r="A61" s="12">
         <v>46079</v>
       </c>
@@ -15557,7 +15704,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="62" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:25">
       <c r="A62" s="12">
         <v>46079</v>
       </c>
@@ -15634,7 +15781,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="63" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:25">
       <c r="A63" s="12">
         <v>46079</v>
       </c>
@@ -15711,7 +15858,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="64" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:25">
       <c r="A64" s="12">
         <v>46080</v>
       </c>
@@ -15788,7 +15935,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="65" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:25">
       <c r="A65" s="12">
         <v>46080</v>
       </c>
@@ -15865,7 +16012,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="66" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:25">
       <c r="A66" s="12">
         <v>46080</v>
       </c>
@@ -15942,7 +16089,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="67" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:25">
       <c r="A67" s="12">
         <v>46083</v>
       </c>
@@ -16019,7 +16166,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="68" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:25">
       <c r="A68" s="12">
         <v>46083</v>
       </c>
@@ -16096,7 +16243,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="69" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:25">
       <c r="A69" s="12">
         <v>46083</v>
       </c>
@@ -16173,7 +16320,7 @@
         <v>5.68</v>
       </c>
     </row>
-    <row r="70" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:25">
       <c r="A70" s="12">
         <v>46084</v>
       </c>
@@ -16250,7 +16397,7 @@
         <v>5.7590000000000003</v>
       </c>
     </row>
-    <row r="71" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:25">
       <c r="A71" s="12">
         <v>46084</v>
       </c>
@@ -16327,7 +16474,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="72" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:25">
       <c r="A72" s="12">
         <v>46084</v>
       </c>
@@ -16404,7 +16551,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="73" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:25">
       <c r="A73" s="12">
         <v>46085</v>
       </c>
@@ -16481,7 +16628,7 @@
         <v>5.8390000000000004</v>
       </c>
     </row>
-    <row r="74" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:25">
       <c r="A74" s="12">
         <v>46085</v>
       </c>
@@ -16558,7 +16705,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:25">
       <c r="A75" s="12">
         <v>46085</v>
       </c>
@@ -16635,7 +16782,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:25">
       <c r="A76" s="12">
         <v>46086</v>
       </c>
@@ -16712,7 +16859,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="77" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:25">
       <c r="A77" s="12">
         <v>46086</v>
       </c>
@@ -16789,7 +16936,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="78" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:25">
       <c r="A78" s="12">
         <v>46086</v>
       </c>
@@ -16866,7 +17013,7 @@
         <v>5.9210000000000003</v>
       </c>
     </row>
-    <row r="79" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:25">
       <c r="A79" s="12">
         <v>46087</v>
       </c>
@@ -16943,7 +17090,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="80" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:25">
       <c r="A80" s="12">
         <v>46087</v>
       </c>
@@ -17020,7 +17167,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="81" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:25">
       <c r="A81" s="12">
         <v>46087</v>
       </c>
@@ -17097,7 +17244,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="82" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:25">
       <c r="A82" s="12">
         <v>46090</v>
       </c>
@@ -17174,7 +17321,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="83" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:25">
       <c r="A83" s="12">
         <v>46090</v>
       </c>
@@ -17251,7 +17398,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="84" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:25">
       <c r="A84" s="12">
         <v>46090</v>
       </c>
@@ -17328,7 +17475,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="85" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:25">
       <c r="A85" s="12">
         <v>46091</v>
       </c>
@@ -17405,7 +17552,7 @@
         <v>6.157</v>
       </c>
     </row>
-    <row r="86" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:25">
       <c r="A86" s="12">
         <v>46091</v>
       </c>
@@ -17482,7 +17629,7 @@
         <v>6.181</v>
       </c>
     </row>
-    <row r="87" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:25">
       <c r="A87" s="12">
         <v>46091</v>
       </c>
@@ -17559,7 +17706,7 @@
         <v>6.181</v>
       </c>
     </row>
-    <row r="88" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:25">
       <c r="A88" s="12">
         <v>46092</v>
       </c>
@@ -17636,7 +17783,7 @@
         <v>6.2430000000000003</v>
       </c>
     </row>
-    <row r="89" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:25">
       <c r="A89" s="12">
         <v>46092</v>
       </c>
@@ -17713,7 +17860,7 @@
         <v>6.29</v>
       </c>
     </row>
-    <row r="90" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:25">
       <c r="A90" s="12">
         <v>46092</v>
       </c>
@@ -17790,7 +17937,7 @@
         <v>6.3049999999999997</v>
       </c>
     </row>
-    <row r="91" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:25">
       <c r="A91" s="12">
         <v>46093</v>
       </c>
@@ -17867,7 +18014,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="92" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:25">
       <c r="A92" s="12">
         <v>46093</v>
       </c>
@@ -17944,7 +18091,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="93" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:25">
       <c r="A93" s="12">
         <v>46093</v>
       </c>
@@ -18021,7 +18168,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="94" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:25">
       <c r="A94" s="12">
         <v>46094</v>
       </c>
@@ -18098,7 +18245,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="95" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:25">
       <c r="A95" s="12">
         <v>46094</v>
       </c>
@@ -18175,7 +18322,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="96" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:25">
       <c r="A96" s="12">
         <v>46094</v>
       </c>
@@ -18252,7 +18399,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="97" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:25">
       <c r="A97" s="12">
         <v>46097</v>
       </c>
@@ -18329,7 +18476,7 @@
         <v>6.5330000000000004</v>
       </c>
     </row>
-    <row r="98" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:25">
       <c r="A98" s="12">
         <v>46097</v>
       </c>
@@ -18406,7 +18553,7 @@
         <v>6.5119999999999996</v>
       </c>
     </row>
-    <row r="99" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:25">
       <c r="A99" s="12">
         <v>46097</v>
       </c>
@@ -18483,7 +18630,7 @@
         <v>6.5119999999999996</v>
       </c>
     </row>
-    <row r="100" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:25">
       <c r="A100" s="12">
         <v>46098</v>
       </c>
@@ -18560,7 +18707,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="101" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:25">
       <c r="A101" s="12">
         <v>46098</v>
       </c>
@@ -18637,7 +18784,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="102" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:25">
       <c r="A102" s="12">
         <v>46098</v>
       </c>
@@ -18714,7 +18861,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="103" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:25">
       <c r="A103" s="12">
         <v>46099</v>
       </c>
@@ -18791,7 +18938,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="104" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:25">
       <c r="A104" s="12">
         <v>46099</v>
       </c>
@@ -18868,7 +19015,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="105" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:25">
       <c r="A105" s="12">
         <v>46099</v>
       </c>
@@ -18945,7 +19092,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="106" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:25">
       <c r="A106" s="12">
         <v>46100</v>
       </c>
@@ -19022,7 +19169,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="107" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:25">
       <c r="A107" s="12">
         <v>46100</v>
       </c>
@@ -19099,7 +19246,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="108" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:25">
       <c r="A108" s="12">
         <v>46100</v>
       </c>
@@ -19176,7 +19323,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="109" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:25">
       <c r="A109" s="12">
         <v>46101</v>
       </c>
@@ -19253,7 +19400,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="110" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:25">
       <c r="A110" s="12">
         <v>46101</v>
       </c>
@@ -19330,7 +19477,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="111" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:25">
       <c r="A111" s="12">
         <v>46101</v>
       </c>
@@ -19407,7 +19554,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="112" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:25">
       <c r="A112" s="12">
         <v>46104</v>
       </c>
@@ -19484,7 +19631,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="113" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:25">
       <c r="A113" s="12">
         <v>46104</v>
       </c>
@@ -19561,7 +19708,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="114" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:25">
       <c r="A114" s="12">
         <v>46104</v>
       </c>
@@ -19638,7 +19785,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="115" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:25">
       <c r="A115" s="12">
         <v>46105</v>
       </c>
@@ -19715,7 +19862,7 @@
         <v>7.0250000000000004</v>
       </c>
     </row>
-    <row r="116" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:25">
       <c r="A116" s="12">
         <v>46105</v>
       </c>
@@ -19792,7 +19939,7 @@
         <v>7.125</v>
       </c>
     </row>
-    <row r="117" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:25">
       <c r="A117" s="12">
         <v>46105</v>
       </c>
@@ -19869,7 +20016,7 @@
         <v>7.125</v>
       </c>
     </row>
-    <row r="118" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:25">
       <c r="A118" s="12">
         <v>46106</v>
       </c>
@@ -19946,7 +20093,7 @@
         <v>7.15</v>
       </c>
     </row>
-    <row r="119" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:25">
       <c r="A119" s="12">
         <v>46106</v>
       </c>
@@ -20023,7 +20170,7 @@
         <v>7.2249999999999996</v>
       </c>
     </row>
-    <row r="120" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:25">
       <c r="A120" s="12">
         <v>46106</v>
       </c>
@@ -20100,7 +20247,7 @@
         <v>7.2249999999999996</v>
       </c>
     </row>
-    <row r="121" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:25">
       <c r="A121" s="12">
         <v>46107</v>
       </c>
@@ -20177,7 +20324,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="122" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:25">
       <c r="A122" s="12">
         <v>46107</v>
       </c>
@@ -20254,7 +20401,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="123" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:25">
       <c r="A123" s="12">
         <v>46107</v>
       </c>
@@ -20331,7 +20478,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="124" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:25">
       <c r="A124" s="12">
         <v>46108</v>
       </c>
@@ -20408,7 +20555,7 @@
         <v>7.375</v>
       </c>
     </row>
-    <row r="125" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:25">
       <c r="A125" s="12">
         <v>46108</v>
       </c>
@@ -20485,7 +20632,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="126" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:25">
       <c r="A126" s="12">
         <v>46108</v>
       </c>
@@ -20562,7 +20709,7 @@
         <v>7.375</v>
       </c>
     </row>
-    <row r="127" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:25">
       <c r="A127" s="12">
         <v>46111</v>
       </c>
@@ -20639,7 +20786,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="128" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:25">
       <c r="A128" s="12">
         <v>46111</v>
       </c>
@@ -20716,7 +20863,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="129" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:25">
       <c r="A129" s="12">
         <v>46111</v>
       </c>
@@ -20793,7 +20940,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="130" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:25">
       <c r="A130" s="12">
         <v>46112</v>
       </c>
@@ -20870,7 +21017,7 @@
         <v>7.5250000000000004</v>
       </c>
     </row>
-    <row r="131" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:25">
       <c r="A131" s="12">
         <v>46112</v>
       </c>
@@ -20947,7 +21094,7 @@
         <v>7.5250000000000004</v>
       </c>
     </row>
-    <row r="132" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:25">
       <c r="A132" s="12">
         <v>46112</v>
       </c>
@@ -21024,7 +21171,7 @@
         <v>7.55</v>
       </c>
     </row>
-    <row r="133" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:25">
       <c r="A133" s="12">
         <v>46113</v>
       </c>
@@ -21101,7 +21248,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="134" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:25">
       <c r="A134" s="12">
         <v>46113</v>
       </c>
@@ -21178,7 +21325,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="135" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:25">
       <c r="A135" s="12">
         <v>46113</v>
       </c>
@@ -21255,7 +21402,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="136" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:25">
       <c r="A136" s="12">
         <v>46114</v>
       </c>
@@ -21332,7 +21479,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="137" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:25">
       <c r="A137" s="12">
         <v>46114</v>
       </c>
@@ -21409,7 +21556,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="138" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:25">
       <c r="A138" s="12">
         <v>46114</v>
       </c>
@@ -21486,7 +21633,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="139" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:25">
       <c r="A139" s="12">
         <v>46115</v>
       </c>
@@ -21563,7 +21710,7 @@
         <v>7.6749999999999998</v>
       </c>
     </row>
-    <row r="140" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:25">
       <c r="A140" s="12">
         <v>46115</v>
       </c>
@@ -21640,7 +21787,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="141" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:25">
       <c r="A141" s="12">
         <v>46115</v>
       </c>
@@ -21717,7 +21864,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="142" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:25">
       <c r="A142" s="12">
         <v>46119</v>
       </c>
@@ -21794,7 +21941,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="143" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:25">
       <c r="A143" s="12">
         <v>46119</v>
       </c>
@@ -21871,7 +22018,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="144" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:25">
       <c r="A144" s="12">
         <v>46119</v>
       </c>
@@ -21948,7 +22095,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="145" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:25">
       <c r="A145" s="12">
         <v>46120</v>
       </c>
@@ -22025,7 +22172,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="146" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:25">
       <c r="A146" s="12">
         <v>46120</v>
       </c>
@@ -22102,7 +22249,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="147" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:25">
       <c r="A147" s="12">
         <v>46120</v>
       </c>
@@ -22179,7 +22326,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="148" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:25">
       <c r="A148" s="12">
         <v>46121</v>
       </c>
@@ -22256,7 +22403,7 @@
         <v>7.7249999999999996</v>
       </c>
     </row>
-    <row r="149" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:25">
       <c r="A149" s="12">
         <v>46121</v>
       </c>
@@ -22333,7 +22480,7 @@
         <v>7.7249999999999996</v>
       </c>
     </row>
-    <row r="150" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:25">
       <c r="A150" s="12">
         <v>46121</v>
       </c>
@@ -22410,7 +22557,7 @@
         <v>7.7249999999999996</v>
       </c>
     </row>
-    <row r="151" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:25">
       <c r="A151" s="12">
         <v>46122</v>
       </c>
@@ -22487,7 +22634,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="152" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:25">
       <c r="A152" s="12">
         <v>46122</v>
       </c>
@@ -22564,7 +22711,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="153" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:25">
       <c r="A153" s="12">
         <v>46122</v>
       </c>
@@ -22641,7 +22788,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="154" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:25">
       <c r="A154" s="12">
         <v>46125</v>
       </c>
@@ -22718,7 +22865,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="155" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:25">
       <c r="A155" s="12">
         <v>46125</v>
       </c>
@@ -22795,7 +22942,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="156" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:25">
       <c r="A156" s="12">
         <v>46125</v>
       </c>
@@ -22872,7 +23019,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="157" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:25">
       <c r="A157" s="12">
         <v>46126</v>
       </c>
@@ -22949,7 +23096,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="158" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:25">
       <c r="A158" s="12">
         <v>46126</v>
       </c>
@@ -23026,7 +23173,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="159" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:25">
       <c r="A159" s="12">
         <v>46126</v>
       </c>
@@ -23103,7 +23250,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="160" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:25">
       <c r="A160" s="12">
         <v>46127</v>
       </c>
@@ -23180,7 +23327,7 @@
         <v>7.85</v>
       </c>
     </row>
-    <row r="161" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:25">
       <c r="A161" s="12">
         <v>46127</v>
       </c>
@@ -23257,7 +23404,7 @@
         <v>7.85</v>
       </c>
     </row>
-    <row r="162" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:25">
       <c r="A162" s="12">
         <v>46127</v>
       </c>
@@ -23269,6 +23416,300 @@
       </c>
       <c r="D162" s="7" t="s">
         <v>53</v>
+      </c>
+      <c r="E162" s="11">
+        <v>49.5</v>
+      </c>
+      <c r="F162" s="11">
+        <v>27</v>
+      </c>
+      <c r="G162" s="11">
+        <v>37.433</v>
+      </c>
+      <c r="H162" s="11">
+        <v>24</v>
+      </c>
+      <c r="I162" s="11">
+        <v>20.6</v>
+      </c>
+      <c r="J162" s="11">
+        <v>21.5</v>
+      </c>
+      <c r="K162" s="11">
+        <v>87.5</v>
+      </c>
+      <c r="L162" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="M162" s="11">
+        <v>70.5</v>
+      </c>
+      <c r="N162" s="11">
+        <v>14.7</v>
+      </c>
+      <c r="O162" s="11">
+        <v>13</v>
+      </c>
+      <c r="P162" s="11">
+        <v>13.475</v>
+      </c>
+      <c r="Q162" s="11">
+        <v>49.3</v>
+      </c>
+      <c r="R162" s="11">
+        <v>14</v>
+      </c>
+      <c r="S162" s="11">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="T162" s="11">
+        <v>7.4</v>
+      </c>
+      <c r="U162" s="11">
+        <v>5.4</v>
+      </c>
+      <c r="V162" s="11">
+        <v>6.53</v>
+      </c>
+      <c r="W162" s="11">
+        <v>10.1</v>
+      </c>
+      <c r="X162" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="Y162" s="11">
+        <v>7.8630000000000004</v>
+      </c>
+    </row>
+    <row r="163" spans="1:25">
+      <c r="A163" s="12">
+        <v>46128</v>
+      </c>
+      <c r="B163" s="12">
+        <v>46128</v>
+      </c>
+      <c r="C163" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D163" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E163" s="11">
+        <v>49.5</v>
+      </c>
+      <c r="F163" s="11">
+        <v>28</v>
+      </c>
+      <c r="G163" s="11">
+        <v>37.700000000000003</v>
+      </c>
+      <c r="H163" s="11">
+        <v>24</v>
+      </c>
+      <c r="I163" s="11">
+        <v>20.6</v>
+      </c>
+      <c r="J163" s="11">
+        <v>21.5</v>
+      </c>
+      <c r="K163" s="11">
+        <v>87.5</v>
+      </c>
+      <c r="L163" s="11">
+        <v>29</v>
+      </c>
+      <c r="M163" s="11">
+        <v>70</v>
+      </c>
+      <c r="N163" s="11">
+        <v>14.7</v>
+      </c>
+      <c r="O163" s="11">
+        <v>13</v>
+      </c>
+      <c r="P163" s="11">
+        <v>13.475</v>
+      </c>
+      <c r="Q163" s="11">
+        <v>49.3</v>
+      </c>
+      <c r="R163" s="11">
+        <v>14.5</v>
+      </c>
+      <c r="S163" s="11">
+        <v>33.1</v>
+      </c>
+      <c r="T163" s="11">
+        <v>7.3</v>
+      </c>
+      <c r="U163" s="11">
+        <v>5.3</v>
+      </c>
+      <c r="V163" s="11">
+        <v>6.49</v>
+      </c>
+      <c r="W163" s="11">
+        <v>10.1</v>
+      </c>
+      <c r="X163" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="Y163" s="11">
+        <v>7.8630000000000004</v>
+      </c>
+    </row>
+    <row r="164" spans="1:25">
+      <c r="A164" s="12">
+        <v>46128</v>
+      </c>
+      <c r="B164" s="12">
+        <v>46128</v>
+      </c>
+      <c r="C164" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D164" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E164" s="11">
+        <v>49.5</v>
+      </c>
+      <c r="F164" s="11">
+        <v>28</v>
+      </c>
+      <c r="G164" s="11">
+        <v>37.700000000000003</v>
+      </c>
+      <c r="H164" s="11">
+        <v>24</v>
+      </c>
+      <c r="I164" s="11">
+        <v>20.6</v>
+      </c>
+      <c r="J164" s="11">
+        <v>21.5</v>
+      </c>
+      <c r="K164" s="11">
+        <v>87.5</v>
+      </c>
+      <c r="L164" s="11">
+        <v>29</v>
+      </c>
+      <c r="M164" s="11">
+        <v>69.454999999999998</v>
+      </c>
+      <c r="N164" s="11">
+        <v>14.7</v>
+      </c>
+      <c r="O164" s="11">
+        <v>13</v>
+      </c>
+      <c r="P164" s="11">
+        <v>13.475</v>
+      </c>
+      <c r="Q164" s="11">
+        <v>49.3</v>
+      </c>
+      <c r="R164" s="11">
+        <v>14.5</v>
+      </c>
+      <c r="S164" s="11">
+        <v>33.1</v>
+      </c>
+      <c r="T164" s="11">
+        <v>7.3</v>
+      </c>
+      <c r="U164" s="11">
+        <v>5.3</v>
+      </c>
+      <c r="V164" s="11">
+        <v>6.49</v>
+      </c>
+      <c r="W164" s="11">
+        <v>10.1</v>
+      </c>
+      <c r="X164" s="11">
+        <v>5.3</v>
+      </c>
+      <c r="Y164" s="11">
+        <v>7.9749999999999996</v>
+      </c>
+    </row>
+    <row r="165" spans="1:25">
+      <c r="A165" s="12">
+        <v>46128</v>
+      </c>
+      <c r="B165" s="12">
+        <v>46128</v>
+      </c>
+      <c r="C165" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D165" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E165" s="11">
+        <v>49.5</v>
+      </c>
+      <c r="F165" s="11">
+        <v>28</v>
+      </c>
+      <c r="G165" s="11">
+        <v>37.700000000000003</v>
+      </c>
+      <c r="H165" s="11">
+        <v>24</v>
+      </c>
+      <c r="I165" s="11">
+        <v>20.6</v>
+      </c>
+      <c r="J165" s="11">
+        <v>21.5</v>
+      </c>
+      <c r="K165" s="11">
+        <v>87.5</v>
+      </c>
+      <c r="L165" s="11">
+        <v>29</v>
+      </c>
+      <c r="M165" s="11">
+        <v>69.454999999999998</v>
+      </c>
+      <c r="N165" s="11">
+        <v>14.7</v>
+      </c>
+      <c r="O165" s="11">
+        <v>13</v>
+      </c>
+      <c r="P165" s="11">
+        <v>13.475</v>
+      </c>
+      <c r="Q165" s="11">
+        <v>49.3</v>
+      </c>
+      <c r="R165" s="11">
+        <v>14.5</v>
+      </c>
+      <c r="S165" s="11">
+        <v>33.1</v>
+      </c>
+      <c r="T165" s="11">
+        <v>7.3</v>
+      </c>
+      <c r="U165" s="11">
+        <v>5.3</v>
+      </c>
+      <c r="V165" s="11">
+        <v>6.49</v>
+      </c>
+      <c r="W165" s="11">
+        <v>10.1</v>
+      </c>
+      <c r="X165" s="11">
+        <v>5.3</v>
+      </c>
+      <c r="Y165" s="11">
+        <v>7.9749999999999996</v>
       </c>
     </row>
   </sheetData>
@@ -23288,19 +23729,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:AK6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.3984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.09765625" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.296875" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.36328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.26953125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="9" style="11"/>
-    <col min="8" max="10" width="9.09765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:37" s="5" customFormat="1">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -23389,7 +23830,7 @@
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:37">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -23470,7 +23911,7 @@
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:37">
       <c r="A3" s="6">
         <v>45962</v>
       </c>
@@ -23559,7 +24000,7 @@
       <c r="AJ3" s="2"/>
       <c r="AK3" s="2"/>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:37">
       <c r="A4" s="6">
         <v>45992</v>
       </c>
@@ -23648,7 +24089,7 @@
       <c r="AJ4" s="2"/>
       <c r="AK4" s="2"/>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37">
       <c r="A5" s="6">
         <v>46023</v>
       </c>
@@ -23680,7 +24121,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37">
       <c r="A6" s="6">
         <v>46054</v>
       </c>
@@ -23773,24 +24214,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:Y13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.09765625" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.09765625" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="14"/>
-    <col min="7" max="7" width="9.09765625" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.453125" style="14" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="14"/>
-    <col min="10" max="10" width="9.09765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="9" style="14"/>
-    <col min="13" max="13" width="13.296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.26953125" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="5" customFormat="1">
       <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
@@ -23843,7 +24284,7 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -23888,7 +24329,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -23941,7 +24382,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -23994,7 +24435,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -24035,7 +24476,7 @@
         <v>118.333</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -24076,7 +24517,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -24117,7 +24558,7 @@
         <v>122.667</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25">
       <c r="A8" s="12">
         <v>46083</v>
       </c>
@@ -24158,7 +24599,7 @@
         <v>123.333</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25">
       <c r="A9" s="12">
         <v>46090</v>
       </c>
@@ -24199,7 +24640,7 @@
         <v>126.667</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25">
       <c r="A10" s="12">
         <v>46097</v>
       </c>
@@ -24240,7 +24681,7 @@
         <v>132.333</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25">
       <c r="A11" s="12">
         <v>46104</v>
       </c>
@@ -24281,7 +24722,7 @@
         <v>143.333</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25">
       <c r="A12" s="12">
         <v>46111</v>
       </c>
@@ -24322,7 +24763,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25">
       <c r="A13" s="12">
         <v>46118</v>
       </c>
@@ -24380,18 +24821,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:Y13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.09765625" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.09765625" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.59765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.6328125" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="5" customFormat="1">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -24438,7 +24879,7 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -24477,7 +24918,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -24524,7 +24965,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -24571,7 +25012,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -24603,7 +25044,7 @@
         <v>9.6539999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -24635,7 +25076,7 @@
         <v>9.8650000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -24667,7 +25108,7 @@
         <v>10.221</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25">
       <c r="A8" s="12">
         <v>46083</v>
       </c>
@@ -24699,7 +25140,7 @@
         <v>10.721</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25">
       <c r="A9" s="12">
         <v>46090</v>
       </c>
@@ -24731,7 +25172,7 @@
         <v>11.462</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25">
       <c r="A10" s="12">
         <v>46097</v>
       </c>
@@ -24763,7 +25204,7 @@
         <v>11.962</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25">
       <c r="A11" s="12">
         <v>46104</v>
       </c>
@@ -24795,7 +25236,7 @@
         <v>12.865</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25">
       <c r="A12" s="12">
         <v>46111</v>
       </c>
@@ -24827,7 +25268,7 @@
         <v>12.71</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25">
       <c r="A13" s="12">
         <v>46118</v>
       </c>
@@ -24875,7 +25316,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="16384" width="9" style="3"/>
   </cols>
@@ -24890,15 +25331,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="22.8984375" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.8984375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.59765625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.90625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.90625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.6328125" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>48</v>
       </c>
@@ -24909,7 +25350,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
@@ -24923,7 +25364,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="s">
         <v>29</v>
@@ -24932,7 +25373,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>31</v>
@@ -24941,7 +25382,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
         <v>33</v>
@@ -24950,7 +25391,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4">
       <c r="A6" s="1"/>
       <c r="B6" s="2" t="s">
         <v>35</v>
@@ -24959,7 +25400,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
         <v>37</v>
@@ -24968,7 +25409,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
         <v>39</v>
@@ -24977,7 +25418,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
         <v>41</v>
       </c>
@@ -24986,49 +25427,49 @@
       </c>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4">
       <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4">
       <c r="A12" s="1"/>
       <c r="B12" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4">
       <c r="A14" s="1"/>
       <c r="B14" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4">
       <c r="A15" s="1"/>
       <c r="B15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4">
       <c r="A16" s="1" t="s">
         <v>42</v>
       </c>
@@ -25039,7 +25480,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3">
       <c r="A17" s="1"/>
       <c r="B17" s="2" t="s">
         <v>8</v>
@@ -25048,7 +25489,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3">
       <c r="A18" s="1"/>
       <c r="B18" s="2" t="s">
         <v>9</v>
@@ -25057,7 +25498,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3">
       <c r="A19" s="1" t="s">
         <v>44</v>
       </c>
@@ -25068,7 +25509,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3">
       <c r="A20" s="1"/>
       <c r="B20" s="2" t="s">
         <v>11</v>
@@ -25077,7 +25518,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3">
       <c r="A21" s="1" t="s">
         <v>45</v>
       </c>
@@ -25086,42 +25527,42 @@
       </c>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3">
       <c r="A22" s="1"/>
       <c r="B22" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3">
       <c r="A23" s="1"/>
       <c r="B23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3">
       <c r="A24" s="1"/>
       <c r="B24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3">
       <c r="A25" s="1"/>
       <c r="B25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3">
       <c r="A26" s="1"/>
       <c r="B26" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3">
       <c r="A27" s="1" t="s">
         <v>46</v>
       </c>
@@ -25130,35 +25571,35 @@
       </c>
       <c r="C27" s="2"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3">
       <c r="A28" s="1"/>
       <c r="B28" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C28" s="2"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3">
       <c r="A29" s="1"/>
       <c r="B29" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C29" s="2"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3">
       <c r="A30" s="1"/>
       <c r="B30" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C30" s="2"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3">
       <c r="A31" s="1"/>
       <c r="B31" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C31" s="2"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3">
       <c r="A32" s="1"/>
       <c r="B32" s="2" t="s">
         <v>23</v>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6582E0DD-050C-4C7A-9BDA-387EF56B9AB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DBC2416-D944-4263-B5B1-D1A38C4E2AB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -244,23 +244,23 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -273,7 +273,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -316,7 +316,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -337,27 +337,27 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -365,8 +365,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -384,7 +384,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -925,6 +925,15 @@
                 <c:pt idx="162">
                   <c:v>46128</c:v>
                 </c:pt>
+                <c:pt idx="163">
+                  <c:v>46129</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>46129</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>46129</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1422,6 +1431,12 @@
                 </c:pt>
                 <c:pt idx="162">
                   <c:v>37.700000000000003</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>37.832999999999998</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>38.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1957,6 +1972,15 @@
                 <c:pt idx="162">
                   <c:v>46128</c:v>
                 </c:pt>
+                <c:pt idx="163">
+                  <c:v>46129</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>46129</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>46129</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2454,6 +2478,12 @@
                 </c:pt>
                 <c:pt idx="162">
                   <c:v>21.5</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>21.5</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>21.7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2989,6 +3019,15 @@
                 <c:pt idx="162">
                   <c:v>46128</c:v>
                 </c:pt>
+                <c:pt idx="163">
+                  <c:v>46129</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>46129</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>46129</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3486,6 +3525,12 @@
                 </c:pt>
                 <c:pt idx="162">
                   <c:v>69.454999999999998</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>69.182000000000002</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>69.182000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4021,6 +4066,15 @@
                 <c:pt idx="162">
                   <c:v>46128</c:v>
                 </c:pt>
+                <c:pt idx="163">
+                  <c:v>46129</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>46129</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>46129</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4517,6 +4571,12 @@
                   <c:v>13.475</c:v>
                 </c:pt>
                 <c:pt idx="162">
+                  <c:v>13.475</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>13.475</c:v>
+                </c:pt>
+                <c:pt idx="164">
                   <c:v>13.475</c:v>
                 </c:pt>
               </c:numCache>
@@ -5053,6 +5113,15 @@
                 <c:pt idx="162">
                   <c:v>46128</c:v>
                 </c:pt>
+                <c:pt idx="163">
+                  <c:v>46129</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>46129</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>46129</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5550,6 +5619,12 @@
                 </c:pt>
                 <c:pt idx="162">
                   <c:v>33.1</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>33</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6101,6 +6176,15 @@
                 <c:pt idx="162">
                   <c:v>46128</c:v>
                 </c:pt>
+                <c:pt idx="163">
+                  <c:v>46129</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>46129</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>46129</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6598,6 +6682,12 @@
                 </c:pt>
                 <c:pt idx="162">
                   <c:v>6.49</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>6.43</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>6.43</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7135,6 +7225,15 @@
                 <c:pt idx="162">
                   <c:v>46128</c:v>
                 </c:pt>
+                <c:pt idx="163">
+                  <c:v>46129</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>46129</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>46129</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7632,6 +7731,12 @@
                 </c:pt>
                 <c:pt idx="162">
                   <c:v>7.9749999999999996</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>8.0250000000000004</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>8.0250000000000004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7909,7 +8014,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -8491,7 +8596,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -11004,18 +11109,18 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y165"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:Y168"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.26953125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.09765625" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.09765625" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.296875" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
+    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
@@ -11092,7 +11197,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -11161,7 +11266,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>46044</v>
       </c>
@@ -11238,7 +11343,7 @@
         <v>4.9450000000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>46045</v>
       </c>
@@ -11315,7 +11420,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <v>46045</v>
       </c>
@@ -11392,7 +11497,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
         <v>46045</v>
       </c>
@@ -11469,7 +11574,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
         <v>46048</v>
       </c>
@@ -11546,7 +11651,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="12">
         <v>46048</v>
       </c>
@@ -11623,7 +11728,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="12">
         <v>46048</v>
       </c>
@@ -11700,7 +11805,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="12">
         <v>46049</v>
       </c>
@@ -11777,7 +11882,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="12">
         <v>46049</v>
       </c>
@@ -11854,7 +11959,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" s="12">
         <v>46049</v>
       </c>
@@ -11931,7 +12036,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" s="12">
         <v>46050</v>
       </c>
@@ -12008,7 +12113,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A14" s="12">
         <v>46050</v>
       </c>
@@ -12085,7 +12190,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A15" s="12">
         <v>46050</v>
       </c>
@@ -12162,7 +12267,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="16" spans="1:25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A16" s="12">
         <v>46051</v>
       </c>
@@ -12239,7 +12344,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:25">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A17" s="12">
         <v>46051</v>
       </c>
@@ -12316,7 +12421,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:25">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A18" s="12">
         <v>46051</v>
       </c>
@@ -12393,7 +12498,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:25">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A19" s="12">
         <v>46052</v>
       </c>
@@ -12470,7 +12575,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="20" spans="1:25">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A20" s="12">
         <v>46052</v>
       </c>
@@ -12547,7 +12652,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="21" spans="1:25">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A21" s="12">
         <v>46052</v>
       </c>
@@ -12624,7 +12729,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="22" spans="1:25">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A22" s="12">
         <v>46055</v>
       </c>
@@ -12701,7 +12806,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="23" spans="1:25">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A23" s="12">
         <v>46055</v>
       </c>
@@ -12778,7 +12883,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="24" spans="1:25">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A24" s="12">
         <v>46055</v>
       </c>
@@ -12855,7 +12960,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="25" spans="1:25">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A25" s="12">
         <v>46056</v>
       </c>
@@ -12932,7 +13037,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="26" spans="1:25">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A26" s="12">
         <v>46056</v>
       </c>
@@ -13009,7 +13114,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="27" spans="1:25">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A27" s="12">
         <v>46056</v>
       </c>
@@ -13086,7 +13191,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="28" spans="1:25">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A28" s="12">
         <v>46057</v>
       </c>
@@ -13163,7 +13268,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="29" spans="1:25">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A29" s="12">
         <v>46057</v>
       </c>
@@ -13240,7 +13345,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="30" spans="1:25">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A30" s="12">
         <v>46057</v>
       </c>
@@ -13317,7 +13422,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="31" spans="1:25">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A31" s="12">
         <v>46058</v>
       </c>
@@ -13394,7 +13499,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="32" spans="1:25">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A32" s="12">
         <v>46058</v>
       </c>
@@ -13471,7 +13576,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="33" spans="1:25">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A33" s="12">
         <v>46058</v>
       </c>
@@ -13548,7 +13653,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="34" spans="1:25">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A34" s="12">
         <v>46059</v>
       </c>
@@ -13625,7 +13730,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:25">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A35" s="12">
         <v>46059</v>
       </c>
@@ -13702,7 +13807,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:25">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A36" s="12">
         <v>46059</v>
       </c>
@@ -13779,7 +13884,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:25">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A37" s="12">
         <v>46062</v>
       </c>
@@ -13856,7 +13961,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="38" spans="1:25">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A38" s="12">
         <v>46062</v>
       </c>
@@ -13933,7 +14038,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="39" spans="1:25">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A39" s="12">
         <v>46062</v>
       </c>
@@ -14010,7 +14115,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="40" spans="1:25">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A40" s="12">
         <v>46063</v>
       </c>
@@ -14087,7 +14192,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="41" spans="1:25">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A41" s="12">
         <v>46063</v>
       </c>
@@ -14164,7 +14269,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="42" spans="1:25">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A42" s="12">
         <v>46063</v>
       </c>
@@ -14241,7 +14346,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="43" spans="1:25">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A43" s="12">
         <v>46064</v>
       </c>
@@ -14318,7 +14423,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="44" spans="1:25">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A44" s="12">
         <v>46064</v>
       </c>
@@ -14395,7 +14500,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="45" spans="1:25">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A45" s="12">
         <v>46064</v>
       </c>
@@ -14472,7 +14577,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="46" spans="1:25">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A46" s="12">
         <v>46065</v>
       </c>
@@ -14549,7 +14654,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:25">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A47" s="12">
         <v>46065</v>
       </c>
@@ -14626,7 +14731,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:25">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A48" s="12">
         <v>46065</v>
       </c>
@@ -14703,7 +14808,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="49" spans="1:25">
+    <row r="49" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A49" s="12">
         <v>46066</v>
       </c>
@@ -14780,7 +14885,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:25">
+    <row r="50" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A50" s="12">
         <v>46066</v>
       </c>
@@ -14857,7 +14962,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:25">
+    <row r="51" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A51" s="12">
         <v>46066</v>
       </c>
@@ -14934,7 +15039,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:25">
+    <row r="52" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A52" s="12">
         <v>46076</v>
       </c>
@@ -15011,7 +15116,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="53" spans="1:25">
+    <row r="53" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A53" s="12">
         <v>46076</v>
       </c>
@@ -15088,7 +15193,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:25">
+    <row r="54" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A54" s="12">
         <v>46076</v>
       </c>
@@ -15165,7 +15270,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="55" spans="1:25">
+    <row r="55" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A55" s="12">
         <v>46077</v>
       </c>
@@ -15242,7 +15347,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="56" spans="1:25">
+    <row r="56" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A56" s="12">
         <v>46077</v>
       </c>
@@ -15319,7 +15424,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="57" spans="1:25">
+    <row r="57" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A57" s="12">
         <v>46077</v>
       </c>
@@ -15396,7 +15501,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="58" spans="1:25">
+    <row r="58" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A58" s="12">
         <v>46078</v>
       </c>
@@ -15473,7 +15578,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="59" spans="1:25">
+    <row r="59" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A59" s="12">
         <v>46078</v>
       </c>
@@ -15550,7 +15655,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="60" spans="1:25">
+    <row r="60" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A60" s="12">
         <v>46078</v>
       </c>
@@ -15627,7 +15732,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="61" spans="1:25">
+    <row r="61" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A61" s="12">
         <v>46079</v>
       </c>
@@ -15704,7 +15809,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="62" spans="1:25">
+    <row r="62" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A62" s="12">
         <v>46079</v>
       </c>
@@ -15781,7 +15886,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="63" spans="1:25">
+    <row r="63" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A63" s="12">
         <v>46079</v>
       </c>
@@ -15858,7 +15963,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="64" spans="1:25">
+    <row r="64" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A64" s="12">
         <v>46080</v>
       </c>
@@ -15935,7 +16040,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="65" spans="1:25">
+    <row r="65" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A65" s="12">
         <v>46080</v>
       </c>
@@ -16012,7 +16117,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="66" spans="1:25">
+    <row r="66" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A66" s="12">
         <v>46080</v>
       </c>
@@ -16089,7 +16194,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="67" spans="1:25">
+    <row r="67" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A67" s="12">
         <v>46083</v>
       </c>
@@ -16166,7 +16271,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="68" spans="1:25">
+    <row r="68" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A68" s="12">
         <v>46083</v>
       </c>
@@ -16243,7 +16348,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="69" spans="1:25">
+    <row r="69" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A69" s="12">
         <v>46083</v>
       </c>
@@ -16320,7 +16425,7 @@
         <v>5.68</v>
       </c>
     </row>
-    <row r="70" spans="1:25">
+    <row r="70" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A70" s="12">
         <v>46084</v>
       </c>
@@ -16397,7 +16502,7 @@
         <v>5.7590000000000003</v>
       </c>
     </row>
-    <row r="71" spans="1:25">
+    <row r="71" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A71" s="12">
         <v>46084</v>
       </c>
@@ -16474,7 +16579,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="72" spans="1:25">
+    <row r="72" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A72" s="12">
         <v>46084</v>
       </c>
@@ -16551,7 +16656,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="73" spans="1:25">
+    <row r="73" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A73" s="12">
         <v>46085</v>
       </c>
@@ -16628,7 +16733,7 @@
         <v>5.8390000000000004</v>
       </c>
     </row>
-    <row r="74" spans="1:25">
+    <row r="74" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A74" s="12">
         <v>46085</v>
       </c>
@@ -16705,7 +16810,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:25">
+    <row r="75" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A75" s="12">
         <v>46085</v>
       </c>
@@ -16782,7 +16887,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:25">
+    <row r="76" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A76" s="12">
         <v>46086</v>
       </c>
@@ -16859,7 +16964,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="77" spans="1:25">
+    <row r="77" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A77" s="12">
         <v>46086</v>
       </c>
@@ -16936,7 +17041,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="78" spans="1:25">
+    <row r="78" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A78" s="12">
         <v>46086</v>
       </c>
@@ -17013,7 +17118,7 @@
         <v>5.9210000000000003</v>
       </c>
     </row>
-    <row r="79" spans="1:25">
+    <row r="79" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A79" s="12">
         <v>46087</v>
       </c>
@@ -17090,7 +17195,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="80" spans="1:25">
+    <row r="80" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A80" s="12">
         <v>46087</v>
       </c>
@@ -17167,7 +17272,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="81" spans="1:25">
+    <row r="81" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A81" s="12">
         <v>46087</v>
       </c>
@@ -17244,7 +17349,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="82" spans="1:25">
+    <row r="82" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A82" s="12">
         <v>46090</v>
       </c>
@@ -17321,7 +17426,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="83" spans="1:25">
+    <row r="83" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A83" s="12">
         <v>46090</v>
       </c>
@@ -17398,7 +17503,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="84" spans="1:25">
+    <row r="84" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A84" s="12">
         <v>46090</v>
       </c>
@@ -17475,7 +17580,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="85" spans="1:25">
+    <row r="85" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A85" s="12">
         <v>46091</v>
       </c>
@@ -17552,7 +17657,7 @@
         <v>6.157</v>
       </c>
     </row>
-    <row r="86" spans="1:25">
+    <row r="86" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A86" s="12">
         <v>46091</v>
       </c>
@@ -17629,7 +17734,7 @@
         <v>6.181</v>
       </c>
     </row>
-    <row r="87" spans="1:25">
+    <row r="87" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A87" s="12">
         <v>46091</v>
       </c>
@@ -17706,7 +17811,7 @@
         <v>6.181</v>
       </c>
     </row>
-    <row r="88" spans="1:25">
+    <row r="88" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A88" s="12">
         <v>46092</v>
       </c>
@@ -17783,7 +17888,7 @@
         <v>6.2430000000000003</v>
       </c>
     </row>
-    <row r="89" spans="1:25">
+    <row r="89" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A89" s="12">
         <v>46092</v>
       </c>
@@ -17860,7 +17965,7 @@
         <v>6.29</v>
       </c>
     </row>
-    <row r="90" spans="1:25">
+    <row r="90" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A90" s="12">
         <v>46092</v>
       </c>
@@ -17937,7 +18042,7 @@
         <v>6.3049999999999997</v>
       </c>
     </row>
-    <row r="91" spans="1:25">
+    <row r="91" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A91" s="12">
         <v>46093</v>
       </c>
@@ -18014,7 +18119,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="92" spans="1:25">
+    <row r="92" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A92" s="12">
         <v>46093</v>
       </c>
@@ -18091,7 +18196,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="93" spans="1:25">
+    <row r="93" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A93" s="12">
         <v>46093</v>
       </c>
@@ -18168,7 +18273,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="94" spans="1:25">
+    <row r="94" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A94" s="12">
         <v>46094</v>
       </c>
@@ -18245,7 +18350,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="95" spans="1:25">
+    <row r="95" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A95" s="12">
         <v>46094</v>
       </c>
@@ -18322,7 +18427,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="96" spans="1:25">
+    <row r="96" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A96" s="12">
         <v>46094</v>
       </c>
@@ -18399,7 +18504,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="97" spans="1:25">
+    <row r="97" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A97" s="12">
         <v>46097</v>
       </c>
@@ -18476,7 +18581,7 @@
         <v>6.5330000000000004</v>
       </c>
     </row>
-    <row r="98" spans="1:25">
+    <row r="98" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A98" s="12">
         <v>46097</v>
       </c>
@@ -18553,7 +18658,7 @@
         <v>6.5119999999999996</v>
       </c>
     </row>
-    <row r="99" spans="1:25">
+    <row r="99" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A99" s="12">
         <v>46097</v>
       </c>
@@ -18630,7 +18735,7 @@
         <v>6.5119999999999996</v>
       </c>
     </row>
-    <row r="100" spans="1:25">
+    <row r="100" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A100" s="12">
         <v>46098</v>
       </c>
@@ -18707,7 +18812,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="101" spans="1:25">
+    <row r="101" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A101" s="12">
         <v>46098</v>
       </c>
@@ -18784,7 +18889,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="102" spans="1:25">
+    <row r="102" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A102" s="12">
         <v>46098</v>
       </c>
@@ -18861,7 +18966,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="103" spans="1:25">
+    <row r="103" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A103" s="12">
         <v>46099</v>
       </c>
@@ -18938,7 +19043,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="104" spans="1:25">
+    <row r="104" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A104" s="12">
         <v>46099</v>
       </c>
@@ -19015,7 +19120,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="105" spans="1:25">
+    <row r="105" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A105" s="12">
         <v>46099</v>
       </c>
@@ -19092,7 +19197,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="106" spans="1:25">
+    <row r="106" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A106" s="12">
         <v>46100</v>
       </c>
@@ -19169,7 +19274,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="107" spans="1:25">
+    <row r="107" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A107" s="12">
         <v>46100</v>
       </c>
@@ -19246,7 +19351,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="108" spans="1:25">
+    <row r="108" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A108" s="12">
         <v>46100</v>
       </c>
@@ -19323,7 +19428,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="109" spans="1:25">
+    <row r="109" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A109" s="12">
         <v>46101</v>
       </c>
@@ -19400,7 +19505,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="110" spans="1:25">
+    <row r="110" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A110" s="12">
         <v>46101</v>
       </c>
@@ -19477,7 +19582,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="111" spans="1:25">
+    <row r="111" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A111" s="12">
         <v>46101</v>
       </c>
@@ -19554,7 +19659,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="112" spans="1:25">
+    <row r="112" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A112" s="12">
         <v>46104</v>
       </c>
@@ -19631,7 +19736,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="113" spans="1:25">
+    <row r="113" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A113" s="12">
         <v>46104</v>
       </c>
@@ -19708,7 +19813,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="114" spans="1:25">
+    <row r="114" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A114" s="12">
         <v>46104</v>
       </c>
@@ -19785,7 +19890,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="115" spans="1:25">
+    <row r="115" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A115" s="12">
         <v>46105</v>
       </c>
@@ -19862,7 +19967,7 @@
         <v>7.0250000000000004</v>
       </c>
     </row>
-    <row r="116" spans="1:25">
+    <row r="116" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A116" s="12">
         <v>46105</v>
       </c>
@@ -19939,7 +20044,7 @@
         <v>7.125</v>
       </c>
     </row>
-    <row r="117" spans="1:25">
+    <row r="117" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A117" s="12">
         <v>46105</v>
       </c>
@@ -20016,7 +20121,7 @@
         <v>7.125</v>
       </c>
     </row>
-    <row r="118" spans="1:25">
+    <row r="118" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A118" s="12">
         <v>46106</v>
       </c>
@@ -20093,7 +20198,7 @@
         <v>7.15</v>
       </c>
     </row>
-    <row r="119" spans="1:25">
+    <row r="119" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A119" s="12">
         <v>46106</v>
       </c>
@@ -20170,7 +20275,7 @@
         <v>7.2249999999999996</v>
       </c>
     </row>
-    <row r="120" spans="1:25">
+    <row r="120" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A120" s="12">
         <v>46106</v>
       </c>
@@ -20247,7 +20352,7 @@
         <v>7.2249999999999996</v>
       </c>
     </row>
-    <row r="121" spans="1:25">
+    <row r="121" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A121" s="12">
         <v>46107</v>
       </c>
@@ -20324,7 +20429,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="122" spans="1:25">
+    <row r="122" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A122" s="12">
         <v>46107</v>
       </c>
@@ -20401,7 +20506,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="123" spans="1:25">
+    <row r="123" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A123" s="12">
         <v>46107</v>
       </c>
@@ -20478,7 +20583,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="124" spans="1:25">
+    <row r="124" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A124" s="12">
         <v>46108</v>
       </c>
@@ -20555,7 +20660,7 @@
         <v>7.375</v>
       </c>
     </row>
-    <row r="125" spans="1:25">
+    <row r="125" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A125" s="12">
         <v>46108</v>
       </c>
@@ -20632,7 +20737,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="126" spans="1:25">
+    <row r="126" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A126" s="12">
         <v>46108</v>
       </c>
@@ -20709,7 +20814,7 @@
         <v>7.375</v>
       </c>
     </row>
-    <row r="127" spans="1:25">
+    <row r="127" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A127" s="12">
         <v>46111</v>
       </c>
@@ -20786,7 +20891,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="128" spans="1:25">
+    <row r="128" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A128" s="12">
         <v>46111</v>
       </c>
@@ -20863,7 +20968,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="129" spans="1:25">
+    <row r="129" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A129" s="12">
         <v>46111</v>
       </c>
@@ -20940,7 +21045,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="130" spans="1:25">
+    <row r="130" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A130" s="12">
         <v>46112</v>
       </c>
@@ -21017,7 +21122,7 @@
         <v>7.5250000000000004</v>
       </c>
     </row>
-    <row r="131" spans="1:25">
+    <row r="131" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A131" s="12">
         <v>46112</v>
       </c>
@@ -21094,7 +21199,7 @@
         <v>7.5250000000000004</v>
       </c>
     </row>
-    <row r="132" spans="1:25">
+    <row r="132" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A132" s="12">
         <v>46112</v>
       </c>
@@ -21171,7 +21276,7 @@
         <v>7.55</v>
       </c>
     </row>
-    <row r="133" spans="1:25">
+    <row r="133" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A133" s="12">
         <v>46113</v>
       </c>
@@ -21248,7 +21353,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="134" spans="1:25">
+    <row r="134" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A134" s="12">
         <v>46113</v>
       </c>
@@ -21325,7 +21430,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="135" spans="1:25">
+    <row r="135" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A135" s="12">
         <v>46113</v>
       </c>
@@ -21402,7 +21507,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="136" spans="1:25">
+    <row r="136" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A136" s="12">
         <v>46114</v>
       </c>
@@ -21479,7 +21584,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="137" spans="1:25">
+    <row r="137" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A137" s="12">
         <v>46114</v>
       </c>
@@ -21556,7 +21661,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="138" spans="1:25">
+    <row r="138" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A138" s="12">
         <v>46114</v>
       </c>
@@ -21633,7 +21738,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="139" spans="1:25">
+    <row r="139" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A139" s="12">
         <v>46115</v>
       </c>
@@ -21710,7 +21815,7 @@
         <v>7.6749999999999998</v>
       </c>
     </row>
-    <row r="140" spans="1:25">
+    <row r="140" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A140" s="12">
         <v>46115</v>
       </c>
@@ -21787,7 +21892,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="141" spans="1:25">
+    <row r="141" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A141" s="12">
         <v>46115</v>
       </c>
@@ -21864,7 +21969,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="142" spans="1:25">
+    <row r="142" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A142" s="12">
         <v>46119</v>
       </c>
@@ -21941,7 +22046,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="143" spans="1:25">
+    <row r="143" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A143" s="12">
         <v>46119</v>
       </c>
@@ -22018,7 +22123,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="144" spans="1:25">
+    <row r="144" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A144" s="12">
         <v>46119</v>
       </c>
@@ -22095,7 +22200,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="145" spans="1:25">
+    <row r="145" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A145" s="12">
         <v>46120</v>
       </c>
@@ -22172,7 +22277,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="146" spans="1:25">
+    <row r="146" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A146" s="12">
         <v>46120</v>
       </c>
@@ -22249,7 +22354,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="147" spans="1:25">
+    <row r="147" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A147" s="12">
         <v>46120</v>
       </c>
@@ -22326,7 +22431,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="148" spans="1:25">
+    <row r="148" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A148" s="12">
         <v>46121</v>
       </c>
@@ -22403,7 +22508,7 @@
         <v>7.7249999999999996</v>
       </c>
     </row>
-    <row r="149" spans="1:25">
+    <row r="149" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A149" s="12">
         <v>46121</v>
       </c>
@@ -22480,7 +22585,7 @@
         <v>7.7249999999999996</v>
       </c>
     </row>
-    <row r="150" spans="1:25">
+    <row r="150" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A150" s="12">
         <v>46121</v>
       </c>
@@ -22557,7 +22662,7 @@
         <v>7.7249999999999996</v>
       </c>
     </row>
-    <row r="151" spans="1:25">
+    <row r="151" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A151" s="12">
         <v>46122</v>
       </c>
@@ -22634,7 +22739,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="152" spans="1:25">
+    <row r="152" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A152" s="12">
         <v>46122</v>
       </c>
@@ -22711,7 +22816,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="153" spans="1:25">
+    <row r="153" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A153" s="12">
         <v>46122</v>
       </c>
@@ -22788,7 +22893,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="154" spans="1:25">
+    <row r="154" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A154" s="12">
         <v>46125</v>
       </c>
@@ -22865,7 +22970,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="155" spans="1:25">
+    <row r="155" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A155" s="12">
         <v>46125</v>
       </c>
@@ -22942,7 +23047,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="156" spans="1:25">
+    <row r="156" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A156" s="12">
         <v>46125</v>
       </c>
@@ -23019,7 +23124,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="157" spans="1:25">
+    <row r="157" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A157" s="12">
         <v>46126</v>
       </c>
@@ -23096,7 +23201,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="158" spans="1:25">
+    <row r="158" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A158" s="12">
         <v>46126</v>
       </c>
@@ -23173,7 +23278,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="159" spans="1:25">
+    <row r="159" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A159" s="12">
         <v>46126</v>
       </c>
@@ -23250,7 +23355,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="160" spans="1:25">
+    <row r="160" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A160" s="12">
         <v>46127</v>
       </c>
@@ -23327,7 +23432,7 @@
         <v>7.85</v>
       </c>
     </row>
-    <row r="161" spans="1:25">
+    <row r="161" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A161" s="12">
         <v>46127</v>
       </c>
@@ -23404,7 +23509,7 @@
         <v>7.85</v>
       </c>
     </row>
-    <row r="162" spans="1:25">
+    <row r="162" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A162" s="12">
         <v>46127</v>
       </c>
@@ -23481,7 +23586,7 @@
         <v>7.8630000000000004</v>
       </c>
     </row>
-    <row r="163" spans="1:25">
+    <row r="163" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A163" s="12">
         <v>46128</v>
       </c>
@@ -23558,7 +23663,7 @@
         <v>7.8630000000000004</v>
       </c>
     </row>
-    <row r="164" spans="1:25">
+    <row r="164" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A164" s="12">
         <v>46128</v>
       </c>
@@ -23635,7 +23740,7 @@
         <v>7.9749999999999996</v>
       </c>
     </row>
-    <row r="165" spans="1:25">
+    <row r="165" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A165" s="12">
         <v>46128</v>
       </c>
@@ -23710,6 +23815,174 @@
       </c>
       <c r="Y165" s="11">
         <v>7.9749999999999996</v>
+      </c>
+    </row>
+    <row r="166" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A166" s="12">
+        <v>46129</v>
+      </c>
+      <c r="B166" s="12">
+        <v>46129</v>
+      </c>
+      <c r="C166" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D166" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E166" s="11">
+        <v>49.5</v>
+      </c>
+      <c r="F166" s="11">
+        <v>28</v>
+      </c>
+      <c r="G166" s="11">
+        <v>37.832999999999998</v>
+      </c>
+      <c r="H166" s="11">
+        <v>24</v>
+      </c>
+      <c r="I166" s="11">
+        <v>20.6</v>
+      </c>
+      <c r="J166" s="11">
+        <v>21.5</v>
+      </c>
+      <c r="K166" s="11">
+        <v>87.5</v>
+      </c>
+      <c r="L166" s="11">
+        <v>29</v>
+      </c>
+      <c r="M166" s="11">
+        <v>69.182000000000002</v>
+      </c>
+      <c r="N166" s="11">
+        <v>14.7</v>
+      </c>
+      <c r="O166" s="11">
+        <v>13</v>
+      </c>
+      <c r="P166" s="11">
+        <v>13.475</v>
+      </c>
+      <c r="Q166" s="11">
+        <v>50</v>
+      </c>
+      <c r="R166" s="11">
+        <v>14.5</v>
+      </c>
+      <c r="S166" s="11">
+        <v>33</v>
+      </c>
+      <c r="T166" s="11">
+        <v>7.3</v>
+      </c>
+      <c r="U166" s="11">
+        <v>5.2</v>
+      </c>
+      <c r="V166" s="11">
+        <v>6.43</v>
+      </c>
+      <c r="W166" s="11">
+        <v>10.1</v>
+      </c>
+      <c r="X166" s="11">
+        <v>5.3</v>
+      </c>
+      <c r="Y166" s="11">
+        <v>8.0250000000000004</v>
+      </c>
+    </row>
+    <row r="167" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A167" s="12">
+        <v>46129</v>
+      </c>
+      <c r="B167" s="12">
+        <v>46129</v>
+      </c>
+      <c r="C167" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D167" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E167" s="11">
+        <v>49.5</v>
+      </c>
+      <c r="F167" s="11">
+        <v>28</v>
+      </c>
+      <c r="G167" s="11">
+        <v>38.5</v>
+      </c>
+      <c r="H167" s="11">
+        <v>24</v>
+      </c>
+      <c r="I167" s="11">
+        <v>20.6</v>
+      </c>
+      <c r="J167" s="11">
+        <v>21.7</v>
+      </c>
+      <c r="K167" s="11">
+        <v>87.5</v>
+      </c>
+      <c r="L167" s="11">
+        <v>29</v>
+      </c>
+      <c r="M167" s="11">
+        <v>69.182000000000002</v>
+      </c>
+      <c r="N167" s="11">
+        <v>14.7</v>
+      </c>
+      <c r="O167" s="11">
+        <v>13</v>
+      </c>
+      <c r="P167" s="11">
+        <v>13.475</v>
+      </c>
+      <c r="Q167" s="11">
+        <v>50</v>
+      </c>
+      <c r="R167" s="11">
+        <v>14.5</v>
+      </c>
+      <c r="S167" s="11">
+        <v>33</v>
+      </c>
+      <c r="T167" s="11">
+        <v>7.3</v>
+      </c>
+      <c r="U167" s="11">
+        <v>5.2</v>
+      </c>
+      <c r="V167" s="11">
+        <v>6.43</v>
+      </c>
+      <c r="W167" s="11">
+        <v>10.1</v>
+      </c>
+      <c r="X167" s="11">
+        <v>5.3</v>
+      </c>
+      <c r="Y167" s="11">
+        <v>8.0250000000000004</v>
+      </c>
+    </row>
+    <row r="168" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A168" s="12">
+        <v>46129</v>
+      </c>
+      <c r="B168" s="12">
+        <v>46129</v>
+      </c>
+      <c r="C168" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D168" s="7" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -23729,19 +24002,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:AK6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.36328125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.26953125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.3984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.09765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.296875" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="9" style="11"/>
-    <col min="8" max="10" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="9.09765625" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="5" customFormat="1">
+    <row r="1" spans="1:37" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -23830,7 +24103,7 @@
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
     </row>
-    <row r="2" spans="1:37">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -23911,7 +24184,7 @@
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
     </row>
-    <row r="3" spans="1:37">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45962</v>
       </c>
@@ -24000,7 +24273,7 @@
       <c r="AJ3" s="2"/>
       <c r="AK3" s="2"/>
     </row>
-    <row r="4" spans="1:37">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45992</v>
       </c>
@@ -24089,7 +24362,7 @@
       <c r="AJ4" s="2"/>
       <c r="AK4" s="2"/>
     </row>
-    <row r="5" spans="1:37">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>46023</v>
       </c>
@@ -24121,7 +24394,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:37">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>46054</v>
       </c>
@@ -24214,24 +24487,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:Y13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.09765625" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.09765625" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="14"/>
-    <col min="7" max="7" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.453125" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.09765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5" style="14" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="14"/>
-    <col min="10" max="10" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.09765625" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="9" style="14"/>
-    <col min="13" max="13" width="13.26953125" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.296875" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
+    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
@@ -24284,7 +24557,7 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -24329,7 +24602,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -24382,7 +24655,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -24435,7 +24708,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -24476,7 +24749,7 @@
         <v>118.333</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -24517,7 +24790,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -24558,7 +24831,7 @@
         <v>122.667</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="12">
         <v>46083</v>
       </c>
@@ -24599,7 +24872,7 @@
         <v>123.333</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="12">
         <v>46090</v>
       </c>
@@ -24640,7 +24913,7 @@
         <v>126.667</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="12">
         <v>46097</v>
       </c>
@@ -24681,7 +24954,7 @@
         <v>132.333</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="12">
         <v>46104</v>
       </c>
@@ -24722,7 +24995,7 @@
         <v>143.333</v>
       </c>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" s="12">
         <v>46111</v>
       </c>
@@ -24763,7 +25036,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" s="12">
         <v>46118</v>
       </c>
@@ -24821,18 +25094,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:Y13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.6328125" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.09765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.09765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.59765625" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
+    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -24879,7 +25152,7 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -24918,7 +25191,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -24965,7 +25238,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -25012,7 +25285,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -25044,7 +25317,7 @@
         <v>9.6539999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -25076,7 +25349,7 @@
         <v>9.8650000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -25108,7 +25381,7 @@
         <v>10.221</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="12">
         <v>46083</v>
       </c>
@@ -25140,7 +25413,7 @@
         <v>10.721</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="12">
         <v>46090</v>
       </c>
@@ -25172,7 +25445,7 @@
         <v>11.462</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="12">
         <v>46097</v>
       </c>
@@ -25204,7 +25477,7 @@
         <v>11.962</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="12">
         <v>46104</v>
       </c>
@@ -25236,7 +25509,7 @@
         <v>12.865</v>
       </c>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" s="12">
         <v>46111</v>
       </c>
@@ -25268,7 +25541,7 @@
         <v>12.71</v>
       </c>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" s="12">
         <v>46118</v>
       </c>
@@ -25316,7 +25589,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="16384" width="9" style="3"/>
   </cols>
@@ -25331,15 +25604,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.90625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.90625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.6328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.8984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.8984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.59765625" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>48</v>
       </c>
@@ -25350,7 +25623,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
@@ -25364,7 +25637,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="s">
         <v>29</v>
@@ -25373,7 +25646,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>31</v>
@@ -25382,7 +25655,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
         <v>33</v>
@@ -25391,7 +25664,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="2" t="s">
         <v>35</v>
@@ -25400,7 +25673,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
         <v>37</v>
@@ -25409,7 +25682,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
         <v>39</v>
@@ -25418,7 +25691,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>41</v>
       </c>
@@ -25427,49 +25700,49 @@
       </c>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>42</v>
       </c>
@@ -25480,7 +25753,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="2" t="s">
         <v>8</v>
@@ -25489,7 +25762,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="2" t="s">
         <v>9</v>
@@ -25498,7 +25771,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>44</v>
       </c>
@@ -25509,7 +25782,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="2" t="s">
         <v>11</v>
@@ -25518,7 +25791,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>45</v>
       </c>
@@ -25527,42 +25800,42 @@
       </c>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C22" s="2"/>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C26" s="2"/>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>46</v>
       </c>
@@ -25571,35 +25844,35 @@
       </c>
       <c r="C27" s="2"/>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C28" s="2"/>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C29" s="2"/>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C30" s="2"/>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C31" s="2"/>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="2" t="s">
         <v>23</v>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A53F82D6-F67C-4D2F-8857-01C732C8B42C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2442FA5-CF84-47EB-A421-ED0262498A33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -20,17 +20,26 @@
     <sheet name="fig" sheetId="6" r:id="rId5"/>
     <sheet name="info" sheetId="1" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -244,23 +253,23 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -273,7 +282,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -316,7 +325,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -337,27 +346,27 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -365,8 +374,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -384,7 +393,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -934,6 +943,15 @@
                 <c:pt idx="165">
                   <c:v>46129</c:v>
                 </c:pt>
+                <c:pt idx="166">
+                  <c:v>46132</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>46132</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>46132</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1440,6 +1458,12 @@
                 </c:pt>
                 <c:pt idx="165">
                   <c:v>38.5</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>38.667000000000002</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>38.667000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1984,6 +2008,15 @@
                 <c:pt idx="165">
                   <c:v>46129</c:v>
                 </c:pt>
+                <c:pt idx="166">
+                  <c:v>46132</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>46132</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>46132</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2490,6 +2523,12 @@
                 </c:pt>
                 <c:pt idx="165">
                   <c:v>21.7</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>21.8</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>21.8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3034,6 +3073,15 @@
                 <c:pt idx="165">
                   <c:v>46129</c:v>
                 </c:pt>
+                <c:pt idx="166">
+                  <c:v>46132</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>46132</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>46132</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3540,6 +3588,12 @@
                 </c:pt>
                 <c:pt idx="165">
                   <c:v>69.182000000000002</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>68.635999999999996</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>68.772999999999996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4084,6 +4138,15 @@
                 <c:pt idx="165">
                   <c:v>46129</c:v>
                 </c:pt>
+                <c:pt idx="166">
+                  <c:v>46132</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>46132</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>46132</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4590,6 +4653,12 @@
                 </c:pt>
                 <c:pt idx="165">
                   <c:v>13.475</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>13.375</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>13.375</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5134,6 +5203,15 @@
                 <c:pt idx="165">
                   <c:v>46129</c:v>
                 </c:pt>
+                <c:pt idx="166">
+                  <c:v>46132</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>46132</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>46132</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5639,6 +5717,12 @@
                   <c:v>33</c:v>
                 </c:pt>
                 <c:pt idx="165">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="167">
                   <c:v>33</c:v>
                 </c:pt>
               </c:numCache>
@@ -6200,6 +6284,15 @@
                 <c:pt idx="165">
                   <c:v>46129</c:v>
                 </c:pt>
+                <c:pt idx="166">
+                  <c:v>46132</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>46132</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>46132</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6706,6 +6799,12 @@
                 </c:pt>
                 <c:pt idx="165">
                   <c:v>6.43</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>6.39</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>6.39</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7252,6 +7351,15 @@
                 <c:pt idx="165">
                   <c:v>46129</c:v>
                 </c:pt>
+                <c:pt idx="166">
+                  <c:v>46132</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>46132</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>46132</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7758,6 +7866,12 @@
                 </c:pt>
                 <c:pt idx="165">
                   <c:v>8.0250000000000004</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>8.0749999999999993</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>8.0749999999999993</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8035,7 +8149,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -8617,7 +8731,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -11130,18 +11244,18 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y168"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:Y171"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.26953125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.09765625" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.09765625" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.296875" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
+    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
@@ -11218,7 +11332,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -11287,7 +11401,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>46044</v>
       </c>
@@ -11364,7 +11478,7 @@
         <v>4.9450000000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>46045</v>
       </c>
@@ -11441,7 +11555,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <v>46045</v>
       </c>
@@ -11518,7 +11632,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
         <v>46045</v>
       </c>
@@ -11595,7 +11709,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
         <v>46048</v>
       </c>
@@ -11672,7 +11786,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="12">
         <v>46048</v>
       </c>
@@ -11749,7 +11863,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="12">
         <v>46048</v>
       </c>
@@ -11826,7 +11940,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="12">
         <v>46049</v>
       </c>
@@ -11903,7 +12017,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="12">
         <v>46049</v>
       </c>
@@ -11980,7 +12094,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" s="12">
         <v>46049</v>
       </c>
@@ -12057,7 +12171,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" s="12">
         <v>46050</v>
       </c>
@@ -12134,7 +12248,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A14" s="12">
         <v>46050</v>
       </c>
@@ -12211,7 +12325,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A15" s="12">
         <v>46050</v>
       </c>
@@ -12288,7 +12402,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="16" spans="1:25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A16" s="12">
         <v>46051</v>
       </c>
@@ -12365,7 +12479,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:25">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A17" s="12">
         <v>46051</v>
       </c>
@@ -12442,7 +12556,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:25">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A18" s="12">
         <v>46051</v>
       </c>
@@ -12519,7 +12633,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:25">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A19" s="12">
         <v>46052</v>
       </c>
@@ -12596,7 +12710,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="20" spans="1:25">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A20" s="12">
         <v>46052</v>
       </c>
@@ -12673,7 +12787,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="21" spans="1:25">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A21" s="12">
         <v>46052</v>
       </c>
@@ -12750,7 +12864,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="22" spans="1:25">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A22" s="12">
         <v>46055</v>
       </c>
@@ -12827,7 +12941,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="23" spans="1:25">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A23" s="12">
         <v>46055</v>
       </c>
@@ -12904,7 +13018,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="24" spans="1:25">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A24" s="12">
         <v>46055</v>
       </c>
@@ -12981,7 +13095,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="25" spans="1:25">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A25" s="12">
         <v>46056</v>
       </c>
@@ -13058,7 +13172,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="26" spans="1:25">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A26" s="12">
         <v>46056</v>
       </c>
@@ -13135,7 +13249,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="27" spans="1:25">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A27" s="12">
         <v>46056</v>
       </c>
@@ -13212,7 +13326,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="28" spans="1:25">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A28" s="12">
         <v>46057</v>
       </c>
@@ -13289,7 +13403,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="29" spans="1:25">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A29" s="12">
         <v>46057</v>
       </c>
@@ -13366,7 +13480,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="30" spans="1:25">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A30" s="12">
         <v>46057</v>
       </c>
@@ -13443,7 +13557,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="31" spans="1:25">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A31" s="12">
         <v>46058</v>
       </c>
@@ -13520,7 +13634,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="32" spans="1:25">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A32" s="12">
         <v>46058</v>
       </c>
@@ -13597,7 +13711,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="33" spans="1:25">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A33" s="12">
         <v>46058</v>
       </c>
@@ -13674,7 +13788,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="34" spans="1:25">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A34" s="12">
         <v>46059</v>
       </c>
@@ -13751,7 +13865,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:25">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A35" s="12">
         <v>46059</v>
       </c>
@@ -13828,7 +13942,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:25">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A36" s="12">
         <v>46059</v>
       </c>
@@ -13905,7 +14019,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:25">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A37" s="12">
         <v>46062</v>
       </c>
@@ -13982,7 +14096,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="38" spans="1:25">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A38" s="12">
         <v>46062</v>
       </c>
@@ -14059,7 +14173,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="39" spans="1:25">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A39" s="12">
         <v>46062</v>
       </c>
@@ -14136,7 +14250,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="40" spans="1:25">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A40" s="12">
         <v>46063</v>
       </c>
@@ -14213,7 +14327,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="41" spans="1:25">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A41" s="12">
         <v>46063</v>
       </c>
@@ -14290,7 +14404,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="42" spans="1:25">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A42" s="12">
         <v>46063</v>
       </c>
@@ -14367,7 +14481,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="43" spans="1:25">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A43" s="12">
         <v>46064</v>
       </c>
@@ -14444,7 +14558,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="44" spans="1:25">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A44" s="12">
         <v>46064</v>
       </c>
@@ -14521,7 +14635,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="45" spans="1:25">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A45" s="12">
         <v>46064</v>
       </c>
@@ -14598,7 +14712,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="46" spans="1:25">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A46" s="12">
         <v>46065</v>
       </c>
@@ -14675,7 +14789,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:25">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A47" s="12">
         <v>46065</v>
       </c>
@@ -14752,7 +14866,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:25">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A48" s="12">
         <v>46065</v>
       </c>
@@ -14829,7 +14943,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="49" spans="1:25">
+    <row r="49" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A49" s="12">
         <v>46066</v>
       </c>
@@ -14906,7 +15020,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:25">
+    <row r="50" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A50" s="12">
         <v>46066</v>
       </c>
@@ -14983,7 +15097,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:25">
+    <row r="51" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A51" s="12">
         <v>46066</v>
       </c>
@@ -15060,7 +15174,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:25">
+    <row r="52" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A52" s="12">
         <v>46076</v>
       </c>
@@ -15137,7 +15251,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="53" spans="1:25">
+    <row r="53" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A53" s="12">
         <v>46076</v>
       </c>
@@ -15214,7 +15328,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:25">
+    <row r="54" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A54" s="12">
         <v>46076</v>
       </c>
@@ -15291,7 +15405,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="55" spans="1:25">
+    <row r="55" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A55" s="12">
         <v>46077</v>
       </c>
@@ -15368,7 +15482,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="56" spans="1:25">
+    <row r="56" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A56" s="12">
         <v>46077</v>
       </c>
@@ -15445,7 +15559,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="57" spans="1:25">
+    <row r="57" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A57" s="12">
         <v>46077</v>
       </c>
@@ -15522,7 +15636,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="58" spans="1:25">
+    <row r="58" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A58" s="12">
         <v>46078</v>
       </c>
@@ -15599,7 +15713,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="59" spans="1:25">
+    <row r="59" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A59" s="12">
         <v>46078</v>
       </c>
@@ -15676,7 +15790,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="60" spans="1:25">
+    <row r="60" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A60" s="12">
         <v>46078</v>
       </c>
@@ -15753,7 +15867,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="61" spans="1:25">
+    <row r="61" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A61" s="12">
         <v>46079</v>
       </c>
@@ -15830,7 +15944,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="62" spans="1:25">
+    <row r="62" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A62" s="12">
         <v>46079</v>
       </c>
@@ -15907,7 +16021,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="63" spans="1:25">
+    <row r="63" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A63" s="12">
         <v>46079</v>
       </c>
@@ -15984,7 +16098,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="64" spans="1:25">
+    <row r="64" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A64" s="12">
         <v>46080</v>
       </c>
@@ -16061,7 +16175,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="65" spans="1:25">
+    <row r="65" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A65" s="12">
         <v>46080</v>
       </c>
@@ -16138,7 +16252,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="66" spans="1:25">
+    <row r="66" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A66" s="12">
         <v>46080</v>
       </c>
@@ -16215,7 +16329,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="67" spans="1:25">
+    <row r="67" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A67" s="12">
         <v>46083</v>
       </c>
@@ -16292,7 +16406,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="68" spans="1:25">
+    <row r="68" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A68" s="12">
         <v>46083</v>
       </c>
@@ -16369,7 +16483,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="69" spans="1:25">
+    <row r="69" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A69" s="12">
         <v>46083</v>
       </c>
@@ -16446,7 +16560,7 @@
         <v>5.68</v>
       </c>
     </row>
-    <row r="70" spans="1:25">
+    <row r="70" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A70" s="12">
         <v>46084</v>
       </c>
@@ -16523,7 +16637,7 @@
         <v>5.7590000000000003</v>
       </c>
     </row>
-    <row r="71" spans="1:25">
+    <row r="71" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A71" s="12">
         <v>46084</v>
       </c>
@@ -16600,7 +16714,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="72" spans="1:25">
+    <row r="72" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A72" s="12">
         <v>46084</v>
       </c>
@@ -16677,7 +16791,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="73" spans="1:25">
+    <row r="73" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A73" s="12">
         <v>46085</v>
       </c>
@@ -16754,7 +16868,7 @@
         <v>5.8390000000000004</v>
       </c>
     </row>
-    <row r="74" spans="1:25">
+    <row r="74" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A74" s="12">
         <v>46085</v>
       </c>
@@ -16831,7 +16945,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:25">
+    <row r="75" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A75" s="12">
         <v>46085</v>
       </c>
@@ -16908,7 +17022,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:25">
+    <row r="76" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A76" s="12">
         <v>46086</v>
       </c>
@@ -16985,7 +17099,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="77" spans="1:25">
+    <row r="77" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A77" s="12">
         <v>46086</v>
       </c>
@@ -17062,7 +17176,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="78" spans="1:25">
+    <row r="78" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A78" s="12">
         <v>46086</v>
       </c>
@@ -17139,7 +17253,7 @@
         <v>5.9210000000000003</v>
       </c>
     </row>
-    <row r="79" spans="1:25">
+    <row r="79" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A79" s="12">
         <v>46087</v>
       </c>
@@ -17216,7 +17330,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="80" spans="1:25">
+    <row r="80" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A80" s="12">
         <v>46087</v>
       </c>
@@ -17293,7 +17407,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="81" spans="1:25">
+    <row r="81" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A81" s="12">
         <v>46087</v>
       </c>
@@ -17370,7 +17484,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="82" spans="1:25">
+    <row r="82" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A82" s="12">
         <v>46090</v>
       </c>
@@ -17447,7 +17561,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="83" spans="1:25">
+    <row r="83" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A83" s="12">
         <v>46090</v>
       </c>
@@ -17524,7 +17638,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="84" spans="1:25">
+    <row r="84" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A84" s="12">
         <v>46090</v>
       </c>
@@ -17601,7 +17715,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="85" spans="1:25">
+    <row r="85" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A85" s="12">
         <v>46091</v>
       </c>
@@ -17678,7 +17792,7 @@
         <v>6.157</v>
       </c>
     </row>
-    <row r="86" spans="1:25">
+    <row r="86" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A86" s="12">
         <v>46091</v>
       </c>
@@ -17755,7 +17869,7 @@
         <v>6.181</v>
       </c>
     </row>
-    <row r="87" spans="1:25">
+    <row r="87" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A87" s="12">
         <v>46091</v>
       </c>
@@ -17832,7 +17946,7 @@
         <v>6.181</v>
       </c>
     </row>
-    <row r="88" spans="1:25">
+    <row r="88" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A88" s="12">
         <v>46092</v>
       </c>
@@ -17909,7 +18023,7 @@
         <v>6.2430000000000003</v>
       </c>
     </row>
-    <row r="89" spans="1:25">
+    <row r="89" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A89" s="12">
         <v>46092</v>
       </c>
@@ -17986,7 +18100,7 @@
         <v>6.29</v>
       </c>
     </row>
-    <row r="90" spans="1:25">
+    <row r="90" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A90" s="12">
         <v>46092</v>
       </c>
@@ -18063,7 +18177,7 @@
         <v>6.3049999999999997</v>
       </c>
     </row>
-    <row r="91" spans="1:25">
+    <row r="91" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A91" s="12">
         <v>46093</v>
       </c>
@@ -18140,7 +18254,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="92" spans="1:25">
+    <row r="92" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A92" s="12">
         <v>46093</v>
       </c>
@@ -18217,7 +18331,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="93" spans="1:25">
+    <row r="93" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A93" s="12">
         <v>46093</v>
       </c>
@@ -18294,7 +18408,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="94" spans="1:25">
+    <row r="94" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A94" s="12">
         <v>46094</v>
       </c>
@@ -18371,7 +18485,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="95" spans="1:25">
+    <row r="95" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A95" s="12">
         <v>46094</v>
       </c>
@@ -18448,7 +18562,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="96" spans="1:25">
+    <row r="96" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A96" s="12">
         <v>46094</v>
       </c>
@@ -18525,7 +18639,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="97" spans="1:25">
+    <row r="97" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A97" s="12">
         <v>46097</v>
       </c>
@@ -18602,7 +18716,7 @@
         <v>6.5330000000000004</v>
       </c>
     </row>
-    <row r="98" spans="1:25">
+    <row r="98" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A98" s="12">
         <v>46097</v>
       </c>
@@ -18679,7 +18793,7 @@
         <v>6.5119999999999996</v>
       </c>
     </row>
-    <row r="99" spans="1:25">
+    <row r="99" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A99" s="12">
         <v>46097</v>
       </c>
@@ -18756,7 +18870,7 @@
         <v>6.5119999999999996</v>
       </c>
     </row>
-    <row r="100" spans="1:25">
+    <row r="100" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A100" s="12">
         <v>46098</v>
       </c>
@@ -18833,7 +18947,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="101" spans="1:25">
+    <row r="101" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A101" s="12">
         <v>46098</v>
       </c>
@@ -18910,7 +19024,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="102" spans="1:25">
+    <row r="102" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A102" s="12">
         <v>46098</v>
       </c>
@@ -18987,7 +19101,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="103" spans="1:25">
+    <row r="103" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A103" s="12">
         <v>46099</v>
       </c>
@@ -19064,7 +19178,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="104" spans="1:25">
+    <row r="104" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A104" s="12">
         <v>46099</v>
       </c>
@@ -19141,7 +19255,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="105" spans="1:25">
+    <row r="105" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A105" s="12">
         <v>46099</v>
       </c>
@@ -19218,7 +19332,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="106" spans="1:25">
+    <row r="106" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A106" s="12">
         <v>46100</v>
       </c>
@@ -19295,7 +19409,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="107" spans="1:25">
+    <row r="107" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A107" s="12">
         <v>46100</v>
       </c>
@@ -19372,7 +19486,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="108" spans="1:25">
+    <row r="108" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A108" s="12">
         <v>46100</v>
       </c>
@@ -19449,7 +19563,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="109" spans="1:25">
+    <row r="109" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A109" s="12">
         <v>46101</v>
       </c>
@@ -19526,7 +19640,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="110" spans="1:25">
+    <row r="110" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A110" s="12">
         <v>46101</v>
       </c>
@@ -19603,7 +19717,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="111" spans="1:25">
+    <row r="111" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A111" s="12">
         <v>46101</v>
       </c>
@@ -19680,7 +19794,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="112" spans="1:25">
+    <row r="112" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A112" s="12">
         <v>46104</v>
       </c>
@@ -19757,7 +19871,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="113" spans="1:25">
+    <row r="113" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A113" s="12">
         <v>46104</v>
       </c>
@@ -19834,7 +19948,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="114" spans="1:25">
+    <row r="114" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A114" s="12">
         <v>46104</v>
       </c>
@@ -19911,7 +20025,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="115" spans="1:25">
+    <row r="115" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A115" s="12">
         <v>46105</v>
       </c>
@@ -19988,7 +20102,7 @@
         <v>7.0250000000000004</v>
       </c>
     </row>
-    <row r="116" spans="1:25">
+    <row r="116" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A116" s="12">
         <v>46105</v>
       </c>
@@ -20065,7 +20179,7 @@
         <v>7.125</v>
       </c>
     </row>
-    <row r="117" spans="1:25">
+    <row r="117" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A117" s="12">
         <v>46105</v>
       </c>
@@ -20142,7 +20256,7 @@
         <v>7.125</v>
       </c>
     </row>
-    <row r="118" spans="1:25">
+    <row r="118" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A118" s="12">
         <v>46106</v>
       </c>
@@ -20219,7 +20333,7 @@
         <v>7.15</v>
       </c>
     </row>
-    <row r="119" spans="1:25">
+    <row r="119" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A119" s="12">
         <v>46106</v>
       </c>
@@ -20296,7 +20410,7 @@
         <v>7.2249999999999996</v>
       </c>
     </row>
-    <row r="120" spans="1:25">
+    <row r="120" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A120" s="12">
         <v>46106</v>
       </c>
@@ -20373,7 +20487,7 @@
         <v>7.2249999999999996</v>
       </c>
     </row>
-    <row r="121" spans="1:25">
+    <row r="121" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A121" s="12">
         <v>46107</v>
       </c>
@@ -20450,7 +20564,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="122" spans="1:25">
+    <row r="122" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A122" s="12">
         <v>46107</v>
       </c>
@@ -20527,7 +20641,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="123" spans="1:25">
+    <row r="123" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A123" s="12">
         <v>46107</v>
       </c>
@@ -20604,7 +20718,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="124" spans="1:25">
+    <row r="124" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A124" s="12">
         <v>46108</v>
       </c>
@@ -20681,7 +20795,7 @@
         <v>7.375</v>
       </c>
     </row>
-    <row r="125" spans="1:25">
+    <row r="125" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A125" s="12">
         <v>46108</v>
       </c>
@@ -20758,7 +20872,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="126" spans="1:25">
+    <row r="126" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A126" s="12">
         <v>46108</v>
       </c>
@@ -20835,7 +20949,7 @@
         <v>7.375</v>
       </c>
     </row>
-    <row r="127" spans="1:25">
+    <row r="127" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A127" s="12">
         <v>46111</v>
       </c>
@@ -20912,7 +21026,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="128" spans="1:25">
+    <row r="128" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A128" s="12">
         <v>46111</v>
       </c>
@@ -20989,7 +21103,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="129" spans="1:25">
+    <row r="129" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A129" s="12">
         <v>46111</v>
       </c>
@@ -21066,7 +21180,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="130" spans="1:25">
+    <row r="130" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A130" s="12">
         <v>46112</v>
       </c>
@@ -21143,7 +21257,7 @@
         <v>7.5250000000000004</v>
       </c>
     </row>
-    <row r="131" spans="1:25">
+    <row r="131" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A131" s="12">
         <v>46112</v>
       </c>
@@ -21220,7 +21334,7 @@
         <v>7.5250000000000004</v>
       </c>
     </row>
-    <row r="132" spans="1:25">
+    <row r="132" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A132" s="12">
         <v>46112</v>
       </c>
@@ -21297,7 +21411,7 @@
         <v>7.55</v>
       </c>
     </row>
-    <row r="133" spans="1:25">
+    <row r="133" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A133" s="12">
         <v>46113</v>
       </c>
@@ -21374,7 +21488,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="134" spans="1:25">
+    <row r="134" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A134" s="12">
         <v>46113</v>
       </c>
@@ -21451,7 +21565,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="135" spans="1:25">
+    <row r="135" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A135" s="12">
         <v>46113</v>
       </c>
@@ -21528,7 +21642,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="136" spans="1:25">
+    <row r="136" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A136" s="12">
         <v>46114</v>
       </c>
@@ -21605,7 +21719,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="137" spans="1:25">
+    <row r="137" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A137" s="12">
         <v>46114</v>
       </c>
@@ -21682,7 +21796,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="138" spans="1:25">
+    <row r="138" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A138" s="12">
         <v>46114</v>
       </c>
@@ -21759,7 +21873,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="139" spans="1:25">
+    <row r="139" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A139" s="12">
         <v>46115</v>
       </c>
@@ -21836,7 +21950,7 @@
         <v>7.6749999999999998</v>
       </c>
     </row>
-    <row r="140" spans="1:25">
+    <row r="140" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A140" s="12">
         <v>46115</v>
       </c>
@@ -21913,7 +22027,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="141" spans="1:25">
+    <row r="141" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A141" s="12">
         <v>46115</v>
       </c>
@@ -21990,7 +22104,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="142" spans="1:25">
+    <row r="142" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A142" s="12">
         <v>46119</v>
       </c>
@@ -22067,7 +22181,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="143" spans="1:25">
+    <row r="143" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A143" s="12">
         <v>46119</v>
       </c>
@@ -22144,7 +22258,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="144" spans="1:25">
+    <row r="144" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A144" s="12">
         <v>46119</v>
       </c>
@@ -22221,7 +22335,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="145" spans="1:25">
+    <row r="145" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A145" s="12">
         <v>46120</v>
       </c>
@@ -22298,7 +22412,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="146" spans="1:25">
+    <row r="146" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A146" s="12">
         <v>46120</v>
       </c>
@@ -22375,7 +22489,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="147" spans="1:25">
+    <row r="147" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A147" s="12">
         <v>46120</v>
       </c>
@@ -22452,7 +22566,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="148" spans="1:25">
+    <row r="148" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A148" s="12">
         <v>46121</v>
       </c>
@@ -22529,7 +22643,7 @@
         <v>7.7249999999999996</v>
       </c>
     </row>
-    <row r="149" spans="1:25">
+    <row r="149" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A149" s="12">
         <v>46121</v>
       </c>
@@ -22606,7 +22720,7 @@
         <v>7.7249999999999996</v>
       </c>
     </row>
-    <row r="150" spans="1:25">
+    <row r="150" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A150" s="12">
         <v>46121</v>
       </c>
@@ -22683,7 +22797,7 @@
         <v>7.7249999999999996</v>
       </c>
     </row>
-    <row r="151" spans="1:25">
+    <row r="151" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A151" s="12">
         <v>46122</v>
       </c>
@@ -22760,7 +22874,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="152" spans="1:25">
+    <row r="152" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A152" s="12">
         <v>46122</v>
       </c>
@@ -22837,7 +22951,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="153" spans="1:25">
+    <row r="153" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A153" s="12">
         <v>46122</v>
       </c>
@@ -22914,7 +23028,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="154" spans="1:25">
+    <row r="154" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A154" s="12">
         <v>46125</v>
       </c>
@@ -22991,7 +23105,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="155" spans="1:25">
+    <row r="155" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A155" s="12">
         <v>46125</v>
       </c>
@@ -23068,7 +23182,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="156" spans="1:25">
+    <row r="156" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A156" s="12">
         <v>46125</v>
       </c>
@@ -23145,7 +23259,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="157" spans="1:25">
+    <row r="157" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A157" s="12">
         <v>46126</v>
       </c>
@@ -23222,7 +23336,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="158" spans="1:25">
+    <row r="158" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A158" s="12">
         <v>46126</v>
       </c>
@@ -23299,7 +23413,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="159" spans="1:25">
+    <row r="159" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A159" s="12">
         <v>46126</v>
       </c>
@@ -23376,7 +23490,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="160" spans="1:25">
+    <row r="160" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A160" s="12">
         <v>46127</v>
       </c>
@@ -23453,7 +23567,7 @@
         <v>7.85</v>
       </c>
     </row>
-    <row r="161" spans="1:25">
+    <row r="161" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A161" s="12">
         <v>46127</v>
       </c>
@@ -23530,7 +23644,7 @@
         <v>7.85</v>
       </c>
     </row>
-    <row r="162" spans="1:25">
+    <row r="162" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A162" s="12">
         <v>46127</v>
       </c>
@@ -23607,7 +23721,7 @@
         <v>7.8630000000000004</v>
       </c>
     </row>
-    <row r="163" spans="1:25">
+    <row r="163" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A163" s="12">
         <v>46128</v>
       </c>
@@ -23684,7 +23798,7 @@
         <v>7.8630000000000004</v>
       </c>
     </row>
-    <row r="164" spans="1:25">
+    <row r="164" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A164" s="12">
         <v>46128</v>
       </c>
@@ -23761,7 +23875,7 @@
         <v>7.9749999999999996</v>
       </c>
     </row>
-    <row r="165" spans="1:25">
+    <row r="165" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A165" s="12">
         <v>46128</v>
       </c>
@@ -23838,7 +23952,7 @@
         <v>7.9749999999999996</v>
       </c>
     </row>
-    <row r="166" spans="1:25">
+    <row r="166" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A166" s="12">
         <v>46129</v>
       </c>
@@ -23915,7 +24029,7 @@
         <v>8.0250000000000004</v>
       </c>
     </row>
-    <row r="167" spans="1:25">
+    <row r="167" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A167" s="12">
         <v>46129</v>
       </c>
@@ -23992,7 +24106,7 @@
         <v>8.0250000000000004</v>
       </c>
     </row>
-    <row r="168" spans="1:25">
+    <row r="168" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A168" s="12">
         <v>46129</v>
       </c>
@@ -24067,6 +24181,174 @@
       </c>
       <c r="Y168" s="11">
         <v>8.0250000000000004</v>
+      </c>
+    </row>
+    <row r="169" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A169" s="12">
+        <v>46132</v>
+      </c>
+      <c r="B169" s="12">
+        <v>46132</v>
+      </c>
+      <c r="C169" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D169" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E169" s="11">
+        <v>50</v>
+      </c>
+      <c r="F169" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="G169" s="11">
+        <v>38.667000000000002</v>
+      </c>
+      <c r="H169" s="11">
+        <v>24.5</v>
+      </c>
+      <c r="I169" s="11">
+        <v>20.8</v>
+      </c>
+      <c r="J169" s="11">
+        <v>21.8</v>
+      </c>
+      <c r="K169" s="11">
+        <v>85</v>
+      </c>
+      <c r="L169" s="11">
+        <v>29.5</v>
+      </c>
+      <c r="M169" s="11">
+        <v>68.635999999999996</v>
+      </c>
+      <c r="N169" s="11">
+        <v>14.5</v>
+      </c>
+      <c r="O169" s="11">
+        <v>12.8</v>
+      </c>
+      <c r="P169" s="11">
+        <v>13.375</v>
+      </c>
+      <c r="Q169" s="11">
+        <v>51</v>
+      </c>
+      <c r="R169" s="11">
+        <v>15</v>
+      </c>
+      <c r="S169" s="11">
+        <v>33</v>
+      </c>
+      <c r="T169" s="11">
+        <v>7</v>
+      </c>
+      <c r="U169" s="11">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="V169" s="11">
+        <v>6.39</v>
+      </c>
+      <c r="W169" s="11">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="X169" s="11">
+        <v>5.2</v>
+      </c>
+      <c r="Y169" s="11">
+        <v>8.0749999999999993</v>
+      </c>
+    </row>
+    <row r="170" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A170" s="12">
+        <v>46132</v>
+      </c>
+      <c r="B170" s="12">
+        <v>46132</v>
+      </c>
+      <c r="C170" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D170" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E170" s="11">
+        <v>50</v>
+      </c>
+      <c r="F170" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="G170" s="11">
+        <v>38.667000000000002</v>
+      </c>
+      <c r="H170" s="11">
+        <v>24.5</v>
+      </c>
+      <c r="I170" s="11">
+        <v>20.8</v>
+      </c>
+      <c r="J170" s="11">
+        <v>21.8</v>
+      </c>
+      <c r="K170" s="11">
+        <v>85</v>
+      </c>
+      <c r="L170" s="11">
+        <v>29.5</v>
+      </c>
+      <c r="M170" s="11">
+        <v>68.772999999999996</v>
+      </c>
+      <c r="N170" s="11">
+        <v>14.5</v>
+      </c>
+      <c r="O170" s="11">
+        <v>12.8</v>
+      </c>
+      <c r="P170" s="11">
+        <v>13.375</v>
+      </c>
+      <c r="Q170" s="11">
+        <v>51</v>
+      </c>
+      <c r="R170" s="11">
+        <v>15</v>
+      </c>
+      <c r="S170" s="11">
+        <v>33</v>
+      </c>
+      <c r="T170" s="11">
+        <v>7</v>
+      </c>
+      <c r="U170" s="11">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="V170" s="11">
+        <v>6.39</v>
+      </c>
+      <c r="W170" s="11">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="X170" s="11">
+        <v>5.2</v>
+      </c>
+      <c r="Y170" s="11">
+        <v>8.0749999999999993</v>
+      </c>
+    </row>
+    <row r="171" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A171" s="12">
+        <v>46132</v>
+      </c>
+      <c r="B171" s="12">
+        <v>46132</v>
+      </c>
+      <c r="C171" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D171" s="7" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -24086,19 +24368,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:AK6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.36328125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.26953125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.3984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.09765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.296875" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="9" style="11"/>
-    <col min="8" max="10" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="9.09765625" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="5" customFormat="1">
+    <row r="1" spans="1:37" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -24187,7 +24469,7 @@
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
     </row>
-    <row r="2" spans="1:37">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -24268,7 +24550,7 @@
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
     </row>
-    <row r="3" spans="1:37">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45962</v>
       </c>
@@ -24357,7 +24639,7 @@
       <c r="AJ3" s="2"/>
       <c r="AK3" s="2"/>
     </row>
-    <row r="4" spans="1:37">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45992</v>
       </c>
@@ -24446,7 +24728,7 @@
       <c r="AJ4" s="2"/>
       <c r="AK4" s="2"/>
     </row>
-    <row r="5" spans="1:37">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>46023</v>
       </c>
@@ -24478,7 +24760,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:37">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>46054</v>
       </c>
@@ -24571,24 +24853,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:Y13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.09765625" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.09765625" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="14"/>
-    <col min="7" max="7" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.453125" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.09765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5" style="14" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="14"/>
-    <col min="10" max="10" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.09765625" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="9" style="14"/>
-    <col min="13" max="13" width="13.26953125" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.296875" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
+    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
@@ -24641,7 +24923,7 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -24686,7 +24968,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -24739,7 +25021,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -24792,7 +25074,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -24833,7 +25115,7 @@
         <v>118.333</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -24874,7 +25156,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -24915,7 +25197,7 @@
         <v>122.667</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="12">
         <v>46083</v>
       </c>
@@ -24956,7 +25238,7 @@
         <v>123.333</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="12">
         <v>46090</v>
       </c>
@@ -24997,7 +25279,7 @@
         <v>126.667</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="12">
         <v>46097</v>
       </c>
@@ -25038,7 +25320,7 @@
         <v>132.333</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="12">
         <v>46104</v>
       </c>
@@ -25079,7 +25361,7 @@
         <v>143.333</v>
       </c>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" s="12">
         <v>46111</v>
       </c>
@@ -25120,7 +25402,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" s="12">
         <v>46118</v>
       </c>
@@ -25178,18 +25460,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:Y13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.6328125" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.09765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.09765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.59765625" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
+    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -25236,7 +25518,7 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -25275,7 +25557,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -25322,7 +25604,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -25369,7 +25651,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -25401,7 +25683,7 @@
         <v>9.6539999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -25433,7 +25715,7 @@
         <v>9.8650000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -25465,7 +25747,7 @@
         <v>10.221</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="12">
         <v>46083</v>
       </c>
@@ -25497,7 +25779,7 @@
         <v>10.721</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="12">
         <v>46090</v>
       </c>
@@ -25529,7 +25811,7 @@
         <v>11.462</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="12">
         <v>46097</v>
       </c>
@@ -25561,7 +25843,7 @@
         <v>11.962</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="12">
         <v>46104</v>
       </c>
@@ -25593,7 +25875,7 @@
         <v>12.865</v>
       </c>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" s="12">
         <v>46111</v>
       </c>
@@ -25625,7 +25907,7 @@
         <v>12.71</v>
       </c>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" s="12">
         <v>46118</v>
       </c>
@@ -25673,7 +25955,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="16384" width="9" style="3"/>
   </cols>
@@ -25688,15 +25970,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.90625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.90625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.6328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.8984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.8984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.59765625" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>48</v>
       </c>
@@ -25707,7 +25989,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
@@ -25721,7 +26003,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="s">
         <v>29</v>
@@ -25730,7 +26012,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>31</v>
@@ -25739,7 +26021,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
         <v>33</v>
@@ -25748,7 +26030,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="2" t="s">
         <v>35</v>
@@ -25757,7 +26039,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
         <v>37</v>
@@ -25766,7 +26048,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
         <v>39</v>
@@ -25775,7 +26057,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>41</v>
       </c>
@@ -25784,49 +26066,49 @@
       </c>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>42</v>
       </c>
@@ -25837,7 +26119,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="2" t="s">
         <v>8</v>
@@ -25846,7 +26128,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="2" t="s">
         <v>9</v>
@@ -25855,7 +26137,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>44</v>
       </c>
@@ -25866,7 +26148,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="2" t="s">
         <v>11</v>
@@ -25875,7 +26157,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>45</v>
       </c>
@@ -25884,42 +26166,42 @@
       </c>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C22" s="2"/>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C26" s="2"/>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>46</v>
       </c>
@@ -25928,35 +26210,35 @@
       </c>
       <c r="C27" s="2"/>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C28" s="2"/>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C29" s="2"/>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C30" s="2"/>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C31" s="2"/>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="2" t="s">
         <v>23</v>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2442FA5-CF84-47EB-A421-ED0262498A33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B979E86-1EF4-43AC-9DDF-1ADD664A07ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11430" yWindow="0" windowWidth="11700" windowHeight="14730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -253,23 +253,23 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -282,7 +282,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -325,7 +325,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -346,27 +346,27 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -374,8 +374,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -393,7 +393,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1465,6 +1465,9 @@
                 <c:pt idx="167">
                   <c:v>38.667000000000002</c:v>
                 </c:pt>
+                <c:pt idx="168">
+                  <c:v>38.667000000000002</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2530,6 +2533,9 @@
                 <c:pt idx="167">
                   <c:v>21.8</c:v>
                 </c:pt>
+                <c:pt idx="168">
+                  <c:v>21.8</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3595,6 +3601,9 @@
                 <c:pt idx="167">
                   <c:v>68.772999999999996</c:v>
                 </c:pt>
+                <c:pt idx="168">
+                  <c:v>68.545000000000002</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4660,6 +4669,9 @@
                 <c:pt idx="167">
                   <c:v>13.375</c:v>
                 </c:pt>
+                <c:pt idx="168">
+                  <c:v>13.375</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -5723,6 +5735,9 @@
                   <c:v>33</c:v>
                 </c:pt>
                 <c:pt idx="167">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="168">
                   <c:v>33</c:v>
                 </c:pt>
               </c:numCache>
@@ -6806,6 +6821,9 @@
                 <c:pt idx="167">
                   <c:v>6.39</c:v>
                 </c:pt>
+                <c:pt idx="168">
+                  <c:v>6.39</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -7871,6 +7889,9 @@
                   <c:v>8.0749999999999993</c:v>
                 </c:pt>
                 <c:pt idx="167">
+                  <c:v>8.0749999999999993</c:v>
+                </c:pt>
+                <c:pt idx="168">
                   <c:v>8.0749999999999993</c:v>
                 </c:pt>
               </c:numCache>
@@ -8149,7 +8170,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -8731,7 +8752,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -11245,17 +11266,17 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:Y171"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.09765625" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.09765625" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.296875" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.26953125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="5" customFormat="1">
       <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
@@ -11332,7 +11353,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -11401,7 +11422,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="12">
         <v>46044</v>
       </c>
@@ -11478,7 +11499,7 @@
         <v>4.9450000000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="12">
         <v>46045</v>
       </c>
@@ -11555,7 +11576,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="12">
         <v>46045</v>
       </c>
@@ -11632,7 +11653,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="12">
         <v>46045</v>
       </c>
@@ -11709,7 +11730,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="12">
         <v>46048</v>
       </c>
@@ -11786,7 +11807,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25">
       <c r="A8" s="12">
         <v>46048</v>
       </c>
@@ -11863,7 +11884,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25">
       <c r="A9" s="12">
         <v>46048</v>
       </c>
@@ -11940,7 +11961,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25">
       <c r="A10" s="12">
         <v>46049</v>
       </c>
@@ -12017,7 +12038,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25">
       <c r="A11" s="12">
         <v>46049</v>
       </c>
@@ -12094,7 +12115,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25">
       <c r="A12" s="12">
         <v>46049</v>
       </c>
@@ -12171,7 +12192,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25">
       <c r="A13" s="12">
         <v>46050</v>
       </c>
@@ -12248,7 +12269,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25">
       <c r="A14" s="12">
         <v>46050</v>
       </c>
@@ -12325,7 +12346,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25">
       <c r="A15" s="12">
         <v>46050</v>
       </c>
@@ -12402,7 +12423,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25">
       <c r="A16" s="12">
         <v>46051</v>
       </c>
@@ -12479,7 +12500,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:25">
       <c r="A17" s="12">
         <v>46051</v>
       </c>
@@ -12556,7 +12577,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:25">
       <c r="A18" s="12">
         <v>46051</v>
       </c>
@@ -12633,7 +12654,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:25">
       <c r="A19" s="12">
         <v>46052</v>
       </c>
@@ -12710,7 +12731,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:25">
       <c r="A20" s="12">
         <v>46052</v>
       </c>
@@ -12787,7 +12808,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:25">
       <c r="A21" s="12">
         <v>46052</v>
       </c>
@@ -12864,7 +12885,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:25">
       <c r="A22" s="12">
         <v>46055</v>
       </c>
@@ -12941,7 +12962,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:25">
       <c r="A23" s="12">
         <v>46055</v>
       </c>
@@ -13018,7 +13039,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:25">
       <c r="A24" s="12">
         <v>46055</v>
       </c>
@@ -13095,7 +13116,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:25">
       <c r="A25" s="12">
         <v>46056</v>
       </c>
@@ -13172,7 +13193,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:25">
       <c r="A26" s="12">
         <v>46056</v>
       </c>
@@ -13249,7 +13270,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:25">
       <c r="A27" s="12">
         <v>46056</v>
       </c>
@@ -13326,7 +13347,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:25">
       <c r="A28" s="12">
         <v>46057</v>
       </c>
@@ -13403,7 +13424,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:25">
       <c r="A29" s="12">
         <v>46057</v>
       </c>
@@ -13480,7 +13501,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:25">
       <c r="A30" s="12">
         <v>46057</v>
       </c>
@@ -13557,7 +13578,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:25">
       <c r="A31" s="12">
         <v>46058</v>
       </c>
@@ -13634,7 +13655,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:25">
       <c r="A32" s="12">
         <v>46058</v>
       </c>
@@ -13711,7 +13732,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:25">
       <c r="A33" s="12">
         <v>46058</v>
       </c>
@@ -13788,7 +13809,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:25">
       <c r="A34" s="12">
         <v>46059</v>
       </c>
@@ -13865,7 +13886,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:25">
       <c r="A35" s="12">
         <v>46059</v>
       </c>
@@ -13942,7 +13963,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:25">
       <c r="A36" s="12">
         <v>46059</v>
       </c>
@@ -14019,7 +14040,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:25">
       <c r="A37" s="12">
         <v>46062</v>
       </c>
@@ -14096,7 +14117,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:25">
       <c r="A38" s="12">
         <v>46062</v>
       </c>
@@ -14173,7 +14194,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:25">
       <c r="A39" s="12">
         <v>46062</v>
       </c>
@@ -14250,7 +14271,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:25">
       <c r="A40" s="12">
         <v>46063</v>
       </c>
@@ -14327,7 +14348,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:25">
       <c r="A41" s="12">
         <v>46063</v>
       </c>
@@ -14404,7 +14425,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:25">
       <c r="A42" s="12">
         <v>46063</v>
       </c>
@@ -14481,7 +14502,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:25">
       <c r="A43" s="12">
         <v>46064</v>
       </c>
@@ -14558,7 +14579,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:25">
       <c r="A44" s="12">
         <v>46064</v>
       </c>
@@ -14635,7 +14656,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:25">
       <c r="A45" s="12">
         <v>46064</v>
       </c>
@@ -14712,7 +14733,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:25">
       <c r="A46" s="12">
         <v>46065</v>
       </c>
@@ -14789,7 +14810,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:25">
       <c r="A47" s="12">
         <v>46065</v>
       </c>
@@ -14866,7 +14887,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:25">
       <c r="A48" s="12">
         <v>46065</v>
       </c>
@@ -14943,7 +14964,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:25">
       <c r="A49" s="12">
         <v>46066</v>
       </c>
@@ -15020,7 +15041,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:25">
       <c r="A50" s="12">
         <v>46066</v>
       </c>
@@ -15097,7 +15118,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:25">
       <c r="A51" s="12">
         <v>46066</v>
       </c>
@@ -15174,7 +15195,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:25">
       <c r="A52" s="12">
         <v>46076</v>
       </c>
@@ -15251,7 +15272,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:25">
       <c r="A53" s="12">
         <v>46076</v>
       </c>
@@ -15328,7 +15349,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:25">
       <c r="A54" s="12">
         <v>46076</v>
       </c>
@@ -15405,7 +15426,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:25">
       <c r="A55" s="12">
         <v>46077</v>
       </c>
@@ -15482,7 +15503,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:25">
       <c r="A56" s="12">
         <v>46077</v>
       </c>
@@ -15559,7 +15580,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:25">
       <c r="A57" s="12">
         <v>46077</v>
       </c>
@@ -15636,7 +15657,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:25">
       <c r="A58" s="12">
         <v>46078</v>
       </c>
@@ -15713,7 +15734,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:25">
       <c r="A59" s="12">
         <v>46078</v>
       </c>
@@ -15790,7 +15811,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:25">
       <c r="A60" s="12">
         <v>46078</v>
       </c>
@@ -15867,7 +15888,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="61" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:25">
       <c r="A61" s="12">
         <v>46079</v>
       </c>
@@ -15944,7 +15965,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="62" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:25">
       <c r="A62" s="12">
         <v>46079</v>
       </c>
@@ -16021,7 +16042,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="63" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:25">
       <c r="A63" s="12">
         <v>46079</v>
       </c>
@@ -16098,7 +16119,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="64" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:25">
       <c r="A64" s="12">
         <v>46080</v>
       </c>
@@ -16175,7 +16196,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="65" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:25">
       <c r="A65" s="12">
         <v>46080</v>
       </c>
@@ -16252,7 +16273,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="66" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:25">
       <c r="A66" s="12">
         <v>46080</v>
       </c>
@@ -16329,7 +16350,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="67" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:25">
       <c r="A67" s="12">
         <v>46083</v>
       </c>
@@ -16406,7 +16427,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="68" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:25">
       <c r="A68" s="12">
         <v>46083</v>
       </c>
@@ -16483,7 +16504,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="69" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:25">
       <c r="A69" s="12">
         <v>46083</v>
       </c>
@@ -16560,7 +16581,7 @@
         <v>5.68</v>
       </c>
     </row>
-    <row r="70" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:25">
       <c r="A70" s="12">
         <v>46084</v>
       </c>
@@ -16637,7 +16658,7 @@
         <v>5.7590000000000003</v>
       </c>
     </row>
-    <row r="71" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:25">
       <c r="A71" s="12">
         <v>46084</v>
       </c>
@@ -16714,7 +16735,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="72" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:25">
       <c r="A72" s="12">
         <v>46084</v>
       </c>
@@ -16791,7 +16812,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="73" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:25">
       <c r="A73" s="12">
         <v>46085</v>
       </c>
@@ -16868,7 +16889,7 @@
         <v>5.8390000000000004</v>
       </c>
     </row>
-    <row r="74" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:25">
       <c r="A74" s="12">
         <v>46085</v>
       </c>
@@ -16945,7 +16966,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:25">
       <c r="A75" s="12">
         <v>46085</v>
       </c>
@@ -17022,7 +17043,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:25">
       <c r="A76" s="12">
         <v>46086</v>
       </c>
@@ -17099,7 +17120,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="77" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:25">
       <c r="A77" s="12">
         <v>46086</v>
       </c>
@@ -17176,7 +17197,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="78" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:25">
       <c r="A78" s="12">
         <v>46086</v>
       </c>
@@ -17253,7 +17274,7 @@
         <v>5.9210000000000003</v>
       </c>
     </row>
-    <row r="79" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:25">
       <c r="A79" s="12">
         <v>46087</v>
       </c>
@@ -17330,7 +17351,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="80" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:25">
       <c r="A80" s="12">
         <v>46087</v>
       </c>
@@ -17407,7 +17428,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="81" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:25">
       <c r="A81" s="12">
         <v>46087</v>
       </c>
@@ -17484,7 +17505,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="82" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:25">
       <c r="A82" s="12">
         <v>46090</v>
       </c>
@@ -17561,7 +17582,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="83" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:25">
       <c r="A83" s="12">
         <v>46090</v>
       </c>
@@ -17638,7 +17659,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="84" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:25">
       <c r="A84" s="12">
         <v>46090</v>
       </c>
@@ -17715,7 +17736,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="85" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:25">
       <c r="A85" s="12">
         <v>46091</v>
       </c>
@@ -17792,7 +17813,7 @@
         <v>6.157</v>
       </c>
     </row>
-    <row r="86" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:25">
       <c r="A86" s="12">
         <v>46091</v>
       </c>
@@ -17869,7 +17890,7 @@
         <v>6.181</v>
       </c>
     </row>
-    <row r="87" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:25">
       <c r="A87" s="12">
         <v>46091</v>
       </c>
@@ -17946,7 +17967,7 @@
         <v>6.181</v>
       </c>
     </row>
-    <row r="88" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:25">
       <c r="A88" s="12">
         <v>46092</v>
       </c>
@@ -18023,7 +18044,7 @@
         <v>6.2430000000000003</v>
       </c>
     </row>
-    <row r="89" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:25">
       <c r="A89" s="12">
         <v>46092</v>
       </c>
@@ -18100,7 +18121,7 @@
         <v>6.29</v>
       </c>
     </row>
-    <row r="90" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:25">
       <c r="A90" s="12">
         <v>46092</v>
       </c>
@@ -18177,7 +18198,7 @@
         <v>6.3049999999999997</v>
       </c>
     </row>
-    <row r="91" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:25">
       <c r="A91" s="12">
         <v>46093</v>
       </c>
@@ -18254,7 +18275,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="92" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:25">
       <c r="A92" s="12">
         <v>46093</v>
       </c>
@@ -18331,7 +18352,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="93" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:25">
       <c r="A93" s="12">
         <v>46093</v>
       </c>
@@ -18408,7 +18429,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="94" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:25">
       <c r="A94" s="12">
         <v>46094</v>
       </c>
@@ -18485,7 +18506,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="95" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:25">
       <c r="A95" s="12">
         <v>46094</v>
       </c>
@@ -18562,7 +18583,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="96" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:25">
       <c r="A96" s="12">
         <v>46094</v>
       </c>
@@ -18639,7 +18660,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="97" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:25">
       <c r="A97" s="12">
         <v>46097</v>
       </c>
@@ -18716,7 +18737,7 @@
         <v>6.5330000000000004</v>
       </c>
     </row>
-    <row r="98" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:25">
       <c r="A98" s="12">
         <v>46097</v>
       </c>
@@ -18793,7 +18814,7 @@
         <v>6.5119999999999996</v>
       </c>
     </row>
-    <row r="99" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:25">
       <c r="A99" s="12">
         <v>46097</v>
       </c>
@@ -18870,7 +18891,7 @@
         <v>6.5119999999999996</v>
       </c>
     </row>
-    <row r="100" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:25">
       <c r="A100" s="12">
         <v>46098</v>
       </c>
@@ -18947,7 +18968,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="101" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:25">
       <c r="A101" s="12">
         <v>46098</v>
       </c>
@@ -19024,7 +19045,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="102" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:25">
       <c r="A102" s="12">
         <v>46098</v>
       </c>
@@ -19101,7 +19122,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="103" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:25">
       <c r="A103" s="12">
         <v>46099</v>
       </c>
@@ -19178,7 +19199,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="104" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:25">
       <c r="A104" s="12">
         <v>46099</v>
       </c>
@@ -19255,7 +19276,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="105" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:25">
       <c r="A105" s="12">
         <v>46099</v>
       </c>
@@ -19332,7 +19353,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="106" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:25">
       <c r="A106" s="12">
         <v>46100</v>
       </c>
@@ -19409,7 +19430,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="107" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:25">
       <c r="A107" s="12">
         <v>46100</v>
       </c>
@@ -19486,7 +19507,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="108" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:25">
       <c r="A108" s="12">
         <v>46100</v>
       </c>
@@ -19563,7 +19584,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="109" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:25">
       <c r="A109" s="12">
         <v>46101</v>
       </c>
@@ -19640,7 +19661,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="110" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:25">
       <c r="A110" s="12">
         <v>46101</v>
       </c>
@@ -19717,7 +19738,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="111" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:25">
       <c r="A111" s="12">
         <v>46101</v>
       </c>
@@ -19794,7 +19815,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="112" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:25">
       <c r="A112" s="12">
         <v>46104</v>
       </c>
@@ -19871,7 +19892,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="113" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:25">
       <c r="A113" s="12">
         <v>46104</v>
       </c>
@@ -19948,7 +19969,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="114" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:25">
       <c r="A114" s="12">
         <v>46104</v>
       </c>
@@ -20025,7 +20046,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="115" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:25">
       <c r="A115" s="12">
         <v>46105</v>
       </c>
@@ -20102,7 +20123,7 @@
         <v>7.0250000000000004</v>
       </c>
     </row>
-    <row r="116" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:25">
       <c r="A116" s="12">
         <v>46105</v>
       </c>
@@ -20179,7 +20200,7 @@
         <v>7.125</v>
       </c>
     </row>
-    <row r="117" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:25">
       <c r="A117" s="12">
         <v>46105</v>
       </c>
@@ -20256,7 +20277,7 @@
         <v>7.125</v>
       </c>
     </row>
-    <row r="118" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:25">
       <c r="A118" s="12">
         <v>46106</v>
       </c>
@@ -20333,7 +20354,7 @@
         <v>7.15</v>
       </c>
     </row>
-    <row r="119" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:25">
       <c r="A119" s="12">
         <v>46106</v>
       </c>
@@ -20410,7 +20431,7 @@
         <v>7.2249999999999996</v>
       </c>
     </row>
-    <row r="120" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:25">
       <c r="A120" s="12">
         <v>46106</v>
       </c>
@@ -20487,7 +20508,7 @@
         <v>7.2249999999999996</v>
       </c>
     </row>
-    <row r="121" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:25">
       <c r="A121" s="12">
         <v>46107</v>
       </c>
@@ -20564,7 +20585,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="122" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:25">
       <c r="A122" s="12">
         <v>46107</v>
       </c>
@@ -20641,7 +20662,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="123" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:25">
       <c r="A123" s="12">
         <v>46107</v>
       </c>
@@ -20718,7 +20739,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="124" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:25">
       <c r="A124" s="12">
         <v>46108</v>
       </c>
@@ -20795,7 +20816,7 @@
         <v>7.375</v>
       </c>
     </row>
-    <row r="125" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:25">
       <c r="A125" s="12">
         <v>46108</v>
       </c>
@@ -20872,7 +20893,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="126" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:25">
       <c r="A126" s="12">
         <v>46108</v>
       </c>
@@ -20949,7 +20970,7 @@
         <v>7.375</v>
       </c>
     </row>
-    <row r="127" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:25">
       <c r="A127" s="12">
         <v>46111</v>
       </c>
@@ -21026,7 +21047,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="128" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:25">
       <c r="A128" s="12">
         <v>46111</v>
       </c>
@@ -21103,7 +21124,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="129" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:25">
       <c r="A129" s="12">
         <v>46111</v>
       </c>
@@ -21180,7 +21201,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="130" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:25">
       <c r="A130" s="12">
         <v>46112</v>
       </c>
@@ -21257,7 +21278,7 @@
         <v>7.5250000000000004</v>
       </c>
     </row>
-    <row r="131" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:25">
       <c r="A131" s="12">
         <v>46112</v>
       </c>
@@ -21334,7 +21355,7 @@
         <v>7.5250000000000004</v>
       </c>
     </row>
-    <row r="132" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:25">
       <c r="A132" s="12">
         <v>46112</v>
       </c>
@@ -21411,7 +21432,7 @@
         <v>7.55</v>
       </c>
     </row>
-    <row r="133" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:25">
       <c r="A133" s="12">
         <v>46113</v>
       </c>
@@ -21488,7 +21509,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="134" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:25">
       <c r="A134" s="12">
         <v>46113</v>
       </c>
@@ -21565,7 +21586,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="135" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:25">
       <c r="A135" s="12">
         <v>46113</v>
       </c>
@@ -21642,7 +21663,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="136" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:25">
       <c r="A136" s="12">
         <v>46114</v>
       </c>
@@ -21719,7 +21740,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="137" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:25">
       <c r="A137" s="12">
         <v>46114</v>
       </c>
@@ -21796,7 +21817,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="138" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:25">
       <c r="A138" s="12">
         <v>46114</v>
       </c>
@@ -21873,7 +21894,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="139" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:25">
       <c r="A139" s="12">
         <v>46115</v>
       </c>
@@ -21950,7 +21971,7 @@
         <v>7.6749999999999998</v>
       </c>
     </row>
-    <row r="140" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:25">
       <c r="A140" s="12">
         <v>46115</v>
       </c>
@@ -22027,7 +22048,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="141" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:25">
       <c r="A141" s="12">
         <v>46115</v>
       </c>
@@ -22104,7 +22125,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="142" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:25">
       <c r="A142" s="12">
         <v>46119</v>
       </c>
@@ -22181,7 +22202,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="143" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:25">
       <c r="A143" s="12">
         <v>46119</v>
       </c>
@@ -22258,7 +22279,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="144" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:25">
       <c r="A144" s="12">
         <v>46119</v>
       </c>
@@ -22335,7 +22356,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="145" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:25">
       <c r="A145" s="12">
         <v>46120</v>
       </c>
@@ -22412,7 +22433,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="146" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:25">
       <c r="A146" s="12">
         <v>46120</v>
       </c>
@@ -22489,7 +22510,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="147" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:25">
       <c r="A147" s="12">
         <v>46120</v>
       </c>
@@ -22566,7 +22587,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="148" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:25">
       <c r="A148" s="12">
         <v>46121</v>
       </c>
@@ -22643,7 +22664,7 @@
         <v>7.7249999999999996</v>
       </c>
     </row>
-    <row r="149" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:25">
       <c r="A149" s="12">
         <v>46121</v>
       </c>
@@ -22720,7 +22741,7 @@
         <v>7.7249999999999996</v>
       </c>
     </row>
-    <row r="150" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:25">
       <c r="A150" s="12">
         <v>46121</v>
       </c>
@@ -22797,7 +22818,7 @@
         <v>7.7249999999999996</v>
       </c>
     </row>
-    <row r="151" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:25">
       <c r="A151" s="12">
         <v>46122</v>
       </c>
@@ -22874,7 +22895,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="152" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:25">
       <c r="A152" s="12">
         <v>46122</v>
       </c>
@@ -22951,7 +22972,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="153" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:25">
       <c r="A153" s="12">
         <v>46122</v>
       </c>
@@ -23028,7 +23049,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="154" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:25">
       <c r="A154" s="12">
         <v>46125</v>
       </c>
@@ -23105,7 +23126,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="155" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:25">
       <c r="A155" s="12">
         <v>46125</v>
       </c>
@@ -23182,7 +23203,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="156" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:25">
       <c r="A156" s="12">
         <v>46125</v>
       </c>
@@ -23259,7 +23280,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="157" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:25">
       <c r="A157" s="12">
         <v>46126</v>
       </c>
@@ -23336,7 +23357,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="158" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:25">
       <c r="A158" s="12">
         <v>46126</v>
       </c>
@@ -23413,7 +23434,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="159" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:25">
       <c r="A159" s="12">
         <v>46126</v>
       </c>
@@ -23490,7 +23511,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="160" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:25">
       <c r="A160" s="12">
         <v>46127</v>
       </c>
@@ -23567,7 +23588,7 @@
         <v>7.85</v>
       </c>
     </row>
-    <row r="161" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:25">
       <c r="A161" s="12">
         <v>46127</v>
       </c>
@@ -23644,7 +23665,7 @@
         <v>7.85</v>
       </c>
     </row>
-    <row r="162" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:25">
       <c r="A162" s="12">
         <v>46127</v>
       </c>
@@ -23721,7 +23742,7 @@
         <v>7.8630000000000004</v>
       </c>
     </row>
-    <row r="163" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:25">
       <c r="A163" s="12">
         <v>46128</v>
       </c>
@@ -23798,7 +23819,7 @@
         <v>7.8630000000000004</v>
       </c>
     </row>
-    <row r="164" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:25">
       <c r="A164" s="12">
         <v>46128</v>
       </c>
@@ -23875,7 +23896,7 @@
         <v>7.9749999999999996</v>
       </c>
     </row>
-    <row r="165" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:25">
       <c r="A165" s="12">
         <v>46128</v>
       </c>
@@ -23952,7 +23973,7 @@
         <v>7.9749999999999996</v>
       </c>
     </row>
-    <row r="166" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:25">
       <c r="A166" s="12">
         <v>46129</v>
       </c>
@@ -24029,7 +24050,7 @@
         <v>8.0250000000000004</v>
       </c>
     </row>
-    <row r="167" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:25">
       <c r="A167" s="12">
         <v>46129</v>
       </c>
@@ -24106,7 +24127,7 @@
         <v>8.0250000000000004</v>
       </c>
     </row>
-    <row r="168" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:25">
       <c r="A168" s="12">
         <v>46129</v>
       </c>
@@ -24183,7 +24204,7 @@
         <v>8.0250000000000004</v>
       </c>
     </row>
-    <row r="169" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:25">
       <c r="A169" s="12">
         <v>46132</v>
       </c>
@@ -24260,7 +24281,7 @@
         <v>8.0749999999999993</v>
       </c>
     </row>
-    <row r="170" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:25">
       <c r="A170" s="12">
         <v>46132</v>
       </c>
@@ -24337,7 +24358,7 @@
         <v>8.0749999999999993</v>
       </c>
     </row>
-    <row r="171" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:25">
       <c r="A171" s="12">
         <v>46132</v>
       </c>
@@ -24349,6 +24370,69 @@
       </c>
       <c r="D171" s="7" t="s">
         <v>53</v>
+      </c>
+      <c r="E171" s="11">
+        <v>50</v>
+      </c>
+      <c r="F171" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="G171" s="11">
+        <v>38.667000000000002</v>
+      </c>
+      <c r="H171" s="11">
+        <v>24.5</v>
+      </c>
+      <c r="I171" s="11">
+        <v>20.8</v>
+      </c>
+      <c r="J171" s="11">
+        <v>21.8</v>
+      </c>
+      <c r="K171" s="11">
+        <v>85</v>
+      </c>
+      <c r="L171" s="11">
+        <v>29.5</v>
+      </c>
+      <c r="M171" s="11">
+        <v>68.545000000000002</v>
+      </c>
+      <c r="N171" s="11">
+        <v>14.5</v>
+      </c>
+      <c r="O171" s="11">
+        <v>12.8</v>
+      </c>
+      <c r="P171" s="11">
+        <v>13.375</v>
+      </c>
+      <c r="Q171" s="11">
+        <v>51</v>
+      </c>
+      <c r="R171" s="11">
+        <v>15</v>
+      </c>
+      <c r="S171" s="11">
+        <v>33</v>
+      </c>
+      <c r="T171" s="11">
+        <v>7</v>
+      </c>
+      <c r="U171" s="11">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="V171" s="11">
+        <v>6.39</v>
+      </c>
+      <c r="W171" s="11">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="X171" s="11">
+        <v>5.2</v>
+      </c>
+      <c r="Y171" s="11">
+        <v>8.0749999999999993</v>
       </c>
     </row>
   </sheetData>
@@ -24368,19 +24452,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:AK6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.3984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.09765625" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.296875" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.36328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.26953125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="9" style="11"/>
-    <col min="8" max="10" width="9.09765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:37" s="5" customFormat="1">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -24469,7 +24553,7 @@
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:37">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -24550,7 +24634,7 @@
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:37">
       <c r="A3" s="6">
         <v>45962</v>
       </c>
@@ -24639,7 +24723,7 @@
       <c r="AJ3" s="2"/>
       <c r="AK3" s="2"/>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:37">
       <c r="A4" s="6">
         <v>45992</v>
       </c>
@@ -24728,7 +24812,7 @@
       <c r="AJ4" s="2"/>
       <c r="AK4" s="2"/>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37">
       <c r="A5" s="6">
         <v>46023</v>
       </c>
@@ -24760,7 +24844,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37">
       <c r="A6" s="6">
         <v>46054</v>
       </c>
@@ -24853,24 +24937,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:Y13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.09765625" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.09765625" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="14"/>
-    <col min="7" max="7" width="9.09765625" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.453125" style="14" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="14"/>
-    <col min="10" max="10" width="9.09765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="9" style="14"/>
-    <col min="13" max="13" width="13.296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.26953125" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="5" customFormat="1">
       <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
@@ -24923,7 +25007,7 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -24968,7 +25052,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -25021,7 +25105,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -25074,7 +25158,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -25115,7 +25199,7 @@
         <v>118.333</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -25156,7 +25240,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -25197,7 +25281,7 @@
         <v>122.667</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25">
       <c r="A8" s="12">
         <v>46083</v>
       </c>
@@ -25238,7 +25322,7 @@
         <v>123.333</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25">
       <c r="A9" s="12">
         <v>46090</v>
       </c>
@@ -25279,7 +25363,7 @@
         <v>126.667</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25">
       <c r="A10" s="12">
         <v>46097</v>
       </c>
@@ -25320,7 +25404,7 @@
         <v>132.333</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25">
       <c r="A11" s="12">
         <v>46104</v>
       </c>
@@ -25361,7 +25445,7 @@
         <v>143.333</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25">
       <c r="A12" s="12">
         <v>46111</v>
       </c>
@@ -25402,7 +25486,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25">
       <c r="A13" s="12">
         <v>46118</v>
       </c>
@@ -25460,18 +25544,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:Y13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.09765625" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.09765625" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.59765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.6328125" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="5" customFormat="1">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -25518,7 +25602,7 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -25557,7 +25641,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -25604,7 +25688,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -25651,7 +25735,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -25683,7 +25767,7 @@
         <v>9.6539999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -25715,7 +25799,7 @@
         <v>9.8650000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -25747,7 +25831,7 @@
         <v>10.221</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25">
       <c r="A8" s="12">
         <v>46083</v>
       </c>
@@ -25779,7 +25863,7 @@
         <v>10.721</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25">
       <c r="A9" s="12">
         <v>46090</v>
       </c>
@@ -25811,7 +25895,7 @@
         <v>11.462</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25">
       <c r="A10" s="12">
         <v>46097</v>
       </c>
@@ -25843,7 +25927,7 @@
         <v>11.962</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25">
       <c r="A11" s="12">
         <v>46104</v>
       </c>
@@ -25875,7 +25959,7 @@
         <v>12.865</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25">
       <c r="A12" s="12">
         <v>46111</v>
       </c>
@@ -25907,7 +25991,7 @@
         <v>12.71</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25">
       <c r="A13" s="12">
         <v>46118</v>
       </c>
@@ -25955,7 +26039,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="16384" width="9" style="3"/>
   </cols>
@@ -25970,15 +26054,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="22.8984375" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.8984375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.59765625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.90625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.90625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.6328125" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>48</v>
       </c>
@@ -25989,7 +26073,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
@@ -26003,7 +26087,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="s">
         <v>29</v>
@@ -26012,7 +26096,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>31</v>
@@ -26021,7 +26105,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
         <v>33</v>
@@ -26030,7 +26114,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4">
       <c r="A6" s="1"/>
       <c r="B6" s="2" t="s">
         <v>35</v>
@@ -26039,7 +26123,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
         <v>37</v>
@@ -26048,7 +26132,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
         <v>39</v>
@@ -26057,7 +26141,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
         <v>41</v>
       </c>
@@ -26066,49 +26150,49 @@
       </c>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4">
       <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4">
       <c r="A12" s="1"/>
       <c r="B12" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4">
       <c r="A14" s="1"/>
       <c r="B14" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4">
       <c r="A15" s="1"/>
       <c r="B15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4">
       <c r="A16" s="1" t="s">
         <v>42</v>
       </c>
@@ -26119,7 +26203,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3">
       <c r="A17" s="1"/>
       <c r="B17" s="2" t="s">
         <v>8</v>
@@ -26128,7 +26212,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3">
       <c r="A18" s="1"/>
       <c r="B18" s="2" t="s">
         <v>9</v>
@@ -26137,7 +26221,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3">
       <c r="A19" s="1" t="s">
         <v>44</v>
       </c>
@@ -26148,7 +26232,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3">
       <c r="A20" s="1"/>
       <c r="B20" s="2" t="s">
         <v>11</v>
@@ -26157,7 +26241,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3">
       <c r="A21" s="1" t="s">
         <v>45</v>
       </c>
@@ -26166,42 +26250,42 @@
       </c>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3">
       <c r="A22" s="1"/>
       <c r="B22" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3">
       <c r="A23" s="1"/>
       <c r="B23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3">
       <c r="A24" s="1"/>
       <c r="B24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3">
       <c r="A25" s="1"/>
       <c r="B25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3">
       <c r="A26" s="1"/>
       <c r="B26" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3">
       <c r="A27" s="1" t="s">
         <v>46</v>
       </c>
@@ -26210,35 +26294,35 @@
       </c>
       <c r="C27" s="2"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3">
       <c r="A28" s="1"/>
       <c r="B28" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C28" s="2"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3">
       <c r="A29" s="1"/>
       <c r="B29" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C29" s="2"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3">
       <c r="A30" s="1"/>
       <c r="B30" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C30" s="2"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3">
       <c r="A31" s="1"/>
       <c r="B31" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C31" s="2"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3">
       <c r="A32" s="1"/>
       <c r="B32" s="2" t="s">
         <v>23</v>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2377663E-6357-427B-ACA4-89239981EAF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADE6605F-C62B-4E58-AFDF-7FA27088E75D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -961,6 +961,15 @@
                 <c:pt idx="171">
                   <c:v>46133</c:v>
                 </c:pt>
+                <c:pt idx="172">
+                  <c:v>46134</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>46134</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>46134</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1481,6 +1490,15 @@
                   <c:v>38.832999999999998</c:v>
                 </c:pt>
                 <c:pt idx="170">
+                  <c:v>38.832999999999998</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>38.832999999999998</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>38.832999999999998</c:v>
+                </c:pt>
+                <c:pt idx="173">
                   <c:v>38.832999999999998</c:v>
                 </c:pt>
               </c:numCache>
@@ -2044,6 +2062,15 @@
                 <c:pt idx="171">
                   <c:v>46133</c:v>
                 </c:pt>
+                <c:pt idx="172">
+                  <c:v>46134</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>46134</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>46134</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2564,6 +2591,15 @@
                   <c:v>21.9</c:v>
                 </c:pt>
                 <c:pt idx="170">
+                  <c:v>21.9</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>21.9</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>21.9</c:v>
+                </c:pt>
+                <c:pt idx="173">
                   <c:v>21.9</c:v>
                 </c:pt>
               </c:numCache>
@@ -3127,6 +3163,15 @@
                 <c:pt idx="171">
                   <c:v>46133</c:v>
                 </c:pt>
+                <c:pt idx="172">
+                  <c:v>46134</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>46134</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>46134</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3648,6 +3693,15 @@
                 </c:pt>
                 <c:pt idx="170">
                   <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>67.5</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>66.454999999999998</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>66.227000000000004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4210,6 +4264,15 @@
                 <c:pt idx="171">
                   <c:v>46133</c:v>
                 </c:pt>
+                <c:pt idx="172">
+                  <c:v>46134</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>46134</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>46134</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4731,6 +4794,15 @@
                 </c:pt>
                 <c:pt idx="170">
                   <c:v>13.375</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>13.375</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>13.25</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>13.25</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5293,6 +5365,15 @@
                 <c:pt idx="171">
                   <c:v>46133</c:v>
                 </c:pt>
+                <c:pt idx="172">
+                  <c:v>46134</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>46134</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>46134</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5813,6 +5894,15 @@
                   <c:v>33</c:v>
                 </c:pt>
                 <c:pt idx="170">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>32.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="173">
                   <c:v>33</c:v>
                 </c:pt>
               </c:numCache>
@@ -6392,6 +6482,15 @@
                 <c:pt idx="171">
                   <c:v>46133</c:v>
                 </c:pt>
+                <c:pt idx="172">
+                  <c:v>46134</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>46134</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>46134</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6913,6 +7012,15 @@
                 </c:pt>
                 <c:pt idx="170">
                   <c:v>6.33</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>6.29</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>6.2</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>6.18</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7477,6 +7585,15 @@
                 <c:pt idx="171">
                   <c:v>46133</c:v>
                 </c:pt>
+                <c:pt idx="172">
+                  <c:v>46134</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>46134</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>46134</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7997,6 +8114,15 @@
                   <c:v>8.125</c:v>
                 </c:pt>
                 <c:pt idx="170">
+                  <c:v>8.125</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>8.125</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>8.125</c:v>
+                </c:pt>
+                <c:pt idx="173">
                   <c:v>8.125</c:v>
                 </c:pt>
               </c:numCache>
@@ -11478,7 +11604,7 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y174"/>
+  <dimension ref="A1:Y177"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="12" bestFit="1" customWidth="1"/>
@@ -24813,6 +24939,237 @@
         <v>0.75694444444444453</v>
       </c>
       <c r="D174" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E174" s="11">
+        <v>50</v>
+      </c>
+      <c r="F174" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="G174" s="11">
+        <v>38.832999999999998</v>
+      </c>
+      <c r="H174" s="11">
+        <v>24.5</v>
+      </c>
+      <c r="I174" s="11">
+        <v>20.8</v>
+      </c>
+      <c r="J174" s="11">
+        <v>21.9</v>
+      </c>
+      <c r="K174" s="11">
+        <v>84</v>
+      </c>
+      <c r="L174" s="11">
+        <v>29.5</v>
+      </c>
+      <c r="M174" s="11">
+        <v>67.5</v>
+      </c>
+      <c r="N174" s="11">
+        <v>14.5</v>
+      </c>
+      <c r="O174" s="11">
+        <v>12.8</v>
+      </c>
+      <c r="P174" s="11">
+        <v>13.375</v>
+      </c>
+      <c r="Q174" s="11">
+        <v>51</v>
+      </c>
+      <c r="R174" s="11">
+        <v>15</v>
+      </c>
+      <c r="S174" s="11">
+        <v>33</v>
+      </c>
+      <c r="T174" s="11">
+        <v>6.8</v>
+      </c>
+      <c r="U174" s="11">
+        <v>5</v>
+      </c>
+      <c r="V174" s="11">
+        <v>6.29</v>
+      </c>
+      <c r="W174" s="11">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="X174" s="11">
+        <v>5.2</v>
+      </c>
+      <c r="Y174" s="11">
+        <v>8.125</v>
+      </c>
+    </row>
+    <row r="175" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A175" s="12">
+        <v>46134</v>
+      </c>
+      <c r="B175" s="12">
+        <v>46134</v>
+      </c>
+      <c r="C175" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D175" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E175" s="11">
+        <v>50.5</v>
+      </c>
+      <c r="F175" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="G175" s="11">
+        <v>38.832999999999998</v>
+      </c>
+      <c r="H175" s="11">
+        <v>24.5</v>
+      </c>
+      <c r="I175" s="11">
+        <v>20.5</v>
+      </c>
+      <c r="J175" s="11">
+        <v>21.9</v>
+      </c>
+      <c r="K175" s="11">
+        <v>83</v>
+      </c>
+      <c r="L175" s="11">
+        <v>29.5</v>
+      </c>
+      <c r="M175" s="11">
+        <v>66.454999999999998</v>
+      </c>
+      <c r="N175" s="11">
+        <v>14.5</v>
+      </c>
+      <c r="O175" s="11">
+        <v>12.8</v>
+      </c>
+      <c r="P175" s="11">
+        <v>13.25</v>
+      </c>
+      <c r="Q175" s="11">
+        <v>51</v>
+      </c>
+      <c r="R175" s="11">
+        <v>15</v>
+      </c>
+      <c r="S175" s="11">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="T175" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="U175" s="11">
+        <v>5</v>
+      </c>
+      <c r="V175" s="11">
+        <v>6.2</v>
+      </c>
+      <c r="W175" s="11">
+        <v>10.3</v>
+      </c>
+      <c r="X175" s="11">
+        <v>5.15</v>
+      </c>
+      <c r="Y175" s="11">
+        <v>8.125</v>
+      </c>
+    </row>
+    <row r="176" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A176" s="12">
+        <v>46134</v>
+      </c>
+      <c r="B176" s="12">
+        <v>46134</v>
+      </c>
+      <c r="C176" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D176" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E176" s="11">
+        <v>50.5</v>
+      </c>
+      <c r="F176" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="G176" s="11">
+        <v>38.832999999999998</v>
+      </c>
+      <c r="H176" s="11">
+        <v>24.5</v>
+      </c>
+      <c r="I176" s="11">
+        <v>20.8</v>
+      </c>
+      <c r="J176" s="11">
+        <v>21.9</v>
+      </c>
+      <c r="K176" s="11">
+        <v>83</v>
+      </c>
+      <c r="L176" s="11">
+        <v>29.5</v>
+      </c>
+      <c r="M176" s="11">
+        <v>66.227000000000004</v>
+      </c>
+      <c r="N176" s="11">
+        <v>14.5</v>
+      </c>
+      <c r="O176" s="11">
+        <v>12.8</v>
+      </c>
+      <c r="P176" s="11">
+        <v>13.25</v>
+      </c>
+      <c r="Q176" s="11">
+        <v>51</v>
+      </c>
+      <c r="R176" s="11">
+        <v>15</v>
+      </c>
+      <c r="S176" s="11">
+        <v>33</v>
+      </c>
+      <c r="T176" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="U176" s="11">
+        <v>5</v>
+      </c>
+      <c r="V176" s="11">
+        <v>6.18</v>
+      </c>
+      <c r="W176" s="11">
+        <v>10.3</v>
+      </c>
+      <c r="X176" s="11">
+        <v>5.15</v>
+      </c>
+      <c r="Y176" s="11">
+        <v>8.125</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A177" s="12">
+        <v>46134</v>
+      </c>
+      <c r="B177" s="12">
+        <v>46134</v>
+      </c>
+      <c r="C177" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D177" s="7" t="s">
         <v>53</v>
       </c>
     </row>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92ADDAE3-4D1C-493F-86CA-92D4DBF57628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{687CC511-7C71-412E-B650-A015FC1E1FAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -979,6 +979,15 @@
                 <c:pt idx="177">
                   <c:v>46135</c:v>
                 </c:pt>
+                <c:pt idx="178">
+                  <c:v>46136</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>46136</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>46136</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1518,6 +1527,15 @@
                 </c:pt>
                 <c:pt idx="176">
                   <c:v>38.667000000000002</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>38.667000000000002</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>38.667000000000002</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>38.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2098,6 +2116,15 @@
                 <c:pt idx="177">
                   <c:v>46135</c:v>
                 </c:pt>
+                <c:pt idx="178">
+                  <c:v>46136</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>46136</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>46136</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2636,6 +2663,15 @@
                   <c:v>21.9</c:v>
                 </c:pt>
                 <c:pt idx="176">
+                  <c:v>21.9</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>21.9</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>21.9</c:v>
+                </c:pt>
+                <c:pt idx="179">
                   <c:v>21.9</c:v>
                 </c:pt>
               </c:numCache>
@@ -3217,6 +3253,15 @@
                 <c:pt idx="177">
                   <c:v>46135</c:v>
                 </c:pt>
+                <c:pt idx="178">
+                  <c:v>46136</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>46136</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>46136</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3756,6 +3801,15 @@
                 </c:pt>
                 <c:pt idx="176">
                   <c:v>64.727000000000004</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>64.727000000000004</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>63.908999999999999</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>63.908999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4336,6 +4390,15 @@
                 <c:pt idx="177">
                   <c:v>46135</c:v>
                 </c:pt>
+                <c:pt idx="178">
+                  <c:v>46136</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>46136</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>46136</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4875,6 +4938,15 @@
                 </c:pt>
                 <c:pt idx="176">
                   <c:v>13.2</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>13.2</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>13.15</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>13.15</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5455,6 +5527,15 @@
                 <c:pt idx="177">
                   <c:v>46135</c:v>
                 </c:pt>
+                <c:pt idx="178">
+                  <c:v>46136</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>46136</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>46136</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5994,6 +6075,15 @@
                 </c:pt>
                 <c:pt idx="176">
                   <c:v>32.6</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>32.6</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>32.5</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>32.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6590,6 +6680,15 @@
                 <c:pt idx="177">
                   <c:v>46135</c:v>
                 </c:pt>
+                <c:pt idx="178">
+                  <c:v>46136</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>46136</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>46136</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7129,6 +7228,15 @@
                 </c:pt>
                 <c:pt idx="176">
                   <c:v>6.12</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>6.12</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>6.06</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>6.06</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7711,6 +7819,15 @@
                 <c:pt idx="177">
                   <c:v>46135</c:v>
                 </c:pt>
+                <c:pt idx="178">
+                  <c:v>46136</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>46136</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>46136</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8249,6 +8366,15 @@
                   <c:v>8.125</c:v>
                 </c:pt>
                 <c:pt idx="176">
+                  <c:v>8.125</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>8.125</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>8.125</c:v>
+                </c:pt>
+                <c:pt idx="179">
                   <c:v>8.125</c:v>
                 </c:pt>
               </c:numCache>
@@ -11730,7 +11856,7 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y180"/>
+  <dimension ref="A1:Y183"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="12" bestFit="1" customWidth="1"/>
@@ -25527,6 +25653,237 @@
         <v>0.75694444444444453</v>
       </c>
       <c r="D180" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E180" s="11">
+        <v>50.5</v>
+      </c>
+      <c r="F180" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="G180" s="11">
+        <v>38.667000000000002</v>
+      </c>
+      <c r="H180" s="11">
+        <v>24.5</v>
+      </c>
+      <c r="I180" s="11">
+        <v>20.8</v>
+      </c>
+      <c r="J180" s="11">
+        <v>21.9</v>
+      </c>
+      <c r="K180" s="11">
+        <v>80</v>
+      </c>
+      <c r="L180" s="11">
+        <v>29.5</v>
+      </c>
+      <c r="M180" s="11">
+        <v>64.727000000000004</v>
+      </c>
+      <c r="N180" s="11">
+        <v>14.5</v>
+      </c>
+      <c r="O180" s="11">
+        <v>12</v>
+      </c>
+      <c r="P180" s="11">
+        <v>13.2</v>
+      </c>
+      <c r="Q180" s="11">
+        <v>51</v>
+      </c>
+      <c r="R180" s="11">
+        <v>15</v>
+      </c>
+      <c r="S180" s="11">
+        <v>32.6</v>
+      </c>
+      <c r="T180" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="U180" s="11">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="V180" s="11">
+        <v>6.12</v>
+      </c>
+      <c r="W180" s="11">
+        <v>10.3</v>
+      </c>
+      <c r="X180" s="11">
+        <v>5.15</v>
+      </c>
+      <c r="Y180" s="11">
+        <v>8.125</v>
+      </c>
+    </row>
+    <row r="181" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A181" s="12">
+        <v>46136</v>
+      </c>
+      <c r="B181" s="12">
+        <v>46136</v>
+      </c>
+      <c r="C181" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D181" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E181" s="11">
+        <v>50.6</v>
+      </c>
+      <c r="F181" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="G181" s="11">
+        <v>38.667000000000002</v>
+      </c>
+      <c r="H181" s="11">
+        <v>24.8</v>
+      </c>
+      <c r="I181" s="11">
+        <v>21</v>
+      </c>
+      <c r="J181" s="11">
+        <v>21.9</v>
+      </c>
+      <c r="K181" s="11">
+        <v>80</v>
+      </c>
+      <c r="L181" s="11">
+        <v>30</v>
+      </c>
+      <c r="M181" s="11">
+        <v>63.908999999999999</v>
+      </c>
+      <c r="N181" s="11">
+        <v>14.4</v>
+      </c>
+      <c r="O181" s="11">
+        <v>12</v>
+      </c>
+      <c r="P181" s="11">
+        <v>13.15</v>
+      </c>
+      <c r="Q181" s="11">
+        <v>51</v>
+      </c>
+      <c r="R181" s="11">
+        <v>15.2</v>
+      </c>
+      <c r="S181" s="11">
+        <v>32.5</v>
+      </c>
+      <c r="T181" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="U181" s="11">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="V181" s="11">
+        <v>6.06</v>
+      </c>
+      <c r="W181" s="11">
+        <v>10.3</v>
+      </c>
+      <c r="X181" s="11">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="Y181" s="11">
+        <v>8.125</v>
+      </c>
+    </row>
+    <row r="182" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A182" s="12">
+        <v>46136</v>
+      </c>
+      <c r="B182" s="12">
+        <v>46136</v>
+      </c>
+      <c r="C182" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D182" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E182" s="11">
+        <v>50.6</v>
+      </c>
+      <c r="F182" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="G182" s="11">
+        <v>38.5</v>
+      </c>
+      <c r="H182" s="11">
+        <v>24.8</v>
+      </c>
+      <c r="I182" s="11">
+        <v>21</v>
+      </c>
+      <c r="J182" s="11">
+        <v>21.9</v>
+      </c>
+      <c r="K182" s="11">
+        <v>80</v>
+      </c>
+      <c r="L182" s="11">
+        <v>30</v>
+      </c>
+      <c r="M182" s="11">
+        <v>63.908999999999999</v>
+      </c>
+      <c r="N182" s="11">
+        <v>14.4</v>
+      </c>
+      <c r="O182" s="11">
+        <v>12</v>
+      </c>
+      <c r="P182" s="11">
+        <v>13.15</v>
+      </c>
+      <c r="Q182" s="11">
+        <v>51</v>
+      </c>
+      <c r="R182" s="11">
+        <v>15.2</v>
+      </c>
+      <c r="S182" s="11">
+        <v>32.5</v>
+      </c>
+      <c r="T182" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="U182" s="11">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="V182" s="11">
+        <v>6.06</v>
+      </c>
+      <c r="W182" s="11">
+        <v>10.3</v>
+      </c>
+      <c r="X182" s="11">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="Y182" s="11">
+        <v>8.125</v>
+      </c>
+    </row>
+    <row r="183" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A183" s="12">
+        <v>46136</v>
+      </c>
+      <c r="B183" s="12">
+        <v>46136</v>
+      </c>
+      <c r="C183" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D183" s="7" t="s">
         <v>53</v>
       </c>
     </row>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6AAA28A-0FD7-43DD-BC80-2D7F07CD9451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01B605CA-2978-4D4A-A4AF-6A4AF9248C7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -253,23 +253,23 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -282,7 +282,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -325,7 +325,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -346,27 +346,27 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -374,8 +374,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -393,7 +393,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1609,6 +1609,9 @@
                 <c:pt idx="191">
                   <c:v>39</c:v>
                 </c:pt>
+                <c:pt idx="192">
+                  <c:v>39</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2818,6 +2821,9 @@
                 <c:pt idx="191">
                   <c:v>22</c:v>
                 </c:pt>
+                <c:pt idx="192">
+                  <c:v>22</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4027,6 +4033,9 @@
                 <c:pt idx="191">
                   <c:v>61.152000000000001</c:v>
                 </c:pt>
+                <c:pt idx="192">
+                  <c:v>61.152000000000001</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -5236,6 +5245,9 @@
                 <c:pt idx="191">
                   <c:v>13.074999999999999</c:v>
                 </c:pt>
+                <c:pt idx="192">
+                  <c:v>13.074999999999999</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -6443,6 +6455,9 @@
                   <c:v>32.479999999999997</c:v>
                 </c:pt>
                 <c:pt idx="191">
+                  <c:v>32.479999999999997</c:v>
+                </c:pt>
+                <c:pt idx="192">
                   <c:v>32.479999999999997</c:v>
                 </c:pt>
               </c:numCache>
@@ -7670,6 +7685,9 @@
                 <c:pt idx="191">
                   <c:v>5.82</c:v>
                 </c:pt>
+                <c:pt idx="192">
+                  <c:v>5.82</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -8879,6 +8897,9 @@
                   <c:v>8.375</c:v>
                 </c:pt>
                 <c:pt idx="191">
+                  <c:v>8.375</c:v>
+                </c:pt>
+                <c:pt idx="192">
                   <c:v>8.375</c:v>
                 </c:pt>
               </c:numCache>
@@ -9157,7 +9178,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -9853,7 +9874,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -12391,17 +12412,17 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:Y195"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.09765625" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.09765625" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.296875" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.26953125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="5" customFormat="1">
       <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
@@ -12478,7 +12499,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -12547,7 +12568,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="12">
         <v>46044</v>
       </c>
@@ -12624,7 +12645,7 @@
         <v>4.9450000000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="12">
         <v>46045</v>
       </c>
@@ -12701,7 +12722,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="12">
         <v>46045</v>
       </c>
@@ -12778,7 +12799,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="12">
         <v>46045</v>
       </c>
@@ -12855,7 +12876,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="12">
         <v>46048</v>
       </c>
@@ -12932,7 +12953,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25">
       <c r="A8" s="12">
         <v>46048</v>
       </c>
@@ -13009,7 +13030,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25">
       <c r="A9" s="12">
         <v>46048</v>
       </c>
@@ -13086,7 +13107,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25">
       <c r="A10" s="12">
         <v>46049</v>
       </c>
@@ -13163,7 +13184,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25">
       <c r="A11" s="12">
         <v>46049</v>
       </c>
@@ -13240,7 +13261,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25">
       <c r="A12" s="12">
         <v>46049</v>
       </c>
@@ -13317,7 +13338,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25">
       <c r="A13" s="12">
         <v>46050</v>
       </c>
@@ -13394,7 +13415,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25">
       <c r="A14" s="12">
         <v>46050</v>
       </c>
@@ -13471,7 +13492,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25">
       <c r="A15" s="12">
         <v>46050</v>
       </c>
@@ -13548,7 +13569,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25">
       <c r="A16" s="12">
         <v>46051</v>
       </c>
@@ -13625,7 +13646,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:25">
       <c r="A17" s="12">
         <v>46051</v>
       </c>
@@ -13702,7 +13723,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:25">
       <c r="A18" s="12">
         <v>46051</v>
       </c>
@@ -13779,7 +13800,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:25">
       <c r="A19" s="12">
         <v>46052</v>
       </c>
@@ -13856,7 +13877,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:25">
       <c r="A20" s="12">
         <v>46052</v>
       </c>
@@ -13933,7 +13954,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:25">
       <c r="A21" s="12">
         <v>46052</v>
       </c>
@@ -14010,7 +14031,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:25">
       <c r="A22" s="12">
         <v>46055</v>
       </c>
@@ -14087,7 +14108,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:25">
       <c r="A23" s="12">
         <v>46055</v>
       </c>
@@ -14164,7 +14185,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:25">
       <c r="A24" s="12">
         <v>46055</v>
       </c>
@@ -14241,7 +14262,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:25">
       <c r="A25" s="12">
         <v>46056</v>
       </c>
@@ -14318,7 +14339,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:25">
       <c r="A26" s="12">
         <v>46056</v>
       </c>
@@ -14395,7 +14416,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:25">
       <c r="A27" s="12">
         <v>46056</v>
       </c>
@@ -14472,7 +14493,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:25">
       <c r="A28" s="12">
         <v>46057</v>
       </c>
@@ -14549,7 +14570,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:25">
       <c r="A29" s="12">
         <v>46057</v>
       </c>
@@ -14626,7 +14647,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:25">
       <c r="A30" s="12">
         <v>46057</v>
       </c>
@@ -14703,7 +14724,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:25">
       <c r="A31" s="12">
         <v>46058</v>
       </c>
@@ -14780,7 +14801,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:25">
       <c r="A32" s="12">
         <v>46058</v>
       </c>
@@ -14857,7 +14878,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:25">
       <c r="A33" s="12">
         <v>46058</v>
       </c>
@@ -14934,7 +14955,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:25">
       <c r="A34" s="12">
         <v>46059</v>
       </c>
@@ -15011,7 +15032,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:25">
       <c r="A35" s="12">
         <v>46059</v>
       </c>
@@ -15088,7 +15109,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:25">
       <c r="A36" s="12">
         <v>46059</v>
       </c>
@@ -15165,7 +15186,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:25">
       <c r="A37" s="12">
         <v>46062</v>
       </c>
@@ -15242,7 +15263,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:25">
       <c r="A38" s="12">
         <v>46062</v>
       </c>
@@ -15319,7 +15340,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:25">
       <c r="A39" s="12">
         <v>46062</v>
       </c>
@@ -15396,7 +15417,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:25">
       <c r="A40" s="12">
         <v>46063</v>
       </c>
@@ -15473,7 +15494,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:25">
       <c r="A41" s="12">
         <v>46063</v>
       </c>
@@ -15550,7 +15571,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:25">
       <c r="A42" s="12">
         <v>46063</v>
       </c>
@@ -15627,7 +15648,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:25">
       <c r="A43" s="12">
         <v>46064</v>
       </c>
@@ -15704,7 +15725,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:25">
       <c r="A44" s="12">
         <v>46064</v>
       </c>
@@ -15781,7 +15802,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:25">
       <c r="A45" s="12">
         <v>46064</v>
       </c>
@@ -15858,7 +15879,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:25">
       <c r="A46" s="12">
         <v>46065</v>
       </c>
@@ -15935,7 +15956,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:25">
       <c r="A47" s="12">
         <v>46065</v>
       </c>
@@ -16012,7 +16033,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:25">
       <c r="A48" s="12">
         <v>46065</v>
       </c>
@@ -16089,7 +16110,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:25">
       <c r="A49" s="12">
         <v>46066</v>
       </c>
@@ -16166,7 +16187,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:25">
       <c r="A50" s="12">
         <v>46066</v>
       </c>
@@ -16243,7 +16264,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:25">
       <c r="A51" s="12">
         <v>46066</v>
       </c>
@@ -16320,7 +16341,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:25">
       <c r="A52" s="12">
         <v>46076</v>
       </c>
@@ -16397,7 +16418,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:25">
       <c r="A53" s="12">
         <v>46076</v>
       </c>
@@ -16474,7 +16495,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:25">
       <c r="A54" s="12">
         <v>46076</v>
       </c>
@@ -16551,7 +16572,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:25">
       <c r="A55" s="12">
         <v>46077</v>
       </c>
@@ -16628,7 +16649,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:25">
       <c r="A56" s="12">
         <v>46077</v>
       </c>
@@ -16705,7 +16726,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:25">
       <c r="A57" s="12">
         <v>46077</v>
       </c>
@@ -16782,7 +16803,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:25">
       <c r="A58" s="12">
         <v>46078</v>
       </c>
@@ -16859,7 +16880,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:25">
       <c r="A59" s="12">
         <v>46078</v>
       </c>
@@ -16936,7 +16957,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:25">
       <c r="A60" s="12">
         <v>46078</v>
       </c>
@@ -17013,7 +17034,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="61" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:25">
       <c r="A61" s="12">
         <v>46079</v>
       </c>
@@ -17090,7 +17111,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="62" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:25">
       <c r="A62" s="12">
         <v>46079</v>
       </c>
@@ -17167,7 +17188,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="63" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:25">
       <c r="A63" s="12">
         <v>46079</v>
       </c>
@@ -17244,7 +17265,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="64" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:25">
       <c r="A64" s="12">
         <v>46080</v>
       </c>
@@ -17321,7 +17342,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="65" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:25">
       <c r="A65" s="12">
         <v>46080</v>
       </c>
@@ -17398,7 +17419,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="66" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:25">
       <c r="A66" s="12">
         <v>46080</v>
       </c>
@@ -17475,7 +17496,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="67" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:25">
       <c r="A67" s="12">
         <v>46083</v>
       </c>
@@ -17552,7 +17573,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="68" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:25">
       <c r="A68" s="12">
         <v>46083</v>
       </c>
@@ -17629,7 +17650,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="69" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:25">
       <c r="A69" s="12">
         <v>46083</v>
       </c>
@@ -17706,7 +17727,7 @@
         <v>5.68</v>
       </c>
     </row>
-    <row r="70" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:25">
       <c r="A70" s="12">
         <v>46084</v>
       </c>
@@ -17783,7 +17804,7 @@
         <v>5.7590000000000003</v>
       </c>
     </row>
-    <row r="71" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:25">
       <c r="A71" s="12">
         <v>46084</v>
       </c>
@@ -17860,7 +17881,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="72" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:25">
       <c r="A72" s="12">
         <v>46084</v>
       </c>
@@ -17937,7 +17958,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="73" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:25">
       <c r="A73" s="12">
         <v>46085</v>
       </c>
@@ -18014,7 +18035,7 @@
         <v>5.8390000000000004</v>
       </c>
     </row>
-    <row r="74" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:25">
       <c r="A74" s="12">
         <v>46085</v>
       </c>
@@ -18091,7 +18112,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:25">
       <c r="A75" s="12">
         <v>46085</v>
       </c>
@@ -18168,7 +18189,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:25">
       <c r="A76" s="12">
         <v>46086</v>
       </c>
@@ -18245,7 +18266,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="77" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:25">
       <c r="A77" s="12">
         <v>46086</v>
       </c>
@@ -18322,7 +18343,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="78" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:25">
       <c r="A78" s="12">
         <v>46086</v>
       </c>
@@ -18399,7 +18420,7 @@
         <v>5.9210000000000003</v>
       </c>
     </row>
-    <row r="79" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:25">
       <c r="A79" s="12">
         <v>46087</v>
       </c>
@@ -18476,7 +18497,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="80" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:25">
       <c r="A80" s="12">
         <v>46087</v>
       </c>
@@ -18553,7 +18574,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="81" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:25">
       <c r="A81" s="12">
         <v>46087</v>
       </c>
@@ -18630,7 +18651,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="82" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:25">
       <c r="A82" s="12">
         <v>46090</v>
       </c>
@@ -18707,7 +18728,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="83" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:25">
       <c r="A83" s="12">
         <v>46090</v>
       </c>
@@ -18784,7 +18805,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="84" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:25">
       <c r="A84" s="12">
         <v>46090</v>
       </c>
@@ -18861,7 +18882,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="85" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:25">
       <c r="A85" s="12">
         <v>46091</v>
       </c>
@@ -18938,7 +18959,7 @@
         <v>6.157</v>
       </c>
     </row>
-    <row r="86" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:25">
       <c r="A86" s="12">
         <v>46091</v>
       </c>
@@ -19015,7 +19036,7 @@
         <v>6.181</v>
       </c>
     </row>
-    <row r="87" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:25">
       <c r="A87" s="12">
         <v>46091</v>
       </c>
@@ -19092,7 +19113,7 @@
         <v>6.181</v>
       </c>
     </row>
-    <row r="88" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:25">
       <c r="A88" s="12">
         <v>46092</v>
       </c>
@@ -19169,7 +19190,7 @@
         <v>6.2430000000000003</v>
       </c>
     </row>
-    <row r="89" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:25">
       <c r="A89" s="12">
         <v>46092</v>
       </c>
@@ -19246,7 +19267,7 @@
         <v>6.29</v>
       </c>
     </row>
-    <row r="90" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:25">
       <c r="A90" s="12">
         <v>46092</v>
       </c>
@@ -19323,7 +19344,7 @@
         <v>6.3049999999999997</v>
       </c>
     </row>
-    <row r="91" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:25">
       <c r="A91" s="12">
         <v>46093</v>
       </c>
@@ -19400,7 +19421,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="92" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:25">
       <c r="A92" s="12">
         <v>46093</v>
       </c>
@@ -19477,7 +19498,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="93" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:25">
       <c r="A93" s="12">
         <v>46093</v>
       </c>
@@ -19554,7 +19575,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="94" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:25">
       <c r="A94" s="12">
         <v>46094</v>
       </c>
@@ -19631,7 +19652,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="95" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:25">
       <c r="A95" s="12">
         <v>46094</v>
       </c>
@@ -19708,7 +19729,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="96" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:25">
       <c r="A96" s="12">
         <v>46094</v>
       </c>
@@ -19785,7 +19806,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="97" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:25">
       <c r="A97" s="12">
         <v>46097</v>
       </c>
@@ -19862,7 +19883,7 @@
         <v>6.5330000000000004</v>
       </c>
     </row>
-    <row r="98" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:25">
       <c r="A98" s="12">
         <v>46097</v>
       </c>
@@ -19939,7 +19960,7 @@
         <v>6.5119999999999996</v>
       </c>
     </row>
-    <row r="99" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:25">
       <c r="A99" s="12">
         <v>46097</v>
       </c>
@@ -20016,7 +20037,7 @@
         <v>6.5119999999999996</v>
       </c>
     </row>
-    <row r="100" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:25">
       <c r="A100" s="12">
         <v>46098</v>
       </c>
@@ -20093,7 +20114,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="101" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:25">
       <c r="A101" s="12">
         <v>46098</v>
       </c>
@@ -20170,7 +20191,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="102" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:25">
       <c r="A102" s="12">
         <v>46098</v>
       </c>
@@ -20247,7 +20268,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="103" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:25">
       <c r="A103" s="12">
         <v>46099</v>
       </c>
@@ -20324,7 +20345,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="104" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:25">
       <c r="A104" s="12">
         <v>46099</v>
       </c>
@@ -20401,7 +20422,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="105" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:25">
       <c r="A105" s="12">
         <v>46099</v>
       </c>
@@ -20478,7 +20499,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="106" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:25">
       <c r="A106" s="12">
         <v>46100</v>
       </c>
@@ -20555,7 +20576,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="107" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:25">
       <c r="A107" s="12">
         <v>46100</v>
       </c>
@@ -20632,7 +20653,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="108" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:25">
       <c r="A108" s="12">
         <v>46100</v>
       </c>
@@ -20709,7 +20730,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="109" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:25">
       <c r="A109" s="12">
         <v>46101</v>
       </c>
@@ -20786,7 +20807,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="110" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:25">
       <c r="A110" s="12">
         <v>46101</v>
       </c>
@@ -20863,7 +20884,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="111" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:25">
       <c r="A111" s="12">
         <v>46101</v>
       </c>
@@ -20940,7 +20961,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="112" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:25">
       <c r="A112" s="12">
         <v>46104</v>
       </c>
@@ -21017,7 +21038,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="113" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:25">
       <c r="A113" s="12">
         <v>46104</v>
       </c>
@@ -21094,7 +21115,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="114" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:25">
       <c r="A114" s="12">
         <v>46104</v>
       </c>
@@ -21171,7 +21192,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="115" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:25">
       <c r="A115" s="12">
         <v>46105</v>
       </c>
@@ -21248,7 +21269,7 @@
         <v>7.0250000000000004</v>
       </c>
     </row>
-    <row r="116" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:25">
       <c r="A116" s="12">
         <v>46105</v>
       </c>
@@ -21325,7 +21346,7 @@
         <v>7.125</v>
       </c>
     </row>
-    <row r="117" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:25">
       <c r="A117" s="12">
         <v>46105</v>
       </c>
@@ -21402,7 +21423,7 @@
         <v>7.125</v>
       </c>
     </row>
-    <row r="118" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:25">
       <c r="A118" s="12">
         <v>46106</v>
       </c>
@@ -21479,7 +21500,7 @@
         <v>7.15</v>
       </c>
     </row>
-    <row r="119" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:25">
       <c r="A119" s="12">
         <v>46106</v>
       </c>
@@ -21556,7 +21577,7 @@
         <v>7.2249999999999996</v>
       </c>
     </row>
-    <row r="120" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:25">
       <c r="A120" s="12">
         <v>46106</v>
       </c>
@@ -21633,7 +21654,7 @@
         <v>7.2249999999999996</v>
       </c>
     </row>
-    <row r="121" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:25">
       <c r="A121" s="12">
         <v>46107</v>
       </c>
@@ -21710,7 +21731,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="122" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:25">
       <c r="A122" s="12">
         <v>46107</v>
       </c>
@@ -21787,7 +21808,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="123" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:25">
       <c r="A123" s="12">
         <v>46107</v>
       </c>
@@ -21864,7 +21885,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="124" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:25">
       <c r="A124" s="12">
         <v>46108</v>
       </c>
@@ -21941,7 +21962,7 @@
         <v>7.375</v>
       </c>
     </row>
-    <row r="125" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:25">
       <c r="A125" s="12">
         <v>46108</v>
       </c>
@@ -22018,7 +22039,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="126" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:25">
       <c r="A126" s="12">
         <v>46108</v>
       </c>
@@ -22095,7 +22116,7 @@
         <v>7.375</v>
       </c>
     </row>
-    <row r="127" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:25">
       <c r="A127" s="12">
         <v>46111</v>
       </c>
@@ -22172,7 +22193,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="128" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:25">
       <c r="A128" s="12">
         <v>46111</v>
       </c>
@@ -22249,7 +22270,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="129" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:25">
       <c r="A129" s="12">
         <v>46111</v>
       </c>
@@ -22326,7 +22347,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="130" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:25">
       <c r="A130" s="12">
         <v>46112</v>
       </c>
@@ -22403,7 +22424,7 @@
         <v>7.5250000000000004</v>
       </c>
     </row>
-    <row r="131" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:25">
       <c r="A131" s="12">
         <v>46112</v>
       </c>
@@ -22480,7 +22501,7 @@
         <v>7.5250000000000004</v>
       </c>
     </row>
-    <row r="132" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:25">
       <c r="A132" s="12">
         <v>46112</v>
       </c>
@@ -22557,7 +22578,7 @@
         <v>7.55</v>
       </c>
     </row>
-    <row r="133" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:25">
       <c r="A133" s="12">
         <v>46113</v>
       </c>
@@ -22634,7 +22655,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="134" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:25">
       <c r="A134" s="12">
         <v>46113</v>
       </c>
@@ -22711,7 +22732,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="135" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:25">
       <c r="A135" s="12">
         <v>46113</v>
       </c>
@@ -22788,7 +22809,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="136" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:25">
       <c r="A136" s="12">
         <v>46114</v>
       </c>
@@ -22865,7 +22886,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="137" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:25">
       <c r="A137" s="12">
         <v>46114</v>
       </c>
@@ -22942,7 +22963,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="138" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:25">
       <c r="A138" s="12">
         <v>46114</v>
       </c>
@@ -23019,7 +23040,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="139" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:25">
       <c r="A139" s="12">
         <v>46115</v>
       </c>
@@ -23096,7 +23117,7 @@
         <v>7.6749999999999998</v>
       </c>
     </row>
-    <row r="140" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:25">
       <c r="A140" s="12">
         <v>46115</v>
       </c>
@@ -23173,7 +23194,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="141" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:25">
       <c r="A141" s="12">
         <v>46115</v>
       </c>
@@ -23250,7 +23271,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="142" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:25">
       <c r="A142" s="12">
         <v>46119</v>
       </c>
@@ -23327,7 +23348,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="143" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:25">
       <c r="A143" s="12">
         <v>46119</v>
       </c>
@@ -23404,7 +23425,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="144" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:25">
       <c r="A144" s="12">
         <v>46119</v>
       </c>
@@ -23481,7 +23502,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="145" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:25">
       <c r="A145" s="12">
         <v>46120</v>
       </c>
@@ -23558,7 +23579,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="146" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:25">
       <c r="A146" s="12">
         <v>46120</v>
       </c>
@@ -23635,7 +23656,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="147" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:25">
       <c r="A147" s="12">
         <v>46120</v>
       </c>
@@ -23712,7 +23733,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="148" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:25">
       <c r="A148" s="12">
         <v>46121</v>
       </c>
@@ -23789,7 +23810,7 @@
         <v>7.7249999999999996</v>
       </c>
     </row>
-    <row r="149" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:25">
       <c r="A149" s="12">
         <v>46121</v>
       </c>
@@ -23866,7 +23887,7 @@
         <v>7.7249999999999996</v>
       </c>
     </row>
-    <row r="150" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:25">
       <c r="A150" s="12">
         <v>46121</v>
       </c>
@@ -23943,7 +23964,7 @@
         <v>7.7249999999999996</v>
       </c>
     </row>
-    <row r="151" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:25">
       <c r="A151" s="12">
         <v>46122</v>
       </c>
@@ -24020,7 +24041,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="152" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:25">
       <c r="A152" s="12">
         <v>46122</v>
       </c>
@@ -24097,7 +24118,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="153" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:25">
       <c r="A153" s="12">
         <v>46122</v>
       </c>
@@ -24174,7 +24195,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="154" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:25">
       <c r="A154" s="12">
         <v>46125</v>
       </c>
@@ -24251,7 +24272,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="155" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:25">
       <c r="A155" s="12">
         <v>46125</v>
       </c>
@@ -24328,7 +24349,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="156" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:25">
       <c r="A156" s="12">
         <v>46125</v>
       </c>
@@ -24405,7 +24426,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="157" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:25">
       <c r="A157" s="12">
         <v>46126</v>
       </c>
@@ -24482,7 +24503,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="158" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:25">
       <c r="A158" s="12">
         <v>46126</v>
       </c>
@@ -24559,7 +24580,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="159" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:25">
       <c r="A159" s="12">
         <v>46126</v>
       </c>
@@ -24636,7 +24657,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="160" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:25">
       <c r="A160" s="12">
         <v>46127</v>
       </c>
@@ -24713,7 +24734,7 @@
         <v>7.85</v>
       </c>
     </row>
-    <row r="161" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:25">
       <c r="A161" s="12">
         <v>46127</v>
       </c>
@@ -24790,7 +24811,7 @@
         <v>7.85</v>
       </c>
     </row>
-    <row r="162" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:25">
       <c r="A162" s="12">
         <v>46127</v>
       </c>
@@ -24867,7 +24888,7 @@
         <v>7.8630000000000004</v>
       </c>
     </row>
-    <row r="163" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:25">
       <c r="A163" s="12">
         <v>46128</v>
       </c>
@@ -24944,7 +24965,7 @@
         <v>7.8630000000000004</v>
       </c>
     </row>
-    <row r="164" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:25">
       <c r="A164" s="12">
         <v>46128</v>
       </c>
@@ -25021,7 +25042,7 @@
         <v>7.9749999999999996</v>
       </c>
     </row>
-    <row r="165" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:25">
       <c r="A165" s="12">
         <v>46128</v>
       </c>
@@ -25098,7 +25119,7 @@
         <v>7.9749999999999996</v>
       </c>
     </row>
-    <row r="166" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:25">
       <c r="A166" s="12">
         <v>46129</v>
       </c>
@@ -25175,7 +25196,7 @@
         <v>8.0250000000000004</v>
       </c>
     </row>
-    <row r="167" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:25">
       <c r="A167" s="12">
         <v>46129</v>
       </c>
@@ -25252,7 +25273,7 @@
         <v>8.0250000000000004</v>
       </c>
     </row>
-    <row r="168" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:25">
       <c r="A168" s="12">
         <v>46129</v>
       </c>
@@ -25329,7 +25350,7 @@
         <v>8.0250000000000004</v>
       </c>
     </row>
-    <row r="169" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:25">
       <c r="A169" s="12">
         <v>46132</v>
       </c>
@@ -25406,7 +25427,7 @@
         <v>8.0749999999999993</v>
       </c>
     </row>
-    <row r="170" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:25">
       <c r="A170" s="12">
         <v>46132</v>
       </c>
@@ -25483,7 +25504,7 @@
         <v>8.0749999999999993</v>
       </c>
     </row>
-    <row r="171" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:25">
       <c r="A171" s="12">
         <v>46132</v>
       </c>
@@ -25560,7 +25581,7 @@
         <v>8.0749999999999993</v>
       </c>
     </row>
-    <row r="172" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:25">
       <c r="A172" s="12">
         <v>46133</v>
       </c>
@@ -25637,7 +25658,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="173" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:25">
       <c r="A173" s="12">
         <v>46133</v>
       </c>
@@ -25714,7 +25735,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="174" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:25">
       <c r="A174" s="12">
         <v>46133</v>
       </c>
@@ -25791,7 +25812,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="175" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:25">
       <c r="A175" s="12">
         <v>46134</v>
       </c>
@@ -25868,7 +25889,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="176" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:25">
       <c r="A176" s="12">
         <v>46134</v>
       </c>
@@ -25945,7 +25966,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="177" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:25">
       <c r="A177" s="12">
         <v>46134</v>
       </c>
@@ -26022,7 +26043,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="178" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:25">
       <c r="A178" s="12">
         <v>46135</v>
       </c>
@@ -26099,7 +26120,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="179" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:25">
       <c r="A179" s="12">
         <v>46135</v>
       </c>
@@ -26176,7 +26197,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="180" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:25">
       <c r="A180" s="12">
         <v>46135</v>
       </c>
@@ -26253,7 +26274,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="181" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:25">
       <c r="A181" s="12">
         <v>46136</v>
       </c>
@@ -26330,7 +26351,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="182" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:25">
       <c r="A182" s="12">
         <v>46136</v>
       </c>
@@ -26407,7 +26428,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="183" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:25">
       <c r="A183" s="12">
         <v>46136</v>
       </c>
@@ -26484,7 +26505,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="184" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:25">
       <c r="A184" s="12">
         <v>46139</v>
       </c>
@@ -26561,7 +26582,7 @@
         <v>8.1750000000000007</v>
       </c>
     </row>
-    <row r="185" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:25">
       <c r="A185" s="12">
         <v>46139</v>
       </c>
@@ -26638,7 +26659,7 @@
         <v>8.1750000000000007</v>
       </c>
     </row>
-    <row r="186" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:25">
       <c r="A186" s="12">
         <v>46139</v>
       </c>
@@ -26715,7 +26736,7 @@
         <v>8.1750000000000007</v>
       </c>
     </row>
-    <row r="187" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:25">
       <c r="A187" s="12">
         <v>46140</v>
       </c>
@@ -26792,7 +26813,7 @@
         <v>8.2249999999999996</v>
       </c>
     </row>
-    <row r="188" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:25">
       <c r="A188" s="12">
         <v>46140</v>
       </c>
@@ -26869,7 +26890,7 @@
         <v>8.2249999999999996</v>
       </c>
     </row>
-    <row r="189" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:25">
       <c r="A189" s="12">
         <v>46140</v>
       </c>
@@ -26946,7 +26967,7 @@
         <v>8.25</v>
       </c>
     </row>
-    <row r="190" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:25">
       <c r="A190" s="12">
         <v>46141</v>
       </c>
@@ -27023,7 +27044,7 @@
         <v>8.3000000000000007</v>
       </c>
     </row>
-    <row r="191" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:25">
       <c r="A191" s="12">
         <v>46141</v>
       </c>
@@ -27100,7 +27121,7 @@
         <v>8.3000000000000007</v>
       </c>
     </row>
-    <row r="192" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:25">
       <c r="A192" s="12">
         <v>46141</v>
       </c>
@@ -27177,7 +27198,7 @@
         <v>8.3000000000000007</v>
       </c>
     </row>
-    <row r="193" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:25">
       <c r="A193" s="12">
         <v>46142</v>
       </c>
@@ -27254,7 +27275,7 @@
         <v>8.375</v>
       </c>
     </row>
-    <row r="194" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:25">
       <c r="A194" s="12">
         <v>46142</v>
       </c>
@@ -27331,7 +27352,7 @@
         <v>8.375</v>
       </c>
     </row>
-    <row r="195" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:25">
       <c r="A195" s="12">
         <v>46142</v>
       </c>
@@ -27343,6 +27364,69 @@
       </c>
       <c r="D195" s="7" t="s">
         <v>53</v>
+      </c>
+      <c r="E195" s="11">
+        <v>51</v>
+      </c>
+      <c r="F195" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="G195" s="11">
+        <v>39</v>
+      </c>
+      <c r="H195" s="11">
+        <v>24.8</v>
+      </c>
+      <c r="I195" s="11">
+        <v>21</v>
+      </c>
+      <c r="J195" s="11">
+        <v>22</v>
+      </c>
+      <c r="K195" s="11">
+        <v>75</v>
+      </c>
+      <c r="L195" s="11">
+        <v>30.5</v>
+      </c>
+      <c r="M195" s="11">
+        <v>61.152000000000001</v>
+      </c>
+      <c r="N195" s="11">
+        <v>14.3</v>
+      </c>
+      <c r="O195" s="11">
+        <v>11.8</v>
+      </c>
+      <c r="P195" s="11">
+        <v>13.074999999999999</v>
+      </c>
+      <c r="Q195" s="11">
+        <v>51</v>
+      </c>
+      <c r="R195" s="11">
+        <v>15.3</v>
+      </c>
+      <c r="S195" s="11">
+        <v>32.479999999999997</v>
+      </c>
+      <c r="T195" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="U195" s="11">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="V195" s="11">
+        <v>5.82</v>
+      </c>
+      <c r="W195" s="11">
+        <v>10.5</v>
+      </c>
+      <c r="X195" s="11">
+        <v>5.15</v>
+      </c>
+      <c r="Y195" s="11">
+        <v>8.375</v>
       </c>
     </row>
   </sheetData>
@@ -27362,19 +27446,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:AK6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.3984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.09765625" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.296875" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.36328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.26953125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="9" style="11"/>
-    <col min="8" max="10" width="9.09765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:37" s="5" customFormat="1">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -27463,7 +27547,7 @@
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:37">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -27544,7 +27628,7 @@
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:37">
       <c r="A3" s="6">
         <v>45962</v>
       </c>
@@ -27633,7 +27717,7 @@
       <c r="AJ3" s="2"/>
       <c r="AK3" s="2"/>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:37">
       <c r="A4" s="6">
         <v>45992</v>
       </c>
@@ -27722,7 +27806,7 @@
       <c r="AJ4" s="2"/>
       <c r="AK4" s="2"/>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37">
       <c r="A5" s="6">
         <v>46023</v>
       </c>
@@ -27754,7 +27838,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37">
       <c r="A6" s="6">
         <v>46054</v>
       </c>
@@ -27847,24 +27931,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:Y15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.09765625" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.09765625" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="14"/>
-    <col min="7" max="7" width="9.09765625" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.453125" style="14" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="14"/>
-    <col min="10" max="10" width="9.09765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="9" style="14"/>
-    <col min="13" max="13" width="13.296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.26953125" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="5" customFormat="1">
       <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
@@ -27917,7 +28001,7 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -27962,7 +28046,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -28015,7 +28099,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -28068,7 +28152,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -28109,7 +28193,7 @@
         <v>118.333</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -28150,7 +28234,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -28191,7 +28275,7 @@
         <v>122.667</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25">
       <c r="A8" s="12">
         <v>46083</v>
       </c>
@@ -28232,7 +28316,7 @@
         <v>123.333</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25">
       <c r="A9" s="12">
         <v>46090</v>
       </c>
@@ -28273,7 +28357,7 @@
         <v>126.667</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25">
       <c r="A10" s="12">
         <v>46097</v>
       </c>
@@ -28314,7 +28398,7 @@
         <v>132.333</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25">
       <c r="A11" s="12">
         <v>46104</v>
       </c>
@@ -28355,7 +28439,7 @@
         <v>143.333</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25">
       <c r="A12" s="12">
         <v>46111</v>
       </c>
@@ -28396,7 +28480,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25">
       <c r="A13" s="12">
         <v>46118</v>
       </c>
@@ -28437,7 +28521,7 @@
         <v>149.333</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25">
       <c r="A14" s="12">
         <v>46125</v>
       </c>
@@ -28478,7 +28562,7 @@
         <v>149.209</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25">
       <c r="A15" s="12">
         <v>46132</v>
       </c>
@@ -28536,18 +28620,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:Y15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.09765625" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.09765625" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.59765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.6328125" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="5" customFormat="1">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -28594,7 +28678,7 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -28633,7 +28717,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -28680,7 +28764,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -28727,7 +28811,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -28759,7 +28843,7 @@
         <v>9.6539999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -28791,7 +28875,7 @@
         <v>9.8650000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -28823,7 +28907,7 @@
         <v>10.221</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25">
       <c r="A8" s="12">
         <v>46083</v>
       </c>
@@ -28855,7 +28939,7 @@
         <v>10.721</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25">
       <c r="A9" s="12">
         <v>46090</v>
       </c>
@@ -28887,7 +28971,7 @@
         <v>11.462</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25">
       <c r="A10" s="12">
         <v>46097</v>
       </c>
@@ -28919,7 +29003,7 @@
         <v>11.962</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25">
       <c r="A11" s="12">
         <v>46104</v>
       </c>
@@ -28951,7 +29035,7 @@
         <v>12.865</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25">
       <c r="A12" s="12">
         <v>46111</v>
       </c>
@@ -28983,7 +29067,7 @@
         <v>12.71</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25">
       <c r="A13" s="12">
         <v>46118</v>
       </c>
@@ -29015,7 +29099,7 @@
         <v>12.412000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25">
       <c r="A14" s="12">
         <v>46125</v>
       </c>
@@ -29047,7 +29131,7 @@
         <v>12.335000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25">
       <c r="A15" s="12">
         <v>46132</v>
       </c>
@@ -29095,7 +29179,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="16384" width="9" style="3"/>
   </cols>
@@ -29110,15 +29194,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="22.8984375" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.8984375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.59765625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.90625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.90625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.6328125" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>48</v>
       </c>
@@ -29129,7 +29213,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
@@ -29143,7 +29227,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="s">
         <v>29</v>
@@ -29152,7 +29236,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>31</v>
@@ -29161,7 +29245,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
         <v>33</v>
@@ -29170,7 +29254,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4">
       <c r="A6" s="1"/>
       <c r="B6" s="2" t="s">
         <v>35</v>
@@ -29179,7 +29263,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
         <v>37</v>
@@ -29188,7 +29272,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
         <v>39</v>
@@ -29197,7 +29281,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
         <v>41</v>
       </c>
@@ -29206,49 +29290,49 @@
       </c>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4">
       <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4">
       <c r="A12" s="1"/>
       <c r="B12" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4">
       <c r="A14" s="1"/>
       <c r="B14" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4">
       <c r="A15" s="1"/>
       <c r="B15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4">
       <c r="A16" s="1" t="s">
         <v>42</v>
       </c>
@@ -29259,7 +29343,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3">
       <c r="A17" s="1"/>
       <c r="B17" s="2" t="s">
         <v>8</v>
@@ -29268,7 +29352,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3">
       <c r="A18" s="1"/>
       <c r="B18" s="2" t="s">
         <v>9</v>
@@ -29277,7 +29361,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3">
       <c r="A19" s="1" t="s">
         <v>44</v>
       </c>
@@ -29288,7 +29372,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3">
       <c r="A20" s="1"/>
       <c r="B20" s="2" t="s">
         <v>11</v>
@@ -29297,7 +29381,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3">
       <c r="A21" s="1" t="s">
         <v>45</v>
       </c>
@@ -29306,42 +29390,42 @@
       </c>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3">
       <c r="A22" s="1"/>
       <c r="B22" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3">
       <c r="A23" s="1"/>
       <c r="B23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3">
       <c r="A24" s="1"/>
       <c r="B24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3">
       <c r="A25" s="1"/>
       <c r="B25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3">
       <c r="A26" s="1"/>
       <c r="B26" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3">
       <c r="A27" s="1" t="s">
         <v>46</v>
       </c>
@@ -29350,35 +29434,35 @@
       </c>
       <c r="C27" s="2"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3">
       <c r="A28" s="1"/>
       <c r="B28" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C28" s="2"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3">
       <c r="A29" s="1"/>
       <c r="B29" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C29" s="2"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3">
       <c r="A30" s="1"/>
       <c r="B30" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C30" s="2"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3">
       <c r="A31" s="1"/>
       <c r="B31" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C31" s="2"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3">
       <c r="A32" s="1"/>
       <c r="B32" s="2" t="s">
         <v>23</v>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77969603-A577-43E2-B0EC-F74D9F2A6F31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A45339E6-B198-4716-8976-715EFD0A2311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -1051,6 +1051,15 @@
                 <c:pt idx="201">
                   <c:v>46148</c:v>
                 </c:pt>
+                <c:pt idx="202">
+                  <c:v>46149</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>46149</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>46149</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1662,6 +1671,15 @@
                 </c:pt>
                 <c:pt idx="200">
                   <c:v>38.832999999999998</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>38.832999999999998</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>39</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2314,6 +2332,15 @@
                 <c:pt idx="201">
                   <c:v>46148</c:v>
                 </c:pt>
+                <c:pt idx="202">
+                  <c:v>46149</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>46149</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>46149</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2925,6 +2952,15 @@
                 </c:pt>
                 <c:pt idx="200">
                   <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>22.1</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>22.1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3577,6 +3613,15 @@
                 <c:pt idx="201">
                   <c:v>46148</c:v>
                 </c:pt>
+                <c:pt idx="202">
+                  <c:v>46149</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>46149</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>46149</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4188,6 +4233,15 @@
                 </c:pt>
                 <c:pt idx="200">
                   <c:v>59.113999999999997</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>59.113999999999997</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>58.795000000000002</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>58.567999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4840,6 +4894,15 @@
                 <c:pt idx="201">
                   <c:v>46148</c:v>
                 </c:pt>
+                <c:pt idx="202">
+                  <c:v>46149</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>46149</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>46149</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5451,6 +5514,15 @@
                 </c:pt>
                 <c:pt idx="200">
                   <c:v>12.875</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>12.875</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>12.75</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>12.75</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6103,6 +6175,15 @@
                 <c:pt idx="201">
                   <c:v>46148</c:v>
                 </c:pt>
+                <c:pt idx="202">
+                  <c:v>46149</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>46149</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>46149</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6713,6 +6794,15 @@
                   <c:v>32</c:v>
                 </c:pt>
                 <c:pt idx="200">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="203">
                   <c:v>32</c:v>
                 </c:pt>
               </c:numCache>
@@ -7382,6 +7472,15 @@
                 <c:pt idx="201">
                   <c:v>46148</c:v>
                 </c:pt>
+                <c:pt idx="202">
+                  <c:v>46149</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>46149</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>46149</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7993,6 +8092,15 @@
                 </c:pt>
                 <c:pt idx="200">
                   <c:v>5.58</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>5.58</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>5.48</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>5.48</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8647,6 +8755,15 @@
                 <c:pt idx="201">
                   <c:v>46148</c:v>
                 </c:pt>
+                <c:pt idx="202">
+                  <c:v>46149</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>46149</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>46149</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9258,6 +9375,15 @@
                 </c:pt>
                 <c:pt idx="200">
                   <c:v>8.5250000000000004</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>8.5250000000000004</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>8.5749999999999993</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>8.625</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12798,7 +12924,7 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y204"/>
+  <dimension ref="A1:Y207"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="12" bestFit="1" customWidth="1"/>
@@ -28443,6 +28569,237 @@
         <v>0.75694444444444453</v>
       </c>
       <c r="D204" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E204" s="11">
+        <v>51</v>
+      </c>
+      <c r="F204" s="11">
+        <v>28</v>
+      </c>
+      <c r="G204" s="11">
+        <v>38.832999999999998</v>
+      </c>
+      <c r="H204" s="11">
+        <v>24.8</v>
+      </c>
+      <c r="I204" s="11">
+        <v>21</v>
+      </c>
+      <c r="J204" s="11">
+        <v>22</v>
+      </c>
+      <c r="K204" s="11">
+        <v>74</v>
+      </c>
+      <c r="L204" s="11">
+        <v>30.8</v>
+      </c>
+      <c r="M204" s="11">
+        <v>59.113999999999997</v>
+      </c>
+      <c r="N204" s="11">
+        <v>14</v>
+      </c>
+      <c r="O204" s="11">
+        <v>11.5</v>
+      </c>
+      <c r="P204" s="11">
+        <v>12.875</v>
+      </c>
+      <c r="Q204" s="11">
+        <v>51.5</v>
+      </c>
+      <c r="R204" s="11">
+        <v>15.4</v>
+      </c>
+      <c r="S204" s="11">
+        <v>32</v>
+      </c>
+      <c r="T204" s="11">
+        <v>6.3</v>
+      </c>
+      <c r="U204" s="11">
+        <v>4.2</v>
+      </c>
+      <c r="V204" s="11">
+        <v>5.58</v>
+      </c>
+      <c r="W204" s="11">
+        <v>10.6</v>
+      </c>
+      <c r="X204" s="11">
+        <v>5.25</v>
+      </c>
+      <c r="Y204" s="11">
+        <v>8.5250000000000004</v>
+      </c>
+    </row>
+    <row r="205" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A205" s="12">
+        <v>46149</v>
+      </c>
+      <c r="B205" s="12">
+        <v>46149</v>
+      </c>
+      <c r="C205" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D205" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E205" s="11">
+        <v>51</v>
+      </c>
+      <c r="F205" s="11">
+        <v>28</v>
+      </c>
+      <c r="G205" s="11">
+        <v>39</v>
+      </c>
+      <c r="H205" s="11">
+        <v>24.8</v>
+      </c>
+      <c r="I205" s="11">
+        <v>21.5</v>
+      </c>
+      <c r="J205" s="11">
+        <v>22.1</v>
+      </c>
+      <c r="K205" s="11">
+        <v>74</v>
+      </c>
+      <c r="L205" s="11">
+        <v>30.8</v>
+      </c>
+      <c r="M205" s="11">
+        <v>58.795000000000002</v>
+      </c>
+      <c r="N205" s="11">
+        <v>14</v>
+      </c>
+      <c r="O205" s="11">
+        <v>11.5</v>
+      </c>
+      <c r="P205" s="11">
+        <v>12.75</v>
+      </c>
+      <c r="Q205" s="11">
+        <v>51.5</v>
+      </c>
+      <c r="R205" s="11">
+        <v>15.4</v>
+      </c>
+      <c r="S205" s="11">
+        <v>32</v>
+      </c>
+      <c r="T205" s="11">
+        <v>6</v>
+      </c>
+      <c r="U205" s="11">
+        <v>4</v>
+      </c>
+      <c r="V205" s="11">
+        <v>5.48</v>
+      </c>
+      <c r="W205" s="11">
+        <v>10.8</v>
+      </c>
+      <c r="X205" s="11">
+        <v>5.25</v>
+      </c>
+      <c r="Y205" s="11">
+        <v>8.5749999999999993</v>
+      </c>
+    </row>
+    <row r="206" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A206" s="12">
+        <v>46149</v>
+      </c>
+      <c r="B206" s="12">
+        <v>46149</v>
+      </c>
+      <c r="C206" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D206" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E206" s="11">
+        <v>51</v>
+      </c>
+      <c r="F206" s="11">
+        <v>28</v>
+      </c>
+      <c r="G206" s="11">
+        <v>39</v>
+      </c>
+      <c r="H206" s="11">
+        <v>24.8</v>
+      </c>
+      <c r="I206" s="11">
+        <v>21.5</v>
+      </c>
+      <c r="J206" s="11">
+        <v>22.1</v>
+      </c>
+      <c r="K206" s="11">
+        <v>72</v>
+      </c>
+      <c r="L206" s="11">
+        <v>31.3</v>
+      </c>
+      <c r="M206" s="11">
+        <v>58.567999999999998</v>
+      </c>
+      <c r="N206" s="11">
+        <v>14</v>
+      </c>
+      <c r="O206" s="11">
+        <v>11.5</v>
+      </c>
+      <c r="P206" s="11">
+        <v>12.75</v>
+      </c>
+      <c r="Q206" s="11">
+        <v>51.5</v>
+      </c>
+      <c r="R206" s="11">
+        <v>15.7</v>
+      </c>
+      <c r="S206" s="11">
+        <v>32</v>
+      </c>
+      <c r="T206" s="11">
+        <v>6</v>
+      </c>
+      <c r="U206" s="11">
+        <v>4</v>
+      </c>
+      <c r="V206" s="11">
+        <v>5.48</v>
+      </c>
+      <c r="W206" s="11">
+        <v>10.8</v>
+      </c>
+      <c r="X206" s="11">
+        <v>5.25</v>
+      </c>
+      <c r="Y206" s="11">
+        <v>8.625</v>
+      </c>
+    </row>
+    <row r="207" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A207" s="12">
+        <v>46149</v>
+      </c>
+      <c r="B207" s="12">
+        <v>46149</v>
+      </c>
+      <c r="C207" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D207" s="7" t="s">
         <v>53</v>
       </c>
     </row>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A07F41B-EFC5-4C6F-AECA-32CA3DFD99C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{765BE480-E5FF-4132-8637-56D87F51EE74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -1069,6 +1069,15 @@
                 <c:pt idx="207">
                   <c:v>46150</c:v>
                 </c:pt>
+                <c:pt idx="208">
+                  <c:v>46153</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>46153</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>46153</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1698,6 +1707,15 @@
                 </c:pt>
                 <c:pt idx="206">
                   <c:v>39.332999999999998</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>39.832999999999998</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>40.167000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2368,6 +2386,15 @@
                 <c:pt idx="207">
                   <c:v>46150</c:v>
                 </c:pt>
+                <c:pt idx="208">
+                  <c:v>46153</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>46153</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>46153</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2996,6 +3023,15 @@
                   <c:v>22.1</c:v>
                 </c:pt>
                 <c:pt idx="206">
+                  <c:v>22.1</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>22.1</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>22.1</c:v>
+                </c:pt>
+                <c:pt idx="209">
                   <c:v>22.1</c:v>
                 </c:pt>
               </c:numCache>
@@ -3667,6 +3703,15 @@
                 <c:pt idx="207">
                   <c:v>46150</c:v>
                 </c:pt>
+                <c:pt idx="208">
+                  <c:v>46153</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>46153</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>46153</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4296,6 +4341,15 @@
                 </c:pt>
                 <c:pt idx="206">
                   <c:v>58.454999999999998</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>58.454999999999998</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>58.475999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4966,6 +5020,15 @@
                 <c:pt idx="207">
                   <c:v>46150</c:v>
                 </c:pt>
+                <c:pt idx="208">
+                  <c:v>46153</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>46153</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>46153</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5595,6 +5658,15 @@
                 </c:pt>
                 <c:pt idx="206">
                   <c:v>12.6</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>12.6</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>12.525</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>12.525</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6265,6 +6337,15 @@
                 <c:pt idx="207">
                   <c:v>46150</c:v>
                 </c:pt>
+                <c:pt idx="208">
+                  <c:v>46153</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>46153</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>46153</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6894,6 +6975,15 @@
                 </c:pt>
                 <c:pt idx="206">
                   <c:v>32.1</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>32.1</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>32.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>32.299999999999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7580,6 +7670,15 @@
                 <c:pt idx="207">
                   <c:v>46150</c:v>
                 </c:pt>
+                <c:pt idx="208">
+                  <c:v>46153</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>46153</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>46153</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8209,6 +8308,15 @@
                 </c:pt>
                 <c:pt idx="206">
                   <c:v>5.3680000000000003</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>5.3680000000000003</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>5.2709999999999999</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>5.2709999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8881,6 +8989,15 @@
                 <c:pt idx="207">
                   <c:v>46150</c:v>
                 </c:pt>
+                <c:pt idx="208">
+                  <c:v>46153</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>46153</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>46153</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9510,6 +9627,15 @@
                 </c:pt>
                 <c:pt idx="206">
                   <c:v>8.7249999999999996</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>8.7249999999999996</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>8.7750000000000004</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>8.7750000000000004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9881,6 +10007,9 @@
                 <c:pt idx="13">
                   <c:v>46146</c:v>
                 </c:pt>
+                <c:pt idx="14">
+                  <c:v>46153</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9931,6 +10060,9 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>216</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>215.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10019,6 +10151,9 @@
                 <c:pt idx="13">
                   <c:v>46146</c:v>
                 </c:pt>
+                <c:pt idx="14">
+                  <c:v>46153</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10069,6 +10204,9 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>148.83000000000001</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>148.435</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10173,6 +10311,9 @@
                 <c:pt idx="13">
                   <c:v>46146</c:v>
                 </c:pt>
+                <c:pt idx="14">
+                  <c:v>46153</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10222,6 +10363,9 @@
                   <c:v>970</c:v>
                 </c:pt>
                 <c:pt idx="13">
+                  <c:v>960</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>960</c:v>
                 </c:pt>
               </c:numCache>
@@ -10595,6 +10739,9 @@
                 <c:pt idx="13">
                   <c:v>46146</c:v>
                 </c:pt>
+                <c:pt idx="14">
+                  <c:v>46153</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10645,6 +10792,9 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>11.773</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>11.635999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10733,6 +10883,9 @@
                 <c:pt idx="13">
                   <c:v>46146</c:v>
                 </c:pt>
+                <c:pt idx="14">
+                  <c:v>46153</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10783,6 +10936,9 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>11.829000000000001</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>11.702</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13050,7 +13206,7 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y210"/>
+  <dimension ref="A1:Y213"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="12" bestFit="1" customWidth="1"/>
@@ -29157,6 +29313,237 @@
         <v>0.75694444444444453</v>
       </c>
       <c r="D210" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E210" s="11">
+        <v>52</v>
+      </c>
+      <c r="F210" s="11">
+        <v>29</v>
+      </c>
+      <c r="G210" s="11">
+        <v>39.832999999999998</v>
+      </c>
+      <c r="H210" s="11">
+        <v>24.8</v>
+      </c>
+      <c r="I210" s="11">
+        <v>21.5</v>
+      </c>
+      <c r="J210" s="11">
+        <v>22.1</v>
+      </c>
+      <c r="K210" s="11">
+        <v>72</v>
+      </c>
+      <c r="L210" s="11">
+        <v>32</v>
+      </c>
+      <c r="M210" s="11">
+        <v>58.454999999999998</v>
+      </c>
+      <c r="N210" s="11">
+        <v>13.5</v>
+      </c>
+      <c r="O210" s="11">
+        <v>11</v>
+      </c>
+      <c r="P210" s="11">
+        <v>12.6</v>
+      </c>
+      <c r="Q210" s="11">
+        <v>52</v>
+      </c>
+      <c r="R210" s="11">
+        <v>16</v>
+      </c>
+      <c r="S210" s="11">
+        <v>32.1</v>
+      </c>
+      <c r="T210" s="11">
+        <v>5.8</v>
+      </c>
+      <c r="U210" s="11">
+        <v>3.8</v>
+      </c>
+      <c r="V210" s="11">
+        <v>5.3680000000000003</v>
+      </c>
+      <c r="W210" s="11">
+        <v>10.8</v>
+      </c>
+      <c r="X210" s="11">
+        <v>5.4</v>
+      </c>
+      <c r="Y210" s="11">
+        <v>8.7249999999999996</v>
+      </c>
+    </row>
+    <row r="211" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A211" s="12">
+        <v>46153</v>
+      </c>
+      <c r="B211" s="12">
+        <v>46153</v>
+      </c>
+      <c r="C211" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D211" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E211" s="11">
+        <v>52</v>
+      </c>
+      <c r="F211" s="11">
+        <v>29.2</v>
+      </c>
+      <c r="G211" s="11">
+        <v>40</v>
+      </c>
+      <c r="H211" s="11">
+        <v>25</v>
+      </c>
+      <c r="I211" s="11">
+        <v>21.6</v>
+      </c>
+      <c r="J211" s="11">
+        <v>22.1</v>
+      </c>
+      <c r="K211" s="11">
+        <v>70</v>
+      </c>
+      <c r="L211" s="11">
+        <v>32.5</v>
+      </c>
+      <c r="M211" s="11">
+        <v>58</v>
+      </c>
+      <c r="N211" s="11">
+        <v>13.2</v>
+      </c>
+      <c r="O211" s="11">
+        <v>10.8</v>
+      </c>
+      <c r="P211" s="11">
+        <v>12.525</v>
+      </c>
+      <c r="Q211" s="11">
+        <v>52.5</v>
+      </c>
+      <c r="R211" s="11">
+        <v>16.2</v>
+      </c>
+      <c r="S211" s="11">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="T211" s="11">
+        <v>5.6</v>
+      </c>
+      <c r="U211" s="11">
+        <v>3.75</v>
+      </c>
+      <c r="V211" s="11">
+        <v>5.2709999999999999</v>
+      </c>
+      <c r="W211" s="11">
+        <v>11</v>
+      </c>
+      <c r="X211" s="11">
+        <v>5.45</v>
+      </c>
+      <c r="Y211" s="11">
+        <v>8.7750000000000004</v>
+      </c>
+    </row>
+    <row r="212" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A212" s="12">
+        <v>46153</v>
+      </c>
+      <c r="B212" s="12">
+        <v>46153</v>
+      </c>
+      <c r="C212" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D212" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E212" s="11">
+        <v>52</v>
+      </c>
+      <c r="F212" s="11">
+        <v>29.5</v>
+      </c>
+      <c r="G212" s="11">
+        <v>40.167000000000002</v>
+      </c>
+      <c r="H212" s="11">
+        <v>25</v>
+      </c>
+      <c r="I212" s="11">
+        <v>21.6</v>
+      </c>
+      <c r="J212" s="11">
+        <v>22.1</v>
+      </c>
+      <c r="K212" s="11">
+        <v>70</v>
+      </c>
+      <c r="L212" s="11">
+        <v>32.5</v>
+      </c>
+      <c r="M212" s="11">
+        <v>58.475999999999999</v>
+      </c>
+      <c r="N212" s="11">
+        <v>13.2</v>
+      </c>
+      <c r="O212" s="11">
+        <v>10.8</v>
+      </c>
+      <c r="P212" s="11">
+        <v>12.525</v>
+      </c>
+      <c r="Q212" s="11">
+        <v>52.8</v>
+      </c>
+      <c r="R212" s="11">
+        <v>16.2</v>
+      </c>
+      <c r="S212" s="11">
+        <v>32.299999999999997</v>
+      </c>
+      <c r="T212" s="11">
+        <v>5.6</v>
+      </c>
+      <c r="U212" s="11">
+        <v>3.75</v>
+      </c>
+      <c r="V212" s="11">
+        <v>5.2709999999999999</v>
+      </c>
+      <c r="W212" s="11">
+        <v>11</v>
+      </c>
+      <c r="X212" s="11">
+        <v>5.45</v>
+      </c>
+      <c r="Y212" s="11">
+        <v>8.7750000000000004</v>
+      </c>
+    </row>
+    <row r="213" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A213" s="12">
+        <v>46153</v>
+      </c>
+      <c r="B213" s="12">
+        <v>46153</v>
+      </c>
+      <c r="C213" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D213" s="7" t="s">
         <v>53</v>
       </c>
     </row>
@@ -29738,7 +30125,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:Y16"/>
+  <dimension ref="A1:Y17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="12" bestFit="1" customWidth="1"/>
@@ -30452,6 +30839,47 @@
         <v>148.83000000000001</v>
       </c>
     </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A17" s="12">
+        <v>46146</v>
+      </c>
+      <c r="B17" s="12">
+        <v>46153</v>
+      </c>
+      <c r="C17" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E17" s="14">
+        <v>218</v>
+      </c>
+      <c r="F17" s="14">
+        <v>193</v>
+      </c>
+      <c r="G17" s="11">
+        <v>215.5</v>
+      </c>
+      <c r="H17" s="14">
+        <v>1180</v>
+      </c>
+      <c r="I17" s="14">
+        <v>860</v>
+      </c>
+      <c r="J17" s="11">
+        <v>960</v>
+      </c>
+      <c r="K17" s="14">
+        <v>170</v>
+      </c>
+      <c r="L17" s="14">
+        <v>136</v>
+      </c>
+      <c r="M17" s="11">
+        <v>148.435</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:A2"/>
@@ -30468,7 +30896,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:Y16"/>
+  <dimension ref="A1:Y17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="7" bestFit="1" customWidth="1"/>
@@ -31042,6 +31470,38 @@
       </c>
       <c r="J16" s="11">
         <v>11.829000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A17" s="12">
+        <v>46146</v>
+      </c>
+      <c r="B17" s="12">
+        <v>46153</v>
+      </c>
+      <c r="C17" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E17" s="11">
+        <v>17.5</v>
+      </c>
+      <c r="F17" s="11">
+        <v>9.5</v>
+      </c>
+      <c r="G17" s="11">
+        <v>11.635999999999999</v>
+      </c>
+      <c r="H17" s="11">
+        <v>17.5</v>
+      </c>
+      <c r="I17" s="11">
+        <v>9.5</v>
+      </c>
+      <c r="J17" s="11">
+        <v>11.702</v>
       </c>
     </row>
   </sheetData>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06DF4B21-405F-4992-B266-2E18A59C1499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C10F5F45-9BB9-4836-BF05-92115BC6D98F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29670" yWindow="870" windowWidth="21600" windowHeight="10875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -1141,6 +1141,15 @@
                 <c:pt idx="231">
                   <c:v>46162</c:v>
                 </c:pt>
+                <c:pt idx="232">
+                  <c:v>46163</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>46163</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>46163</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1842,6 +1851,15 @@
                 </c:pt>
                 <c:pt idx="230">
                   <c:v>41.167000000000002</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>41.167000000000002</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>41.167000000000002</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>41.332999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2584,6 +2602,15 @@
                 <c:pt idx="231">
                   <c:v>46162</c:v>
                 </c:pt>
+                <c:pt idx="232">
+                  <c:v>46163</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>46163</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>46163</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3284,6 +3311,15 @@
                   <c:v>22.5</c:v>
                 </c:pt>
                 <c:pt idx="230">
+                  <c:v>22.5</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>22.5</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>22.5</c:v>
+                </c:pt>
+                <c:pt idx="233">
                   <c:v>22.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -4027,6 +4063,15 @@
                 <c:pt idx="231">
                   <c:v>46162</c:v>
                 </c:pt>
+                <c:pt idx="232">
+                  <c:v>46163</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>46163</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>46163</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4728,6 +4773,15 @@
                 </c:pt>
                 <c:pt idx="230">
                   <c:v>59.429000000000002</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>59.429000000000002</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>60.143000000000001</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>60.143000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5470,6 +5524,15 @@
                 <c:pt idx="231">
                   <c:v>46162</c:v>
                 </c:pt>
+                <c:pt idx="232">
+                  <c:v>46163</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>46163</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>46163</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6171,6 +6234,15 @@
                 </c:pt>
                 <c:pt idx="230">
                   <c:v>12.375</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>12.375</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>12.35</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>12.35</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6913,6 +6985,15 @@
                 <c:pt idx="231">
                   <c:v>46162</c:v>
                 </c:pt>
+                <c:pt idx="232">
+                  <c:v>46163</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>46163</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>46163</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7614,6 +7695,15 @@
                 </c:pt>
                 <c:pt idx="230">
                   <c:v>32.4</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>32.4</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>32.9</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>32.9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8372,6 +8462,15 @@
                 <c:pt idx="231">
                   <c:v>46162</c:v>
                 </c:pt>
+                <c:pt idx="232">
+                  <c:v>46163</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>46163</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>46163</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9072,6 +9171,15 @@
                   <c:v>4.907</c:v>
                 </c:pt>
                 <c:pt idx="230">
+                  <c:v>4.8639999999999999</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>4.8639999999999999</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>4.8639999999999999</c:v>
+                </c:pt>
+                <c:pt idx="233">
                   <c:v>4.8639999999999999</c:v>
                 </c:pt>
               </c:numCache>
@@ -9817,6 +9925,15 @@
                 <c:pt idx="231">
                   <c:v>46162</c:v>
                 </c:pt>
+                <c:pt idx="232">
+                  <c:v>46163</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>46163</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>46163</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10518,6 +10635,15 @@
                 </c:pt>
                 <c:pt idx="230">
                   <c:v>9.0380000000000003</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>9.0380000000000003</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>9.0879999999999992</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>9.0879999999999992</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10843,56 +10969,59 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Module!$B$3:$B$1119</c:f>
+              <c:f>Module!$B$4:$B$1121</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="1117"/>
+                <c:ptCount val="1118"/>
                 <c:pt idx="0">
+                  <c:v>46041</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>46048</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>46055</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>46062</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>46076</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>46083</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>46090</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>46097</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>46104</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>46111</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>46118</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>46125</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>46132</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>46139</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>46146</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>46153</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>46160</c:v>
                 </c:pt>
               </c:numCache>
@@ -10900,56 +11029,59 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Module!$G$3:$G$1119</c:f>
+              <c:f>Module!$G$4:$G$1121</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
-                <c:ptCount val="1117"/>
+                <c:ptCount val="1118"/>
                 <c:pt idx="0">
                   <c:v>177.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>250</c:v>
+                  <c:v>215</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>250</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>245</c:v>
+                  <c:v>250</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>245</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>245</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>240</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>230</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>232.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>232.5</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>232.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>242.5</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>222.5</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>219</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>218.5</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>216</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>215.5</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>215</c:v>
                 </c:pt>
               </c:numCache>
@@ -10993,56 +11125,59 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Module!$B$3:$B$1119</c:f>
+              <c:f>Module!$B$4:$B$1121</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="1117"/>
+                <c:ptCount val="1118"/>
                 <c:pt idx="0">
+                  <c:v>46041</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>46048</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>46055</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>46062</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>46076</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>46083</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>46090</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>46097</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>46104</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>46111</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>46118</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>46125</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>46132</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>46139</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>46146</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>46153</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>46160</c:v>
                 </c:pt>
               </c:numCache>
@@ -11050,56 +11185,59 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Module!$M$3:$M$1119</c:f>
+              <c:f>Module!$M$4:$M$1121</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
-                <c:ptCount val="1117"/>
+                <c:ptCount val="1118"/>
                 <c:pt idx="0">
                   <c:v>94</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>99.667000000000002</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>110</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>118.333</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>121</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>122.667</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>123.333</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>126.667</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>132.333</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>143.333</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>150</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>149.333</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>149.209</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>148.86799999999999</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>148.83000000000001</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>148.435</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>150.761</c:v>
                 </c:pt>
               </c:numCache>
@@ -11159,56 +11297,59 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Module!$B$3:$B$1119</c:f>
+              <c:f>Module!$B$4:$B$1121</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="1117"/>
+                <c:ptCount val="1118"/>
                 <c:pt idx="0">
+                  <c:v>46041</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>46048</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>46055</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>46062</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>46076</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>46083</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>46090</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>46097</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>46104</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>46111</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>46118</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>46125</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>46132</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>46139</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>46146</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>46153</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>46160</c:v>
                 </c:pt>
               </c:numCache>
@@ -11216,56 +11357,59 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Module!$J$3:$J$1119</c:f>
+              <c:f>Module!$J$4:$J$1121</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
-                <c:ptCount val="1117"/>
+                <c:ptCount val="1118"/>
                 <c:pt idx="0">
                   <c:v>545</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>715</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>850</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>870</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>885</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>890</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>900</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>910</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>917.5</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>925</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>935</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>930</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>975</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>970</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>960</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>960</c:v>
                 </c:pt>
                 <c:pt idx="15">
+                  <c:v>960</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>975</c:v>
                 </c:pt>
               </c:numCache>
@@ -11296,10 +11440,11 @@
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="46387"/>
+          <c:min val="46023"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="yyyy/mm/dd;@" sourceLinked="0"/>
+        <c:numFmt formatCode="yyyy/mm;@" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -11593,56 +11738,59 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>GDDR!$B$3:$B$1119</c:f>
+              <c:f>GDDR!$B$4:$B$1121</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="1117"/>
+                <c:ptCount val="1118"/>
                 <c:pt idx="0">
+                  <c:v>46041</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>46048</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>46055</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>46062</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>46076</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>46083</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>46090</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>46097</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>46104</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>46111</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>46118</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>46125</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>46132</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>46139</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>46146</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>46153</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>46160</c:v>
                 </c:pt>
               </c:numCache>
@@ -11650,56 +11798,59 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>GDDR!$G$3:$G$1119</c:f>
+              <c:f>GDDR!$G$4:$G$1121</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
-                <c:ptCount val="1117"/>
+                <c:ptCount val="1118"/>
                 <c:pt idx="0">
                   <c:v>7.0910000000000002</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>7.8819791193826605</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>8.6820000000000004</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>9.4090000000000007</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>9.6359999999999992</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>10</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>10.455</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>11.182</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>11.682</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>12.727</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>12.526999999999999</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>12.318</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>12.227</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>11.864000000000001</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>11.773</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>11.635999999999999</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>11.635999999999999</c:v>
                 </c:pt>
               </c:numCache>
@@ -11743,56 +11894,59 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>GDDR!$B$3:$B$1119</c:f>
+              <c:f>GDDR!$B$4:$B$1121</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="1117"/>
+                <c:ptCount val="1118"/>
                 <c:pt idx="0">
+                  <c:v>46041</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>46048</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>46055</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>46062</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>46076</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>46083</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>46090</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>46097</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>46104</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>46111</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>46118</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>46125</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>46132</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>46139</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>46146</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>46153</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>46160</c:v>
                 </c:pt>
               </c:numCache>
@@ -11800,56 +11954,59 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>GDDR!$J$3:$J$1119</c:f>
+              <c:f>GDDR!$J$4:$J$1121</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
-                <c:ptCount val="1117"/>
+                <c:ptCount val="1118"/>
                 <c:pt idx="0">
                   <c:v>7.1539999999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>8.0379000816030466</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>8.8650000000000002</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>9.6539999999999999</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>9.8650000000000002</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>10.221</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>10.721</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>11.462</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>11.962</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>12.865</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>12.71</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>12.412000000000001</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>12.335000000000001</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>11.962</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>11.829000000000001</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>11.702</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>11.632999999999999</c:v>
                 </c:pt>
               </c:numCache>
@@ -11879,10 +12036,11 @@
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="46387"/>
+          <c:min val="46023"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="yyyy\-mm\-dd;@" sourceLinked="1"/>
+        <c:numFmt formatCode="yyyy\-mm;@" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -14118,7 +14276,7 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y234"/>
+  <dimension ref="A1:Y237"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="12.44140625" style="12" bestFit="1" customWidth="1"/>
@@ -32073,6 +32231,237 @@
         <v>0.75694444444444453</v>
       </c>
       <c r="D234" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E234" s="11">
+        <v>53</v>
+      </c>
+      <c r="F234" s="11">
+        <v>30</v>
+      </c>
+      <c r="G234" s="11">
+        <v>41.167000000000002</v>
+      </c>
+      <c r="H234" s="11">
+        <v>24.6</v>
+      </c>
+      <c r="I234" s="11">
+        <v>22</v>
+      </c>
+      <c r="J234" s="11">
+        <v>22.5</v>
+      </c>
+      <c r="K234" s="11">
+        <v>70</v>
+      </c>
+      <c r="L234" s="11">
+        <v>33.5</v>
+      </c>
+      <c r="M234" s="11">
+        <v>59.429000000000002</v>
+      </c>
+      <c r="N234" s="11">
+        <v>13.2</v>
+      </c>
+      <c r="O234" s="11">
+        <v>10.6</v>
+      </c>
+      <c r="P234" s="11">
+        <v>12.375</v>
+      </c>
+      <c r="Q234" s="11">
+        <v>53</v>
+      </c>
+      <c r="R234" s="11">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="S234" s="11">
+        <v>32.4</v>
+      </c>
+      <c r="T234" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="U234" s="11">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="V234" s="11">
+        <v>4.8639999999999999</v>
+      </c>
+      <c r="W234" s="11">
+        <v>11.5</v>
+      </c>
+      <c r="X234" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="Y234" s="11">
+        <v>9.0380000000000003</v>
+      </c>
+    </row>
+    <row r="235" spans="1:25">
+      <c r="A235" s="12">
+        <v>46163</v>
+      </c>
+      <c r="B235" s="12">
+        <v>46163</v>
+      </c>
+      <c r="C235" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D235" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E235" s="11">
+        <v>52.5</v>
+      </c>
+      <c r="F235" s="11">
+        <v>30.5</v>
+      </c>
+      <c r="G235" s="11">
+        <v>41.167000000000002</v>
+      </c>
+      <c r="H235" s="11">
+        <v>24.8</v>
+      </c>
+      <c r="I235" s="11">
+        <v>22</v>
+      </c>
+      <c r="J235" s="11">
+        <v>22.5</v>
+      </c>
+      <c r="K235" s="11">
+        <v>70.5</v>
+      </c>
+      <c r="L235" s="11">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="M235" s="11">
+        <v>60.143000000000001</v>
+      </c>
+      <c r="N235" s="11">
+        <v>13</v>
+      </c>
+      <c r="O235" s="11">
+        <v>10.5</v>
+      </c>
+      <c r="P235" s="11">
+        <v>12.35</v>
+      </c>
+      <c r="Q235" s="11">
+        <v>53.5</v>
+      </c>
+      <c r="R235" s="11">
+        <v>16.5</v>
+      </c>
+      <c r="S235" s="11">
+        <v>32.9</v>
+      </c>
+      <c r="T235" s="11">
+        <v>5.4</v>
+      </c>
+      <c r="U235" s="11">
+        <v>4.25</v>
+      </c>
+      <c r="V235" s="11">
+        <v>4.8639999999999999</v>
+      </c>
+      <c r="W235" s="11">
+        <v>11.5</v>
+      </c>
+      <c r="X235" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="Y235" s="11">
+        <v>9.0879999999999992</v>
+      </c>
+    </row>
+    <row r="236" spans="1:25">
+      <c r="A236" s="12">
+        <v>46163</v>
+      </c>
+      <c r="B236" s="12">
+        <v>46163</v>
+      </c>
+      <c r="C236" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D236" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E236" s="11">
+        <v>52.5</v>
+      </c>
+      <c r="F236" s="11">
+        <v>30.5</v>
+      </c>
+      <c r="G236" s="11">
+        <v>41.332999999999998</v>
+      </c>
+      <c r="H236" s="11">
+        <v>24.8</v>
+      </c>
+      <c r="I236" s="11">
+        <v>22</v>
+      </c>
+      <c r="J236" s="11">
+        <v>22.5</v>
+      </c>
+      <c r="K236" s="11">
+        <v>70.5</v>
+      </c>
+      <c r="L236" s="11">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="M236" s="11">
+        <v>60.143000000000001</v>
+      </c>
+      <c r="N236" s="11">
+        <v>13</v>
+      </c>
+      <c r="O236" s="11">
+        <v>10.5</v>
+      </c>
+      <c r="P236" s="11">
+        <v>12.35</v>
+      </c>
+      <c r="Q236" s="11">
+        <v>53.5</v>
+      </c>
+      <c r="R236" s="11">
+        <v>16.5</v>
+      </c>
+      <c r="S236" s="11">
+        <v>32.9</v>
+      </c>
+      <c r="T236" s="11">
+        <v>5.4</v>
+      </c>
+      <c r="U236" s="11">
+        <v>4.25</v>
+      </c>
+      <c r="V236" s="11">
+        <v>4.8639999999999999</v>
+      </c>
+      <c r="W236" s="11">
+        <v>11.5</v>
+      </c>
+      <c r="X236" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="Y236" s="11">
+        <v>9.0879999999999992</v>
+      </c>
+    </row>
+    <row r="237" spans="1:25">
+      <c r="A237" s="12">
+        <v>46163</v>
+      </c>
+      <c r="B237" s="12">
+        <v>46163</v>
+      </c>
+      <c r="C237" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D237" s="7" t="s">
         <v>53</v>
       </c>
     </row>
@@ -32654,7 +33043,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:Y18"/>
+  <dimension ref="A1:Y20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="12.109375" style="12" bestFit="1" customWidth="1"/>
@@ -32772,43 +33161,43 @@
     </row>
     <row r="3" spans="1:25">
       <c r="A3" s="12">
+        <v>46027</v>
+      </c>
+      <c r="B3" s="12">
         <v>46034</v>
-      </c>
-      <c r="B3" s="12">
-        <v>46048</v>
       </c>
       <c r="C3" s="8">
         <v>0.61111111111111105</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E3" s="13">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="F3" s="13">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="G3" s="10">
-        <v>177.5</v>
+        <v>157.5</v>
       </c>
       <c r="H3" s="13">
-        <v>630</v>
+        <v>575</v>
       </c>
       <c r="I3" s="13">
-        <v>490</v>
+        <v>450</v>
       </c>
       <c r="J3" s="10">
-        <v>545</v>
+        <v>480</v>
       </c>
       <c r="K3" s="13">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="L3" s="13">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="M3" s="10">
-        <v>94</v>
+        <v>89.332999999999998</v>
       </c>
       <c r="N3" s="10"/>
       <c r="O3" s="10"/>
@@ -32825,10 +33214,10 @@
     </row>
     <row r="4" spans="1:25">
       <c r="A4" s="12">
-        <v>46048</v>
+        <v>46034</v>
       </c>
       <c r="B4" s="12">
-        <v>46055</v>
+        <v>46041</v>
       </c>
       <c r="C4" s="8">
         <v>0.61111111111111105</v>
@@ -32837,51 +33226,51 @@
         <v>53</v>
       </c>
       <c r="E4" s="13">
-        <v>280</v>
+        <v>230</v>
       </c>
       <c r="F4" s="13">
-        <v>230</v>
+        <v>160</v>
       </c>
       <c r="G4" s="10">
-        <v>250</v>
+        <v>177.5</v>
       </c>
       <c r="H4" s="13">
-        <v>1000</v>
+        <v>630</v>
       </c>
       <c r="I4" s="13">
-        <v>700</v>
+        <v>490</v>
       </c>
       <c r="J4" s="10">
-        <v>850</v>
+        <v>545</v>
       </c>
       <c r="K4" s="13">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="L4" s="13">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="M4" s="10">
-        <v>110</v>
-      </c>
-      <c r="N4" s="10"/>
-      <c r="O4" s="10"/>
-      <c r="P4" s="10"/>
-      <c r="Q4" s="10"/>
-      <c r="R4" s="10"/>
-      <c r="S4" s="10"/>
-      <c r="T4" s="10"/>
-      <c r="U4" s="10"/>
-      <c r="V4" s="10"/>
+        <v>94</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="4"/>
+      <c r="S4" s="4"/>
+      <c r="T4" s="4"/>
+      <c r="U4" s="4"/>
+      <c r="V4" s="4"/>
       <c r="W4" s="10"/>
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
     <row r="5" spans="1:25">
       <c r="A5" s="12">
-        <v>46055</v>
+        <v>46041</v>
       </c>
       <c r="B5" s="12">
-        <v>46062</v>
+        <v>46048</v>
       </c>
       <c r="C5" s="8">
         <v>0.61111111111111105</v>
@@ -32889,122 +33278,146 @@
       <c r="D5" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="E5" s="14">
-        <v>280</v>
-      </c>
-      <c r="F5" s="14">
-        <v>235</v>
-      </c>
-      <c r="G5" s="11">
-        <v>250</v>
-      </c>
-      <c r="H5" s="14">
-        <v>1000</v>
-      </c>
-      <c r="I5" s="14">
-        <v>750</v>
-      </c>
-      <c r="J5" s="11">
-        <v>870</v>
-      </c>
-      <c r="K5" s="14">
-        <v>145</v>
-      </c>
-      <c r="L5" s="14">
-        <v>100</v>
-      </c>
-      <c r="M5" s="11">
-        <v>118.333</v>
-      </c>
+      <c r="E5" s="13">
+        <v>270</v>
+      </c>
+      <c r="F5" s="13">
+        <v>180</v>
+      </c>
+      <c r="G5" s="10">
+        <v>215</v>
+      </c>
+      <c r="H5" s="13">
+        <v>830</v>
+      </c>
+      <c r="I5" s="13">
+        <v>620</v>
+      </c>
+      <c r="J5" s="10">
+        <v>715</v>
+      </c>
+      <c r="K5" s="13">
+        <v>140</v>
+      </c>
+      <c r="L5" s="13">
+        <v>88</v>
+      </c>
+      <c r="M5" s="10">
+        <v>99.667000000000002</v>
+      </c>
+      <c r="N5" s="10"/>
+      <c r="O5" s="10"/>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="10"/>
+      <c r="R5" s="10"/>
+      <c r="S5" s="10"/>
+      <c r="T5" s="10"/>
+      <c r="U5" s="10"/>
+      <c r="V5" s="10"/>
+      <c r="W5" s="10"/>
+      <c r="X5" s="10"/>
+      <c r="Y5" s="10"/>
     </row>
     <row r="6" spans="1:25">
       <c r="A6" s="12">
-        <v>46062</v>
+        <v>46048</v>
       </c>
       <c r="B6" s="12">
-        <v>46076</v>
+        <v>46055</v>
       </c>
       <c r="C6" s="8">
         <v>0.61111111111111105</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="E6" s="14">
-        <v>259</v>
-      </c>
-      <c r="F6" s="14">
+        <v>53</v>
+      </c>
+      <c r="E6" s="13">
+        <v>280</v>
+      </c>
+      <c r="F6" s="13">
         <v>230</v>
       </c>
-      <c r="G6" s="11">
-        <v>245</v>
-      </c>
-      <c r="H6" s="14">
-        <v>970</v>
-      </c>
-      <c r="I6" s="14">
-        <v>800</v>
-      </c>
-      <c r="J6" s="11">
-        <v>885</v>
-      </c>
-      <c r="K6" s="14">
-        <v>148</v>
-      </c>
-      <c r="L6" s="14">
-        <v>105</v>
-      </c>
-      <c r="M6" s="11">
-        <v>121</v>
-      </c>
+      <c r="G6" s="10">
+        <v>250</v>
+      </c>
+      <c r="H6" s="13">
+        <v>1000</v>
+      </c>
+      <c r="I6" s="13">
+        <v>700</v>
+      </c>
+      <c r="J6" s="10">
+        <v>850</v>
+      </c>
+      <c r="K6" s="13">
+        <v>145</v>
+      </c>
+      <c r="L6" s="13">
+        <v>95</v>
+      </c>
+      <c r="M6" s="10">
+        <v>110</v>
+      </c>
+      <c r="N6" s="10"/>
+      <c r="O6" s="10"/>
+      <c r="P6" s="10"/>
+      <c r="Q6" s="10"/>
+      <c r="R6" s="10"/>
+      <c r="S6" s="10"/>
+      <c r="T6" s="10"/>
+      <c r="U6" s="10"/>
+      <c r="V6" s="10"/>
+      <c r="W6" s="10"/>
+      <c r="X6" s="10"/>
+      <c r="Y6" s="10"/>
     </row>
     <row r="7" spans="1:25">
       <c r="A7" s="12">
-        <v>46076</v>
+        <v>46055</v>
       </c>
       <c r="B7" s="12">
-        <v>46083</v>
+        <v>46062</v>
       </c>
       <c r="C7" s="8">
         <v>0.61111111111111105</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E7" s="14">
-        <v>259</v>
+        <v>280</v>
       </c>
       <c r="F7" s="14">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="G7" s="11">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="H7" s="14">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="I7" s="14">
-        <v>800</v>
+        <v>750</v>
       </c>
       <c r="J7" s="11">
-        <v>890</v>
+        <v>870</v>
       </c>
       <c r="K7" s="14">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="L7" s="14">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="M7" s="11">
-        <v>122.667</v>
+        <v>118.333</v>
       </c>
     </row>
     <row r="8" spans="1:25">
       <c r="A8" s="12">
-        <v>46083</v>
+        <v>46062</v>
       </c>
       <c r="B8" s="12">
-        <v>46090</v>
+        <v>46076</v>
       </c>
       <c r="C8" s="8">
         <v>0.61111111111111105</v>
@@ -33013,39 +33426,39 @@
         <v>57</v>
       </c>
       <c r="E8" s="14">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="F8" s="14">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="G8" s="11">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="H8" s="14">
-        <v>980</v>
+        <v>970</v>
       </c>
       <c r="I8" s="14">
-        <v>830</v>
+        <v>800</v>
       </c>
       <c r="J8" s="11">
-        <v>900</v>
+        <v>885</v>
       </c>
       <c r="K8" s="14">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="L8" s="14">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M8" s="11">
-        <v>123.333</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:25">
       <c r="A9" s="12">
-        <v>46090</v>
+        <v>46076</v>
       </c>
       <c r="B9" s="12">
-        <v>46097</v>
+        <v>46083</v>
       </c>
       <c r="C9" s="8">
         <v>0.61111111111111105</v>
@@ -33054,39 +33467,39 @@
         <v>57</v>
       </c>
       <c r="E9" s="14">
-        <v>240</v>
+        <v>259</v>
       </c>
       <c r="F9" s="14">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="G9" s="11">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="H9" s="14">
-        <v>990</v>
+        <v>970</v>
       </c>
       <c r="I9" s="14">
-        <v>850</v>
+        <v>800</v>
       </c>
       <c r="J9" s="11">
-        <v>910</v>
+        <v>890</v>
       </c>
       <c r="K9" s="14">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="L9" s="14">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="M9" s="11">
-        <v>126.667</v>
+        <v>122.667</v>
       </c>
     </row>
     <row r="10" spans="1:25">
       <c r="A10" s="12">
-        <v>46097</v>
+        <v>46083</v>
       </c>
       <c r="B10" s="12">
-        <v>46104</v>
+        <v>46090</v>
       </c>
       <c r="C10" s="8">
         <v>0.61111111111111105</v>
@@ -33095,39 +33508,39 @@
         <v>57</v>
       </c>
       <c r="E10" s="14">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="F10" s="14">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="G10" s="11">
-        <v>232.5</v>
+        <v>240</v>
       </c>
       <c r="H10" s="14">
-        <v>1050</v>
+        <v>980</v>
       </c>
       <c r="I10" s="14">
-        <v>860</v>
+        <v>830</v>
       </c>
       <c r="J10" s="11">
-        <v>917.5</v>
+        <v>900</v>
       </c>
       <c r="K10" s="14">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="L10" s="14">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="M10" s="11">
-        <v>132.333</v>
+        <v>123.333</v>
       </c>
     </row>
     <row r="11" spans="1:25">
       <c r="A11" s="12">
-        <v>46104</v>
+        <v>46090</v>
       </c>
       <c r="B11" s="12">
-        <v>46111</v>
+        <v>46097</v>
       </c>
       <c r="C11" s="8">
         <v>0.61111111111111105</v>
@@ -33136,39 +33549,39 @@
         <v>57</v>
       </c>
       <c r="E11" s="14">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="F11" s="14">
         <v>200</v>
       </c>
       <c r="G11" s="11">
-        <v>232.5</v>
+        <v>230</v>
       </c>
       <c r="H11" s="14">
-        <v>1060</v>
+        <v>990</v>
       </c>
       <c r="I11" s="14">
-        <v>870</v>
+        <v>850</v>
       </c>
       <c r="J11" s="11">
-        <v>925</v>
+        <v>910</v>
       </c>
       <c r="K11" s="14">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="L11" s="14">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="M11" s="11">
-        <v>143.333</v>
+        <v>126.667</v>
       </c>
     </row>
     <row r="12" spans="1:25">
       <c r="A12" s="12">
-        <v>46111</v>
+        <v>46097</v>
       </c>
       <c r="B12" s="12">
-        <v>46118</v>
+        <v>46104</v>
       </c>
       <c r="C12" s="8">
         <v>0.61111111111111105</v>
@@ -33177,39 +33590,39 @@
         <v>57</v>
       </c>
       <c r="E12" s="14">
-        <v>260</v>
+        <v>245</v>
       </c>
       <c r="F12" s="14">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="G12" s="11">
-        <v>242.5</v>
+        <v>232.5</v>
       </c>
       <c r="H12" s="14">
-        <v>1150</v>
+        <v>1050</v>
       </c>
       <c r="I12" s="14">
-        <v>880</v>
+        <v>860</v>
       </c>
       <c r="J12" s="11">
-        <v>935</v>
+        <v>917.5</v>
       </c>
       <c r="K12" s="14">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="L12" s="14">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="M12" s="11">
-        <v>150</v>
+        <v>132.333</v>
       </c>
     </row>
     <row r="13" spans="1:25">
       <c r="A13" s="12">
-        <v>46118</v>
+        <v>46104</v>
       </c>
       <c r="B13" s="12">
-        <v>46125</v>
+        <v>46111</v>
       </c>
       <c r="C13" s="8">
         <v>0.61111111111111105</v>
@@ -33218,39 +33631,39 @@
         <v>57</v>
       </c>
       <c r="E13" s="14">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="F13" s="14">
         <v>200</v>
       </c>
       <c r="G13" s="11">
-        <v>222.5</v>
+        <v>232.5</v>
       </c>
       <c r="H13" s="14">
-        <v>1150</v>
+        <v>1060</v>
       </c>
       <c r="I13" s="14">
-        <v>880</v>
+        <v>870</v>
       </c>
       <c r="J13" s="11">
-        <v>930</v>
+        <v>925</v>
       </c>
       <c r="K13" s="14">
         <v>171</v>
       </c>
       <c r="L13" s="14">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="M13" s="11">
-        <v>149.333</v>
+        <v>143.333</v>
       </c>
     </row>
     <row r="14" spans="1:25">
       <c r="A14" s="12">
-        <v>46125</v>
+        <v>46111</v>
       </c>
       <c r="B14" s="12">
-        <v>46132</v>
+        <v>46118</v>
       </c>
       <c r="C14" s="8">
         <v>0.61111111111111105</v>
@@ -33259,39 +33672,39 @@
         <v>57</v>
       </c>
       <c r="E14" s="14">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="F14" s="14">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="G14" s="11">
-        <v>219</v>
+        <v>242.5</v>
       </c>
       <c r="H14" s="14">
         <v>1150</v>
       </c>
       <c r="I14" s="14">
-        <v>900</v>
+        <v>880</v>
       </c>
       <c r="J14" s="11">
-        <v>975</v>
+        <v>935</v>
       </c>
       <c r="K14" s="14">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L14" s="14">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="M14" s="11">
-        <v>149.209</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:25">
       <c r="A15" s="12">
-        <v>46132</v>
+        <v>46118</v>
       </c>
       <c r="B15" s="12">
-        <v>46139</v>
+        <v>46125</v>
       </c>
       <c r="C15" s="8">
         <v>0.61111111111111105</v>
@@ -33300,39 +33713,39 @@
         <v>57</v>
       </c>
       <c r="E15" s="14">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="F15" s="14">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="G15" s="11">
-        <v>218.5</v>
+        <v>222.5</v>
       </c>
       <c r="H15" s="14">
-        <v>1185</v>
+        <v>1150</v>
       </c>
       <c r="I15" s="14">
         <v>880</v>
       </c>
       <c r="J15" s="11">
-        <v>970</v>
+        <v>930</v>
       </c>
       <c r="K15" s="14">
         <v>171</v>
       </c>
       <c r="L15" s="14">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M15" s="11">
-        <v>148.86799999999999</v>
+        <v>149.333</v>
       </c>
     </row>
     <row r="16" spans="1:25">
       <c r="A16" s="12">
-        <v>46139</v>
+        <v>46125</v>
       </c>
       <c r="B16" s="12">
-        <v>46146</v>
+        <v>46132</v>
       </c>
       <c r="C16" s="8">
         <v>0.61111111111111105</v>
@@ -33341,39 +33754,39 @@
         <v>57</v>
       </c>
       <c r="E16" s="14">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="F16" s="14">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="G16" s="11">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="H16" s="14">
-        <v>1170</v>
+        <v>1150</v>
       </c>
       <c r="I16" s="14">
-        <v>850</v>
+        <v>900</v>
       </c>
       <c r="J16" s="11">
-        <v>960</v>
+        <v>975</v>
       </c>
       <c r="K16" s="14">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L16" s="14">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="M16" s="11">
-        <v>148.83000000000001</v>
+        <v>149.209</v>
       </c>
     </row>
     <row r="17" spans="1:13">
       <c r="A17" s="12">
-        <v>46146</v>
+        <v>46132</v>
       </c>
       <c r="B17" s="12">
-        <v>46153</v>
+        <v>46139</v>
       </c>
       <c r="C17" s="8">
         <v>0.61111111111111105</v>
@@ -33382,39 +33795,39 @@
         <v>57</v>
       </c>
       <c r="E17" s="14">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="F17" s="14">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G17" s="11">
-        <v>215.5</v>
+        <v>218.5</v>
       </c>
       <c r="H17" s="14">
-        <v>1180</v>
+        <v>1185</v>
       </c>
       <c r="I17" s="14">
-        <v>860</v>
+        <v>880</v>
       </c>
       <c r="J17" s="11">
-        <v>960</v>
+        <v>970</v>
       </c>
       <c r="K17" s="14">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L17" s="14">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="M17" s="11">
-        <v>148.435</v>
+        <v>148.86799999999999</v>
       </c>
     </row>
     <row r="18" spans="1:13">
       <c r="A18" s="12">
-        <v>46153</v>
+        <v>46139</v>
       </c>
       <c r="B18" s="12">
-        <v>46160</v>
+        <v>46146</v>
       </c>
       <c r="C18" s="8">
         <v>0.61111111111111105</v>
@@ -33426,19 +33839,19 @@
         <v>220</v>
       </c>
       <c r="F18" s="14">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G18" s="11">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H18" s="14">
-        <v>1180</v>
+        <v>1170</v>
       </c>
       <c r="I18" s="14">
-        <v>900</v>
+        <v>850</v>
       </c>
       <c r="J18" s="11">
-        <v>975</v>
+        <v>960</v>
       </c>
       <c r="K18" s="14">
         <v>171</v>
@@ -33447,6 +33860,88 @@
         <v>138</v>
       </c>
       <c r="M18" s="11">
+        <v>148.83000000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
+      <c r="A19" s="12">
+        <v>46146</v>
+      </c>
+      <c r="B19" s="12">
+        <v>46153</v>
+      </c>
+      <c r="C19" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E19" s="14">
+        <v>218</v>
+      </c>
+      <c r="F19" s="14">
+        <v>193</v>
+      </c>
+      <c r="G19" s="11">
+        <v>215.5</v>
+      </c>
+      <c r="H19" s="14">
+        <v>1180</v>
+      </c>
+      <c r="I19" s="14">
+        <v>860</v>
+      </c>
+      <c r="J19" s="11">
+        <v>960</v>
+      </c>
+      <c r="K19" s="14">
+        <v>170</v>
+      </c>
+      <c r="L19" s="14">
+        <v>136</v>
+      </c>
+      <c r="M19" s="11">
+        <v>148.435</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20" s="12">
+        <v>46153</v>
+      </c>
+      <c r="B20" s="12">
+        <v>46160</v>
+      </c>
+      <c r="C20" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E20" s="14">
+        <v>220</v>
+      </c>
+      <c r="F20" s="14">
+        <v>195</v>
+      </c>
+      <c r="G20" s="11">
+        <v>215</v>
+      </c>
+      <c r="H20" s="14">
+        <v>1180</v>
+      </c>
+      <c r="I20" s="14">
+        <v>900</v>
+      </c>
+      <c r="J20" s="11">
+        <v>975</v>
+      </c>
+      <c r="K20" s="14">
+        <v>171</v>
+      </c>
+      <c r="L20" s="14">
+        <v>138</v>
+      </c>
+      <c r="M20" s="11">
         <v>150.761</v>
       </c>
     </row>
@@ -33466,7 +33961,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:Y18"/>
+  <dimension ref="A1:Y20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="12.109375" style="7" bestFit="1" customWidth="1"/>
@@ -33566,10 +34061,10 @@
     </row>
     <row r="3" spans="1:25">
       <c r="A3" s="12">
+        <v>46027</v>
+      </c>
+      <c r="B3" s="12">
         <v>46034</v>
-      </c>
-      <c r="B3" s="12">
-        <v>46048</v>
       </c>
       <c r="C3" s="8">
         <v>0.61111111111111105</v>
@@ -33578,22 +34073,22 @@
         <v>53</v>
       </c>
       <c r="E3" s="10">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="F3" s="10">
+        <v>5.2</v>
+      </c>
+      <c r="G3" s="10">
         <v>6</v>
       </c>
-      <c r="G3" s="10">
-        <v>7.0910000000000002</v>
-      </c>
       <c r="H3" s="10">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I3" s="10">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="J3" s="10">
-        <v>7.1539999999999999</v>
+        <v>5.9690000000000003</v>
       </c>
       <c r="K3" s="10"/>
       <c r="L3" s="10"/>
@@ -33613,10 +34108,10 @@
     </row>
     <row r="4" spans="1:25">
       <c r="A4" s="12">
-        <v>46048</v>
+        <v>46034</v>
       </c>
       <c r="B4" s="12">
-        <v>46055</v>
+        <v>46041</v>
       </c>
       <c r="C4" s="8">
         <v>0.61111111111111105</v>
@@ -33625,22 +34120,22 @@
         <v>53</v>
       </c>
       <c r="E4" s="10">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="F4" s="10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G4" s="10">
-        <v>8.6820000000000004</v>
+        <v>7.0910000000000002</v>
       </c>
       <c r="H4" s="10">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I4" s="10">
-        <v>7.5</v>
+        <v>5.8</v>
       </c>
       <c r="J4" s="10">
-        <v>8.8650000000000002</v>
+        <v>7.1539999999999999</v>
       </c>
       <c r="K4" s="10"/>
       <c r="L4" s="10"/>
@@ -33660,10 +34155,10 @@
     </row>
     <row r="5" spans="1:25">
       <c r="A5" s="12">
-        <v>46055</v>
+        <v>46041</v>
       </c>
       <c r="B5" s="12">
-        <v>46062</v>
+        <v>46048</v>
       </c>
       <c r="C5" s="8">
         <v>0.61111111111111105</v>
@@ -33671,95 +34166,117 @@
       <c r="D5" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="E5" s="11">
-        <v>15.5</v>
-      </c>
-      <c r="F5" s="11">
-        <v>7.5</v>
-      </c>
-      <c r="G5" s="11">
-        <v>9.4090000000000007</v>
-      </c>
-      <c r="H5" s="11">
-        <v>16</v>
-      </c>
-      <c r="I5" s="11">
-        <v>8</v>
-      </c>
-      <c r="J5" s="11">
-        <v>9.6539999999999999</v>
-      </c>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10">
+        <v>7.8819791193826605</v>
+      </c>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10">
+        <v>8.0379000816030466</v>
+      </c>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="10"/>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="10"/>
+      <c r="R5" s="10"/>
+      <c r="S5" s="10"/>
+      <c r="T5" s="10"/>
+      <c r="U5" s="10"/>
+      <c r="V5" s="10"/>
+      <c r="W5" s="10"/>
+      <c r="X5" s="10"/>
+      <c r="Y5" s="10"/>
     </row>
     <row r="6" spans="1:25">
       <c r="A6" s="12">
-        <v>46062</v>
+        <v>46048</v>
       </c>
       <c r="B6" s="12">
-        <v>46076</v>
+        <v>46055</v>
       </c>
       <c r="C6" s="8">
         <v>0.61111111111111105</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="E6" s="11">
+        <v>53</v>
+      </c>
+      <c r="E6" s="10">
         <v>15.5</v>
       </c>
-      <c r="F6" s="11">
-        <v>8</v>
-      </c>
-      <c r="G6" s="11">
-        <v>9.6359999999999992</v>
-      </c>
-      <c r="H6" s="11">
+      <c r="F6" s="10">
+        <v>7</v>
+      </c>
+      <c r="G6" s="10">
+        <v>8.6820000000000004</v>
+      </c>
+      <c r="H6" s="10">
         <v>16</v>
       </c>
-      <c r="I6" s="11">
-        <v>8.5</v>
-      </c>
-      <c r="J6" s="11">
-        <v>9.8650000000000002</v>
-      </c>
+      <c r="I6" s="10">
+        <v>7.5</v>
+      </c>
+      <c r="J6" s="10">
+        <v>8.8650000000000002</v>
+      </c>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="10"/>
+      <c r="P6" s="10"/>
+      <c r="Q6" s="10"/>
+      <c r="R6" s="10"/>
+      <c r="S6" s="10"/>
+      <c r="T6" s="10"/>
+      <c r="U6" s="10"/>
+      <c r="V6" s="10"/>
+      <c r="W6" s="10"/>
+      <c r="X6" s="10"/>
+      <c r="Y6" s="10"/>
     </row>
     <row r="7" spans="1:25">
       <c r="A7" s="12">
-        <v>46076</v>
+        <v>46055</v>
       </c>
       <c r="B7" s="12">
-        <v>46083</v>
+        <v>46062</v>
       </c>
       <c r="C7" s="8">
         <v>0.61111111111111105</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E7" s="11">
         <v>15.5</v>
       </c>
       <c r="F7" s="11">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="G7" s="11">
-        <v>10</v>
+        <v>9.4090000000000007</v>
       </c>
       <c r="H7" s="11">
         <v>16</v>
       </c>
       <c r="I7" s="11">
-        <v>8.8000000000000007</v>
+        <v>8</v>
       </c>
       <c r="J7" s="11">
-        <v>10.221</v>
+        <v>9.6539999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:25">
       <c r="A8" s="12">
-        <v>46083</v>
+        <v>46062</v>
       </c>
       <c r="B8" s="12">
-        <v>46090</v>
+        <v>46076</v>
       </c>
       <c r="C8" s="8">
         <v>0.61111111111111105</v>
@@ -33768,30 +34285,30 @@
         <v>57</v>
       </c>
       <c r="E8" s="11">
+        <v>15.5</v>
+      </c>
+      <c r="F8" s="11">
+        <v>8</v>
+      </c>
+      <c r="G8" s="11">
+        <v>9.6359999999999992</v>
+      </c>
+      <c r="H8" s="11">
         <v>16</v>
       </c>
-      <c r="F8" s="11">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="G8" s="11">
-        <v>10.455</v>
-      </c>
-      <c r="H8" s="11">
-        <v>16.5</v>
-      </c>
       <c r="I8" s="11">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="J8" s="11">
-        <v>10.721</v>
+        <v>9.8650000000000002</v>
       </c>
     </row>
     <row r="9" spans="1:25">
       <c r="A9" s="12">
-        <v>46090</v>
+        <v>46076</v>
       </c>
       <c r="B9" s="12">
-        <v>46097</v>
+        <v>46083</v>
       </c>
       <c r="C9" s="8">
         <v>0.61111111111111105</v>
@@ -33800,30 +34317,30 @@
         <v>57</v>
       </c>
       <c r="E9" s="11">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="F9" s="11">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="G9" s="11">
-        <v>11.182</v>
+        <v>10</v>
       </c>
       <c r="H9" s="11">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I9" s="11">
-        <v>10</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="J9" s="11">
-        <v>11.462</v>
+        <v>10.221</v>
       </c>
     </row>
     <row r="10" spans="1:25">
       <c r="A10" s="12">
-        <v>46097</v>
+        <v>46083</v>
       </c>
       <c r="B10" s="12">
-        <v>46104</v>
+        <v>46090</v>
       </c>
       <c r="C10" s="8">
         <v>0.61111111111111105</v>
@@ -33832,30 +34349,30 @@
         <v>57</v>
       </c>
       <c r="E10" s="11">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F10" s="11">
-        <v>10</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="G10" s="11">
-        <v>11.682</v>
+        <v>10.455</v>
       </c>
       <c r="H10" s="11">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="I10" s="11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J10" s="11">
-        <v>11.962</v>
+        <v>10.721</v>
       </c>
     </row>
     <row r="11" spans="1:25">
       <c r="A11" s="12">
-        <v>46104</v>
+        <v>46090</v>
       </c>
       <c r="B11" s="12">
-        <v>46111</v>
+        <v>46097</v>
       </c>
       <c r="C11" s="8">
         <v>0.61111111111111105</v>
@@ -33864,30 +34381,30 @@
         <v>57</v>
       </c>
       <c r="E11" s="11">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F11" s="11">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="G11" s="11">
-        <v>12.727</v>
+        <v>11.182</v>
       </c>
       <c r="H11" s="11">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I11" s="11">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J11" s="11">
-        <v>12.865</v>
+        <v>11.462</v>
       </c>
     </row>
     <row r="12" spans="1:25">
       <c r="A12" s="12">
-        <v>46111</v>
+        <v>46097</v>
       </c>
       <c r="B12" s="12">
-        <v>46118</v>
+        <v>46104</v>
       </c>
       <c r="C12" s="8">
         <v>0.61111111111111105</v>
@@ -33896,30 +34413,30 @@
         <v>57</v>
       </c>
       <c r="E12" s="11">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F12" s="11">
         <v>10</v>
       </c>
       <c r="G12" s="11">
-        <v>12.526999999999999</v>
+        <v>11.682</v>
       </c>
       <c r="H12" s="11">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I12" s="11">
         <v>10</v>
       </c>
       <c r="J12" s="11">
-        <v>12.71</v>
+        <v>11.962</v>
       </c>
     </row>
     <row r="13" spans="1:25">
       <c r="A13" s="12">
-        <v>46118</v>
+        <v>46104</v>
       </c>
       <c r="B13" s="12">
-        <v>46125</v>
+        <v>46111</v>
       </c>
       <c r="C13" s="8">
         <v>0.61111111111111105</v>
@@ -33931,27 +34448,27 @@
         <v>20</v>
       </c>
       <c r="F13" s="11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G13" s="11">
-        <v>12.318</v>
+        <v>12.727</v>
       </c>
       <c r="H13" s="11">
         <v>20</v>
       </c>
       <c r="I13" s="11">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="J13" s="11">
-        <v>12.412000000000001</v>
+        <v>12.865</v>
       </c>
     </row>
     <row r="14" spans="1:25">
       <c r="A14" s="12">
-        <v>46125</v>
+        <v>46111</v>
       </c>
       <c r="B14" s="12">
-        <v>46132</v>
+        <v>46118</v>
       </c>
       <c r="C14" s="8">
         <v>0.61111111111111105</v>
@@ -33960,30 +34477,30 @@
         <v>57</v>
       </c>
       <c r="E14" s="11">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="F14" s="11">
         <v>10</v>
       </c>
       <c r="G14" s="11">
-        <v>12.227</v>
+        <v>12.526999999999999</v>
       </c>
       <c r="H14" s="11">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I14" s="11">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="J14" s="11">
-        <v>12.335000000000001</v>
+        <v>12.71</v>
       </c>
     </row>
     <row r="15" spans="1:25">
       <c r="A15" s="12">
-        <v>46132</v>
+        <v>46118</v>
       </c>
       <c r="B15" s="12">
-        <v>46139</v>
+        <v>46125</v>
       </c>
       <c r="C15" s="8">
         <v>0.61111111111111105</v>
@@ -33992,30 +34509,30 @@
         <v>57</v>
       </c>
       <c r="E15" s="11">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F15" s="11">
+        <v>10</v>
+      </c>
+      <c r="G15" s="11">
+        <v>12.318</v>
+      </c>
+      <c r="H15" s="11">
+        <v>20</v>
+      </c>
+      <c r="I15" s="11">
         <v>9.5</v>
       </c>
-      <c r="G15" s="11">
-        <v>11.864000000000001</v>
-      </c>
-      <c r="H15" s="11">
-        <v>18</v>
-      </c>
-      <c r="I15" s="11">
-        <v>9</v>
-      </c>
       <c r="J15" s="11">
-        <v>11.962</v>
+        <v>12.412000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:25">
       <c r="A16" s="12">
-        <v>46139</v>
+        <v>46125</v>
       </c>
       <c r="B16" s="12">
-        <v>46146</v>
+        <v>46132</v>
       </c>
       <c r="C16" s="8">
         <v>0.61111111111111105</v>
@@ -34024,30 +34541,30 @@
         <v>57</v>
       </c>
       <c r="E16" s="11">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="F16" s="11">
+        <v>10</v>
+      </c>
+      <c r="G16" s="11">
+        <v>12.227</v>
+      </c>
+      <c r="H16" s="11">
+        <v>19</v>
+      </c>
+      <c r="I16" s="11">
         <v>9.5</v>
       </c>
-      <c r="G16" s="11">
-        <v>11.773</v>
-      </c>
-      <c r="H16" s="11">
-        <v>17.8</v>
-      </c>
-      <c r="I16" s="11">
-        <v>9</v>
-      </c>
       <c r="J16" s="11">
-        <v>11.829000000000001</v>
+        <v>12.335000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="12">
-        <v>46146</v>
+        <v>46132</v>
       </c>
       <c r="B17" s="12">
-        <v>46153</v>
+        <v>46139</v>
       </c>
       <c r="C17" s="8">
         <v>0.61111111111111105</v>
@@ -34056,30 +34573,30 @@
         <v>57</v>
       </c>
       <c r="E17" s="11">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="F17" s="11">
         <v>9.5</v>
       </c>
       <c r="G17" s="11">
-        <v>11.635999999999999</v>
+        <v>11.864000000000001</v>
       </c>
       <c r="H17" s="11">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="I17" s="11">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="J17" s="11">
-        <v>11.702</v>
+        <v>11.962</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="12">
-        <v>46153</v>
+        <v>46139</v>
       </c>
       <c r="B18" s="12">
-        <v>46160</v>
+        <v>46146</v>
       </c>
       <c r="C18" s="8">
         <v>0.61111111111111105</v>
@@ -34088,21 +34605,85 @@
         <v>57</v>
       </c>
       <c r="E18" s="11">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="F18" s="11">
         <v>9.5</v>
       </c>
       <c r="G18" s="11">
+        <v>11.773</v>
+      </c>
+      <c r="H18" s="11">
+        <v>17.8</v>
+      </c>
+      <c r="I18" s="11">
+        <v>9</v>
+      </c>
+      <c r="J18" s="11">
+        <v>11.829000000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="12">
+        <v>46146</v>
+      </c>
+      <c r="B19" s="12">
+        <v>46153</v>
+      </c>
+      <c r="C19" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E19" s="11">
+        <v>17.5</v>
+      </c>
+      <c r="F19" s="11">
+        <v>9.5</v>
+      </c>
+      <c r="G19" s="11">
         <v>11.635999999999999</v>
       </c>
-      <c r="H18" s="11">
+      <c r="H19" s="11">
         <v>17.5</v>
       </c>
-      <c r="I18" s="11">
+      <c r="I19" s="11">
         <v>9.5</v>
       </c>
-      <c r="J18" s="11">
+      <c r="J19" s="11">
+        <v>11.702</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="12">
+        <v>46153</v>
+      </c>
+      <c r="B20" s="12">
+        <v>46160</v>
+      </c>
+      <c r="C20" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E20" s="11">
+        <v>17.5</v>
+      </c>
+      <c r="F20" s="11">
+        <v>9.5</v>
+      </c>
+      <c r="G20" s="11">
+        <v>11.635999999999999</v>
+      </c>
+      <c r="H20" s="11">
+        <v>17.5</v>
+      </c>
+      <c r="I20" s="11">
+        <v>9.5</v>
+      </c>
+      <c r="J20" s="11">
         <v>11.632999999999999</v>
       </c>
     </row>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C10F5F45-9BB9-4836-BF05-92115BC6D98F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BDBDB94-E607-49AA-AA60-571B3B5C5494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -1861,6 +1861,9 @@
                 <c:pt idx="233">
                   <c:v>41.332999999999998</c:v>
                 </c:pt>
+                <c:pt idx="234">
+                  <c:v>41.332999999999998</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3322,6 +3325,9 @@
                 <c:pt idx="233">
                   <c:v>22.5</c:v>
                 </c:pt>
+                <c:pt idx="234">
+                  <c:v>22.5</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4783,6 +4789,9 @@
                 <c:pt idx="233">
                   <c:v>60.143000000000001</c:v>
                 </c:pt>
+                <c:pt idx="234">
+                  <c:v>60.143000000000001</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -6244,6 +6253,9 @@
                 <c:pt idx="233">
                   <c:v>12.35</c:v>
                 </c:pt>
+                <c:pt idx="234">
+                  <c:v>12.35</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -7703,6 +7715,9 @@
                   <c:v>32.9</c:v>
                 </c:pt>
                 <c:pt idx="233">
+                  <c:v>32.9</c:v>
+                </c:pt>
+                <c:pt idx="234">
                   <c:v>32.9</c:v>
                 </c:pt>
               </c:numCache>
@@ -9182,6 +9197,9 @@
                 <c:pt idx="233">
                   <c:v>4.8639999999999999</c:v>
                 </c:pt>
+                <c:pt idx="234">
+                  <c:v>4.8639999999999999</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -10643,6 +10661,9 @@
                   <c:v>9.0879999999999992</c:v>
                 </c:pt>
                 <c:pt idx="233">
+                  <c:v>9.0879999999999992</c:v>
+                </c:pt>
+                <c:pt idx="234">
                   <c:v>9.0879999999999992</c:v>
                 </c:pt>
               </c:numCache>
@@ -32464,6 +32485,69 @@
       <c r="D237" s="7" t="s">
         <v>53</v>
       </c>
+      <c r="E237" s="11">
+        <v>52.5</v>
+      </c>
+      <c r="F237" s="11">
+        <v>30.5</v>
+      </c>
+      <c r="G237" s="11">
+        <v>41.332999999999998</v>
+      </c>
+      <c r="H237" s="11">
+        <v>24.8</v>
+      </c>
+      <c r="I237" s="11">
+        <v>22</v>
+      </c>
+      <c r="J237" s="11">
+        <v>22.5</v>
+      </c>
+      <c r="K237" s="11">
+        <v>70.5</v>
+      </c>
+      <c r="L237" s="11">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="M237" s="11">
+        <v>60.143000000000001</v>
+      </c>
+      <c r="N237" s="11">
+        <v>13</v>
+      </c>
+      <c r="O237" s="11">
+        <v>10.5</v>
+      </c>
+      <c r="P237" s="11">
+        <v>12.35</v>
+      </c>
+      <c r="Q237" s="11">
+        <v>53.5</v>
+      </c>
+      <c r="R237" s="11">
+        <v>16.5</v>
+      </c>
+      <c r="S237" s="11">
+        <v>32.9</v>
+      </c>
+      <c r="T237" s="11">
+        <v>5.4</v>
+      </c>
+      <c r="U237" s="11">
+        <v>4.25</v>
+      </c>
+      <c r="V237" s="11">
+        <v>4.8639999999999999</v>
+      </c>
+      <c r="W237" s="11">
+        <v>11.5</v>
+      </c>
+      <c r="X237" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="Y237" s="11">
+        <v>9.0879999999999992</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BDBDB94-E607-49AA-AA60-571B3B5C5494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAAD2BE3-BE00-43DC-A072-EC3EB4743ABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -374,8 +374,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -393,7 +393,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1150,6 +1150,15 @@
                 <c:pt idx="234">
                   <c:v>46163</c:v>
                 </c:pt>
+                <c:pt idx="235">
+                  <c:v>46164</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>46164</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>46164</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1863,6 +1872,15 @@
                 </c:pt>
                 <c:pt idx="234">
                   <c:v>41.332999999999998</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>41.5</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>41.5</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>41.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2614,6 +2632,15 @@
                 <c:pt idx="234">
                   <c:v>46163</c:v>
                 </c:pt>
+                <c:pt idx="235">
+                  <c:v>46164</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>46164</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>46164</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3326,6 +3353,15 @@
                   <c:v>22.5</c:v>
                 </c:pt>
                 <c:pt idx="234">
+                  <c:v>22.5</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>22.5</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>22.5</c:v>
+                </c:pt>
+                <c:pt idx="237">
                   <c:v>22.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -4078,6 +4114,15 @@
                 <c:pt idx="234">
                   <c:v>46163</c:v>
                 </c:pt>
+                <c:pt idx="235">
+                  <c:v>46164</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>46164</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>46164</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4791,6 +4836,15 @@
                 </c:pt>
                 <c:pt idx="234">
                   <c:v>60.143000000000001</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>60.856999999999999</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>60.856999999999999</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>60.856999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5542,6 +5596,15 @@
                 <c:pt idx="234">
                   <c:v>46163</c:v>
                 </c:pt>
+                <c:pt idx="235">
+                  <c:v>46164</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>46164</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>46164</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6254,6 +6317,15 @@
                   <c:v>12.35</c:v>
                 </c:pt>
                 <c:pt idx="234">
+                  <c:v>12.35</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>12.35</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>12.35</c:v>
+                </c:pt>
+                <c:pt idx="237">
                   <c:v>12.35</c:v>
                 </c:pt>
               </c:numCache>
@@ -7006,6 +7078,15 @@
                 <c:pt idx="234">
                   <c:v>46163</c:v>
                 </c:pt>
+                <c:pt idx="235">
+                  <c:v>46164</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>46164</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>46164</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7719,6 +7800,15 @@
                 </c:pt>
                 <c:pt idx="234">
                   <c:v>32.9</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>33.299999999999997</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>33.299999999999997</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>33.299999999999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8486,6 +8576,15 @@
                 <c:pt idx="234">
                   <c:v>46163</c:v>
                 </c:pt>
+                <c:pt idx="235">
+                  <c:v>46164</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>46164</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>46164</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9198,6 +9297,15 @@
                   <c:v>4.8639999999999999</c:v>
                 </c:pt>
                 <c:pt idx="234">
+                  <c:v>4.8639999999999999</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>4.8639999999999999</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>4.8639999999999999</c:v>
+                </c:pt>
+                <c:pt idx="237">
                   <c:v>4.8639999999999999</c:v>
                 </c:pt>
               </c:numCache>
@@ -9952,6 +10060,15 @@
                 <c:pt idx="234">
                   <c:v>46163</c:v>
                 </c:pt>
+                <c:pt idx="235">
+                  <c:v>46164</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>46164</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>46164</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10665,6 +10782,15 @@
                 </c:pt>
                 <c:pt idx="234">
                   <c:v>9.0879999999999992</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>9.1630000000000003</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>9.1630000000000003</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>9.1630000000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10942,7 +11068,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -11711,7 +11837,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -14297,13 +14423,13 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y237"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <dimension ref="A1:Y240"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.44140625" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.77734375" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.453125" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.81640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.36328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.453125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
@@ -32547,6 +32673,237 @@
       </c>
       <c r="Y237" s="11">
         <v>9.0879999999999992</v>
+      </c>
+    </row>
+    <row r="238" spans="1:25">
+      <c r="A238" s="12">
+        <v>46164</v>
+      </c>
+      <c r="B238" s="12">
+        <v>46164</v>
+      </c>
+      <c r="C238" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D238" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E238" s="11">
+        <v>52.5</v>
+      </c>
+      <c r="F238" s="11">
+        <v>30.5</v>
+      </c>
+      <c r="G238" s="11">
+        <v>41.5</v>
+      </c>
+      <c r="H238" s="11">
+        <v>24.8</v>
+      </c>
+      <c r="I238" s="11">
+        <v>22</v>
+      </c>
+      <c r="J238" s="11">
+        <v>22.5</v>
+      </c>
+      <c r="K238" s="11">
+        <v>70.5</v>
+      </c>
+      <c r="L238" s="11">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="M238" s="11">
+        <v>60.856999999999999</v>
+      </c>
+      <c r="N238" s="11">
+        <v>13</v>
+      </c>
+      <c r="O238" s="11">
+        <v>10.5</v>
+      </c>
+      <c r="P238" s="11">
+        <v>12.35</v>
+      </c>
+      <c r="Q238" s="11">
+        <v>53.5</v>
+      </c>
+      <c r="R238" s="11">
+        <v>16.5</v>
+      </c>
+      <c r="S238" s="11">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="T238" s="11">
+        <v>5.4</v>
+      </c>
+      <c r="U238" s="11">
+        <v>4.25</v>
+      </c>
+      <c r="V238" s="11">
+        <v>4.8639999999999999</v>
+      </c>
+      <c r="W238" s="11">
+        <v>11.5</v>
+      </c>
+      <c r="X238" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="Y238" s="11">
+        <v>9.1630000000000003</v>
+      </c>
+    </row>
+    <row r="239" spans="1:25">
+      <c r="A239" s="12">
+        <v>46164</v>
+      </c>
+      <c r="B239" s="12">
+        <v>46164</v>
+      </c>
+      <c r="C239" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D239" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E239" s="11">
+        <v>52.5</v>
+      </c>
+      <c r="F239" s="11">
+        <v>30.5</v>
+      </c>
+      <c r="G239" s="11">
+        <v>41.5</v>
+      </c>
+      <c r="H239" s="11">
+        <v>24.8</v>
+      </c>
+      <c r="I239" s="11">
+        <v>22</v>
+      </c>
+      <c r="J239" s="11">
+        <v>22.5</v>
+      </c>
+      <c r="K239" s="11">
+        <v>70.5</v>
+      </c>
+      <c r="L239" s="11">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="M239" s="11">
+        <v>60.856999999999999</v>
+      </c>
+      <c r="N239" s="11">
+        <v>13</v>
+      </c>
+      <c r="O239" s="11">
+        <v>10.5</v>
+      </c>
+      <c r="P239" s="11">
+        <v>12.35</v>
+      </c>
+      <c r="Q239" s="11">
+        <v>53.5</v>
+      </c>
+      <c r="R239" s="11">
+        <v>16.5</v>
+      </c>
+      <c r="S239" s="11">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="T239" s="11">
+        <v>5.4</v>
+      </c>
+      <c r="U239" s="11">
+        <v>4.25</v>
+      </c>
+      <c r="V239" s="11">
+        <v>4.8639999999999999</v>
+      </c>
+      <c r="W239" s="11">
+        <v>11.5</v>
+      </c>
+      <c r="X239" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="Y239" s="11">
+        <v>9.1630000000000003</v>
+      </c>
+    </row>
+    <row r="240" spans="1:25">
+      <c r="A240" s="12">
+        <v>46164</v>
+      </c>
+      <c r="B240" s="12">
+        <v>46164</v>
+      </c>
+      <c r="C240" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D240" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E240" s="11">
+        <v>52.5</v>
+      </c>
+      <c r="F240" s="11">
+        <v>30.5</v>
+      </c>
+      <c r="G240" s="11">
+        <v>41.5</v>
+      </c>
+      <c r="H240" s="11">
+        <v>24.8</v>
+      </c>
+      <c r="I240" s="11">
+        <v>22</v>
+      </c>
+      <c r="J240" s="11">
+        <v>22.5</v>
+      </c>
+      <c r="K240" s="11">
+        <v>70.5</v>
+      </c>
+      <c r="L240" s="11">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="M240" s="11">
+        <v>60.856999999999999</v>
+      </c>
+      <c r="N240" s="11">
+        <v>13</v>
+      </c>
+      <c r="O240" s="11">
+        <v>10.5</v>
+      </c>
+      <c r="P240" s="11">
+        <v>12.35</v>
+      </c>
+      <c r="Q240" s="11">
+        <v>53.5</v>
+      </c>
+      <c r="R240" s="11">
+        <v>16.5</v>
+      </c>
+      <c r="S240" s="11">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="T240" s="11">
+        <v>5.4</v>
+      </c>
+      <c r="U240" s="11">
+        <v>4.25</v>
+      </c>
+      <c r="V240" s="11">
+        <v>4.8639999999999999</v>
+      </c>
+      <c r="W240" s="11">
+        <v>11.5</v>
+      </c>
+      <c r="X240" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="Y240" s="11">
+        <v>9.1630000000000003</v>
       </c>
     </row>
   </sheetData>
@@ -32566,14 +32923,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:AK7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.453125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.36328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.453125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="9" style="11"/>
-    <col min="8" max="10" width="9.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
@@ -33128,19 +33485,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:Y20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.109375" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.453125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.453125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="14"/>
-    <col min="7" max="7" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.44140625" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.453125" style="14" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="14"/>
-    <col min="10" max="10" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.453125" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="9" style="14"/>
-    <col min="13" max="13" width="13.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.36328125" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
@@ -34046,13 +34403,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:Y20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.453125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.453125" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.453125" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
@@ -34787,7 +35144,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="16384" width="9" style="3"/>
   </cols>
@@ -34802,11 +35159,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="22.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.77734375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="22.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.81640625" style="3" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A4FF8A0-C238-4486-A032-4CD60625574E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B062D4C4-EB52-4C12-912A-D6DDFABDB238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -374,8 +374,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -393,7 +393,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1168,6 +1168,15 @@
                 <c:pt idx="240">
                   <c:v>46167</c:v>
                 </c:pt>
+                <c:pt idx="241">
+                  <c:v>46168</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>46168</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>46168</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1899,6 +1908,12 @@
                 </c:pt>
                 <c:pt idx="240">
                   <c:v>41.667000000000002</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>41.832999999999998</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>41.832999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2668,6 +2683,15 @@
                 <c:pt idx="240">
                   <c:v>46167</c:v>
                 </c:pt>
+                <c:pt idx="241">
+                  <c:v>46168</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>46168</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>46168</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3398,6 +3422,12 @@
                   <c:v>22.5</c:v>
                 </c:pt>
                 <c:pt idx="240">
+                  <c:v>22.5</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>22.5</c:v>
+                </c:pt>
+                <c:pt idx="242">
                   <c:v>22.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -4168,6 +4198,15 @@
                 <c:pt idx="240">
                   <c:v>46167</c:v>
                 </c:pt>
+                <c:pt idx="241">
+                  <c:v>46168</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>46168</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>46168</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4899,6 +4938,12 @@
                 </c:pt>
                 <c:pt idx="240">
                   <c:v>61.094999999999999</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>61.143000000000001</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>61.143000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5668,6 +5713,15 @@
                 <c:pt idx="240">
                   <c:v>46167</c:v>
                 </c:pt>
+                <c:pt idx="241">
+                  <c:v>46168</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>46168</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>46168</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6398,6 +6452,12 @@
                   <c:v>12.35</c:v>
                 </c:pt>
                 <c:pt idx="240">
+                  <c:v>12.35</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>12.35</c:v>
+                </c:pt>
+                <c:pt idx="242">
                   <c:v>12.35</c:v>
                 </c:pt>
               </c:numCache>
@@ -7168,6 +7228,15 @@
                 <c:pt idx="240">
                   <c:v>46167</c:v>
                 </c:pt>
+                <c:pt idx="241">
+                  <c:v>46168</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>46168</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>46168</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7899,6 +7968,12 @@
                 </c:pt>
                 <c:pt idx="240">
                   <c:v>33.5</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>33.6</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>33.6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8684,6 +8759,15 @@
                 <c:pt idx="240">
                   <c:v>46167</c:v>
                 </c:pt>
+                <c:pt idx="241">
+                  <c:v>46168</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>46168</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>46168</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9414,6 +9498,12 @@
                   <c:v>4.8639999999999999</c:v>
                 </c:pt>
                 <c:pt idx="240">
+                  <c:v>4.8639999999999999</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>4.8639999999999999</c:v>
+                </c:pt>
+                <c:pt idx="242">
                   <c:v>4.8639999999999999</c:v>
                 </c:pt>
               </c:numCache>
@@ -10186,6 +10276,15 @@
                 <c:pt idx="240">
                   <c:v>46167</c:v>
                 </c:pt>
+                <c:pt idx="241">
+                  <c:v>46168</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>46168</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>46168</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10917,6 +11016,12 @@
                 </c:pt>
                 <c:pt idx="240">
                   <c:v>9.1630000000000003</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>9.2129999999999992</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>9.2129999999999992</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11055,6 +11160,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10"/>
+          <c:min val="4"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="r"/>
@@ -11194,7 +11300,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -11981,7 +12087,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -14579,13 +14685,13 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y243"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:Y246"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.453125" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.81640625" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.36328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.453125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.44140625" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.77734375" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.77734375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
@@ -33291,6 +33397,174 @@
       </c>
       <c r="Y243" s="11">
         <v>9.1630000000000003</v>
+      </c>
+    </row>
+    <row r="244" spans="1:25">
+      <c r="A244" s="12">
+        <v>46168</v>
+      </c>
+      <c r="B244" s="12">
+        <v>46168</v>
+      </c>
+      <c r="C244" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D244" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E244" s="11">
+        <v>52.5</v>
+      </c>
+      <c r="F244" s="11">
+        <v>30.5</v>
+      </c>
+      <c r="G244" s="11">
+        <v>41.832999999999998</v>
+      </c>
+      <c r="H244" s="11">
+        <v>24.8</v>
+      </c>
+      <c r="I244" s="11">
+        <v>22</v>
+      </c>
+      <c r="J244" s="11">
+        <v>22.5</v>
+      </c>
+      <c r="K244" s="11">
+        <v>71</v>
+      </c>
+      <c r="L244" s="11">
+        <v>34</v>
+      </c>
+      <c r="M244" s="11">
+        <v>61.143000000000001</v>
+      </c>
+      <c r="N244" s="11">
+        <v>12.8</v>
+      </c>
+      <c r="O244" s="11">
+        <v>10.3</v>
+      </c>
+      <c r="P244" s="11">
+        <v>12.35</v>
+      </c>
+      <c r="Q244" s="11">
+        <v>53</v>
+      </c>
+      <c r="R244" s="11">
+        <v>16.7</v>
+      </c>
+      <c r="S244" s="11">
+        <v>33.6</v>
+      </c>
+      <c r="T244" s="11">
+        <v>5.4</v>
+      </c>
+      <c r="U244" s="11">
+        <v>4.25</v>
+      </c>
+      <c r="V244" s="11">
+        <v>4.8639999999999999</v>
+      </c>
+      <c r="W244" s="11">
+        <v>11.6</v>
+      </c>
+      <c r="X244" s="11">
+        <v>5.55</v>
+      </c>
+      <c r="Y244" s="11">
+        <v>9.2129999999999992</v>
+      </c>
+    </row>
+    <row r="245" spans="1:25">
+      <c r="A245" s="12">
+        <v>46168</v>
+      </c>
+      <c r="B245" s="12">
+        <v>46168</v>
+      </c>
+      <c r="C245" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D245" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E245" s="11">
+        <v>52.5</v>
+      </c>
+      <c r="F245" s="11">
+        <v>30.5</v>
+      </c>
+      <c r="G245" s="11">
+        <v>41.832999999999998</v>
+      </c>
+      <c r="H245" s="11">
+        <v>24.8</v>
+      </c>
+      <c r="I245" s="11">
+        <v>22</v>
+      </c>
+      <c r="J245" s="11">
+        <v>22.5</v>
+      </c>
+      <c r="K245" s="11">
+        <v>71</v>
+      </c>
+      <c r="L245" s="11">
+        <v>34</v>
+      </c>
+      <c r="M245" s="11">
+        <v>61.143000000000001</v>
+      </c>
+      <c r="N245" s="11">
+        <v>12.8</v>
+      </c>
+      <c r="O245" s="11">
+        <v>10.3</v>
+      </c>
+      <c r="P245" s="11">
+        <v>12.35</v>
+      </c>
+      <c r="Q245" s="11">
+        <v>53</v>
+      </c>
+      <c r="R245" s="11">
+        <v>16.7</v>
+      </c>
+      <c r="S245" s="11">
+        <v>33.6</v>
+      </c>
+      <c r="T245" s="11">
+        <v>5.4</v>
+      </c>
+      <c r="U245" s="11">
+        <v>4.25</v>
+      </c>
+      <c r="V245" s="11">
+        <v>4.8639999999999999</v>
+      </c>
+      <c r="W245" s="11">
+        <v>11.6</v>
+      </c>
+      <c r="X245" s="11">
+        <v>5.55</v>
+      </c>
+      <c r="Y245" s="11">
+        <v>9.2129999999999992</v>
+      </c>
+    </row>
+    <row r="246" spans="1:25">
+      <c r="A246" s="12">
+        <v>46168</v>
+      </c>
+      <c r="B246" s="12">
+        <v>46168</v>
+      </c>
+      <c r="C246" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D246" s="7" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -33310,14 +33584,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:AK7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="11.453125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.36328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.453125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="9" style="11"/>
-    <col min="8" max="10" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.5546875" style="11" customWidth="1"/>
+    <col min="9" max="9" width="9.77734375" style="11" customWidth="1"/>
+    <col min="10" max="10" width="10.33203125" style="11" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
@@ -33872,19 +34148,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:Y21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.453125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.453125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="14"/>
-    <col min="7" max="7" width="9.453125" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.453125" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.44140625" style="14" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="14"/>
-    <col min="10" max="10" width="11" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.88671875" style="11" customWidth="1"/>
     <col min="11" max="12" width="9" style="14"/>
-    <col min="13" max="13" width="13.36328125" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.33203125" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
@@ -34831,13 +35107,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:Y21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.453125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.453125" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
@@ -35604,7 +35880,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="16384" width="9" style="3"/>
   </cols>
@@ -35619,11 +35895,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="22.81640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.81640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.81640625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="22.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.77734375" style="3" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B062D4C4-EB52-4C12-912A-D6DDFABDB238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E01904A9-9E1D-4EE3-9ED6-F2A8EEA4AD3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -1177,6 +1177,15 @@
                 <c:pt idx="243">
                   <c:v>46168</c:v>
                 </c:pt>
+                <c:pt idx="244">
+                  <c:v>46169</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>46169</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>46169</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1914,6 +1923,15 @@
                 </c:pt>
                 <c:pt idx="242">
                   <c:v>41.832999999999998</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>41.667000000000002</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>41.667000000000002</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>41.667000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2692,6 +2710,15 @@
                 <c:pt idx="243">
                   <c:v>46168</c:v>
                 </c:pt>
+                <c:pt idx="244">
+                  <c:v>46169</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>46169</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>46169</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3428,6 +3455,15 @@
                   <c:v>22.5</c:v>
                 </c:pt>
                 <c:pt idx="242">
+                  <c:v>22.5</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>22.5</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>22.5</c:v>
+                </c:pt>
+                <c:pt idx="245">
                   <c:v>22.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -4207,6 +4243,15 @@
                 <c:pt idx="243">
                   <c:v>46168</c:v>
                 </c:pt>
+                <c:pt idx="244">
+                  <c:v>46169</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>46169</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>46169</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4944,6 +4989,15 @@
                 </c:pt>
                 <c:pt idx="242">
                   <c:v>61.143000000000001</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>61.143000000000001</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>61.143000000000001</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>61.332999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5722,6 +5776,15 @@
                 <c:pt idx="243">
                   <c:v>46168</c:v>
                 </c:pt>
+                <c:pt idx="244">
+                  <c:v>46169</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>46169</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>46169</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6458,6 +6521,15 @@
                   <c:v>12.35</c:v>
                 </c:pt>
                 <c:pt idx="242">
+                  <c:v>12.35</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>12.35</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>12.35</c:v>
+                </c:pt>
+                <c:pt idx="245">
                   <c:v>12.35</c:v>
                 </c:pt>
               </c:numCache>
@@ -7237,6 +7309,15 @@
                 <c:pt idx="243">
                   <c:v>46168</c:v>
                 </c:pt>
+                <c:pt idx="244">
+                  <c:v>46169</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>46169</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>46169</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7973,6 +8054,15 @@
                   <c:v>33.6</c:v>
                 </c:pt>
                 <c:pt idx="242">
+                  <c:v>33.6</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>33.6</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>33.6</c:v>
+                </c:pt>
+                <c:pt idx="245">
                   <c:v>33.6</c:v>
                 </c:pt>
               </c:numCache>
@@ -8768,6 +8858,15 @@
                 <c:pt idx="243">
                   <c:v>46168</c:v>
                 </c:pt>
+                <c:pt idx="244">
+                  <c:v>46169</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>46169</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>46169</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9505,6 +9604,15 @@
                 </c:pt>
                 <c:pt idx="242">
                   <c:v>4.8639999999999999</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>4.8639999999999999</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>4.8540000000000001</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>4.8540000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10285,6 +10393,15 @@
                 <c:pt idx="243">
                   <c:v>46168</c:v>
                 </c:pt>
+                <c:pt idx="244">
+                  <c:v>46169</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>46169</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>46169</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -11021,6 +11138,15 @@
                   <c:v>9.2129999999999992</c:v>
                 </c:pt>
                 <c:pt idx="242">
+                  <c:v>9.2129999999999992</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>9.2129999999999992</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>9.2129999999999992</c:v>
+                </c:pt>
+                <c:pt idx="245">
                   <c:v>9.2129999999999992</c:v>
                 </c:pt>
               </c:numCache>
@@ -11054,7 +11180,7 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="yyyy/mm/dd;@" sourceLinked="0"/>
+        <c:numFmt formatCode="yyyy\-mm\-dd;@" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -14685,7 +14811,7 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y246"/>
+  <dimension ref="A1:Y249"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="12.44140625" style="12" bestFit="1" customWidth="1"/>
@@ -33564,6 +33690,237 @@
         <v>0.75694444444444453</v>
       </c>
       <c r="D246" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E246" s="11">
+        <v>52.5</v>
+      </c>
+      <c r="F246" s="11">
+        <v>30.5</v>
+      </c>
+      <c r="G246" s="11">
+        <v>41.667000000000002</v>
+      </c>
+      <c r="H246" s="11">
+        <v>24.8</v>
+      </c>
+      <c r="I246" s="11">
+        <v>22</v>
+      </c>
+      <c r="J246" s="11">
+        <v>22.5</v>
+      </c>
+      <c r="K246" s="11">
+        <v>71</v>
+      </c>
+      <c r="L246" s="11">
+        <v>34</v>
+      </c>
+      <c r="M246" s="11">
+        <v>61.143000000000001</v>
+      </c>
+      <c r="N246" s="11">
+        <v>12.8</v>
+      </c>
+      <c r="O246" s="11">
+        <v>10.3</v>
+      </c>
+      <c r="P246" s="11">
+        <v>12.35</v>
+      </c>
+      <c r="Q246" s="11">
+        <v>53</v>
+      </c>
+      <c r="R246" s="11">
+        <v>16.7</v>
+      </c>
+      <c r="S246" s="11">
+        <v>33.6</v>
+      </c>
+      <c r="T246" s="11">
+        <v>5.4</v>
+      </c>
+      <c r="U246" s="11">
+        <v>4.25</v>
+      </c>
+      <c r="V246" s="11">
+        <v>4.8639999999999999</v>
+      </c>
+      <c r="W246" s="11">
+        <v>11.6</v>
+      </c>
+      <c r="X246" s="11">
+        <v>5.55</v>
+      </c>
+      <c r="Y246" s="11">
+        <v>9.2129999999999992</v>
+      </c>
+    </row>
+    <row r="247" spans="1:25">
+      <c r="A247" s="12">
+        <v>46169</v>
+      </c>
+      <c r="B247" s="12">
+        <v>46169</v>
+      </c>
+      <c r="C247" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D247" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E247" s="11">
+        <v>52.5</v>
+      </c>
+      <c r="F247" s="11">
+        <v>30.5</v>
+      </c>
+      <c r="G247" s="11">
+        <v>41.667000000000002</v>
+      </c>
+      <c r="H247" s="11">
+        <v>24.8</v>
+      </c>
+      <c r="I247" s="11">
+        <v>22</v>
+      </c>
+      <c r="J247" s="11">
+        <v>22.5</v>
+      </c>
+      <c r="K247" s="11">
+        <v>71</v>
+      </c>
+      <c r="L247" s="11">
+        <v>34</v>
+      </c>
+      <c r="M247" s="11">
+        <v>61.143000000000001</v>
+      </c>
+      <c r="N247" s="11">
+        <v>12.8</v>
+      </c>
+      <c r="O247" s="11">
+        <v>10.3</v>
+      </c>
+      <c r="P247" s="11">
+        <v>12.35</v>
+      </c>
+      <c r="Q247" s="11">
+        <v>53</v>
+      </c>
+      <c r="R247" s="11">
+        <v>16.7</v>
+      </c>
+      <c r="S247" s="11">
+        <v>33.6</v>
+      </c>
+      <c r="T247" s="11">
+        <v>5.4</v>
+      </c>
+      <c r="U247" s="11">
+        <v>4.25</v>
+      </c>
+      <c r="V247" s="11">
+        <v>4.8540000000000001</v>
+      </c>
+      <c r="W247" s="11">
+        <v>11.6</v>
+      </c>
+      <c r="X247" s="11">
+        <v>5.55</v>
+      </c>
+      <c r="Y247" s="11">
+        <v>9.2129999999999992</v>
+      </c>
+    </row>
+    <row r="248" spans="1:25">
+      <c r="A248" s="12">
+        <v>46169</v>
+      </c>
+      <c r="B248" s="12">
+        <v>46169</v>
+      </c>
+      <c r="C248" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D248" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E248" s="11">
+        <v>52.5</v>
+      </c>
+      <c r="F248" s="11">
+        <v>30.5</v>
+      </c>
+      <c r="G248" s="11">
+        <v>41.667000000000002</v>
+      </c>
+      <c r="H248" s="11">
+        <v>24.8</v>
+      </c>
+      <c r="I248" s="11">
+        <v>22</v>
+      </c>
+      <c r="J248" s="11">
+        <v>22.5</v>
+      </c>
+      <c r="K248" s="11">
+        <v>71</v>
+      </c>
+      <c r="L248" s="11">
+        <v>34</v>
+      </c>
+      <c r="M248" s="11">
+        <v>61.332999999999998</v>
+      </c>
+      <c r="N248" s="11">
+        <v>12.8</v>
+      </c>
+      <c r="O248" s="11">
+        <v>10.3</v>
+      </c>
+      <c r="P248" s="11">
+        <v>12.35</v>
+      </c>
+      <c r="Q248" s="11">
+        <v>53</v>
+      </c>
+      <c r="R248" s="11">
+        <v>16.7</v>
+      </c>
+      <c r="S248" s="11">
+        <v>33.6</v>
+      </c>
+      <c r="T248" s="11">
+        <v>5.4</v>
+      </c>
+      <c r="U248" s="11">
+        <v>4.25</v>
+      </c>
+      <c r="V248" s="11">
+        <v>4.8540000000000001</v>
+      </c>
+      <c r="W248" s="11">
+        <v>11.6</v>
+      </c>
+      <c r="X248" s="11">
+        <v>5.55</v>
+      </c>
+      <c r="Y248" s="11">
+        <v>9.2129999999999992</v>
+      </c>
+    </row>
+    <row r="249" spans="1:25">
+      <c r="A249" s="12">
+        <v>46169</v>
+      </c>
+      <c r="B249" s="12">
+        <v>46169</v>
+      </c>
+      <c r="C249" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D249" s="7" t="s">
         <v>53</v>
       </c>
     </row>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E557854-AB59-4A68-8E45-8126786DD45E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77ACEAC1-6464-4634-8971-723C4B32F37D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -374,8 +374,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -393,7 +393,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1195,6 +1195,15 @@
                 <c:pt idx="249">
                   <c:v>46170</c:v>
                 </c:pt>
+                <c:pt idx="250">
+                  <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>46171</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1953,6 +1962,12 @@
                 </c:pt>
                 <c:pt idx="249">
                   <c:v>41.832999999999998</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>41.832999999999998</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>41.9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2749,6 +2764,15 @@
                 <c:pt idx="249">
                   <c:v>46170</c:v>
                 </c:pt>
+                <c:pt idx="250">
+                  <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>46171</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3506,6 +3530,12 @@
                   <c:v>22.5</c:v>
                 </c:pt>
                 <c:pt idx="249">
+                  <c:v>22.5</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>22.5</c:v>
+                </c:pt>
+                <c:pt idx="251">
                   <c:v>22.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -4303,6 +4333,15 @@
                 <c:pt idx="249">
                   <c:v>46170</c:v>
                 </c:pt>
+                <c:pt idx="250">
+                  <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>46171</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5061,6 +5100,12 @@
                 </c:pt>
                 <c:pt idx="249">
                   <c:v>61.594999999999999</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>61.951999999999998</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>61.951999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5857,6 +5902,15 @@
                 <c:pt idx="249">
                   <c:v>46170</c:v>
                 </c:pt>
+                <c:pt idx="250">
+                  <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>46171</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6615,6 +6669,12 @@
                 </c:pt>
                 <c:pt idx="249">
                   <c:v>12.324999999999999</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>12.275</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>12.275</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7411,6 +7471,15 @@
                 <c:pt idx="249">
                   <c:v>46170</c:v>
                 </c:pt>
+                <c:pt idx="250">
+                  <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>46171</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8169,6 +8238,12 @@
                 </c:pt>
                 <c:pt idx="249">
                   <c:v>33.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>34.1</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>34.1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8981,6 +9056,15 @@
                 <c:pt idx="249">
                   <c:v>46170</c:v>
                 </c:pt>
+                <c:pt idx="250">
+                  <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>46171</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9739,6 +9823,12 @@
                 </c:pt>
                 <c:pt idx="249">
                   <c:v>4.8540000000000001</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>4.8609999999999998</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>4.8609999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10537,6 +10627,15 @@
                 <c:pt idx="249">
                   <c:v>46170</c:v>
                 </c:pt>
+                <c:pt idx="250">
+                  <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>46171</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -11295,6 +11394,12 @@
                 </c:pt>
                 <c:pt idx="249">
                   <c:v>9.2750000000000004</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>9.4</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>9.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11573,7 +11678,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -12360,7 +12465,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -14958,14 +15063,16 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y252"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:Y255"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.453125" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.81640625" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.81640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.453125" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="25" width="9" style="11"/>
+    <col min="1" max="1" width="12.44140625" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.77734375" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.77734375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="13" width="9" style="11"/>
+    <col min="14" max="14" width="9.5546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="15" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -34363,6 +34470,174 @@
       </c>
       <c r="Y252" s="11">
         <v>9.2750000000000004</v>
+      </c>
+    </row>
+    <row r="253" spans="1:25">
+      <c r="A253" s="12">
+        <v>46171</v>
+      </c>
+      <c r="B253" s="12">
+        <v>46171</v>
+      </c>
+      <c r="C253" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D253" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E253" s="11">
+        <v>52.6</v>
+      </c>
+      <c r="F253" s="11">
+        <v>30</v>
+      </c>
+      <c r="G253" s="11">
+        <v>41.832999999999998</v>
+      </c>
+      <c r="H253" s="11">
+        <v>24.7</v>
+      </c>
+      <c r="I253" s="11">
+        <v>22</v>
+      </c>
+      <c r="J253" s="11">
+        <v>22.5</v>
+      </c>
+      <c r="K253" s="11">
+        <v>71.2</v>
+      </c>
+      <c r="L253" s="11">
+        <v>34</v>
+      </c>
+      <c r="M253" s="11">
+        <v>61.951999999999998</v>
+      </c>
+      <c r="N253" s="11">
+        <v>12.7</v>
+      </c>
+      <c r="O253" s="11">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="P253" s="11">
+        <v>12.275</v>
+      </c>
+      <c r="Q253" s="11">
+        <v>53</v>
+      </c>
+      <c r="R253" s="11">
+        <v>16.8</v>
+      </c>
+      <c r="S253" s="11">
+        <v>34.1</v>
+      </c>
+      <c r="T253" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="U253" s="11">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="V253" s="11">
+        <v>4.8609999999999998</v>
+      </c>
+      <c r="W253" s="11">
+        <v>12</v>
+      </c>
+      <c r="X253" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="Y253" s="11">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="254" spans="1:25">
+      <c r="A254" s="12">
+        <v>46171</v>
+      </c>
+      <c r="B254" s="12">
+        <v>46171</v>
+      </c>
+      <c r="C254" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D254" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E254" s="11">
+        <v>52.6</v>
+      </c>
+      <c r="F254" s="11">
+        <v>30</v>
+      </c>
+      <c r="G254" s="11">
+        <v>41.9</v>
+      </c>
+      <c r="H254" s="11">
+        <v>24.7</v>
+      </c>
+      <c r="I254" s="11">
+        <v>22</v>
+      </c>
+      <c r="J254" s="11">
+        <v>22.5</v>
+      </c>
+      <c r="K254" s="11">
+        <v>71.2</v>
+      </c>
+      <c r="L254" s="11">
+        <v>34</v>
+      </c>
+      <c r="M254" s="11">
+        <v>61.951999999999998</v>
+      </c>
+      <c r="N254" s="11">
+        <v>12.7</v>
+      </c>
+      <c r="O254" s="11">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="P254" s="11">
+        <v>12.275</v>
+      </c>
+      <c r="Q254" s="11">
+        <v>53</v>
+      </c>
+      <c r="R254" s="11">
+        <v>16.8</v>
+      </c>
+      <c r="S254" s="11">
+        <v>34.1</v>
+      </c>
+      <c r="T254" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="U254" s="11">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="V254" s="11">
+        <v>4.8609999999999998</v>
+      </c>
+      <c r="W254" s="11">
+        <v>12</v>
+      </c>
+      <c r="X254" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="Y254" s="11">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="255" spans="1:25">
+      <c r="A255" s="12">
+        <v>46171</v>
+      </c>
+      <c r="B255" s="12">
+        <v>46171</v>
+      </c>
+      <c r="C255" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D255" s="7" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -34382,16 +34657,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:AK7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="11.453125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.36328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.453125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="9" style="11"/>
-    <col min="8" max="8" width="9.54296875" style="11" customWidth="1"/>
-    <col min="9" max="9" width="9.81640625" style="11" customWidth="1"/>
-    <col min="10" max="10" width="10.36328125" style="11" customWidth="1"/>
+    <col min="8" max="8" width="9.5546875" style="11" customWidth="1"/>
+    <col min="9" max="9" width="9.77734375" style="11" customWidth="1"/>
+    <col min="10" max="10" width="10.33203125" style="11" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
@@ -34946,19 +35221,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:Y21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.54296875" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.453125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.453125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="14"/>
-    <col min="7" max="7" width="9.453125" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.453125" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.44140625" style="14" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="14"/>
-    <col min="10" max="10" width="11.90625" style="11" customWidth="1"/>
+    <col min="10" max="10" width="11.88671875" style="11" customWidth="1"/>
     <col min="11" max="12" width="9" style="14"/>
-    <col min="13" max="13" width="13.36328125" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.33203125" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
@@ -35905,13 +36180,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:Y21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.54296875" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.453125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.453125" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
@@ -36678,7 +36953,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="16384" width="9" style="3"/>
   </cols>
@@ -36693,11 +36968,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="22.81640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.81640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.81640625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="22.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.77734375" style="3" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77ACEAC1-6464-4634-8971-723C4B32F37D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFF45D7A-BCE4-4109-91BC-8BEA83DED490}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9910" yWindow="0" windowWidth="13220" windowHeight="14730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -374,8 +374,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -393,7 +393,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1969,6 +1969,9 @@
                 <c:pt idx="251">
                   <c:v>41.9</c:v>
                 </c:pt>
+                <c:pt idx="252">
+                  <c:v>41.9</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3538,6 +3541,9 @@
                 <c:pt idx="251">
                   <c:v>22.5</c:v>
                 </c:pt>
+                <c:pt idx="252">
+                  <c:v>22.5</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -5107,6 +5113,9 @@
                 <c:pt idx="251">
                   <c:v>61.951999999999998</c:v>
                 </c:pt>
+                <c:pt idx="252">
+                  <c:v>61.951999999999998</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -6676,6 +6685,9 @@
                 <c:pt idx="251">
                   <c:v>12.275</c:v>
                 </c:pt>
+                <c:pt idx="252">
+                  <c:v>12.275</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -8243,6 +8255,9 @@
                   <c:v>34.1</c:v>
                 </c:pt>
                 <c:pt idx="251">
+                  <c:v>34.1</c:v>
+                </c:pt>
+                <c:pt idx="252">
                   <c:v>34.1</c:v>
                 </c:pt>
               </c:numCache>
@@ -9830,6 +9845,9 @@
                 <c:pt idx="251">
                   <c:v>4.8609999999999998</c:v>
                 </c:pt>
+                <c:pt idx="252">
+                  <c:v>4.8609999999999998</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -11399,6 +11417,9 @@
                   <c:v>9.4</c:v>
                 </c:pt>
                 <c:pt idx="251">
+                  <c:v>9.4</c:v>
+                </c:pt>
+                <c:pt idx="252">
                   <c:v>9.4</c:v>
                 </c:pt>
               </c:numCache>
@@ -11678,7 +11699,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -12465,7 +12486,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -15064,14 +15085,14 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:Y255"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.44140625" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.77734375" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.77734375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.453125" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.81640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.81640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.453125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="13" width="9" style="11"/>
-    <col min="14" max="14" width="9.5546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.54296875" style="11" bestFit="1" customWidth="1"/>
     <col min="15" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
@@ -34638,6 +34659,69 @@
       </c>
       <c r="D255" s="7" t="s">
         <v>53</v>
+      </c>
+      <c r="E255" s="11">
+        <v>52.6</v>
+      </c>
+      <c r="F255" s="11">
+        <v>30</v>
+      </c>
+      <c r="G255" s="11">
+        <v>41.9</v>
+      </c>
+      <c r="H255" s="11">
+        <v>24.7</v>
+      </c>
+      <c r="I255" s="11">
+        <v>22</v>
+      </c>
+      <c r="J255" s="11">
+        <v>22.5</v>
+      </c>
+      <c r="K255" s="11">
+        <v>71.2</v>
+      </c>
+      <c r="L255" s="11">
+        <v>34</v>
+      </c>
+      <c r="M255" s="11">
+        <v>61.951999999999998</v>
+      </c>
+      <c r="N255" s="11">
+        <v>12.7</v>
+      </c>
+      <c r="O255" s="11">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="P255" s="11">
+        <v>12.275</v>
+      </c>
+      <c r="Q255" s="11">
+        <v>53</v>
+      </c>
+      <c r="R255" s="11">
+        <v>16.8</v>
+      </c>
+      <c r="S255" s="11">
+        <v>34.1</v>
+      </c>
+      <c r="T255" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="U255" s="11">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="V255" s="11">
+        <v>4.8609999999999998</v>
+      </c>
+      <c r="W255" s="11">
+        <v>12</v>
+      </c>
+      <c r="X255" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="Y255" s="11">
+        <v>9.4</v>
       </c>
     </row>
   </sheetData>
@@ -34657,16 +34741,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:AK7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.453125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.36328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.453125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="9" style="11"/>
-    <col min="8" max="8" width="9.5546875" style="11" customWidth="1"/>
-    <col min="9" max="9" width="9.77734375" style="11" customWidth="1"/>
-    <col min="10" max="10" width="10.33203125" style="11" customWidth="1"/>
+    <col min="8" max="8" width="9.54296875" style="11" customWidth="1"/>
+    <col min="9" max="9" width="9.81640625" style="11" customWidth="1"/>
+    <col min="10" max="10" width="10.36328125" style="11" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
@@ -35221,19 +35305,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:Y21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.54296875" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.453125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.453125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="14"/>
-    <col min="7" max="7" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.44140625" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.453125" style="14" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="14"/>
-    <col min="10" max="10" width="11.88671875" style="11" customWidth="1"/>
+    <col min="10" max="10" width="11.90625" style="11" customWidth="1"/>
     <col min="11" max="12" width="9" style="14"/>
-    <col min="13" max="13" width="13.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.36328125" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
@@ -36180,13 +36264,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:Y21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.54296875" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.453125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.453125" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.453125" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
@@ -36953,7 +37037,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="16384" width="9" style="3"/>
   </cols>
@@ -36968,11 +37052,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="22.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.77734375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="22.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.81640625" style="3" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3E6D472-43DF-46A5-B793-C6C98A7859E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05A3C9D0-9DFA-4393-91D0-C060D5B677FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,26 +20,17 @@
     <sheet name="fig" sheetId="6" r:id="rId5"/>
     <sheet name="info" sheetId="1" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -1237,6 +1228,15 @@
                 <c:pt idx="264">
                   <c:v>46177</c:v>
                 </c:pt>
+                <c:pt idx="265">
+                  <c:v>46178</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>46178</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>46178</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2037,6 +2037,15 @@
                 </c:pt>
                 <c:pt idx="263">
                   <c:v>43.232999999999997</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>43.232999999999997</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>43.4</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>43.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2878,6 +2887,15 @@
                 <c:pt idx="264">
                   <c:v>46177</c:v>
                 </c:pt>
+                <c:pt idx="265">
+                  <c:v>46178</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>46178</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>46178</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3678,6 +3696,15 @@
                 </c:pt>
                 <c:pt idx="263">
                   <c:v>22.65</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>22.65</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>22.7</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>22.7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4519,6 +4546,15 @@
                 <c:pt idx="264">
                   <c:v>46177</c:v>
                 </c:pt>
+                <c:pt idx="265">
+                  <c:v>46178</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>46178</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>46178</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5319,6 +5355,15 @@
                 </c:pt>
                 <c:pt idx="263">
                   <c:v>63.75</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>63.75</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>64</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6160,6 +6205,15 @@
                 <c:pt idx="264">
                   <c:v>46177</c:v>
                 </c:pt>
+                <c:pt idx="265">
+                  <c:v>46178</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>46178</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>46178</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6959,6 +7013,15 @@
                   <c:v>12.3</c:v>
                 </c:pt>
                 <c:pt idx="263">
+                  <c:v>12.3</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>12.3</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>12.3</c:v>
+                </c:pt>
+                <c:pt idx="266">
                   <c:v>12.3</c:v>
                 </c:pt>
               </c:numCache>
@@ -7801,6 +7864,15 @@
                 <c:pt idx="264">
                   <c:v>46177</c:v>
                 </c:pt>
+                <c:pt idx="265">
+                  <c:v>46178</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>46178</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>46178</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8601,6 +8673,15 @@
                 </c:pt>
                 <c:pt idx="263">
                   <c:v>35.42</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>35.42</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>35.5</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>35.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9458,6 +9539,15 @@
                 <c:pt idx="264">
                   <c:v>46177</c:v>
                 </c:pt>
+                <c:pt idx="265">
+                  <c:v>46178</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>46178</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>46178</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10258,6 +10348,15 @@
                 </c:pt>
                 <c:pt idx="263">
                   <c:v>4.8250000000000002</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>4.8250000000000002</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>4.7930000000000001</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>4.7930000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11101,6 +11200,15 @@
                 <c:pt idx="264">
                   <c:v>46177</c:v>
                 </c:pt>
+                <c:pt idx="265">
+                  <c:v>46178</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>46178</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>46178</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -11901,6 +12009,15 @@
                 </c:pt>
                 <c:pt idx="263">
                   <c:v>9.9</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>9.9</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>10.025</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>10.025</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12038,7 +12155,7 @@
         <c:axId val="1583758912"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="10"/>
+          <c:max val="12"/>
           <c:min val="4"/>
         </c:scaling>
         <c:delete val="0"/>
@@ -15594,7 +15711,7 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y267"/>
+  <dimension ref="A1:Y270"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="12.44140625" style="11" bestFit="1" customWidth="1"/>
@@ -36092,6 +36209,237 @@
         <v>0.75694444444444453</v>
       </c>
       <c r="D267" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E267" s="10">
+        <v>54</v>
+      </c>
+      <c r="F267" s="10">
+        <v>30.5</v>
+      </c>
+      <c r="G267" s="10">
+        <v>43.232999999999997</v>
+      </c>
+      <c r="H267" s="10">
+        <v>25</v>
+      </c>
+      <c r="I267" s="10">
+        <v>21.8</v>
+      </c>
+      <c r="J267" s="10">
+        <v>22.65</v>
+      </c>
+      <c r="K267" s="10">
+        <v>75</v>
+      </c>
+      <c r="L267" s="10">
+        <v>34.5</v>
+      </c>
+      <c r="M267" s="10">
+        <v>63.75</v>
+      </c>
+      <c r="N267" s="10">
+        <v>12.5</v>
+      </c>
+      <c r="O267" s="10">
+        <v>10.6</v>
+      </c>
+      <c r="P267" s="10">
+        <v>12.3</v>
+      </c>
+      <c r="Q267" s="10">
+        <v>54</v>
+      </c>
+      <c r="R267" s="10">
+        <v>17</v>
+      </c>
+      <c r="S267" s="10">
+        <v>35.42</v>
+      </c>
+      <c r="T267" s="10">
+        <v>5.5</v>
+      </c>
+      <c r="U267" s="10">
+        <v>4.2</v>
+      </c>
+      <c r="V267" s="10">
+        <v>4.8250000000000002</v>
+      </c>
+      <c r="W267" s="10">
+        <v>13.5</v>
+      </c>
+      <c r="X267" s="10">
+        <v>5.55</v>
+      </c>
+      <c r="Y267" s="10">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="268" spans="1:25">
+      <c r="A268" s="11">
+        <v>46178</v>
+      </c>
+      <c r="B268" s="11">
+        <v>46178</v>
+      </c>
+      <c r="C268" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D268" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E268" s="10">
+        <v>54</v>
+      </c>
+      <c r="F268" s="10">
+        <v>30.5</v>
+      </c>
+      <c r="G268" s="10">
+        <v>43.4</v>
+      </c>
+      <c r="H268" s="10">
+        <v>25</v>
+      </c>
+      <c r="I268" s="10">
+        <v>21.8</v>
+      </c>
+      <c r="J268" s="10">
+        <v>22.7</v>
+      </c>
+      <c r="K268" s="10">
+        <v>75</v>
+      </c>
+      <c r="L268" s="10">
+        <v>34.5</v>
+      </c>
+      <c r="M268" s="10">
+        <v>64</v>
+      </c>
+      <c r="N268" s="10">
+        <v>12.5</v>
+      </c>
+      <c r="O268" s="10">
+        <v>10.6</v>
+      </c>
+      <c r="P268" s="10">
+        <v>12.3</v>
+      </c>
+      <c r="Q268" s="10">
+        <v>54</v>
+      </c>
+      <c r="R268" s="10">
+        <v>17</v>
+      </c>
+      <c r="S268" s="10">
+        <v>35.5</v>
+      </c>
+      <c r="T268" s="10">
+        <v>5.3</v>
+      </c>
+      <c r="U268" s="10">
+        <v>4.2</v>
+      </c>
+      <c r="V268" s="10">
+        <v>4.7930000000000001</v>
+      </c>
+      <c r="W268" s="10">
+        <v>14</v>
+      </c>
+      <c r="X268" s="10">
+        <v>5.55</v>
+      </c>
+      <c r="Y268" s="10">
+        <v>10.025</v>
+      </c>
+    </row>
+    <row r="269" spans="1:25">
+      <c r="A269" s="11">
+        <v>46178</v>
+      </c>
+      <c r="B269" s="11">
+        <v>46178</v>
+      </c>
+      <c r="C269" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D269" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E269" s="10">
+        <v>54</v>
+      </c>
+      <c r="F269" s="10">
+        <v>30.5</v>
+      </c>
+      <c r="G269" s="10">
+        <v>43.4</v>
+      </c>
+      <c r="H269" s="10">
+        <v>25</v>
+      </c>
+      <c r="I269" s="10">
+        <v>21.8</v>
+      </c>
+      <c r="J269" s="10">
+        <v>22.7</v>
+      </c>
+      <c r="K269" s="10">
+        <v>75</v>
+      </c>
+      <c r="L269" s="10">
+        <v>34.5</v>
+      </c>
+      <c r="M269" s="10">
+        <v>64</v>
+      </c>
+      <c r="N269" s="10">
+        <v>12.5</v>
+      </c>
+      <c r="O269" s="10">
+        <v>10.6</v>
+      </c>
+      <c r="P269" s="10">
+        <v>12.3</v>
+      </c>
+      <c r="Q269" s="10">
+        <v>54</v>
+      </c>
+      <c r="R269" s="10">
+        <v>17</v>
+      </c>
+      <c r="S269" s="10">
+        <v>35.5</v>
+      </c>
+      <c r="T269" s="10">
+        <v>5.3</v>
+      </c>
+      <c r="U269" s="10">
+        <v>4.2</v>
+      </c>
+      <c r="V269" s="10">
+        <v>4.7930000000000001</v>
+      </c>
+      <c r="W269" s="10">
+        <v>14</v>
+      </c>
+      <c r="X269" s="10">
+        <v>5.55</v>
+      </c>
+      <c r="Y269" s="10">
+        <v>10.025</v>
+      </c>
+    </row>
+    <row r="270" spans="1:25">
+      <c r="A270" s="11">
+        <v>46178</v>
+      </c>
+      <c r="B270" s="11">
+        <v>46178</v>
+      </c>
+      <c r="C270" s="7">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D270" s="6" t="s">
         <v>53</v>
       </c>
     </row>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05A3C9D0-9DFA-4393-91D0-C060D5B677FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4632C7D6-1298-4246-AD96-E2B5605A156C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -362,8 +362,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -381,7 +381,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2047,6 +2047,9 @@
                 <c:pt idx="266">
                   <c:v>43.4</c:v>
                 </c:pt>
+                <c:pt idx="267">
+                  <c:v>43.4</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3706,6 +3709,9 @@
                 <c:pt idx="266">
                   <c:v>22.7</c:v>
                 </c:pt>
+                <c:pt idx="267">
+                  <c:v>22.7</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -5365,6 +5371,9 @@
                 <c:pt idx="266">
                   <c:v>64</c:v>
                 </c:pt>
+                <c:pt idx="267">
+                  <c:v>64.125</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -7024,6 +7033,9 @@
                 <c:pt idx="266">
                   <c:v>12.3</c:v>
                 </c:pt>
+                <c:pt idx="267">
+                  <c:v>12.25</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -8681,6 +8693,9 @@
                   <c:v>35.5</c:v>
                 </c:pt>
                 <c:pt idx="266">
+                  <c:v>35.5</c:v>
+                </c:pt>
+                <c:pt idx="267">
                   <c:v>35.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -10358,6 +10373,9 @@
                 <c:pt idx="266">
                   <c:v>4.7930000000000001</c:v>
                 </c:pt>
+                <c:pt idx="267">
+                  <c:v>4.7930000000000001</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -12017,6 +12035,9 @@
                   <c:v>10.025</c:v>
                 </c:pt>
                 <c:pt idx="266">
+                  <c:v>10.025</c:v>
+                </c:pt>
+                <c:pt idx="267">
                   <c:v>10.025</c:v>
                 </c:pt>
               </c:numCache>
@@ -12296,7 +12317,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -13101,7 +13122,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -15712,14 +15733,14 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:Y270"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.44140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.77734375" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.77734375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.81640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.81640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.453125" style="6" bestFit="1" customWidth="1"/>
     <col min="5" max="13" width="9" style="10"/>
-    <col min="14" max="14" width="9.5546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.54296875" style="10" bestFit="1" customWidth="1"/>
     <col min="15" max="25" width="9" style="10"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
@@ -36441,6 +36462,69 @@
       </c>
       <c r="D270" s="6" t="s">
         <v>53</v>
+      </c>
+      <c r="E270" s="10">
+        <v>54</v>
+      </c>
+      <c r="F270" s="10">
+        <v>30.5</v>
+      </c>
+      <c r="G270" s="10">
+        <v>43.4</v>
+      </c>
+      <c r="H270" s="10">
+        <v>25</v>
+      </c>
+      <c r="I270" s="10">
+        <v>21.8</v>
+      </c>
+      <c r="J270" s="10">
+        <v>22.7</v>
+      </c>
+      <c r="K270" s="10">
+        <v>75</v>
+      </c>
+      <c r="L270" s="10">
+        <v>34.5</v>
+      </c>
+      <c r="M270" s="10">
+        <v>64.125</v>
+      </c>
+      <c r="N270" s="10">
+        <v>12.5</v>
+      </c>
+      <c r="O270" s="10">
+        <v>10.6</v>
+      </c>
+      <c r="P270" s="10">
+        <v>12.25</v>
+      </c>
+      <c r="Q270" s="10">
+        <v>54</v>
+      </c>
+      <c r="R270" s="10">
+        <v>19</v>
+      </c>
+      <c r="S270" s="10">
+        <v>35.5</v>
+      </c>
+      <c r="T270" s="10">
+        <v>5.3</v>
+      </c>
+      <c r="U270" s="10">
+        <v>4.2</v>
+      </c>
+      <c r="V270" s="10">
+        <v>4.7930000000000001</v>
+      </c>
+      <c r="W270" s="10">
+        <v>14</v>
+      </c>
+      <c r="X270" s="10">
+        <v>5.55</v>
+      </c>
+      <c r="Y270" s="10">
+        <v>10.025</v>
       </c>
     </row>
   </sheetData>
@@ -36460,21 +36544,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:AK8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.44140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.54296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1796875" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.36328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.453125" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.54296875" style="10" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="10"/>
-    <col min="7" max="7" width="9.5546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.5546875" style="10" customWidth="1"/>
-    <col min="9" max="9" width="9.77734375" style="10" customWidth="1"/>
-    <col min="10" max="10" width="10.33203125" style="10" customWidth="1"/>
-    <col min="11" max="11" width="9.5546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.54296875" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.54296875" style="10" customWidth="1"/>
+    <col min="9" max="9" width="9.81640625" style="10" customWidth="1"/>
+    <col min="10" max="10" width="10.36328125" style="10" customWidth="1"/>
+    <col min="11" max="11" width="9.54296875" style="10" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" style="10"/>
-    <col min="13" max="13" width="9.5546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.54296875" style="10" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="10"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
@@ -37106,19 +37190,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:Y22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.54296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.453125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.453125" style="6" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="13"/>
-    <col min="7" max="7" width="9.44140625" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.453125" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.453125" style="13" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="13"/>
-    <col min="10" max="10" width="11.88671875" style="10" customWidth="1"/>
+    <col min="10" max="10" width="11.90625" style="10" customWidth="1"/>
     <col min="11" max="12" width="9" style="13"/>
-    <col min="13" max="13" width="13.33203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.36328125" style="10" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="10"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
@@ -38106,13 +38190,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:Y22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.44140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.44140625" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.54296875" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.453125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.453125" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.453125" style="10" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="10"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
@@ -38911,7 +38995,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="16384" width="9" style="3"/>
   </cols>
@@ -38926,11 +39010,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="22.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.77734375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="22.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.81640625" style="3" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50C3E1A5-0C4E-4868-AC4E-11BAF6C301AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D141CA19-CAB8-4DC0-9941-275058252359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11430" yWindow="0" windowWidth="11700" windowHeight="14730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -362,8 +362,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -381,7 +381,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1246,6 +1246,15 @@
                 <c:pt idx="270">
                   <c:v>46181</c:v>
                 </c:pt>
+                <c:pt idx="271">
+                  <c:v>46182</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>46182</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>46182</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2067,6 +2076,12 @@
                 </c:pt>
                 <c:pt idx="270">
                   <c:v>43.567</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>43.832999999999998</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>44</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2926,6 +2941,15 @@
                 <c:pt idx="270">
                   <c:v>46181</c:v>
                 </c:pt>
+                <c:pt idx="271">
+                  <c:v>46182</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>46182</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>46182</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3747,6 +3771,12 @@
                 </c:pt>
                 <c:pt idx="270">
                   <c:v>22.7</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>22.8</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>22.8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4606,6 +4636,15 @@
                 <c:pt idx="270">
                   <c:v>46181</c:v>
                 </c:pt>
+                <c:pt idx="271">
+                  <c:v>46182</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>46182</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>46182</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5427,6 +5466,12 @@
                 </c:pt>
                 <c:pt idx="270">
                   <c:v>64.375</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>64.875</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>64.875</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6286,6 +6331,15 @@
                 <c:pt idx="270">
                   <c:v>46181</c:v>
                 </c:pt>
+                <c:pt idx="271">
+                  <c:v>46182</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>46182</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>46182</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7107,6 +7161,12 @@
                 </c:pt>
                 <c:pt idx="270">
                   <c:v>12.15</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>12.1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7966,6 +8026,15 @@
                 <c:pt idx="270">
                   <c:v>46181</c:v>
                 </c:pt>
+                <c:pt idx="271">
+                  <c:v>46182</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>46182</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>46182</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8787,6 +8856,12 @@
                 </c:pt>
                 <c:pt idx="270">
                   <c:v>35.700000000000003</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>35.9</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>35.9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9662,6 +9737,15 @@
                 <c:pt idx="270">
                   <c:v>46181</c:v>
                 </c:pt>
+                <c:pt idx="271">
+                  <c:v>46182</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>46182</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>46182</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10483,6 +10567,12 @@
                 </c:pt>
                 <c:pt idx="270">
                   <c:v>4.75</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>4.7290000000000001</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>4.7290000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11344,6 +11434,15 @@
                 <c:pt idx="270">
                   <c:v>46181</c:v>
                 </c:pt>
+                <c:pt idx="271">
+                  <c:v>46182</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>46182</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>46182</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -12165,6 +12264,12 @@
                 </c:pt>
                 <c:pt idx="270">
                   <c:v>10.167</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>10.286</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>10.314</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12443,7 +12548,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -13266,7 +13371,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -15888,15 +15993,15 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y273"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:Y276"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.453125" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.81640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.81640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.453125" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.77734375" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.77734375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" style="6" bestFit="1" customWidth="1"/>
     <col min="5" max="13" width="9" style="10"/>
-    <col min="14" max="14" width="9.54296875" style="10" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.5546875" style="10" bestFit="1" customWidth="1"/>
     <col min="15" max="25" width="9" style="10"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
@@ -36912,6 +37017,174 @@
       </c>
       <c r="Y273" s="10">
         <v>10.167</v>
+      </c>
+    </row>
+    <row r="274" spans="1:25">
+      <c r="A274" s="11">
+        <v>46182</v>
+      </c>
+      <c r="B274" s="11">
+        <v>46182</v>
+      </c>
+      <c r="C274" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D274" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E274" s="10">
+        <v>54.5</v>
+      </c>
+      <c r="F274" s="10">
+        <v>31</v>
+      </c>
+      <c r="G274" s="10">
+        <v>43.832999999999998</v>
+      </c>
+      <c r="H274" s="10">
+        <v>25.5</v>
+      </c>
+      <c r="I274" s="10">
+        <v>21.7</v>
+      </c>
+      <c r="J274" s="10">
+        <v>22.8</v>
+      </c>
+      <c r="K274" s="10">
+        <v>76</v>
+      </c>
+      <c r="L274" s="10">
+        <v>34.6</v>
+      </c>
+      <c r="M274" s="10">
+        <v>64.875</v>
+      </c>
+      <c r="N274" s="10">
+        <v>12.4</v>
+      </c>
+      <c r="O274" s="10">
+        <v>10.5</v>
+      </c>
+      <c r="P274" s="10">
+        <v>12.1</v>
+      </c>
+      <c r="Q274" s="10">
+        <v>55</v>
+      </c>
+      <c r="R274" s="10">
+        <v>17.2</v>
+      </c>
+      <c r="S274" s="10">
+        <v>35.9</v>
+      </c>
+      <c r="T274" s="10">
+        <v>5.2</v>
+      </c>
+      <c r="U274" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="V274" s="10">
+        <v>4.7290000000000001</v>
+      </c>
+      <c r="W274" s="10">
+        <v>14.8</v>
+      </c>
+      <c r="X274" s="10">
+        <v>5.8</v>
+      </c>
+      <c r="Y274" s="10">
+        <v>10.286</v>
+      </c>
+    </row>
+    <row r="275" spans="1:25">
+      <c r="A275" s="11">
+        <v>46182</v>
+      </c>
+      <c r="B275" s="11">
+        <v>46182</v>
+      </c>
+      <c r="C275" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D275" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E275" s="10">
+        <v>55</v>
+      </c>
+      <c r="F275" s="10">
+        <v>31</v>
+      </c>
+      <c r="G275" s="10">
+        <v>44</v>
+      </c>
+      <c r="H275" s="10">
+        <v>25.2</v>
+      </c>
+      <c r="I275" s="10">
+        <v>21.7</v>
+      </c>
+      <c r="J275" s="10">
+        <v>22.8</v>
+      </c>
+      <c r="K275" s="10">
+        <v>76</v>
+      </c>
+      <c r="L275" s="10">
+        <v>35</v>
+      </c>
+      <c r="M275" s="10">
+        <v>64.875</v>
+      </c>
+      <c r="N275" s="10">
+        <v>12.4</v>
+      </c>
+      <c r="O275" s="10">
+        <v>10.5</v>
+      </c>
+      <c r="P275" s="10">
+        <v>12.1</v>
+      </c>
+      <c r="Q275" s="10">
+        <v>55</v>
+      </c>
+      <c r="R275" s="10">
+        <v>17.5</v>
+      </c>
+      <c r="S275" s="10">
+        <v>35.9</v>
+      </c>
+      <c r="T275" s="10">
+        <v>5.2</v>
+      </c>
+      <c r="U275" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="V275" s="10">
+        <v>4.7290000000000001</v>
+      </c>
+      <c r="W275" s="10">
+        <v>14.8</v>
+      </c>
+      <c r="X275" s="10">
+        <v>5.8</v>
+      </c>
+      <c r="Y275" s="10">
+        <v>10.314</v>
+      </c>
+    </row>
+    <row r="276" spans="1:25">
+      <c r="A276" s="11">
+        <v>46182</v>
+      </c>
+      <c r="B276" s="11">
+        <v>46182</v>
+      </c>
+      <c r="C276" s="7">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D276" s="6" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -36931,21 +37204,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:AK8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.54296875" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.1796875" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.36328125" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.453125" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.54296875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5546875" style="10" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="10"/>
-    <col min="7" max="7" width="9.54296875" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.54296875" style="10" customWidth="1"/>
-    <col min="9" max="9" width="9.81640625" style="10" customWidth="1"/>
-    <col min="10" max="10" width="10.36328125" style="10" customWidth="1"/>
-    <col min="11" max="11" width="9.54296875" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.5546875" style="10" customWidth="1"/>
+    <col min="9" max="9" width="9.77734375" style="10" customWidth="1"/>
+    <col min="10" max="10" width="10.33203125" style="10" customWidth="1"/>
+    <col min="11" max="11" width="9.5546875" style="10" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" style="10"/>
-    <col min="13" max="13" width="9.54296875" style="10" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.5546875" style="10" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="10"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
@@ -37577,19 +37850,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:Y23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.54296875" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.453125" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.453125" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" style="6" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="13"/>
-    <col min="7" max="7" width="9.453125" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.453125" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.44140625" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.44140625" style="13" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="13"/>
-    <col min="10" max="10" width="11.90625" style="10" customWidth="1"/>
+    <col min="10" max="10" width="11.88671875" style="10" customWidth="1"/>
     <col min="11" max="12" width="9" style="13"/>
-    <col min="13" max="13" width="13.36328125" style="10" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.33203125" style="10" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="10"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
@@ -38618,13 +38891,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:Y23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.54296875" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.453125" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.453125" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.453125" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.44140625" style="10" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="10"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
@@ -39455,7 +39728,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="16384" width="9" style="3"/>
   </cols>
@@ -39470,11 +39743,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="22.81640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.81640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.81640625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="22.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.77734375" style="3" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D141CA19-CAB8-4DC0-9941-275058252359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{583BCC87-F102-48E7-9578-373042A51510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -1255,6 +1255,15 @@
                 <c:pt idx="273">
                   <c:v>46182</c:v>
                 </c:pt>
+                <c:pt idx="274">
+                  <c:v>46183</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>46183</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>46183</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2082,6 +2091,12 @@
                 </c:pt>
                 <c:pt idx="272">
                   <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>44.332999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2950,6 +2965,15 @@
                 <c:pt idx="273">
                   <c:v>46182</c:v>
                 </c:pt>
+                <c:pt idx="274">
+                  <c:v>46183</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>46183</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>46183</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3777,6 +3801,12 @@
                 </c:pt>
                 <c:pt idx="272">
                   <c:v>22.8</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>22.8</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>23</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4645,6 +4675,15 @@
                 <c:pt idx="273">
                   <c:v>46182</c:v>
                 </c:pt>
+                <c:pt idx="274">
+                  <c:v>46183</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>46183</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>46183</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5472,6 +5511,12 @@
                 </c:pt>
                 <c:pt idx="272">
                   <c:v>64.875</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>64.875</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>65.25</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6340,6 +6385,15 @@
                 <c:pt idx="273">
                   <c:v>46182</c:v>
                 </c:pt>
+                <c:pt idx="274">
+                  <c:v>46183</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>46183</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>46183</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7166,6 +7220,12 @@
                   <c:v>12.1</c:v>
                 </c:pt>
                 <c:pt idx="272">
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="274">
                   <c:v>12.1</c:v>
                 </c:pt>
               </c:numCache>
@@ -8035,6 +8095,15 @@
                 <c:pt idx="273">
                   <c:v>46182</c:v>
                 </c:pt>
+                <c:pt idx="274">
+                  <c:v>46183</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>46183</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>46183</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8861,6 +8930,12 @@
                   <c:v>35.9</c:v>
                 </c:pt>
                 <c:pt idx="272">
+                  <c:v>35.9</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>35.9</c:v>
+                </c:pt>
+                <c:pt idx="274">
                   <c:v>35.9</c:v>
                 </c:pt>
               </c:numCache>
@@ -9746,6 +9821,15 @@
                 <c:pt idx="273">
                   <c:v>46182</c:v>
                 </c:pt>
+                <c:pt idx="274">
+                  <c:v>46183</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>46183</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>46183</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10573,6 +10657,12 @@
                 </c:pt>
                 <c:pt idx="272">
                   <c:v>4.7290000000000001</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>4.7290000000000001</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>4.7069999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11443,6 +11533,15 @@
                 <c:pt idx="273">
                   <c:v>46182</c:v>
                 </c:pt>
+                <c:pt idx="274">
+                  <c:v>46183</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>46183</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>46183</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -12270,6 +12369,12 @@
                 </c:pt>
                 <c:pt idx="272">
                   <c:v>10.314</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>10.314</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>10.433</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12596,68 +12701,71 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Module!$B$4:$B$1121</c:f>
+              <c:f>Module!$B$3:$B$1121</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="1118"/>
+                <c:ptCount val="1119"/>
                 <c:pt idx="0">
+                  <c:v>46034</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>46041</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>46048</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>46055</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>46062</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>46076</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>46083</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>46090</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>46097</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>46104</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>46111</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>46118</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>46125</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>46132</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>46139</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>46146</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>46153</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>46160</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>46167</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="19">
                   <c:v>46174</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="20">
                   <c:v>46181</c:v>
                 </c:pt>
               </c:numCache>
@@ -12665,68 +12773,71 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Module!$G$4:$G$1121</c:f>
+              <c:f>Module!$G$3:$G$1121</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
-                <c:ptCount val="1118"/>
+                <c:ptCount val="1119"/>
                 <c:pt idx="0">
+                  <c:v>157.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>177.5</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>215</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>250</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>250</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>245</c:v>
+                  <c:v>250</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>245</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>245</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>240</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>230</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>232.5</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>232.5</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>232.5</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>242.5</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>222.5</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>219</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>218.5</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>216</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>215.5</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>215</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>214</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="19">
                   <c:v>212.5</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="20">
                   <c:v>211</c:v>
                 </c:pt>
               </c:numCache>
@@ -12770,68 +12881,71 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Module!$B$4:$B$1121</c:f>
+              <c:f>Module!$B$3:$B$1121</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="1118"/>
+                <c:ptCount val="1119"/>
                 <c:pt idx="0">
+                  <c:v>46034</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>46041</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>46048</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>46055</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>46062</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>46076</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>46083</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>46090</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>46097</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>46104</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>46111</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>46118</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>46125</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>46132</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>46139</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>46146</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>46153</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>46160</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>46167</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="19">
                   <c:v>46174</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="20">
                   <c:v>46181</c:v>
                 </c:pt>
               </c:numCache>
@@ -12839,68 +12953,71 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Module!$M$4:$M$1121</c:f>
+              <c:f>Module!$M$3:$M$1121</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
-                <c:ptCount val="1118"/>
+                <c:ptCount val="1119"/>
                 <c:pt idx="0">
+                  <c:v>89.332999999999998</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>94</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>99.667000000000002</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>110</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>118.333</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>121</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>122.667</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>123.333</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>126.667</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>132.333</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>143.333</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>150</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>149.333</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>149.209</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>148.86799999999999</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>148.83000000000001</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>148.435</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>150.761</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>150.435</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="19">
                   <c:v>150.261</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="20">
                   <c:v>150.08699999999999</c:v>
                 </c:pt>
               </c:numCache>
@@ -12960,68 +13077,71 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Module!$B$4:$B$1121</c:f>
+              <c:f>Module!$B$3:$B$1121</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="1118"/>
+                <c:ptCount val="1119"/>
                 <c:pt idx="0">
+                  <c:v>46034</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>46041</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>46048</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>46055</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>46062</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>46076</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>46083</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>46090</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>46097</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>46104</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>46111</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>46118</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>46125</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>46132</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>46139</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>46146</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>46153</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>46160</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>46167</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="19">
                   <c:v>46174</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="20">
                   <c:v>46181</c:v>
                 </c:pt>
               </c:numCache>
@@ -13029,68 +13149,71 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Module!$J$4:$J$1121</c:f>
+              <c:f>Module!$J$3:$J$1121</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
-                <c:ptCount val="1118"/>
+                <c:ptCount val="1119"/>
                 <c:pt idx="0">
+                  <c:v>480</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>545</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>715</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>850</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>870</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>885</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>890</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>900</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>910</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>917.5</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>925</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>935</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>930</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>975</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>970</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>960</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>960</c:v>
                 </c:pt>
                 <c:pt idx="16">
+                  <c:v>960</c:v>
+                </c:pt>
+                <c:pt idx="17">
                   <c:v>975</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>1020</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="19">
                   <c:v>1035</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="20">
                   <c:v>1075</c:v>
                 </c:pt>
               </c:numCache>
@@ -13419,68 +13542,71 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>GDDR!$B$4:$B$1121</c:f>
+              <c:f>GDDR!$B$3:$B$1121</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="1118"/>
+                <c:ptCount val="1119"/>
                 <c:pt idx="0">
+                  <c:v>46034</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>46041</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>46048</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>46055</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>46062</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>46076</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>46083</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>46090</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>46097</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>46104</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>46111</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>46118</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>46125</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>46132</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>46139</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>46146</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>46153</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>46160</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>46167</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="19">
                   <c:v>46174</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="20">
                   <c:v>46181</c:v>
                 </c:pt>
               </c:numCache>
@@ -13488,57 +13614,57 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>GDDR!$G$4:$G$1121</c:f>
+              <c:f>GDDR!$G$3:$G$1121</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
-                <c:ptCount val="1118"/>
+                <c:ptCount val="1119"/>
                 <c:pt idx="0">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>7.0910000000000002</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>7.8819791193826605</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>8.6820000000000004</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>9.4090000000000007</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>9.6359999999999992</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>10</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>10.455</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>11.182</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>11.682</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>12.727</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>12.526999999999999</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>12.318</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>12.227</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>11.864000000000001</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>11.773</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>11.635999999999999</c:v>
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>11.635999999999999</c:v>
@@ -13550,6 +13676,9 @@
                   <c:v>11.635999999999999</c:v>
                 </c:pt>
                 <c:pt idx="19">
+                  <c:v>11.635999999999999</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>11.545</c:v>
                 </c:pt>
               </c:numCache>
@@ -13593,68 +13722,71 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>GDDR!$B$4:$B$1121</c:f>
+              <c:f>GDDR!$B$3:$B$1121</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="1118"/>
+                <c:ptCount val="1119"/>
                 <c:pt idx="0">
+                  <c:v>46034</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>46041</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>46048</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>46055</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>46062</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>46076</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>46083</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>46090</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>46097</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>46104</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>46111</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>46118</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>46125</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>46132</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>46139</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>46146</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>46153</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>46160</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>46167</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="19">
                   <c:v>46174</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="20">
                   <c:v>46181</c:v>
                 </c:pt>
               </c:numCache>
@@ -13662,68 +13794,71 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>GDDR!$J$4:$J$1121</c:f>
+              <c:f>GDDR!$J$3:$J$1121</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
-                <c:ptCount val="1118"/>
+                <c:ptCount val="1119"/>
                 <c:pt idx="0">
+                  <c:v>5.9690000000000003</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>7.1539999999999999</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>8.0379000816030466</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>8.8650000000000002</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>9.6539999999999999</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>9.8650000000000002</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>10.221</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>10.721</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>11.462</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>11.962</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>12.865</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>12.71</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>12.412000000000001</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>12.335000000000001</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>11.962</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>11.829000000000001</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>11.702</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>11.632999999999999</c:v>
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>11.632999999999999</c:v>
                 </c:pt>
                 <c:pt idx="18">
+                  <c:v>11.632999999999999</c:v>
+                </c:pt>
+                <c:pt idx="19">
                   <c:v>11.651999999999999</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="20">
                   <c:v>11.537000000000001</c:v>
                 </c:pt>
               </c:numCache>
@@ -13806,7 +13941,7 @@
         <c:axId val="1382523328"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:min val="6"/>
+          <c:min val="5"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -15993,7 +16128,7 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y276"/>
+  <dimension ref="A1:Y279"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="12.44140625" style="11" bestFit="1" customWidth="1"/>
@@ -37184,6 +37319,174 @@
         <v>0.75694444444444453</v>
       </c>
       <c r="D276" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E276" s="10">
+        <v>55.5</v>
+      </c>
+      <c r="F276" s="10">
+        <v>31</v>
+      </c>
+      <c r="G276" s="10">
+        <v>44</v>
+      </c>
+      <c r="H276" s="10">
+        <v>25.2</v>
+      </c>
+      <c r="I276" s="10">
+        <v>21.7</v>
+      </c>
+      <c r="J276" s="10">
+        <v>22.8</v>
+      </c>
+      <c r="K276" s="10">
+        <v>76</v>
+      </c>
+      <c r="L276" s="10">
+        <v>35</v>
+      </c>
+      <c r="M276" s="10">
+        <v>64.875</v>
+      </c>
+      <c r="N276" s="10">
+        <v>12.4</v>
+      </c>
+      <c r="O276" s="10">
+        <v>10.5</v>
+      </c>
+      <c r="P276" s="10">
+        <v>12.1</v>
+      </c>
+      <c r="Q276" s="10">
+        <v>55</v>
+      </c>
+      <c r="R276" s="10">
+        <v>17.5</v>
+      </c>
+      <c r="S276" s="10">
+        <v>35.9</v>
+      </c>
+      <c r="T276" s="10">
+        <v>5.2</v>
+      </c>
+      <c r="U276" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="V276" s="10">
+        <v>4.7290000000000001</v>
+      </c>
+      <c r="W276" s="10">
+        <v>14.8</v>
+      </c>
+      <c r="X276" s="10">
+        <v>5.8</v>
+      </c>
+      <c r="Y276" s="10">
+        <v>10.314</v>
+      </c>
+    </row>
+    <row r="277" spans="1:25">
+      <c r="A277" s="11">
+        <v>46183</v>
+      </c>
+      <c r="B277" s="11">
+        <v>46183</v>
+      </c>
+      <c r="C277" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D277" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E277" s="10">
+        <v>56</v>
+      </c>
+      <c r="F277" s="10">
+        <v>31</v>
+      </c>
+      <c r="G277" s="10">
+        <v>44.332999999999998</v>
+      </c>
+      <c r="H277" s="10">
+        <v>25.2</v>
+      </c>
+      <c r="I277" s="10">
+        <v>21.7</v>
+      </c>
+      <c r="J277" s="10">
+        <v>23</v>
+      </c>
+      <c r="K277" s="10">
+        <v>77</v>
+      </c>
+      <c r="L277" s="10">
+        <v>35</v>
+      </c>
+      <c r="M277" s="10">
+        <v>65.25</v>
+      </c>
+      <c r="N277" s="10">
+        <v>12.4</v>
+      </c>
+      <c r="O277" s="10">
+        <v>10.5</v>
+      </c>
+      <c r="P277" s="10">
+        <v>12.1</v>
+      </c>
+      <c r="Q277" s="10">
+        <v>55</v>
+      </c>
+      <c r="R277" s="10">
+        <v>17.5</v>
+      </c>
+      <c r="S277" s="10">
+        <v>35.9</v>
+      </c>
+      <c r="T277" s="10">
+        <v>5.2</v>
+      </c>
+      <c r="U277" s="10">
+        <v>4</v>
+      </c>
+      <c r="V277" s="10">
+        <v>4.7069999999999999</v>
+      </c>
+      <c r="W277" s="10">
+        <v>15</v>
+      </c>
+      <c r="X277" s="10">
+        <v>5.8</v>
+      </c>
+      <c r="Y277" s="10">
+        <v>10.433</v>
+      </c>
+    </row>
+    <row r="278" spans="1:25">
+      <c r="A278" s="11">
+        <v>46183</v>
+      </c>
+      <c r="B278" s="11">
+        <v>46183</v>
+      </c>
+      <c r="C278" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D278" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="279" spans="1:25">
+      <c r="A279" s="11">
+        <v>46183</v>
+      </c>
+      <c r="B279" s="11">
+        <v>46183</v>
+      </c>
+      <c r="C279" s="7">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D279" s="6" t="s">
         <v>53</v>
       </c>
     </row>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{583BCC87-F102-48E7-9578-373042A51510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A2D4DBE-2558-41CF-A532-2FDDCC6A18B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -362,8 +362,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -381,7 +381,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2098,6 +2098,12 @@
                 <c:pt idx="274">
                   <c:v>44.332999999999998</c:v>
                 </c:pt>
+                <c:pt idx="275">
+                  <c:v>44.332999999999998</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>44.5</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3808,6 +3814,12 @@
                 <c:pt idx="274">
                   <c:v>23</c:v>
                 </c:pt>
+                <c:pt idx="275">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>23</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -5518,6 +5530,12 @@
                 <c:pt idx="274">
                   <c:v>65.25</c:v>
                 </c:pt>
+                <c:pt idx="275">
+                  <c:v>65.25</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>65.55</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -7228,6 +7246,12 @@
                 <c:pt idx="274">
                   <c:v>12.1</c:v>
                 </c:pt>
+                <c:pt idx="275">
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>12.1</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -8936,6 +8960,12 @@
                   <c:v>35.9</c:v>
                 </c:pt>
                 <c:pt idx="274">
+                  <c:v>35.9</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>35.9</c:v>
+                </c:pt>
+                <c:pt idx="276">
                   <c:v>35.9</c:v>
                 </c:pt>
               </c:numCache>
@@ -10664,6 +10694,12 @@
                 <c:pt idx="274">
                   <c:v>4.7069999999999999</c:v>
                 </c:pt>
+                <c:pt idx="275">
+                  <c:v>4.7069999999999999</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>4.7069999999999999</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -12374,6 +12410,12 @@
                   <c:v>10.314</c:v>
                 </c:pt>
                 <c:pt idx="274">
+                  <c:v>10.433</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>10.433</c:v>
+                </c:pt>
+                <c:pt idx="276">
                   <c:v>10.433</c:v>
                 </c:pt>
               </c:numCache>
@@ -12653,7 +12695,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -13494,7 +13536,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -16129,14 +16171,14 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:Y279"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.44140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.77734375" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.77734375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.81640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.81640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.453125" style="6" bestFit="1" customWidth="1"/>
     <col min="5" max="13" width="9" style="10"/>
-    <col min="14" max="14" width="9.5546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.54296875" style="10" bestFit="1" customWidth="1"/>
     <col min="15" max="25" width="9" style="10"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
@@ -37475,6 +37517,69 @@
       <c r="D278" s="6" t="s">
         <v>53</v>
       </c>
+      <c r="E278" s="10">
+        <v>56</v>
+      </c>
+      <c r="F278" s="10">
+        <v>31</v>
+      </c>
+      <c r="G278" s="10">
+        <v>44.332999999999998</v>
+      </c>
+      <c r="H278" s="10">
+        <v>25.2</v>
+      </c>
+      <c r="I278" s="10">
+        <v>21.7</v>
+      </c>
+      <c r="J278" s="10">
+        <v>23</v>
+      </c>
+      <c r="K278" s="10">
+        <v>77</v>
+      </c>
+      <c r="L278" s="10">
+        <v>35</v>
+      </c>
+      <c r="M278" s="10">
+        <v>65.25</v>
+      </c>
+      <c r="N278" s="10">
+        <v>12.4</v>
+      </c>
+      <c r="O278" s="10">
+        <v>10.5</v>
+      </c>
+      <c r="P278" s="10">
+        <v>12.1</v>
+      </c>
+      <c r="Q278" s="10">
+        <v>55</v>
+      </c>
+      <c r="R278" s="10">
+        <v>17.5</v>
+      </c>
+      <c r="S278" s="10">
+        <v>35.9</v>
+      </c>
+      <c r="T278" s="10">
+        <v>5.2</v>
+      </c>
+      <c r="U278" s="10">
+        <v>4</v>
+      </c>
+      <c r="V278" s="10">
+        <v>4.7069999999999999</v>
+      </c>
+      <c r="W278" s="10">
+        <v>15</v>
+      </c>
+      <c r="X278" s="10">
+        <v>5.8</v>
+      </c>
+      <c r="Y278" s="10">
+        <v>10.433</v>
+      </c>
     </row>
     <row r="279" spans="1:25">
       <c r="A279" s="11">
@@ -37488,6 +37593,69 @@
       </c>
       <c r="D279" s="6" t="s">
         <v>53</v>
+      </c>
+      <c r="E279" s="10">
+        <v>56</v>
+      </c>
+      <c r="F279" s="10">
+        <v>31</v>
+      </c>
+      <c r="G279" s="10">
+        <v>44.5</v>
+      </c>
+      <c r="H279" s="10">
+        <v>25.2</v>
+      </c>
+      <c r="I279" s="10">
+        <v>21.7</v>
+      </c>
+      <c r="J279" s="10">
+        <v>23</v>
+      </c>
+      <c r="K279" s="10">
+        <v>77</v>
+      </c>
+      <c r="L279" s="10">
+        <v>35</v>
+      </c>
+      <c r="M279" s="10">
+        <v>65.55</v>
+      </c>
+      <c r="N279" s="10">
+        <v>12.4</v>
+      </c>
+      <c r="O279" s="10">
+        <v>10.5</v>
+      </c>
+      <c r="P279" s="10">
+        <v>12.1</v>
+      </c>
+      <c r="Q279" s="10">
+        <v>55</v>
+      </c>
+      <c r="R279" s="10">
+        <v>17.5</v>
+      </c>
+      <c r="S279" s="10">
+        <v>35.9</v>
+      </c>
+      <c r="T279" s="10">
+        <v>5.2</v>
+      </c>
+      <c r="U279" s="10">
+        <v>4</v>
+      </c>
+      <c r="V279" s="10">
+        <v>4.7069999999999999</v>
+      </c>
+      <c r="W279" s="10">
+        <v>15</v>
+      </c>
+      <c r="X279" s="10">
+        <v>5.8</v>
+      </c>
+      <c r="Y279" s="10">
+        <v>10.433</v>
       </c>
     </row>
   </sheetData>
@@ -37507,21 +37675,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:AK8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.44140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.54296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1796875" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.36328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.453125" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.54296875" style="10" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="10"/>
-    <col min="7" max="7" width="9.5546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.5546875" style="10" customWidth="1"/>
-    <col min="9" max="9" width="9.77734375" style="10" customWidth="1"/>
-    <col min="10" max="10" width="10.33203125" style="10" customWidth="1"/>
-    <col min="11" max="11" width="9.5546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.54296875" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.54296875" style="10" customWidth="1"/>
+    <col min="9" max="9" width="9.81640625" style="10" customWidth="1"/>
+    <col min="10" max="10" width="10.36328125" style="10" customWidth="1"/>
+    <col min="11" max="11" width="9.54296875" style="10" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" style="10"/>
-    <col min="13" max="13" width="9.5546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.54296875" style="10" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="10"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
@@ -38153,19 +38321,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:Y23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.54296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.453125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.453125" style="6" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="13"/>
-    <col min="7" max="7" width="9.44140625" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.453125" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.453125" style="13" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="13"/>
-    <col min="10" max="10" width="11.88671875" style="10" customWidth="1"/>
+    <col min="10" max="10" width="11.90625" style="10" customWidth="1"/>
     <col min="11" max="12" width="9" style="13"/>
-    <col min="13" max="13" width="13.33203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.36328125" style="10" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="10"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
@@ -39194,13 +39362,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:Y23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.44140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.44140625" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.54296875" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.453125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.453125" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.453125" style="10" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="10"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
@@ -40031,7 +40199,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="16384" width="9" style="3"/>
   </cols>
@@ -40046,11 +40214,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="22.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.77734375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="22.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.81640625" style="3" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10118"/>
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data/industry/TrendForce/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6796756C-8D67-43B1-BFE3-30F3048F972A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DD8C268-E2BA-F440-9D9A-455D33CA69FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22160" yWindow="600" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -370,19 +370,19 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -400,7 +400,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2174,6 +2174,9 @@
                 <c:pt idx="284">
                   <c:v>45</c:v>
                 </c:pt>
+                <c:pt idx="285">
+                  <c:v>45</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3941,6 +3944,9 @@
                 <c:pt idx="284">
                   <c:v>23</c:v>
                 </c:pt>
+                <c:pt idx="285">
+                  <c:v>23</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -5708,6 +5714,9 @@
                 <c:pt idx="284">
                   <c:v>67.5</c:v>
                 </c:pt>
+                <c:pt idx="285">
+                  <c:v>67.5</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -7475,6 +7484,9 @@
                 <c:pt idx="284">
                   <c:v>11.975</c:v>
                 </c:pt>
+                <c:pt idx="285">
+                  <c:v>11.975</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -9240,6 +9252,9 @@
                   <c:v>35.9</c:v>
                 </c:pt>
                 <c:pt idx="284">
+                  <c:v>35.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="285">
                   <c:v>35.799999999999997</c:v>
                 </c:pt>
               </c:numCache>
@@ -11025,6 +11040,9 @@
                 <c:pt idx="284">
                   <c:v>4.5999999999999996</c:v>
                 </c:pt>
+                <c:pt idx="285">
+                  <c:v>4.5999999999999996</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -12792,6 +12810,9 @@
                   <c:v>10.743</c:v>
                 </c:pt>
                 <c:pt idx="284">
+                  <c:v>10.743</c:v>
+                </c:pt>
+                <c:pt idx="285">
                   <c:v>10.743</c:v>
                 </c:pt>
               </c:numCache>
@@ -13071,7 +13092,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -13930,7 +13951,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -16577,29 +16598,29 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:Y288"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.21875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="13" width="9" style="11"/>
-    <col min="14" max="14" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.5" style="11" bestFit="1" customWidth="1"/>
     <col min="15" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="5" customFormat="1">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="18" t="s">
         <v>50</v>
       </c>
       <c r="C1" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="16" t="s">
         <v>52</v>
       </c>
       <c r="E1" s="4" t="s">
@@ -16667,10 +16688,10 @@
       </c>
     </row>
     <row r="2" spans="1:25">
-      <c r="A2" s="16"/>
-      <c r="B2" s="16"/>
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
       <c r="C2" s="17"/>
-      <c r="D2" s="18"/>
+      <c r="D2" s="16"/>
       <c r="E2" s="6" t="s">
         <v>54</v>
       </c>
@@ -38692,6 +38713,69 @@
       </c>
       <c r="D288" s="10" t="s">
         <v>53</v>
+      </c>
+      <c r="E288" s="11">
+        <v>56.5</v>
+      </c>
+      <c r="F288" s="11">
+        <v>30</v>
+      </c>
+      <c r="G288" s="11">
+        <v>45</v>
+      </c>
+      <c r="H288" s="11">
+        <v>25</v>
+      </c>
+      <c r="I288" s="11">
+        <v>21.6</v>
+      </c>
+      <c r="J288" s="11">
+        <v>23</v>
+      </c>
+      <c r="K288" s="11">
+        <v>80</v>
+      </c>
+      <c r="L288" s="11">
+        <v>37.5</v>
+      </c>
+      <c r="M288" s="11">
+        <v>67.5</v>
+      </c>
+      <c r="N288" s="11">
+        <v>12.3</v>
+      </c>
+      <c r="O288" s="11">
+        <v>10.5</v>
+      </c>
+      <c r="P288" s="11">
+        <v>11.975</v>
+      </c>
+      <c r="Q288" s="11">
+        <v>56</v>
+      </c>
+      <c r="R288" s="11">
+        <v>18.8</v>
+      </c>
+      <c r="S288" s="11">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="T288" s="11">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="U288" s="11">
+        <v>3.9</v>
+      </c>
+      <c r="V288" s="11">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="W288" s="11">
+        <v>16</v>
+      </c>
+      <c r="X288" s="11">
+        <v>6.2</v>
+      </c>
+      <c r="Y288" s="11">
+        <v>10.743</v>
       </c>
     </row>
   </sheetData>
@@ -38711,36 +38795,36 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:AK8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1640625" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.1640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5" style="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.44140625" style="11" customWidth="1"/>
-    <col min="9" max="9" width="9.77734375" style="11" customWidth="1"/>
+    <col min="7" max="7" width="9.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.5" style="11" customWidth="1"/>
+    <col min="9" max="9" width="9.83203125" style="11" customWidth="1"/>
     <col min="10" max="10" width="10.33203125" style="11" customWidth="1"/>
-    <col min="11" max="11" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.5" style="11" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" style="11"/>
-    <col min="13" max="13" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.5" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" s="5" customFormat="1">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="18" t="s">
         <v>50</v>
       </c>
       <c r="C1" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="16" t="s">
         <v>52</v>
       </c>
       <c r="E1" s="6" t="s">
@@ -38820,10 +38904,10 @@
       <c r="AK1" s="12"/>
     </row>
     <row r="2" spans="1:37">
-      <c r="A2" s="16"/>
-      <c r="B2" s="16"/>
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
       <c r="C2" s="17"/>
-      <c r="D2" s="18"/>
+      <c r="D2" s="16"/>
       <c r="E2" s="6" t="s">
         <v>54</v>
       </c>
@@ -39357,17 +39441,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:Y24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1640625" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="15"/>
-    <col min="7" max="7" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.44140625" style="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5" style="15" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="15"/>
-    <col min="10" max="10" width="11.77734375" style="11" customWidth="1"/>
+    <col min="10" max="10" width="11.83203125" style="11" customWidth="1"/>
     <col min="11" max="12" width="9" style="15"/>
     <col min="13" max="13" width="13.33203125" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
@@ -39375,16 +39459,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="5" customFormat="1">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="18" t="s">
         <v>50</v>
       </c>
       <c r="C1" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="16" t="s">
         <v>52</v>
       </c>
       <c r="E1" s="14" t="s">
@@ -39428,10 +39512,10 @@
       <c r="Y1" s="4"/>
     </row>
     <row r="2" spans="1:25">
-      <c r="A2" s="16"/>
-      <c r="B2" s="16"/>
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
       <c r="C2" s="17"/>
-      <c r="D2" s="18"/>
+      <c r="D2" s="16"/>
       <c r="E2" s="14" t="s">
         <v>54</v>
       </c>
@@ -40439,28 +40523,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:Y24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.1640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.1640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.5" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="5" customFormat="1">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="16" t="s">
         <v>50</v>
       </c>
       <c r="C1" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="16" t="s">
         <v>52</v>
       </c>
       <c r="E1" s="13" t="s">
@@ -40498,10 +40582,10 @@
       <c r="Y1" s="4"/>
     </row>
     <row r="2" spans="1:25">
-      <c r="A2" s="18"/>
-      <c r="B2" s="18"/>
+      <c r="A2" s="16"/>
+      <c r="B2" s="16"/>
       <c r="C2" s="17"/>
-      <c r="D2" s="18"/>
+      <c r="D2" s="16"/>
       <c r="E2" s="6" t="s">
         <v>54</v>
       </c>
@@ -41308,7 +41392,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="16384" width="9" style="3"/>
   </cols>
@@ -41323,11 +41407,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="22.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.77734375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="22.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.83203125" style="3" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data/industry/TrendForce/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DD8C268-E2BA-F440-9D9A-455D33CA69FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C10E1C07-156F-44E0-A2AD-7F86883E6005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22160" yWindow="600" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -370,19 +370,19 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -400,7 +400,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1310,6 +1310,15 @@
                 <c:pt idx="285">
                   <c:v>46188</c:v>
                 </c:pt>
+                <c:pt idx="286">
+                  <c:v>46189</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>46189</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>46189</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2176,6 +2185,12 @@
                 </c:pt>
                 <c:pt idx="285">
                   <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>45.2</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>45.232999999999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3080,6 +3095,15 @@
                 <c:pt idx="285">
                   <c:v>46188</c:v>
                 </c:pt>
+                <c:pt idx="286">
+                  <c:v>46189</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>46189</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>46189</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3946,6 +3970,12 @@
                 </c:pt>
                 <c:pt idx="285">
                   <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>23.2</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>23.2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4850,6 +4880,15 @@
                 <c:pt idx="285">
                   <c:v>46188</c:v>
                 </c:pt>
+                <c:pt idx="286">
+                  <c:v>46189</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>46189</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>46189</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5716,6 +5755,12 @@
                 </c:pt>
                 <c:pt idx="285">
                   <c:v>67.5</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>68.125</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>68.125</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6620,6 +6665,15 @@
                 <c:pt idx="285">
                   <c:v>46188</c:v>
                 </c:pt>
+                <c:pt idx="286">
+                  <c:v>46189</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>46189</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>46189</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7485,6 +7539,12 @@
                   <c:v>11.975</c:v>
                 </c:pt>
                 <c:pt idx="285">
+                  <c:v>11.975</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>11.975</c:v>
+                </c:pt>
+                <c:pt idx="287">
                   <c:v>11.975</c:v>
                 </c:pt>
               </c:numCache>
@@ -8390,6 +8450,15 @@
                 <c:pt idx="285">
                   <c:v>46188</c:v>
                 </c:pt>
+                <c:pt idx="286">
+                  <c:v>46189</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>46189</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>46189</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9255,6 +9324,12 @@
                   <c:v>35.799999999999997</c:v>
                 </c:pt>
                 <c:pt idx="285">
+                  <c:v>35.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>35.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="287">
                   <c:v>35.799999999999997</c:v>
                 </c:pt>
               </c:numCache>
@@ -10176,6 +10251,15 @@
                 <c:pt idx="285">
                   <c:v>46188</c:v>
                 </c:pt>
+                <c:pt idx="286">
+                  <c:v>46189</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>46189</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>46189</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -11042,6 +11126,12 @@
                 </c:pt>
                 <c:pt idx="285">
                   <c:v>4.5999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>4.5359999999999996</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>4.5190000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11948,6 +12038,15 @@
                 <c:pt idx="285">
                   <c:v>46188</c:v>
                 </c:pt>
+                <c:pt idx="286">
+                  <c:v>46189</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>46189</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>46189</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -12814,6 +12913,12 @@
                 </c:pt>
                 <c:pt idx="285">
                   <c:v>10.743</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>10.856999999999999</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>10.856999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13092,7 +13197,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -13951,7 +14056,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -16597,30 +16702,30 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y288"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <dimension ref="A1:Y291"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="13" width="9" style="11"/>
-    <col min="14" max="14" width="9.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="15" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="5" customFormat="1">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="16" t="s">
         <v>50</v>
       </c>
       <c r="C1" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="18" t="s">
         <v>52</v>
       </c>
       <c r="E1" s="4" t="s">
@@ -16688,10 +16793,10 @@
       </c>
     </row>
     <row r="2" spans="1:25">
-      <c r="A2" s="18"/>
-      <c r="B2" s="18"/>
+      <c r="A2" s="16"/>
+      <c r="B2" s="16"/>
       <c r="C2" s="17"/>
-      <c r="D2" s="16"/>
+      <c r="D2" s="18"/>
       <c r="E2" s="6" t="s">
         <v>54</v>
       </c>
@@ -38776,6 +38881,174 @@
       </c>
       <c r="Y288" s="11">
         <v>10.743</v>
+      </c>
+    </row>
+    <row r="289" spans="1:25">
+      <c r="A289" s="8">
+        <v>46189</v>
+      </c>
+      <c r="B289" s="8">
+        <v>46189</v>
+      </c>
+      <c r="C289" s="9">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D289" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E289" s="11">
+        <v>57</v>
+      </c>
+      <c r="F289" s="11">
+        <v>30.5</v>
+      </c>
+      <c r="G289" s="11">
+        <v>45.2</v>
+      </c>
+      <c r="H289" s="11">
+        <v>25</v>
+      </c>
+      <c r="I289" s="11">
+        <v>22</v>
+      </c>
+      <c r="J289" s="11">
+        <v>23.2</v>
+      </c>
+      <c r="K289" s="11">
+        <v>80</v>
+      </c>
+      <c r="L289" s="11">
+        <v>37.5</v>
+      </c>
+      <c r="M289" s="11">
+        <v>68.125</v>
+      </c>
+      <c r="N289" s="11">
+        <v>12.3</v>
+      </c>
+      <c r="O289" s="11">
+        <v>10.5</v>
+      </c>
+      <c r="P289" s="11">
+        <v>11.975</v>
+      </c>
+      <c r="Q289" s="11">
+        <v>56</v>
+      </c>
+      <c r="R289" s="11">
+        <v>18.8</v>
+      </c>
+      <c r="S289" s="11">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="T289" s="11">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="U289" s="11">
+        <v>3.9</v>
+      </c>
+      <c r="V289" s="11">
+        <v>4.5359999999999996</v>
+      </c>
+      <c r="W289" s="11">
+        <v>16</v>
+      </c>
+      <c r="X289" s="11">
+        <v>6.3</v>
+      </c>
+      <c r="Y289" s="11">
+        <v>10.856999999999999</v>
+      </c>
+    </row>
+    <row r="290" spans="1:25">
+      <c r="A290" s="8">
+        <v>46189</v>
+      </c>
+      <c r="B290" s="8">
+        <v>46189</v>
+      </c>
+      <c r="C290" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D290" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E290" s="11">
+        <v>57</v>
+      </c>
+      <c r="F290" s="11">
+        <v>30.5</v>
+      </c>
+      <c r="G290" s="11">
+        <v>45.232999999999997</v>
+      </c>
+      <c r="H290" s="11">
+        <v>25</v>
+      </c>
+      <c r="I290" s="11">
+        <v>22</v>
+      </c>
+      <c r="J290" s="11">
+        <v>23.2</v>
+      </c>
+      <c r="K290" s="11">
+        <v>80</v>
+      </c>
+      <c r="L290" s="11">
+        <v>37.5</v>
+      </c>
+      <c r="M290" s="11">
+        <v>68.125</v>
+      </c>
+      <c r="N290" s="11">
+        <v>12.3</v>
+      </c>
+      <c r="O290" s="11">
+        <v>10.5</v>
+      </c>
+      <c r="P290" s="11">
+        <v>11.975</v>
+      </c>
+      <c r="Q290" s="11">
+        <v>56</v>
+      </c>
+      <c r="R290" s="11">
+        <v>18.8</v>
+      </c>
+      <c r="S290" s="11">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="T290" s="11">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="U290" s="11">
+        <v>3.9</v>
+      </c>
+      <c r="V290" s="11">
+        <v>4.5190000000000001</v>
+      </c>
+      <c r="W290" s="11">
+        <v>16</v>
+      </c>
+      <c r="X290" s="11">
+        <v>6.3</v>
+      </c>
+      <c r="Y290" s="11">
+        <v>10.856999999999999</v>
+      </c>
+    </row>
+    <row r="291" spans="1:25">
+      <c r="A291" s="8">
+        <v>46189</v>
+      </c>
+      <c r="B291" s="8">
+        <v>46189</v>
+      </c>
+      <c r="C291" s="9">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D291" s="10" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -38795,36 +39068,36 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:AK8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.1640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.109375" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.1640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="9.5" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.5" style="11" customWidth="1"/>
-    <col min="9" max="9" width="9.83203125" style="11" customWidth="1"/>
+    <col min="7" max="7" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.44140625" style="11" customWidth="1"/>
+    <col min="9" max="9" width="9.77734375" style="11" customWidth="1"/>
     <col min="10" max="10" width="10.33203125" style="11" customWidth="1"/>
-    <col min="11" max="11" width="9.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" style="11"/>
-    <col min="13" max="13" width="9.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" s="5" customFormat="1">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="16" t="s">
         <v>50</v>
       </c>
       <c r="C1" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="18" t="s">
         <v>52</v>
       </c>
       <c r="E1" s="6" t="s">
@@ -38904,10 +39177,10 @@
       <c r="AK1" s="12"/>
     </row>
     <row r="2" spans="1:37">
-      <c r="A2" s="18"/>
-      <c r="B2" s="18"/>
+      <c r="A2" s="16"/>
+      <c r="B2" s="16"/>
       <c r="C2" s="17"/>
-      <c r="D2" s="16"/>
+      <c r="D2" s="18"/>
       <c r="E2" s="6" t="s">
         <v>54</v>
       </c>
@@ -39441,17 +39714,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:Y24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.1640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.109375" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.1640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="15"/>
-    <col min="7" max="7" width="9.5" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5" style="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.44140625" style="15" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="15"/>
-    <col min="10" max="10" width="11.83203125" style="11" customWidth="1"/>
+    <col min="10" max="10" width="11.77734375" style="11" customWidth="1"/>
     <col min="11" max="12" width="9" style="15"/>
     <col min="13" max="13" width="13.33203125" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
@@ -39459,16 +39732,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="5" customFormat="1">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="16" t="s">
         <v>50</v>
       </c>
       <c r="C1" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="18" t="s">
         <v>52</v>
       </c>
       <c r="E1" s="14" t="s">
@@ -39512,10 +39785,10 @@
       <c r="Y1" s="4"/>
     </row>
     <row r="2" spans="1:25">
-      <c r="A2" s="18"/>
-      <c r="B2" s="18"/>
+      <c r="A2" s="16"/>
+      <c r="B2" s="16"/>
       <c r="C2" s="17"/>
-      <c r="D2" s="16"/>
+      <c r="D2" s="18"/>
       <c r="E2" s="14" t="s">
         <v>54</v>
       </c>
@@ -40523,28 +40796,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:Y24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.1640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.1640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.109375" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.1640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="5" customFormat="1">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="18" t="s">
         <v>50</v>
       </c>
       <c r="C1" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="18" t="s">
         <v>52</v>
       </c>
       <c r="E1" s="13" t="s">
@@ -40582,10 +40855,10 @@
       <c r="Y1" s="4"/>
     </row>
     <row r="2" spans="1:25">
-      <c r="A2" s="16"/>
-      <c r="B2" s="16"/>
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
       <c r="C2" s="17"/>
-      <c r="D2" s="16"/>
+      <c r="D2" s="18"/>
       <c r="E2" s="6" t="s">
         <v>54</v>
       </c>
@@ -41392,7 +41665,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="16384" width="9" style="3"/>
   </cols>
@@ -41407,11 +41680,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:D32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="22.83203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.83203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.83203125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="22.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.77734375" style="3" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10118"/>
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data/industry/TrendForce/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C10E1C07-156F-44E0-A2AD-7F86883E6005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21E1220A-862A-094B-B1B5-DA5540B1F345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24360" yWindow="600" windowWidth="26840" windowHeight="22820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -381,8 +381,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -400,7 +400,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2192,6 +2192,9 @@
                 <c:pt idx="287">
                   <c:v>45.232999999999997</c:v>
                 </c:pt>
+                <c:pt idx="288">
+                  <c:v>45.232999999999997</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3977,6 +3980,9 @@
                 <c:pt idx="287">
                   <c:v>23.2</c:v>
                 </c:pt>
+                <c:pt idx="288">
+                  <c:v>23.2</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -5762,6 +5768,9 @@
                 <c:pt idx="287">
                   <c:v>68.125</c:v>
                 </c:pt>
+                <c:pt idx="288">
+                  <c:v>68.125</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -7547,6 +7556,9 @@
                 <c:pt idx="287">
                   <c:v>11.975</c:v>
                 </c:pt>
+                <c:pt idx="288">
+                  <c:v>11.975</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -9330,6 +9342,9 @@
                   <c:v>35.799999999999997</c:v>
                 </c:pt>
                 <c:pt idx="287">
+                  <c:v>35.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="288">
                   <c:v>35.799999999999997</c:v>
                 </c:pt>
               </c:numCache>
@@ -11133,6 +11148,9 @@
                 <c:pt idx="287">
                   <c:v>4.5190000000000001</c:v>
                 </c:pt>
+                <c:pt idx="288">
+                  <c:v>4.5190000000000001</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -12918,6 +12936,9 @@
                   <c:v>10.856999999999999</c:v>
                 </c:pt>
                 <c:pt idx="287">
+                  <c:v>10.856999999999999</c:v>
+                </c:pt>
+                <c:pt idx="288">
                   <c:v>10.856999999999999</c:v>
                 </c:pt>
               </c:numCache>
@@ -13197,7 +13218,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -14056,7 +14077,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -16703,14 +16724,14 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:Y291"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="13" width="9" style="11"/>
-    <col min="14" max="14" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.5" style="11" bestFit="1" customWidth="1"/>
     <col min="15" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -39049,6 +39070,69 @@
       </c>
       <c r="D291" s="10" t="s">
         <v>53</v>
+      </c>
+      <c r="E291" s="11">
+        <v>57</v>
+      </c>
+      <c r="F291" s="11">
+        <v>30.5</v>
+      </c>
+      <c r="G291" s="11">
+        <v>45.232999999999997</v>
+      </c>
+      <c r="H291" s="11">
+        <v>25</v>
+      </c>
+      <c r="I291" s="11">
+        <v>22</v>
+      </c>
+      <c r="J291" s="11">
+        <v>23.2</v>
+      </c>
+      <c r="K291" s="11">
+        <v>80</v>
+      </c>
+      <c r="L291" s="11">
+        <v>37.5</v>
+      </c>
+      <c r="M291" s="11">
+        <v>68.125</v>
+      </c>
+      <c r="N291" s="11">
+        <v>12.3</v>
+      </c>
+      <c r="O291" s="11">
+        <v>10.5</v>
+      </c>
+      <c r="P291" s="11">
+        <v>11.975</v>
+      </c>
+      <c r="Q291" s="11">
+        <v>56</v>
+      </c>
+      <c r="R291" s="11">
+        <v>18.8</v>
+      </c>
+      <c r="S291" s="11">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="T291" s="11">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="U291" s="11">
+        <v>3.9</v>
+      </c>
+      <c r="V291" s="11">
+        <v>4.5190000000000001</v>
+      </c>
+      <c r="W291" s="11">
+        <v>16</v>
+      </c>
+      <c r="X291" s="11">
+        <v>6.3</v>
+      </c>
+      <c r="Y291" s="11">
+        <v>10.856999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -39068,21 +39152,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:AK8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1640625" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.1640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5" style="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.44140625" style="11" customWidth="1"/>
-    <col min="9" max="9" width="9.77734375" style="11" customWidth="1"/>
+    <col min="7" max="7" width="9.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.5" style="11" customWidth="1"/>
+    <col min="9" max="9" width="9.83203125" style="11" customWidth="1"/>
     <col min="10" max="10" width="10.33203125" style="11" customWidth="1"/>
-    <col min="11" max="11" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.5" style="11" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" style="11"/>
-    <col min="13" max="13" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.5" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -39714,17 +39798,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:Y24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1640625" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="15"/>
-    <col min="7" max="7" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.44140625" style="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5" style="15" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="15"/>
-    <col min="10" max="10" width="11.77734375" style="11" customWidth="1"/>
+    <col min="10" max="10" width="11.83203125" style="11" customWidth="1"/>
     <col min="11" max="12" width="9" style="15"/>
     <col min="13" max="13" width="13.33203125" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
@@ -40796,13 +40880,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:Y24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.1640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.1640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.5" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -41665,7 +41749,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="16384" width="9" style="3"/>
   </cols>
@@ -41680,11 +41764,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="22.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.77734375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="22.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.83203125" style="3" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data/industry/TrendForce/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21E1220A-862A-094B-B1B5-DA5540B1F345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAF15D21-2B7A-43F8-8C8D-A70906FCBD04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24360" yWindow="600" windowWidth="26840" windowHeight="22820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -243,11 +243,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="6">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
     <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="168" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -327,13 +329,14 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -379,10 +382,15 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="3">
+    <cellStyle name="쉼표" xfId="2" builtinId="3"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -400,7 +408,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1319,6 +1327,15 @@
                 <c:pt idx="288">
                   <c:v>46189</c:v>
                 </c:pt>
+                <c:pt idx="289">
+                  <c:v>46190</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>46190</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>46190</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2194,6 +2211,12 @@
                 </c:pt>
                 <c:pt idx="288">
                   <c:v>45.232999999999997</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>45.4</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>45.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3107,6 +3130,15 @@
                 <c:pt idx="288">
                   <c:v>46189</c:v>
                 </c:pt>
+                <c:pt idx="289">
+                  <c:v>46190</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>46190</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>46190</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3981,6 +4013,12 @@
                   <c:v>23.2</c:v>
                 </c:pt>
                 <c:pt idx="288">
+                  <c:v>23.2</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>23.2</c:v>
+                </c:pt>
+                <c:pt idx="290">
                   <c:v>23.2</c:v>
                 </c:pt>
               </c:numCache>
@@ -4895,6 +4933,15 @@
                 <c:pt idx="288">
                   <c:v>46189</c:v>
                 </c:pt>
+                <c:pt idx="289">
+                  <c:v>46190</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>46190</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>46190</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5770,6 +5817,12 @@
                 </c:pt>
                 <c:pt idx="288">
                   <c:v>68.125</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>68.5</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>68.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6683,6 +6736,15 @@
                 <c:pt idx="288">
                   <c:v>46189</c:v>
                 </c:pt>
+                <c:pt idx="289">
+                  <c:v>46190</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>46190</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>46190</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7558,6 +7620,12 @@
                 </c:pt>
                 <c:pt idx="288">
                   <c:v>11.975</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>11.975</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>11.875</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8471,6 +8539,15 @@
                 <c:pt idx="288">
                   <c:v>46189</c:v>
                 </c:pt>
+                <c:pt idx="289">
+                  <c:v>46190</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>46190</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>46190</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9345,6 +9422,12 @@
                   <c:v>35.799999999999997</c:v>
                 </c:pt>
                 <c:pt idx="288">
+                  <c:v>35.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>35.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="290">
                   <c:v>35.799999999999997</c:v>
                 </c:pt>
               </c:numCache>
@@ -10275,6 +10358,15 @@
                 <c:pt idx="288">
                   <c:v>46189</c:v>
                 </c:pt>
+                <c:pt idx="289">
+                  <c:v>46190</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>46190</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>46190</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -11150,6 +11242,12 @@
                 </c:pt>
                 <c:pt idx="288">
                   <c:v>4.5190000000000001</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>4.476</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>4.476</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12065,6 +12163,15 @@
                 <c:pt idx="288">
                   <c:v>46189</c:v>
                 </c:pt>
+                <c:pt idx="289">
+                  <c:v>46190</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>46190</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>46190</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -12940,6 +13047,12 @@
                 </c:pt>
                 <c:pt idx="288">
                   <c:v>10.856999999999999</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>10.952</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>10.952</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12994,14 +13107,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
@@ -13054,14 +13167,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
@@ -13077,7 +13190,7 @@
         <c:axId val="1583758912"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="11"/>
+          <c:max val="12"/>
           <c:min val="4"/>
         </c:scaling>
         <c:delete val="0"/>
@@ -13098,14 +13211,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
@@ -13157,14 +13270,14 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
                   <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:latin typeface="+mn-lt"/>
               <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
@@ -13199,8 +13312,8 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr>
-          <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+        <a:defRPr sz="1050">
+          <a:latin typeface="+mn-lt"/>
           <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
         </a:defRPr>
       </a:pPr>
@@ -13218,7 +13331,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -13244,7 +13357,7 @@
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>DDR5 UDIMM 16GB 4800/5600</c:v>
+                  <c:v> DDR5 UDIMM 16GB 4800/5600 </c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v> Average </c:v>
@@ -13343,7 +13456,7 @@
             <c:numRef>
               <c:f>Module!$G$3:$G$1121</c:f>
               <c:numCache>
-                <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:formatCode>_(* #,##0.0_);_(* \(#,##0.0\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="1119"/>
                 <c:pt idx="0">
                   <c:v>157.5</c:v>
@@ -13632,7 +13745,7 @@
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>DDR5 RDIMM 32GB 4800/5600</c:v>
+                  <c:v> DDR5 RDIMM 32GB 4800/5600 </c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v> Average </c:v>
@@ -13731,7 +13844,7 @@
             <c:numRef>
               <c:f>Module!$J$3:$J$1121</c:f>
               <c:numCache>
-                <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:formatCode>_(* #,##0.0_);_(* \(#,##0.0\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="1119"/>
                 <c:pt idx="0">
                   <c:v>480</c:v>
@@ -13853,14 +13966,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
@@ -13914,14 +14027,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
@@ -13957,14 +14070,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
@@ -14016,14 +14129,14 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
                   <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:latin typeface="+mn-lt"/>
               <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
@@ -14058,8 +14171,8 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr>
-          <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+        <a:defRPr sz="1050">
+          <a:latin typeface="+mn-lt"/>
           <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
         </a:defRPr>
       </a:pPr>
@@ -14077,7 +14190,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -14509,14 +14622,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
@@ -14570,14 +14683,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
@@ -14612,14 +14725,14 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
                   <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:latin typeface="+mn-lt"/>
               <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
@@ -14654,8 +14767,8 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr>
-          <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+        <a:defRPr sz="1050">
+          <a:latin typeface="+mn-lt"/>
           <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
         </a:defRPr>
       </a:pPr>
@@ -16723,15 +16836,15 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y291"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <dimension ref="A1:Y294"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="13" width="9" style="11"/>
-    <col min="14" max="14" width="9.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="15" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -39133,6 +39246,174 @@
       </c>
       <c r="Y291" s="11">
         <v>10.856999999999999</v>
+      </c>
+    </row>
+    <row r="292" spans="1:25">
+      <c r="A292" s="8">
+        <v>46190</v>
+      </c>
+      <c r="B292" s="8">
+        <v>46190</v>
+      </c>
+      <c r="C292" s="9">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D292" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E292" s="11">
+        <v>58</v>
+      </c>
+      <c r="F292" s="11">
+        <v>30.5</v>
+      </c>
+      <c r="G292" s="11">
+        <v>45.4</v>
+      </c>
+      <c r="H292" s="11">
+        <v>25</v>
+      </c>
+      <c r="I292" s="11">
+        <v>22</v>
+      </c>
+      <c r="J292" s="11">
+        <v>23.2</v>
+      </c>
+      <c r="K292" s="11">
+        <v>80</v>
+      </c>
+      <c r="L292" s="11">
+        <v>37.5</v>
+      </c>
+      <c r="M292" s="11">
+        <v>68.5</v>
+      </c>
+      <c r="N292" s="11">
+        <v>12.3</v>
+      </c>
+      <c r="O292" s="11">
+        <v>10.5</v>
+      </c>
+      <c r="P292" s="11">
+        <v>11.975</v>
+      </c>
+      <c r="Q292" s="11">
+        <v>56</v>
+      </c>
+      <c r="R292" s="11">
+        <v>18.8</v>
+      </c>
+      <c r="S292" s="11">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="T292" s="11">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="U292" s="11">
+        <v>3.9</v>
+      </c>
+      <c r="V292" s="11">
+        <v>4.476</v>
+      </c>
+      <c r="W292" s="11">
+        <v>16</v>
+      </c>
+      <c r="X292" s="11">
+        <v>6.3</v>
+      </c>
+      <c r="Y292" s="11">
+        <v>10.952</v>
+      </c>
+    </row>
+    <row r="293" spans="1:25">
+      <c r="A293" s="8">
+        <v>46190</v>
+      </c>
+      <c r="B293" s="8">
+        <v>46190</v>
+      </c>
+      <c r="C293" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D293" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E293" s="11">
+        <v>58</v>
+      </c>
+      <c r="F293" s="11">
+        <v>30.5</v>
+      </c>
+      <c r="G293" s="11">
+        <v>45.4</v>
+      </c>
+      <c r="H293" s="11">
+        <v>25</v>
+      </c>
+      <c r="I293" s="11">
+        <v>22</v>
+      </c>
+      <c r="J293" s="11">
+        <v>23.2</v>
+      </c>
+      <c r="K293" s="11">
+        <v>80</v>
+      </c>
+      <c r="L293" s="11">
+        <v>37.5</v>
+      </c>
+      <c r="M293" s="11">
+        <v>68.5</v>
+      </c>
+      <c r="N293" s="11">
+        <v>12.3</v>
+      </c>
+      <c r="O293" s="11">
+        <v>10.5</v>
+      </c>
+      <c r="P293" s="11">
+        <v>11.875</v>
+      </c>
+      <c r="Q293" s="11">
+        <v>56</v>
+      </c>
+      <c r="R293" s="11">
+        <v>18.8</v>
+      </c>
+      <c r="S293" s="11">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="T293" s="11">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="U293" s="11">
+        <v>3.9</v>
+      </c>
+      <c r="V293" s="11">
+        <v>4.476</v>
+      </c>
+      <c r="W293" s="11">
+        <v>16</v>
+      </c>
+      <c r="X293" s="11">
+        <v>6.3</v>
+      </c>
+      <c r="Y293" s="11">
+        <v>10.952</v>
+      </c>
+    </row>
+    <row r="294" spans="1:25">
+      <c r="A294" s="8">
+        <v>46190</v>
+      </c>
+      <c r="B294" s="8">
+        <v>46190</v>
+      </c>
+      <c r="C294" s="9">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D294" s="10" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -39152,21 +39433,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:AK8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.1640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.21875" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.1640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="9.5" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.5" style="11" customWidth="1"/>
-    <col min="9" max="9" width="9.83203125" style="11" customWidth="1"/>
+    <col min="7" max="7" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.44140625" style="11" customWidth="1"/>
+    <col min="9" max="9" width="9.77734375" style="11" customWidth="1"/>
     <col min="10" max="10" width="10.33203125" style="11" customWidth="1"/>
-    <col min="11" max="11" width="9.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" style="11"/>
-    <col min="13" max="13" width="9.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -39798,17 +40079,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:Y24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.1640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.109375" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.1640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="15"/>
-    <col min="7" max="7" width="9.5" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5" style="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.44140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.44140625" style="15" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="15"/>
-    <col min="10" max="10" width="11.83203125" style="11" customWidth="1"/>
+    <col min="10" max="10" width="11.77734375" style="20" customWidth="1"/>
     <col min="11" max="12" width="9" style="15"/>
     <col min="13" max="13" width="13.33203125" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
@@ -39834,7 +40115,7 @@
       <c r="F1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="19" t="s">
         <v>7</v>
       </c>
       <c r="H1" s="14" t="s">
@@ -39843,7 +40124,7 @@
       <c r="I1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="J1" s="19" t="s">
         <v>8</v>
       </c>
       <c r="K1" s="14" t="s">
@@ -39879,7 +40160,7 @@
       <c r="F2" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="19" t="s">
         <v>56</v>
       </c>
       <c r="H2" s="14" t="s">
@@ -39888,7 +40169,7 @@
       <c r="I2" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="19" t="s">
         <v>56</v>
       </c>
       <c r="K2" s="14" t="s">
@@ -39932,7 +40213,7 @@
       <c r="F3" s="14">
         <v>140</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="19">
         <v>157.5</v>
       </c>
       <c r="H3" s="14">
@@ -39941,7 +40222,7 @@
       <c r="I3" s="14">
         <v>450</v>
       </c>
-      <c r="J3" s="6">
+      <c r="J3" s="19">
         <v>480</v>
       </c>
       <c r="K3" s="14">
@@ -39985,7 +40266,7 @@
       <c r="F4" s="14">
         <v>160</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="19">
         <v>177.5</v>
       </c>
       <c r="H4" s="14">
@@ -39994,7 +40275,7 @@
       <c r="I4" s="14">
         <v>490</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="19">
         <v>545</v>
       </c>
       <c r="K4" s="14">
@@ -40038,7 +40319,7 @@
       <c r="F5" s="14">
         <v>180</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="19">
         <v>215</v>
       </c>
       <c r="H5" s="14">
@@ -40047,7 +40328,7 @@
       <c r="I5" s="14">
         <v>620</v>
       </c>
-      <c r="J5" s="6">
+      <c r="J5" s="19">
         <v>715</v>
       </c>
       <c r="K5" s="14">
@@ -40091,7 +40372,7 @@
       <c r="F6" s="14">
         <v>230</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="19">
         <v>250</v>
       </c>
       <c r="H6" s="14">
@@ -40100,7 +40381,7 @@
       <c r="I6" s="14">
         <v>700</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="19">
         <v>850</v>
       </c>
       <c r="K6" s="14">
@@ -40144,7 +40425,7 @@
       <c r="F7" s="15">
         <v>235</v>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="20">
         <v>250</v>
       </c>
       <c r="H7" s="15">
@@ -40153,7 +40434,7 @@
       <c r="I7" s="15">
         <v>750</v>
       </c>
-      <c r="J7" s="11">
+      <c r="J7" s="20">
         <v>870</v>
       </c>
       <c r="K7" s="15">
@@ -40185,7 +40466,7 @@
       <c r="F8" s="15">
         <v>230</v>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="20">
         <v>245</v>
       </c>
       <c r="H8" s="15">
@@ -40194,7 +40475,7 @@
       <c r="I8" s="15">
         <v>800</v>
       </c>
-      <c r="J8" s="11">
+      <c r="J8" s="20">
         <v>885</v>
       </c>
       <c r="K8" s="15">
@@ -40226,7 +40507,7 @@
       <c r="F9" s="15">
         <v>230</v>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="20">
         <v>245</v>
       </c>
       <c r="H9" s="15">
@@ -40235,7 +40516,7 @@
       <c r="I9" s="15">
         <v>800</v>
       </c>
-      <c r="J9" s="11">
+      <c r="J9" s="20">
         <v>890</v>
       </c>
       <c r="K9" s="15">
@@ -40267,7 +40548,7 @@
       <c r="F10" s="15">
         <v>200</v>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="20">
         <v>240</v>
       </c>
       <c r="H10" s="15">
@@ -40276,7 +40557,7 @@
       <c r="I10" s="15">
         <v>830</v>
       </c>
-      <c r="J10" s="11">
+      <c r="J10" s="20">
         <v>900</v>
       </c>
       <c r="K10" s="15">
@@ -40308,7 +40589,7 @@
       <c r="F11" s="15">
         <v>200</v>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="20">
         <v>230</v>
       </c>
       <c r="H11" s="15">
@@ -40317,7 +40598,7 @@
       <c r="I11" s="15">
         <v>850</v>
       </c>
-      <c r="J11" s="11">
+      <c r="J11" s="20">
         <v>910</v>
       </c>
       <c r="K11" s="15">
@@ -40349,7 +40630,7 @@
       <c r="F12" s="15">
         <v>205</v>
       </c>
-      <c r="G12" s="11">
+      <c r="G12" s="20">
         <v>232.5</v>
       </c>
       <c r="H12" s="15">
@@ -40358,7 +40639,7 @@
       <c r="I12" s="15">
         <v>860</v>
       </c>
-      <c r="J12" s="11">
+      <c r="J12" s="20">
         <v>917.5</v>
       </c>
       <c r="K12" s="15">
@@ -40390,7 +40671,7 @@
       <c r="F13" s="15">
         <v>200</v>
       </c>
-      <c r="G13" s="11">
+      <c r="G13" s="20">
         <v>232.5</v>
       </c>
       <c r="H13" s="15">
@@ -40399,7 +40680,7 @@
       <c r="I13" s="15">
         <v>870</v>
       </c>
-      <c r="J13" s="11">
+      <c r="J13" s="20">
         <v>925</v>
       </c>
       <c r="K13" s="15">
@@ -40431,7 +40712,7 @@
       <c r="F14" s="15">
         <v>220</v>
       </c>
-      <c r="G14" s="11">
+      <c r="G14" s="20">
         <v>242.5</v>
       </c>
       <c r="H14" s="15">
@@ -40440,7 +40721,7 @@
       <c r="I14" s="15">
         <v>880</v>
       </c>
-      <c r="J14" s="11">
+      <c r="J14" s="20">
         <v>935</v>
       </c>
       <c r="K14" s="15">
@@ -40472,7 +40753,7 @@
       <c r="F15" s="15">
         <v>200</v>
       </c>
-      <c r="G15" s="11">
+      <c r="G15" s="20">
         <v>222.5</v>
       </c>
       <c r="H15" s="15">
@@ -40481,7 +40762,7 @@
       <c r="I15" s="15">
         <v>880</v>
       </c>
-      <c r="J15" s="11">
+      <c r="J15" s="20">
         <v>930</v>
       </c>
       <c r="K15" s="15">
@@ -40513,7 +40794,7 @@
       <c r="F16" s="15">
         <v>200</v>
       </c>
-      <c r="G16" s="11">
+      <c r="G16" s="20">
         <v>219</v>
       </c>
       <c r="H16" s="15">
@@ -40522,7 +40803,7 @@
       <c r="I16" s="15">
         <v>900</v>
       </c>
-      <c r="J16" s="11">
+      <c r="J16" s="20">
         <v>975</v>
       </c>
       <c r="K16" s="15">
@@ -40554,7 +40835,7 @@
       <c r="F17" s="15">
         <v>195</v>
       </c>
-      <c r="G17" s="11">
+      <c r="G17" s="20">
         <v>218.5</v>
       </c>
       <c r="H17" s="15">
@@ -40563,7 +40844,7 @@
       <c r="I17" s="15">
         <v>880</v>
       </c>
-      <c r="J17" s="11">
+      <c r="J17" s="20">
         <v>970</v>
       </c>
       <c r="K17" s="15">
@@ -40595,7 +40876,7 @@
       <c r="F18" s="15">
         <v>194</v>
       </c>
-      <c r="G18" s="11">
+      <c r="G18" s="20">
         <v>216</v>
       </c>
       <c r="H18" s="15">
@@ -40604,7 +40885,7 @@
       <c r="I18" s="15">
         <v>850</v>
       </c>
-      <c r="J18" s="11">
+      <c r="J18" s="20">
         <v>960</v>
       </c>
       <c r="K18" s="15">
@@ -40636,7 +40917,7 @@
       <c r="F19" s="15">
         <v>193</v>
       </c>
-      <c r="G19" s="11">
+      <c r="G19" s="20">
         <v>215.5</v>
       </c>
       <c r="H19" s="15">
@@ -40645,7 +40926,7 @@
       <c r="I19" s="15">
         <v>860</v>
       </c>
-      <c r="J19" s="11">
+      <c r="J19" s="20">
         <v>960</v>
       </c>
       <c r="K19" s="15">
@@ -40677,7 +40958,7 @@
       <c r="F20" s="15">
         <v>195</v>
       </c>
-      <c r="G20" s="11">
+      <c r="G20" s="20">
         <v>215</v>
       </c>
       <c r="H20" s="15">
@@ -40686,7 +40967,7 @@
       <c r="I20" s="15">
         <v>900</v>
       </c>
-      <c r="J20" s="11">
+      <c r="J20" s="20">
         <v>975</v>
       </c>
       <c r="K20" s="15">
@@ -40718,7 +40999,7 @@
       <c r="F21" s="15">
         <v>200</v>
       </c>
-      <c r="G21" s="11">
+      <c r="G21" s="20">
         <v>214</v>
       </c>
       <c r="H21" s="15">
@@ -40727,7 +41008,7 @@
       <c r="I21" s="15">
         <v>920</v>
       </c>
-      <c r="J21" s="11">
+      <c r="J21" s="20">
         <v>1020</v>
       </c>
       <c r="K21" s="15">
@@ -40759,7 +41040,7 @@
       <c r="F22" s="15">
         <v>205</v>
       </c>
-      <c r="G22" s="11">
+      <c r="G22" s="20">
         <v>212.5</v>
       </c>
       <c r="H22" s="15">
@@ -40768,7 +41049,7 @@
       <c r="I22" s="15">
         <v>950</v>
       </c>
-      <c r="J22" s="11">
+      <c r="J22" s="20">
         <v>1035</v>
       </c>
       <c r="K22" s="15">
@@ -40800,7 +41081,7 @@
       <c r="F23" s="15">
         <v>203</v>
       </c>
-      <c r="G23" s="11">
+      <c r="G23" s="20">
         <v>211</v>
       </c>
       <c r="H23" s="15">
@@ -40809,7 +41090,7 @@
       <c r="I23" s="15">
         <v>1000</v>
       </c>
-      <c r="J23" s="11">
+      <c r="J23" s="20">
         <v>1075</v>
       </c>
       <c r="K23" s="15">
@@ -40841,7 +41122,7 @@
       <c r="F24" s="15">
         <v>200</v>
       </c>
-      <c r="G24" s="11">
+      <c r="G24" s="20">
         <v>209</v>
       </c>
       <c r="H24" s="15">
@@ -40850,7 +41131,7 @@
       <c r="I24" s="15">
         <v>1200</v>
       </c>
-      <c r="J24" s="11">
+      <c r="J24" s="20">
         <v>1250</v>
       </c>
       <c r="K24" s="15">
@@ -40880,13 +41161,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:Y24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.1640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.1640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.1640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.21875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.21875" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -41749,7 +42030,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="16384" width="9" style="3"/>
   </cols>
@@ -41764,11 +42045,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:D32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="22.83203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.83203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.83203125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="22.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.77734375" style="3" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10118"/>
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data/industry/TrendForce/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAF15D21-2B7A-43F8-8C8D-A70906FCBD04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A574A92-5185-E643-A24E-587D9F58D676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22160" yWindow="600" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -373,6 +373,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -382,15 +386,11 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="쉼표" xfId="2" builtinId="3"/>
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="2" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -408,7 +408,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2218,6 +2218,9 @@
                 <c:pt idx="290">
                   <c:v>45.4</c:v>
                 </c:pt>
+                <c:pt idx="291">
+                  <c:v>45.4</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4021,6 +4024,9 @@
                 <c:pt idx="290">
                   <c:v>23.2</c:v>
                 </c:pt>
+                <c:pt idx="291">
+                  <c:v>23.2</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -5824,6 +5830,9 @@
                 <c:pt idx="290">
                   <c:v>68.5</c:v>
                 </c:pt>
+                <c:pt idx="291">
+                  <c:v>68.5</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -7627,6 +7636,9 @@
                 <c:pt idx="290">
                   <c:v>11.875</c:v>
                 </c:pt>
+                <c:pt idx="291">
+                  <c:v>11.875</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -9428,6 +9440,9 @@
                   <c:v>35.799999999999997</c:v>
                 </c:pt>
                 <c:pt idx="290">
+                  <c:v>35.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="291">
                   <c:v>35.799999999999997</c:v>
                 </c:pt>
               </c:numCache>
@@ -11249,6 +11264,9 @@
                 <c:pt idx="290">
                   <c:v>4.476</c:v>
                 </c:pt>
+                <c:pt idx="291">
+                  <c:v>4.476</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -13052,6 +13070,9 @@
                   <c:v>10.952</c:v>
                 </c:pt>
                 <c:pt idx="290">
+                  <c:v>10.952</c:v>
+                </c:pt>
+                <c:pt idx="291">
                   <c:v>10.952</c:v>
                 </c:pt>
               </c:numCache>
@@ -13331,7 +13352,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -14190,7 +14211,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -16837,29 +16858,29 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:Y294"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="13" width="9" style="11"/>
-    <col min="14" max="14" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.5" style="11" bestFit="1" customWidth="1"/>
     <col min="15" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="5" customFormat="1">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="20" t="s">
         <v>52</v>
       </c>
       <c r="E1" s="4" t="s">
@@ -16927,10 +16948,10 @@
       </c>
     </row>
     <row r="2" spans="1:25">
-      <c r="A2" s="16"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="18"/>
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="20"/>
       <c r="E2" s="6" t="s">
         <v>54</v>
       </c>
@@ -39414,6 +39435,69 @@
       </c>
       <c r="D294" s="10" t="s">
         <v>53</v>
+      </c>
+      <c r="E294" s="11">
+        <v>58</v>
+      </c>
+      <c r="F294" s="11">
+        <v>30.5</v>
+      </c>
+      <c r="G294" s="11">
+        <v>45.4</v>
+      </c>
+      <c r="H294" s="11">
+        <v>25</v>
+      </c>
+      <c r="I294" s="11">
+        <v>22</v>
+      </c>
+      <c r="J294" s="11">
+        <v>23.2</v>
+      </c>
+      <c r="K294" s="11">
+        <v>80</v>
+      </c>
+      <c r="L294" s="11">
+        <v>37.5</v>
+      </c>
+      <c r="M294" s="11">
+        <v>68.5</v>
+      </c>
+      <c r="N294" s="11">
+        <v>12.3</v>
+      </c>
+      <c r="O294" s="11">
+        <v>10.5</v>
+      </c>
+      <c r="P294" s="11">
+        <v>11.875</v>
+      </c>
+      <c r="Q294" s="11">
+        <v>56</v>
+      </c>
+      <c r="R294" s="11">
+        <v>18.8</v>
+      </c>
+      <c r="S294" s="11">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="T294" s="11">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="U294" s="11">
+        <v>3.9</v>
+      </c>
+      <c r="V294" s="11">
+        <v>4.476</v>
+      </c>
+      <c r="W294" s="11">
+        <v>16</v>
+      </c>
+      <c r="X294" s="11">
+        <v>6.3</v>
+      </c>
+      <c r="Y294" s="11">
+        <v>10.952</v>
       </c>
     </row>
   </sheetData>
@@ -39433,36 +39517,36 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:AK8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.21875" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.1640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5" style="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.44140625" style="11" customWidth="1"/>
-    <col min="9" max="9" width="9.77734375" style="11" customWidth="1"/>
+    <col min="7" max="7" width="9.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.5" style="11" customWidth="1"/>
+    <col min="9" max="9" width="9.83203125" style="11" customWidth="1"/>
     <col min="10" max="10" width="10.33203125" style="11" customWidth="1"/>
-    <col min="11" max="11" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.5" style="11" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" style="11"/>
-    <col min="13" max="13" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.5" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" s="5" customFormat="1">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="20" t="s">
         <v>52</v>
       </c>
       <c r="E1" s="6" t="s">
@@ -39542,10 +39626,10 @@
       <c r="AK1" s="12"/>
     </row>
     <row r="2" spans="1:37">
-      <c r="A2" s="16"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="18"/>
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="20"/>
       <c r="E2" s="6" t="s">
         <v>54</v>
       </c>
@@ -40079,17 +40163,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:Y24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1640625" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="15"/>
-    <col min="7" max="7" width="9.44140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.44140625" style="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5" style="17" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5" style="15" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="15"/>
-    <col min="10" max="10" width="11.77734375" style="20" customWidth="1"/>
+    <col min="10" max="10" width="11.83203125" style="17" customWidth="1"/>
     <col min="11" max="12" width="9" style="15"/>
     <col min="13" max="13" width="13.33203125" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
@@ -40097,16 +40181,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="5" customFormat="1">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="20" t="s">
         <v>52</v>
       </c>
       <c r="E1" s="14" t="s">
@@ -40115,7 +40199,7 @@
       <c r="F1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="16" t="s">
         <v>7</v>
       </c>
       <c r="H1" s="14" t="s">
@@ -40124,7 +40208,7 @@
       <c r="I1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="19" t="s">
+      <c r="J1" s="16" t="s">
         <v>8</v>
       </c>
       <c r="K1" s="14" t="s">
@@ -40150,17 +40234,17 @@
       <c r="Y1" s="4"/>
     </row>
     <row r="2" spans="1:25">
-      <c r="A2" s="16"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="18"/>
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="20"/>
       <c r="E2" s="14" t="s">
         <v>54</v>
       </c>
       <c r="F2" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="G2" s="19" t="s">
+      <c r="G2" s="16" t="s">
         <v>56</v>
       </c>
       <c r="H2" s="14" t="s">
@@ -40169,7 +40253,7 @@
       <c r="I2" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="J2" s="19" t="s">
+      <c r="J2" s="16" t="s">
         <v>56</v>
       </c>
       <c r="K2" s="14" t="s">
@@ -40213,7 +40297,7 @@
       <c r="F3" s="14">
         <v>140</v>
       </c>
-      <c r="G3" s="19">
+      <c r="G3" s="16">
         <v>157.5</v>
       </c>
       <c r="H3" s="14">
@@ -40222,7 +40306,7 @@
       <c r="I3" s="14">
         <v>450</v>
       </c>
-      <c r="J3" s="19">
+      <c r="J3" s="16">
         <v>480</v>
       </c>
       <c r="K3" s="14">
@@ -40266,7 +40350,7 @@
       <c r="F4" s="14">
         <v>160</v>
       </c>
-      <c r="G4" s="19">
+      <c r="G4" s="16">
         <v>177.5</v>
       </c>
       <c r="H4" s="14">
@@ -40275,7 +40359,7 @@
       <c r="I4" s="14">
         <v>490</v>
       </c>
-      <c r="J4" s="19">
+      <c r="J4" s="16">
         <v>545</v>
       </c>
       <c r="K4" s="14">
@@ -40319,7 +40403,7 @@
       <c r="F5" s="14">
         <v>180</v>
       </c>
-      <c r="G5" s="19">
+      <c r="G5" s="16">
         <v>215</v>
       </c>
       <c r="H5" s="14">
@@ -40328,7 +40412,7 @@
       <c r="I5" s="14">
         <v>620</v>
       </c>
-      <c r="J5" s="19">
+      <c r="J5" s="16">
         <v>715</v>
       </c>
       <c r="K5" s="14">
@@ -40372,7 +40456,7 @@
       <c r="F6" s="14">
         <v>230</v>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="16">
         <v>250</v>
       </c>
       <c r="H6" s="14">
@@ -40381,7 +40465,7 @@
       <c r="I6" s="14">
         <v>700</v>
       </c>
-      <c r="J6" s="19">
+      <c r="J6" s="16">
         <v>850</v>
       </c>
       <c r="K6" s="14">
@@ -40425,7 +40509,7 @@
       <c r="F7" s="15">
         <v>235</v>
       </c>
-      <c r="G7" s="20">
+      <c r="G7" s="17">
         <v>250</v>
       </c>
       <c r="H7" s="15">
@@ -40434,7 +40518,7 @@
       <c r="I7" s="15">
         <v>750</v>
       </c>
-      <c r="J7" s="20">
+      <c r="J7" s="17">
         <v>870</v>
       </c>
       <c r="K7" s="15">
@@ -40466,7 +40550,7 @@
       <c r="F8" s="15">
         <v>230</v>
       </c>
-      <c r="G8" s="20">
+      <c r="G8" s="17">
         <v>245</v>
       </c>
       <c r="H8" s="15">
@@ -40475,7 +40559,7 @@
       <c r="I8" s="15">
         <v>800</v>
       </c>
-      <c r="J8" s="20">
+      <c r="J8" s="17">
         <v>885</v>
       </c>
       <c r="K8" s="15">
@@ -40507,7 +40591,7 @@
       <c r="F9" s="15">
         <v>230</v>
       </c>
-      <c r="G9" s="20">
+      <c r="G9" s="17">
         <v>245</v>
       </c>
       <c r="H9" s="15">
@@ -40516,7 +40600,7 @@
       <c r="I9" s="15">
         <v>800</v>
       </c>
-      <c r="J9" s="20">
+      <c r="J9" s="17">
         <v>890</v>
       </c>
       <c r="K9" s="15">
@@ -40548,7 +40632,7 @@
       <c r="F10" s="15">
         <v>200</v>
       </c>
-      <c r="G10" s="20">
+      <c r="G10" s="17">
         <v>240</v>
       </c>
       <c r="H10" s="15">
@@ -40557,7 +40641,7 @@
       <c r="I10" s="15">
         <v>830</v>
       </c>
-      <c r="J10" s="20">
+      <c r="J10" s="17">
         <v>900</v>
       </c>
       <c r="K10" s="15">
@@ -40589,7 +40673,7 @@
       <c r="F11" s="15">
         <v>200</v>
       </c>
-      <c r="G11" s="20">
+      <c r="G11" s="17">
         <v>230</v>
       </c>
       <c r="H11" s="15">
@@ -40598,7 +40682,7 @@
       <c r="I11" s="15">
         <v>850</v>
       </c>
-      <c r="J11" s="20">
+      <c r="J11" s="17">
         <v>910</v>
       </c>
       <c r="K11" s="15">
@@ -40630,7 +40714,7 @@
       <c r="F12" s="15">
         <v>205</v>
       </c>
-      <c r="G12" s="20">
+      <c r="G12" s="17">
         <v>232.5</v>
       </c>
       <c r="H12" s="15">
@@ -40639,7 +40723,7 @@
       <c r="I12" s="15">
         <v>860</v>
       </c>
-      <c r="J12" s="20">
+      <c r="J12" s="17">
         <v>917.5</v>
       </c>
       <c r="K12" s="15">
@@ -40671,7 +40755,7 @@
       <c r="F13" s="15">
         <v>200</v>
       </c>
-      <c r="G13" s="20">
+      <c r="G13" s="17">
         <v>232.5</v>
       </c>
       <c r="H13" s="15">
@@ -40680,7 +40764,7 @@
       <c r="I13" s="15">
         <v>870</v>
       </c>
-      <c r="J13" s="20">
+      <c r="J13" s="17">
         <v>925</v>
       </c>
       <c r="K13" s="15">
@@ -40712,7 +40796,7 @@
       <c r="F14" s="15">
         <v>220</v>
       </c>
-      <c r="G14" s="20">
+      <c r="G14" s="17">
         <v>242.5</v>
       </c>
       <c r="H14" s="15">
@@ -40721,7 +40805,7 @@
       <c r="I14" s="15">
         <v>880</v>
       </c>
-      <c r="J14" s="20">
+      <c r="J14" s="17">
         <v>935</v>
       </c>
       <c r="K14" s="15">
@@ -40753,7 +40837,7 @@
       <c r="F15" s="15">
         <v>200</v>
       </c>
-      <c r="G15" s="20">
+      <c r="G15" s="17">
         <v>222.5</v>
       </c>
       <c r="H15" s="15">
@@ -40762,7 +40846,7 @@
       <c r="I15" s="15">
         <v>880</v>
       </c>
-      <c r="J15" s="20">
+      <c r="J15" s="17">
         <v>930</v>
       </c>
       <c r="K15" s="15">
@@ -40794,7 +40878,7 @@
       <c r="F16" s="15">
         <v>200</v>
       </c>
-      <c r="G16" s="20">
+      <c r="G16" s="17">
         <v>219</v>
       </c>
       <c r="H16" s="15">
@@ -40803,7 +40887,7 @@
       <c r="I16" s="15">
         <v>900</v>
       </c>
-      <c r="J16" s="20">
+      <c r="J16" s="17">
         <v>975</v>
       </c>
       <c r="K16" s="15">
@@ -40835,7 +40919,7 @@
       <c r="F17" s="15">
         <v>195</v>
       </c>
-      <c r="G17" s="20">
+      <c r="G17" s="17">
         <v>218.5</v>
       </c>
       <c r="H17" s="15">
@@ -40844,7 +40928,7 @@
       <c r="I17" s="15">
         <v>880</v>
       </c>
-      <c r="J17" s="20">
+      <c r="J17" s="17">
         <v>970</v>
       </c>
       <c r="K17" s="15">
@@ -40876,7 +40960,7 @@
       <c r="F18" s="15">
         <v>194</v>
       </c>
-      <c r="G18" s="20">
+      <c r="G18" s="17">
         <v>216</v>
       </c>
       <c r="H18" s="15">
@@ -40885,7 +40969,7 @@
       <c r="I18" s="15">
         <v>850</v>
       </c>
-      <c r="J18" s="20">
+      <c r="J18" s="17">
         <v>960</v>
       </c>
       <c r="K18" s="15">
@@ -40917,7 +41001,7 @@
       <c r="F19" s="15">
         <v>193</v>
       </c>
-      <c r="G19" s="20">
+      <c r="G19" s="17">
         <v>215.5</v>
       </c>
       <c r="H19" s="15">
@@ -40926,7 +41010,7 @@
       <c r="I19" s="15">
         <v>860</v>
       </c>
-      <c r="J19" s="20">
+      <c r="J19" s="17">
         <v>960</v>
       </c>
       <c r="K19" s="15">
@@ -40958,7 +41042,7 @@
       <c r="F20" s="15">
         <v>195</v>
       </c>
-      <c r="G20" s="20">
+      <c r="G20" s="17">
         <v>215</v>
       </c>
       <c r="H20" s="15">
@@ -40967,7 +41051,7 @@
       <c r="I20" s="15">
         <v>900</v>
       </c>
-      <c r="J20" s="20">
+      <c r="J20" s="17">
         <v>975</v>
       </c>
       <c r="K20" s="15">
@@ -40999,7 +41083,7 @@
       <c r="F21" s="15">
         <v>200</v>
       </c>
-      <c r="G21" s="20">
+      <c r="G21" s="17">
         <v>214</v>
       </c>
       <c r="H21" s="15">
@@ -41008,7 +41092,7 @@
       <c r="I21" s="15">
         <v>920</v>
       </c>
-      <c r="J21" s="20">
+      <c r="J21" s="17">
         <v>1020</v>
       </c>
       <c r="K21" s="15">
@@ -41040,7 +41124,7 @@
       <c r="F22" s="15">
         <v>205</v>
       </c>
-      <c r="G22" s="20">
+      <c r="G22" s="17">
         <v>212.5</v>
       </c>
       <c r="H22" s="15">
@@ -41049,7 +41133,7 @@
       <c r="I22" s="15">
         <v>950</v>
       </c>
-      <c r="J22" s="20">
+      <c r="J22" s="17">
         <v>1035</v>
       </c>
       <c r="K22" s="15">
@@ -41081,7 +41165,7 @@
       <c r="F23" s="15">
         <v>203</v>
       </c>
-      <c r="G23" s="20">
+      <c r="G23" s="17">
         <v>211</v>
       </c>
       <c r="H23" s="15">
@@ -41090,7 +41174,7 @@
       <c r="I23" s="15">
         <v>1000</v>
       </c>
-      <c r="J23" s="20">
+      <c r="J23" s="17">
         <v>1075</v>
       </c>
       <c r="K23" s="15">
@@ -41122,7 +41206,7 @@
       <c r="F24" s="15">
         <v>200</v>
       </c>
-      <c r="G24" s="20">
+      <c r="G24" s="17">
         <v>209</v>
       </c>
       <c r="H24" s="15">
@@ -41131,7 +41215,7 @@
       <c r="I24" s="15">
         <v>1200</v>
       </c>
-      <c r="J24" s="20">
+      <c r="J24" s="17">
         <v>1250</v>
       </c>
       <c r="K24" s="15">
@@ -41161,28 +41245,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:Y24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.21875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.21875" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.1640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.5" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="5" customFormat="1">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="20" t="s">
         <v>52</v>
       </c>
       <c r="E1" s="13" t="s">
@@ -41220,10 +41304,10 @@
       <c r="Y1" s="4"/>
     </row>
     <row r="2" spans="1:25">
-      <c r="A2" s="18"/>
-      <c r="B2" s="18"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="18"/>
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="20"/>
       <c r="E2" s="6" t="s">
         <v>54</v>
       </c>
@@ -42030,7 +42114,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="16384" width="9" style="3"/>
   </cols>
@@ -42045,11 +42129,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="22.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.77734375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="22.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.83203125" style="3" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data/industry/TrendForce/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A574A92-5185-E643-A24E-587D9F58D676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD1EC142-5923-443E-A29D-870838302A5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22160" yWindow="600" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -20,17 +20,26 @@
     <sheet name="fig" sheetId="6" r:id="rId5"/>
     <sheet name="info" sheetId="1" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -329,14 +338,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -377,6 +387,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -387,10 +398,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="Comma" xfId="2" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="4">
+    <cellStyle name="백분율" xfId="3" builtinId="5"/>
+    <cellStyle name="쉼표" xfId="2" builtinId="3"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -408,7 +420,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1336,6 +1348,15 @@
                 <c:pt idx="291">
                   <c:v>46190</c:v>
                 </c:pt>
+                <c:pt idx="292">
+                  <c:v>46191</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>46191</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>46191</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2220,6 +2241,12 @@
                 </c:pt>
                 <c:pt idx="291">
                   <c:v>45.4</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>45.832999999999998</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>46</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3142,6 +3169,15 @@
                 <c:pt idx="291">
                   <c:v>46190</c:v>
                 </c:pt>
+                <c:pt idx="292">
+                  <c:v>46191</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>46191</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>46191</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4026,6 +4062,12 @@
                 </c:pt>
                 <c:pt idx="291">
                   <c:v>23.2</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>23.5</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>23.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4948,6 +4990,15 @@
                 <c:pt idx="291">
                   <c:v>46190</c:v>
                 </c:pt>
+                <c:pt idx="292">
+                  <c:v>46191</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>46191</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>46191</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5832,6 +5883,12 @@
                 </c:pt>
                 <c:pt idx="291">
                   <c:v>68.5</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>69</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>69.125</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6754,6 +6811,15 @@
                 <c:pt idx="291">
                   <c:v>46190</c:v>
                 </c:pt>
+                <c:pt idx="292">
+                  <c:v>46191</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>46191</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>46191</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7638,6 +7704,12 @@
                 </c:pt>
                 <c:pt idx="291">
                   <c:v>11.875</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>11.8</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>11.8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8560,6 +8632,15 @@
                 <c:pt idx="291">
                   <c:v>46190</c:v>
                 </c:pt>
+                <c:pt idx="292">
+                  <c:v>46191</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>46191</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>46191</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9444,6 +9525,12 @@
                 </c:pt>
                 <c:pt idx="291">
                   <c:v>35.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>35.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>35.9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10382,6 +10469,15 @@
                 <c:pt idx="291">
                   <c:v>46190</c:v>
                 </c:pt>
+                <c:pt idx="292">
+                  <c:v>46191</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>46191</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>46191</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -11266,6 +11362,12 @@
                 </c:pt>
                 <c:pt idx="291">
                   <c:v>4.476</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>4.45</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>4.45</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12190,6 +12292,15 @@
                 <c:pt idx="291">
                   <c:v>46190</c:v>
                 </c:pt>
+                <c:pt idx="292">
+                  <c:v>46191</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>46191</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>46191</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13074,6 +13185,12 @@
                 </c:pt>
                 <c:pt idx="291">
                   <c:v>10.952</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>10.976000000000001</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>10.976000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13352,7 +13469,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -14211,7 +14328,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -16857,30 +16974,30 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y294"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <dimension ref="A1:Z297"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="13" width="9" style="11"/>
-    <col min="14" max="14" width="9.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="15" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:26" s="5" customFormat="1">
+      <c r="A1" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="21" t="s">
         <v>52</v>
       </c>
       <c r="E1" s="4" t="s">
@@ -16947,11 +17064,11 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
-      <c r="A2" s="18"/>
-      <c r="B2" s="18"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="20"/>
+    <row r="2" spans="1:26">
+      <c r="A2" s="19"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="21"/>
       <c r="E2" s="6" t="s">
         <v>54</v>
       </c>
@@ -17016,7 +17133,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:26">
       <c r="A3" s="8">
         <v>46044</v>
       </c>
@@ -17093,7 +17210,7 @@
         <v>4.9450000000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:26">
       <c r="A4" s="8">
         <v>46045</v>
       </c>
@@ -17169,8 +17286,9 @@
       <c r="Y4" s="6">
         <v>5.0250000000000004</v>
       </c>
+      <c r="Z4" s="18"/>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:26">
       <c r="A5" s="8">
         <v>46045</v>
       </c>
@@ -17246,8 +17364,9 @@
       <c r="Y5" s="11">
         <v>5.0250000000000004</v>
       </c>
+      <c r="Z5" s="18"/>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:26">
       <c r="A6" s="8">
         <v>46045</v>
       </c>
@@ -17323,8 +17442,9 @@
       <c r="Y6" s="11">
         <v>5.0250000000000004</v>
       </c>
+      <c r="Z6" s="18"/>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:26">
       <c r="A7" s="8">
         <v>46048</v>
       </c>
@@ -17400,8 +17520,9 @@
       <c r="Y7" s="11">
         <v>5.1479999999999997</v>
       </c>
+      <c r="Z7" s="18"/>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:26">
       <c r="A8" s="8">
         <v>46048</v>
       </c>
@@ -17477,8 +17598,9 @@
       <c r="Y8" s="11">
         <v>5.1479999999999997</v>
       </c>
+      <c r="Z8" s="18"/>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:26">
       <c r="A9" s="8">
         <v>46048</v>
       </c>
@@ -17554,8 +17676,9 @@
       <c r="Y9" s="11">
         <v>5.1479999999999997</v>
       </c>
+      <c r="Z9" s="18"/>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:26">
       <c r="A10" s="8">
         <v>46049</v>
       </c>
@@ -17631,8 +17754,9 @@
       <c r="Y10" s="11">
         <v>5.17</v>
       </c>
+      <c r="Z10" s="18"/>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:26">
       <c r="A11" s="8">
         <v>46049</v>
       </c>
@@ -17708,8 +17832,9 @@
       <c r="Y11" s="11">
         <v>5.17</v>
       </c>
+      <c r="Z11" s="18"/>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:26">
       <c r="A12" s="8">
         <v>46049</v>
       </c>
@@ -17785,8 +17910,9 @@
       <c r="Y12" s="11">
         <v>5.17</v>
       </c>
+      <c r="Z12" s="18"/>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:26">
       <c r="A13" s="8">
         <v>46050</v>
       </c>
@@ -17862,8 +17988,9 @@
       <c r="Y13" s="11">
         <v>5.2089999999999996</v>
       </c>
+      <c r="Z13" s="18"/>
     </row>
-    <row r="14" spans="1:25">
+    <row r="14" spans="1:26">
       <c r="A14" s="8">
         <v>46050</v>
       </c>
@@ -17939,8 +18066,9 @@
       <c r="Y14" s="11">
         <v>5.2089999999999996</v>
       </c>
+      <c r="Z14" s="18"/>
     </row>
-    <row r="15" spans="1:25">
+    <row r="15" spans="1:26">
       <c r="A15" s="8">
         <v>46050</v>
       </c>
@@ -18016,8 +18144,9 @@
       <c r="Y15" s="11">
         <v>5.2089999999999996</v>
       </c>
+      <c r="Z15" s="18"/>
     </row>
-    <row r="16" spans="1:25">
+    <row r="16" spans="1:26">
       <c r="A16" s="8">
         <v>46051</v>
       </c>
@@ -18093,8 +18222,9 @@
       <c r="Y16" s="11">
         <v>5.3319999999999999</v>
       </c>
+      <c r="Z16" s="18"/>
     </row>
-    <row r="17" spans="1:25">
+    <row r="17" spans="1:26">
       <c r="A17" s="8">
         <v>46051</v>
       </c>
@@ -18170,8 +18300,9 @@
       <c r="Y17" s="11">
         <v>5.3319999999999999</v>
       </c>
+      <c r="Z17" s="18"/>
     </row>
-    <row r="18" spans="1:25">
+    <row r="18" spans="1:26">
       <c r="A18" s="8">
         <v>46051</v>
       </c>
@@ -18247,8 +18378,9 @@
       <c r="Y18" s="11">
         <v>5.3319999999999999</v>
       </c>
+      <c r="Z18" s="18"/>
     </row>
-    <row r="19" spans="1:25">
+    <row r="19" spans="1:26">
       <c r="A19" s="8">
         <v>46052</v>
       </c>
@@ -18324,8 +18456,9 @@
       <c r="Y19" s="11">
         <v>5.4</v>
       </c>
+      <c r="Z19" s="18"/>
     </row>
-    <row r="20" spans="1:25">
+    <row r="20" spans="1:26">
       <c r="A20" s="8">
         <v>46052</v>
       </c>
@@ -18401,8 +18534,9 @@
       <c r="Y20" s="11">
         <v>5.4</v>
       </c>
+      <c r="Z20" s="18"/>
     </row>
-    <row r="21" spans="1:25">
+    <row r="21" spans="1:26">
       <c r="A21" s="8">
         <v>46052</v>
       </c>
@@ -18478,8 +18612,9 @@
       <c r="Y21" s="11">
         <v>5.4</v>
       </c>
+      <c r="Z21" s="18"/>
     </row>
-    <row r="22" spans="1:25">
+    <row r="22" spans="1:26">
       <c r="A22" s="8">
         <v>46055</v>
       </c>
@@ -18555,8 +18690,9 @@
       <c r="Y22" s="11">
         <v>5.4</v>
       </c>
+      <c r="Z22" s="18"/>
     </row>
-    <row r="23" spans="1:25">
+    <row r="23" spans="1:26">
       <c r="A23" s="8">
         <v>46055</v>
       </c>
@@ -18632,8 +18768,9 @@
       <c r="Y23" s="11">
         <v>5.4</v>
       </c>
+      <c r="Z23" s="18"/>
     </row>
-    <row r="24" spans="1:25">
+    <row r="24" spans="1:26">
       <c r="A24" s="8">
         <v>46055</v>
       </c>
@@ -18709,8 +18846,9 @@
       <c r="Y24" s="11">
         <v>5.4</v>
       </c>
+      <c r="Z24" s="18"/>
     </row>
-    <row r="25" spans="1:25">
+    <row r="25" spans="1:26">
       <c r="A25" s="8">
         <v>46056</v>
       </c>
@@ -18786,8 +18924,9 @@
       <c r="Y25" s="11">
         <v>5.4</v>
       </c>
+      <c r="Z25" s="18"/>
     </row>
-    <row r="26" spans="1:25">
+    <row r="26" spans="1:26">
       <c r="A26" s="8">
         <v>46056</v>
       </c>
@@ -18863,8 +19002,9 @@
       <c r="Y26" s="11">
         <v>5.4</v>
       </c>
+      <c r="Z26" s="18"/>
     </row>
-    <row r="27" spans="1:25">
+    <row r="27" spans="1:26">
       <c r="A27" s="8">
         <v>46056</v>
       </c>
@@ -18940,8 +19080,9 @@
       <c r="Y27" s="11">
         <v>5.4</v>
       </c>
+      <c r="Z27" s="18"/>
     </row>
-    <row r="28" spans="1:25">
+    <row r="28" spans="1:26">
       <c r="A28" s="8">
         <v>46057</v>
       </c>
@@ -19017,8 +19158,9 @@
       <c r="Y28" s="11">
         <v>5.468</v>
       </c>
+      <c r="Z28" s="18"/>
     </row>
-    <row r="29" spans="1:25">
+    <row r="29" spans="1:26">
       <c r="A29" s="8">
         <v>46057</v>
       </c>
@@ -19094,8 +19236,9 @@
       <c r="Y29" s="11">
         <v>5.468</v>
       </c>
+      <c r="Z29" s="18"/>
     </row>
-    <row r="30" spans="1:25">
+    <row r="30" spans="1:26">
       <c r="A30" s="8">
         <v>46057</v>
       </c>
@@ -19171,8 +19314,9 @@
       <c r="Y30" s="11">
         <v>5.468</v>
       </c>
+      <c r="Z30" s="18"/>
     </row>
-    <row r="31" spans="1:25">
+    <row r="31" spans="1:26">
       <c r="A31" s="8">
         <v>46058</v>
       </c>
@@ -19248,8 +19392,9 @@
       <c r="Y31" s="11">
         <v>5.48</v>
       </c>
+      <c r="Z31" s="18"/>
     </row>
-    <row r="32" spans="1:25">
+    <row r="32" spans="1:26">
       <c r="A32" s="8">
         <v>46058</v>
       </c>
@@ -19325,8 +19470,9 @@
       <c r="Y32" s="11">
         <v>5.48</v>
       </c>
+      <c r="Z32" s="18"/>
     </row>
-    <row r="33" spans="1:25">
+    <row r="33" spans="1:26">
       <c r="A33" s="8">
         <v>46058</v>
       </c>
@@ -19402,8 +19548,9 @@
       <c r="Y33" s="11">
         <v>5.48</v>
       </c>
+      <c r="Z33" s="18"/>
     </row>
-    <row r="34" spans="1:25">
+    <row r="34" spans="1:26">
       <c r="A34" s="8">
         <v>46059</v>
       </c>
@@ -19479,8 +19626,9 @@
       <c r="Y34" s="11">
         <v>5.4950000000000001</v>
       </c>
+      <c r="Z34" s="18"/>
     </row>
-    <row r="35" spans="1:25">
+    <row r="35" spans="1:26">
       <c r="A35" s="8">
         <v>46059</v>
       </c>
@@ -19556,8 +19704,9 @@
       <c r="Y35" s="11">
         <v>5.4950000000000001</v>
       </c>
+      <c r="Z35" s="18"/>
     </row>
-    <row r="36" spans="1:25">
+    <row r="36" spans="1:26">
       <c r="A36" s="8">
         <v>46059</v>
       </c>
@@ -19633,8 +19782,9 @@
       <c r="Y36" s="11">
         <v>5.4950000000000001</v>
       </c>
+      <c r="Z36" s="18"/>
     </row>
-    <row r="37" spans="1:25">
+    <row r="37" spans="1:26">
       <c r="A37" s="8">
         <v>46062</v>
       </c>
@@ -19710,8 +19860,9 @@
       <c r="Y37" s="11">
         <v>5.5069999999999997</v>
       </c>
+      <c r="Z37" s="18"/>
     </row>
-    <row r="38" spans="1:25">
+    <row r="38" spans="1:26">
       <c r="A38" s="8">
         <v>46062</v>
       </c>
@@ -19787,8 +19938,9 @@
       <c r="Y38" s="11">
         <v>5.5069999999999997</v>
       </c>
+      <c r="Z38" s="18"/>
     </row>
-    <row r="39" spans="1:25">
+    <row r="39" spans="1:26">
       <c r="A39" s="8">
         <v>46062</v>
       </c>
@@ -19864,8 +20016,9 @@
       <c r="Y39" s="11">
         <v>5.5069999999999997</v>
       </c>
+      <c r="Z39" s="18"/>
     </row>
-    <row r="40" spans="1:25">
+    <row r="40" spans="1:26">
       <c r="A40" s="8">
         <v>46063</v>
       </c>
@@ -19941,8 +20094,9 @@
       <c r="Y40" s="11">
         <v>5.5069999999999997</v>
       </c>
+      <c r="Z40" s="18"/>
     </row>
-    <row r="41" spans="1:25">
+    <row r="41" spans="1:26">
       <c r="A41" s="8">
         <v>46063</v>
       </c>
@@ -20018,8 +20172,9 @@
       <c r="Y41" s="11">
         <v>5.5069999999999997</v>
       </c>
+      <c r="Z41" s="18"/>
     </row>
-    <row r="42" spans="1:25">
+    <row r="42" spans="1:26">
       <c r="A42" s="8">
         <v>46063</v>
       </c>
@@ -20095,8 +20250,9 @@
       <c r="Y42" s="11">
         <v>5.5069999999999997</v>
       </c>
+      <c r="Z42" s="18"/>
     </row>
-    <row r="43" spans="1:25">
+    <row r="43" spans="1:26">
       <c r="A43" s="8">
         <v>46064</v>
       </c>
@@ -20172,8 +20328,9 @@
       <c r="Y43" s="11">
         <v>5.5229999999999997</v>
       </c>
+      <c r="Z43" s="18"/>
     </row>
-    <row r="44" spans="1:25">
+    <row r="44" spans="1:26">
       <c r="A44" s="8">
         <v>46064</v>
       </c>
@@ -20249,8 +20406,9 @@
       <c r="Y44" s="11">
         <v>5.5229999999999997</v>
       </c>
+      <c r="Z44" s="18"/>
     </row>
-    <row r="45" spans="1:25">
+    <row r="45" spans="1:26">
       <c r="A45" s="8">
         <v>46064</v>
       </c>
@@ -20326,8 +20484,9 @@
       <c r="Y45" s="11">
         <v>5.5229999999999997</v>
       </c>
+      <c r="Z45" s="18"/>
     </row>
-    <row r="46" spans="1:25">
+    <row r="46" spans="1:26">
       <c r="A46" s="8">
         <v>46065</v>
       </c>
@@ -20403,8 +20562,9 @@
       <c r="Y46" s="11">
         <v>5.5449999999999999</v>
       </c>
+      <c r="Z46" s="18"/>
     </row>
-    <row r="47" spans="1:25">
+    <row r="47" spans="1:26">
       <c r="A47" s="8">
         <v>46065</v>
       </c>
@@ -20480,8 +20640,9 @@
       <c r="Y47" s="11">
         <v>5.5449999999999999</v>
       </c>
+      <c r="Z47" s="18"/>
     </row>
-    <row r="48" spans="1:25">
+    <row r="48" spans="1:26">
       <c r="A48" s="8">
         <v>46065</v>
       </c>
@@ -20557,8 +20718,9 @@
       <c r="Y48" s="11">
         <v>5.5449999999999999</v>
       </c>
+      <c r="Z48" s="18"/>
     </row>
-    <row r="49" spans="1:25">
+    <row r="49" spans="1:26">
       <c r="A49" s="8">
         <v>46066</v>
       </c>
@@ -20634,8 +20796,9 @@
       <c r="Y49" s="11">
         <v>5.5449999999999999</v>
       </c>
+      <c r="Z49" s="18"/>
     </row>
-    <row r="50" spans="1:25">
+    <row r="50" spans="1:26">
       <c r="A50" s="8">
         <v>46066</v>
       </c>
@@ -20711,8 +20874,9 @@
       <c r="Y50" s="11">
         <v>5.5449999999999999</v>
       </c>
+      <c r="Z50" s="18"/>
     </row>
-    <row r="51" spans="1:25">
+    <row r="51" spans="1:26">
       <c r="A51" s="8">
         <v>46066</v>
       </c>
@@ -20788,8 +20952,9 @@
       <c r="Y51" s="11">
         <v>5.5449999999999999</v>
       </c>
+      <c r="Z51" s="18"/>
     </row>
-    <row r="52" spans="1:25">
+    <row r="52" spans="1:26">
       <c r="A52" s="8">
         <v>46076</v>
       </c>
@@ -20865,8 +21030,9 @@
       <c r="Y52" s="11">
         <v>5.5609999999999999</v>
       </c>
+      <c r="Z52" s="18"/>
     </row>
-    <row r="53" spans="1:25">
+    <row r="53" spans="1:26">
       <c r="A53" s="8">
         <v>46076</v>
       </c>
@@ -20942,8 +21108,9 @@
       <c r="Y53" s="11">
         <v>5.5609999999999999</v>
       </c>
+      <c r="Z53" s="18"/>
     </row>
-    <row r="54" spans="1:25">
+    <row r="54" spans="1:26">
       <c r="A54" s="8">
         <v>46076</v>
       </c>
@@ -21019,8 +21186,9 @@
       <c r="Y54" s="11">
         <v>5.5609999999999999</v>
       </c>
+      <c r="Z54" s="18"/>
     </row>
-    <row r="55" spans="1:25">
+    <row r="55" spans="1:26">
       <c r="A55" s="8">
         <v>46077</v>
       </c>
@@ -21096,8 +21264,9 @@
       <c r="Y55" s="11">
         <v>5.5730000000000004</v>
       </c>
+      <c r="Z55" s="18"/>
     </row>
-    <row r="56" spans="1:25">
+    <row r="56" spans="1:26">
       <c r="A56" s="8">
         <v>46077</v>
       </c>
@@ -21173,8 +21342,9 @@
       <c r="Y56" s="11">
         <v>5.5730000000000004</v>
       </c>
+      <c r="Z56" s="18"/>
     </row>
-    <row r="57" spans="1:25">
+    <row r="57" spans="1:26">
       <c r="A57" s="8">
         <v>46077</v>
       </c>
@@ -21250,8 +21420,9 @@
       <c r="Y57" s="11">
         <v>5.5730000000000004</v>
       </c>
+      <c r="Z57" s="18"/>
     </row>
-    <row r="58" spans="1:25">
+    <row r="58" spans="1:26">
       <c r="A58" s="8">
         <v>46078</v>
       </c>
@@ -21327,8 +21498,9 @@
       <c r="Y58" s="11">
         <v>5.5730000000000004</v>
       </c>
+      <c r="Z58" s="18"/>
     </row>
-    <row r="59" spans="1:25">
+    <row r="59" spans="1:26">
       <c r="A59" s="8">
         <v>46078</v>
       </c>
@@ -21404,8 +21576,9 @@
       <c r="Y59" s="11">
         <v>5.5730000000000004</v>
       </c>
+      <c r="Z59" s="18"/>
     </row>
-    <row r="60" spans="1:25">
+    <row r="60" spans="1:26">
       <c r="A60" s="8">
         <v>46078</v>
       </c>
@@ -21481,8 +21654,9 @@
       <c r="Y60" s="11">
         <v>5.5730000000000004</v>
       </c>
+      <c r="Z60" s="18"/>
     </row>
-    <row r="61" spans="1:25">
+    <row r="61" spans="1:26">
       <c r="A61" s="8">
         <v>46079</v>
       </c>
@@ -21558,8 +21732,9 @@
       <c r="Y61" s="11">
         <v>5.5890000000000004</v>
       </c>
+      <c r="Z61" s="18"/>
     </row>
-    <row r="62" spans="1:25">
+    <row r="62" spans="1:26">
       <c r="A62" s="8">
         <v>46079</v>
       </c>
@@ -21635,8 +21810,9 @@
       <c r="Y62" s="11">
         <v>5.5890000000000004</v>
       </c>
+      <c r="Z62" s="18"/>
     </row>
-    <row r="63" spans="1:25">
+    <row r="63" spans="1:26">
       <c r="A63" s="8">
         <v>46079</v>
       </c>
@@ -21712,8 +21888,9 @@
       <c r="Y63" s="11">
         <v>5.5890000000000004</v>
       </c>
+      <c r="Z63" s="18"/>
     </row>
-    <row r="64" spans="1:25">
+    <row r="64" spans="1:26">
       <c r="A64" s="8">
         <v>46080</v>
       </c>
@@ -21789,8 +21966,9 @@
       <c r="Y64" s="11">
         <v>5.5890000000000004</v>
       </c>
+      <c r="Z64" s="18"/>
     </row>
-    <row r="65" spans="1:25">
+    <row r="65" spans="1:26">
       <c r="A65" s="8">
         <v>46080</v>
       </c>
@@ -21866,8 +22044,9 @@
       <c r="Y65" s="11">
         <v>5.5890000000000004</v>
       </c>
+      <c r="Z65" s="18"/>
     </row>
-    <row r="66" spans="1:25">
+    <row r="66" spans="1:26">
       <c r="A66" s="8">
         <v>46080</v>
       </c>
@@ -21943,8 +22122,9 @@
       <c r="Y66" s="11">
         <v>5.5890000000000004</v>
       </c>
+      <c r="Z66" s="18"/>
     </row>
-    <row r="67" spans="1:25">
+    <row r="67" spans="1:26">
       <c r="A67" s="8">
         <v>46083</v>
       </c>
@@ -22020,8 +22200,9 @@
       <c r="Y67" s="11">
         <v>5.5890000000000004</v>
       </c>
+      <c r="Z67" s="18"/>
     </row>
-    <row r="68" spans="1:25">
+    <row r="68" spans="1:26">
       <c r="A68" s="8">
         <v>46083</v>
       </c>
@@ -22097,8 +22278,9 @@
       <c r="Y68" s="11">
         <v>5.5890000000000004</v>
       </c>
+      <c r="Z68" s="18"/>
     </row>
-    <row r="69" spans="1:25">
+    <row r="69" spans="1:26">
       <c r="A69" s="8">
         <v>46083</v>
       </c>
@@ -22174,8 +22356,9 @@
       <c r="Y69" s="11">
         <v>5.68</v>
       </c>
+      <c r="Z69" s="18"/>
     </row>
-    <row r="70" spans="1:25">
+    <row r="70" spans="1:26">
       <c r="A70" s="8">
         <v>46084</v>
       </c>
@@ -22251,8 +22434,9 @@
       <c r="Y70" s="11">
         <v>5.7590000000000003</v>
       </c>
+      <c r="Z70" s="18"/>
     </row>
-    <row r="71" spans="1:25">
+    <row r="71" spans="1:26">
       <c r="A71" s="8">
         <v>46084</v>
       </c>
@@ -22328,8 +22512,9 @@
       <c r="Y71" s="11">
         <v>5.7889999999999997</v>
       </c>
+      <c r="Z71" s="18"/>
     </row>
-    <row r="72" spans="1:25">
+    <row r="72" spans="1:26">
       <c r="A72" s="8">
         <v>46084</v>
       </c>
@@ -22405,8 +22590,9 @@
       <c r="Y72" s="11">
         <v>5.7889999999999997</v>
       </c>
+      <c r="Z72" s="18"/>
     </row>
-    <row r="73" spans="1:25">
+    <row r="73" spans="1:26">
       <c r="A73" s="8">
         <v>46085</v>
       </c>
@@ -22482,8 +22668,9 @@
       <c r="Y73" s="11">
         <v>5.8390000000000004</v>
       </c>
+      <c r="Z73" s="18"/>
     </row>
-    <row r="74" spans="1:25">
+    <row r="74" spans="1:26">
       <c r="A74" s="8">
         <v>46085</v>
       </c>
@@ -22559,8 +22746,9 @@
       <c r="Y74" s="11">
         <v>5.8620000000000001</v>
       </c>
+      <c r="Z74" s="18"/>
     </row>
-    <row r="75" spans="1:25">
+    <row r="75" spans="1:26">
       <c r="A75" s="8">
         <v>46085</v>
       </c>
@@ -22636,8 +22824,9 @@
       <c r="Y75" s="11">
         <v>5.8620000000000001</v>
       </c>
+      <c r="Z75" s="18"/>
     </row>
-    <row r="76" spans="1:25">
+    <row r="76" spans="1:26">
       <c r="A76" s="8">
         <v>46086</v>
       </c>
@@ -22713,8 +22902,9 @@
       <c r="Y76" s="11">
         <v>5.8979999999999997</v>
       </c>
+      <c r="Z76" s="18"/>
     </row>
-    <row r="77" spans="1:25">
+    <row r="77" spans="1:26">
       <c r="A77" s="8">
         <v>46086</v>
       </c>
@@ -22790,8 +22980,9 @@
       <c r="Y77" s="11">
         <v>5.8979999999999997</v>
       </c>
+      <c r="Z77" s="18"/>
     </row>
-    <row r="78" spans="1:25">
+    <row r="78" spans="1:26">
       <c r="A78" s="8">
         <v>46086</v>
       </c>
@@ -22867,8 +23058,9 @@
       <c r="Y78" s="11">
         <v>5.9210000000000003</v>
       </c>
+      <c r="Z78" s="18"/>
     </row>
-    <row r="79" spans="1:25">
+    <row r="79" spans="1:26">
       <c r="A79" s="8">
         <v>46087</v>
       </c>
@@ -22944,8 +23136,9 @@
       <c r="Y79" s="11">
         <v>6.0380000000000003</v>
       </c>
+      <c r="Z79" s="18"/>
     </row>
-    <row r="80" spans="1:25">
+    <row r="80" spans="1:26">
       <c r="A80" s="8">
         <v>46087</v>
       </c>
@@ -23021,8 +23214,9 @@
       <c r="Y80" s="11">
         <v>6.0380000000000003</v>
       </c>
+      <c r="Z80" s="18"/>
     </row>
-    <row r="81" spans="1:25">
+    <row r="81" spans="1:26">
       <c r="A81" s="8">
         <v>46087</v>
       </c>
@@ -23098,8 +23292,9 @@
       <c r="Y81" s="11">
         <v>6.0380000000000003</v>
       </c>
+      <c r="Z81" s="18"/>
     </row>
-    <row r="82" spans="1:25">
+    <row r="82" spans="1:26">
       <c r="A82" s="8">
         <v>46090</v>
       </c>
@@ -23175,8 +23370,9 @@
       <c r="Y82" s="11">
         <v>6.11</v>
       </c>
+      <c r="Z82" s="18"/>
     </row>
-    <row r="83" spans="1:25">
+    <row r="83" spans="1:26">
       <c r="A83" s="8">
         <v>46090</v>
       </c>
@@ -23252,8 +23448,9 @@
       <c r="Y83" s="11">
         <v>6.11</v>
       </c>
+      <c r="Z83" s="18"/>
     </row>
-    <row r="84" spans="1:25">
+    <row r="84" spans="1:26">
       <c r="A84" s="8">
         <v>46090</v>
       </c>
@@ -23329,8 +23526,9 @@
       <c r="Y84" s="11">
         <v>6.11</v>
       </c>
+      <c r="Z84" s="18"/>
     </row>
-    <row r="85" spans="1:25">
+    <row r="85" spans="1:26">
       <c r="A85" s="8">
         <v>46091</v>
       </c>
@@ -23406,8 +23604,9 @@
       <c r="Y85" s="11">
         <v>6.157</v>
       </c>
+      <c r="Z85" s="18"/>
     </row>
-    <row r="86" spans="1:25">
+    <row r="86" spans="1:26">
       <c r="A86" s="8">
         <v>46091</v>
       </c>
@@ -23483,8 +23682,9 @@
       <c r="Y86" s="11">
         <v>6.181</v>
       </c>
+      <c r="Z86" s="18"/>
     </row>
-    <row r="87" spans="1:25">
+    <row r="87" spans="1:26">
       <c r="A87" s="8">
         <v>46091</v>
       </c>
@@ -23560,8 +23760,9 @@
       <c r="Y87" s="11">
         <v>6.181</v>
       </c>
+      <c r="Z87" s="18"/>
     </row>
-    <row r="88" spans="1:25">
+    <row r="88" spans="1:26">
       <c r="A88" s="8">
         <v>46092</v>
       </c>
@@ -23637,8 +23838,9 @@
       <c r="Y88" s="11">
         <v>6.2430000000000003</v>
       </c>
+      <c r="Z88" s="18"/>
     </row>
-    <row r="89" spans="1:25">
+    <row r="89" spans="1:26">
       <c r="A89" s="8">
         <v>46092</v>
       </c>
@@ -23714,8 +23916,9 @@
       <c r="Y89" s="11">
         <v>6.29</v>
       </c>
+      <c r="Z89" s="18"/>
     </row>
-    <row r="90" spans="1:25">
+    <row r="90" spans="1:26">
       <c r="A90" s="8">
         <v>46092</v>
       </c>
@@ -23791,8 +23994,9 @@
       <c r="Y90" s="11">
         <v>6.3049999999999997</v>
       </c>
+      <c r="Z90" s="18"/>
     </row>
-    <row r="91" spans="1:25">
+    <row r="91" spans="1:26">
       <c r="A91" s="8">
         <v>46093</v>
       </c>
@@ -23868,8 +24072,9 @@
       <c r="Y91" s="11">
         <v>6.3810000000000002</v>
       </c>
+      <c r="Z91" s="18"/>
     </row>
-    <row r="92" spans="1:25">
+    <row r="92" spans="1:26">
       <c r="A92" s="8">
         <v>46093</v>
       </c>
@@ -23945,8 +24150,9 @@
       <c r="Y92" s="11">
         <v>6.3810000000000002</v>
       </c>
+      <c r="Z92" s="18"/>
     </row>
-    <row r="93" spans="1:25">
+    <row r="93" spans="1:26">
       <c r="A93" s="8">
         <v>46093</v>
       </c>
@@ -24022,8 +24228,9 @@
       <c r="Y93" s="11">
         <v>6.3810000000000002</v>
       </c>
+      <c r="Z93" s="18"/>
     </row>
-    <row r="94" spans="1:25">
+    <row r="94" spans="1:26">
       <c r="A94" s="8">
         <v>46094</v>
       </c>
@@ -24099,8 +24306,9 @@
       <c r="Y94" s="11">
         <v>6.4379999999999997</v>
       </c>
+      <c r="Z94" s="18"/>
     </row>
-    <row r="95" spans="1:25">
+    <row r="95" spans="1:26">
       <c r="A95" s="8">
         <v>46094</v>
       </c>
@@ -24176,8 +24384,9 @@
       <c r="Y95" s="11">
         <v>6.4379999999999997</v>
       </c>
+      <c r="Z95" s="18"/>
     </row>
-    <row r="96" spans="1:25">
+    <row r="96" spans="1:26">
       <c r="A96" s="8">
         <v>46094</v>
       </c>
@@ -24253,8 +24462,9 @@
       <c r="Y96" s="11">
         <v>6.4379999999999997</v>
       </c>
+      <c r="Z96" s="18"/>
     </row>
-    <row r="97" spans="1:25">
+    <row r="97" spans="1:26">
       <c r="A97" s="8">
         <v>46097</v>
       </c>
@@ -24330,8 +24540,9 @@
       <c r="Y97" s="11">
         <v>6.5330000000000004</v>
       </c>
+      <c r="Z97" s="18"/>
     </row>
-    <row r="98" spans="1:25">
+    <row r="98" spans="1:26">
       <c r="A98" s="8">
         <v>46097</v>
       </c>
@@ -24407,8 +24618,9 @@
       <c r="Y98" s="11">
         <v>6.5119999999999996</v>
       </c>
+      <c r="Z98" s="18"/>
     </row>
-    <row r="99" spans="1:25">
+    <row r="99" spans="1:26">
       <c r="A99" s="8">
         <v>46097</v>
       </c>
@@ -24484,8 +24696,9 @@
       <c r="Y99" s="11">
         <v>6.5119999999999996</v>
       </c>
+      <c r="Z99" s="18"/>
     </row>
-    <row r="100" spans="1:25">
+    <row r="100" spans="1:26">
       <c r="A100" s="8">
         <v>46098</v>
       </c>
@@ -24561,8 +24774,9 @@
       <c r="Y100" s="11">
         <v>6.6189999999999998</v>
       </c>
+      <c r="Z100" s="18"/>
     </row>
-    <row r="101" spans="1:25">
+    <row r="101" spans="1:26">
       <c r="A101" s="8">
         <v>46098</v>
       </c>
@@ -24638,8 +24852,9 @@
       <c r="Y101" s="11">
         <v>6.6189999999999998</v>
       </c>
+      <c r="Z101" s="18"/>
     </row>
-    <row r="102" spans="1:25">
+    <row r="102" spans="1:26">
       <c r="A102" s="8">
         <v>46098</v>
       </c>
@@ -24715,8 +24930,9 @@
       <c r="Y102" s="11">
         <v>6.6189999999999998</v>
       </c>
+      <c r="Z102" s="18"/>
     </row>
-    <row r="103" spans="1:25">
+    <row r="103" spans="1:26">
       <c r="A103" s="8">
         <v>46099</v>
       </c>
@@ -24792,8 +25008,9 @@
       <c r="Y103" s="11">
         <v>6.7</v>
       </c>
+      <c r="Z103" s="18"/>
     </row>
-    <row r="104" spans="1:25">
+    <row r="104" spans="1:26">
       <c r="A104" s="8">
         <v>46099</v>
       </c>
@@ -24869,8 +25086,9 @@
       <c r="Y104" s="11">
         <v>6.7</v>
       </c>
+      <c r="Z104" s="18"/>
     </row>
-    <row r="105" spans="1:25">
+    <row r="105" spans="1:26">
       <c r="A105" s="8">
         <v>46099</v>
       </c>
@@ -24946,8 +25164,9 @@
       <c r="Y105" s="11">
         <v>6.7</v>
       </c>
+      <c r="Z105" s="18"/>
     </row>
-    <row r="106" spans="1:25">
+    <row r="106" spans="1:26">
       <c r="A106" s="8">
         <v>46100</v>
       </c>
@@ -25023,8 +25242,9 @@
       <c r="Y106" s="11">
         <v>6.75</v>
       </c>
+      <c r="Z106" s="18"/>
     </row>
-    <row r="107" spans="1:25">
+    <row r="107" spans="1:26">
       <c r="A107" s="8">
         <v>46100</v>
       </c>
@@ -25100,8 +25320,9 @@
       <c r="Y107" s="11">
         <v>6.75</v>
       </c>
+      <c r="Z107" s="18"/>
     </row>
-    <row r="108" spans="1:25">
+    <row r="108" spans="1:26">
       <c r="A108" s="8">
         <v>46100</v>
       </c>
@@ -25177,8 +25398,9 @@
       <c r="Y108" s="11">
         <v>6.75</v>
       </c>
+      <c r="Z108" s="18"/>
     </row>
-    <row r="109" spans="1:25">
+    <row r="109" spans="1:26">
       <c r="A109" s="8">
         <v>46101</v>
       </c>
@@ -25254,8 +25476,9 @@
       <c r="Y109" s="11">
         <v>6.8879999999999999</v>
       </c>
+      <c r="Z109" s="18"/>
     </row>
-    <row r="110" spans="1:25">
+    <row r="110" spans="1:26">
       <c r="A110" s="8">
         <v>46101</v>
       </c>
@@ -25331,8 +25554,9 @@
       <c r="Y110" s="11">
         <v>6.8879999999999999</v>
       </c>
+      <c r="Z110" s="18"/>
     </row>
-    <row r="111" spans="1:25">
+    <row r="111" spans="1:26">
       <c r="A111" s="8">
         <v>46101</v>
       </c>
@@ -25408,8 +25632,9 @@
       <c r="Y111" s="11">
         <v>6.8879999999999999</v>
       </c>
+      <c r="Z111" s="18"/>
     </row>
-    <row r="112" spans="1:25">
+    <row r="112" spans="1:26">
       <c r="A112" s="8">
         <v>46104</v>
       </c>
@@ -25485,8 +25710,9 @@
       <c r="Y112" s="11">
         <v>6.95</v>
       </c>
+      <c r="Z112" s="18"/>
     </row>
-    <row r="113" spans="1:25">
+    <row r="113" spans="1:26">
       <c r="A113" s="8">
         <v>46104</v>
       </c>
@@ -25562,8 +25788,9 @@
       <c r="Y113" s="11">
         <v>6.95</v>
       </c>
+      <c r="Z113" s="18"/>
     </row>
-    <row r="114" spans="1:25">
+    <row r="114" spans="1:26">
       <c r="A114" s="8">
         <v>46104</v>
       </c>
@@ -25639,8 +25866,9 @@
       <c r="Y114" s="11">
         <v>6.95</v>
       </c>
+      <c r="Z114" s="18"/>
     </row>
-    <row r="115" spans="1:25">
+    <row r="115" spans="1:26">
       <c r="A115" s="8">
         <v>46105</v>
       </c>
@@ -25716,8 +25944,9 @@
       <c r="Y115" s="11">
         <v>7.0250000000000004</v>
       </c>
+      <c r="Z115" s="18"/>
     </row>
-    <row r="116" spans="1:25">
+    <row r="116" spans="1:26">
       <c r="A116" s="8">
         <v>46105</v>
       </c>
@@ -25793,8 +26022,9 @@
       <c r="Y116" s="11">
         <v>7.125</v>
       </c>
+      <c r="Z116" s="18"/>
     </row>
-    <row r="117" spans="1:25">
+    <row r="117" spans="1:26">
       <c r="A117" s="8">
         <v>46105</v>
       </c>
@@ -25870,8 +26100,9 @@
       <c r="Y117" s="11">
         <v>7.125</v>
       </c>
+      <c r="Z117" s="18"/>
     </row>
-    <row r="118" spans="1:25">
+    <row r="118" spans="1:26">
       <c r="A118" s="8">
         <v>46106</v>
       </c>
@@ -25947,8 +26178,9 @@
       <c r="Y118" s="11">
         <v>7.15</v>
       </c>
+      <c r="Z118" s="18"/>
     </row>
-    <row r="119" spans="1:25">
+    <row r="119" spans="1:26">
       <c r="A119" s="8">
         <v>46106</v>
       </c>
@@ -26024,8 +26256,9 @@
       <c r="Y119" s="11">
         <v>7.2249999999999996</v>
       </c>
+      <c r="Z119" s="18"/>
     </row>
-    <row r="120" spans="1:25">
+    <row r="120" spans="1:26">
       <c r="A120" s="8">
         <v>46106</v>
       </c>
@@ -26101,8 +26334,9 @@
       <c r="Y120" s="11">
         <v>7.2249999999999996</v>
       </c>
+      <c r="Z120" s="18"/>
     </row>
-    <row r="121" spans="1:25">
+    <row r="121" spans="1:26">
       <c r="A121" s="8">
         <v>46107</v>
       </c>
@@ -26178,8 +26412,9 @@
       <c r="Y121" s="11">
         <v>7.3250000000000002</v>
       </c>
+      <c r="Z121" s="18"/>
     </row>
-    <row r="122" spans="1:25">
+    <row r="122" spans="1:26">
       <c r="A122" s="8">
         <v>46107</v>
       </c>
@@ -26255,8 +26490,9 @@
       <c r="Y122" s="11">
         <v>7.3250000000000002</v>
       </c>
+      <c r="Z122" s="18"/>
     </row>
-    <row r="123" spans="1:25">
+    <row r="123" spans="1:26">
       <c r="A123" s="8">
         <v>46107</v>
       </c>
@@ -26332,8 +26568,9 @@
       <c r="Y123" s="11">
         <v>7.3250000000000002</v>
       </c>
+      <c r="Z123" s="18"/>
     </row>
-    <row r="124" spans="1:25">
+    <row r="124" spans="1:26">
       <c r="A124" s="8">
         <v>46108</v>
       </c>
@@ -26409,8 +26646,9 @@
       <c r="Y124" s="11">
         <v>7.375</v>
       </c>
+      <c r="Z124" s="18"/>
     </row>
-    <row r="125" spans="1:25">
+    <row r="125" spans="1:26">
       <c r="A125" s="8">
         <v>46108</v>
       </c>
@@ -26486,8 +26724,9 @@
       <c r="Y125" s="11">
         <v>7.3250000000000002</v>
       </c>
+      <c r="Z125" s="18"/>
     </row>
-    <row r="126" spans="1:25">
+    <row r="126" spans="1:26">
       <c r="A126" s="8">
         <v>46108</v>
       </c>
@@ -26563,8 +26802,9 @@
       <c r="Y126" s="11">
         <v>7.375</v>
       </c>
+      <c r="Z126" s="18"/>
     </row>
-    <row r="127" spans="1:25">
+    <row r="127" spans="1:26">
       <c r="A127" s="8">
         <v>46111</v>
       </c>
@@ -26640,8 +26880,9 @@
       <c r="Y127" s="11">
         <v>7.4249999999999998</v>
       </c>
+      <c r="Z127" s="18"/>
     </row>
-    <row r="128" spans="1:25">
+    <row r="128" spans="1:26">
       <c r="A128" s="8">
         <v>46111</v>
       </c>
@@ -26717,8 +26958,9 @@
       <c r="Y128" s="11">
         <v>7.4249999999999998</v>
       </c>
+      <c r="Z128" s="18"/>
     </row>
-    <row r="129" spans="1:25">
+    <row r="129" spans="1:26">
       <c r="A129" s="8">
         <v>46111</v>
       </c>
@@ -26794,8 +27036,9 @@
       <c r="Y129" s="11">
         <v>7.4249999999999998</v>
       </c>
+      <c r="Z129" s="18"/>
     </row>
-    <row r="130" spans="1:25">
+    <row r="130" spans="1:26">
       <c r="A130" s="8">
         <v>46112</v>
       </c>
@@ -26871,8 +27114,9 @@
       <c r="Y130" s="11">
         <v>7.5250000000000004</v>
       </c>
+      <c r="Z130" s="18"/>
     </row>
-    <row r="131" spans="1:25">
+    <row r="131" spans="1:26">
       <c r="A131" s="8">
         <v>46112</v>
       </c>
@@ -26948,8 +27192,9 @@
       <c r="Y131" s="11">
         <v>7.5250000000000004</v>
       </c>
+      <c r="Z131" s="18"/>
     </row>
-    <row r="132" spans="1:25">
+    <row r="132" spans="1:26">
       <c r="A132" s="8">
         <v>46112</v>
       </c>
@@ -27025,8 +27270,9 @@
       <c r="Y132" s="11">
         <v>7.55</v>
       </c>
+      <c r="Z132" s="18"/>
     </row>
-    <row r="133" spans="1:25">
+    <row r="133" spans="1:26">
       <c r="A133" s="8">
         <v>46113</v>
       </c>
@@ -27102,8 +27348,9 @@
       <c r="Y133" s="11">
         <v>7.625</v>
       </c>
+      <c r="Z133" s="18"/>
     </row>
-    <row r="134" spans="1:25">
+    <row r="134" spans="1:26">
       <c r="A134" s="8">
         <v>46113</v>
       </c>
@@ -27179,8 +27426,9 @@
       <c r="Y134" s="11">
         <v>7.625</v>
       </c>
+      <c r="Z134" s="18"/>
     </row>
-    <row r="135" spans="1:25">
+    <row r="135" spans="1:26">
       <c r="A135" s="8">
         <v>46113</v>
       </c>
@@ -27256,8 +27504,9 @@
       <c r="Y135" s="11">
         <v>7.625</v>
       </c>
+      <c r="Z135" s="18"/>
     </row>
-    <row r="136" spans="1:25">
+    <row r="136" spans="1:26">
       <c r="A136" s="8">
         <v>46114</v>
       </c>
@@ -27333,8 +27582,9 @@
       <c r="Y136" s="11">
         <v>7.625</v>
       </c>
+      <c r="Z136" s="18"/>
     </row>
-    <row r="137" spans="1:25">
+    <row r="137" spans="1:26">
       <c r="A137" s="8">
         <v>46114</v>
       </c>
@@ -27410,8 +27660,9 @@
       <c r="Y137" s="11">
         <v>7.625</v>
       </c>
+      <c r="Z137" s="18"/>
     </row>
-    <row r="138" spans="1:25">
+    <row r="138" spans="1:26">
       <c r="A138" s="8">
         <v>46114</v>
       </c>
@@ -27487,8 +27738,9 @@
       <c r="Y138" s="11">
         <v>7.625</v>
       </c>
+      <c r="Z138" s="18"/>
     </row>
-    <row r="139" spans="1:25">
+    <row r="139" spans="1:26">
       <c r="A139" s="8">
         <v>46115</v>
       </c>
@@ -27564,8 +27816,9 @@
       <c r="Y139" s="11">
         <v>7.6749999999999998</v>
       </c>
+      <c r="Z139" s="18"/>
     </row>
-    <row r="140" spans="1:25">
+    <row r="140" spans="1:26">
       <c r="A140" s="8">
         <v>46115</v>
       </c>
@@ -27641,8 +27894,9 @@
       <c r="Y140" s="11">
         <v>7.7</v>
       </c>
+      <c r="Z140" s="18"/>
     </row>
-    <row r="141" spans="1:25">
+    <row r="141" spans="1:26">
       <c r="A141" s="8">
         <v>46115</v>
       </c>
@@ -27718,8 +27972,9 @@
       <c r="Y141" s="11">
         <v>7.7</v>
       </c>
+      <c r="Z141" s="18"/>
     </row>
-    <row r="142" spans="1:25">
+    <row r="142" spans="1:26">
       <c r="A142" s="8">
         <v>46119</v>
       </c>
@@ -27795,8 +28050,9 @@
       <c r="Y142" s="11">
         <v>7.7</v>
       </c>
+      <c r="Z142" s="18"/>
     </row>
-    <row r="143" spans="1:25">
+    <row r="143" spans="1:26">
       <c r="A143" s="8">
         <v>46119</v>
       </c>
@@ -27872,8 +28128,9 @@
       <c r="Y143" s="11">
         <v>7.7</v>
       </c>
+      <c r="Z143" s="18"/>
     </row>
-    <row r="144" spans="1:25">
+    <row r="144" spans="1:26">
       <c r="A144" s="8">
         <v>46119</v>
       </c>
@@ -27949,8 +28206,9 @@
       <c r="Y144" s="11">
         <v>7.7</v>
       </c>
+      <c r="Z144" s="18"/>
     </row>
-    <row r="145" spans="1:25">
+    <row r="145" spans="1:26">
       <c r="A145" s="8">
         <v>46120</v>
       </c>
@@ -28026,8 +28284,9 @@
       <c r="Y145" s="11">
         <v>7.7</v>
       </c>
+      <c r="Z145" s="18"/>
     </row>
-    <row r="146" spans="1:25">
+    <row r="146" spans="1:26">
       <c r="A146" s="8">
         <v>46120</v>
       </c>
@@ -28103,8 +28362,9 @@
       <c r="Y146" s="11">
         <v>7.7</v>
       </c>
+      <c r="Z146" s="18"/>
     </row>
-    <row r="147" spans="1:25">
+    <row r="147" spans="1:26">
       <c r="A147" s="8">
         <v>46120</v>
       </c>
@@ -28180,8 +28440,9 @@
       <c r="Y147" s="11">
         <v>7.7</v>
       </c>
+      <c r="Z147" s="18"/>
     </row>
-    <row r="148" spans="1:25">
+    <row r="148" spans="1:26">
       <c r="A148" s="8">
         <v>46121</v>
       </c>
@@ -28257,8 +28518,9 @@
       <c r="Y148" s="11">
         <v>7.7249999999999996</v>
       </c>
+      <c r="Z148" s="18"/>
     </row>
-    <row r="149" spans="1:25">
+    <row r="149" spans="1:26">
       <c r="A149" s="8">
         <v>46121</v>
       </c>
@@ -28334,8 +28596,9 @@
       <c r="Y149" s="11">
         <v>7.7249999999999996</v>
       </c>
+      <c r="Z149" s="18"/>
     </row>
-    <row r="150" spans="1:25">
+    <row r="150" spans="1:26">
       <c r="A150" s="8">
         <v>46121</v>
       </c>
@@ -28411,8 +28674,9 @@
       <c r="Y150" s="11">
         <v>7.7249999999999996</v>
       </c>
+      <c r="Z150" s="18"/>
     </row>
-    <row r="151" spans="1:25">
+    <row r="151" spans="1:26">
       <c r="A151" s="8">
         <v>46122</v>
       </c>
@@ -28488,8 +28752,9 @@
       <c r="Y151" s="11">
         <v>7.75</v>
       </c>
+      <c r="Z151" s="18"/>
     </row>
-    <row r="152" spans="1:25">
+    <row r="152" spans="1:26">
       <c r="A152" s="8">
         <v>46122</v>
       </c>
@@ -28565,8 +28830,9 @@
       <c r="Y152" s="11">
         <v>7.75</v>
       </c>
+      <c r="Z152" s="18"/>
     </row>
-    <row r="153" spans="1:25">
+    <row r="153" spans="1:26">
       <c r="A153" s="8">
         <v>46122</v>
       </c>
@@ -28642,8 +28908,9 @@
       <c r="Y153" s="11">
         <v>7.75</v>
       </c>
+      <c r="Z153" s="18"/>
     </row>
-    <row r="154" spans="1:25">
+    <row r="154" spans="1:26">
       <c r="A154" s="8">
         <v>46125</v>
       </c>
@@ -28719,8 +28986,9 @@
       <c r="Y154" s="11">
         <v>7.8</v>
       </c>
+      <c r="Z154" s="18"/>
     </row>
-    <row r="155" spans="1:25">
+    <row r="155" spans="1:26">
       <c r="A155" s="8">
         <v>46125</v>
       </c>
@@ -28796,8 +29064,9 @@
       <c r="Y155" s="11">
         <v>7.8</v>
       </c>
+      <c r="Z155" s="18"/>
     </row>
-    <row r="156" spans="1:25">
+    <row r="156" spans="1:26">
       <c r="A156" s="8">
         <v>46125</v>
       </c>
@@ -28873,8 +29142,9 @@
       <c r="Y156" s="11">
         <v>7.8</v>
       </c>
+      <c r="Z156" s="18"/>
     </row>
-    <row r="157" spans="1:25">
+    <row r="157" spans="1:26">
       <c r="A157" s="8">
         <v>46126</v>
       </c>
@@ -28950,8 +29220,9 @@
       <c r="Y157" s="11">
         <v>7.8</v>
       </c>
+      <c r="Z157" s="18"/>
     </row>
-    <row r="158" spans="1:25">
+    <row r="158" spans="1:26">
       <c r="A158" s="8">
         <v>46126</v>
       </c>
@@ -29027,8 +29298,9 @@
       <c r="Y158" s="11">
         <v>7.8</v>
       </c>
+      <c r="Z158" s="18"/>
     </row>
-    <row r="159" spans="1:25">
+    <row r="159" spans="1:26">
       <c r="A159" s="8">
         <v>46126</v>
       </c>
@@ -29104,8 +29376,9 @@
       <c r="Y159" s="11">
         <v>7.8</v>
       </c>
+      <c r="Z159" s="18"/>
     </row>
-    <row r="160" spans="1:25">
+    <row r="160" spans="1:26">
       <c r="A160" s="8">
         <v>46127</v>
       </c>
@@ -29181,8 +29454,9 @@
       <c r="Y160" s="11">
         <v>7.85</v>
       </c>
+      <c r="Z160" s="18"/>
     </row>
-    <row r="161" spans="1:25">
+    <row r="161" spans="1:26">
       <c r="A161" s="8">
         <v>46127</v>
       </c>
@@ -29258,8 +29532,9 @@
       <c r="Y161" s="11">
         <v>7.85</v>
       </c>
+      <c r="Z161" s="18"/>
     </row>
-    <row r="162" spans="1:25">
+    <row r="162" spans="1:26">
       <c r="A162" s="8">
         <v>46127</v>
       </c>
@@ -29335,8 +29610,9 @@
       <c r="Y162" s="11">
         <v>7.8630000000000004</v>
       </c>
+      <c r="Z162" s="18"/>
     </row>
-    <row r="163" spans="1:25">
+    <row r="163" spans="1:26">
       <c r="A163" s="8">
         <v>46128</v>
       </c>
@@ -29412,8 +29688,9 @@
       <c r="Y163" s="11">
         <v>7.8630000000000004</v>
       </c>
+      <c r="Z163" s="18"/>
     </row>
-    <row r="164" spans="1:25">
+    <row r="164" spans="1:26">
       <c r="A164" s="8">
         <v>46128</v>
       </c>
@@ -29489,8 +29766,9 @@
       <c r="Y164" s="11">
         <v>7.9749999999999996</v>
       </c>
+      <c r="Z164" s="18"/>
     </row>
-    <row r="165" spans="1:25">
+    <row r="165" spans="1:26">
       <c r="A165" s="8">
         <v>46128</v>
       </c>
@@ -29566,8 +29844,9 @@
       <c r="Y165" s="11">
         <v>7.9749999999999996</v>
       </c>
+      <c r="Z165" s="18"/>
     </row>
-    <row r="166" spans="1:25">
+    <row r="166" spans="1:26">
       <c r="A166" s="8">
         <v>46129</v>
       </c>
@@ -29643,8 +29922,9 @@
       <c r="Y166" s="11">
         <v>8.0250000000000004</v>
       </c>
+      <c r="Z166" s="18"/>
     </row>
-    <row r="167" spans="1:25">
+    <row r="167" spans="1:26">
       <c r="A167" s="8">
         <v>46129</v>
       </c>
@@ -29720,8 +30000,9 @@
       <c r="Y167" s="11">
         <v>8.0250000000000004</v>
       </c>
+      <c r="Z167" s="18"/>
     </row>
-    <row r="168" spans="1:25">
+    <row r="168" spans="1:26">
       <c r="A168" s="8">
         <v>46129</v>
       </c>
@@ -29797,8 +30078,9 @@
       <c r="Y168" s="11">
         <v>8.0250000000000004</v>
       </c>
+      <c r="Z168" s="18"/>
     </row>
-    <row r="169" spans="1:25">
+    <row r="169" spans="1:26">
       <c r="A169" s="8">
         <v>46132</v>
       </c>
@@ -29874,8 +30156,9 @@
       <c r="Y169" s="11">
         <v>8.0749999999999993</v>
       </c>
+      <c r="Z169" s="18"/>
     </row>
-    <row r="170" spans="1:25">
+    <row r="170" spans="1:26">
       <c r="A170" s="8">
         <v>46132</v>
       </c>
@@ -29951,8 +30234,9 @@
       <c r="Y170" s="11">
         <v>8.0749999999999993</v>
       </c>
+      <c r="Z170" s="18"/>
     </row>
-    <row r="171" spans="1:25">
+    <row r="171" spans="1:26">
       <c r="A171" s="8">
         <v>46132</v>
       </c>
@@ -30028,8 +30312,9 @@
       <c r="Y171" s="11">
         <v>8.0749999999999993</v>
       </c>
+      <c r="Z171" s="18"/>
     </row>
-    <row r="172" spans="1:25">
+    <row r="172" spans="1:26">
       <c r="A172" s="8">
         <v>46133</v>
       </c>
@@ -30105,8 +30390,9 @@
       <c r="Y172" s="11">
         <v>8.125</v>
       </c>
+      <c r="Z172" s="18"/>
     </row>
-    <row r="173" spans="1:25">
+    <row r="173" spans="1:26">
       <c r="A173" s="8">
         <v>46133</v>
       </c>
@@ -30182,8 +30468,9 @@
       <c r="Y173" s="11">
         <v>8.125</v>
       </c>
+      <c r="Z173" s="18"/>
     </row>
-    <row r="174" spans="1:25">
+    <row r="174" spans="1:26">
       <c r="A174" s="8">
         <v>46133</v>
       </c>
@@ -30259,8 +30546,9 @@
       <c r="Y174" s="11">
         <v>8.125</v>
       </c>
+      <c r="Z174" s="18"/>
     </row>
-    <row r="175" spans="1:25">
+    <row r="175" spans="1:26">
       <c r="A175" s="8">
         <v>46134</v>
       </c>
@@ -30336,8 +30624,9 @@
       <c r="Y175" s="11">
         <v>8.125</v>
       </c>
+      <c r="Z175" s="18"/>
     </row>
-    <row r="176" spans="1:25">
+    <row r="176" spans="1:26">
       <c r="A176" s="8">
         <v>46134</v>
       </c>
@@ -30413,8 +30702,9 @@
       <c r="Y176" s="11">
         <v>8.125</v>
       </c>
+      <c r="Z176" s="18"/>
     </row>
-    <row r="177" spans="1:25">
+    <row r="177" spans="1:26">
       <c r="A177" s="8">
         <v>46134</v>
       </c>
@@ -30490,8 +30780,9 @@
       <c r="Y177" s="11">
         <v>8.125</v>
       </c>
+      <c r="Z177" s="18"/>
     </row>
-    <row r="178" spans="1:25">
+    <row r="178" spans="1:26">
       <c r="A178" s="8">
         <v>46135</v>
       </c>
@@ -30567,8 +30858,9 @@
       <c r="Y178" s="11">
         <v>8.125</v>
       </c>
+      <c r="Z178" s="18"/>
     </row>
-    <row r="179" spans="1:25">
+    <row r="179" spans="1:26">
       <c r="A179" s="8">
         <v>46135</v>
       </c>
@@ -30644,8 +30936,9 @@
       <c r="Y179" s="11">
         <v>8.125</v>
       </c>
+      <c r="Z179" s="18"/>
     </row>
-    <row r="180" spans="1:25">
+    <row r="180" spans="1:26">
       <c r="A180" s="8">
         <v>46135</v>
       </c>
@@ -30721,8 +31014,9 @@
       <c r="Y180" s="11">
         <v>8.125</v>
       </c>
+      <c r="Z180" s="18"/>
     </row>
-    <row r="181" spans="1:25">
+    <row r="181" spans="1:26">
       <c r="A181" s="8">
         <v>46136</v>
       </c>
@@ -30798,8 +31092,9 @@
       <c r="Y181" s="11">
         <v>8.125</v>
       </c>
+      <c r="Z181" s="18"/>
     </row>
-    <row r="182" spans="1:25">
+    <row r="182" spans="1:26">
       <c r="A182" s="8">
         <v>46136</v>
       </c>
@@ -30875,8 +31170,9 @@
       <c r="Y182" s="11">
         <v>8.125</v>
       </c>
+      <c r="Z182" s="18"/>
     </row>
-    <row r="183" spans="1:25">
+    <row r="183" spans="1:26">
       <c r="A183" s="8">
         <v>46136</v>
       </c>
@@ -30952,8 +31248,9 @@
       <c r="Y183" s="11">
         <v>8.125</v>
       </c>
+      <c r="Z183" s="18"/>
     </row>
-    <row r="184" spans="1:25">
+    <row r="184" spans="1:26">
       <c r="A184" s="8">
         <v>46139</v>
       </c>
@@ -31029,8 +31326,9 @@
       <c r="Y184" s="11">
         <v>8.1750000000000007</v>
       </c>
+      <c r="Z184" s="18"/>
     </row>
-    <row r="185" spans="1:25">
+    <row r="185" spans="1:26">
       <c r="A185" s="8">
         <v>46139</v>
       </c>
@@ -31106,8 +31404,9 @@
       <c r="Y185" s="11">
         <v>8.1750000000000007</v>
       </c>
+      <c r="Z185" s="18"/>
     </row>
-    <row r="186" spans="1:25">
+    <row r="186" spans="1:26">
       <c r="A186" s="8">
         <v>46139</v>
       </c>
@@ -31183,8 +31482,9 @@
       <c r="Y186" s="11">
         <v>8.1750000000000007</v>
       </c>
+      <c r="Z186" s="18"/>
     </row>
-    <row r="187" spans="1:25">
+    <row r="187" spans="1:26">
       <c r="A187" s="8">
         <v>46140</v>
       </c>
@@ -31260,8 +31560,9 @@
       <c r="Y187" s="11">
         <v>8.2249999999999996</v>
       </c>
+      <c r="Z187" s="18"/>
     </row>
-    <row r="188" spans="1:25">
+    <row r="188" spans="1:26">
       <c r="A188" s="8">
         <v>46140</v>
       </c>
@@ -31337,8 +31638,9 @@
       <c r="Y188" s="11">
         <v>8.2249999999999996</v>
       </c>
+      <c r="Z188" s="18"/>
     </row>
-    <row r="189" spans="1:25">
+    <row r="189" spans="1:26">
       <c r="A189" s="8">
         <v>46140</v>
       </c>
@@ -31414,8 +31716,9 @@
       <c r="Y189" s="11">
         <v>8.25</v>
       </c>
+      <c r="Z189" s="18"/>
     </row>
-    <row r="190" spans="1:25">
+    <row r="190" spans="1:26">
       <c r="A190" s="8">
         <v>46141</v>
       </c>
@@ -31491,8 +31794,9 @@
       <c r="Y190" s="11">
         <v>8.3000000000000007</v>
       </c>
+      <c r="Z190" s="18"/>
     </row>
-    <row r="191" spans="1:25">
+    <row r="191" spans="1:26">
       <c r="A191" s="8">
         <v>46141</v>
       </c>
@@ -31568,8 +31872,9 @@
       <c r="Y191" s="11">
         <v>8.3000000000000007</v>
       </c>
+      <c r="Z191" s="18"/>
     </row>
-    <row r="192" spans="1:25">
+    <row r="192" spans="1:26">
       <c r="A192" s="8">
         <v>46141</v>
       </c>
@@ -31645,8 +31950,9 @@
       <c r="Y192" s="11">
         <v>8.3000000000000007</v>
       </c>
+      <c r="Z192" s="18"/>
     </row>
-    <row r="193" spans="1:25">
+    <row r="193" spans="1:26">
       <c r="A193" s="8">
         <v>46142</v>
       </c>
@@ -31722,8 +32028,9 @@
       <c r="Y193" s="11">
         <v>8.375</v>
       </c>
+      <c r="Z193" s="18"/>
     </row>
-    <row r="194" spans="1:25">
+    <row r="194" spans="1:26">
       <c r="A194" s="8">
         <v>46142</v>
       </c>
@@ -31799,8 +32106,9 @@
       <c r="Y194" s="11">
         <v>8.375</v>
       </c>
+      <c r="Z194" s="18"/>
     </row>
-    <row r="195" spans="1:25">
+    <row r="195" spans="1:26">
       <c r="A195" s="8">
         <v>46142</v>
       </c>
@@ -31876,8 +32184,9 @@
       <c r="Y195" s="11">
         <v>8.375</v>
       </c>
+      <c r="Z195" s="18"/>
     </row>
-    <row r="196" spans="1:25">
+    <row r="196" spans="1:26">
       <c r="A196" s="8">
         <v>46146</v>
       </c>
@@ -31953,8 +32262,9 @@
       <c r="Y196" s="11">
         <v>8.4499999999999993</v>
       </c>
+      <c r="Z196" s="18"/>
     </row>
-    <row r="197" spans="1:25">
+    <row r="197" spans="1:26">
       <c r="A197" s="8">
         <v>46146</v>
       </c>
@@ -32030,8 +32340,9 @@
       <c r="Y197" s="11">
         <v>8.4499999999999993</v>
       </c>
+      <c r="Z197" s="18"/>
     </row>
-    <row r="198" spans="1:25">
+    <row r="198" spans="1:26">
       <c r="A198" s="8">
         <v>46146</v>
       </c>
@@ -32107,8 +32418,9 @@
       <c r="Y198" s="11">
         <v>8.4499999999999993</v>
       </c>
+      <c r="Z198" s="18"/>
     </row>
-    <row r="199" spans="1:25">
+    <row r="199" spans="1:26">
       <c r="A199" s="8">
         <v>46147</v>
       </c>
@@ -32184,8 +32496,9 @@
       <c r="Y199" s="11">
         <v>8.4749999999999996</v>
       </c>
+      <c r="Z199" s="18"/>
     </row>
-    <row r="200" spans="1:25">
+    <row r="200" spans="1:26">
       <c r="A200" s="8">
         <v>46147</v>
       </c>
@@ -32261,8 +32574,9 @@
       <c r="Y200" s="11">
         <v>8.4749999999999996</v>
       </c>
+      <c r="Z200" s="18"/>
     </row>
-    <row r="201" spans="1:25">
+    <row r="201" spans="1:26">
       <c r="A201" s="8">
         <v>46147</v>
       </c>
@@ -32338,8 +32652,9 @@
       <c r="Y201" s="11">
         <v>8.4749999999999996</v>
       </c>
+      <c r="Z201" s="18"/>
     </row>
-    <row r="202" spans="1:25">
+    <row r="202" spans="1:26">
       <c r="A202" s="8">
         <v>46148</v>
       </c>
@@ -32415,8 +32730,9 @@
       <c r="Y202" s="11">
         <v>8.5250000000000004</v>
       </c>
+      <c r="Z202" s="18"/>
     </row>
-    <row r="203" spans="1:25">
+    <row r="203" spans="1:26">
       <c r="A203" s="8">
         <v>46148</v>
       </c>
@@ -32492,8 +32808,9 @@
       <c r="Y203" s="11">
         <v>8.5250000000000004</v>
       </c>
+      <c r="Z203" s="18"/>
     </row>
-    <row r="204" spans="1:25">
+    <row r="204" spans="1:26">
       <c r="A204" s="8">
         <v>46148</v>
       </c>
@@ -32569,8 +32886,9 @@
       <c r="Y204" s="11">
         <v>8.5250000000000004</v>
       </c>
+      <c r="Z204" s="18"/>
     </row>
-    <row r="205" spans="1:25">
+    <row r="205" spans="1:26">
       <c r="A205" s="8">
         <v>46149</v>
       </c>
@@ -32646,8 +32964,9 @@
       <c r="Y205" s="11">
         <v>8.5749999999999993</v>
       </c>
+      <c r="Z205" s="18"/>
     </row>
-    <row r="206" spans="1:25">
+    <row r="206" spans="1:26">
       <c r="A206" s="8">
         <v>46149</v>
       </c>
@@ -32723,8 +33042,9 @@
       <c r="Y206" s="11">
         <v>8.625</v>
       </c>
+      <c r="Z206" s="18"/>
     </row>
-    <row r="207" spans="1:25">
+    <row r="207" spans="1:26">
       <c r="A207" s="8">
         <v>46149</v>
       </c>
@@ -32800,8 +33120,9 @@
       <c r="Y207" s="11">
         <v>8.625</v>
       </c>
+      <c r="Z207" s="18"/>
     </row>
-    <row r="208" spans="1:25">
+    <row r="208" spans="1:26">
       <c r="A208" s="8">
         <v>46150</v>
       </c>
@@ -32877,8 +33198,9 @@
       <c r="Y208" s="11">
         <v>8.7249999999999996</v>
       </c>
+      <c r="Z208" s="18"/>
     </row>
-    <row r="209" spans="1:25">
+    <row r="209" spans="1:26">
       <c r="A209" s="8">
         <v>46150</v>
       </c>
@@ -32954,8 +33276,9 @@
       <c r="Y209" s="11">
         <v>8.7249999999999996</v>
       </c>
+      <c r="Z209" s="18"/>
     </row>
-    <row r="210" spans="1:25">
+    <row r="210" spans="1:26">
       <c r="A210" s="8">
         <v>46150</v>
       </c>
@@ -33031,8 +33354,9 @@
       <c r="Y210" s="11">
         <v>8.7249999999999996</v>
       </c>
+      <c r="Z210" s="18"/>
     </row>
-    <row r="211" spans="1:25">
+    <row r="211" spans="1:26">
       <c r="A211" s="8">
         <v>46153</v>
       </c>
@@ -33108,8 +33432,9 @@
       <c r="Y211" s="11">
         <v>8.7750000000000004</v>
       </c>
+      <c r="Z211" s="18"/>
     </row>
-    <row r="212" spans="1:25">
+    <row r="212" spans="1:26">
       <c r="A212" s="8">
         <v>46153</v>
       </c>
@@ -33185,8 +33510,9 @@
       <c r="Y212" s="11">
         <v>8.7750000000000004</v>
       </c>
+      <c r="Z212" s="18"/>
     </row>
-    <row r="213" spans="1:25">
+    <row r="213" spans="1:26">
       <c r="A213" s="8">
         <v>46153</v>
       </c>
@@ -33262,8 +33588,9 @@
       <c r="Y213" s="11">
         <v>8.7750000000000004</v>
       </c>
+      <c r="Z213" s="18"/>
     </row>
-    <row r="214" spans="1:25">
+    <row r="214" spans="1:26">
       <c r="A214" s="8">
         <v>46154</v>
       </c>
@@ -33339,8 +33666,9 @@
       <c r="Y214" s="11">
         <v>8.7750000000000004</v>
       </c>
+      <c r="Z214" s="18"/>
     </row>
-    <row r="215" spans="1:25">
+    <row r="215" spans="1:26">
       <c r="A215" s="8">
         <v>46154</v>
       </c>
@@ -33416,8 +33744,9 @@
       <c r="Y215" s="11">
         <v>8.7750000000000004</v>
       </c>
+      <c r="Z215" s="18"/>
     </row>
-    <row r="216" spans="1:25">
+    <row r="216" spans="1:26">
       <c r="A216" s="8">
         <v>46154</v>
       </c>
@@ -33493,8 +33822,9 @@
       <c r="Y216" s="11">
         <v>8.875</v>
       </c>
+      <c r="Z216" s="18"/>
     </row>
-    <row r="217" spans="1:25">
+    <row r="217" spans="1:26">
       <c r="A217" s="8">
         <v>46155</v>
       </c>
@@ -33570,8 +33900,9 @@
       <c r="Y217" s="11">
         <v>8.9499999999999993</v>
       </c>
+      <c r="Z217" s="18"/>
     </row>
-    <row r="218" spans="1:25">
+    <row r="218" spans="1:26">
       <c r="A218" s="8">
         <v>46155</v>
       </c>
@@ -33647,8 +33978,9 @@
       <c r="Y218" s="11">
         <v>8.9499999999999993</v>
       </c>
+      <c r="Z218" s="18"/>
     </row>
-    <row r="219" spans="1:25">
+    <row r="219" spans="1:26">
       <c r="A219" s="8">
         <v>46155</v>
       </c>
@@ -33724,8 +34056,9 @@
       <c r="Y219" s="11">
         <v>8.9499999999999993</v>
       </c>
+      <c r="Z219" s="18"/>
     </row>
-    <row r="220" spans="1:25">
+    <row r="220" spans="1:26">
       <c r="A220" s="8">
         <v>46156</v>
       </c>
@@ -33801,8 +34134,9 @@
       <c r="Y220" s="11">
         <v>8.9629999999999992</v>
       </c>
+      <c r="Z220" s="18"/>
     </row>
-    <row r="221" spans="1:25">
+    <row r="221" spans="1:26">
       <c r="A221" s="8">
         <v>46156</v>
       </c>
@@ -33878,8 +34212,9 @@
       <c r="Y221" s="11">
         <v>8.9629999999999992</v>
       </c>
+      <c r="Z221" s="18"/>
     </row>
-    <row r="222" spans="1:25">
+    <row r="222" spans="1:26">
       <c r="A222" s="8">
         <v>46156</v>
       </c>
@@ -33955,8 +34290,9 @@
       <c r="Y222" s="11">
         <v>8.9629999999999992</v>
       </c>
+      <c r="Z222" s="18"/>
     </row>
-    <row r="223" spans="1:25">
+    <row r="223" spans="1:26">
       <c r="A223" s="8">
         <v>46157</v>
       </c>
@@ -34032,8 +34368,9 @@
       <c r="Y223" s="11">
         <v>8.9879999999999995</v>
       </c>
+      <c r="Z223" s="18"/>
     </row>
-    <row r="224" spans="1:25">
+    <row r="224" spans="1:26">
       <c r="A224" s="8">
         <v>46157</v>
       </c>
@@ -34109,8 +34446,9 @@
       <c r="Y224" s="11">
         <v>8.9879999999999995</v>
       </c>
+      <c r="Z224" s="18"/>
     </row>
-    <row r="225" spans="1:25">
+    <row r="225" spans="1:26">
       <c r="A225" s="8">
         <v>46157</v>
       </c>
@@ -34186,8 +34524,9 @@
       <c r="Y225" s="11">
         <v>8.9879999999999995</v>
       </c>
+      <c r="Z225" s="18"/>
     </row>
-    <row r="226" spans="1:25">
+    <row r="226" spans="1:26">
       <c r="A226" s="8">
         <v>46160</v>
       </c>
@@ -34263,8 +34602,9 @@
       <c r="Y226" s="11">
         <v>8.9879999999999995</v>
       </c>
+      <c r="Z226" s="18"/>
     </row>
-    <row r="227" spans="1:25">
+    <row r="227" spans="1:26">
       <c r="A227" s="8">
         <v>46160</v>
       </c>
@@ -34340,8 +34680,9 @@
       <c r="Y227" s="11">
         <v>8.9879999999999995</v>
       </c>
+      <c r="Z227" s="18"/>
     </row>
-    <row r="228" spans="1:25">
+    <row r="228" spans="1:26">
       <c r="A228" s="8">
         <v>46160</v>
       </c>
@@ -34417,8 +34758,9 @@
       <c r="Y228" s="11">
         <v>8.9879999999999995</v>
       </c>
+      <c r="Z228" s="18"/>
     </row>
-    <row r="229" spans="1:25">
+    <row r="229" spans="1:26">
       <c r="A229" s="8">
         <v>46161</v>
       </c>
@@ -34494,8 +34836,9 @@
       <c r="Y229" s="11">
         <v>8.9879999999999995</v>
       </c>
+      <c r="Z229" s="18"/>
     </row>
-    <row r="230" spans="1:25">
+    <row r="230" spans="1:26">
       <c r="A230" s="8">
         <v>46161</v>
       </c>
@@ -34571,8 +34914,9 @@
       <c r="Y230" s="11">
         <v>8.9879999999999995</v>
       </c>
+      <c r="Z230" s="18"/>
     </row>
-    <row r="231" spans="1:25">
+    <row r="231" spans="1:26">
       <c r="A231" s="8">
         <v>46161</v>
       </c>
@@ -34648,8 +34992,9 @@
       <c r="Y231" s="11">
         <v>8.9879999999999995</v>
       </c>
+      <c r="Z231" s="18"/>
     </row>
-    <row r="232" spans="1:25">
+    <row r="232" spans="1:26">
       <c r="A232" s="8">
         <v>46162</v>
       </c>
@@ -34725,8 +35070,9 @@
       <c r="Y232" s="11">
         <v>9.0380000000000003</v>
       </c>
+      <c r="Z232" s="18"/>
     </row>
-    <row r="233" spans="1:25">
+    <row r="233" spans="1:26">
       <c r="A233" s="8">
         <v>46162</v>
       </c>
@@ -34802,8 +35148,9 @@
       <c r="Y233" s="11">
         <v>9.0380000000000003</v>
       </c>
+      <c r="Z233" s="18"/>
     </row>
-    <row r="234" spans="1:25">
+    <row r="234" spans="1:26">
       <c r="A234" s="8">
         <v>46162</v>
       </c>
@@ -34879,8 +35226,9 @@
       <c r="Y234" s="11">
         <v>9.0380000000000003</v>
       </c>
+      <c r="Z234" s="18"/>
     </row>
-    <row r="235" spans="1:25">
+    <row r="235" spans="1:26">
       <c r="A235" s="8">
         <v>46163</v>
       </c>
@@ -34956,8 +35304,9 @@
       <c r="Y235" s="11">
         <v>9.0879999999999992</v>
       </c>
+      <c r="Z235" s="18"/>
     </row>
-    <row r="236" spans="1:25">
+    <row r="236" spans="1:26">
       <c r="A236" s="8">
         <v>46163</v>
       </c>
@@ -35033,8 +35382,9 @@
       <c r="Y236" s="11">
         <v>9.0879999999999992</v>
       </c>
+      <c r="Z236" s="18"/>
     </row>
-    <row r="237" spans="1:25">
+    <row r="237" spans="1:26">
       <c r="A237" s="8">
         <v>46163</v>
       </c>
@@ -35110,8 +35460,9 @@
       <c r="Y237" s="11">
         <v>9.0879999999999992</v>
       </c>
+      <c r="Z237" s="18"/>
     </row>
-    <row r="238" spans="1:25">
+    <row r="238" spans="1:26">
       <c r="A238" s="8">
         <v>46164</v>
       </c>
@@ -35187,8 +35538,9 @@
       <c r="Y238" s="11">
         <v>9.1630000000000003</v>
       </c>
+      <c r="Z238" s="18"/>
     </row>
-    <row r="239" spans="1:25">
+    <row r="239" spans="1:26">
       <c r="A239" s="8">
         <v>46164</v>
       </c>
@@ -35264,8 +35616,9 @@
       <c r="Y239" s="11">
         <v>9.1630000000000003</v>
       </c>
+      <c r="Z239" s="18"/>
     </row>
-    <row r="240" spans="1:25">
+    <row r="240" spans="1:26">
       <c r="A240" s="8">
         <v>46164</v>
       </c>
@@ -35341,8 +35694,9 @@
       <c r="Y240" s="11">
         <v>9.1630000000000003</v>
       </c>
+      <c r="Z240" s="18"/>
     </row>
-    <row r="241" spans="1:25">
+    <row r="241" spans="1:26">
       <c r="A241" s="8">
         <v>46167</v>
       </c>
@@ -35418,8 +35772,9 @@
       <c r="Y241" s="11">
         <v>9.1630000000000003</v>
       </c>
+      <c r="Z241" s="18"/>
     </row>
-    <row r="242" spans="1:25">
+    <row r="242" spans="1:26">
       <c r="A242" s="8">
         <v>46167</v>
       </c>
@@ -35495,8 +35850,9 @@
       <c r="Y242" s="11">
         <v>9.1630000000000003</v>
       </c>
+      <c r="Z242" s="18"/>
     </row>
-    <row r="243" spans="1:25">
+    <row r="243" spans="1:26">
       <c r="A243" s="8">
         <v>46167</v>
       </c>
@@ -35572,8 +35928,9 @@
       <c r="Y243" s="11">
         <v>9.1630000000000003</v>
       </c>
+      <c r="Z243" s="18"/>
     </row>
-    <row r="244" spans="1:25">
+    <row r="244" spans="1:26">
       <c r="A244" s="8">
         <v>46168</v>
       </c>
@@ -35649,8 +36006,9 @@
       <c r="Y244" s="11">
         <v>9.2129999999999992</v>
       </c>
+      <c r="Z244" s="18"/>
     </row>
-    <row r="245" spans="1:25">
+    <row r="245" spans="1:26">
       <c r="A245" s="8">
         <v>46168</v>
       </c>
@@ -35726,8 +36084,9 @@
       <c r="Y245" s="11">
         <v>9.2129999999999992</v>
       </c>
+      <c r="Z245" s="18"/>
     </row>
-    <row r="246" spans="1:25">
+    <row r="246" spans="1:26">
       <c r="A246" s="8">
         <v>46168</v>
       </c>
@@ -35803,8 +36162,9 @@
       <c r="Y246" s="11">
         <v>9.2129999999999992</v>
       </c>
+      <c r="Z246" s="18"/>
     </row>
-    <row r="247" spans="1:25">
+    <row r="247" spans="1:26">
       <c r="A247" s="8">
         <v>46169</v>
       </c>
@@ -35880,8 +36240,9 @@
       <c r="Y247" s="11">
         <v>9.2129999999999992</v>
       </c>
+      <c r="Z247" s="18"/>
     </row>
-    <row r="248" spans="1:25">
+    <row r="248" spans="1:26">
       <c r="A248" s="8">
         <v>46169</v>
       </c>
@@ -35957,8 +36318,9 @@
       <c r="Y248" s="11">
         <v>9.2129999999999992</v>
       </c>
+      <c r="Z248" s="18"/>
     </row>
-    <row r="249" spans="1:25">
+    <row r="249" spans="1:26">
       <c r="A249" s="8">
         <v>46169</v>
       </c>
@@ -36034,8 +36396,9 @@
       <c r="Y249" s="11">
         <v>9.2129999999999992</v>
       </c>
+      <c r="Z249" s="18"/>
     </row>
-    <row r="250" spans="1:25">
+    <row r="250" spans="1:26">
       <c r="A250" s="8">
         <v>46170</v>
       </c>
@@ -36111,8 +36474,9 @@
       <c r="Y250" s="11">
         <v>9.2880000000000003</v>
       </c>
+      <c r="Z250" s="18"/>
     </row>
-    <row r="251" spans="1:25">
+    <row r="251" spans="1:26">
       <c r="A251" s="8">
         <v>46170</v>
       </c>
@@ -36188,8 +36552,9 @@
       <c r="Y251" s="11">
         <v>9.2750000000000004</v>
       </c>
+      <c r="Z251" s="18"/>
     </row>
-    <row r="252" spans="1:25">
+    <row r="252" spans="1:26">
       <c r="A252" s="8">
         <v>46170</v>
       </c>
@@ -36265,8 +36630,9 @@
       <c r="Y252" s="11">
         <v>9.2750000000000004</v>
       </c>
+      <c r="Z252" s="18"/>
     </row>
-    <row r="253" spans="1:25">
+    <row r="253" spans="1:26">
       <c r="A253" s="8">
         <v>46171</v>
       </c>
@@ -36342,8 +36708,9 @@
       <c r="Y253" s="11">
         <v>9.4</v>
       </c>
+      <c r="Z253" s="18"/>
     </row>
-    <row r="254" spans="1:25">
+    <row r="254" spans="1:26">
       <c r="A254" s="8">
         <v>46171</v>
       </c>
@@ -36419,8 +36786,9 @@
       <c r="Y254" s="11">
         <v>9.4</v>
       </c>
+      <c r="Z254" s="18"/>
     </row>
-    <row r="255" spans="1:25">
+    <row r="255" spans="1:26">
       <c r="A255" s="8">
         <v>46171</v>
       </c>
@@ -36496,8 +36864,9 @@
       <c r="Y255" s="11">
         <v>9.4</v>
       </c>
+      <c r="Z255" s="18"/>
     </row>
-    <row r="256" spans="1:25">
+    <row r="256" spans="1:26">
       <c r="A256" s="8">
         <v>46174</v>
       </c>
@@ -36573,8 +36942,9 @@
       <c r="Y256" s="11">
         <v>9.4749999999999996</v>
       </c>
+      <c r="Z256" s="18"/>
     </row>
-    <row r="257" spans="1:25">
+    <row r="257" spans="1:26">
       <c r="A257" s="8">
         <v>46174</v>
       </c>
@@ -36650,8 +37020,9 @@
       <c r="Y257" s="11">
         <v>9.4749999999999996</v>
       </c>
+      <c r="Z257" s="18"/>
     </row>
-    <row r="258" spans="1:25">
+    <row r="258" spans="1:26">
       <c r="A258" s="8">
         <v>46174</v>
       </c>
@@ -36727,8 +37098,9 @@
       <c r="Y258" s="11">
         <v>9.4749999999999996</v>
       </c>
+      <c r="Z258" s="18"/>
     </row>
-    <row r="259" spans="1:25">
+    <row r="259" spans="1:26">
       <c r="A259" s="8">
         <v>46175</v>
       </c>
@@ -36804,8 +37176,9 @@
       <c r="Y259" s="11">
         <v>9.5500000000000007</v>
       </c>
+      <c r="Z259" s="18"/>
     </row>
-    <row r="260" spans="1:25">
+    <row r="260" spans="1:26">
       <c r="A260" s="8">
         <v>46175</v>
       </c>
@@ -36881,8 +37254,9 @@
       <c r="Y260" s="11">
         <v>9.5500000000000007</v>
       </c>
+      <c r="Z260" s="18"/>
     </row>
-    <row r="261" spans="1:25">
+    <row r="261" spans="1:26">
       <c r="A261" s="8">
         <v>46175</v>
       </c>
@@ -36958,8 +37332,9 @@
       <c r="Y261" s="11">
         <v>9.625</v>
       </c>
+      <c r="Z261" s="18"/>
     </row>
-    <row r="262" spans="1:25">
+    <row r="262" spans="1:26">
       <c r="A262" s="8">
         <v>46176</v>
       </c>
@@ -37035,8 +37410,9 @@
       <c r="Y262" s="11">
         <v>9.7750000000000004</v>
       </c>
+      <c r="Z262" s="18"/>
     </row>
-    <row r="263" spans="1:25">
+    <row r="263" spans="1:26">
       <c r="A263" s="8">
         <v>46176</v>
       </c>
@@ -37112,8 +37488,9 @@
       <c r="Y263" s="11">
         <v>9.8000000000000007</v>
       </c>
+      <c r="Z263" s="18"/>
     </row>
-    <row r="264" spans="1:25">
+    <row r="264" spans="1:26">
       <c r="A264" s="8">
         <v>46176</v>
       </c>
@@ -37189,8 +37566,9 @@
       <c r="Y264" s="11">
         <v>9.8000000000000007</v>
       </c>
+      <c r="Z264" s="18"/>
     </row>
-    <row r="265" spans="1:25">
+    <row r="265" spans="1:26">
       <c r="A265" s="8">
         <v>46177</v>
       </c>
@@ -37266,8 +37644,9 @@
       <c r="Y265" s="11">
         <v>9.9</v>
       </c>
+      <c r="Z265" s="18"/>
     </row>
-    <row r="266" spans="1:25">
+    <row r="266" spans="1:26">
       <c r="A266" s="8">
         <v>46177</v>
       </c>
@@ -37343,8 +37722,9 @@
       <c r="Y266" s="11">
         <v>9.9</v>
       </c>
+      <c r="Z266" s="18"/>
     </row>
-    <row r="267" spans="1:25">
+    <row r="267" spans="1:26">
       <c r="A267" s="8">
         <v>46177</v>
       </c>
@@ -37420,8 +37800,9 @@
       <c r="Y267" s="11">
         <v>9.9</v>
       </c>
+      <c r="Z267" s="18"/>
     </row>
-    <row r="268" spans="1:25">
+    <row r="268" spans="1:26">
       <c r="A268" s="8">
         <v>46178</v>
       </c>
@@ -37497,8 +37878,9 @@
       <c r="Y268" s="11">
         <v>10.025</v>
       </c>
+      <c r="Z268" s="18"/>
     </row>
-    <row r="269" spans="1:25">
+    <row r="269" spans="1:26">
       <c r="A269" s="8">
         <v>46178</v>
       </c>
@@ -37574,8 +37956,9 @@
       <c r="Y269" s="11">
         <v>10.025</v>
       </c>
+      <c r="Z269" s="18"/>
     </row>
-    <row r="270" spans="1:25">
+    <row r="270" spans="1:26">
       <c r="A270" s="8">
         <v>46178</v>
       </c>
@@ -37651,8 +38034,9 @@
       <c r="Y270" s="11">
         <v>10.025</v>
       </c>
+      <c r="Z270" s="18"/>
     </row>
-    <row r="271" spans="1:25">
+    <row r="271" spans="1:26">
       <c r="A271" s="8">
         <v>46181</v>
       </c>
@@ -37728,8 +38112,9 @@
       <c r="Y271" s="11">
         <v>10.167</v>
       </c>
+      <c r="Z271" s="18"/>
     </row>
-    <row r="272" spans="1:25">
+    <row r="272" spans="1:26">
       <c r="A272" s="8">
         <v>46181</v>
       </c>
@@ -37805,8 +38190,9 @@
       <c r="Y272" s="11">
         <v>10.167</v>
       </c>
+      <c r="Z272" s="18"/>
     </row>
-    <row r="273" spans="1:25">
+    <row r="273" spans="1:26">
       <c r="A273" s="8">
         <v>46181</v>
       </c>
@@ -37882,8 +38268,9 @@
       <c r="Y273" s="11">
         <v>10.167</v>
       </c>
+      <c r="Z273" s="18"/>
     </row>
-    <row r="274" spans="1:25">
+    <row r="274" spans="1:26">
       <c r="A274" s="8">
         <v>46182</v>
       </c>
@@ -37959,8 +38346,9 @@
       <c r="Y274" s="11">
         <v>10.286</v>
       </c>
+      <c r="Z274" s="18"/>
     </row>
-    <row r="275" spans="1:25">
+    <row r="275" spans="1:26">
       <c r="A275" s="8">
         <v>46182</v>
       </c>
@@ -38036,8 +38424,9 @@
       <c r="Y275" s="11">
         <v>10.314</v>
       </c>
+      <c r="Z275" s="18"/>
     </row>
-    <row r="276" spans="1:25">
+    <row r="276" spans="1:26">
       <c r="A276" s="8">
         <v>46182</v>
       </c>
@@ -38113,8 +38502,9 @@
       <c r="Y276" s="11">
         <v>10.314</v>
       </c>
+      <c r="Z276" s="18"/>
     </row>
-    <row r="277" spans="1:25">
+    <row r="277" spans="1:26">
       <c r="A277" s="8">
         <v>46183</v>
       </c>
@@ -38190,8 +38580,9 @@
       <c r="Y277" s="11">
         <v>10.433</v>
       </c>
+      <c r="Z277" s="18"/>
     </row>
-    <row r="278" spans="1:25">
+    <row r="278" spans="1:26">
       <c r="A278" s="8">
         <v>46183</v>
       </c>
@@ -38267,8 +38658,9 @@
       <c r="Y278" s="11">
         <v>10.433</v>
       </c>
+      <c r="Z278" s="18"/>
     </row>
-    <row r="279" spans="1:25">
+    <row r="279" spans="1:26">
       <c r="A279" s="8">
         <v>46183</v>
       </c>
@@ -38344,8 +38736,9 @@
       <c r="Y279" s="11">
         <v>10.433</v>
       </c>
+      <c r="Z279" s="18"/>
     </row>
-    <row r="280" spans="1:25">
+    <row r="280" spans="1:26">
       <c r="A280" s="8">
         <v>46184</v>
       </c>
@@ -38421,8 +38814,9 @@
       <c r="Y280" s="11">
         <v>10.548</v>
       </c>
+      <c r="Z280" s="18"/>
     </row>
-    <row r="281" spans="1:25">
+    <row r="281" spans="1:26">
       <c r="A281" s="8">
         <v>46184</v>
       </c>
@@ -38498,8 +38892,9 @@
       <c r="Y281" s="11">
         <v>10.548</v>
       </c>
+      <c r="Z281" s="18"/>
     </row>
-    <row r="282" spans="1:25">
+    <row r="282" spans="1:26">
       <c r="A282" s="8">
         <v>46184</v>
       </c>
@@ -38575,8 +38970,9 @@
       <c r="Y282" s="11">
         <v>10.548</v>
       </c>
+      <c r="Z282" s="18"/>
     </row>
-    <row r="283" spans="1:25">
+    <row r="283" spans="1:26">
       <c r="A283" s="8">
         <v>46185</v>
       </c>
@@ -38652,8 +39048,9 @@
       <c r="Y283" s="11">
         <v>10.648</v>
       </c>
+      <c r="Z283" s="18"/>
     </row>
-    <row r="284" spans="1:25">
+    <row r="284" spans="1:26">
       <c r="A284" s="8">
         <v>46185</v>
       </c>
@@ -38729,8 +39126,9 @@
       <c r="Y284" s="11">
         <v>10.670999999999999</v>
       </c>
+      <c r="Z284" s="18"/>
     </row>
-    <row r="285" spans="1:25">
+    <row r="285" spans="1:26">
       <c r="A285" s="8">
         <v>46185</v>
       </c>
@@ -38806,8 +39204,9 @@
       <c r="Y285" s="11">
         <v>10.670999999999999</v>
       </c>
+      <c r="Z285" s="18"/>
     </row>
-    <row r="286" spans="1:25">
+    <row r="286" spans="1:26">
       <c r="A286" s="8">
         <v>46188</v>
       </c>
@@ -38883,8 +39282,9 @@
       <c r="Y286" s="11">
         <v>10.743</v>
       </c>
+      <c r="Z286" s="18"/>
     </row>
-    <row r="287" spans="1:25">
+    <row r="287" spans="1:26">
       <c r="A287" s="8">
         <v>46188</v>
       </c>
@@ -38960,8 +39360,9 @@
       <c r="Y287" s="11">
         <v>10.743</v>
       </c>
+      <c r="Z287" s="18"/>
     </row>
-    <row r="288" spans="1:25">
+    <row r="288" spans="1:26">
       <c r="A288" s="8">
         <v>46188</v>
       </c>
@@ -39037,8 +39438,9 @@
       <c r="Y288" s="11">
         <v>10.743</v>
       </c>
+      <c r="Z288" s="18"/>
     </row>
-    <row r="289" spans="1:25">
+    <row r="289" spans="1:26">
       <c r="A289" s="8">
         <v>46189</v>
       </c>
@@ -39114,8 +39516,9 @@
       <c r="Y289" s="11">
         <v>10.856999999999999</v>
       </c>
+      <c r="Z289" s="18"/>
     </row>
-    <row r="290" spans="1:25">
+    <row r="290" spans="1:26">
       <c r="A290" s="8">
         <v>46189</v>
       </c>
@@ -39191,8 +39594,9 @@
       <c r="Y290" s="11">
         <v>10.856999999999999</v>
       </c>
+      <c r="Z290" s="18"/>
     </row>
-    <row r="291" spans="1:25">
+    <row r="291" spans="1:26">
       <c r="A291" s="8">
         <v>46189</v>
       </c>
@@ -39268,8 +39672,9 @@
       <c r="Y291" s="11">
         <v>10.856999999999999</v>
       </c>
+      <c r="Z291" s="18"/>
     </row>
-    <row r="292" spans="1:25">
+    <row r="292" spans="1:26">
       <c r="A292" s="8">
         <v>46190</v>
       </c>
@@ -39345,8 +39750,9 @@
       <c r="Y292" s="11">
         <v>10.952</v>
       </c>
+      <c r="Z292" s="18"/>
     </row>
-    <row r="293" spans="1:25">
+    <row r="293" spans="1:26">
       <c r="A293" s="8">
         <v>46190</v>
       </c>
@@ -39422,8 +39828,9 @@
       <c r="Y293" s="11">
         <v>10.952</v>
       </c>
+      <c r="Z293" s="18"/>
     </row>
-    <row r="294" spans="1:25">
+    <row r="294" spans="1:26">
       <c r="A294" s="8">
         <v>46190</v>
       </c>
@@ -39499,6 +39906,178 @@
       <c r="Y294" s="11">
         <v>10.952</v>
       </c>
+      <c r="Z294" s="18"/>
+    </row>
+    <row r="295" spans="1:26">
+      <c r="A295" s="8">
+        <v>46191</v>
+      </c>
+      <c r="B295" s="8">
+        <v>46191</v>
+      </c>
+      <c r="C295" s="9">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D295" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E295" s="11">
+        <v>59.5</v>
+      </c>
+      <c r="F295" s="11">
+        <v>30.5</v>
+      </c>
+      <c r="G295" s="11">
+        <v>45.832999999999998</v>
+      </c>
+      <c r="H295" s="11">
+        <v>25.2</v>
+      </c>
+      <c r="I295" s="11">
+        <v>22.1</v>
+      </c>
+      <c r="J295" s="11">
+        <v>23.5</v>
+      </c>
+      <c r="K295" s="11">
+        <v>81</v>
+      </c>
+      <c r="L295" s="11">
+        <v>37.6</v>
+      </c>
+      <c r="M295" s="11">
+        <v>69</v>
+      </c>
+      <c r="N295" s="11">
+        <v>12.3</v>
+      </c>
+      <c r="O295" s="11">
+        <v>10.4</v>
+      </c>
+      <c r="P295" s="11">
+        <v>11.8</v>
+      </c>
+      <c r="Q295" s="11">
+        <v>55</v>
+      </c>
+      <c r="R295" s="11">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="S295" s="11">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="T295" s="11">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="U295" s="11">
+        <v>3.85</v>
+      </c>
+      <c r="V295" s="11">
+        <v>4.45</v>
+      </c>
+      <c r="W295" s="11">
+        <v>16</v>
+      </c>
+      <c r="X295" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="Y295" s="11">
+        <v>10.976000000000001</v>
+      </c>
+      <c r="Z295" s="18"/>
+    </row>
+    <row r="296" spans="1:26">
+      <c r="A296" s="8">
+        <v>46191</v>
+      </c>
+      <c r="B296" s="8">
+        <v>46191</v>
+      </c>
+      <c r="C296" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D296" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E296" s="11">
+        <v>59.5</v>
+      </c>
+      <c r="F296" s="11">
+        <v>30.5</v>
+      </c>
+      <c r="G296" s="11">
+        <v>46</v>
+      </c>
+      <c r="H296" s="11">
+        <v>25.2</v>
+      </c>
+      <c r="I296" s="11">
+        <v>22.1</v>
+      </c>
+      <c r="J296" s="11">
+        <v>23.5</v>
+      </c>
+      <c r="K296" s="11">
+        <v>81</v>
+      </c>
+      <c r="L296" s="11">
+        <v>37.6</v>
+      </c>
+      <c r="M296" s="11">
+        <v>69.125</v>
+      </c>
+      <c r="N296" s="11">
+        <v>12.3</v>
+      </c>
+      <c r="O296" s="11">
+        <v>10.4</v>
+      </c>
+      <c r="P296" s="11">
+        <v>11.8</v>
+      </c>
+      <c r="Q296" s="11">
+        <v>56</v>
+      </c>
+      <c r="R296" s="11">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="S296" s="11">
+        <v>35.9</v>
+      </c>
+      <c r="T296" s="11">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="U296" s="11">
+        <v>3.85</v>
+      </c>
+      <c r="V296" s="11">
+        <v>4.45</v>
+      </c>
+      <c r="W296" s="11">
+        <v>16</v>
+      </c>
+      <c r="X296" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="Y296" s="11">
+        <v>10.976000000000001</v>
+      </c>
+      <c r="Z296" s="18"/>
+    </row>
+    <row r="297" spans="1:26">
+      <c r="A297" s="8">
+        <v>46191</v>
+      </c>
+      <c r="B297" s="8">
+        <v>46191</v>
+      </c>
+      <c r="C297" s="9">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D297" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z297" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -39517,36 +40096,36 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:AK8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.1640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.1640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="9.5" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.5" style="11" customWidth="1"/>
-    <col min="9" max="9" width="9.83203125" style="11" customWidth="1"/>
+    <col min="7" max="7" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.44140625" style="11" customWidth="1"/>
+    <col min="9" max="9" width="9.77734375" style="11" customWidth="1"/>
     <col min="10" max="10" width="10.33203125" style="11" customWidth="1"/>
-    <col min="11" max="11" width="9.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" style="11"/>
-    <col min="13" max="13" width="9.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" s="5" customFormat="1">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="21" t="s">
         <v>52</v>
       </c>
       <c r="E1" s="6" t="s">
@@ -39626,10 +40205,10 @@
       <c r="AK1" s="12"/>
     </row>
     <row r="2" spans="1:37">
-      <c r="A2" s="18"/>
-      <c r="B2" s="18"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="20"/>
+      <c r="A2" s="19"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="21"/>
       <c r="E2" s="6" t="s">
         <v>54</v>
       </c>
@@ -40163,17 +40742,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:Y24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.1640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.109375" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.1640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="15"/>
-    <col min="7" max="7" width="9.5" style="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5" style="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.44140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.44140625" style="15" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="15"/>
-    <col min="10" max="10" width="11.83203125" style="17" customWidth="1"/>
+    <col min="10" max="10" width="11.77734375" style="17" customWidth="1"/>
     <col min="11" max="12" width="9" style="15"/>
     <col min="13" max="13" width="13.33203125" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
@@ -40181,16 +40760,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="5" customFormat="1">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="21" t="s">
         <v>52</v>
       </c>
       <c r="E1" s="14" t="s">
@@ -40234,10 +40813,10 @@
       <c r="Y1" s="4"/>
     </row>
     <row r="2" spans="1:25">
-      <c r="A2" s="18"/>
-      <c r="B2" s="18"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="20"/>
+      <c r="A2" s="19"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="21"/>
       <c r="E2" s="14" t="s">
         <v>54</v>
       </c>
@@ -41245,28 +41824,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:Y24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.1640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="5" customFormat="1">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="21" t="s">
         <v>52</v>
       </c>
       <c r="E1" s="13" t="s">
@@ -41304,10 +41883,10 @@
       <c r="Y1" s="4"/>
     </row>
     <row r="2" spans="1:25">
-      <c r="A2" s="20"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="20"/>
+      <c r="A2" s="21"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="21"/>
       <c r="E2" s="6" t="s">
         <v>54</v>
       </c>
@@ -42114,7 +42693,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="16384" width="9" style="3"/>
   </cols>
@@ -42129,11 +42708,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:D32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="22.83203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.83203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.83203125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="22.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.77734375" style="3" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD1EC142-5923-443E-A29D-870838302A5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6B5358B-32CC-4CDE-8E46-CCD3CCED3A7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -2248,6 +2248,9 @@
                 <c:pt idx="293">
                   <c:v>46</c:v>
                 </c:pt>
+                <c:pt idx="294">
+                  <c:v>46</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4069,6 +4072,9 @@
                 <c:pt idx="293">
                   <c:v>23.5</c:v>
                 </c:pt>
+                <c:pt idx="294">
+                  <c:v>23.5</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -5890,6 +5896,9 @@
                 <c:pt idx="293">
                   <c:v>69.125</c:v>
                 </c:pt>
+                <c:pt idx="294">
+                  <c:v>69.125</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -7711,6 +7720,9 @@
                 <c:pt idx="293">
                   <c:v>11.8</c:v>
                 </c:pt>
+                <c:pt idx="294">
+                  <c:v>11.8</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -9530,6 +9542,9 @@
                   <c:v>35.799999999999997</c:v>
                 </c:pt>
                 <c:pt idx="293">
+                  <c:v>35.9</c:v>
+                </c:pt>
+                <c:pt idx="294">
                   <c:v>35.9</c:v>
                 </c:pt>
               </c:numCache>
@@ -11369,6 +11384,9 @@
                 <c:pt idx="293">
                   <c:v>4.45</c:v>
                 </c:pt>
+                <c:pt idx="294">
+                  <c:v>4.45</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -13190,6 +13208,9 @@
                   <c:v>10.976000000000001</c:v>
                 </c:pt>
                 <c:pt idx="293">
+                  <c:v>10.976000000000001</c:v>
+                </c:pt>
+                <c:pt idx="294">
                   <c:v>10.976000000000001</c:v>
                 </c:pt>
               </c:numCache>
@@ -40077,6 +40098,69 @@
       <c r="D297" s="10" t="s">
         <v>53</v>
       </c>
+      <c r="E297" s="11">
+        <v>59.5</v>
+      </c>
+      <c r="F297" s="11">
+        <v>30.5</v>
+      </c>
+      <c r="G297" s="11">
+        <v>46</v>
+      </c>
+      <c r="H297" s="11">
+        <v>25.2</v>
+      </c>
+      <c r="I297" s="11">
+        <v>22.1</v>
+      </c>
+      <c r="J297" s="11">
+        <v>23.5</v>
+      </c>
+      <c r="K297" s="11">
+        <v>81</v>
+      </c>
+      <c r="L297" s="11">
+        <v>37.6</v>
+      </c>
+      <c r="M297" s="11">
+        <v>69.125</v>
+      </c>
+      <c r="N297" s="11">
+        <v>12.3</v>
+      </c>
+      <c r="O297" s="11">
+        <v>10.4</v>
+      </c>
+      <c r="P297" s="11">
+        <v>11.8</v>
+      </c>
+      <c r="Q297" s="11">
+        <v>56</v>
+      </c>
+      <c r="R297" s="11">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="S297" s="11">
+        <v>35.9</v>
+      </c>
+      <c r="T297" s="11">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="U297" s="11">
+        <v>3.85</v>
+      </c>
+      <c r="V297" s="11">
+        <v>4.45</v>
+      </c>
+      <c r="W297" s="11">
+        <v>16</v>
+      </c>
+      <c r="X297" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="Y297" s="11">
+        <v>10.976000000000001</v>
+      </c>
       <c r="Z297" s="18"/>
     </row>
   </sheetData>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6B5358B-32CC-4CDE-8E46-CCD3CCED3A7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBB8B64E-3A0A-4B65-802B-AF80D35C5F35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -1357,6 +1357,15 @@
                 <c:pt idx="294">
                   <c:v>46191</c:v>
                 </c:pt>
+                <c:pt idx="295">
+                  <c:v>46195</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>46195</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>46195</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2250,6 +2259,12 @@
                 </c:pt>
                 <c:pt idx="294">
                   <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>46.167000000000002</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>46.167000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3181,6 +3196,15 @@
                 <c:pt idx="294">
                   <c:v>46191</c:v>
                 </c:pt>
+                <c:pt idx="295">
+                  <c:v>46195</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>46195</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>46195</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4073,6 +4097,12 @@
                   <c:v>23.5</c:v>
                 </c:pt>
                 <c:pt idx="294">
+                  <c:v>23.5</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>23.5</c:v>
+                </c:pt>
+                <c:pt idx="296">
                   <c:v>23.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -5005,6 +5035,15 @@
                 <c:pt idx="294">
                   <c:v>46191</c:v>
                 </c:pt>
+                <c:pt idx="295">
+                  <c:v>46195</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>46195</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>46195</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5898,6 +5937,12 @@
                 </c:pt>
                 <c:pt idx="294">
                   <c:v>69.125</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>69.5</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>69.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6829,6 +6874,15 @@
                 <c:pt idx="294">
                   <c:v>46191</c:v>
                 </c:pt>
+                <c:pt idx="295">
+                  <c:v>46195</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>46195</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>46195</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7722,6 +7776,12 @@
                 </c:pt>
                 <c:pt idx="294">
                   <c:v>11.8</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>11.75</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>11.75</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8653,6 +8713,15 @@
                 <c:pt idx="294">
                   <c:v>46191</c:v>
                 </c:pt>
+                <c:pt idx="295">
+                  <c:v>46195</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>46195</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>46195</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9545,6 +9614,12 @@
                   <c:v>35.9</c:v>
                 </c:pt>
                 <c:pt idx="294">
+                  <c:v>35.9</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>35.9</c:v>
+                </c:pt>
+                <c:pt idx="296">
                   <c:v>35.9</c:v>
                 </c:pt>
               </c:numCache>
@@ -10493,6 +10568,15 @@
                 <c:pt idx="294">
                   <c:v>46191</c:v>
                 </c:pt>
+                <c:pt idx="295">
+                  <c:v>46195</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>46195</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>46195</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -11386,6 +11470,12 @@
                 </c:pt>
                 <c:pt idx="294">
                   <c:v>4.45</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>4.407</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>4.407</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12319,6 +12409,15 @@
                 <c:pt idx="294">
                   <c:v>46191</c:v>
                 </c:pt>
+                <c:pt idx="295">
+                  <c:v>46195</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>46195</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>46195</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13212,6 +13311,12 @@
                 </c:pt>
                 <c:pt idx="294">
                   <c:v>10.976000000000001</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>11.032999999999999</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>11.151999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13538,149 +13643,164 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Module!$B$3:$B$1121</c:f>
+              <c:f>Module!$B$4:$B$1123</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="1119"/>
+                <c:ptCount val="1120"/>
                 <c:pt idx="0">
+                  <c:v>46027</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>46034</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>46041</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>46048</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>46055</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>46062</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>46076</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>46083</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>46090</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>46097</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>46104</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>46111</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>46118</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>46125</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>46132</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>46139</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>46146</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>46153</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>46160</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="19">
                   <c:v>46167</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="20">
                   <c:v>46174</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="21">
                   <c:v>46181</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="22">
                   <c:v>46188</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>46195</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Module!$G$3:$G$1121</c:f>
+              <c:f>Module!$G$3:$G$1123</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0.0_);_(* \(#,##0.0\);_(* "-"??_);_(@_)</c:formatCode>
-                <c:ptCount val="1119"/>
+                <c:ptCount val="1121"/>
                 <c:pt idx="0">
+                  <c:v>142.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>157.5</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>177.5</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>215</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>250</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="6">
                   <c:v>250</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
                   <c:v>245</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="8">
                   <c:v>245</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="9">
                   <c:v>240</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="10">
                   <c:v>230</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="11">
                   <c:v>232.5</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="12">
                   <c:v>232.5</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="13">
                   <c:v>242.5</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="14">
                   <c:v>222.5</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="15">
                   <c:v>219</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="16">
                   <c:v>218.5</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="17">
                   <c:v>216</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="18">
                   <c:v>215.5</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="19">
                   <c:v>215</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="20">
                   <c:v>214</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="21">
                   <c:v>212.5</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="22">
                   <c:v>211</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="23">
+                  <c:v>209</c:v>
+                </c:pt>
+                <c:pt idx="24">
                   <c:v>209</c:v>
                 </c:pt>
               </c:numCache>
@@ -13724,150 +13844,165 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Module!$B$3:$B$1121</c:f>
+              <c:f>Module!$B$4:$B$1123</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="1119"/>
+                <c:ptCount val="1120"/>
                 <c:pt idx="0">
+                  <c:v>46027</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>46034</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>46041</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>46048</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>46055</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>46062</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>46076</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>46083</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>46090</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>46097</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>46104</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>46111</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>46118</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>46125</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>46132</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>46139</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>46146</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>46153</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>46160</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="19">
                   <c:v>46167</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="20">
                   <c:v>46174</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="21">
                   <c:v>46181</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="22">
                   <c:v>46188</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>46195</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Module!$M$3:$M$1121</c:f>
+              <c:f>Module!$M$3:$M$1123</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
-                <c:ptCount val="1119"/>
+                <c:ptCount val="1121"/>
                 <c:pt idx="0">
+                  <c:v>79.599999999999994</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>84.667000000000002</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>89.332999999999998</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>94</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>99.667000000000002</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>110</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="6">
                   <c:v>118.333</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
                   <c:v>121</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="8">
                   <c:v>122.667</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="9">
                   <c:v>123.333</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="10">
                   <c:v>126.667</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="11">
                   <c:v>132.333</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="12">
                   <c:v>143.333</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="13">
                   <c:v>150</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="14">
                   <c:v>149.333</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="15">
                   <c:v>149.209</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="16">
                   <c:v>148.86799999999999</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="17">
                   <c:v>148.83000000000001</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="18">
                   <c:v>148.435</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="19">
                   <c:v>150.761</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="20">
                   <c:v>150.435</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="21">
                   <c:v>150.261</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="22">
                   <c:v>150.08699999999999</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="23">
                   <c:v>150.08699999999999</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>149.92400000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13926,150 +14061,165 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Module!$B$3:$B$1121</c:f>
+              <c:f>Module!$B$4:$B$1123</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="1119"/>
+                <c:ptCount val="1120"/>
                 <c:pt idx="0">
+                  <c:v>46027</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>46034</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>46041</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>46048</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>46055</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>46062</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>46076</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>46083</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>46090</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>46097</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>46104</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>46111</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>46118</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>46125</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>46132</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>46139</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>46146</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>46153</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>46160</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="19">
                   <c:v>46167</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="20">
                   <c:v>46174</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="21">
                   <c:v>46181</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="22">
                   <c:v>46188</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>46195</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Module!$J$3:$J$1121</c:f>
+              <c:f>Module!$J$3:$J$1123</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0.0_);_(* \(#,##0.0\);_(* "-"??_);_(@_)</c:formatCode>
-                <c:ptCount val="1119"/>
+                <c:ptCount val="1121"/>
                 <c:pt idx="0">
+                  <c:v>447.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>460</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>480</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>545</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>715</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>850</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="6">
                   <c:v>870</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
                   <c:v>885</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="8">
                   <c:v>890</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="9">
                   <c:v>900</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="10">
                   <c:v>910</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="11">
                   <c:v>917.5</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="12">
                   <c:v>925</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="13">
                   <c:v>935</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="14">
                   <c:v>930</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="15">
                   <c:v>975</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="16">
                   <c:v>970</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="17">
                   <c:v>960</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="18">
                   <c:v>960</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="19">
                   <c:v>975</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="20">
                   <c:v>1020</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="21">
                   <c:v>1035</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="22">
                   <c:v>1075</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="23">
                   <c:v>1250</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1275</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14397,138 +14547,144 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>GDDR!$B$3:$B$1121</c:f>
+              <c:f>GDDR!$B$4:$B$1123</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="1119"/>
+                <c:ptCount val="1120"/>
                 <c:pt idx="0">
+                  <c:v>46027</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>46034</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>46041</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>46048</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>46055</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>46062</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>46076</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>46083</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>46090</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>46097</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>46104</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>46111</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>46118</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>46125</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>46132</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>46139</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>46146</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>46153</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>46160</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="19">
                   <c:v>46167</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="20">
                   <c:v>46174</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="21">
                   <c:v>46181</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="22">
                   <c:v>46188</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>46195</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>GDDR!$G$3:$G$1121</c:f>
+              <c:f>GDDR!$G$3:$G$1123</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
-                <c:ptCount val="1119"/>
+                <c:ptCount val="1121"/>
                 <c:pt idx="0">
+                  <c:v>5.4359999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.5449999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>6</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>7.0910000000000002</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>7.8819791193826605</c:v>
-                </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
+                  <c:v>7.8819999999999997</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>8.6820000000000004</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="6">
                   <c:v>9.4090000000000007</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
                   <c:v>9.6359999999999992</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="8">
                   <c:v>10</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="9">
                   <c:v>10.455</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="10">
                   <c:v>11.182</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="11">
                   <c:v>11.682</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="12">
                   <c:v>12.727</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="13">
                   <c:v>12.526999999999999</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="14">
                   <c:v>12.318</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="15">
                   <c:v>12.227</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="16">
                   <c:v>11.864000000000001</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="17">
                   <c:v>11.773</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>11.635999999999999</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>11.635999999999999</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>11.635999999999999</c:v>
@@ -14537,9 +14693,18 @@
                   <c:v>11.635999999999999</c:v>
                 </c:pt>
                 <c:pt idx="20">
+                  <c:v>11.635999999999999</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>11.635999999999999</c:v>
+                </c:pt>
+                <c:pt idx="22">
                   <c:v>11.545</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="23">
+                  <c:v>11.545</c:v>
+                </c:pt>
+                <c:pt idx="24">
                   <c:v>11.545</c:v>
                 </c:pt>
               </c:numCache>
@@ -14583,149 +14748,164 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>GDDR!$B$3:$B$1121</c:f>
+              <c:f>GDDR!$B$4:$B$1123</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="1119"/>
+                <c:ptCount val="1120"/>
                 <c:pt idx="0">
+                  <c:v>46027</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>46034</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>46041</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>46048</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>46055</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>46062</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>46076</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>46083</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>46090</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>46097</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>46104</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>46111</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>46118</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>46125</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>46132</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>46139</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>46146</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>46153</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>46160</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="19">
                   <c:v>46167</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="20">
                   <c:v>46174</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="21">
                   <c:v>46181</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="22">
                   <c:v>46188</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>46195</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>GDDR!$J$3:$J$1121</c:f>
+              <c:f>GDDR!$J$3:$J$1123</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
-                <c:ptCount val="1119"/>
+                <c:ptCount val="1121"/>
                 <c:pt idx="0">
+                  <c:v>5.2210000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.45</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>5.9690000000000003</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>7.1539999999999999</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>8.0379000816030466</c:v>
-                </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
+                  <c:v>8.0380000000000003</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>8.8650000000000002</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="6">
                   <c:v>9.6539999999999999</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
                   <c:v>9.8650000000000002</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="8">
                   <c:v>10.221</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="9">
                   <c:v>10.721</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="10">
                   <c:v>11.462</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="11">
                   <c:v>11.962</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="12">
                   <c:v>12.865</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="13">
                   <c:v>12.71</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="14">
                   <c:v>12.412000000000001</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="15">
                   <c:v>12.335000000000001</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="16">
                   <c:v>11.962</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="17">
                   <c:v>11.829000000000001</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="18">
                   <c:v>11.702</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="19">
                   <c:v>11.632999999999999</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="20">
                   <c:v>11.632999999999999</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="21">
                   <c:v>11.651999999999999</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="22">
                   <c:v>11.537000000000001</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="23">
+                  <c:v>11.522</c:v>
+                </c:pt>
+                <c:pt idx="24">
                   <c:v>11.522</c:v>
                 </c:pt>
               </c:numCache>
@@ -16995,7 +17175,7 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Z297"/>
+  <dimension ref="A1:Z300"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="8" bestFit="1" customWidth="1"/>
@@ -40162,6 +40342,174 @@
         <v>10.976000000000001</v>
       </c>
       <c r="Z297" s="18"/>
+    </row>
+    <row r="298" spans="1:26">
+      <c r="A298" s="8">
+        <v>46195</v>
+      </c>
+      <c r="B298" s="8">
+        <v>46195</v>
+      </c>
+      <c r="C298" s="9">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D298" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E298" s="11">
+        <v>59.5</v>
+      </c>
+      <c r="F298" s="11">
+        <v>31</v>
+      </c>
+      <c r="G298" s="11">
+        <v>46.167000000000002</v>
+      </c>
+      <c r="H298" s="11">
+        <v>25.2</v>
+      </c>
+      <c r="I298" s="11">
+        <v>22.1</v>
+      </c>
+      <c r="J298" s="11">
+        <v>23.5</v>
+      </c>
+      <c r="K298" s="11">
+        <v>82</v>
+      </c>
+      <c r="L298" s="11">
+        <v>38</v>
+      </c>
+      <c r="M298" s="11">
+        <v>69.5</v>
+      </c>
+      <c r="N298" s="11">
+        <v>12.2</v>
+      </c>
+      <c r="O298" s="11">
+        <v>10.3</v>
+      </c>
+      <c r="P298" s="11">
+        <v>11.75</v>
+      </c>
+      <c r="Q298" s="11">
+        <v>55.5</v>
+      </c>
+      <c r="R298" s="11">
+        <v>19</v>
+      </c>
+      <c r="S298" s="11">
+        <v>35.9</v>
+      </c>
+      <c r="T298" s="11">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="U298" s="11">
+        <v>3.85</v>
+      </c>
+      <c r="V298" s="11">
+        <v>4.407</v>
+      </c>
+      <c r="W298" s="11">
+        <v>16</v>
+      </c>
+      <c r="X298" s="11">
+        <v>6.6</v>
+      </c>
+      <c r="Y298" s="11">
+        <v>11.032999999999999</v>
+      </c>
+    </row>
+    <row r="299" spans="1:26">
+      <c r="A299" s="8">
+        <v>46195</v>
+      </c>
+      <c r="B299" s="8">
+        <v>46195</v>
+      </c>
+      <c r="C299" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D299" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E299" s="11">
+        <v>59.5</v>
+      </c>
+      <c r="F299" s="11">
+        <v>31</v>
+      </c>
+      <c r="G299" s="11">
+        <v>46.167000000000002</v>
+      </c>
+      <c r="H299" s="11">
+        <v>25.2</v>
+      </c>
+      <c r="I299" s="11">
+        <v>22.1</v>
+      </c>
+      <c r="J299" s="11">
+        <v>23.5</v>
+      </c>
+      <c r="K299" s="11">
+        <v>82</v>
+      </c>
+      <c r="L299" s="11">
+        <v>38</v>
+      </c>
+      <c r="M299" s="11">
+        <v>69.5</v>
+      </c>
+      <c r="N299" s="11">
+        <v>12.2</v>
+      </c>
+      <c r="O299" s="11">
+        <v>10.3</v>
+      </c>
+      <c r="P299" s="11">
+        <v>11.75</v>
+      </c>
+      <c r="Q299" s="11">
+        <v>55.5</v>
+      </c>
+      <c r="R299" s="11">
+        <v>19</v>
+      </c>
+      <c r="S299" s="11">
+        <v>35.9</v>
+      </c>
+      <c r="T299" s="11">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="U299" s="11">
+        <v>3.8</v>
+      </c>
+      <c r="V299" s="11">
+        <v>4.407</v>
+      </c>
+      <c r="W299" s="11">
+        <v>16.5</v>
+      </c>
+      <c r="X299" s="11">
+        <v>6.6</v>
+      </c>
+      <c r="Y299" s="11">
+        <v>11.151999999999999</v>
+      </c>
+    </row>
+    <row r="300" spans="1:26">
+      <c r="A300" s="8">
+        <v>46195</v>
+      </c>
+      <c r="B300" s="8">
+        <v>46195</v>
+      </c>
+      <c r="C300" s="9">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D300" s="10" t="s">
+        <v>53</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -40825,13 +41173,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:Y24"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.21875" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="15"/>
     <col min="7" max="7" width="9.44140625" style="17" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.44140625" style="15" bestFit="1" customWidth="1"/>
@@ -40943,10 +41291,10 @@
     </row>
     <row r="3" spans="1:25">
       <c r="A3" s="8">
-        <v>46027</v>
+        <v>46013</v>
       </c>
       <c r="B3" s="8">
-        <v>46034</v>
+        <v>46020</v>
       </c>
       <c r="C3" s="9">
         <v>0.61111111111111105</v>
@@ -40955,31 +41303,31 @@
         <v>57</v>
       </c>
       <c r="E3" s="14">
-        <v>210</v>
+        <v>175</v>
       </c>
       <c r="F3" s="14">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="G3" s="16">
-        <v>157.5</v>
+        <v>142.5</v>
       </c>
       <c r="H3" s="14">
-        <v>575</v>
+        <v>475</v>
       </c>
       <c r="I3" s="14">
-        <v>450</v>
+        <v>420</v>
       </c>
       <c r="J3" s="16">
-        <v>480</v>
+        <v>447.5</v>
       </c>
       <c r="K3" s="14">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="L3" s="14">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="M3" s="6">
-        <v>89.332999999999998</v>
+        <v>79.599999999999994</v>
       </c>
       <c r="N3" s="6"/>
       <c r="O3" s="6"/>
@@ -40996,96 +41344,96 @@
     </row>
     <row r="4" spans="1:25">
       <c r="A4" s="8">
-        <v>46034</v>
+        <v>46020</v>
       </c>
       <c r="B4" s="8">
-        <v>46041</v>
+        <v>46027</v>
       </c>
       <c r="C4" s="9">
         <v>0.61111111111111105</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E4" s="14">
-        <v>230</v>
+        <v>195</v>
       </c>
       <c r="F4" s="14">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="G4" s="16">
-        <v>177.5</v>
+        <v>150</v>
       </c>
       <c r="H4" s="14">
-        <v>630</v>
+        <v>500</v>
       </c>
       <c r="I4" s="14">
-        <v>490</v>
+        <v>430</v>
       </c>
       <c r="J4" s="16">
-        <v>545</v>
+        <v>460</v>
       </c>
       <c r="K4" s="14">
-        <v>130</v>
+        <v>98</v>
       </c>
       <c r="L4" s="14">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="M4" s="6">
-        <v>94</v>
-      </c>
-      <c r="N4" s="7"/>
-      <c r="O4" s="7"/>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="7"/>
-      <c r="S4" s="7"/>
-      <c r="T4" s="7"/>
-      <c r="U4" s="7"/>
-      <c r="V4" s="7"/>
+        <v>84.667000000000002</v>
+      </c>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6"/>
+      <c r="U4" s="6"/>
+      <c r="V4" s="6"/>
       <c r="W4" s="6"/>
       <c r="X4" s="6"/>
       <c r="Y4" s="6"/>
     </row>
     <row r="5" spans="1:25">
       <c r="A5" s="8">
-        <v>46041</v>
+        <v>46027</v>
       </c>
       <c r="B5" s="8">
-        <v>46048</v>
+        <v>46034</v>
       </c>
       <c r="C5" s="9">
         <v>0.61111111111111105</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E5" s="14">
-        <v>270</v>
+        <v>210</v>
       </c>
       <c r="F5" s="14">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="G5" s="16">
-        <v>215</v>
+        <v>157.5</v>
       </c>
       <c r="H5" s="14">
-        <v>830</v>
+        <v>575</v>
       </c>
       <c r="I5" s="14">
-        <v>620</v>
+        <v>450</v>
       </c>
       <c r="J5" s="16">
-        <v>715</v>
+        <v>480</v>
       </c>
       <c r="K5" s="14">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="L5" s="14">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="M5" s="6">
-        <v>99.667000000000002</v>
+        <v>89.332999999999998</v>
       </c>
       <c r="N5" s="6"/>
       <c r="O5" s="6"/>
@@ -41102,10 +41450,10 @@
     </row>
     <row r="6" spans="1:25">
       <c r="A6" s="8">
-        <v>46048</v>
+        <v>46034</v>
       </c>
       <c r="B6" s="8">
-        <v>46055</v>
+        <v>46041</v>
       </c>
       <c r="C6" s="9">
         <v>0.61111111111111105</v>
@@ -41114,51 +41462,51 @@
         <v>53</v>
       </c>
       <c r="E6" s="14">
-        <v>280</v>
+        <v>230</v>
       </c>
       <c r="F6" s="14">
-        <v>230</v>
+        <v>160</v>
       </c>
       <c r="G6" s="16">
-        <v>250</v>
+        <v>177.5</v>
       </c>
       <c r="H6" s="14">
-        <v>1000</v>
+        <v>630</v>
       </c>
       <c r="I6" s="14">
-        <v>700</v>
+        <v>490</v>
       </c>
       <c r="J6" s="16">
-        <v>850</v>
+        <v>545</v>
       </c>
       <c r="K6" s="14">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="L6" s="14">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="M6" s="6">
-        <v>110</v>
-      </c>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="6"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="6"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
+        <v>94</v>
+      </c>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7"/>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="7"/>
+      <c r="V6" s="7"/>
       <c r="W6" s="6"/>
       <c r="X6" s="6"/>
       <c r="Y6" s="6"/>
     </row>
     <row r="7" spans="1:25">
       <c r="A7" s="8">
-        <v>46055</v>
+        <v>46041</v>
       </c>
       <c r="B7" s="8">
-        <v>46062</v>
+        <v>46048</v>
       </c>
       <c r="C7" s="9">
         <v>0.61111111111111105</v>
@@ -41166,122 +41514,146 @@
       <c r="D7" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="15">
-        <v>280</v>
-      </c>
-      <c r="F7" s="15">
-        <v>235</v>
-      </c>
-      <c r="G7" s="17">
-        <v>250</v>
-      </c>
-      <c r="H7" s="15">
-        <v>1000</v>
-      </c>
-      <c r="I7" s="15">
-        <v>750</v>
-      </c>
-      <c r="J7" s="17">
-        <v>870</v>
-      </c>
-      <c r="K7" s="15">
-        <v>145</v>
-      </c>
-      <c r="L7" s="15">
-        <v>100</v>
-      </c>
-      <c r="M7" s="11">
-        <v>118.333</v>
-      </c>
+      <c r="E7" s="14">
+        <v>270</v>
+      </c>
+      <c r="F7" s="14">
+        <v>180</v>
+      </c>
+      <c r="G7" s="16">
+        <v>215</v>
+      </c>
+      <c r="H7" s="14">
+        <v>830</v>
+      </c>
+      <c r="I7" s="14">
+        <v>620</v>
+      </c>
+      <c r="J7" s="16">
+        <v>715</v>
+      </c>
+      <c r="K7" s="14">
+        <v>140</v>
+      </c>
+      <c r="L7" s="14">
+        <v>88</v>
+      </c>
+      <c r="M7" s="6">
+        <v>99.667000000000002</v>
+      </c>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="6"/>
+      <c r="T7" s="6"/>
+      <c r="U7" s="6"/>
+      <c r="V7" s="6"/>
+      <c r="W7" s="6"/>
+      <c r="X7" s="6"/>
+      <c r="Y7" s="6"/>
     </row>
     <row r="8" spans="1:25">
       <c r="A8" s="8">
-        <v>46062</v>
+        <v>46048</v>
       </c>
       <c r="B8" s="8">
-        <v>46076</v>
+        <v>46055</v>
       </c>
       <c r="C8" s="9">
         <v>0.61111111111111105</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="E8" s="15">
-        <v>259</v>
-      </c>
-      <c r="F8" s="15">
+        <v>53</v>
+      </c>
+      <c r="E8" s="14">
+        <v>280</v>
+      </c>
+      <c r="F8" s="14">
         <v>230</v>
       </c>
-      <c r="G8" s="17">
-        <v>245</v>
-      </c>
-      <c r="H8" s="15">
-        <v>970</v>
-      </c>
-      <c r="I8" s="15">
-        <v>800</v>
-      </c>
-      <c r="J8" s="17">
-        <v>885</v>
-      </c>
-      <c r="K8" s="15">
-        <v>148</v>
-      </c>
-      <c r="L8" s="15">
-        <v>105</v>
-      </c>
-      <c r="M8" s="11">
-        <v>121</v>
-      </c>
+      <c r="G8" s="16">
+        <v>250</v>
+      </c>
+      <c r="H8" s="14">
+        <v>1000</v>
+      </c>
+      <c r="I8" s="14">
+        <v>700</v>
+      </c>
+      <c r="J8" s="16">
+        <v>850</v>
+      </c>
+      <c r="K8" s="14">
+        <v>145</v>
+      </c>
+      <c r="L8" s="14">
+        <v>95</v>
+      </c>
+      <c r="M8" s="6">
+        <v>110</v>
+      </c>
+      <c r="N8" s="6"/>
+      <c r="O8" s="6"/>
+      <c r="P8" s="6"/>
+      <c r="Q8" s="6"/>
+      <c r="R8" s="6"/>
+      <c r="S8" s="6"/>
+      <c r="T8" s="6"/>
+      <c r="U8" s="6"/>
+      <c r="V8" s="6"/>
+      <c r="W8" s="6"/>
+      <c r="X8" s="6"/>
+      <c r="Y8" s="6"/>
     </row>
     <row r="9" spans="1:25">
       <c r="A9" s="8">
-        <v>46076</v>
+        <v>46055</v>
       </c>
       <c r="B9" s="8">
-        <v>46083</v>
+        <v>46062</v>
       </c>
       <c r="C9" s="9">
         <v>0.61111111111111105</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E9" s="15">
-        <v>259</v>
+        <v>280</v>
       </c>
       <c r="F9" s="15">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="G9" s="17">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="H9" s="15">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="I9" s="15">
-        <v>800</v>
+        <v>750</v>
       </c>
       <c r="J9" s="17">
-        <v>890</v>
+        <v>870</v>
       </c>
       <c r="K9" s="15">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="L9" s="15">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="M9" s="11">
-        <v>122.667</v>
+        <v>118.333</v>
       </c>
     </row>
     <row r="10" spans="1:25">
       <c r="A10" s="8">
-        <v>46083</v>
+        <v>46062</v>
       </c>
       <c r="B10" s="8">
-        <v>46090</v>
+        <v>46076</v>
       </c>
       <c r="C10" s="9">
         <v>0.61111111111111105</v>
@@ -41290,39 +41662,39 @@
         <v>57</v>
       </c>
       <c r="E10" s="15">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="F10" s="15">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="G10" s="17">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="H10" s="15">
-        <v>980</v>
+        <v>970</v>
       </c>
       <c r="I10" s="15">
-        <v>830</v>
+        <v>800</v>
       </c>
       <c r="J10" s="17">
-        <v>900</v>
+        <v>885</v>
       </c>
       <c r="K10" s="15">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="L10" s="15">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M10" s="11">
-        <v>123.333</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:25">
       <c r="A11" s="8">
-        <v>46090</v>
+        <v>46076</v>
       </c>
       <c r="B11" s="8">
-        <v>46097</v>
+        <v>46083</v>
       </c>
       <c r="C11" s="9">
         <v>0.61111111111111105</v>
@@ -41331,39 +41703,39 @@
         <v>57</v>
       </c>
       <c r="E11" s="15">
-        <v>240</v>
+        <v>259</v>
       </c>
       <c r="F11" s="15">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="G11" s="17">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="H11" s="15">
-        <v>990</v>
+        <v>970</v>
       </c>
       <c r="I11" s="15">
-        <v>850</v>
+        <v>800</v>
       </c>
       <c r="J11" s="17">
-        <v>910</v>
+        <v>890</v>
       </c>
       <c r="K11" s="15">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="L11" s="15">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="M11" s="11">
-        <v>126.667</v>
+        <v>122.667</v>
       </c>
     </row>
     <row r="12" spans="1:25">
       <c r="A12" s="8">
-        <v>46097</v>
+        <v>46083</v>
       </c>
       <c r="B12" s="8">
-        <v>46104</v>
+        <v>46090</v>
       </c>
       <c r="C12" s="9">
         <v>0.61111111111111105</v>
@@ -41372,39 +41744,39 @@
         <v>57</v>
       </c>
       <c r="E12" s="15">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="F12" s="15">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="G12" s="17">
-        <v>232.5</v>
+        <v>240</v>
       </c>
       <c r="H12" s="15">
-        <v>1050</v>
+        <v>980</v>
       </c>
       <c r="I12" s="15">
-        <v>860</v>
+        <v>830</v>
       </c>
       <c r="J12" s="17">
-        <v>917.5</v>
+        <v>900</v>
       </c>
       <c r="K12" s="15">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="L12" s="15">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="M12" s="11">
-        <v>132.333</v>
+        <v>123.333</v>
       </c>
     </row>
     <row r="13" spans="1:25">
       <c r="A13" s="8">
-        <v>46104</v>
+        <v>46090</v>
       </c>
       <c r="B13" s="8">
-        <v>46111</v>
+        <v>46097</v>
       </c>
       <c r="C13" s="9">
         <v>0.61111111111111105</v>
@@ -41413,39 +41785,39 @@
         <v>57</v>
       </c>
       <c r="E13" s="15">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="F13" s="15">
         <v>200</v>
       </c>
       <c r="G13" s="17">
-        <v>232.5</v>
+        <v>230</v>
       </c>
       <c r="H13" s="15">
-        <v>1060</v>
+        <v>990</v>
       </c>
       <c r="I13" s="15">
-        <v>870</v>
+        <v>850</v>
       </c>
       <c r="J13" s="17">
-        <v>925</v>
+        <v>910</v>
       </c>
       <c r="K13" s="15">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="L13" s="15">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="M13" s="11">
-        <v>143.333</v>
+        <v>126.667</v>
       </c>
     </row>
     <row r="14" spans="1:25">
       <c r="A14" s="8">
-        <v>46111</v>
+        <v>46097</v>
       </c>
       <c r="B14" s="8">
-        <v>46118</v>
+        <v>46104</v>
       </c>
       <c r="C14" s="9">
         <v>0.61111111111111105</v>
@@ -41454,39 +41826,39 @@
         <v>57</v>
       </c>
       <c r="E14" s="15">
-        <v>260</v>
+        <v>245</v>
       </c>
       <c r="F14" s="15">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="G14" s="17">
-        <v>242.5</v>
+        <v>232.5</v>
       </c>
       <c r="H14" s="15">
-        <v>1150</v>
+        <v>1050</v>
       </c>
       <c r="I14" s="15">
-        <v>880</v>
+        <v>860</v>
       </c>
       <c r="J14" s="17">
-        <v>935</v>
+        <v>917.5</v>
       </c>
       <c r="K14" s="15">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="L14" s="15">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="M14" s="11">
-        <v>150</v>
+        <v>132.333</v>
       </c>
     </row>
     <row r="15" spans="1:25">
       <c r="A15" s="8">
-        <v>46118</v>
+        <v>46104</v>
       </c>
       <c r="B15" s="8">
-        <v>46125</v>
+        <v>46111</v>
       </c>
       <c r="C15" s="9">
         <v>0.61111111111111105</v>
@@ -41495,39 +41867,39 @@
         <v>57</v>
       </c>
       <c r="E15" s="15">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="F15" s="15">
         <v>200</v>
       </c>
       <c r="G15" s="17">
-        <v>222.5</v>
+        <v>232.5</v>
       </c>
       <c r="H15" s="15">
-        <v>1150</v>
+        <v>1060</v>
       </c>
       <c r="I15" s="15">
-        <v>880</v>
+        <v>870</v>
       </c>
       <c r="J15" s="17">
-        <v>930</v>
+        <v>925</v>
       </c>
       <c r="K15" s="15">
         <v>171</v>
       </c>
       <c r="L15" s="15">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="M15" s="11">
-        <v>149.333</v>
+        <v>143.333</v>
       </c>
     </row>
     <row r="16" spans="1:25">
       <c r="A16" s="8">
-        <v>46125</v>
+        <v>46111</v>
       </c>
       <c r="B16" s="8">
-        <v>46132</v>
+        <v>46118</v>
       </c>
       <c r="C16" s="9">
         <v>0.61111111111111105</v>
@@ -41536,39 +41908,39 @@
         <v>57</v>
       </c>
       <c r="E16" s="15">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="F16" s="15">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="G16" s="17">
-        <v>219</v>
+        <v>242.5</v>
       </c>
       <c r="H16" s="15">
         <v>1150</v>
       </c>
       <c r="I16" s="15">
-        <v>900</v>
+        <v>880</v>
       </c>
       <c r="J16" s="17">
-        <v>975</v>
+        <v>935</v>
       </c>
       <c r="K16" s="15">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L16" s="15">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="M16" s="11">
-        <v>149.209</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17" spans="1:13">
       <c r="A17" s="8">
-        <v>46132</v>
+        <v>46118</v>
       </c>
       <c r="B17" s="8">
-        <v>46139</v>
+        <v>46125</v>
       </c>
       <c r="C17" s="9">
         <v>0.61111111111111105</v>
@@ -41577,39 +41949,39 @@
         <v>57</v>
       </c>
       <c r="E17" s="15">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="F17" s="15">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="G17" s="17">
-        <v>218.5</v>
+        <v>222.5</v>
       </c>
       <c r="H17" s="15">
-        <v>1185</v>
+        <v>1150</v>
       </c>
       <c r="I17" s="15">
         <v>880</v>
       </c>
       <c r="J17" s="17">
-        <v>970</v>
+        <v>930</v>
       </c>
       <c r="K17" s="15">
         <v>171</v>
       </c>
       <c r="L17" s="15">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M17" s="11">
-        <v>148.86799999999999</v>
+        <v>149.333</v>
       </c>
     </row>
     <row r="18" spans="1:13">
       <c r="A18" s="8">
-        <v>46139</v>
+        <v>46125</v>
       </c>
       <c r="B18" s="8">
-        <v>46146</v>
+        <v>46132</v>
       </c>
       <c r="C18" s="9">
         <v>0.61111111111111105</v>
@@ -41618,39 +41990,39 @@
         <v>57</v>
       </c>
       <c r="E18" s="15">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="F18" s="15">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="G18" s="17">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="H18" s="15">
-        <v>1170</v>
+        <v>1150</v>
       </c>
       <c r="I18" s="15">
-        <v>850</v>
+        <v>900</v>
       </c>
       <c r="J18" s="17">
-        <v>960</v>
+        <v>975</v>
       </c>
       <c r="K18" s="15">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L18" s="15">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="M18" s="11">
-        <v>148.83000000000001</v>
+        <v>149.209</v>
       </c>
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="8">
-        <v>46146</v>
+        <v>46132</v>
       </c>
       <c r="B19" s="8">
-        <v>46153</v>
+        <v>46139</v>
       </c>
       <c r="C19" s="9">
         <v>0.61111111111111105</v>
@@ -41659,39 +42031,39 @@
         <v>57</v>
       </c>
       <c r="E19" s="15">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="F19" s="15">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G19" s="17">
-        <v>215.5</v>
+        <v>218.5</v>
       </c>
       <c r="H19" s="15">
-        <v>1180</v>
+        <v>1185</v>
       </c>
       <c r="I19" s="15">
-        <v>860</v>
+        <v>880</v>
       </c>
       <c r="J19" s="17">
-        <v>960</v>
+        <v>970</v>
       </c>
       <c r="K19" s="15">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L19" s="15">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="M19" s="11">
-        <v>148.435</v>
+        <v>148.86799999999999</v>
       </c>
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="8">
-        <v>46153</v>
+        <v>46139</v>
       </c>
       <c r="B20" s="8">
-        <v>46160</v>
+        <v>46146</v>
       </c>
       <c r="C20" s="9">
         <v>0.61111111111111105</v>
@@ -41703,19 +42075,19 @@
         <v>220</v>
       </c>
       <c r="F20" s="15">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G20" s="17">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H20" s="15">
-        <v>1180</v>
+        <v>1170</v>
       </c>
       <c r="I20" s="15">
-        <v>900</v>
+        <v>850</v>
       </c>
       <c r="J20" s="17">
-        <v>975</v>
+        <v>960</v>
       </c>
       <c r="K20" s="15">
         <v>171</v>
@@ -41724,15 +42096,15 @@
         <v>138</v>
       </c>
       <c r="M20" s="11">
-        <v>150.761</v>
+        <v>148.83000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="8">
-        <v>46160</v>
+        <v>46146</v>
       </c>
       <c r="B21" s="8">
-        <v>46167</v>
+        <v>46153</v>
       </c>
       <c r="C21" s="9">
         <v>0.61111111111111105</v>
@@ -41741,39 +42113,39 @@
         <v>57</v>
       </c>
       <c r="E21" s="15">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F21" s="15">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="G21" s="17">
-        <v>214</v>
+        <v>215.5</v>
       </c>
       <c r="H21" s="15">
-        <v>1200</v>
+        <v>1180</v>
       </c>
       <c r="I21" s="15">
-        <v>920</v>
+        <v>860</v>
       </c>
       <c r="J21" s="17">
-        <v>1020</v>
+        <v>960</v>
       </c>
       <c r="K21" s="15">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="L21" s="15">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M21" s="11">
-        <v>150.435</v>
+        <v>148.435</v>
       </c>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="8">
-        <v>46167</v>
+        <v>46153</v>
       </c>
       <c r="B22" s="8">
-        <v>46174</v>
+        <v>46160</v>
       </c>
       <c r="C22" s="9">
         <v>0.61111111111111105</v>
@@ -41785,36 +42157,36 @@
         <v>220</v>
       </c>
       <c r="F22" s="15">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="G22" s="17">
-        <v>212.5</v>
+        <v>215</v>
       </c>
       <c r="H22" s="15">
-        <v>1200</v>
+        <v>1180</v>
       </c>
       <c r="I22" s="15">
-        <v>950</v>
+        <v>900</v>
       </c>
       <c r="J22" s="17">
-        <v>1035</v>
+        <v>975</v>
       </c>
       <c r="K22" s="15">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="L22" s="15">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M22" s="11">
-        <v>150.261</v>
+        <v>150.761</v>
       </c>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" s="8">
-        <v>46174</v>
+        <v>46160</v>
       </c>
       <c r="B23" s="8">
-        <v>46181</v>
+        <v>46167</v>
       </c>
       <c r="C23" s="9">
         <v>0.61111111111111105</v>
@@ -41823,39 +42195,39 @@
         <v>57</v>
       </c>
       <c r="E23" s="15">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F23" s="15">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G23" s="17">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="H23" s="15">
-        <v>1350</v>
+        <v>1200</v>
       </c>
       <c r="I23" s="15">
-        <v>1000</v>
+        <v>920</v>
       </c>
       <c r="J23" s="17">
-        <v>1075</v>
+        <v>1020</v>
       </c>
       <c r="K23" s="15">
         <v>173</v>
       </c>
       <c r="L23" s="15">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="M23" s="11">
-        <v>150.08699999999999</v>
+        <v>150.435</v>
       </c>
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="8">
-        <v>46181</v>
+        <v>46167</v>
       </c>
       <c r="B24" s="8">
-        <v>46188</v>
+        <v>46174</v>
       </c>
       <c r="C24" s="9">
         <v>0.61111111111111105</v>
@@ -41864,31 +42236,154 @@
         <v>57</v>
       </c>
       <c r="E24" s="15">
+        <v>220</v>
+      </c>
+      <c r="F24" s="15">
+        <v>205</v>
+      </c>
+      <c r="G24" s="17">
+        <v>212.5</v>
+      </c>
+      <c r="H24" s="15">
+        <v>1200</v>
+      </c>
+      <c r="I24" s="15">
+        <v>950</v>
+      </c>
+      <c r="J24" s="17">
+        <v>1035</v>
+      </c>
+      <c r="K24" s="15">
+        <v>174</v>
+      </c>
+      <c r="L24" s="15">
+        <v>137</v>
+      </c>
+      <c r="M24" s="11">
+        <v>150.261</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25" s="8">
+        <v>46174</v>
+      </c>
+      <c r="B25" s="8">
+        <v>46181</v>
+      </c>
+      <c r="C25" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="E25" s="15">
+        <v>218</v>
+      </c>
+      <c r="F25" s="15">
+        <v>203</v>
+      </c>
+      <c r="G25" s="17">
+        <v>211</v>
+      </c>
+      <c r="H25" s="15">
+        <v>1350</v>
+      </c>
+      <c r="I25" s="15">
+        <v>1000</v>
+      </c>
+      <c r="J25" s="17">
+        <v>1075</v>
+      </c>
+      <c r="K25" s="15">
+        <v>173</v>
+      </c>
+      <c r="L25" s="15">
+        <v>135</v>
+      </c>
+      <c r="M25" s="11">
+        <v>150.08699999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
+      <c r="A26" s="8">
+        <v>46181</v>
+      </c>
+      <c r="B26" s="8">
+        <v>46188</v>
+      </c>
+      <c r="C26" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="E26" s="15">
         <v>217</v>
       </c>
-      <c r="F24" s="15">
+      <c r="F26" s="15">
         <v>200</v>
       </c>
-      <c r="G24" s="17">
+      <c r="G26" s="17">
         <v>209</v>
       </c>
-      <c r="H24" s="15">
+      <c r="H26" s="15">
         <v>1550</v>
       </c>
-      <c r="I24" s="15">
+      <c r="I26" s="15">
         <v>1200</v>
       </c>
-      <c r="J24" s="17">
+      <c r="J26" s="17">
         <v>1250</v>
       </c>
-      <c r="K24" s="15">
+      <c r="K26" s="15">
         <v>170</v>
       </c>
-      <c r="L24" s="15">
+      <c r="L26" s="15">
         <v>136</v>
       </c>
-      <c r="M24" s="11">
+      <c r="M26" s="11">
         <v>150.08699999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
+      <c r="A27" s="8">
+        <v>46188</v>
+      </c>
+      <c r="B27" s="8">
+        <v>46195</v>
+      </c>
+      <c r="C27" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="E27" s="15">
+        <v>215</v>
+      </c>
+      <c r="F27" s="15">
+        <v>200</v>
+      </c>
+      <c r="G27" s="17">
+        <v>209</v>
+      </c>
+      <c r="H27" s="15">
+        <v>1580</v>
+      </c>
+      <c r="I27" s="15">
+        <v>1230</v>
+      </c>
+      <c r="J27" s="17">
+        <v>1275</v>
+      </c>
+      <c r="K27" s="15">
+        <v>170</v>
+      </c>
+      <c r="L27" s="15">
+        <v>135</v>
+      </c>
+      <c r="M27" s="11">
+        <v>149.92400000000001</v>
       </c>
     </row>
   </sheetData>
@@ -41907,13 +42402,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:Y24"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="10" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.109375" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="10" width="10.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
@@ -42007,34 +42502,34 @@
     </row>
     <row r="3" spans="1:25">
       <c r="A3" s="8">
-        <v>46027</v>
+        <v>46013</v>
       </c>
       <c r="B3" s="8">
-        <v>46034</v>
+        <v>46020</v>
       </c>
       <c r="C3" s="9">
         <v>0.61111111111111105</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E3" s="6">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F3" s="6">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="G3" s="6">
-        <v>6</v>
+        <v>5.4359999999999999</v>
       </c>
       <c r="H3" s="6">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I3" s="6">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="J3" s="6">
-        <v>5.9690000000000003</v>
+        <v>5.2210000000000001</v>
       </c>
       <c r="K3" s="6"/>
       <c r="L3" s="6"/>
@@ -42054,34 +42549,34 @@
     </row>
     <row r="4" spans="1:25">
       <c r="A4" s="8">
-        <v>46034</v>
+        <v>46020</v>
       </c>
       <c r="B4" s="8">
-        <v>46041</v>
+        <v>46027</v>
       </c>
       <c r="C4" s="9">
         <v>0.61111111111111105</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E4" s="6">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="F4" s="6">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="G4" s="6">
-        <v>7.0910000000000002</v>
+        <v>5.5449999999999999</v>
       </c>
       <c r="H4" s="6">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I4" s="6">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="J4" s="6">
-        <v>7.1539999999999999</v>
+        <v>5.45</v>
       </c>
       <c r="K4" s="6"/>
       <c r="L4" s="6"/>
@@ -42101,10 +42596,10 @@
     </row>
     <row r="5" spans="1:25">
       <c r="A5" s="8">
-        <v>46041</v>
+        <v>46027</v>
       </c>
       <c r="B5" s="8">
-        <v>46048</v>
+        <v>46034</v>
       </c>
       <c r="C5" s="9">
         <v>0.61111111111111105</v>
@@ -42112,15 +42607,23 @@
       <c r="D5" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
+      <c r="E5" s="6">
+        <v>12</v>
+      </c>
+      <c r="F5" s="6">
+        <v>5.2</v>
+      </c>
       <c r="G5" s="6">
-        <v>7.8819791193826605</v>
-      </c>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
+        <v>6</v>
+      </c>
+      <c r="H5" s="6">
+        <v>12</v>
+      </c>
+      <c r="I5" s="6">
+        <v>4.8</v>
+      </c>
       <c r="J5" s="6">
-        <v>8.0379000816030466</v>
+        <v>5.9690000000000003</v>
       </c>
       <c r="K5" s="6"/>
       <c r="L5" s="6"/>
@@ -42140,10 +42643,10 @@
     </row>
     <row r="6" spans="1:25">
       <c r="A6" s="8">
-        <v>46048</v>
+        <v>46034</v>
       </c>
       <c r="B6" s="8">
-        <v>46055</v>
+        <v>46041</v>
       </c>
       <c r="C6" s="9">
         <v>0.61111111111111105</v>
@@ -42152,22 +42655,22 @@
         <v>53</v>
       </c>
       <c r="E6" s="6">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="F6" s="6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G6" s="6">
-        <v>8.6820000000000004</v>
+        <v>7.0910000000000002</v>
       </c>
       <c r="H6" s="6">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I6" s="6">
-        <v>7.5</v>
+        <v>5.8</v>
       </c>
       <c r="J6" s="6">
-        <v>8.8650000000000002</v>
+        <v>7.1539999999999999</v>
       </c>
       <c r="K6" s="6"/>
       <c r="L6" s="6"/>
@@ -42187,10 +42690,10 @@
     </row>
     <row r="7" spans="1:25">
       <c r="A7" s="8">
-        <v>46055</v>
+        <v>46041</v>
       </c>
       <c r="B7" s="8">
-        <v>46062</v>
+        <v>46048</v>
       </c>
       <c r="C7" s="9">
         <v>0.61111111111111105</v>
@@ -42198,95 +42701,125 @@
       <c r="D7" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="11">
-        <v>15.5</v>
-      </c>
-      <c r="F7" s="11">
-        <v>7.5</v>
-      </c>
-      <c r="G7" s="11">
-        <v>9.4090000000000007</v>
-      </c>
-      <c r="H7" s="11">
-        <v>16</v>
-      </c>
-      <c r="I7" s="11">
-        <v>8</v>
-      </c>
-      <c r="J7" s="11">
-        <v>9.6539999999999999</v>
-      </c>
+      <c r="E7" s="6">
+        <v>14.5</v>
+      </c>
+      <c r="F7" s="6">
+        <v>6.3</v>
+      </c>
+      <c r="G7" s="6">
+        <v>7.8819999999999997</v>
+      </c>
+      <c r="H7" s="6">
+        <v>14</v>
+      </c>
+      <c r="I7" s="6">
+        <v>6.5</v>
+      </c>
+      <c r="J7" s="6">
+        <v>8.0380000000000003</v>
+      </c>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="6"/>
+      <c r="T7" s="6"/>
+      <c r="U7" s="6"/>
+      <c r="V7" s="6"/>
+      <c r="W7" s="6"/>
+      <c r="X7" s="6"/>
+      <c r="Y7" s="6"/>
     </row>
     <row r="8" spans="1:25">
       <c r="A8" s="8">
-        <v>46062</v>
+        <v>46048</v>
       </c>
       <c r="B8" s="8">
-        <v>46076</v>
+        <v>46055</v>
       </c>
       <c r="C8" s="9">
         <v>0.61111111111111105</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="E8" s="11">
+        <v>53</v>
+      </c>
+      <c r="E8" s="6">
         <v>15.5</v>
       </c>
-      <c r="F8" s="11">
-        <v>8</v>
-      </c>
-      <c r="G8" s="11">
-        <v>9.6359999999999992</v>
-      </c>
-      <c r="H8" s="11">
+      <c r="F8" s="6">
+        <v>7</v>
+      </c>
+      <c r="G8" s="6">
+        <v>8.6820000000000004</v>
+      </c>
+      <c r="H8" s="6">
         <v>16</v>
       </c>
-      <c r="I8" s="11">
-        <v>8.5</v>
-      </c>
-      <c r="J8" s="11">
-        <v>9.8650000000000002</v>
-      </c>
+      <c r="I8" s="6">
+        <v>7.5</v>
+      </c>
+      <c r="J8" s="6">
+        <v>8.8650000000000002</v>
+      </c>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="6"/>
+      <c r="P8" s="6"/>
+      <c r="Q8" s="6"/>
+      <c r="R8" s="6"/>
+      <c r="S8" s="6"/>
+      <c r="T8" s="6"/>
+      <c r="U8" s="6"/>
+      <c r="V8" s="6"/>
+      <c r="W8" s="6"/>
+      <c r="X8" s="6"/>
+      <c r="Y8" s="6"/>
     </row>
     <row r="9" spans="1:25">
       <c r="A9" s="8">
-        <v>46076</v>
+        <v>46055</v>
       </c>
       <c r="B9" s="8">
-        <v>46083</v>
+        <v>46062</v>
       </c>
       <c r="C9" s="9">
         <v>0.61111111111111105</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E9" s="11">
         <v>15.5</v>
       </c>
       <c r="F9" s="11">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="G9" s="11">
-        <v>10</v>
+        <v>9.4090000000000007</v>
       </c>
       <c r="H9" s="11">
         <v>16</v>
       </c>
       <c r="I9" s="11">
-        <v>8.8000000000000007</v>
+        <v>8</v>
       </c>
       <c r="J9" s="11">
-        <v>10.221</v>
+        <v>9.6539999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:25">
       <c r="A10" s="8">
-        <v>46083</v>
+        <v>46062</v>
       </c>
       <c r="B10" s="8">
-        <v>46090</v>
+        <v>46076</v>
       </c>
       <c r="C10" s="9">
         <v>0.61111111111111105</v>
@@ -42295,30 +42828,30 @@
         <v>57</v>
       </c>
       <c r="E10" s="11">
+        <v>15.5</v>
+      </c>
+      <c r="F10" s="11">
+        <v>8</v>
+      </c>
+      <c r="G10" s="11">
+        <v>9.6359999999999992</v>
+      </c>
+      <c r="H10" s="11">
         <v>16</v>
       </c>
-      <c r="F10" s="11">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="G10" s="11">
-        <v>10.455</v>
-      </c>
-      <c r="H10" s="11">
-        <v>16.5</v>
-      </c>
       <c r="I10" s="11">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="J10" s="11">
-        <v>10.721</v>
+        <v>9.8650000000000002</v>
       </c>
     </row>
     <row r="11" spans="1:25">
       <c r="A11" s="8">
-        <v>46090</v>
+        <v>46076</v>
       </c>
       <c r="B11" s="8">
-        <v>46097</v>
+        <v>46083</v>
       </c>
       <c r="C11" s="9">
         <v>0.61111111111111105</v>
@@ -42327,30 +42860,30 @@
         <v>57</v>
       </c>
       <c r="E11" s="11">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="F11" s="11">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="G11" s="11">
-        <v>11.182</v>
+        <v>10</v>
       </c>
       <c r="H11" s="11">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I11" s="11">
-        <v>10</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="J11" s="11">
-        <v>11.462</v>
+        <v>10.221</v>
       </c>
     </row>
     <row r="12" spans="1:25">
       <c r="A12" s="8">
-        <v>46097</v>
+        <v>46083</v>
       </c>
       <c r="B12" s="8">
-        <v>46104</v>
+        <v>46090</v>
       </c>
       <c r="C12" s="9">
         <v>0.61111111111111105</v>
@@ -42359,30 +42892,30 @@
         <v>57</v>
       </c>
       <c r="E12" s="11">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F12" s="11">
-        <v>10</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="G12" s="11">
-        <v>11.682</v>
+        <v>10.455</v>
       </c>
       <c r="H12" s="11">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="I12" s="11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J12" s="11">
-        <v>11.962</v>
+        <v>10.721</v>
       </c>
     </row>
     <row r="13" spans="1:25">
       <c r="A13" s="8">
-        <v>46104</v>
+        <v>46090</v>
       </c>
       <c r="B13" s="8">
-        <v>46111</v>
+        <v>46097</v>
       </c>
       <c r="C13" s="9">
         <v>0.61111111111111105</v>
@@ -42391,30 +42924,30 @@
         <v>57</v>
       </c>
       <c r="E13" s="11">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F13" s="11">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="G13" s="11">
-        <v>12.727</v>
+        <v>11.182</v>
       </c>
       <c r="H13" s="11">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I13" s="11">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J13" s="11">
-        <v>12.865</v>
+        <v>11.462</v>
       </c>
     </row>
     <row r="14" spans="1:25">
       <c r="A14" s="8">
-        <v>46111</v>
+        <v>46097</v>
       </c>
       <c r="B14" s="8">
-        <v>46118</v>
+        <v>46104</v>
       </c>
       <c r="C14" s="9">
         <v>0.61111111111111105</v>
@@ -42423,30 +42956,30 @@
         <v>57</v>
       </c>
       <c r="E14" s="11">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F14" s="11">
         <v>10</v>
       </c>
       <c r="G14" s="11">
-        <v>12.526999999999999</v>
+        <v>11.682</v>
       </c>
       <c r="H14" s="11">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I14" s="11">
         <v>10</v>
       </c>
       <c r="J14" s="11">
-        <v>12.71</v>
+        <v>11.962</v>
       </c>
     </row>
     <row r="15" spans="1:25">
       <c r="A15" s="8">
-        <v>46118</v>
+        <v>46104</v>
       </c>
       <c r="B15" s="8">
-        <v>46125</v>
+        <v>46111</v>
       </c>
       <c r="C15" s="9">
         <v>0.61111111111111105</v>
@@ -42458,27 +42991,27 @@
         <v>20</v>
       </c>
       <c r="F15" s="11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G15" s="11">
-        <v>12.318</v>
+        <v>12.727</v>
       </c>
       <c r="H15" s="11">
         <v>20</v>
       </c>
       <c r="I15" s="11">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="J15" s="11">
-        <v>12.412000000000001</v>
+        <v>12.865</v>
       </c>
     </row>
     <row r="16" spans="1:25">
       <c r="A16" s="8">
-        <v>46125</v>
+        <v>46111</v>
       </c>
       <c r="B16" s="8">
-        <v>46132</v>
+        <v>46118</v>
       </c>
       <c r="C16" s="9">
         <v>0.61111111111111105</v>
@@ -42487,30 +43020,30 @@
         <v>57</v>
       </c>
       <c r="E16" s="11">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="F16" s="11">
         <v>10</v>
       </c>
       <c r="G16" s="11">
-        <v>12.227</v>
+        <v>12.526999999999999</v>
       </c>
       <c r="H16" s="11">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I16" s="11">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="J16" s="11">
-        <v>12.335000000000001</v>
+        <v>12.71</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="8">
-        <v>46132</v>
+        <v>46118</v>
       </c>
       <c r="B17" s="8">
-        <v>46139</v>
+        <v>46125</v>
       </c>
       <c r="C17" s="9">
         <v>0.61111111111111105</v>
@@ -42519,30 +43052,30 @@
         <v>57</v>
       </c>
       <c r="E17" s="11">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F17" s="11">
+        <v>10</v>
+      </c>
+      <c r="G17" s="11">
+        <v>12.318</v>
+      </c>
+      <c r="H17" s="11">
+        <v>20</v>
+      </c>
+      <c r="I17" s="11">
         <v>9.5</v>
       </c>
-      <c r="G17" s="11">
-        <v>11.864000000000001</v>
-      </c>
-      <c r="H17" s="11">
-        <v>18</v>
-      </c>
-      <c r="I17" s="11">
-        <v>9</v>
-      </c>
       <c r="J17" s="11">
-        <v>11.962</v>
+        <v>12.412000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="8">
-        <v>46139</v>
+        <v>46125</v>
       </c>
       <c r="B18" s="8">
-        <v>46146</v>
+        <v>46132</v>
       </c>
       <c r="C18" s="9">
         <v>0.61111111111111105</v>
@@ -42551,30 +43084,30 @@
         <v>57</v>
       </c>
       <c r="E18" s="11">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="F18" s="11">
+        <v>10</v>
+      </c>
+      <c r="G18" s="11">
+        <v>12.227</v>
+      </c>
+      <c r="H18" s="11">
+        <v>19</v>
+      </c>
+      <c r="I18" s="11">
         <v>9.5</v>
       </c>
-      <c r="G18" s="11">
-        <v>11.773</v>
-      </c>
-      <c r="H18" s="11">
-        <v>17.8</v>
-      </c>
-      <c r="I18" s="11">
-        <v>9</v>
-      </c>
       <c r="J18" s="11">
-        <v>11.829000000000001</v>
+        <v>12.335000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="8">
-        <v>46146</v>
+        <v>46132</v>
       </c>
       <c r="B19" s="8">
-        <v>46153</v>
+        <v>46139</v>
       </c>
       <c r="C19" s="9">
         <v>0.61111111111111105</v>
@@ -42583,30 +43116,30 @@
         <v>57</v>
       </c>
       <c r="E19" s="11">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="F19" s="11">
         <v>9.5</v>
       </c>
       <c r="G19" s="11">
-        <v>11.635999999999999</v>
+        <v>11.864000000000001</v>
       </c>
       <c r="H19" s="11">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="I19" s="11">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="J19" s="11">
-        <v>11.702</v>
+        <v>11.962</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="8">
-        <v>46153</v>
+        <v>46139</v>
       </c>
       <c r="B20" s="8">
-        <v>46160</v>
+        <v>46146</v>
       </c>
       <c r="C20" s="9">
         <v>0.61111111111111105</v>
@@ -42615,30 +43148,30 @@
         <v>57</v>
       </c>
       <c r="E20" s="11">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="F20" s="11">
         <v>9.5</v>
       </c>
       <c r="G20" s="11">
-        <v>11.635999999999999</v>
+        <v>11.773</v>
       </c>
       <c r="H20" s="11">
-        <v>17.5</v>
+        <v>17.8</v>
       </c>
       <c r="I20" s="11">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="J20" s="11">
-        <v>11.632999999999999</v>
+        <v>11.829000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="8">
-        <v>46160</v>
+        <v>46146</v>
       </c>
       <c r="B21" s="8">
-        <v>46167</v>
+        <v>46153</v>
       </c>
       <c r="C21" s="9">
         <v>0.61111111111111105</v>
@@ -42662,15 +43195,15 @@
         <v>9.5</v>
       </c>
       <c r="J21" s="11">
-        <v>11.632999999999999</v>
+        <v>11.702</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="8">
-        <v>46167</v>
+        <v>46153</v>
       </c>
       <c r="B22" s="8">
-        <v>46174</v>
+        <v>46160</v>
       </c>
       <c r="C22" s="9">
         <v>0.61111111111111105</v>
@@ -42694,15 +43227,15 @@
         <v>9.5</v>
       </c>
       <c r="J22" s="11">
-        <v>11.651999999999999</v>
+        <v>11.632999999999999</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="8">
-        <v>46174</v>
+        <v>46160</v>
       </c>
       <c r="B23" s="8">
-        <v>46181</v>
+        <v>46167</v>
       </c>
       <c r="C23" s="9">
         <v>0.61111111111111105</v>
@@ -42717,7 +43250,7 @@
         <v>9.5</v>
       </c>
       <c r="G23" s="11">
-        <v>11.545</v>
+        <v>11.635999999999999</v>
       </c>
       <c r="H23" s="11">
         <v>17.5</v>
@@ -42726,15 +43259,15 @@
         <v>9.5</v>
       </c>
       <c r="J23" s="11">
-        <v>11.537000000000001</v>
+        <v>11.632999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="8">
-        <v>46181</v>
+        <v>46167</v>
       </c>
       <c r="B24" s="8">
-        <v>46188</v>
+        <v>46174</v>
       </c>
       <c r="C24" s="9">
         <v>0.61111111111111105</v>
@@ -42749,15 +43282,111 @@
         <v>9.5</v>
       </c>
       <c r="G24" s="11">
-        <v>11.545</v>
+        <v>11.635999999999999</v>
       </c>
       <c r="H24" s="11">
         <v>17.5</v>
       </c>
       <c r="I24" s="11">
+        <v>9.5</v>
+      </c>
+      <c r="J24" s="11">
+        <v>11.651999999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="8">
+        <v>46174</v>
+      </c>
+      <c r="B25" s="8">
+        <v>46181</v>
+      </c>
+      <c r="C25" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="E25" s="11">
+        <v>17.5</v>
+      </c>
+      <c r="F25" s="11">
+        <v>9.5</v>
+      </c>
+      <c r="G25" s="11">
+        <v>11.545</v>
+      </c>
+      <c r="H25" s="11">
+        <v>17.5</v>
+      </c>
+      <c r="I25" s="11">
+        <v>9.5</v>
+      </c>
+      <c r="J25" s="11">
+        <v>11.537000000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="8">
+        <v>46181</v>
+      </c>
+      <c r="B26" s="8">
+        <v>46188</v>
+      </c>
+      <c r="C26" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="E26" s="11">
+        <v>17.5</v>
+      </c>
+      <c r="F26" s="11">
+        <v>9.5</v>
+      </c>
+      <c r="G26" s="11">
+        <v>11.545</v>
+      </c>
+      <c r="H26" s="11">
+        <v>17.5</v>
+      </c>
+      <c r="I26" s="11">
         <v>9</v>
       </c>
-      <c r="J24" s="11">
+      <c r="J26" s="11">
+        <v>11.522</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="8">
+        <v>46188</v>
+      </c>
+      <c r="B27" s="8">
+        <v>46195</v>
+      </c>
+      <c r="C27" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="E27" s="11">
+        <v>17.5</v>
+      </c>
+      <c r="F27" s="11">
+        <v>9.5</v>
+      </c>
+      <c r="G27" s="11">
+        <v>11.545</v>
+      </c>
+      <c r="H27" s="11">
+        <v>17.5</v>
+      </c>
+      <c r="I27" s="11">
+        <v>9</v>
+      </c>
+      <c r="J27" s="11">
         <v>11.522</v>
       </c>
     </row>
@@ -42777,14 +43406,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
-  <cols>
-    <col min="1" max="16384" width="9" style="3"/>
-  </cols>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10118"/>
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data/industry/TrendForce/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBB8B64E-3A0A-4B65-802B-AF80D35C5F35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34EB8659-B381-E047-B620-4A87C8C4AD14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25660" yWindow="600" windowWidth="25540" windowHeight="26040" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="61">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -247,6 +247,15 @@
   <si>
     <t>UTC+8</t>
   </si>
+  <si>
+    <t>DDR4 SODIMM 8GB 2666</t>
+  </si>
+  <si>
+    <t>DDR4 UDIMM 8GB 2666</t>
+  </si>
+  <si>
+    <t>DDR4 RDIMM 16GB 3200</t>
+  </si>
 </sst>
 </file>
 
@@ -399,10 +408,10 @@
     </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="백분율" xfId="3" builtinId="5"/>
-    <cellStyle name="쉼표" xfId="2" builtinId="3"/>
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="2" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -420,7 +429,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2266,6 +2275,9 @@
                 <c:pt idx="296">
                   <c:v>46.167000000000002</c:v>
                 </c:pt>
+                <c:pt idx="297">
+                  <c:v>46.167000000000002</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4105,6 +4117,9 @@
                 <c:pt idx="296">
                   <c:v>23.5</c:v>
                 </c:pt>
+                <c:pt idx="297">
+                  <c:v>23.5</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -5944,6 +5959,9 @@
                 <c:pt idx="296">
                   <c:v>69.5</c:v>
                 </c:pt>
+                <c:pt idx="297">
+                  <c:v>69.75</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -7783,6 +7801,9 @@
                 <c:pt idx="296">
                   <c:v>11.75</c:v>
                 </c:pt>
+                <c:pt idx="297">
+                  <c:v>11.75</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -9620,6 +9641,9 @@
                   <c:v>35.9</c:v>
                 </c:pt>
                 <c:pt idx="296">
+                  <c:v>35.9</c:v>
+                </c:pt>
+                <c:pt idx="297">
                   <c:v>35.9</c:v>
                 </c:pt>
               </c:numCache>
@@ -11477,6 +11501,9 @@
                 <c:pt idx="296">
                   <c:v>4.407</c:v>
                 </c:pt>
+                <c:pt idx="297">
+                  <c:v>4.407</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -13316,6 +13343,9 @@
                   <c:v>11.032999999999999</c:v>
                 </c:pt>
                 <c:pt idx="296">
+                  <c:v>11.151999999999999</c:v>
+                </c:pt>
+                <c:pt idx="297">
                   <c:v>11.151999999999999</c:v>
                 </c:pt>
               </c:numCache>
@@ -13595,7 +13625,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -13643,80 +13673,104 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Module!$B$4:$B$1123</c:f>
+              <c:f>Module!$B$3:$B$1130</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="1120"/>
+                <c:ptCount val="1128"/>
                 <c:pt idx="0">
+                  <c:v>45971</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>45978</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45985</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>45992</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46006</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46013</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46020</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>46027</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="9">
                   <c:v>46034</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="10">
                   <c:v>46041</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="11">
                   <c:v>46048</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="12">
                   <c:v>46055</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="13">
                   <c:v>46062</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="14">
                   <c:v>46076</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="15">
                   <c:v>46083</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="16">
                   <c:v>46090</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="17">
                   <c:v>46097</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="18">
                   <c:v>46104</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="19">
                   <c:v>46111</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="20">
                   <c:v>46118</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="21">
                   <c:v>46125</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="22">
                   <c:v>46132</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="23">
                   <c:v>46139</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="24">
                   <c:v>46146</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="25">
                   <c:v>46153</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="26">
                   <c:v>46160</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="27">
                   <c:v>46167</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="28">
                   <c:v>46174</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="29">
                   <c:v>46181</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="30">
                   <c:v>46188</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="31">
                   <c:v>46195</c:v>
                 </c:pt>
               </c:numCache>
@@ -13724,83 +13778,98 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Module!$G$3:$G$1123</c:f>
+              <c:f>Module!$G$3:$G$1130</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0.0_);_(* \(#,##0.0\);_(* "-"??_);_(@_)</c:formatCode>
-                <c:ptCount val="1121"/>
-                <c:pt idx="0">
+                <c:ptCount val="1128"/>
+                <c:pt idx="2">
+                  <c:v>100.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>115</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>117.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>127.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>142.5</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="8">
                   <c:v>150</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="9">
                   <c:v>157.5</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="10">
                   <c:v>177.5</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="11">
                   <c:v>215</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="12">
                   <c:v>250</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="13">
                   <c:v>250</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="14">
                   <c:v>245</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="15">
                   <c:v>245</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="16">
                   <c:v>240</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="17">
                   <c:v>230</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="18">
                   <c:v>232.5</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="19">
                   <c:v>232.5</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="20">
                   <c:v>242.5</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="21">
                   <c:v>222.5</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="22">
                   <c:v>219</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="23">
                   <c:v>218.5</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="24">
                   <c:v>216</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="25">
                   <c:v>215.5</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="26">
                   <c:v>215</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="27">
                   <c:v>214</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="28">
                   <c:v>212.5</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="29">
                   <c:v>211</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="30">
                   <c:v>209</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="31">
                   <c:v>209</c:v>
                 </c:pt>
               </c:numCache>
@@ -13844,80 +13913,104 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Module!$B$4:$B$1123</c:f>
+              <c:f>Module!$B$3:$B$1130</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="1120"/>
+                <c:ptCount val="1128"/>
                 <c:pt idx="0">
+                  <c:v>45971</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>45978</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45985</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>45992</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46006</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46013</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46020</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>46027</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="9">
                   <c:v>46034</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="10">
                   <c:v>46041</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="11">
                   <c:v>46048</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="12">
                   <c:v>46055</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="13">
                   <c:v>46062</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="14">
                   <c:v>46076</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="15">
                   <c:v>46083</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="16">
                   <c:v>46090</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="17">
                   <c:v>46097</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="18">
                   <c:v>46104</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="19">
                   <c:v>46111</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="20">
                   <c:v>46118</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="21">
                   <c:v>46125</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="22">
                   <c:v>46132</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="23">
                   <c:v>46139</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="24">
                   <c:v>46146</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="25">
                   <c:v>46153</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="26">
                   <c:v>46160</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="27">
                   <c:v>46167</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="28">
                   <c:v>46174</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="29">
                   <c:v>46181</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="30">
                   <c:v>46188</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="31">
                   <c:v>46195</c:v>
                 </c:pt>
               </c:numCache>
@@ -13925,83 +14018,98 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Module!$M$3:$M$1123</c:f>
+              <c:f>Module!$M$3:$M$1130</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
-                <c:ptCount val="1121"/>
-                <c:pt idx="0">
+                <c:ptCount val="1128"/>
+                <c:pt idx="2">
+                  <c:v>50.232999999999997</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>54.884</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>60.93</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>65.465000000000003</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>73.14</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>79.599999999999994</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="8">
                   <c:v>84.667000000000002</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="9">
                   <c:v>89.332999999999998</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="10">
                   <c:v>94</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="11">
                   <c:v>99.667000000000002</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="12">
                   <c:v>110</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="13">
                   <c:v>118.333</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="14">
                   <c:v>121</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="15">
                   <c:v>122.667</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="16">
                   <c:v>123.333</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="17">
                   <c:v>126.667</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="18">
                   <c:v>132.333</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="19">
                   <c:v>143.333</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="20">
                   <c:v>150</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="21">
                   <c:v>149.333</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="22">
                   <c:v>149.209</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="23">
                   <c:v>148.86799999999999</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="24">
                   <c:v>148.83000000000001</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="25">
                   <c:v>148.435</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="26">
                   <c:v>150.761</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="27">
                   <c:v>150.435</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="28">
                   <c:v>150.261</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="29">
                   <c:v>150.08699999999999</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="30">
                   <c:v>150.08699999999999</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="31">
                   <c:v>149.92400000000001</c:v>
                 </c:pt>
               </c:numCache>
@@ -14061,80 +14169,104 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Module!$B$4:$B$1123</c:f>
+              <c:f>Module!$B$3:$B$1130</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="1120"/>
+                <c:ptCount val="1128"/>
                 <c:pt idx="0">
+                  <c:v>45971</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>45978</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45985</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>45992</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46006</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46013</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46020</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>46027</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="9">
                   <c:v>46034</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="10">
                   <c:v>46041</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="11">
                   <c:v>46048</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="12">
                   <c:v>46055</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="13">
                   <c:v>46062</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="14">
                   <c:v>46076</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="15">
                   <c:v>46083</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="16">
                   <c:v>46090</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="17">
                   <c:v>46097</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="18">
                   <c:v>46104</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="19">
                   <c:v>46111</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="20">
                   <c:v>46118</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="21">
                   <c:v>46125</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="22">
                   <c:v>46132</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="23">
                   <c:v>46139</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="24">
                   <c:v>46146</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="25">
                   <c:v>46153</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="26">
                   <c:v>46160</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="27">
                   <c:v>46167</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="28">
                   <c:v>46174</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="29">
                   <c:v>46181</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="30">
                   <c:v>46188</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="31">
                   <c:v>46195</c:v>
                 </c:pt>
               </c:numCache>
@@ -14142,83 +14274,98 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Module!$J$3:$J$1123</c:f>
+              <c:f>Module!$J$3:$J$1130</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0.0_);_(* \(#,##0.0\);_(* "-"??_);_(@_)</c:formatCode>
-                <c:ptCount val="1121"/>
-                <c:pt idx="0">
+                <c:ptCount val="1128"/>
+                <c:pt idx="2">
+                  <c:v>380</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>395</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>404</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>410</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>437.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>447.5</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="8">
                   <c:v>460</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="9">
                   <c:v>480</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="10">
                   <c:v>545</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="11">
                   <c:v>715</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="12">
                   <c:v>850</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="13">
                   <c:v>870</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="14">
                   <c:v>885</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="15">
                   <c:v>890</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="16">
                   <c:v>900</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="17">
                   <c:v>910</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="18">
                   <c:v>917.5</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="19">
                   <c:v>925</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="20">
                   <c:v>935</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="21">
                   <c:v>930</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="22">
                   <c:v>975</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="23">
                   <c:v>970</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="24">
                   <c:v>960</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="25">
                   <c:v>960</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="26">
                   <c:v>975</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="27">
                   <c:v>1020</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="28">
                   <c:v>1035</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="29">
                   <c:v>1075</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="30">
                   <c:v>1250</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="31">
                   <c:v>1275</c:v>
                 </c:pt>
               </c:numCache>
@@ -14249,7 +14396,6 @@
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="46387"/>
-          <c:min val="46023"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -14359,7 +14505,7 @@
         <c:axId val="1552697919"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:min val="400"/>
+          <c:min val="300"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="r"/>
@@ -14397,6 +14543,7 @@
         <c:crossAx val="1552709439"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
+        <c:majorUnit val="300"/>
       </c:valAx>
       <c:dateAx>
         <c:axId val="1552709439"/>
@@ -14499,7 +14646,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -14547,80 +14694,104 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>GDDR!$B$4:$B$1123</c:f>
+              <c:f>GDDR!$B$3:$B$1130</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="1120"/>
+                <c:ptCount val="1128"/>
                 <c:pt idx="0">
+                  <c:v>45971</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>45978</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45985</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>45992</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46006</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46013</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46020</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>46027</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="9">
                   <c:v>46034</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="10">
                   <c:v>46041</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="11">
                   <c:v>46048</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="12">
                   <c:v>46055</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="13">
                   <c:v>46062</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="14">
                   <c:v>46076</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="15">
                   <c:v>46083</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="16">
                   <c:v>46090</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="17">
                   <c:v>46097</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="18">
                   <c:v>46104</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="19">
                   <c:v>46111</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="20">
                   <c:v>46118</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="21">
                   <c:v>46125</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="22">
                   <c:v>46132</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="23">
                   <c:v>46139</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="24">
                   <c:v>46146</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="25">
                   <c:v>46153</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="26">
                   <c:v>46160</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="27">
                   <c:v>46167</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="28">
                   <c:v>46174</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="29">
                   <c:v>46181</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="30">
                   <c:v>46188</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="31">
                   <c:v>46195</c:v>
                 </c:pt>
               </c:numCache>
@@ -14628,83 +14799,104 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>GDDR!$G$3:$G$1123</c:f>
+              <c:f>GDDR!$G$3:$G$1130</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
-                <c:ptCount val="1121"/>
+                <c:ptCount val="1128"/>
                 <c:pt idx="0">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.2270000000000003</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.3179999999999996</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.4550000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.7</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.9269999999999996</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.1550000000000002</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>5.4359999999999999</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="8">
                   <c:v>5.5449999999999999</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="9">
                   <c:v>6</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="10">
                   <c:v>7.0910000000000002</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="11">
                   <c:v>7.8819999999999997</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="12">
                   <c:v>8.6820000000000004</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="13">
                   <c:v>9.4090000000000007</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="14">
                   <c:v>9.6359999999999992</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="15">
                   <c:v>10</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="16">
                   <c:v>10.455</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="17">
                   <c:v>11.182</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="18">
                   <c:v>11.682</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="19">
                   <c:v>12.727</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="20">
                   <c:v>12.526999999999999</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="21">
                   <c:v>12.318</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="22">
                   <c:v>12.227</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="23">
                   <c:v>11.864000000000001</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="24">
                   <c:v>11.773</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="25">
                   <c:v>11.635999999999999</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="26">
                   <c:v>11.635999999999999</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="27">
                   <c:v>11.635999999999999</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="28">
                   <c:v>11.635999999999999</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="29">
                   <c:v>11.545</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="30">
                   <c:v>11.545</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="31">
                   <c:v>11.545</c:v>
                 </c:pt>
               </c:numCache>
@@ -14748,80 +14940,104 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>GDDR!$B$4:$B$1123</c:f>
+              <c:f>GDDR!$B$3:$B$1130</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="1120"/>
+                <c:ptCount val="1128"/>
                 <c:pt idx="0">
+                  <c:v>45971</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>45978</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45985</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>45992</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46006</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46013</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46020</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>46027</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="9">
                   <c:v>46034</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="10">
                   <c:v>46041</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="11">
                   <c:v>46048</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="12">
                   <c:v>46055</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="13">
                   <c:v>46062</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="14">
                   <c:v>46076</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="15">
                   <c:v>46083</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="16">
                   <c:v>46090</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="17">
                   <c:v>46097</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="18">
                   <c:v>46104</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="19">
                   <c:v>46111</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="20">
                   <c:v>46118</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="21">
                   <c:v>46125</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="22">
                   <c:v>46132</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="23">
                   <c:v>46139</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="24">
                   <c:v>46146</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="25">
                   <c:v>46153</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="26">
                   <c:v>46160</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="27">
                   <c:v>46167</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="28">
                   <c:v>46174</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="29">
                   <c:v>46181</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="30">
                   <c:v>46188</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="31">
                   <c:v>46195</c:v>
                 </c:pt>
               </c:numCache>
@@ -14829,83 +15045,104 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>GDDR!$J$3:$J$1123</c:f>
+              <c:f>GDDR!$J$3:$J$1130</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
-                <c:ptCount val="1121"/>
+                <c:ptCount val="1128"/>
                 <c:pt idx="0">
+                  <c:v>3.3290000000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.5979999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.7080000000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.94</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.2309999999999999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.45</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.8369999999999997</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>5.2210000000000001</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="8">
                   <c:v>5.45</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="9">
                   <c:v>5.9690000000000003</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="10">
                   <c:v>7.1539999999999999</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="11">
                   <c:v>8.0380000000000003</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="12">
                   <c:v>8.8650000000000002</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="13">
                   <c:v>9.6539999999999999</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="14">
                   <c:v>9.8650000000000002</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="15">
                   <c:v>10.221</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="16">
                   <c:v>10.721</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="17">
                   <c:v>11.462</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="18">
                   <c:v>11.962</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="19">
                   <c:v>12.865</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="20">
                   <c:v>12.71</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="21">
                   <c:v>12.412000000000001</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="22">
                   <c:v>12.335000000000001</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="23">
                   <c:v>11.962</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="24">
                   <c:v>11.829000000000001</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="25">
                   <c:v>11.702</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="26">
                   <c:v>11.632999999999999</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="27">
                   <c:v>11.632999999999999</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="28">
                   <c:v>11.651999999999999</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="29">
                   <c:v>11.537000000000001</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="30">
                   <c:v>11.522</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="31">
                   <c:v>11.522</c:v>
                 </c:pt>
               </c:numCache>
@@ -14935,7 +15172,6 @@
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="46387"/>
-          <c:min val="46023"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -14988,7 +15224,7 @@
         <c:axId val="1382523328"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:min val="5"/>
+          <c:min val="2"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -17176,14 +17412,14 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:Z300"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="13" width="9" style="11"/>
-    <col min="14" max="14" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.5" style="11" bestFit="1" customWidth="1"/>
     <col min="15" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -40509,6 +40745,69 @@
       </c>
       <c r="D300" s="10" t="s">
         <v>53</v>
+      </c>
+      <c r="E300" s="11">
+        <v>59.5</v>
+      </c>
+      <c r="F300" s="11">
+        <v>31</v>
+      </c>
+      <c r="G300" s="11">
+        <v>46.167000000000002</v>
+      </c>
+      <c r="H300" s="11">
+        <v>25.2</v>
+      </c>
+      <c r="I300" s="11">
+        <v>22.1</v>
+      </c>
+      <c r="J300" s="11">
+        <v>23.5</v>
+      </c>
+      <c r="K300" s="11">
+        <v>83</v>
+      </c>
+      <c r="L300" s="11">
+        <v>38</v>
+      </c>
+      <c r="M300" s="11">
+        <v>69.75</v>
+      </c>
+      <c r="N300" s="11">
+        <v>12.2</v>
+      </c>
+      <c r="O300" s="11">
+        <v>10.3</v>
+      </c>
+      <c r="P300" s="11">
+        <v>11.75</v>
+      </c>
+      <c r="Q300" s="11">
+        <v>55.5</v>
+      </c>
+      <c r="R300" s="11">
+        <v>19</v>
+      </c>
+      <c r="S300" s="11">
+        <v>35.9</v>
+      </c>
+      <c r="T300" s="11">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="U300" s="11">
+        <v>3.8</v>
+      </c>
+      <c r="V300" s="11">
+        <v>4.407</v>
+      </c>
+      <c r="W300" s="11">
+        <v>16.5</v>
+      </c>
+      <c r="X300" s="11">
+        <v>6.6</v>
+      </c>
+      <c r="Y300" s="11">
+        <v>11.151999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -40528,21 +40827,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:AK8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.1640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5" style="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.44140625" style="11" customWidth="1"/>
-    <col min="9" max="9" width="9.77734375" style="11" customWidth="1"/>
+    <col min="7" max="7" width="9.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.5" style="11" customWidth="1"/>
+    <col min="9" max="9" width="9.83203125" style="11" customWidth="1"/>
     <col min="10" max="10" width="10.33203125" style="11" customWidth="1"/>
-    <col min="11" max="11" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.5" style="11" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" style="11"/>
-    <col min="13" max="13" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.5" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -41173,18 +41472,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:Y27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:Y34"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.21875" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="15"/>
-    <col min="7" max="7" width="9.44140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.44140625" style="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5" style="17" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5" style="15" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="15"/>
-    <col min="10" max="10" width="11.77734375" style="17" customWidth="1"/>
+    <col min="10" max="10" width="11.83203125" style="17" customWidth="1"/>
     <col min="11" max="12" width="9" style="15"/>
     <col min="13" max="13" width="13.33203125" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
@@ -41231,15 +41530,33 @@
       <c r="M1" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="4"/>
-      <c r="R1" s="4"/>
-      <c r="S1" s="4"/>
-      <c r="T1" s="4"/>
-      <c r="U1" s="4"/>
-      <c r="V1" s="4"/>
+      <c r="N1" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="S1" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="U1" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="V1" s="4" t="s">
+        <v>60</v>
+      </c>
       <c r="W1" s="4"/>
       <c r="X1" s="4"/>
       <c r="Y1" s="4"/>
@@ -41276,25 +41593,43 @@
       <c r="M2" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="6"/>
-      <c r="T2" s="6"/>
-      <c r="U2" s="6"/>
-      <c r="V2" s="6"/>
+      <c r="N2" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="O2" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q2" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="R2" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="S2" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="T2" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="U2" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="V2" s="6" t="s">
+        <v>56</v>
+      </c>
       <c r="W2" s="6"/>
       <c r="X2" s="6"/>
       <c r="Y2" s="6"/>
     </row>
     <row r="3" spans="1:25">
       <c r="A3" s="8">
-        <v>46013</v>
+        <v>45964</v>
       </c>
       <c r="B3" s="8">
-        <v>46020</v>
+        <v>45971</v>
       </c>
       <c r="C3" s="9">
         <v>0.61111111111111105</v>
@@ -41302,52 +41637,52 @@
       <c r="D3" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="E3" s="14">
-        <v>175</v>
-      </c>
-      <c r="F3" s="14">
-        <v>120</v>
-      </c>
-      <c r="G3" s="16">
-        <v>142.5</v>
-      </c>
-      <c r="H3" s="14">
-        <v>475</v>
-      </c>
-      <c r="I3" s="14">
-        <v>420</v>
-      </c>
-      <c r="J3" s="16">
-        <v>447.5</v>
-      </c>
-      <c r="K3" s="14">
-        <v>98</v>
-      </c>
-      <c r="L3" s="14">
-        <v>65</v>
-      </c>
-      <c r="M3" s="6">
-        <v>79.599999999999994</v>
-      </c>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6">
+        <v>36</v>
+      </c>
+      <c r="O3" s="6">
+        <v>12.5</v>
+      </c>
+      <c r="P3" s="6">
+        <v>20.940999999999999</v>
+      </c>
+      <c r="Q3" s="6">
+        <v>35</v>
+      </c>
+      <c r="R3" s="6">
+        <v>12.5</v>
+      </c>
+      <c r="S3" s="6">
+        <v>20.545000000000002</v>
+      </c>
+      <c r="T3" s="6">
+        <v>195</v>
+      </c>
+      <c r="U3" s="6">
+        <v>170</v>
+      </c>
+      <c r="V3" s="6">
+        <v>180</v>
+      </c>
       <c r="W3" s="6"/>
       <c r="X3" s="6"/>
       <c r="Y3" s="6"/>
     </row>
     <row r="4" spans="1:25">
       <c r="A4" s="8">
-        <v>46020</v>
+        <v>45971</v>
       </c>
       <c r="B4" s="8">
-        <v>46027</v>
+        <v>45978</v>
       </c>
       <c r="C4" s="9">
         <v>0.61111111111111105</v>
@@ -41355,52 +41690,52 @@
       <c r="D4" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="E4" s="14">
-        <v>195</v>
-      </c>
-      <c r="F4" s="14">
-        <v>135</v>
-      </c>
-      <c r="G4" s="16">
-        <v>150</v>
-      </c>
-      <c r="H4" s="14">
-        <v>500</v>
-      </c>
-      <c r="I4" s="14">
-        <v>430</v>
-      </c>
-      <c r="J4" s="16">
-        <v>460</v>
-      </c>
-      <c r="K4" s="14">
-        <v>98</v>
-      </c>
-      <c r="L4" s="14">
-        <v>70</v>
-      </c>
-      <c r="M4" s="6">
-        <v>84.667000000000002</v>
-      </c>
-      <c r="N4" s="6"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
-      <c r="S4" s="6"/>
-      <c r="T4" s="6"/>
-      <c r="U4" s="6"/>
-      <c r="V4" s="6"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6">
+        <v>42</v>
+      </c>
+      <c r="O4" s="6">
+        <v>13</v>
+      </c>
+      <c r="P4" s="6">
+        <v>23.206</v>
+      </c>
+      <c r="Q4" s="6">
+        <v>37</v>
+      </c>
+      <c r="R4" s="6">
+        <v>13</v>
+      </c>
+      <c r="S4" s="6">
+        <v>22.727</v>
+      </c>
+      <c r="T4" s="6">
+        <v>210</v>
+      </c>
+      <c r="U4" s="6">
+        <v>180</v>
+      </c>
+      <c r="V4" s="6">
+        <v>192.5</v>
+      </c>
       <c r="W4" s="6"/>
       <c r="X4" s="6"/>
       <c r="Y4" s="6"/>
     </row>
     <row r="5" spans="1:25">
       <c r="A5" s="8">
-        <v>46027</v>
+        <v>45978</v>
       </c>
       <c r="B5" s="8">
-        <v>46034</v>
+        <v>45985</v>
       </c>
       <c r="C5" s="9">
         <v>0.61111111111111105</v>
@@ -41409,31 +41744,31 @@
         <v>57</v>
       </c>
       <c r="E5" s="14">
-        <v>210</v>
+        <v>145</v>
       </c>
       <c r="F5" s="14">
-        <v>140</v>
+        <v>90</v>
       </c>
       <c r="G5" s="16">
-        <v>157.5</v>
+        <v>100.5</v>
       </c>
       <c r="H5" s="14">
-        <v>575</v>
+        <v>430</v>
       </c>
       <c r="I5" s="14">
-        <v>450</v>
+        <v>350</v>
       </c>
       <c r="J5" s="16">
-        <v>480</v>
+        <v>380</v>
       </c>
       <c r="K5" s="14">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="L5" s="14">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="M5" s="6">
-        <v>89.332999999999998</v>
+        <v>50.232999999999997</v>
       </c>
       <c r="N5" s="6"/>
       <c r="O5" s="6"/>
@@ -41450,96 +41785,96 @@
     </row>
     <row r="6" spans="1:25">
       <c r="A6" s="8">
-        <v>46034</v>
+        <v>45985</v>
       </c>
       <c r="B6" s="8">
-        <v>46041</v>
+        <v>45992</v>
       </c>
       <c r="C6" s="9">
         <v>0.61111111111111105</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E6" s="14">
-        <v>230</v>
+        <v>145</v>
       </c>
       <c r="F6" s="14">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="G6" s="16">
-        <v>177.5</v>
+        <v>115</v>
       </c>
       <c r="H6" s="14">
-        <v>630</v>
+        <v>430</v>
       </c>
       <c r="I6" s="14">
-        <v>490</v>
+        <v>360</v>
       </c>
       <c r="J6" s="16">
-        <v>545</v>
+        <v>395</v>
       </c>
       <c r="K6" s="14">
-        <v>130</v>
+        <v>97</v>
       </c>
       <c r="L6" s="14">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="M6" s="6">
-        <v>94</v>
-      </c>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="7"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="7"/>
-      <c r="T6" s="7"/>
-      <c r="U6" s="7"/>
-      <c r="V6" s="7"/>
+        <v>54.884</v>
+      </c>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="6"/>
+      <c r="R6" s="6"/>
+      <c r="S6" s="6"/>
+      <c r="T6" s="6"/>
+      <c r="U6" s="6"/>
+      <c r="V6" s="6"/>
       <c r="W6" s="6"/>
       <c r="X6" s="6"/>
       <c r="Y6" s="6"/>
     </row>
     <row r="7" spans="1:25">
       <c r="A7" s="8">
-        <v>46041</v>
+        <v>45992</v>
       </c>
       <c r="B7" s="8">
-        <v>46048</v>
+        <v>45999</v>
       </c>
       <c r="C7" s="9">
         <v>0.61111111111111105</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E7" s="14">
-        <v>270</v>
+        <v>145</v>
       </c>
       <c r="F7" s="14">
-        <v>180</v>
+        <v>105</v>
       </c>
       <c r="G7" s="16">
-        <v>215</v>
+        <v>117.5</v>
       </c>
       <c r="H7" s="14">
-        <v>830</v>
+        <v>435</v>
       </c>
       <c r="I7" s="14">
-        <v>620</v>
+        <v>370</v>
       </c>
       <c r="J7" s="16">
-        <v>715</v>
+        <v>404</v>
       </c>
       <c r="K7" s="14">
-        <v>140</v>
+        <v>97</v>
       </c>
       <c r="L7" s="14">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="M7" s="6">
-        <v>99.667000000000002</v>
+        <v>60.93</v>
       </c>
       <c r="N7" s="6"/>
       <c r="O7" s="6"/>
@@ -41556,43 +41891,43 @@
     </row>
     <row r="8" spans="1:25">
       <c r="A8" s="8">
-        <v>46048</v>
+        <v>45999</v>
       </c>
       <c r="B8" s="8">
-        <v>46055</v>
+        <v>46006</v>
       </c>
       <c r="C8" s="9">
         <v>0.61111111111111105</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E8" s="14">
-        <v>280</v>
+        <v>140</v>
       </c>
       <c r="F8" s="14">
-        <v>230</v>
+        <v>105</v>
       </c>
       <c r="G8" s="16">
-        <v>250</v>
+        <v>120</v>
       </c>
       <c r="H8" s="14">
-        <v>1000</v>
+        <v>435</v>
       </c>
       <c r="I8" s="14">
-        <v>700</v>
+        <v>390</v>
       </c>
       <c r="J8" s="16">
-        <v>850</v>
+        <v>410</v>
       </c>
       <c r="K8" s="14">
-        <v>145</v>
+        <v>95</v>
       </c>
       <c r="L8" s="14">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="M8" s="6">
-        <v>110</v>
+        <v>65.465000000000003</v>
       </c>
       <c r="N8" s="6"/>
       <c r="O8" s="6"/>
@@ -41609,51 +41944,63 @@
     </row>
     <row r="9" spans="1:25">
       <c r="A9" s="8">
-        <v>46055</v>
+        <v>46006</v>
       </c>
       <c r="B9" s="8">
-        <v>46062</v>
+        <v>46013</v>
       </c>
       <c r="C9" s="9">
         <v>0.61111111111111105</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="E9" s="15">
-        <v>280</v>
-      </c>
-      <c r="F9" s="15">
-        <v>235</v>
-      </c>
-      <c r="G9" s="17">
-        <v>250</v>
-      </c>
-      <c r="H9" s="15">
-        <v>1000</v>
-      </c>
-      <c r="I9" s="15">
-        <v>750</v>
-      </c>
-      <c r="J9" s="17">
-        <v>870</v>
-      </c>
-      <c r="K9" s="15">
-        <v>145</v>
-      </c>
-      <c r="L9" s="15">
-        <v>100</v>
-      </c>
-      <c r="M9" s="11">
-        <v>118.333</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="E9" s="14">
+        <v>160</v>
+      </c>
+      <c r="F9" s="14">
+        <v>110</v>
+      </c>
+      <c r="G9" s="16">
+        <v>127.5</v>
+      </c>
+      <c r="H9" s="14">
+        <v>465</v>
+      </c>
+      <c r="I9" s="14">
+        <v>400</v>
+      </c>
+      <c r="J9" s="16">
+        <v>437.5</v>
+      </c>
+      <c r="K9" s="14">
+        <v>95</v>
+      </c>
+      <c r="L9" s="14">
+        <v>60</v>
+      </c>
+      <c r="M9" s="6">
+        <v>73.14</v>
+      </c>
+      <c r="N9" s="6"/>
+      <c r="O9" s="6"/>
+      <c r="P9" s="6"/>
+      <c r="Q9" s="6"/>
+      <c r="R9" s="6"/>
+      <c r="S9" s="6"/>
+      <c r="T9" s="6"/>
+      <c r="U9" s="6"/>
+      <c r="V9" s="6"/>
+      <c r="W9" s="6"/>
+      <c r="X9" s="6"/>
+      <c r="Y9" s="6"/>
     </row>
     <row r="10" spans="1:25">
       <c r="A10" s="8">
-        <v>46062</v>
+        <v>46013</v>
       </c>
       <c r="B10" s="8">
-        <v>46076</v>
+        <v>46020</v>
       </c>
       <c r="C10" s="9">
         <v>0.61111111111111105</v>
@@ -41661,40 +42008,52 @@
       <c r="D10" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="E10" s="15">
-        <v>259</v>
-      </c>
-      <c r="F10" s="15">
-        <v>230</v>
-      </c>
-      <c r="G10" s="17">
-        <v>245</v>
-      </c>
-      <c r="H10" s="15">
-        <v>970</v>
-      </c>
-      <c r="I10" s="15">
-        <v>800</v>
-      </c>
-      <c r="J10" s="17">
-        <v>885</v>
-      </c>
-      <c r="K10" s="15">
-        <v>148</v>
-      </c>
-      <c r="L10" s="15">
-        <v>105</v>
-      </c>
-      <c r="M10" s="11">
-        <v>121</v>
-      </c>
+      <c r="E10" s="14">
+        <v>175</v>
+      </c>
+      <c r="F10" s="14">
+        <v>120</v>
+      </c>
+      <c r="G10" s="16">
+        <v>142.5</v>
+      </c>
+      <c r="H10" s="14">
+        <v>475</v>
+      </c>
+      <c r="I10" s="14">
+        <v>420</v>
+      </c>
+      <c r="J10" s="16">
+        <v>447.5</v>
+      </c>
+      <c r="K10" s="14">
+        <v>98</v>
+      </c>
+      <c r="L10" s="14">
+        <v>65</v>
+      </c>
+      <c r="M10" s="6">
+        <v>79.599999999999994</v>
+      </c>
+      <c r="N10" s="6"/>
+      <c r="O10" s="6"/>
+      <c r="P10" s="6"/>
+      <c r="Q10" s="6"/>
+      <c r="R10" s="6"/>
+      <c r="S10" s="6"/>
+      <c r="T10" s="6"/>
+      <c r="U10" s="6"/>
+      <c r="V10" s="6"/>
+      <c r="W10" s="6"/>
+      <c r="X10" s="6"/>
+      <c r="Y10" s="6"/>
     </row>
     <row r="11" spans="1:25">
       <c r="A11" s="8">
-        <v>46076</v>
+        <v>46020</v>
       </c>
       <c r="B11" s="8">
-        <v>46083</v>
+        <v>46027</v>
       </c>
       <c r="C11" s="9">
         <v>0.61111111111111105</v>
@@ -41702,40 +42061,52 @@
       <c r="D11" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="E11" s="15">
-        <v>259</v>
-      </c>
-      <c r="F11" s="15">
-        <v>230</v>
-      </c>
-      <c r="G11" s="17">
-        <v>245</v>
-      </c>
-      <c r="H11" s="15">
-        <v>970</v>
-      </c>
-      <c r="I11" s="15">
-        <v>800</v>
-      </c>
-      <c r="J11" s="17">
-        <v>890</v>
-      </c>
-      <c r="K11" s="15">
-        <v>148</v>
-      </c>
-      <c r="L11" s="15">
-        <v>105</v>
-      </c>
-      <c r="M11" s="11">
-        <v>122.667</v>
-      </c>
+      <c r="E11" s="14">
+        <v>195</v>
+      </c>
+      <c r="F11" s="14">
+        <v>135</v>
+      </c>
+      <c r="G11" s="16">
+        <v>150</v>
+      </c>
+      <c r="H11" s="14">
+        <v>500</v>
+      </c>
+      <c r="I11" s="14">
+        <v>430</v>
+      </c>
+      <c r="J11" s="16">
+        <v>460</v>
+      </c>
+      <c r="K11" s="14">
+        <v>98</v>
+      </c>
+      <c r="L11" s="14">
+        <v>70</v>
+      </c>
+      <c r="M11" s="6">
+        <v>84.667000000000002</v>
+      </c>
+      <c r="N11" s="6"/>
+      <c r="O11" s="6"/>
+      <c r="P11" s="6"/>
+      <c r="Q11" s="6"/>
+      <c r="R11" s="6"/>
+      <c r="S11" s="6"/>
+      <c r="T11" s="6"/>
+      <c r="U11" s="6"/>
+      <c r="V11" s="6"/>
+      <c r="W11" s="6"/>
+      <c r="X11" s="6"/>
+      <c r="Y11" s="6"/>
     </row>
     <row r="12" spans="1:25">
       <c r="A12" s="8">
-        <v>46083</v>
+        <v>46027</v>
       </c>
       <c r="B12" s="8">
-        <v>46090</v>
+        <v>46034</v>
       </c>
       <c r="C12" s="9">
         <v>0.61111111111111105</v>
@@ -41743,204 +42114,252 @@
       <c r="D12" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="E12" s="15">
-        <v>250</v>
-      </c>
-      <c r="F12" s="15">
-        <v>200</v>
-      </c>
-      <c r="G12" s="17">
-        <v>240</v>
-      </c>
-      <c r="H12" s="15">
-        <v>980</v>
-      </c>
-      <c r="I12" s="15">
-        <v>830</v>
-      </c>
-      <c r="J12" s="17">
-        <v>900</v>
-      </c>
-      <c r="K12" s="15">
-        <v>145</v>
-      </c>
-      <c r="L12" s="15">
-        <v>107</v>
-      </c>
-      <c r="M12" s="11">
-        <v>123.333</v>
-      </c>
+      <c r="E12" s="14">
+        <v>210</v>
+      </c>
+      <c r="F12" s="14">
+        <v>140</v>
+      </c>
+      <c r="G12" s="16">
+        <v>157.5</v>
+      </c>
+      <c r="H12" s="14">
+        <v>575</v>
+      </c>
+      <c r="I12" s="14">
+        <v>450</v>
+      </c>
+      <c r="J12" s="16">
+        <v>480</v>
+      </c>
+      <c r="K12" s="14">
+        <v>115</v>
+      </c>
+      <c r="L12" s="14">
+        <v>80</v>
+      </c>
+      <c r="M12" s="6">
+        <v>89.332999999999998</v>
+      </c>
+      <c r="N12" s="6"/>
+      <c r="O12" s="6"/>
+      <c r="P12" s="6"/>
+      <c r="Q12" s="6"/>
+      <c r="R12" s="6"/>
+      <c r="S12" s="6"/>
+      <c r="T12" s="6"/>
+      <c r="U12" s="6"/>
+      <c r="V12" s="6"/>
+      <c r="W12" s="6"/>
+      <c r="X12" s="6"/>
+      <c r="Y12" s="6"/>
     </row>
     <row r="13" spans="1:25">
       <c r="A13" s="8">
-        <v>46090</v>
+        <v>46034</v>
       </c>
       <c r="B13" s="8">
-        <v>46097</v>
+        <v>46041</v>
       </c>
       <c r="C13" s="9">
         <v>0.61111111111111105</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="E13" s="15">
-        <v>240</v>
-      </c>
-      <c r="F13" s="15">
-        <v>200</v>
-      </c>
-      <c r="G13" s="17">
+        <v>53</v>
+      </c>
+      <c r="E13" s="14">
         <v>230</v>
       </c>
-      <c r="H13" s="15">
-        <v>990</v>
-      </c>
-      <c r="I13" s="15">
-        <v>850</v>
-      </c>
-      <c r="J13" s="17">
-        <v>910</v>
-      </c>
-      <c r="K13" s="15">
+      <c r="F13" s="14">
         <v>160</v>
       </c>
-      <c r="L13" s="15">
-        <v>115</v>
-      </c>
-      <c r="M13" s="11">
-        <v>126.667</v>
-      </c>
+      <c r="G13" s="16">
+        <v>177.5</v>
+      </c>
+      <c r="H13" s="14">
+        <v>630</v>
+      </c>
+      <c r="I13" s="14">
+        <v>490</v>
+      </c>
+      <c r="J13" s="16">
+        <v>545</v>
+      </c>
+      <c r="K13" s="14">
+        <v>130</v>
+      </c>
+      <c r="L13" s="14">
+        <v>85</v>
+      </c>
+      <c r="M13" s="6">
+        <v>94</v>
+      </c>
+      <c r="N13" s="7"/>
+      <c r="O13" s="7"/>
+      <c r="P13" s="7"/>
+      <c r="Q13" s="7"/>
+      <c r="R13" s="7"/>
+      <c r="S13" s="7"/>
+      <c r="T13" s="7"/>
+      <c r="U13" s="7"/>
+      <c r="V13" s="7"/>
+      <c r="W13" s="6"/>
+      <c r="X13" s="6"/>
+      <c r="Y13" s="6"/>
     </row>
     <row r="14" spans="1:25">
       <c r="A14" s="8">
-        <v>46097</v>
+        <v>46041</v>
       </c>
       <c r="B14" s="8">
-        <v>46104</v>
+        <v>46048</v>
       </c>
       <c r="C14" s="9">
         <v>0.61111111111111105</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="E14" s="15">
-        <v>245</v>
-      </c>
-      <c r="F14" s="15">
-        <v>205</v>
-      </c>
-      <c r="G14" s="17">
-        <v>232.5</v>
-      </c>
-      <c r="H14" s="15">
-        <v>1050</v>
-      </c>
-      <c r="I14" s="15">
-        <v>860</v>
-      </c>
-      <c r="J14" s="17">
-        <v>917.5</v>
-      </c>
-      <c r="K14" s="15">
-        <v>162</v>
-      </c>
-      <c r="L14" s="15">
-        <v>120</v>
-      </c>
-      <c r="M14" s="11">
-        <v>132.333</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="E14" s="14">
+        <v>270</v>
+      </c>
+      <c r="F14" s="14">
+        <v>180</v>
+      </c>
+      <c r="G14" s="16">
+        <v>215</v>
+      </c>
+      <c r="H14" s="14">
+        <v>830</v>
+      </c>
+      <c r="I14" s="14">
+        <v>620</v>
+      </c>
+      <c r="J14" s="16">
+        <v>715</v>
+      </c>
+      <c r="K14" s="14">
+        <v>140</v>
+      </c>
+      <c r="L14" s="14">
+        <v>88</v>
+      </c>
+      <c r="M14" s="6">
+        <v>99.667000000000002</v>
+      </c>
+      <c r="N14" s="6"/>
+      <c r="O14" s="6"/>
+      <c r="P14" s="6"/>
+      <c r="Q14" s="6"/>
+      <c r="R14" s="6"/>
+      <c r="S14" s="6"/>
+      <c r="T14" s="6"/>
+      <c r="U14" s="6"/>
+      <c r="V14" s="6"/>
+      <c r="W14" s="6"/>
+      <c r="X14" s="6"/>
+      <c r="Y14" s="6"/>
     </row>
     <row r="15" spans="1:25">
       <c r="A15" s="8">
-        <v>46104</v>
+        <v>46048</v>
       </c>
       <c r="B15" s="8">
-        <v>46111</v>
+        <v>46055</v>
       </c>
       <c r="C15" s="9">
         <v>0.61111111111111105</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="E15" s="15">
+        <v>53</v>
+      </c>
+      <c r="E15" s="14">
+        <v>280</v>
+      </c>
+      <c r="F15" s="14">
+        <v>230</v>
+      </c>
+      <c r="G15" s="16">
         <v>250</v>
       </c>
-      <c r="F15" s="15">
-        <v>200</v>
-      </c>
-      <c r="G15" s="17">
-        <v>232.5</v>
-      </c>
-      <c r="H15" s="15">
-        <v>1060</v>
-      </c>
-      <c r="I15" s="15">
-        <v>870</v>
-      </c>
-      <c r="J15" s="17">
-        <v>925</v>
-      </c>
-      <c r="K15" s="15">
-        <v>171</v>
-      </c>
-      <c r="L15" s="15">
-        <v>130</v>
-      </c>
-      <c r="M15" s="11">
-        <v>143.333</v>
-      </c>
+      <c r="H15" s="14">
+        <v>1000</v>
+      </c>
+      <c r="I15" s="14">
+        <v>700</v>
+      </c>
+      <c r="J15" s="16">
+        <v>850</v>
+      </c>
+      <c r="K15" s="14">
+        <v>145</v>
+      </c>
+      <c r="L15" s="14">
+        <v>95</v>
+      </c>
+      <c r="M15" s="6">
+        <v>110</v>
+      </c>
+      <c r="N15" s="6"/>
+      <c r="O15" s="6"/>
+      <c r="P15" s="6"/>
+      <c r="Q15" s="6"/>
+      <c r="R15" s="6"/>
+      <c r="S15" s="6"/>
+      <c r="T15" s="6"/>
+      <c r="U15" s="6"/>
+      <c r="V15" s="6"/>
+      <c r="W15" s="6"/>
+      <c r="X15" s="6"/>
+      <c r="Y15" s="6"/>
     </row>
     <row r="16" spans="1:25">
       <c r="A16" s="8">
-        <v>46111</v>
+        <v>46055</v>
       </c>
       <c r="B16" s="8">
-        <v>46118</v>
+        <v>46062</v>
       </c>
       <c r="C16" s="9">
         <v>0.61111111111111105</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E16" s="15">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="F16" s="15">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="G16" s="17">
-        <v>242.5</v>
+        <v>250</v>
       </c>
       <c r="H16" s="15">
-        <v>1150</v>
+        <v>1000</v>
       </c>
       <c r="I16" s="15">
-        <v>880</v>
+        <v>750</v>
       </c>
       <c r="J16" s="17">
-        <v>935</v>
+        <v>870</v>
       </c>
       <c r="K16" s="15">
-        <v>171</v>
+        <v>145</v>
       </c>
       <c r="L16" s="15">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="M16" s="11">
-        <v>150</v>
+        <v>118.333</v>
       </c>
     </row>
     <row r="17" spans="1:13">
       <c r="A17" s="8">
-        <v>46118</v>
+        <v>46062</v>
       </c>
       <c r="B17" s="8">
-        <v>46125</v>
+        <v>46076</v>
       </c>
       <c r="C17" s="9">
         <v>0.61111111111111105</v>
@@ -41949,39 +42368,39 @@
         <v>57</v>
       </c>
       <c r="E17" s="15">
-        <v>240</v>
+        <v>259</v>
       </c>
       <c r="F17" s="15">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="G17" s="17">
-        <v>222.5</v>
+        <v>245</v>
       </c>
       <c r="H17" s="15">
-        <v>1150</v>
+        <v>970</v>
       </c>
       <c r="I17" s="15">
-        <v>880</v>
+        <v>800</v>
       </c>
       <c r="J17" s="17">
-        <v>930</v>
+        <v>885</v>
       </c>
       <c r="K17" s="15">
-        <v>171</v>
+        <v>148</v>
       </c>
       <c r="L17" s="15">
-        <v>134</v>
+        <v>105</v>
       </c>
       <c r="M17" s="11">
-        <v>149.333</v>
+        <v>121</v>
       </c>
     </row>
     <row r="18" spans="1:13">
       <c r="A18" s="8">
-        <v>46125</v>
+        <v>46076</v>
       </c>
       <c r="B18" s="8">
-        <v>46132</v>
+        <v>46083</v>
       </c>
       <c r="C18" s="9">
         <v>0.61111111111111105</v>
@@ -41990,39 +42409,39 @@
         <v>57</v>
       </c>
       <c r="E18" s="15">
+        <v>259</v>
+      </c>
+      <c r="F18" s="15">
         <v>230</v>
       </c>
-      <c r="F18" s="15">
-        <v>200</v>
-      </c>
       <c r="G18" s="17">
-        <v>219</v>
+        <v>245</v>
       </c>
       <c r="H18" s="15">
-        <v>1150</v>
+        <v>970</v>
       </c>
       <c r="I18" s="15">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="J18" s="17">
-        <v>975</v>
+        <v>890</v>
       </c>
       <c r="K18" s="15">
-        <v>172</v>
+        <v>148</v>
       </c>
       <c r="L18" s="15">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="M18" s="11">
-        <v>149.209</v>
+        <v>122.667</v>
       </c>
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="8">
-        <v>46132</v>
+        <v>46083</v>
       </c>
       <c r="B19" s="8">
-        <v>46139</v>
+        <v>46090</v>
       </c>
       <c r="C19" s="9">
         <v>0.61111111111111105</v>
@@ -42031,39 +42450,39 @@
         <v>57</v>
       </c>
       <c r="E19" s="15">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="F19" s="15">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="G19" s="17">
-        <v>218.5</v>
+        <v>240</v>
       </c>
       <c r="H19" s="15">
-        <v>1185</v>
+        <v>980</v>
       </c>
       <c r="I19" s="15">
-        <v>880</v>
+        <v>830</v>
       </c>
       <c r="J19" s="17">
-        <v>970</v>
+        <v>900</v>
       </c>
       <c r="K19" s="15">
-        <v>171</v>
+        <v>145</v>
       </c>
       <c r="L19" s="15">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="M19" s="11">
-        <v>148.86799999999999</v>
+        <v>123.333</v>
       </c>
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="8">
-        <v>46139</v>
+        <v>46090</v>
       </c>
       <c r="B20" s="8">
-        <v>46146</v>
+        <v>46097</v>
       </c>
       <c r="C20" s="9">
         <v>0.61111111111111105</v>
@@ -42072,39 +42491,39 @@
         <v>57</v>
       </c>
       <c r="E20" s="15">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="F20" s="15">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="G20" s="17">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="H20" s="15">
-        <v>1170</v>
+        <v>990</v>
       </c>
       <c r="I20" s="15">
         <v>850</v>
       </c>
       <c r="J20" s="17">
-        <v>960</v>
+        <v>910</v>
       </c>
       <c r="K20" s="15">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="L20" s="15">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="M20" s="11">
-        <v>148.83000000000001</v>
+        <v>126.667</v>
       </c>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="8">
-        <v>46146</v>
+        <v>46097</v>
       </c>
       <c r="B21" s="8">
-        <v>46153</v>
+        <v>46104</v>
       </c>
       <c r="C21" s="9">
         <v>0.61111111111111105</v>
@@ -42113,39 +42532,39 @@
         <v>57</v>
       </c>
       <c r="E21" s="15">
-        <v>218</v>
+        <v>245</v>
       </c>
       <c r="F21" s="15">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="G21" s="17">
-        <v>215.5</v>
+        <v>232.5</v>
       </c>
       <c r="H21" s="15">
-        <v>1180</v>
+        <v>1050</v>
       </c>
       <c r="I21" s="15">
         <v>860</v>
       </c>
       <c r="J21" s="17">
-        <v>960</v>
+        <v>917.5</v>
       </c>
       <c r="K21" s="15">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="L21" s="15">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="M21" s="11">
-        <v>148.435</v>
+        <v>132.333</v>
       </c>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="8">
-        <v>46153</v>
+        <v>46104</v>
       </c>
       <c r="B22" s="8">
-        <v>46160</v>
+        <v>46111</v>
       </c>
       <c r="C22" s="9">
         <v>0.61111111111111105</v>
@@ -42154,39 +42573,39 @@
         <v>57</v>
       </c>
       <c r="E22" s="15">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="F22" s="15">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="G22" s="17">
-        <v>215</v>
+        <v>232.5</v>
       </c>
       <c r="H22" s="15">
-        <v>1180</v>
+        <v>1060</v>
       </c>
       <c r="I22" s="15">
-        <v>900</v>
+        <v>870</v>
       </c>
       <c r="J22" s="17">
-        <v>975</v>
+        <v>925</v>
       </c>
       <c r="K22" s="15">
         <v>171</v>
       </c>
       <c r="L22" s="15">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="M22" s="11">
-        <v>150.761</v>
+        <v>143.333</v>
       </c>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" s="8">
-        <v>46160</v>
+        <v>46111</v>
       </c>
       <c r="B23" s="8">
-        <v>46167</v>
+        <v>46118</v>
       </c>
       <c r="C23" s="9">
         <v>0.61111111111111105</v>
@@ -42195,39 +42614,39 @@
         <v>57</v>
       </c>
       <c r="E23" s="15">
+        <v>260</v>
+      </c>
+      <c r="F23" s="15">
         <v>220</v>
       </c>
-      <c r="F23" s="15">
-        <v>200</v>
-      </c>
       <c r="G23" s="17">
-        <v>214</v>
+        <v>242.5</v>
       </c>
       <c r="H23" s="15">
-        <v>1200</v>
+        <v>1150</v>
       </c>
       <c r="I23" s="15">
-        <v>920</v>
+        <v>880</v>
       </c>
       <c r="J23" s="17">
-        <v>1020</v>
+        <v>935</v>
       </c>
       <c r="K23" s="15">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L23" s="15">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="M23" s="11">
-        <v>150.435</v>
+        <v>150</v>
       </c>
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="8">
-        <v>46167</v>
+        <v>46118</v>
       </c>
       <c r="B24" s="8">
-        <v>46174</v>
+        <v>46125</v>
       </c>
       <c r="C24" s="9">
         <v>0.61111111111111105</v>
@@ -42236,39 +42655,39 @@
         <v>57</v>
       </c>
       <c r="E24" s="15">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="F24" s="15">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="G24" s="17">
-        <v>212.5</v>
+        <v>222.5</v>
       </c>
       <c r="H24" s="15">
-        <v>1200</v>
+        <v>1150</v>
       </c>
       <c r="I24" s="15">
-        <v>950</v>
+        <v>880</v>
       </c>
       <c r="J24" s="17">
-        <v>1035</v>
+        <v>930</v>
       </c>
       <c r="K24" s="15">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="L24" s="15">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="M24" s="11">
-        <v>150.261</v>
+        <v>149.333</v>
       </c>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="8">
-        <v>46174</v>
+        <v>46125</v>
       </c>
       <c r="B25" s="8">
-        <v>46181</v>
+        <v>46132</v>
       </c>
       <c r="C25" s="9">
         <v>0.61111111111111105</v>
@@ -42277,39 +42696,39 @@
         <v>57</v>
       </c>
       <c r="E25" s="15">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="F25" s="15">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G25" s="17">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="H25" s="15">
-        <v>1350</v>
+        <v>1150</v>
       </c>
       <c r="I25" s="15">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="J25" s="17">
-        <v>1075</v>
+        <v>975</v>
       </c>
       <c r="K25" s="15">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L25" s="15">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M25" s="11">
-        <v>150.08699999999999</v>
+        <v>149.209</v>
       </c>
     </row>
     <row r="26" spans="1:13">
       <c r="A26" s="8">
-        <v>46181</v>
+        <v>46132</v>
       </c>
       <c r="B26" s="8">
-        <v>46188</v>
+        <v>46139</v>
       </c>
       <c r="C26" s="9">
         <v>0.61111111111111105</v>
@@ -42318,39 +42737,39 @@
         <v>57</v>
       </c>
       <c r="E26" s="15">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="F26" s="15">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="G26" s="17">
-        <v>209</v>
+        <v>218.5</v>
       </c>
       <c r="H26" s="15">
-        <v>1550</v>
+        <v>1185</v>
       </c>
       <c r="I26" s="15">
-        <v>1200</v>
+        <v>880</v>
       </c>
       <c r="J26" s="17">
-        <v>1250</v>
+        <v>970</v>
       </c>
       <c r="K26" s="15">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L26" s="15">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="M26" s="11">
-        <v>150.08699999999999</v>
+        <v>148.86799999999999</v>
       </c>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="8">
-        <v>46188</v>
+        <v>46139</v>
       </c>
       <c r="B27" s="8">
-        <v>46195</v>
+        <v>46146</v>
       </c>
       <c r="C27" s="9">
         <v>0.61111111111111105</v>
@@ -42359,30 +42778,317 @@
         <v>57</v>
       </c>
       <c r="E27" s="15">
+        <v>220</v>
+      </c>
+      <c r="F27" s="15">
+        <v>194</v>
+      </c>
+      <c r="G27" s="17">
+        <v>216</v>
+      </c>
+      <c r="H27" s="15">
+        <v>1170</v>
+      </c>
+      <c r="I27" s="15">
+        <v>850</v>
+      </c>
+      <c r="J27" s="17">
+        <v>960</v>
+      </c>
+      <c r="K27" s="15">
+        <v>171</v>
+      </c>
+      <c r="L27" s="15">
+        <v>138</v>
+      </c>
+      <c r="M27" s="11">
+        <v>148.83000000000001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
+      <c r="A28" s="8">
+        <v>46146</v>
+      </c>
+      <c r="B28" s="8">
+        <v>46153</v>
+      </c>
+      <c r="C28" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="E28" s="15">
+        <v>218</v>
+      </c>
+      <c r="F28" s="15">
+        <v>193</v>
+      </c>
+      <c r="G28" s="17">
+        <v>215.5</v>
+      </c>
+      <c r="H28" s="15">
+        <v>1180</v>
+      </c>
+      <c r="I28" s="15">
+        <v>860</v>
+      </c>
+      <c r="J28" s="17">
+        <v>960</v>
+      </c>
+      <c r="K28" s="15">
+        <v>170</v>
+      </c>
+      <c r="L28" s="15">
+        <v>136</v>
+      </c>
+      <c r="M28" s="11">
+        <v>148.435</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
+      <c r="A29" s="8">
+        <v>46153</v>
+      </c>
+      <c r="B29" s="8">
+        <v>46160</v>
+      </c>
+      <c r="C29" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="E29" s="15">
+        <v>220</v>
+      </c>
+      <c r="F29" s="15">
+        <v>195</v>
+      </c>
+      <c r="G29" s="17">
         <v>215</v>
       </c>
-      <c r="F27" s="15">
+      <c r="H29" s="15">
+        <v>1180</v>
+      </c>
+      <c r="I29" s="15">
+        <v>900</v>
+      </c>
+      <c r="J29" s="17">
+        <v>975</v>
+      </c>
+      <c r="K29" s="15">
+        <v>171</v>
+      </c>
+      <c r="L29" s="15">
+        <v>138</v>
+      </c>
+      <c r="M29" s="11">
+        <v>150.761</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
+      <c r="A30" s="8">
+        <v>46160</v>
+      </c>
+      <c r="B30" s="8">
+        <v>46167</v>
+      </c>
+      <c r="C30" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="E30" s="15">
+        <v>220</v>
+      </c>
+      <c r="F30" s="15">
         <v>200</v>
       </c>
-      <c r="G27" s="17">
+      <c r="G30" s="17">
+        <v>214</v>
+      </c>
+      <c r="H30" s="15">
+        <v>1200</v>
+      </c>
+      <c r="I30" s="15">
+        <v>920</v>
+      </c>
+      <c r="J30" s="17">
+        <v>1020</v>
+      </c>
+      <c r="K30" s="15">
+        <v>173</v>
+      </c>
+      <c r="L30" s="15">
+        <v>137</v>
+      </c>
+      <c r="M30" s="11">
+        <v>150.435</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
+      <c r="A31" s="8">
+        <v>46167</v>
+      </c>
+      <c r="B31" s="8">
+        <v>46174</v>
+      </c>
+      <c r="C31" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="E31" s="15">
+        <v>220</v>
+      </c>
+      <c r="F31" s="15">
+        <v>205</v>
+      </c>
+      <c r="G31" s="17">
+        <v>212.5</v>
+      </c>
+      <c r="H31" s="15">
+        <v>1200</v>
+      </c>
+      <c r="I31" s="15">
+        <v>950</v>
+      </c>
+      <c r="J31" s="17">
+        <v>1035</v>
+      </c>
+      <c r="K31" s="15">
+        <v>174</v>
+      </c>
+      <c r="L31" s="15">
+        <v>137</v>
+      </c>
+      <c r="M31" s="11">
+        <v>150.261</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
+      <c r="A32" s="8">
+        <v>46174</v>
+      </c>
+      <c r="B32" s="8">
+        <v>46181</v>
+      </c>
+      <c r="C32" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="E32" s="15">
+        <v>218</v>
+      </c>
+      <c r="F32" s="15">
+        <v>203</v>
+      </c>
+      <c r="G32" s="17">
+        <v>211</v>
+      </c>
+      <c r="H32" s="15">
+        <v>1350</v>
+      </c>
+      <c r="I32" s="15">
+        <v>1000</v>
+      </c>
+      <c r="J32" s="17">
+        <v>1075</v>
+      </c>
+      <c r="K32" s="15">
+        <v>173</v>
+      </c>
+      <c r="L32" s="15">
+        <v>135</v>
+      </c>
+      <c r="M32" s="11">
+        <v>150.08699999999999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
+      <c r="A33" s="8">
+        <v>46181</v>
+      </c>
+      <c r="B33" s="8">
+        <v>46188</v>
+      </c>
+      <c r="C33" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="E33" s="15">
+        <v>217</v>
+      </c>
+      <c r="F33" s="15">
+        <v>200</v>
+      </c>
+      <c r="G33" s="17">
         <v>209</v>
       </c>
-      <c r="H27" s="15">
+      <c r="H33" s="15">
+        <v>1550</v>
+      </c>
+      <c r="I33" s="15">
+        <v>1200</v>
+      </c>
+      <c r="J33" s="17">
+        <v>1250</v>
+      </c>
+      <c r="K33" s="15">
+        <v>170</v>
+      </c>
+      <c r="L33" s="15">
+        <v>136</v>
+      </c>
+      <c r="M33" s="11">
+        <v>150.08699999999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
+      <c r="A34" s="8">
+        <v>46188</v>
+      </c>
+      <c r="B34" s="8">
+        <v>46195</v>
+      </c>
+      <c r="C34" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="E34" s="15">
+        <v>215</v>
+      </c>
+      <c r="F34" s="15">
+        <v>200</v>
+      </c>
+      <c r="G34" s="17">
+        <v>209</v>
+      </c>
+      <c r="H34" s="15">
         <v>1580</v>
       </c>
-      <c r="I27" s="15">
+      <c r="I34" s="15">
         <v>1230</v>
       </c>
-      <c r="J27" s="17">
+      <c r="J34" s="17">
         <v>1275</v>
       </c>
-      <c r="K27" s="15">
+      <c r="K34" s="15">
         <v>170</v>
       </c>
-      <c r="L27" s="15">
+      <c r="L34" s="15">
         <v>135</v>
       </c>
-      <c r="M27" s="11">
+      <c r="M34" s="11">
         <v>149.92400000000001</v>
       </c>
     </row>
@@ -42402,14 +43108,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:Y27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:Y34"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1640625" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.5" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -42502,10 +43208,10 @@
     </row>
     <row r="3" spans="1:25">
       <c r="A3" s="8">
-        <v>46013</v>
+        <v>45964</v>
       </c>
       <c r="B3" s="8">
-        <v>46020</v>
+        <v>45971</v>
       </c>
       <c r="C3" s="9">
         <v>0.61111111111111105</v>
@@ -42514,22 +43220,22 @@
         <v>57</v>
       </c>
       <c r="E3" s="6">
-        <v>10</v>
+        <v>6.5</v>
       </c>
       <c r="F3" s="6">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="G3" s="6">
-        <v>5.4359999999999999</v>
+        <v>4</v>
       </c>
       <c r="H3" s="6">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I3" s="6">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="J3" s="6">
-        <v>5.2210000000000001</v>
+        <v>3.3290000000000002</v>
       </c>
       <c r="K3" s="6"/>
       <c r="L3" s="6"/>
@@ -42549,10 +43255,10 @@
     </row>
     <row r="4" spans="1:25">
       <c r="A4" s="8">
-        <v>46020</v>
+        <v>45971</v>
       </c>
       <c r="B4" s="8">
-        <v>46027</v>
+        <v>45978</v>
       </c>
       <c r="C4" s="9">
         <v>0.61111111111111105</v>
@@ -42561,22 +43267,22 @@
         <v>57</v>
       </c>
       <c r="E4" s="6">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F4" s="6">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="G4" s="6">
-        <v>5.5449999999999999</v>
+        <v>4.2270000000000003</v>
       </c>
       <c r="H4" s="6">
-        <v>11</v>
+        <v>7.5</v>
       </c>
       <c r="I4" s="6">
-        <v>4.3</v>
+        <v>2.5</v>
       </c>
       <c r="J4" s="6">
-        <v>5.45</v>
+        <v>3.5979999999999999</v>
       </c>
       <c r="K4" s="6"/>
       <c r="L4" s="6"/>
@@ -42596,34 +43302,34 @@
     </row>
     <row r="5" spans="1:25">
       <c r="A5" s="8">
-        <v>46027</v>
+        <v>45978</v>
       </c>
       <c r="B5" s="8">
-        <v>46034</v>
+        <v>45985</v>
       </c>
       <c r="C5" s="9">
         <v>0.61111111111111105</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E5" s="6">
-        <v>12</v>
+        <v>7.5</v>
       </c>
       <c r="F5" s="6">
-        <v>5.2</v>
+        <v>3.5</v>
       </c>
       <c r="G5" s="6">
-        <v>6</v>
+        <v>4.3179999999999996</v>
       </c>
       <c r="H5" s="6">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I5" s="6">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="J5" s="6">
-        <v>5.9690000000000003</v>
+        <v>3.7080000000000002</v>
       </c>
       <c r="K5" s="6"/>
       <c r="L5" s="6"/>
@@ -42643,34 +43349,34 @@
     </row>
     <row r="6" spans="1:25">
       <c r="A6" s="8">
-        <v>46034</v>
+        <v>45985</v>
       </c>
       <c r="B6" s="8">
-        <v>46041</v>
+        <v>45992</v>
       </c>
       <c r="C6" s="9">
         <v>0.61111111111111105</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E6" s="6">
-        <v>13.5</v>
+        <v>8</v>
       </c>
       <c r="F6" s="6">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="G6" s="6">
-        <v>7.0910000000000002</v>
+        <v>4.4550000000000001</v>
       </c>
       <c r="H6" s="6">
-        <v>13</v>
+        <v>8.5</v>
       </c>
       <c r="I6" s="6">
-        <v>5.8</v>
+        <v>3</v>
       </c>
       <c r="J6" s="6">
-        <v>7.1539999999999999</v>
+        <v>3.94</v>
       </c>
       <c r="K6" s="6"/>
       <c r="L6" s="6"/>
@@ -42690,34 +43396,34 @@
     </row>
     <row r="7" spans="1:25">
       <c r="A7" s="8">
-        <v>46041</v>
+        <v>45992</v>
       </c>
       <c r="B7" s="8">
-        <v>46048</v>
+        <v>45999</v>
       </c>
       <c r="C7" s="9">
         <v>0.61111111111111105</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E7" s="6">
-        <v>14.5</v>
+        <v>9</v>
       </c>
       <c r="F7" s="6">
-        <v>6.3</v>
+        <v>3.8</v>
       </c>
       <c r="G7" s="6">
-        <v>7.8819999999999997</v>
+        <v>4.7</v>
       </c>
       <c r="H7" s="6">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I7" s="6">
-        <v>6.5</v>
+        <v>3.2</v>
       </c>
       <c r="J7" s="6">
-        <v>8.0380000000000003</v>
+        <v>4.2309999999999999</v>
       </c>
       <c r="K7" s="6"/>
       <c r="L7" s="6"/>
@@ -42737,34 +43443,34 @@
     </row>
     <row r="8" spans="1:25">
       <c r="A8" s="8">
-        <v>46048</v>
+        <v>45999</v>
       </c>
       <c r="B8" s="8">
-        <v>46055</v>
+        <v>46006</v>
       </c>
       <c r="C8" s="9">
         <v>0.61111111111111105</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E8" s="6">
-        <v>15.5</v>
+        <v>9</v>
       </c>
       <c r="F8" s="6">
-        <v>7</v>
+        <v>3.8</v>
       </c>
       <c r="G8" s="6">
-        <v>8.6820000000000004</v>
+        <v>4.9269999999999996</v>
       </c>
       <c r="H8" s="6">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I8" s="6">
-        <v>7.5</v>
+        <v>3.4</v>
       </c>
       <c r="J8" s="6">
-        <v>8.8650000000000002</v>
+        <v>4.45</v>
       </c>
       <c r="K8" s="6"/>
       <c r="L8" s="6"/>
@@ -42784,42 +43490,57 @@
     </row>
     <row r="9" spans="1:25">
       <c r="A9" s="8">
-        <v>46055</v>
+        <v>46006</v>
       </c>
       <c r="B9" s="8">
-        <v>46062</v>
+        <v>46013</v>
       </c>
       <c r="C9" s="9">
         <v>0.61111111111111105</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="E9" s="11">
-        <v>15.5</v>
-      </c>
-      <c r="F9" s="11">
-        <v>7.5</v>
-      </c>
-      <c r="G9" s="11">
-        <v>9.4090000000000007</v>
-      </c>
-      <c r="H9" s="11">
-        <v>16</v>
-      </c>
-      <c r="I9" s="11">
-        <v>8</v>
-      </c>
-      <c r="J9" s="11">
-        <v>9.6539999999999999</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="E9" s="6">
+        <v>9</v>
+      </c>
+      <c r="F9" s="6">
+        <v>4</v>
+      </c>
+      <c r="G9" s="6">
+        <v>5.1550000000000002</v>
+      </c>
+      <c r="H9" s="6">
+        <v>10</v>
+      </c>
+      <c r="I9" s="6">
+        <v>3.4</v>
+      </c>
+      <c r="J9" s="6">
+        <v>4.8369999999999997</v>
+      </c>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="6"/>
+      <c r="P9" s="6"/>
+      <c r="Q9" s="6"/>
+      <c r="R9" s="6"/>
+      <c r="S9" s="6"/>
+      <c r="T9" s="6"/>
+      <c r="U9" s="6"/>
+      <c r="V9" s="6"/>
+      <c r="W9" s="6"/>
+      <c r="X9" s="6"/>
+      <c r="Y9" s="6"/>
     </row>
     <row r="10" spans="1:25">
       <c r="A10" s="8">
-        <v>46062</v>
+        <v>46013</v>
       </c>
       <c r="B10" s="8">
-        <v>46076</v>
+        <v>46020</v>
       </c>
       <c r="C10" s="9">
         <v>0.61111111111111105</v>
@@ -42827,31 +43548,46 @@
       <c r="D10" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="E10" s="11">
-        <v>15.5</v>
-      </c>
-      <c r="F10" s="11">
-        <v>8</v>
-      </c>
-      <c r="G10" s="11">
-        <v>9.6359999999999992</v>
-      </c>
-      <c r="H10" s="11">
-        <v>16</v>
-      </c>
-      <c r="I10" s="11">
-        <v>8.5</v>
-      </c>
-      <c r="J10" s="11">
-        <v>9.8650000000000002</v>
-      </c>
+      <c r="E10" s="6">
+        <v>10</v>
+      </c>
+      <c r="F10" s="6">
+        <v>4.3</v>
+      </c>
+      <c r="G10" s="6">
+        <v>5.4359999999999999</v>
+      </c>
+      <c r="H10" s="6">
+        <v>11</v>
+      </c>
+      <c r="I10" s="6">
+        <v>4</v>
+      </c>
+      <c r="J10" s="6">
+        <v>5.2210000000000001</v>
+      </c>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="6"/>
+      <c r="P10" s="6"/>
+      <c r="Q10" s="6"/>
+      <c r="R10" s="6"/>
+      <c r="S10" s="6"/>
+      <c r="T10" s="6"/>
+      <c r="U10" s="6"/>
+      <c r="V10" s="6"/>
+      <c r="W10" s="6"/>
+      <c r="X10" s="6"/>
+      <c r="Y10" s="6"/>
     </row>
     <row r="11" spans="1:25">
       <c r="A11" s="8">
-        <v>46076</v>
+        <v>46020</v>
       </c>
       <c r="B11" s="8">
-        <v>46083</v>
+        <v>46027</v>
       </c>
       <c r="C11" s="9">
         <v>0.61111111111111105</v>
@@ -42859,191 +43595,266 @@
       <c r="D11" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="E11" s="11">
-        <v>15.5</v>
-      </c>
-      <c r="F11" s="11">
-        <v>8.5</v>
-      </c>
-      <c r="G11" s="11">
-        <v>10</v>
-      </c>
-      <c r="H11" s="11">
-        <v>16</v>
-      </c>
-      <c r="I11" s="11">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="J11" s="11">
-        <v>10.221</v>
-      </c>
+      <c r="E11" s="6">
+        <v>11</v>
+      </c>
+      <c r="F11" s="6">
+        <v>4.5</v>
+      </c>
+      <c r="G11" s="6">
+        <v>5.5449999999999999</v>
+      </c>
+      <c r="H11" s="6">
+        <v>11</v>
+      </c>
+      <c r="I11" s="6">
+        <v>4.3</v>
+      </c>
+      <c r="J11" s="6">
+        <v>5.45</v>
+      </c>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="6"/>
+      <c r="P11" s="6"/>
+      <c r="Q11" s="6"/>
+      <c r="R11" s="6"/>
+      <c r="S11" s="6"/>
+      <c r="T11" s="6"/>
+      <c r="U11" s="6"/>
+      <c r="V11" s="6"/>
+      <c r="W11" s="6"/>
+      <c r="X11" s="6"/>
+      <c r="Y11" s="6"/>
     </row>
     <row r="12" spans="1:25">
       <c r="A12" s="8">
-        <v>46083</v>
+        <v>46027</v>
       </c>
       <c r="B12" s="8">
-        <v>46090</v>
+        <v>46034</v>
       </c>
       <c r="C12" s="9">
         <v>0.61111111111111105</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="E12" s="11">
-        <v>16</v>
-      </c>
-      <c r="F12" s="11">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="G12" s="11">
-        <v>10.455</v>
-      </c>
-      <c r="H12" s="11">
-        <v>16.5</v>
-      </c>
-      <c r="I12" s="11">
-        <v>9</v>
-      </c>
-      <c r="J12" s="11">
-        <v>10.721</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="E12" s="6">
+        <v>12</v>
+      </c>
+      <c r="F12" s="6">
+        <v>5.2</v>
+      </c>
+      <c r="G12" s="6">
+        <v>6</v>
+      </c>
+      <c r="H12" s="6">
+        <v>12</v>
+      </c>
+      <c r="I12" s="6">
+        <v>4.8</v>
+      </c>
+      <c r="J12" s="6">
+        <v>5.9690000000000003</v>
+      </c>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="6"/>
+      <c r="P12" s="6"/>
+      <c r="Q12" s="6"/>
+      <c r="R12" s="6"/>
+      <c r="S12" s="6"/>
+      <c r="T12" s="6"/>
+      <c r="U12" s="6"/>
+      <c r="V12" s="6"/>
+      <c r="W12" s="6"/>
+      <c r="X12" s="6"/>
+      <c r="Y12" s="6"/>
     </row>
     <row r="13" spans="1:25">
       <c r="A13" s="8">
-        <v>46090</v>
+        <v>46034</v>
       </c>
       <c r="B13" s="8">
-        <v>46097</v>
+        <v>46041</v>
       </c>
       <c r="C13" s="9">
         <v>0.61111111111111105</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="E13" s="11">
-        <v>17</v>
-      </c>
-      <c r="F13" s="11">
-        <v>9.5</v>
-      </c>
-      <c r="G13" s="11">
-        <v>11.182</v>
-      </c>
-      <c r="H13" s="11">
-        <v>18</v>
-      </c>
-      <c r="I13" s="11">
-        <v>10</v>
-      </c>
-      <c r="J13" s="11">
-        <v>11.462</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="E13" s="6">
+        <v>13.5</v>
+      </c>
+      <c r="F13" s="6">
+        <v>6</v>
+      </c>
+      <c r="G13" s="6">
+        <v>7.0910000000000002</v>
+      </c>
+      <c r="H13" s="6">
+        <v>13</v>
+      </c>
+      <c r="I13" s="6">
+        <v>5.8</v>
+      </c>
+      <c r="J13" s="6">
+        <v>7.1539999999999999</v>
+      </c>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6"/>
+      <c r="P13" s="6"/>
+      <c r="Q13" s="6"/>
+      <c r="R13" s="6"/>
+      <c r="S13" s="6"/>
+      <c r="T13" s="6"/>
+      <c r="U13" s="6"/>
+      <c r="V13" s="6"/>
+      <c r="W13" s="6"/>
+      <c r="X13" s="6"/>
+      <c r="Y13" s="6"/>
     </row>
     <row r="14" spans="1:25">
       <c r="A14" s="8">
-        <v>46097</v>
+        <v>46041</v>
       </c>
       <c r="B14" s="8">
-        <v>46104</v>
+        <v>46048</v>
       </c>
       <c r="C14" s="9">
         <v>0.61111111111111105</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="E14" s="11">
-        <v>17</v>
-      </c>
-      <c r="F14" s="11">
-        <v>10</v>
-      </c>
-      <c r="G14" s="11">
-        <v>11.682</v>
-      </c>
-      <c r="H14" s="11">
-        <v>18</v>
-      </c>
-      <c r="I14" s="11">
-        <v>10</v>
-      </c>
-      <c r="J14" s="11">
-        <v>11.962</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="E14" s="6">
+        <v>14.5</v>
+      </c>
+      <c r="F14" s="6">
+        <v>6.3</v>
+      </c>
+      <c r="G14" s="6">
+        <v>7.8819999999999997</v>
+      </c>
+      <c r="H14" s="6">
+        <v>14</v>
+      </c>
+      <c r="I14" s="6">
+        <v>6.5</v>
+      </c>
+      <c r="J14" s="6">
+        <v>8.0380000000000003</v>
+      </c>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
+      <c r="M14" s="6"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="6"/>
+      <c r="P14" s="6"/>
+      <c r="Q14" s="6"/>
+      <c r="R14" s="6"/>
+      <c r="S14" s="6"/>
+      <c r="T14" s="6"/>
+      <c r="U14" s="6"/>
+      <c r="V14" s="6"/>
+      <c r="W14" s="6"/>
+      <c r="X14" s="6"/>
+      <c r="Y14" s="6"/>
     </row>
     <row r="15" spans="1:25">
       <c r="A15" s="8">
-        <v>46104</v>
+        <v>46048</v>
       </c>
       <c r="B15" s="8">
-        <v>46111</v>
+        <v>46055</v>
       </c>
       <c r="C15" s="9">
         <v>0.61111111111111105</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="E15" s="11">
-        <v>20</v>
-      </c>
-      <c r="F15" s="11">
-        <v>11</v>
-      </c>
-      <c r="G15" s="11">
-        <v>12.727</v>
-      </c>
-      <c r="H15" s="11">
-        <v>20</v>
-      </c>
-      <c r="I15" s="11">
-        <v>11</v>
-      </c>
-      <c r="J15" s="11">
-        <v>12.865</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="E15" s="6">
+        <v>15.5</v>
+      </c>
+      <c r="F15" s="6">
+        <v>7</v>
+      </c>
+      <c r="G15" s="6">
+        <v>8.6820000000000004</v>
+      </c>
+      <c r="H15" s="6">
+        <v>16</v>
+      </c>
+      <c r="I15" s="6">
+        <v>7.5</v>
+      </c>
+      <c r="J15" s="6">
+        <v>8.8650000000000002</v>
+      </c>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="6"/>
+      <c r="P15" s="6"/>
+      <c r="Q15" s="6"/>
+      <c r="R15" s="6"/>
+      <c r="S15" s="6"/>
+      <c r="T15" s="6"/>
+      <c r="U15" s="6"/>
+      <c r="V15" s="6"/>
+      <c r="W15" s="6"/>
+      <c r="X15" s="6"/>
+      <c r="Y15" s="6"/>
     </row>
     <row r="16" spans="1:25">
       <c r="A16" s="8">
-        <v>46111</v>
+        <v>46055</v>
       </c>
       <c r="B16" s="8">
-        <v>46118</v>
+        <v>46062</v>
       </c>
       <c r="C16" s="9">
         <v>0.61111111111111105</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E16" s="11">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="F16" s="11">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="G16" s="11">
-        <v>12.526999999999999</v>
+        <v>9.4090000000000007</v>
       </c>
       <c r="H16" s="11">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I16" s="11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J16" s="11">
-        <v>12.71</v>
+        <v>9.6539999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="8">
-        <v>46118</v>
+        <v>46062</v>
       </c>
       <c r="B17" s="8">
-        <v>46125</v>
+        <v>46076</v>
       </c>
       <c r="C17" s="9">
         <v>0.61111111111111105</v>
@@ -43052,30 +43863,30 @@
         <v>57</v>
       </c>
       <c r="E17" s="11">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="F17" s="11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G17" s="11">
-        <v>12.318</v>
+        <v>9.6359999999999992</v>
       </c>
       <c r="H17" s="11">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I17" s="11">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="J17" s="11">
-        <v>12.412000000000001</v>
+        <v>9.8650000000000002</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="8">
-        <v>46125</v>
+        <v>46076</v>
       </c>
       <c r="B18" s="8">
-        <v>46132</v>
+        <v>46083</v>
       </c>
       <c r="C18" s="9">
         <v>0.61111111111111105</v>
@@ -43084,30 +43895,30 @@
         <v>57</v>
       </c>
       <c r="E18" s="11">
-        <v>19.5</v>
+        <v>15.5</v>
       </c>
       <c r="F18" s="11">
+        <v>8.5</v>
+      </c>
+      <c r="G18" s="11">
         <v>10</v>
       </c>
-      <c r="G18" s="11">
-        <v>12.227</v>
-      </c>
       <c r="H18" s="11">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I18" s="11">
-        <v>9.5</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="J18" s="11">
-        <v>12.335000000000001</v>
+        <v>10.221</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="8">
-        <v>46132</v>
+        <v>46083</v>
       </c>
       <c r="B19" s="8">
-        <v>46139</v>
+        <v>46090</v>
       </c>
       <c r="C19" s="9">
         <v>0.61111111111111105</v>
@@ -43116,30 +43927,30 @@
         <v>57</v>
       </c>
       <c r="E19" s="11">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F19" s="11">
-        <v>9.5</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="G19" s="11">
-        <v>11.864000000000001</v>
+        <v>10.455</v>
       </c>
       <c r="H19" s="11">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="I19" s="11">
         <v>9</v>
       </c>
       <c r="J19" s="11">
-        <v>11.962</v>
+        <v>10.721</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="8">
-        <v>46139</v>
+        <v>46090</v>
       </c>
       <c r="B20" s="8">
-        <v>46146</v>
+        <v>46097</v>
       </c>
       <c r="C20" s="9">
         <v>0.61111111111111105</v>
@@ -43148,30 +43959,30 @@
         <v>57</v>
       </c>
       <c r="E20" s="11">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F20" s="11">
         <v>9.5</v>
       </c>
       <c r="G20" s="11">
-        <v>11.773</v>
+        <v>11.182</v>
       </c>
       <c r="H20" s="11">
-        <v>17.8</v>
+        <v>18</v>
       </c>
       <c r="I20" s="11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J20" s="11">
-        <v>11.829000000000001</v>
+        <v>11.462</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="8">
-        <v>46146</v>
+        <v>46097</v>
       </c>
       <c r="B21" s="8">
-        <v>46153</v>
+        <v>46104</v>
       </c>
       <c r="C21" s="9">
         <v>0.61111111111111105</v>
@@ -43180,30 +43991,30 @@
         <v>57</v>
       </c>
       <c r="E21" s="11">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="F21" s="11">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="G21" s="11">
-        <v>11.635999999999999</v>
+        <v>11.682</v>
       </c>
       <c r="H21" s="11">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="I21" s="11">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="J21" s="11">
-        <v>11.702</v>
+        <v>11.962</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="8">
-        <v>46153</v>
+        <v>46104</v>
       </c>
       <c r="B22" s="8">
-        <v>46160</v>
+        <v>46111</v>
       </c>
       <c r="C22" s="9">
         <v>0.61111111111111105</v>
@@ -43212,30 +44023,30 @@
         <v>57</v>
       </c>
       <c r="E22" s="11">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="F22" s="11">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="G22" s="11">
-        <v>11.635999999999999</v>
+        <v>12.727</v>
       </c>
       <c r="H22" s="11">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="I22" s="11">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="J22" s="11">
-        <v>11.632999999999999</v>
+        <v>12.865</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="8">
-        <v>46160</v>
+        <v>46111</v>
       </c>
       <c r="B23" s="8">
-        <v>46167</v>
+        <v>46118</v>
       </c>
       <c r="C23" s="9">
         <v>0.61111111111111105</v>
@@ -43244,30 +44055,30 @@
         <v>57</v>
       </c>
       <c r="E23" s="11">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="F23" s="11">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="G23" s="11">
-        <v>11.635999999999999</v>
+        <v>12.526999999999999</v>
       </c>
       <c r="H23" s="11">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="I23" s="11">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="J23" s="11">
-        <v>11.632999999999999</v>
+        <v>12.71</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="8">
-        <v>46167</v>
+        <v>46118</v>
       </c>
       <c r="B24" s="8">
-        <v>46174</v>
+        <v>46125</v>
       </c>
       <c r="C24" s="9">
         <v>0.61111111111111105</v>
@@ -43276,30 +44087,30 @@
         <v>57</v>
       </c>
       <c r="E24" s="11">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="F24" s="11">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="G24" s="11">
-        <v>11.635999999999999</v>
+        <v>12.318</v>
       </c>
       <c r="H24" s="11">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="I24" s="11">
         <v>9.5</v>
       </c>
       <c r="J24" s="11">
-        <v>11.651999999999999</v>
+        <v>12.412000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="8">
-        <v>46174</v>
+        <v>46125</v>
       </c>
       <c r="B25" s="8">
-        <v>46181</v>
+        <v>46132</v>
       </c>
       <c r="C25" s="9">
         <v>0.61111111111111105</v>
@@ -43308,30 +44119,30 @@
         <v>57</v>
       </c>
       <c r="E25" s="11">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="F25" s="11">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="G25" s="11">
-        <v>11.545</v>
+        <v>12.227</v>
       </c>
       <c r="H25" s="11">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="I25" s="11">
         <v>9.5</v>
       </c>
       <c r="J25" s="11">
-        <v>11.537000000000001</v>
+        <v>12.335000000000001</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="8">
-        <v>46181</v>
+        <v>46132</v>
       </c>
       <c r="B26" s="8">
-        <v>46188</v>
+        <v>46139</v>
       </c>
       <c r="C26" s="9">
         <v>0.61111111111111105</v>
@@ -43340,30 +44151,30 @@
         <v>57</v>
       </c>
       <c r="E26" s="11">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="F26" s="11">
         <v>9.5</v>
       </c>
       <c r="G26" s="11">
-        <v>11.545</v>
+        <v>11.864000000000001</v>
       </c>
       <c r="H26" s="11">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="I26" s="11">
         <v>9</v>
       </c>
       <c r="J26" s="11">
-        <v>11.522</v>
+        <v>11.962</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="8">
-        <v>46188</v>
+        <v>46139</v>
       </c>
       <c r="B27" s="8">
-        <v>46195</v>
+        <v>46146</v>
       </c>
       <c r="C27" s="9">
         <v>0.61111111111111105</v>
@@ -43372,21 +44183,245 @@
         <v>57</v>
       </c>
       <c r="E27" s="11">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="F27" s="11">
         <v>9.5</v>
       </c>
       <c r="G27" s="11">
-        <v>11.545</v>
+        <v>11.773</v>
       </c>
       <c r="H27" s="11">
-        <v>17.5</v>
+        <v>17.8</v>
       </c>
       <c r="I27" s="11">
         <v>9</v>
       </c>
       <c r="J27" s="11">
+        <v>11.829000000000001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="8">
+        <v>46146</v>
+      </c>
+      <c r="B28" s="8">
+        <v>46153</v>
+      </c>
+      <c r="C28" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="E28" s="11">
+        <v>17.5</v>
+      </c>
+      <c r="F28" s="11">
+        <v>9.5</v>
+      </c>
+      <c r="G28" s="11">
+        <v>11.635999999999999</v>
+      </c>
+      <c r="H28" s="11">
+        <v>17.5</v>
+      </c>
+      <c r="I28" s="11">
+        <v>9.5</v>
+      </c>
+      <c r="J28" s="11">
+        <v>11.702</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="8">
+        <v>46153</v>
+      </c>
+      <c r="B29" s="8">
+        <v>46160</v>
+      </c>
+      <c r="C29" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="E29" s="11">
+        <v>17.5</v>
+      </c>
+      <c r="F29" s="11">
+        <v>9.5</v>
+      </c>
+      <c r="G29" s="11">
+        <v>11.635999999999999</v>
+      </c>
+      <c r="H29" s="11">
+        <v>17.5</v>
+      </c>
+      <c r="I29" s="11">
+        <v>9.5</v>
+      </c>
+      <c r="J29" s="11">
+        <v>11.632999999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="8">
+        <v>46160</v>
+      </c>
+      <c r="B30" s="8">
+        <v>46167</v>
+      </c>
+      <c r="C30" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="E30" s="11">
+        <v>17.5</v>
+      </c>
+      <c r="F30" s="11">
+        <v>9.5</v>
+      </c>
+      <c r="G30" s="11">
+        <v>11.635999999999999</v>
+      </c>
+      <c r="H30" s="11">
+        <v>17.5</v>
+      </c>
+      <c r="I30" s="11">
+        <v>9.5</v>
+      </c>
+      <c r="J30" s="11">
+        <v>11.632999999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="8">
+        <v>46167</v>
+      </c>
+      <c r="B31" s="8">
+        <v>46174</v>
+      </c>
+      <c r="C31" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="E31" s="11">
+        <v>17.5</v>
+      </c>
+      <c r="F31" s="11">
+        <v>9.5</v>
+      </c>
+      <c r="G31" s="11">
+        <v>11.635999999999999</v>
+      </c>
+      <c r="H31" s="11">
+        <v>17.5</v>
+      </c>
+      <c r="I31" s="11">
+        <v>9.5</v>
+      </c>
+      <c r="J31" s="11">
+        <v>11.651999999999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="8">
+        <v>46174</v>
+      </c>
+      <c r="B32" s="8">
+        <v>46181</v>
+      </c>
+      <c r="C32" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="E32" s="11">
+        <v>17.5</v>
+      </c>
+      <c r="F32" s="11">
+        <v>9.5</v>
+      </c>
+      <c r="G32" s="11">
+        <v>11.545</v>
+      </c>
+      <c r="H32" s="11">
+        <v>17.5</v>
+      </c>
+      <c r="I32" s="11">
+        <v>9.5</v>
+      </c>
+      <c r="J32" s="11">
+        <v>11.537000000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" s="8">
+        <v>46181</v>
+      </c>
+      <c r="B33" s="8">
+        <v>46188</v>
+      </c>
+      <c r="C33" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="E33" s="11">
+        <v>17.5</v>
+      </c>
+      <c r="F33" s="11">
+        <v>9.5</v>
+      </c>
+      <c r="G33" s="11">
+        <v>11.545</v>
+      </c>
+      <c r="H33" s="11">
+        <v>17.5</v>
+      </c>
+      <c r="I33" s="11">
+        <v>9</v>
+      </c>
+      <c r="J33" s="11">
+        <v>11.522</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" s="8">
+        <v>46188</v>
+      </c>
+      <c r="B34" s="8">
+        <v>46195</v>
+      </c>
+      <c r="C34" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="E34" s="11">
+        <v>17.5</v>
+      </c>
+      <c r="F34" s="11">
+        <v>9.5</v>
+      </c>
+      <c r="G34" s="11">
+        <v>11.545</v>
+      </c>
+      <c r="H34" s="11">
+        <v>17.5</v>
+      </c>
+      <c r="I34" s="11">
+        <v>9</v>
+      </c>
+      <c r="J34" s="11">
         <v>11.522</v>
       </c>
     </row>
@@ -43406,7 +44441,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -43419,11 +44454,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="22.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.77734375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="22.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.83203125" style="3" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data/industry/TrendForce/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34EB8659-B381-E047-B620-4A87C8C4AD14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCFECDAD-6183-45B6-98AE-8A62A91F0EC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25660" yWindow="600" windowWidth="25540" windowHeight="26040" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="61">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -408,10 +408,10 @@
     </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Comma" xfId="2" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="백분율" xfId="3" builtinId="5"/>
+    <cellStyle name="쉼표" xfId="2" builtinId="3"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -429,7 +429,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1375,6 +1375,15 @@
                 <c:pt idx="297">
                   <c:v>46195</c:v>
                 </c:pt>
+                <c:pt idx="298">
+                  <c:v>46196</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>46196</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>46196</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2277,6 +2286,12 @@
                 </c:pt>
                 <c:pt idx="297">
                   <c:v>46.167000000000002</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>46.5</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>46.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3217,6 +3232,15 @@
                 <c:pt idx="297">
                   <c:v>46195</c:v>
                 </c:pt>
+                <c:pt idx="298">
+                  <c:v>46196</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>46196</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>46196</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4118,6 +4142,12 @@
                   <c:v>23.5</c:v>
                 </c:pt>
                 <c:pt idx="297">
+                  <c:v>23.5</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>23.5</c:v>
+                </c:pt>
+                <c:pt idx="299">
                   <c:v>23.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -5059,6 +5089,15 @@
                 <c:pt idx="297">
                   <c:v>46195</c:v>
                 </c:pt>
+                <c:pt idx="298">
+                  <c:v>46196</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>46196</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>46196</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5961,6 +6000,12 @@
                 </c:pt>
                 <c:pt idx="297">
                   <c:v>69.75</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>70.22</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>70.634</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6901,6 +6946,15 @@
                 <c:pt idx="297">
                   <c:v>46195</c:v>
                 </c:pt>
+                <c:pt idx="298">
+                  <c:v>46196</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>46196</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>46196</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7802,6 +7856,12 @@
                   <c:v>11.75</c:v>
                 </c:pt>
                 <c:pt idx="297">
+                  <c:v>11.75</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>11.75</c:v>
+                </c:pt>
+                <c:pt idx="299">
                   <c:v>11.75</c:v>
                 </c:pt>
               </c:numCache>
@@ -8743,6 +8803,15 @@
                 <c:pt idx="297">
                   <c:v>46195</c:v>
                 </c:pt>
+                <c:pt idx="298">
+                  <c:v>46196</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>46196</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>46196</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9644,6 +9713,12 @@
                   <c:v>35.9</c:v>
                 </c:pt>
                 <c:pt idx="297">
+                  <c:v>35.9</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>35.9</c:v>
+                </c:pt>
+                <c:pt idx="299">
                   <c:v>35.9</c:v>
                 </c:pt>
               </c:numCache>
@@ -10601,6 +10676,15 @@
                 <c:pt idx="297">
                   <c:v>46195</c:v>
                 </c:pt>
+                <c:pt idx="298">
+                  <c:v>46196</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>46196</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>46196</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -11502,6 +11586,12 @@
                   <c:v>4.407</c:v>
                 </c:pt>
                 <c:pt idx="297">
+                  <c:v>4.407</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>4.407</c:v>
+                </c:pt>
+                <c:pt idx="299">
                   <c:v>4.407</c:v>
                 </c:pt>
               </c:numCache>
@@ -12445,6 +12535,15 @@
                 <c:pt idx="297">
                   <c:v>46195</c:v>
                 </c:pt>
+                <c:pt idx="298">
+                  <c:v>46196</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>46196</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>46196</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13347,6 +13446,12 @@
                 </c:pt>
                 <c:pt idx="297">
                   <c:v>11.151999999999999</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>11.271000000000001</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>11.271000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13625,7 +13730,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -14646,7 +14751,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -17411,15 +17516,15 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Z300"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <dimension ref="A1:Z303"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.33203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.77734375" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.77734375" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="13" width="9" style="11"/>
-    <col min="14" max="14" width="9.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="15" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -40808,6 +40913,174 @@
       </c>
       <c r="Y300" s="11">
         <v>11.151999999999999</v>
+      </c>
+    </row>
+    <row r="301" spans="1:26">
+      <c r="A301" s="8">
+        <v>46196</v>
+      </c>
+      <c r="B301" s="8">
+        <v>46196</v>
+      </c>
+      <c r="C301" s="9">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D301" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E301" s="11">
+        <v>59.5</v>
+      </c>
+      <c r="F301" s="11">
+        <v>31</v>
+      </c>
+      <c r="G301" s="11">
+        <v>46.5</v>
+      </c>
+      <c r="H301" s="11">
+        <v>25.2</v>
+      </c>
+      <c r="I301" s="11">
+        <v>22.1</v>
+      </c>
+      <c r="J301" s="11">
+        <v>23.5</v>
+      </c>
+      <c r="K301" s="11">
+        <v>83</v>
+      </c>
+      <c r="L301" s="11">
+        <v>38</v>
+      </c>
+      <c r="M301" s="11">
+        <v>70.22</v>
+      </c>
+      <c r="N301" s="11">
+        <v>12.2</v>
+      </c>
+      <c r="O301" s="11">
+        <v>10.3</v>
+      </c>
+      <c r="P301" s="11">
+        <v>11.75</v>
+      </c>
+      <c r="Q301" s="11">
+        <v>55.5</v>
+      </c>
+      <c r="R301" s="11">
+        <v>19</v>
+      </c>
+      <c r="S301" s="11">
+        <v>35.9</v>
+      </c>
+      <c r="T301" s="11">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="U301" s="11">
+        <v>3.8</v>
+      </c>
+      <c r="V301" s="11">
+        <v>4.407</v>
+      </c>
+      <c r="W301" s="11">
+        <v>16.5</v>
+      </c>
+      <c r="X301" s="11">
+        <v>6.6</v>
+      </c>
+      <c r="Y301" s="11">
+        <v>11.271000000000001</v>
+      </c>
+    </row>
+    <row r="302" spans="1:26">
+      <c r="A302" s="8">
+        <v>46196</v>
+      </c>
+      <c r="B302" s="8">
+        <v>46196</v>
+      </c>
+      <c r="C302" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D302" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E302" s="11">
+        <v>59.5</v>
+      </c>
+      <c r="F302" s="11">
+        <v>31</v>
+      </c>
+      <c r="G302" s="11">
+        <v>46.5</v>
+      </c>
+      <c r="H302" s="11">
+        <v>25.2</v>
+      </c>
+      <c r="I302" s="11">
+        <v>22.1</v>
+      </c>
+      <c r="J302" s="11">
+        <v>23.5</v>
+      </c>
+      <c r="K302" s="11">
+        <v>85</v>
+      </c>
+      <c r="L302" s="11">
+        <v>38</v>
+      </c>
+      <c r="M302" s="11">
+        <v>70.634</v>
+      </c>
+      <c r="N302" s="11">
+        <v>12.2</v>
+      </c>
+      <c r="O302" s="11">
+        <v>10.3</v>
+      </c>
+      <c r="P302" s="11">
+        <v>11.75</v>
+      </c>
+      <c r="Q302" s="11">
+        <v>55.5</v>
+      </c>
+      <c r="R302" s="11">
+        <v>19</v>
+      </c>
+      <c r="S302" s="11">
+        <v>35.9</v>
+      </c>
+      <c r="T302" s="11">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="U302" s="11">
+        <v>3.8</v>
+      </c>
+      <c r="V302" s="11">
+        <v>4.407</v>
+      </c>
+      <c r="W302" s="11">
+        <v>16.5</v>
+      </c>
+      <c r="X302" s="11">
+        <v>6.6</v>
+      </c>
+      <c r="Y302" s="11">
+        <v>11.271000000000001</v>
+      </c>
+    </row>
+    <row r="303" spans="1:26">
+      <c r="A303" s="8">
+        <v>46196</v>
+      </c>
+      <c r="B303" s="8">
+        <v>46196</v>
+      </c>
+      <c r="C303" s="9">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D303" s="10" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -40827,21 +41100,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:AK8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.1640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.1640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.77734375" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.77734375" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="9.5" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.5" style="11" customWidth="1"/>
-    <col min="9" max="9" width="9.83203125" style="11" customWidth="1"/>
+    <col min="7" max="7" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.44140625" style="11" customWidth="1"/>
+    <col min="9" max="9" width="9.77734375" style="11" customWidth="1"/>
     <col min="10" max="10" width="10.33203125" style="11" customWidth="1"/>
-    <col min="11" max="11" width="9.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" style="11"/>
-    <col min="13" max="13" width="9.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -41473,17 +41746,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:Y34"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.1640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="15"/>
-    <col min="7" max="7" width="9.5" style="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5" style="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.44140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.44140625" style="15" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="15"/>
-    <col min="10" max="10" width="11.83203125" style="17" customWidth="1"/>
+    <col min="10" max="10" width="11.77734375" style="17" customWidth="1"/>
     <col min="11" max="12" width="9" style="15"/>
     <col min="13" max="13" width="13.33203125" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
@@ -43109,13 +43382,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:Y34"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -44441,7 +44714,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -44454,11 +44727,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:D32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="22.83203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.83203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.83203125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="22.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.77734375" style="3" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10118"/>
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data/industry/TrendForce/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCFECDAD-6183-45B6-98AE-8A62A91F0EC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC1655EC-BE9E-0A4F-9F61-7AB106C9AA6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25420" yWindow="600" windowWidth="25780" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -408,10 +408,10 @@
     </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="백분율" xfId="3" builtinId="5"/>
-    <cellStyle name="쉼표" xfId="2" builtinId="3"/>
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="2" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -429,7 +429,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2293,6 +2293,9 @@
                 <c:pt idx="299">
                   <c:v>46.5</c:v>
                 </c:pt>
+                <c:pt idx="300">
+                  <c:v>46.5</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4150,6 +4153,9 @@
                 <c:pt idx="299">
                   <c:v>23.5</c:v>
                 </c:pt>
+                <c:pt idx="300">
+                  <c:v>23.5</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -6007,6 +6013,9 @@
                 <c:pt idx="299">
                   <c:v>70.634</c:v>
                 </c:pt>
+                <c:pt idx="300">
+                  <c:v>70.634</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -7864,6 +7873,9 @@
                 <c:pt idx="299">
                   <c:v>11.75</c:v>
                 </c:pt>
+                <c:pt idx="300">
+                  <c:v>11.75</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -9719,6 +9731,9 @@
                   <c:v>35.9</c:v>
                 </c:pt>
                 <c:pt idx="299">
+                  <c:v>35.9</c:v>
+                </c:pt>
+                <c:pt idx="300">
                   <c:v>35.9</c:v>
                 </c:pt>
               </c:numCache>
@@ -11594,6 +11609,9 @@
                 <c:pt idx="299">
                   <c:v>4.407</c:v>
                 </c:pt>
+                <c:pt idx="300">
+                  <c:v>4.407</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -13451,6 +13469,9 @@
                   <c:v>11.271000000000001</c:v>
                 </c:pt>
                 <c:pt idx="299">
+                  <c:v>11.271000000000001</c:v>
+                </c:pt>
+                <c:pt idx="300">
                   <c:v>11.271000000000001</c:v>
                 </c:pt>
               </c:numCache>
@@ -13730,7 +13751,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -14751,7 +14772,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -17517,14 +17538,14 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:Z303"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.77734375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.77734375" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.83203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.83203125" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="13" width="9" style="11"/>
-    <col min="14" max="14" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.5" style="11" bestFit="1" customWidth="1"/>
     <col min="15" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -41081,6 +41102,69 @@
       </c>
       <c r="D303" s="10" t="s">
         <v>53</v>
+      </c>
+      <c r="E303" s="11">
+        <v>59.5</v>
+      </c>
+      <c r="F303" s="11">
+        <v>31</v>
+      </c>
+      <c r="G303" s="11">
+        <v>46.5</v>
+      </c>
+      <c r="H303" s="11">
+        <v>25.2</v>
+      </c>
+      <c r="I303" s="11">
+        <v>22.1</v>
+      </c>
+      <c r="J303" s="11">
+        <v>23.5</v>
+      </c>
+      <c r="K303" s="11">
+        <v>85</v>
+      </c>
+      <c r="L303" s="11">
+        <v>38</v>
+      </c>
+      <c r="M303" s="11">
+        <v>70.634</v>
+      </c>
+      <c r="N303" s="11">
+        <v>12.2</v>
+      </c>
+      <c r="O303" s="11">
+        <v>10.3</v>
+      </c>
+      <c r="P303" s="11">
+        <v>11.75</v>
+      </c>
+      <c r="Q303" s="11">
+        <v>55.5</v>
+      </c>
+      <c r="R303" s="11">
+        <v>19</v>
+      </c>
+      <c r="S303" s="11">
+        <v>35.9</v>
+      </c>
+      <c r="T303" s="11">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="U303" s="11">
+        <v>3.8</v>
+      </c>
+      <c r="V303" s="11">
+        <v>4.407</v>
+      </c>
+      <c r="W303" s="11">
+        <v>16.5</v>
+      </c>
+      <c r="X303" s="11">
+        <v>6.6</v>
+      </c>
+      <c r="Y303" s="11">
+        <v>11.271000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -41100,21 +41184,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:AK8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.77734375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.77734375" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.83203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.83203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.1640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5" style="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.44140625" style="11" customWidth="1"/>
-    <col min="9" max="9" width="9.77734375" style="11" customWidth="1"/>
+    <col min="7" max="7" width="9.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.5" style="11" customWidth="1"/>
+    <col min="9" max="9" width="9.83203125" style="11" customWidth="1"/>
     <col min="10" max="10" width="10.33203125" style="11" customWidth="1"/>
-    <col min="11" max="11" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.5" style="11" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" style="11"/>
-    <col min="13" max="13" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.5" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -41746,17 +41830,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:Y34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="15"/>
-    <col min="7" max="7" width="9.44140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.44140625" style="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5" style="17" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5" style="15" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="15"/>
-    <col min="10" max="10" width="11.77734375" style="17" customWidth="1"/>
+    <col min="10" max="10" width="11.83203125" style="17" customWidth="1"/>
     <col min="11" max="12" width="9" style="15"/>
     <col min="13" max="13" width="13.33203125" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
@@ -43382,13 +43466,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:Y34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1640625" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.5" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -44714,7 +44798,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -44727,11 +44811,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="22.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.77734375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="22.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.83203125" style="3" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data/industry/TrendForce/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC1655EC-BE9E-0A4F-9F61-7AB106C9AA6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74BFFD3D-FDBB-4CAD-B519-6860121F945E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25420" yWindow="600" windowWidth="25780" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="61">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -408,10 +408,10 @@
     </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Comma" xfId="2" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="백분율" xfId="3" builtinId="5"/>
+    <cellStyle name="쉼표" xfId="2" builtinId="3"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -429,7 +429,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1384,6 +1384,15 @@
                 <c:pt idx="300">
                   <c:v>46196</c:v>
                 </c:pt>
+                <c:pt idx="301">
+                  <c:v>46197</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>46197</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>46197</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2295,6 +2304,12 @@
                 </c:pt>
                 <c:pt idx="300">
                   <c:v>46.5</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>46.667000000000002</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>46.667000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3244,6 +3259,15 @@
                 <c:pt idx="300">
                   <c:v>46196</c:v>
                 </c:pt>
+                <c:pt idx="301">
+                  <c:v>46197</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>46197</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>46197</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4154,6 +4178,12 @@
                   <c:v>23.5</c:v>
                 </c:pt>
                 <c:pt idx="300">
+                  <c:v>23.5</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>23.5</c:v>
+                </c:pt>
+                <c:pt idx="302">
                   <c:v>23.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -5104,6 +5134,15 @@
                 <c:pt idx="300">
                   <c:v>46196</c:v>
                 </c:pt>
+                <c:pt idx="301">
+                  <c:v>46197</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>46197</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>46197</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6015,6 +6054,12 @@
                 </c:pt>
                 <c:pt idx="300">
                   <c:v>70.634</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>71.171000000000006</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>71.305000000000007</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6964,6 +7009,15 @@
                 <c:pt idx="300">
                   <c:v>46196</c:v>
                 </c:pt>
+                <c:pt idx="301">
+                  <c:v>46197</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>46197</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>46197</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7875,6 +7929,12 @@
                 </c:pt>
                 <c:pt idx="300">
                   <c:v>11.75</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>11.675000000000001</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>11.675000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8824,6 +8884,15 @@
                 <c:pt idx="300">
                   <c:v>46196</c:v>
                 </c:pt>
+                <c:pt idx="301">
+                  <c:v>46197</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>46197</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>46197</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9734,6 +9803,12 @@
                   <c:v>35.9</c:v>
                 </c:pt>
                 <c:pt idx="300">
+                  <c:v>35.9</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>35.9</c:v>
+                </c:pt>
+                <c:pt idx="302">
                   <c:v>35.9</c:v>
                 </c:pt>
               </c:numCache>
@@ -10700,6 +10775,15 @@
                 <c:pt idx="300">
                   <c:v>46196</c:v>
                 </c:pt>
+                <c:pt idx="301">
+                  <c:v>46197</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>46197</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>46197</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -11611,6 +11695,12 @@
                 </c:pt>
                 <c:pt idx="300">
                   <c:v>4.407</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>4.3639999999999999</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>4.3639999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12562,6 +12652,15 @@
                 <c:pt idx="300">
                   <c:v>46196</c:v>
                 </c:pt>
+                <c:pt idx="301">
+                  <c:v>46197</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>46197</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>46197</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13473,6 +13572,12 @@
                 </c:pt>
                 <c:pt idx="300">
                   <c:v>11.271000000000001</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>11.356999999999999</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>11.385999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13751,7 +13856,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -14772,7 +14877,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -17537,15 +17642,15 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Z303"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <dimension ref="A1:Z306"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.83203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.77734375" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.77734375" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="13" width="9" style="11"/>
-    <col min="14" max="14" width="9.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="15" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -41165,6 +41270,174 @@
       </c>
       <c r="Y303" s="11">
         <v>11.271000000000001</v>
+      </c>
+    </row>
+    <row r="304" spans="1:26">
+      <c r="A304" s="8">
+        <v>46197</v>
+      </c>
+      <c r="B304" s="8">
+        <v>46197</v>
+      </c>
+      <c r="C304" s="9">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D304" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E304" s="11">
+        <v>59.5</v>
+      </c>
+      <c r="F304" s="11">
+        <v>31</v>
+      </c>
+      <c r="G304" s="11">
+        <v>46.667000000000002</v>
+      </c>
+      <c r="H304" s="11">
+        <v>25.2</v>
+      </c>
+      <c r="I304" s="11">
+        <v>22</v>
+      </c>
+      <c r="J304" s="11">
+        <v>23.5</v>
+      </c>
+      <c r="K304" s="11">
+        <v>87</v>
+      </c>
+      <c r="L304" s="11">
+        <v>39</v>
+      </c>
+      <c r="M304" s="11">
+        <v>71.171000000000006</v>
+      </c>
+      <c r="N304" s="11">
+        <v>12.2</v>
+      </c>
+      <c r="O304" s="11">
+        <v>10.3</v>
+      </c>
+      <c r="P304" s="11">
+        <v>11.675000000000001</v>
+      </c>
+      <c r="Q304" s="11">
+        <v>55.5</v>
+      </c>
+      <c r="R304" s="11">
+        <v>19.5</v>
+      </c>
+      <c r="S304" s="11">
+        <v>35.9</v>
+      </c>
+      <c r="T304" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="U304" s="11">
+        <v>3.8</v>
+      </c>
+      <c r="V304" s="11">
+        <v>4.3639999999999999</v>
+      </c>
+      <c r="W304" s="11">
+        <v>16.5</v>
+      </c>
+      <c r="X304" s="11">
+        <v>7</v>
+      </c>
+      <c r="Y304" s="11">
+        <v>11.356999999999999</v>
+      </c>
+    </row>
+    <row r="305" spans="1:25">
+      <c r="A305" s="8">
+        <v>46197</v>
+      </c>
+      <c r="B305" s="8">
+        <v>46197</v>
+      </c>
+      <c r="C305" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D305" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E305" s="11">
+        <v>59.5</v>
+      </c>
+      <c r="F305" s="11">
+        <v>31</v>
+      </c>
+      <c r="G305" s="11">
+        <v>46.667000000000002</v>
+      </c>
+      <c r="H305" s="11">
+        <v>25.2</v>
+      </c>
+      <c r="I305" s="11">
+        <v>22</v>
+      </c>
+      <c r="J305" s="11">
+        <v>23.5</v>
+      </c>
+      <c r="K305" s="11">
+        <v>87</v>
+      </c>
+      <c r="L305" s="11">
+        <v>39</v>
+      </c>
+      <c r="M305" s="11">
+        <v>71.305000000000007</v>
+      </c>
+      <c r="N305" s="11">
+        <v>12.2</v>
+      </c>
+      <c r="O305" s="11">
+        <v>10.3</v>
+      </c>
+      <c r="P305" s="11">
+        <v>11.675000000000001</v>
+      </c>
+      <c r="Q305" s="11">
+        <v>55.5</v>
+      </c>
+      <c r="R305" s="11">
+        <v>19.5</v>
+      </c>
+      <c r="S305" s="11">
+        <v>35.9</v>
+      </c>
+      <c r="T305" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="U305" s="11">
+        <v>3.8</v>
+      </c>
+      <c r="V305" s="11">
+        <v>4.3639999999999999</v>
+      </c>
+      <c r="W305" s="11">
+        <v>16.5</v>
+      </c>
+      <c r="X305" s="11">
+        <v>7</v>
+      </c>
+      <c r="Y305" s="11">
+        <v>11.385999999999999</v>
+      </c>
+    </row>
+    <row r="306" spans="1:25">
+      <c r="A306" s="8">
+        <v>46197</v>
+      </c>
+      <c r="B306" s="8">
+        <v>46197</v>
+      </c>
+      <c r="C306" s="9">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D306" s="10" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -41184,21 +41457,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:AK8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.83203125" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.1640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.77734375" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.77734375" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="9.5" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.5" style="11" customWidth="1"/>
-    <col min="9" max="9" width="9.83203125" style="11" customWidth="1"/>
+    <col min="7" max="7" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.44140625" style="11" customWidth="1"/>
+    <col min="9" max="9" width="9.77734375" style="11" customWidth="1"/>
     <col min="10" max="10" width="10.33203125" style="11" customWidth="1"/>
-    <col min="11" max="11" width="9.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" style="11"/>
-    <col min="13" max="13" width="9.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -41830,17 +42103,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:Y34"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.1640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="15"/>
-    <col min="7" max="7" width="9.5" style="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5" style="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.44140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.44140625" style="15" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="15"/>
-    <col min="10" max="10" width="11.83203125" style="17" customWidth="1"/>
+    <col min="10" max="10" width="11.77734375" style="17" customWidth="1"/>
     <col min="11" max="12" width="9" style="15"/>
     <col min="13" max="13" width="13.33203125" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
@@ -43466,13 +43739,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:Y34"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -44798,7 +45071,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -44811,11 +45084,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:D32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="22.83203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.83203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.83203125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="22.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.77734375" style="3" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74BFFD3D-FDBB-4CAD-B519-6860121F945E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9AC9CD6-345F-4752-AE3C-C53DB5FD0211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="61">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -114,135 +114,135 @@
   </si>
   <si>
     <t>Item</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Supplier</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DRAM</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DDR5 16G (2Gx8) 4800/5600</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>SK Hynix, Samsung</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DDR5 16Gb (2Gx8) eTT</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Samsung</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DDR4 16Gb (2Gx8)3200</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Samsung, SK Hynix</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DDR4 16Gb (2Gx8) eTT</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>SK Hynix, Samsung, Spectek</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DDR4 8Gb (1Gx8) 3200</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Samsung, SK Hynix, Micron</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DDR4 8Gb (1Gx8) eTT</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>SK Hynix, Spectek, Samsung, CXMT</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DDR3 4Gb 512Mx8 1600/1866</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>SK Hynix, Micron, Samsung, Nanya</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DRAM Contract</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Module</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Crucial, Kingston, Klevv, Samsung</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>GDDR</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>LPDDR</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mobile DRAM Contract</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.dramexchange.com/</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Group</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>Supplier</t>
+    <t>Base Date</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>DRAM</t>
+    <t>Release Date</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>DDR5 16G (2Gx8) 4800/5600</t>
+    <t>Time</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>SK Hynix, Samsung</t>
+    <t>Time Zone</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>DDR5 16Gb (2Gx8) eTT</t>
+    <t>UTC+8</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>Samsung</t>
+    <t>High</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>DDR4 16Gb (2Gx8)3200</t>
+    <t>Low</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>Samsung, SK Hynix</t>
+    <t>Average</t>
     <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>DDR4 16Gb (2Gx8) eTT</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>SK Hynix, Samsung, Spectek</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>DDR4 8Gb (1Gx8) 3200</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Samsung, SK Hynix, Micron</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>DDR4 8Gb (1Gx8) eTT</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>SK Hynix, Spectek, Samsung, CXMT</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>DDR3 4Gb 512Mx8 1600/1866</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>SK Hynix, Micron, Samsung, Nanya</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>DRAM Contract</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Module</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Crucial, Kingston, Klevv, Samsung</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>GDDR</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>LPDDR</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Mobile DRAM Contract</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.dramexchange.com/</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Group</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Date</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Release Date</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Time</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Time Zone</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>UTC+8</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>High</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Low</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Average</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>UTC+8</t>
@@ -269,13 +269,19 @@
     <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="168" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -349,61 +355,64 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="10" fontId="8" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1393,6 +1402,15 @@
                 <c:pt idx="303">
                   <c:v>46197</c:v>
                 </c:pt>
+                <c:pt idx="304">
+                  <c:v>46198</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>46198</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>46198</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2310,6 +2328,15 @@
                 </c:pt>
                 <c:pt idx="302">
                   <c:v>46.667000000000002</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>46.667000000000002</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>46.732999999999997</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>46.732999999999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3268,6 +3295,15 @@
                 <c:pt idx="303">
                   <c:v>46197</c:v>
                 </c:pt>
+                <c:pt idx="304">
+                  <c:v>46198</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>46198</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>46198</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4184,6 +4220,15 @@
                   <c:v>23.5</c:v>
                 </c:pt>
                 <c:pt idx="302">
+                  <c:v>23.5</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>23.5</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>23.5</c:v>
+                </c:pt>
+                <c:pt idx="305">
                   <c:v>23.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -5143,6 +5188,15 @@
                 <c:pt idx="303">
                   <c:v>46197</c:v>
                 </c:pt>
+                <c:pt idx="304">
+                  <c:v>46198</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>46198</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>46198</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6060,6 +6114,15 @@
                 </c:pt>
                 <c:pt idx="302">
                   <c:v>71.305000000000007</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>71.305000000000007</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>71.584999999999994</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>71.584999999999994</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7018,6 +7081,15 @@
                 <c:pt idx="303">
                   <c:v>46197</c:v>
                 </c:pt>
+                <c:pt idx="304">
+                  <c:v>46198</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>46198</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>46198</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7934,6 +8006,15 @@
                   <c:v>11.675000000000001</c:v>
                 </c:pt>
                 <c:pt idx="302">
+                  <c:v>11.675000000000001</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>11.675000000000001</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>11.675000000000001</c:v>
+                </c:pt>
+                <c:pt idx="305">
                   <c:v>11.675000000000001</c:v>
                 </c:pt>
               </c:numCache>
@@ -8893,6 +8974,15 @@
                 <c:pt idx="303">
                   <c:v>46197</c:v>
                 </c:pt>
+                <c:pt idx="304">
+                  <c:v>46198</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>46198</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>46198</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9810,6 +9900,15 @@
                 </c:pt>
                 <c:pt idx="302">
                   <c:v>35.9</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>35.9</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>36</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10784,6 +10883,15 @@
                 <c:pt idx="303">
                   <c:v>46197</c:v>
                 </c:pt>
+                <c:pt idx="304">
+                  <c:v>46198</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>46198</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>46198</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -11701,6 +11809,15 @@
                 </c:pt>
                 <c:pt idx="302">
                   <c:v>4.3639999999999999</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>4.3639999999999999</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>4.3209999999999997</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>4.3209999999999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12661,6 +12778,15 @@
                 <c:pt idx="303">
                   <c:v>46197</c:v>
                 </c:pt>
+                <c:pt idx="304">
+                  <c:v>46198</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>46198</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>46198</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13578,6 +13704,15 @@
                 </c:pt>
                 <c:pt idx="302">
                   <c:v>11.385999999999999</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>11.385999999999999</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>11.5</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>11.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17642,7 +17777,7 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Z306"/>
+  <dimension ref="A1:Z309"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.77734375" style="8" bestFit="1" customWidth="1"/>
@@ -17656,16 +17791,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" s="5" customFormat="1">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="22" t="s">
         <v>52</v>
       </c>
       <c r="E1" s="4" t="s">
@@ -17733,10 +17868,10 @@
       </c>
     </row>
     <row r="2" spans="1:26">
-      <c r="A2" s="19"/>
-      <c r="B2" s="19"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="21"/>
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="22"/>
       <c r="E2" s="6" t="s">
         <v>54</v>
       </c>
@@ -41437,6 +41572,237 @@
         <v>0.75694444444444453</v>
       </c>
       <c r="D306" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E306" s="11">
+        <v>59.5</v>
+      </c>
+      <c r="F306" s="11">
+        <v>31</v>
+      </c>
+      <c r="G306" s="11">
+        <v>46.667000000000002</v>
+      </c>
+      <c r="H306" s="11">
+        <v>25.2</v>
+      </c>
+      <c r="I306" s="11">
+        <v>22</v>
+      </c>
+      <c r="J306" s="11">
+        <v>23.5</v>
+      </c>
+      <c r="K306" s="11">
+        <v>87</v>
+      </c>
+      <c r="L306" s="11">
+        <v>39</v>
+      </c>
+      <c r="M306" s="11">
+        <v>71.305000000000007</v>
+      </c>
+      <c r="N306" s="11">
+        <v>12.2</v>
+      </c>
+      <c r="O306" s="11">
+        <v>10.3</v>
+      </c>
+      <c r="P306" s="11">
+        <v>11.675000000000001</v>
+      </c>
+      <c r="Q306" s="11">
+        <v>55.5</v>
+      </c>
+      <c r="R306" s="11">
+        <v>19.5</v>
+      </c>
+      <c r="S306" s="11">
+        <v>35.9</v>
+      </c>
+      <c r="T306" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="U306" s="11">
+        <v>3.8</v>
+      </c>
+      <c r="V306" s="11">
+        <v>4.3639999999999999</v>
+      </c>
+      <c r="W306" s="11">
+        <v>16.5</v>
+      </c>
+      <c r="X306" s="11">
+        <v>7</v>
+      </c>
+      <c r="Y306" s="11">
+        <v>11.385999999999999</v>
+      </c>
+    </row>
+    <row r="307" spans="1:25">
+      <c r="A307" s="8">
+        <v>46198</v>
+      </c>
+      <c r="B307" s="8">
+        <v>46198</v>
+      </c>
+      <c r="C307" s="9">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D307" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E307" s="11">
+        <v>59.7</v>
+      </c>
+      <c r="F307" s="11">
+        <v>31</v>
+      </c>
+      <c r="G307" s="11">
+        <v>46.732999999999997</v>
+      </c>
+      <c r="H307" s="11">
+        <v>25.2</v>
+      </c>
+      <c r="I307" s="11">
+        <v>22</v>
+      </c>
+      <c r="J307" s="11">
+        <v>23.5</v>
+      </c>
+      <c r="K307" s="11">
+        <v>90</v>
+      </c>
+      <c r="L307" s="11">
+        <v>39</v>
+      </c>
+      <c r="M307" s="11">
+        <v>71.584999999999994</v>
+      </c>
+      <c r="N307" s="11">
+        <v>12.2</v>
+      </c>
+      <c r="O307" s="11">
+        <v>10.3</v>
+      </c>
+      <c r="P307" s="11">
+        <v>11.675000000000001</v>
+      </c>
+      <c r="Q307" s="11">
+        <v>55.5</v>
+      </c>
+      <c r="R307" s="11">
+        <v>19.5</v>
+      </c>
+      <c r="S307" s="11">
+        <v>36</v>
+      </c>
+      <c r="T307" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="U307" s="11">
+        <v>3.8</v>
+      </c>
+      <c r="V307" s="11">
+        <v>4.3209999999999997</v>
+      </c>
+      <c r="W307" s="11">
+        <v>16.5</v>
+      </c>
+      <c r="X307" s="11">
+        <v>7.2</v>
+      </c>
+      <c r="Y307" s="11">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="308" spans="1:25">
+      <c r="A308" s="8">
+        <v>46198</v>
+      </c>
+      <c r="B308" s="8">
+        <v>46198</v>
+      </c>
+      <c r="C308" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D308" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E308" s="11">
+        <v>59.7</v>
+      </c>
+      <c r="F308" s="11">
+        <v>31</v>
+      </c>
+      <c r="G308" s="11">
+        <v>46.732999999999997</v>
+      </c>
+      <c r="H308" s="11">
+        <v>25.2</v>
+      </c>
+      <c r="I308" s="11">
+        <v>22</v>
+      </c>
+      <c r="J308" s="11">
+        <v>23.5</v>
+      </c>
+      <c r="K308" s="11">
+        <v>90</v>
+      </c>
+      <c r="L308" s="11">
+        <v>39</v>
+      </c>
+      <c r="M308" s="11">
+        <v>71.584999999999994</v>
+      </c>
+      <c r="N308" s="11">
+        <v>12.2</v>
+      </c>
+      <c r="O308" s="11">
+        <v>10.3</v>
+      </c>
+      <c r="P308" s="11">
+        <v>11.675000000000001</v>
+      </c>
+      <c r="Q308" s="11">
+        <v>55.5</v>
+      </c>
+      <c r="R308" s="11">
+        <v>19.5</v>
+      </c>
+      <c r="S308" s="11">
+        <v>36</v>
+      </c>
+      <c r="T308" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="U308" s="11">
+        <v>3.8</v>
+      </c>
+      <c r="V308" s="11">
+        <v>4.3209999999999997</v>
+      </c>
+      <c r="W308" s="11">
+        <v>16.5</v>
+      </c>
+      <c r="X308" s="11">
+        <v>7.2</v>
+      </c>
+      <c r="Y308" s="11">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="309" spans="1:25">
+      <c r="A309" s="8">
+        <v>46198</v>
+      </c>
+      <c r="B309" s="8">
+        <v>46198</v>
+      </c>
+      <c r="C309" s="9">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D309" s="10" t="s">
         <v>53</v>
       </c>
     </row>
@@ -41447,7 +41813,7 @@
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
   </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -41477,16 +41843,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" s="5" customFormat="1">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="22" t="s">
         <v>52</v>
       </c>
       <c r="E1" s="6" t="s">
@@ -41566,10 +41932,10 @@
       <c r="AK1" s="12"/>
     </row>
     <row r="2" spans="1:37">
-      <c r="A2" s="19"/>
-      <c r="B2" s="19"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="21"/>
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="22"/>
       <c r="E2" s="6" t="s">
         <v>54</v>
       </c>
@@ -42094,7 +42460,7 @@
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
   </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -42121,16 +42487,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="5" customFormat="1">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="22" t="s">
         <v>52</v>
       </c>
       <c r="E1" s="14" t="s">
@@ -42160,31 +42526,31 @@
       <c r="M1" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="O1" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="P1" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="Q1" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="R1" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="S1" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="T1" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="U1" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="V1" s="19" t="s">
         <v>60</v>
       </c>
       <c r="W1" s="4"/>
@@ -42192,10 +42558,10 @@
       <c r="Y1" s="4"/>
     </row>
     <row r="2" spans="1:25">
-      <c r="A2" s="19"/>
-      <c r="B2" s="19"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="21"/>
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="22"/>
       <c r="E2" s="14" t="s">
         <v>54</v>
       </c>
@@ -43729,7 +44095,7 @@
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
   </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -43751,16 +44117,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="5" customFormat="1">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="22" t="s">
         <v>52</v>
       </c>
       <c r="E1" s="13" t="s">
@@ -43798,10 +44164,10 @@
       <c r="Y1" s="4"/>
     </row>
     <row r="2" spans="1:25">
-      <c r="A2" s="21"/>
-      <c r="B2" s="21"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="21"/>
+      <c r="A2" s="22"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="22"/>
       <c r="E2" s="6" t="s">
         <v>54</v>
       </c>
@@ -45062,7 +45428,7 @@
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
   </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -45073,7 +45439,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
@@ -45360,7 +45726,7 @@
       <c r="C32" s="2"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10118"/>
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data/industry/TrendForce/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9AC9CD6-345F-4752-AE3C-C53DB5FD0211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{755DC687-63DC-6349-B4B5-CF838ABDADD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22160" yWindow="600" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -417,10 +417,10 @@
     </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="백분율" xfId="3" builtinId="5"/>
-    <cellStyle name="쉼표" xfId="2" builtinId="3"/>
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="2" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -438,7 +438,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2338,6 +2338,9 @@
                 <c:pt idx="305">
                   <c:v>46.732999999999997</c:v>
                 </c:pt>
+                <c:pt idx="306">
+                  <c:v>46.732999999999997</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4231,6 +4234,9 @@
                 <c:pt idx="305">
                   <c:v>23.5</c:v>
                 </c:pt>
+                <c:pt idx="306">
+                  <c:v>23.5</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -6124,6 +6130,9 @@
                 <c:pt idx="305">
                   <c:v>71.584999999999994</c:v>
                 </c:pt>
+                <c:pt idx="306">
+                  <c:v>71.584999999999994</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -8017,6 +8026,9 @@
                 <c:pt idx="305">
                   <c:v>11.675000000000001</c:v>
                 </c:pt>
+                <c:pt idx="306">
+                  <c:v>11.675000000000001</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -9908,6 +9920,9 @@
                   <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="305">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="306">
                   <c:v>36</c:v>
                 </c:pt>
               </c:numCache>
@@ -11819,6 +11834,9 @@
                 <c:pt idx="305">
                   <c:v>4.3209999999999997</c:v>
                 </c:pt>
+                <c:pt idx="306">
+                  <c:v>4.3209999999999997</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -13712,6 +13730,9 @@
                   <c:v>11.5</c:v>
                 </c:pt>
                 <c:pt idx="305">
+                  <c:v>11.5</c:v>
+                </c:pt>
+                <c:pt idx="306">
                   <c:v>11.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -13991,7 +14012,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -15012,7 +15033,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -17778,14 +17799,14 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:Z309"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.77734375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.77734375" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.83203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.83203125" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="13" width="9" style="11"/>
-    <col min="14" max="14" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.5" style="11" bestFit="1" customWidth="1"/>
     <col min="15" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -41804,6 +41825,69 @@
       </c>
       <c r="D309" s="10" t="s">
         <v>53</v>
+      </c>
+      <c r="E309" s="11">
+        <v>59.7</v>
+      </c>
+      <c r="F309" s="11">
+        <v>31</v>
+      </c>
+      <c r="G309" s="11">
+        <v>46.732999999999997</v>
+      </c>
+      <c r="H309" s="11">
+        <v>25.2</v>
+      </c>
+      <c r="I309" s="11">
+        <v>22</v>
+      </c>
+      <c r="J309" s="11">
+        <v>23.5</v>
+      </c>
+      <c r="K309" s="11">
+        <v>90</v>
+      </c>
+      <c r="L309" s="11">
+        <v>39</v>
+      </c>
+      <c r="M309" s="11">
+        <v>71.584999999999994</v>
+      </c>
+      <c r="N309" s="11">
+        <v>12.2</v>
+      </c>
+      <c r="O309" s="11">
+        <v>10.3</v>
+      </c>
+      <c r="P309" s="11">
+        <v>11.675000000000001</v>
+      </c>
+      <c r="Q309" s="11">
+        <v>55.5</v>
+      </c>
+      <c r="R309" s="11">
+        <v>19.5</v>
+      </c>
+      <c r="S309" s="11">
+        <v>36</v>
+      </c>
+      <c r="T309" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="U309" s="11">
+        <v>3.8</v>
+      </c>
+      <c r="V309" s="11">
+        <v>4.3209999999999997</v>
+      </c>
+      <c r="W309" s="11">
+        <v>16.5</v>
+      </c>
+      <c r="X309" s="11">
+        <v>7.2</v>
+      </c>
+      <c r="Y309" s="11">
+        <v>11.5</v>
       </c>
     </row>
   </sheetData>
@@ -41823,21 +41907,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:AK8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.77734375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.77734375" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.83203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.83203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.1640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5" style="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.44140625" style="11" customWidth="1"/>
-    <col min="9" max="9" width="9.77734375" style="11" customWidth="1"/>
+    <col min="7" max="7" width="9.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.5" style="11" customWidth="1"/>
+    <col min="9" max="9" width="9.83203125" style="11" customWidth="1"/>
     <col min="10" max="10" width="10.33203125" style="11" customWidth="1"/>
-    <col min="11" max="11" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.5" style="11" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" style="11"/>
-    <col min="13" max="13" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.5" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -42469,17 +42553,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:Y34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="15"/>
-    <col min="7" max="7" width="9.44140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.44140625" style="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5" style="17" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5" style="15" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="15"/>
-    <col min="10" max="10" width="11.77734375" style="17" customWidth="1"/>
+    <col min="10" max="10" width="11.83203125" style="17" customWidth="1"/>
     <col min="11" max="12" width="9" style="15"/>
     <col min="13" max="13" width="13.33203125" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
@@ -44105,13 +44189,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:Y34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1640625" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.5" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -45437,7 +45521,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <sheetData/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -45450,11 +45534,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="22.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.77734375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="22.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.83203125" style="3" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data/industry/TrendForce/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{755DC687-63DC-6349-B4B5-CF838ABDADD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB6FC6F1-8323-42E9-9E16-18F250D2B7B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22160" yWindow="600" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="61">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -417,10 +417,10 @@
     </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Comma" xfId="2" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="백분율" xfId="3" builtinId="5"/>
+    <cellStyle name="쉼표" xfId="2" builtinId="3"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -438,7 +438,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1411,6 +1411,15 @@
                 <c:pt idx="306">
                   <c:v>46198</c:v>
                 </c:pt>
+                <c:pt idx="307">
+                  <c:v>46199</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>46199</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>46199</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2339,6 +2348,9 @@
                   <c:v>46.732999999999997</c:v>
                 </c:pt>
                 <c:pt idx="306">
+                  <c:v>46.732999999999997</c:v>
+                </c:pt>
+                <c:pt idx="307">
                   <c:v>46.732999999999997</c:v>
                 </c:pt>
               </c:numCache>
@@ -3307,6 +3319,15 @@
                 <c:pt idx="306">
                   <c:v>46198</c:v>
                 </c:pt>
+                <c:pt idx="307">
+                  <c:v>46199</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>46199</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>46199</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4235,6 +4256,9 @@
                   <c:v>23.5</c:v>
                 </c:pt>
                 <c:pt idx="306">
+                  <c:v>23.5</c:v>
+                </c:pt>
+                <c:pt idx="307">
                   <c:v>23.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -5203,6 +5227,15 @@
                 <c:pt idx="306">
                   <c:v>46198</c:v>
                 </c:pt>
+                <c:pt idx="307">
+                  <c:v>46199</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>46199</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>46199</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6132,6 +6165,9 @@
                 </c:pt>
                 <c:pt idx="306">
                   <c:v>71.584999999999994</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>72.316999999999993</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7099,6 +7135,15 @@
                 <c:pt idx="306">
                   <c:v>46198</c:v>
                 </c:pt>
+                <c:pt idx="307">
+                  <c:v>46199</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>46199</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>46199</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8027,6 +8072,9 @@
                   <c:v>11.675000000000001</c:v>
                 </c:pt>
                 <c:pt idx="306">
+                  <c:v>11.675000000000001</c:v>
+                </c:pt>
+                <c:pt idx="307">
                   <c:v>11.675000000000001</c:v>
                 </c:pt>
               </c:numCache>
@@ -8995,6 +9043,15 @@
                 <c:pt idx="306">
                   <c:v>46198</c:v>
                 </c:pt>
+                <c:pt idx="307">
+                  <c:v>46199</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>46199</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>46199</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9923,6 +9980,9 @@
                   <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="306">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="307">
                   <c:v>36</c:v>
                 </c:pt>
               </c:numCache>
@@ -10907,6 +10967,15 @@
                 <c:pt idx="306">
                   <c:v>46198</c:v>
                 </c:pt>
+                <c:pt idx="307">
+                  <c:v>46199</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>46199</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>46199</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -11836,6 +11905,9 @@
                 </c:pt>
                 <c:pt idx="306">
                   <c:v>4.3209999999999997</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>4.3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12805,6 +12877,15 @@
                 <c:pt idx="306">
                   <c:v>46198</c:v>
                 </c:pt>
+                <c:pt idx="307">
+                  <c:v>46199</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>46199</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>46199</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13734,6 +13815,9 @@
                 </c:pt>
                 <c:pt idx="306">
                   <c:v>11.5</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>11.571</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14012,7 +14096,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -15033,7 +15117,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -17798,15 +17882,15 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Z309"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <dimension ref="A1:Z312"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.83203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.77734375" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.77734375" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="13" width="9" style="11"/>
-    <col min="14" max="14" width="9.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="15" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -41888,6 +41972,111 @@
       </c>
       <c r="Y309" s="11">
         <v>11.5</v>
+      </c>
+    </row>
+    <row r="310" spans="1:25">
+      <c r="A310" s="8">
+        <v>46199</v>
+      </c>
+      <c r="B310" s="8">
+        <v>46199</v>
+      </c>
+      <c r="C310" s="9">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D310" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E310" s="11">
+        <v>59.7</v>
+      </c>
+      <c r="F310" s="11">
+        <v>31</v>
+      </c>
+      <c r="G310" s="11">
+        <v>46.732999999999997</v>
+      </c>
+      <c r="H310" s="11">
+        <v>25.2</v>
+      </c>
+      <c r="I310" s="11">
+        <v>22</v>
+      </c>
+      <c r="J310" s="11">
+        <v>23.5</v>
+      </c>
+      <c r="K310" s="11">
+        <v>90</v>
+      </c>
+      <c r="L310" s="11">
+        <v>39</v>
+      </c>
+      <c r="M310" s="11">
+        <v>72.316999999999993</v>
+      </c>
+      <c r="N310" s="11">
+        <v>12.2</v>
+      </c>
+      <c r="O310" s="11">
+        <v>10.3</v>
+      </c>
+      <c r="P310" s="11">
+        <v>11.675000000000001</v>
+      </c>
+      <c r="Q310" s="11">
+        <v>55.5</v>
+      </c>
+      <c r="R310" s="11">
+        <v>19.5</v>
+      </c>
+      <c r="S310" s="11">
+        <v>36</v>
+      </c>
+      <c r="T310" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="U310" s="11">
+        <v>3.8</v>
+      </c>
+      <c r="V310" s="11">
+        <v>4.3</v>
+      </c>
+      <c r="W310" s="11">
+        <v>16.5</v>
+      </c>
+      <c r="X310" s="11">
+        <v>7.2</v>
+      </c>
+      <c r="Y310" s="11">
+        <v>11.571</v>
+      </c>
+    </row>
+    <row r="311" spans="1:25">
+      <c r="A311" s="8">
+        <v>46199</v>
+      </c>
+      <c r="B311" s="8">
+        <v>46199</v>
+      </c>
+      <c r="C311" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D311" s="10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="312" spans="1:25">
+      <c r="A312" s="8">
+        <v>46199</v>
+      </c>
+      <c r="B312" s="8">
+        <v>46199</v>
+      </c>
+      <c r="C312" s="9">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D312" s="10" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -41907,21 +42096,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:AK8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.83203125" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.1640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.77734375" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.77734375" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="9.5" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.5" style="11" customWidth="1"/>
-    <col min="9" max="9" width="9.83203125" style="11" customWidth="1"/>
+    <col min="7" max="7" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.44140625" style="11" customWidth="1"/>
+    <col min="9" max="9" width="9.77734375" style="11" customWidth="1"/>
     <col min="10" max="10" width="10.33203125" style="11" customWidth="1"/>
-    <col min="11" max="11" width="9.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" style="11"/>
-    <col min="13" max="13" width="9.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -42553,17 +42742,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:Y34"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.1640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="15"/>
-    <col min="7" max="7" width="9.5" style="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5" style="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.44140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.44140625" style="15" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="15"/>
-    <col min="10" max="10" width="11.83203125" style="17" customWidth="1"/>
+    <col min="10" max="10" width="11.77734375" style="17" customWidth="1"/>
     <col min="11" max="12" width="9" style="15"/>
     <col min="13" max="13" width="13.33203125" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
@@ -44189,13 +44378,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:Y34"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -45521,7 +45710,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -45534,11 +45723,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:D32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="22.83203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.83203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.83203125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="22.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.77734375" style="3" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB6FC6F1-8323-42E9-9E16-18F250D2B7B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{271D43FC-BC3A-4F67-8139-1E76DEBE0897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -417,10 +417,10 @@
     </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="백분율" xfId="3" builtinId="5"/>
-    <cellStyle name="쉼표" xfId="2" builtinId="3"/>
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="2" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -438,7 +438,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2353,6 +2353,12 @@
                 <c:pt idx="307">
                   <c:v>46.732999999999997</c:v>
                 </c:pt>
+                <c:pt idx="308">
+                  <c:v>46.732999999999997</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>46.732999999999997</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4261,6 +4267,12 @@
                 <c:pt idx="307">
                   <c:v>23.5</c:v>
                 </c:pt>
+                <c:pt idx="308">
+                  <c:v>23.5</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>23.5</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -6169,6 +6181,12 @@
                 <c:pt idx="307">
                   <c:v>72.316999999999993</c:v>
                 </c:pt>
+                <c:pt idx="308">
+                  <c:v>72.316999999999993</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>72.316999999999993</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -8077,6 +8095,12 @@
                 <c:pt idx="307">
                   <c:v>11.675000000000001</c:v>
                 </c:pt>
+                <c:pt idx="308">
+                  <c:v>11.675000000000001</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>11.675000000000001</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -9983,6 +10007,12 @@
                   <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="307">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="309">
                   <c:v>36</c:v>
                 </c:pt>
               </c:numCache>
@@ -11909,6 +11939,12 @@
                 <c:pt idx="307">
                   <c:v>4.3</c:v>
                 </c:pt>
+                <c:pt idx="308">
+                  <c:v>4.3</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>4.3</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -13817,6 +13853,12 @@
                   <c:v>11.5</c:v>
                 </c:pt>
                 <c:pt idx="307">
+                  <c:v>11.571</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>11.571</c:v>
+                </c:pt>
+                <c:pt idx="309">
                   <c:v>11.571</c:v>
                 </c:pt>
               </c:numCache>
@@ -14096,7 +14138,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -15117,7 +15159,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -17883,14 +17925,14 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:Z312"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="10.77734375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.77734375" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.81640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.08984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="13" width="9" style="11"/>
-    <col min="14" max="14" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.453125" style="11" bestFit="1" customWidth="1"/>
     <col min="15" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -42064,6 +42106,69 @@
       <c r="D311" s="10" t="s">
         <v>53</v>
       </c>
+      <c r="E311" s="11">
+        <v>59.7</v>
+      </c>
+      <c r="F311" s="11">
+        <v>31</v>
+      </c>
+      <c r="G311" s="11">
+        <v>46.732999999999997</v>
+      </c>
+      <c r="H311" s="11">
+        <v>25.2</v>
+      </c>
+      <c r="I311" s="11">
+        <v>22</v>
+      </c>
+      <c r="J311" s="11">
+        <v>23.5</v>
+      </c>
+      <c r="K311" s="11">
+        <v>90</v>
+      </c>
+      <c r="L311" s="11">
+        <v>39</v>
+      </c>
+      <c r="M311" s="11">
+        <v>72.316999999999993</v>
+      </c>
+      <c r="N311" s="11">
+        <v>12.2</v>
+      </c>
+      <c r="O311" s="11">
+        <v>10.3</v>
+      </c>
+      <c r="P311" s="11">
+        <v>11.675000000000001</v>
+      </c>
+      <c r="Q311" s="11">
+        <v>55.5</v>
+      </c>
+      <c r="R311" s="11">
+        <v>19.5</v>
+      </c>
+      <c r="S311" s="11">
+        <v>36</v>
+      </c>
+      <c r="T311" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="U311" s="11">
+        <v>3.8</v>
+      </c>
+      <c r="V311" s="11">
+        <v>4.3</v>
+      </c>
+      <c r="W311" s="11">
+        <v>16.5</v>
+      </c>
+      <c r="X311" s="11">
+        <v>7.2</v>
+      </c>
+      <c r="Y311" s="11">
+        <v>11.571</v>
+      </c>
     </row>
     <row r="312" spans="1:25">
       <c r="A312" s="8">
@@ -42077,6 +42182,69 @@
       </c>
       <c r="D312" s="10" t="s">
         <v>53</v>
+      </c>
+      <c r="E312" s="11">
+        <v>59.7</v>
+      </c>
+      <c r="F312" s="11">
+        <v>31</v>
+      </c>
+      <c r="G312" s="11">
+        <v>46.732999999999997</v>
+      </c>
+      <c r="H312" s="11">
+        <v>25.2</v>
+      </c>
+      <c r="I312" s="11">
+        <v>22</v>
+      </c>
+      <c r="J312" s="11">
+        <v>23.5</v>
+      </c>
+      <c r="K312" s="11">
+        <v>90</v>
+      </c>
+      <c r="L312" s="11">
+        <v>39</v>
+      </c>
+      <c r="M312" s="11">
+        <v>72.316999999999993</v>
+      </c>
+      <c r="N312" s="11">
+        <v>12.2</v>
+      </c>
+      <c r="O312" s="11">
+        <v>10.3</v>
+      </c>
+      <c r="P312" s="11">
+        <v>11.675000000000001</v>
+      </c>
+      <c r="Q312" s="11">
+        <v>55.5</v>
+      </c>
+      <c r="R312" s="11">
+        <v>19.5</v>
+      </c>
+      <c r="S312" s="11">
+        <v>36</v>
+      </c>
+      <c r="T312" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="U312" s="11">
+        <v>3.8</v>
+      </c>
+      <c r="V312" s="11">
+        <v>4.3</v>
+      </c>
+      <c r="W312" s="11">
+        <v>16.5</v>
+      </c>
+      <c r="X312" s="11">
+        <v>7.2</v>
+      </c>
+      <c r="Y312" s="11">
+        <v>11.571</v>
       </c>
     </row>
   </sheetData>
@@ -42096,21 +42264,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:AK8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="10.77734375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.77734375" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.81640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.08984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.08984375" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.453125" style="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.44140625" style="11" customWidth="1"/>
-    <col min="9" max="9" width="9.77734375" style="11" customWidth="1"/>
-    <col min="10" max="10" width="10.33203125" style="11" customWidth="1"/>
-    <col min="11" max="11" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.453125" style="11" customWidth="1"/>
+    <col min="9" max="9" width="9.81640625" style="11" customWidth="1"/>
+    <col min="10" max="10" width="10.36328125" style="11" customWidth="1"/>
+    <col min="11" max="11" width="9.453125" style="11" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" style="11"/>
-    <col min="13" max="13" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.453125" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -42742,19 +42910,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:Y34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="10.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.08984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.08984375" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="15"/>
-    <col min="7" max="7" width="9.44140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.44140625" style="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.453125" style="17" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.453125" style="15" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="15"/>
-    <col min="10" max="10" width="11.77734375" style="17" customWidth="1"/>
+    <col min="10" max="10" width="11.81640625" style="17" customWidth="1"/>
     <col min="11" max="12" width="9" style="15"/>
-    <col min="13" max="13" width="13.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.36328125" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -44378,13 +44546,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:Y34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.36328125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.08984375" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.08984375" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.453125" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -45710,7 +45878,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <sheetData/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -45723,11 +45891,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="22.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.77734375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="22.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.81640625" style="3" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{271D43FC-BC3A-4F67-8139-1E76DEBE0897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8876DAC5-F82B-4BD2-88B9-56ABD397D8A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="61">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -406,21 +406,21 @@
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Comma" xfId="2" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="백분율" xfId="3" builtinId="5"/>
+    <cellStyle name="쉼표" xfId="2" builtinId="3"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -438,7 +438,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1420,6 +1420,15 @@
                 <c:pt idx="309">
                   <c:v>46199</c:v>
                 </c:pt>
+                <c:pt idx="310">
+                  <c:v>46202</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>46202</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>46202</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2357,6 +2366,12 @@
                   <c:v>46.732999999999997</c:v>
                 </c:pt>
                 <c:pt idx="309">
+                  <c:v>46.732999999999997</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>46.732999999999997</c:v>
+                </c:pt>
+                <c:pt idx="311">
                   <c:v>46.732999999999997</c:v>
                 </c:pt>
               </c:numCache>
@@ -3334,6 +3349,15 @@
                 <c:pt idx="309">
                   <c:v>46199</c:v>
                 </c:pt>
+                <c:pt idx="310">
+                  <c:v>46202</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>46202</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>46202</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4271,6 +4295,12 @@
                   <c:v>23.5</c:v>
                 </c:pt>
                 <c:pt idx="309">
+                  <c:v>23.5</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>23.5</c:v>
+                </c:pt>
+                <c:pt idx="311">
                   <c:v>23.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -5248,6 +5278,15 @@
                 <c:pt idx="309">
                   <c:v>46199</c:v>
                 </c:pt>
+                <c:pt idx="310">
+                  <c:v>46202</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>46202</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>46202</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6186,6 +6225,12 @@
                 </c:pt>
                 <c:pt idx="309">
                   <c:v>72.316999999999993</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>72.988</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>72.988</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7162,6 +7207,15 @@
                 <c:pt idx="309">
                   <c:v>46199</c:v>
                 </c:pt>
+                <c:pt idx="310">
+                  <c:v>46202</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>46202</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>46202</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8100,6 +8154,12 @@
                 </c:pt>
                 <c:pt idx="309">
                   <c:v>11.675000000000001</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>11.65</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>11.65</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9076,6 +9136,15 @@
                 <c:pt idx="309">
                   <c:v>46199</c:v>
                 </c:pt>
+                <c:pt idx="310">
+                  <c:v>46202</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>46202</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>46202</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10013,6 +10082,12 @@
                   <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="309">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="311">
                   <c:v>36</c:v>
                 </c:pt>
               </c:numCache>
@@ -11006,6 +11081,15 @@
                 <c:pt idx="309">
                   <c:v>46199</c:v>
                 </c:pt>
+                <c:pt idx="310">
+                  <c:v>46202</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>46202</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>46202</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -11944,6 +12028,12 @@
                 </c:pt>
                 <c:pt idx="309">
                   <c:v>4.3</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>4.2789999999999999</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>4.2789999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12922,6 +13012,15 @@
                 <c:pt idx="309">
                   <c:v>46199</c:v>
                 </c:pt>
+                <c:pt idx="310">
+                  <c:v>46202</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>46202</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>46202</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13860,6 +13959,12 @@
                 </c:pt>
                 <c:pt idx="309">
                   <c:v>11.571</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>11.714</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>11.762</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14138,7 +14243,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -14286,6 +14391,9 @@
                 <c:pt idx="31">
                   <c:v>46195</c:v>
                 </c:pt>
+                <c:pt idx="32">
+                  <c:v>46202</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -14384,6 +14492,9 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>209</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>208.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14526,6 +14637,9 @@
                 <c:pt idx="31">
                   <c:v>46195</c:v>
                 </c:pt>
+                <c:pt idx="32">
+                  <c:v>46202</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -14624,6 +14738,9 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>149.92400000000001</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>149.57599999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14782,6 +14899,9 @@
                 <c:pt idx="31">
                   <c:v>46195</c:v>
                 </c:pt>
+                <c:pt idx="32">
+                  <c:v>46202</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -14880,6 +15000,9 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>1275</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1335</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15159,7 +15282,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -15307,6 +15430,9 @@
                 <c:pt idx="31">
                   <c:v>46195</c:v>
                 </c:pt>
+                <c:pt idx="32">
+                  <c:v>46202</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -15410,6 +15536,9 @@
                   <c:v>11.545</c:v>
                 </c:pt>
                 <c:pt idx="31">
+                  <c:v>11.545</c:v>
+                </c:pt>
+                <c:pt idx="32">
                   <c:v>11.545</c:v>
                 </c:pt>
               </c:numCache>
@@ -15553,6 +15682,9 @@
                 <c:pt idx="31">
                   <c:v>46195</c:v>
                 </c:pt>
+                <c:pt idx="32">
+                  <c:v>46202</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -15656,6 +15788,9 @@
                   <c:v>11.522</c:v>
                 </c:pt>
                 <c:pt idx="31">
+                  <c:v>11.522</c:v>
+                </c:pt>
+                <c:pt idx="32">
                   <c:v>11.522</c:v>
                 </c:pt>
               </c:numCache>
@@ -17924,30 +18059,30 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Z312"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <dimension ref="A1:Z315"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.81640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.08984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.81640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.77734375" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.77734375" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="13" width="9" style="11"/>
-    <col min="14" max="14" width="9.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="15" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" s="5" customFormat="1">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="22" t="s">
         <v>50</v>
       </c>
       <c r="C1" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="20" t="s">
         <v>52</v>
       </c>
       <c r="E1" s="4" t="s">
@@ -18015,10 +18150,10 @@
       </c>
     </row>
     <row r="2" spans="1:26">
-      <c r="A2" s="20"/>
-      <c r="B2" s="20"/>
+      <c r="A2" s="22"/>
+      <c r="B2" s="22"/>
       <c r="C2" s="21"/>
-      <c r="D2" s="22"/>
+      <c r="D2" s="20"/>
       <c r="E2" s="6" t="s">
         <v>54</v>
       </c>
@@ -42245,6 +42380,174 @@
       </c>
       <c r="Y312" s="11">
         <v>11.571</v>
+      </c>
+    </row>
+    <row r="313" spans="1:25">
+      <c r="A313" s="8">
+        <v>46202</v>
+      </c>
+      <c r="B313" s="8">
+        <v>46202</v>
+      </c>
+      <c r="C313" s="9">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D313" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E313" s="11">
+        <v>59.8</v>
+      </c>
+      <c r="F313" s="11">
+        <v>31.5</v>
+      </c>
+      <c r="G313" s="11">
+        <v>46.732999999999997</v>
+      </c>
+      <c r="H313" s="11">
+        <v>25.3</v>
+      </c>
+      <c r="I313" s="11">
+        <v>22.1</v>
+      </c>
+      <c r="J313" s="11">
+        <v>23.5</v>
+      </c>
+      <c r="K313" s="11">
+        <v>92</v>
+      </c>
+      <c r="L313" s="11">
+        <v>39.1</v>
+      </c>
+      <c r="M313" s="11">
+        <v>72.988</v>
+      </c>
+      <c r="N313" s="11">
+        <v>12</v>
+      </c>
+      <c r="O313" s="11">
+        <v>10.5</v>
+      </c>
+      <c r="P313" s="11">
+        <v>11.65</v>
+      </c>
+      <c r="Q313" s="11">
+        <v>56</v>
+      </c>
+      <c r="R313" s="11">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="S313" s="11">
+        <v>36</v>
+      </c>
+      <c r="T313" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="U313" s="11">
+        <v>3.85</v>
+      </c>
+      <c r="V313" s="11">
+        <v>4.2789999999999999</v>
+      </c>
+      <c r="W313" s="11">
+        <v>16.5</v>
+      </c>
+      <c r="X313" s="11">
+        <v>7.5</v>
+      </c>
+      <c r="Y313" s="11">
+        <v>11.714</v>
+      </c>
+    </row>
+    <row r="314" spans="1:25">
+      <c r="A314" s="8">
+        <v>46202</v>
+      </c>
+      <c r="B314" s="8">
+        <v>46202</v>
+      </c>
+      <c r="C314" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D314" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E314" s="11">
+        <v>59.8</v>
+      </c>
+      <c r="F314" s="11">
+        <v>31.5</v>
+      </c>
+      <c r="G314" s="11">
+        <v>46.732999999999997</v>
+      </c>
+      <c r="H314" s="11">
+        <v>25.3</v>
+      </c>
+      <c r="I314" s="11">
+        <v>22.1</v>
+      </c>
+      <c r="J314" s="11">
+        <v>23.5</v>
+      </c>
+      <c r="K314" s="11">
+        <v>92</v>
+      </c>
+      <c r="L314" s="11">
+        <v>39.1</v>
+      </c>
+      <c r="M314" s="11">
+        <v>72.988</v>
+      </c>
+      <c r="N314" s="11">
+        <v>12</v>
+      </c>
+      <c r="O314" s="11">
+        <v>10.5</v>
+      </c>
+      <c r="P314" s="11">
+        <v>11.65</v>
+      </c>
+      <c r="Q314" s="11">
+        <v>56</v>
+      </c>
+      <c r="R314" s="11">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="S314" s="11">
+        <v>36</v>
+      </c>
+      <c r="T314" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="U314" s="11">
+        <v>3.85</v>
+      </c>
+      <c r="V314" s="11">
+        <v>4.2789999999999999</v>
+      </c>
+      <c r="W314" s="11">
+        <v>16.5</v>
+      </c>
+      <c r="X314" s="11">
+        <v>7.5</v>
+      </c>
+      <c r="Y314" s="11">
+        <v>11.762</v>
+      </c>
+    </row>
+    <row r="315" spans="1:25">
+      <c r="A315" s="8">
+        <v>46202</v>
+      </c>
+      <c r="B315" s="8">
+        <v>46202</v>
+      </c>
+      <c r="C315" s="9">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D315" s="10" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -42264,36 +42567,36 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:AK8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.81640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.08984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.81640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.08984375" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.77734375" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.77734375" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="9.453125" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.453125" style="11" customWidth="1"/>
-    <col min="9" max="9" width="9.81640625" style="11" customWidth="1"/>
-    <col min="10" max="10" width="10.36328125" style="11" customWidth="1"/>
-    <col min="11" max="11" width="9.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.44140625" style="11" customWidth="1"/>
+    <col min="9" max="9" width="9.77734375" style="11" customWidth="1"/>
+    <col min="10" max="10" width="10.33203125" style="11" customWidth="1"/>
+    <col min="11" max="11" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" style="11"/>
-    <col min="13" max="13" width="9.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" s="5" customFormat="1">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="22" t="s">
         <v>50</v>
       </c>
       <c r="C1" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="20" t="s">
         <v>52</v>
       </c>
       <c r="E1" s="6" t="s">
@@ -42373,10 +42676,10 @@
       <c r="AK1" s="12"/>
     </row>
     <row r="2" spans="1:37">
-      <c r="A2" s="20"/>
-      <c r="B2" s="20"/>
+      <c r="A2" s="22"/>
+      <c r="B2" s="22"/>
       <c r="C2" s="21"/>
-      <c r="D2" s="22"/>
+      <c r="D2" s="20"/>
       <c r="E2" s="6" t="s">
         <v>54</v>
       </c>
@@ -42909,35 +43212,35 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:Y34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <dimension ref="A1:Y35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.08984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.08984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="15"/>
-    <col min="7" max="7" width="9.453125" style="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.453125" style="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.44140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.44140625" style="15" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="15"/>
-    <col min="10" max="10" width="11.81640625" style="17" customWidth="1"/>
+    <col min="10" max="10" width="11.77734375" style="17" customWidth="1"/>
     <col min="11" max="12" width="9" style="15"/>
-    <col min="13" max="13" width="13.36328125" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.33203125" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="5" customFormat="1">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="22" t="s">
         <v>50</v>
       </c>
       <c r="C1" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="20" t="s">
         <v>52</v>
       </c>
       <c r="E1" s="14" t="s">
@@ -42999,10 +43302,10 @@
       <c r="Y1" s="4"/>
     </row>
     <row r="2" spans="1:25">
-      <c r="A2" s="20"/>
-      <c r="B2" s="20"/>
+      <c r="A2" s="22"/>
+      <c r="B2" s="22"/>
       <c r="C2" s="21"/>
-      <c r="D2" s="22"/>
+      <c r="D2" s="20"/>
       <c r="E2" s="14" t="s">
         <v>54</v>
       </c>
@@ -44527,6 +44830,47 @@
       </c>
       <c r="M34" s="11">
         <v>149.92400000000001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
+      <c r="A35" s="8">
+        <v>46195</v>
+      </c>
+      <c r="B35" s="8">
+        <v>46202</v>
+      </c>
+      <c r="C35" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="E35" s="15">
+        <v>215</v>
+      </c>
+      <c r="F35" s="15">
+        <v>200</v>
+      </c>
+      <c r="G35" s="17">
+        <v>208.5</v>
+      </c>
+      <c r="H35" s="15">
+        <v>1600</v>
+      </c>
+      <c r="I35" s="15">
+        <v>1250</v>
+      </c>
+      <c r="J35" s="17">
+        <v>1335</v>
+      </c>
+      <c r="K35" s="15">
+        <v>170</v>
+      </c>
+      <c r="L35" s="15">
+        <v>133</v>
+      </c>
+      <c r="M35" s="11">
+        <v>149.57599999999999</v>
       </c>
     </row>
   </sheetData>
@@ -44545,29 +44889,29 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:Y34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <dimension ref="A1:Y35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.36328125" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.08984375" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.08984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="5" customFormat="1">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="B1" s="20" t="s">
         <v>50</v>
       </c>
       <c r="C1" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="20" t="s">
         <v>52</v>
       </c>
       <c r="E1" s="13" t="s">
@@ -44605,10 +44949,10 @@
       <c r="Y1" s="4"/>
     </row>
     <row r="2" spans="1:25">
-      <c r="A2" s="22"/>
-      <c r="B2" s="22"/>
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
       <c r="C2" s="21"/>
-      <c r="D2" s="22"/>
+      <c r="D2" s="20"/>
       <c r="E2" s="6" t="s">
         <v>54</v>
       </c>
@@ -45862,6 +46206,38 @@
         <v>11.522</v>
       </c>
     </row>
+    <row r="35" spans="1:10">
+      <c r="A35" s="8">
+        <v>46195</v>
+      </c>
+      <c r="B35" s="8">
+        <v>46202</v>
+      </c>
+      <c r="C35" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="E35" s="11">
+        <v>17.5</v>
+      </c>
+      <c r="F35" s="11">
+        <v>9.5</v>
+      </c>
+      <c r="G35" s="11">
+        <v>11.545</v>
+      </c>
+      <c r="H35" s="11">
+        <v>17.5</v>
+      </c>
+      <c r="I35" s="11">
+        <v>9</v>
+      </c>
+      <c r="J35" s="11">
+        <v>11.522</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:A2"/>
@@ -45878,7 +46254,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -45891,11 +46267,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="22.81640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.81640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.81640625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="22.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.77734375" style="3" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8876DAC5-F82B-4BD2-88B9-56ABD397D8A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C513667-4B3F-437A-A787-C345F3F6284E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -406,21 +406,21 @@
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="백분율" xfId="3" builtinId="5"/>
-    <cellStyle name="쉼표" xfId="2" builtinId="3"/>
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="2" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -438,7 +438,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2374,6 +2374,9 @@
                 <c:pt idx="311">
                   <c:v>46.732999999999997</c:v>
                 </c:pt>
+                <c:pt idx="312">
+                  <c:v>46.732999999999997</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4303,6 +4306,9 @@
                 <c:pt idx="311">
                   <c:v>23.5</c:v>
                 </c:pt>
+                <c:pt idx="312">
+                  <c:v>23.5</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -6232,6 +6238,9 @@
                 <c:pt idx="311">
                   <c:v>72.988</c:v>
                 </c:pt>
+                <c:pt idx="312">
+                  <c:v>72.988</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -8161,6 +8170,9 @@
                 <c:pt idx="311">
                   <c:v>11.65</c:v>
                 </c:pt>
+                <c:pt idx="312">
+                  <c:v>11.65</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -10088,6 +10100,9 @@
                   <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="311">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="312">
                   <c:v>36</c:v>
                 </c:pt>
               </c:numCache>
@@ -12035,6 +12050,9 @@
                 <c:pt idx="311">
                   <c:v>4.2789999999999999</c:v>
                 </c:pt>
+                <c:pt idx="312">
+                  <c:v>4.2789999999999999</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -13964,6 +13982,9 @@
                   <c:v>11.714</c:v>
                 </c:pt>
                 <c:pt idx="311">
+                  <c:v>11.762</c:v>
+                </c:pt>
+                <c:pt idx="312">
                   <c:v>11.762</c:v>
                 </c:pt>
               </c:numCache>
@@ -14243,7 +14264,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -15282,7 +15303,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -18060,29 +18081,29 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:Z315"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="10.77734375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.77734375" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.81640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.08984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="13" width="9" style="11"/>
-    <col min="14" max="14" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.453125" style="11" bestFit="1" customWidth="1"/>
     <col min="15" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" s="5" customFormat="1">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="B1" s="20" t="s">
         <v>50</v>
       </c>
       <c r="C1" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="22" t="s">
         <v>52</v>
       </c>
       <c r="E1" s="4" t="s">
@@ -18150,10 +18171,10 @@
       </c>
     </row>
     <row r="2" spans="1:26">
-      <c r="A2" s="22"/>
-      <c r="B2" s="22"/>
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
       <c r="C2" s="21"/>
-      <c r="D2" s="20"/>
+      <c r="D2" s="22"/>
       <c r="E2" s="6" t="s">
         <v>54</v>
       </c>
@@ -42548,6 +42569,69 @@
       </c>
       <c r="D315" s="10" t="s">
         <v>53</v>
+      </c>
+      <c r="E315" s="11">
+        <v>59.8</v>
+      </c>
+      <c r="F315" s="11">
+        <v>31.5</v>
+      </c>
+      <c r="G315" s="11">
+        <v>46.732999999999997</v>
+      </c>
+      <c r="H315" s="11">
+        <v>25.3</v>
+      </c>
+      <c r="I315" s="11">
+        <v>22.1</v>
+      </c>
+      <c r="J315" s="11">
+        <v>23.5</v>
+      </c>
+      <c r="K315" s="11">
+        <v>92</v>
+      </c>
+      <c r="L315" s="11">
+        <v>39.1</v>
+      </c>
+      <c r="M315" s="11">
+        <v>72.988</v>
+      </c>
+      <c r="N315" s="11">
+        <v>12</v>
+      </c>
+      <c r="O315" s="11">
+        <v>10.5</v>
+      </c>
+      <c r="P315" s="11">
+        <v>11.65</v>
+      </c>
+      <c r="Q315" s="11">
+        <v>56</v>
+      </c>
+      <c r="R315" s="11">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="S315" s="11">
+        <v>36</v>
+      </c>
+      <c r="T315" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="U315" s="11">
+        <v>3.85</v>
+      </c>
+      <c r="V315" s="11">
+        <v>4.2789999999999999</v>
+      </c>
+      <c r="W315" s="11">
+        <v>16.5</v>
+      </c>
+      <c r="X315" s="11">
+        <v>7.5</v>
+      </c>
+      <c r="Y315" s="11">
+        <v>11.762</v>
       </c>
     </row>
   </sheetData>
@@ -42567,36 +42651,36 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:AK8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="10.77734375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.77734375" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.81640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.08984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.08984375" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.453125" style="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.44140625" style="11" customWidth="1"/>
-    <col min="9" max="9" width="9.77734375" style="11" customWidth="1"/>
-    <col min="10" max="10" width="10.33203125" style="11" customWidth="1"/>
-    <col min="11" max="11" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.453125" style="11" customWidth="1"/>
+    <col min="9" max="9" width="9.81640625" style="11" customWidth="1"/>
+    <col min="10" max="10" width="10.36328125" style="11" customWidth="1"/>
+    <col min="11" max="11" width="9.453125" style="11" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" style="11"/>
-    <col min="13" max="13" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.453125" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" s="5" customFormat="1">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="B1" s="20" t="s">
         <v>50</v>
       </c>
       <c r="C1" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="22" t="s">
         <v>52</v>
       </c>
       <c r="E1" s="6" t="s">
@@ -42676,10 +42760,10 @@
       <c r="AK1" s="12"/>
     </row>
     <row r="2" spans="1:37">
-      <c r="A2" s="22"/>
-      <c r="B2" s="22"/>
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
       <c r="C2" s="21"/>
-      <c r="D2" s="20"/>
+      <c r="D2" s="22"/>
       <c r="E2" s="6" t="s">
         <v>54</v>
       </c>
@@ -43213,34 +43297,34 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:Y35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="10.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.08984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.08984375" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="15"/>
-    <col min="7" max="7" width="9.44140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.44140625" style="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.453125" style="17" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.453125" style="15" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="15"/>
-    <col min="10" max="10" width="11.77734375" style="17" customWidth="1"/>
+    <col min="10" max="10" width="11.81640625" style="17" customWidth="1"/>
     <col min="11" max="12" width="9" style="15"/>
-    <col min="13" max="13" width="13.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.36328125" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="5" customFormat="1">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="B1" s="20" t="s">
         <v>50</v>
       </c>
       <c r="C1" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="22" t="s">
         <v>52</v>
       </c>
       <c r="E1" s="14" t="s">
@@ -43302,10 +43386,10 @@
       <c r="Y1" s="4"/>
     </row>
     <row r="2" spans="1:25">
-      <c r="A2" s="22"/>
-      <c r="B2" s="22"/>
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
       <c r="C2" s="21"/>
-      <c r="D2" s="20"/>
+      <c r="D2" s="22"/>
       <c r="E2" s="14" t="s">
         <v>54</v>
       </c>
@@ -44890,28 +44974,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:Y35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.36328125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.08984375" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.08984375" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.453125" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="5" customFormat="1">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="22" t="s">
         <v>50</v>
       </c>
       <c r="C1" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="22" t="s">
         <v>52</v>
       </c>
       <c r="E1" s="13" t="s">
@@ -44949,10 +45033,10 @@
       <c r="Y1" s="4"/>
     </row>
     <row r="2" spans="1:25">
-      <c r="A2" s="20"/>
-      <c r="B2" s="20"/>
+      <c r="A2" s="22"/>
+      <c r="B2" s="22"/>
       <c r="C2" s="21"/>
-      <c r="D2" s="20"/>
+      <c r="D2" s="22"/>
       <c r="E2" s="6" t="s">
         <v>54</v>
       </c>
@@ -46254,7 +46338,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <sheetData/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -46267,11 +46351,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="22.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.77734375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="22.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.81640625" style="3" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C513667-4B3F-437A-A787-C345F3F6284E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{119CCF0D-13A1-4E10-8DE7-9CD3626547C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="61">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -417,10 +417,10 @@
     </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Comma" xfId="2" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="백분율" xfId="3" builtinId="5"/>
+    <cellStyle name="쉼표" xfId="2" builtinId="3"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -438,7 +438,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1429,6 +1429,15 @@
                 <c:pt idx="312">
                   <c:v>46202</c:v>
                 </c:pt>
+                <c:pt idx="313">
+                  <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>46203</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2376,6 +2385,12 @@
                 </c:pt>
                 <c:pt idx="312">
                   <c:v>46.732999999999997</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>46.832999999999998</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>46.832999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3361,6 +3376,15 @@
                 <c:pt idx="312">
                   <c:v>46202</c:v>
                 </c:pt>
+                <c:pt idx="313">
+                  <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>46203</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4307,6 +4331,12 @@
                   <c:v>23.5</c:v>
                 </c:pt>
                 <c:pt idx="312">
+                  <c:v>23.5</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>23.5</c:v>
+                </c:pt>
+                <c:pt idx="314">
                   <c:v>23.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -5293,6 +5323,15 @@
                 <c:pt idx="312">
                   <c:v>46202</c:v>
                 </c:pt>
+                <c:pt idx="313">
+                  <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>46203</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6240,6 +6279,12 @@
                 </c:pt>
                 <c:pt idx="312">
                   <c:v>72.988</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>73.744</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>73.744</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7225,6 +7270,15 @@
                 <c:pt idx="312">
                   <c:v>46202</c:v>
                 </c:pt>
+                <c:pt idx="313">
+                  <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>46203</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8171,6 +8225,12 @@
                   <c:v>11.65</c:v>
                 </c:pt>
                 <c:pt idx="312">
+                  <c:v>11.65</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>11.65</c:v>
+                </c:pt>
+                <c:pt idx="314">
                   <c:v>11.65</c:v>
                 </c:pt>
               </c:numCache>
@@ -9157,6 +9217,15 @@
                 <c:pt idx="312">
                   <c:v>46202</c:v>
                 </c:pt>
+                <c:pt idx="313">
+                  <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>46203</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10103,6 +10172,12 @@
                   <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="312">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="314">
                   <c:v>36</c:v>
                 </c:pt>
               </c:numCache>
@@ -11105,6 +11180,15 @@
                 <c:pt idx="312">
                   <c:v>46202</c:v>
                 </c:pt>
+                <c:pt idx="313">
+                  <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>46203</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -12052,6 +12136,12 @@
                 </c:pt>
                 <c:pt idx="312">
                   <c:v>4.2789999999999999</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>4.2569999999999997</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>4.2569999999999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13039,6 +13129,15 @@
                 <c:pt idx="312">
                   <c:v>46202</c:v>
                 </c:pt>
+                <c:pt idx="313">
+                  <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>46203</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13986,6 +14085,12 @@
                 </c:pt>
                 <c:pt idx="312">
                   <c:v>11.762</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>11.952</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>12.038</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14123,7 +14228,7 @@
         <c:axId val="1583758912"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="12"/>
+          <c:max val="13"/>
           <c:min val="4"/>
         </c:scaling>
         <c:delete val="0"/>
@@ -14264,7 +14369,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -15303,7 +15408,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -18080,15 +18185,15 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Z315"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <dimension ref="A1:Z318"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.81640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.08984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.81640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.77734375" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.77734375" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="13" width="9" style="11"/>
-    <col min="14" max="14" width="9.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="15" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -42632,6 +42737,174 @@
       </c>
       <c r="Y315" s="11">
         <v>11.762</v>
+      </c>
+    </row>
+    <row r="316" spans="1:25">
+      <c r="A316" s="8">
+        <v>46203</v>
+      </c>
+      <c r="B316" s="8">
+        <v>46203</v>
+      </c>
+      <c r="C316" s="9">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D316" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E316" s="11">
+        <v>61</v>
+      </c>
+      <c r="F316" s="11">
+        <v>31.5</v>
+      </c>
+      <c r="G316" s="11">
+        <v>46.832999999999998</v>
+      </c>
+      <c r="H316" s="11">
+        <v>25.3</v>
+      </c>
+      <c r="I316" s="11">
+        <v>22.1</v>
+      </c>
+      <c r="J316" s="11">
+        <v>23.5</v>
+      </c>
+      <c r="K316" s="11">
+        <v>92</v>
+      </c>
+      <c r="L316" s="11">
+        <v>39.1</v>
+      </c>
+      <c r="M316" s="11">
+        <v>73.744</v>
+      </c>
+      <c r="N316" s="11">
+        <v>12</v>
+      </c>
+      <c r="O316" s="11">
+        <v>10.5</v>
+      </c>
+      <c r="P316" s="11">
+        <v>11.65</v>
+      </c>
+      <c r="Q316" s="11">
+        <v>56</v>
+      </c>
+      <c r="R316" s="11">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="S316" s="11">
+        <v>36</v>
+      </c>
+      <c r="T316" s="11">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="U316" s="11">
+        <v>3.8</v>
+      </c>
+      <c r="V316" s="11">
+        <v>4.2569999999999997</v>
+      </c>
+      <c r="W316" s="11">
+        <v>16.5</v>
+      </c>
+      <c r="X316" s="11">
+        <v>7.7</v>
+      </c>
+      <c r="Y316" s="11">
+        <v>11.952</v>
+      </c>
+    </row>
+    <row r="317" spans="1:25">
+      <c r="A317" s="8">
+        <v>46203</v>
+      </c>
+      <c r="B317" s="8">
+        <v>46203</v>
+      </c>
+      <c r="C317" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D317" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E317" s="11">
+        <v>61</v>
+      </c>
+      <c r="F317" s="11">
+        <v>31.5</v>
+      </c>
+      <c r="G317" s="11">
+        <v>46.832999999999998</v>
+      </c>
+      <c r="H317" s="11">
+        <v>25.3</v>
+      </c>
+      <c r="I317" s="11">
+        <v>22.1</v>
+      </c>
+      <c r="J317" s="11">
+        <v>23.5</v>
+      </c>
+      <c r="K317" s="11">
+        <v>92</v>
+      </c>
+      <c r="L317" s="11">
+        <v>39.1</v>
+      </c>
+      <c r="M317" s="11">
+        <v>73.744</v>
+      </c>
+      <c r="N317" s="11">
+        <v>12</v>
+      </c>
+      <c r="O317" s="11">
+        <v>10.5</v>
+      </c>
+      <c r="P317" s="11">
+        <v>11.65</v>
+      </c>
+      <c r="Q317" s="11">
+        <v>56</v>
+      </c>
+      <c r="R317" s="11">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="S317" s="11">
+        <v>36</v>
+      </c>
+      <c r="T317" s="11">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="U317" s="11">
+        <v>3.8</v>
+      </c>
+      <c r="V317" s="11">
+        <v>4.2569999999999997</v>
+      </c>
+      <c r="W317" s="11">
+        <v>16.5</v>
+      </c>
+      <c r="X317" s="11">
+        <v>7.8</v>
+      </c>
+      <c r="Y317" s="11">
+        <v>12.038</v>
+      </c>
+    </row>
+    <row r="318" spans="1:25">
+      <c r="A318" s="8">
+        <v>46203</v>
+      </c>
+      <c r="B318" s="8">
+        <v>46203</v>
+      </c>
+      <c r="C318" s="9">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D318" s="10" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -42651,21 +42924,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:AK8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.81640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.08984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.81640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.08984375" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.77734375" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.77734375" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="9.453125" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.453125" style="11" customWidth="1"/>
-    <col min="9" max="9" width="9.81640625" style="11" customWidth="1"/>
-    <col min="10" max="10" width="10.36328125" style="11" customWidth="1"/>
-    <col min="11" max="11" width="9.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.44140625" style="11" customWidth="1"/>
+    <col min="9" max="9" width="9.77734375" style="11" customWidth="1"/>
+    <col min="10" max="10" width="10.33203125" style="11" customWidth="1"/>
+    <col min="11" max="11" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" style="11"/>
-    <col min="13" max="13" width="9.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -43297,19 +43570,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:Y35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.08984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.08984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="15"/>
-    <col min="7" max="7" width="9.453125" style="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.453125" style="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.44140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.44140625" style="15" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="15"/>
-    <col min="10" max="10" width="11.81640625" style="17" customWidth="1"/>
+    <col min="10" max="10" width="11.77734375" style="17" customWidth="1"/>
     <col min="11" max="12" width="9" style="15"/>
-    <col min="13" max="13" width="13.36328125" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.33203125" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -44974,13 +45247,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:Y35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.36328125" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.08984375" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.08984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -46338,7 +46611,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -46351,11 +46624,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="22.81640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.81640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.81640625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="22.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.77734375" style="3" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{119CCF0D-13A1-4E10-8DE7-9CD3626547C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B0E0A87-4BD7-4A4D-ADEE-6773DB435648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -417,10 +417,10 @@
     </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="백분율" xfId="3" builtinId="5"/>
-    <cellStyle name="쉼표" xfId="2" builtinId="3"/>
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="2" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -438,7 +438,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2392,6 +2392,9 @@
                 <c:pt idx="314">
                   <c:v>46.832999999999998</c:v>
                 </c:pt>
+                <c:pt idx="315">
+                  <c:v>46.832999999999998</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4339,6 +4342,9 @@
                 <c:pt idx="314">
                   <c:v>23.5</c:v>
                 </c:pt>
+                <c:pt idx="315">
+                  <c:v>23.5</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -6286,6 +6292,9 @@
                 <c:pt idx="314">
                   <c:v>73.744</c:v>
                 </c:pt>
+                <c:pt idx="315">
+                  <c:v>73.744</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -8233,6 +8242,9 @@
                 <c:pt idx="314">
                   <c:v>11.65</c:v>
                 </c:pt>
+                <c:pt idx="315">
+                  <c:v>11.65</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -10178,6 +10190,9 @@
                   <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="314">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="315">
                   <c:v>36</c:v>
                 </c:pt>
               </c:numCache>
@@ -12143,6 +12158,9 @@
                 <c:pt idx="314">
                   <c:v>4.2569999999999997</c:v>
                 </c:pt>
+                <c:pt idx="315">
+                  <c:v>4.2569999999999997</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -14090,6 +14108,9 @@
                   <c:v>11.952</c:v>
                 </c:pt>
                 <c:pt idx="314">
+                  <c:v>12.038</c:v>
+                </c:pt>
+                <c:pt idx="315">
                   <c:v>12.038</c:v>
                 </c:pt>
               </c:numCache>
@@ -14369,7 +14390,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -15408,7 +15429,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -18186,14 +18207,14 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:Z318"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="10.77734375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.77734375" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.81640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.08984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="13" width="9" style="11"/>
-    <col min="14" max="14" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.453125" style="11" bestFit="1" customWidth="1"/>
     <col min="15" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -42905,6 +42926,69 @@
       </c>
       <c r="D318" s="10" t="s">
         <v>53</v>
+      </c>
+      <c r="E318" s="11">
+        <v>61</v>
+      </c>
+      <c r="F318" s="11">
+        <v>31.5</v>
+      </c>
+      <c r="G318" s="11">
+        <v>46.832999999999998</v>
+      </c>
+      <c r="H318" s="11">
+        <v>25.3</v>
+      </c>
+      <c r="I318" s="11">
+        <v>22.1</v>
+      </c>
+      <c r="J318" s="11">
+        <v>23.5</v>
+      </c>
+      <c r="K318" s="11">
+        <v>92</v>
+      </c>
+      <c r="L318" s="11">
+        <v>39.1</v>
+      </c>
+      <c r="M318" s="11">
+        <v>73.744</v>
+      </c>
+      <c r="N318" s="11">
+        <v>12</v>
+      </c>
+      <c r="O318" s="11">
+        <v>10.5</v>
+      </c>
+      <c r="P318" s="11">
+        <v>11.65</v>
+      </c>
+      <c r="Q318" s="11">
+        <v>56</v>
+      </c>
+      <c r="R318" s="11">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="S318" s="11">
+        <v>36</v>
+      </c>
+      <c r="T318" s="11">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="U318" s="11">
+        <v>3.8</v>
+      </c>
+      <c r="V318" s="11">
+        <v>4.2569999999999997</v>
+      </c>
+      <c r="W318" s="11">
+        <v>16.5</v>
+      </c>
+      <c r="X318" s="11">
+        <v>7.8</v>
+      </c>
+      <c r="Y318" s="11">
+        <v>12.038</v>
       </c>
     </row>
   </sheetData>
@@ -42924,21 +43008,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:AK8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="10.77734375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.77734375" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.81640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.08984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.08984375" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.453125" style="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.44140625" style="11" customWidth="1"/>
-    <col min="9" max="9" width="9.77734375" style="11" customWidth="1"/>
-    <col min="10" max="10" width="10.33203125" style="11" customWidth="1"/>
-    <col min="11" max="11" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.453125" style="11" customWidth="1"/>
+    <col min="9" max="9" width="9.81640625" style="11" customWidth="1"/>
+    <col min="10" max="10" width="10.36328125" style="11" customWidth="1"/>
+    <col min="11" max="11" width="9.453125" style="11" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" style="11"/>
-    <col min="13" max="13" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.453125" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -43570,19 +43654,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:Y35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="10.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.08984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.08984375" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="15"/>
-    <col min="7" max="7" width="9.44140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.44140625" style="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.453125" style="17" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.453125" style="15" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="15"/>
-    <col min="10" max="10" width="11.77734375" style="17" customWidth="1"/>
+    <col min="10" max="10" width="11.81640625" style="17" customWidth="1"/>
     <col min="11" max="12" width="9" style="15"/>
-    <col min="13" max="13" width="13.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.36328125" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -45247,13 +45331,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:Y35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.36328125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.08984375" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.08984375" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.453125" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -46611,7 +46695,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <sheetData/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -46624,11 +46708,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="22.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.77734375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="22.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.81640625" style="3" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B0E0A87-4BD7-4A4D-ADEE-6773DB435648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA4BED85-03A6-486D-B84F-29AC35FCDCD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="61">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -417,10 +417,10 @@
     </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Comma" xfId="2" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="백분율" xfId="3" builtinId="5"/>
+    <cellStyle name="쉼표" xfId="2" builtinId="3"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -438,7 +438,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1438,6 +1438,15 @@
                 <c:pt idx="315">
                   <c:v>46203</c:v>
                 </c:pt>
+                <c:pt idx="316">
+                  <c:v>46204</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>46204</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>46204</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2393,6 +2402,12 @@
                   <c:v>46.832999999999998</c:v>
                 </c:pt>
                 <c:pt idx="315">
+                  <c:v>46.832999999999998</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>46.832999999999998</c:v>
+                </c:pt>
+                <c:pt idx="317">
                   <c:v>46.832999999999998</c:v>
                 </c:pt>
               </c:numCache>
@@ -3388,6 +3403,15 @@
                 <c:pt idx="315">
                   <c:v>46203</c:v>
                 </c:pt>
+                <c:pt idx="316">
+                  <c:v>46204</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>46204</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>46204</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4344,6 +4368,12 @@
                 </c:pt>
                 <c:pt idx="315">
                   <c:v>23.5</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>23.3</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>23.3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5338,6 +5368,15 @@
                 <c:pt idx="315">
                   <c:v>46203</c:v>
                 </c:pt>
+                <c:pt idx="316">
+                  <c:v>46204</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>46204</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>46204</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6294,6 +6333,12 @@
                 </c:pt>
                 <c:pt idx="315">
                   <c:v>73.744</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>74.625</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>74.625</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7288,6 +7333,15 @@
                 <c:pt idx="315">
                   <c:v>46203</c:v>
                 </c:pt>
+                <c:pt idx="316">
+                  <c:v>46204</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>46204</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>46204</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8244,6 +8298,12 @@
                 </c:pt>
                 <c:pt idx="315">
                   <c:v>11.65</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>11.625</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>11.625</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9238,6 +9298,15 @@
                 <c:pt idx="315">
                   <c:v>46203</c:v>
                 </c:pt>
+                <c:pt idx="316">
+                  <c:v>46204</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>46204</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>46204</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10194,6 +10263,12 @@
                 </c:pt>
                 <c:pt idx="315">
                   <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>36.1</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>36.1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11204,6 +11279,15 @@
                 <c:pt idx="315">
                   <c:v>46203</c:v>
                 </c:pt>
+                <c:pt idx="316">
+                  <c:v>46204</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>46204</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>46204</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -12160,6 +12244,12 @@
                 </c:pt>
                 <c:pt idx="315">
                   <c:v>4.2569999999999997</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>4.2359999999999998</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>4.2359999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13156,6 +13246,15 @@
                 <c:pt idx="315">
                   <c:v>46203</c:v>
                 </c:pt>
+                <c:pt idx="316">
+                  <c:v>46204</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>46204</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>46204</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -14112,6 +14211,12 @@
                 </c:pt>
                 <c:pt idx="315">
                   <c:v>12.038</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>12.170999999999999</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>12.170999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14390,7 +14495,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -15429,7 +15534,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -18206,15 +18311,15 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Z318"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <dimension ref="A1:Z321"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.81640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.08984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.81640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.77734375" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.77734375" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="13" width="9" style="11"/>
-    <col min="14" max="14" width="9.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="15" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -42989,6 +43094,174 @@
       </c>
       <c r="Y318" s="11">
         <v>12.038</v>
+      </c>
+    </row>
+    <row r="319" spans="1:25">
+      <c r="A319" s="8">
+        <v>46204</v>
+      </c>
+      <c r="B319" s="8">
+        <v>46204</v>
+      </c>
+      <c r="C319" s="9">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D319" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E319" s="11">
+        <v>61</v>
+      </c>
+      <c r="F319" s="11">
+        <v>31.3</v>
+      </c>
+      <c r="G319" s="11">
+        <v>46.832999999999998</v>
+      </c>
+      <c r="H319" s="11">
+        <v>25.3</v>
+      </c>
+      <c r="I319" s="11">
+        <v>22.3</v>
+      </c>
+      <c r="J319" s="11">
+        <v>23.3</v>
+      </c>
+      <c r="K319" s="11">
+        <v>93</v>
+      </c>
+      <c r="L319" s="11">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="M319" s="11">
+        <v>74.625</v>
+      </c>
+      <c r="N319" s="11">
+        <v>12</v>
+      </c>
+      <c r="O319" s="11">
+        <v>10.5</v>
+      </c>
+      <c r="P319" s="11">
+        <v>11.625</v>
+      </c>
+      <c r="Q319" s="11">
+        <v>57</v>
+      </c>
+      <c r="R319" s="11">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="S319" s="11">
+        <v>36.1</v>
+      </c>
+      <c r="T319" s="11">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="U319" s="11">
+        <v>3.8</v>
+      </c>
+      <c r="V319" s="11">
+        <v>4.2359999999999998</v>
+      </c>
+      <c r="W319" s="11">
+        <v>16.5</v>
+      </c>
+      <c r="X319" s="11">
+        <v>8</v>
+      </c>
+      <c r="Y319" s="11">
+        <v>12.170999999999999</v>
+      </c>
+    </row>
+    <row r="320" spans="1:25">
+      <c r="A320" s="8">
+        <v>46204</v>
+      </c>
+      <c r="B320" s="8">
+        <v>46204</v>
+      </c>
+      <c r="C320" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D320" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E320" s="11">
+        <v>61</v>
+      </c>
+      <c r="F320" s="11">
+        <v>31.3</v>
+      </c>
+      <c r="G320" s="11">
+        <v>46.832999999999998</v>
+      </c>
+      <c r="H320" s="11">
+        <v>25.3</v>
+      </c>
+      <c r="I320" s="11">
+        <v>22.3</v>
+      </c>
+      <c r="J320" s="11">
+        <v>23.3</v>
+      </c>
+      <c r="K320" s="11">
+        <v>93</v>
+      </c>
+      <c r="L320" s="11">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="M320" s="11">
+        <v>74.625</v>
+      </c>
+      <c r="N320" s="11">
+        <v>12</v>
+      </c>
+      <c r="O320" s="11">
+        <v>10.5</v>
+      </c>
+      <c r="P320" s="11">
+        <v>11.625</v>
+      </c>
+      <c r="Q320" s="11">
+        <v>57</v>
+      </c>
+      <c r="R320" s="11">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="S320" s="11">
+        <v>36.1</v>
+      </c>
+      <c r="T320" s="11">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="U320" s="11">
+        <v>3.8</v>
+      </c>
+      <c r="V320" s="11">
+        <v>4.2359999999999998</v>
+      </c>
+      <c r="W320" s="11">
+        <v>16.5</v>
+      </c>
+      <c r="X320" s="11">
+        <v>8</v>
+      </c>
+      <c r="Y320" s="11">
+        <v>12.170999999999999</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4">
+      <c r="A321" s="8">
+        <v>46204</v>
+      </c>
+      <c r="B321" s="8">
+        <v>46204</v>
+      </c>
+      <c r="C321" s="9">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D321" s="10" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -43008,21 +43281,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:AK8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.81640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.08984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.81640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.08984375" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.77734375" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.77734375" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="9.453125" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.453125" style="11" customWidth="1"/>
-    <col min="9" max="9" width="9.81640625" style="11" customWidth="1"/>
-    <col min="10" max="10" width="10.36328125" style="11" customWidth="1"/>
-    <col min="11" max="11" width="9.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.44140625" style="11" customWidth="1"/>
+    <col min="9" max="9" width="9.77734375" style="11" customWidth="1"/>
+    <col min="10" max="10" width="10.33203125" style="11" customWidth="1"/>
+    <col min="11" max="11" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" style="11"/>
-    <col min="13" max="13" width="9.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -43654,19 +43927,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:Y35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.08984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.08984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="15"/>
-    <col min="7" max="7" width="9.453125" style="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.453125" style="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.44140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.44140625" style="15" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="15"/>
-    <col min="10" max="10" width="11.81640625" style="17" customWidth="1"/>
+    <col min="10" max="10" width="11.77734375" style="17" customWidth="1"/>
     <col min="11" max="12" width="9" style="15"/>
-    <col min="13" max="13" width="13.36328125" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.33203125" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -45331,13 +45604,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:Y35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.36328125" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.08984375" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.08984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -46695,7 +46968,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -46708,11 +46981,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="22.81640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.81640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.81640625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="22.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.77734375" style="3" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA4BED85-03A6-486D-B84F-29AC35FCDCD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FD1BE1F-B20D-4DE2-9487-4ED89630B318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -417,10 +417,10 @@
     </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="백분율" xfId="3" builtinId="5"/>
-    <cellStyle name="쉼표" xfId="2" builtinId="3"/>
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="2" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -438,7 +438,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2410,6 +2410,9 @@
                 <c:pt idx="317">
                   <c:v>46.832999999999998</c:v>
                 </c:pt>
+                <c:pt idx="318">
+                  <c:v>46.832999999999998</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4375,6 +4378,9 @@
                 <c:pt idx="317">
                   <c:v>23.3</c:v>
                 </c:pt>
+                <c:pt idx="318">
+                  <c:v>23.3</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -6340,6 +6346,9 @@
                 <c:pt idx="317">
                   <c:v>74.625</c:v>
                 </c:pt>
+                <c:pt idx="318">
+                  <c:v>74.625</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -8305,6 +8314,9 @@
                 <c:pt idx="317">
                   <c:v>11.625</c:v>
                 </c:pt>
+                <c:pt idx="318">
+                  <c:v>11.625</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -10268,6 +10280,9 @@
                   <c:v>36.1</c:v>
                 </c:pt>
                 <c:pt idx="317">
+                  <c:v>36.1</c:v>
+                </c:pt>
+                <c:pt idx="318">
                   <c:v>36.1</c:v>
                 </c:pt>
               </c:numCache>
@@ -12251,6 +12266,9 @@
                 <c:pt idx="317">
                   <c:v>4.2359999999999998</c:v>
                 </c:pt>
+                <c:pt idx="318">
+                  <c:v>4.2359999999999998</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -14216,6 +14234,9 @@
                   <c:v>12.170999999999999</c:v>
                 </c:pt>
                 <c:pt idx="317">
+                  <c:v>12.170999999999999</c:v>
+                </c:pt>
+                <c:pt idx="318">
                   <c:v>12.170999999999999</c:v>
                 </c:pt>
               </c:numCache>
@@ -14495,7 +14516,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -15534,7 +15555,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -18312,14 +18333,14 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:Z321"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="10.77734375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.77734375" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.81640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.08984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="13" width="9" style="11"/>
-    <col min="14" max="14" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.453125" style="11" bestFit="1" customWidth="1"/>
     <col min="15" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -43250,7 +43271,7 @@
         <v>12.170999999999999</v>
       </c>
     </row>
-    <row r="321" spans="1:4">
+    <row r="321" spans="1:25">
       <c r="A321" s="8">
         <v>46204</v>
       </c>
@@ -43262,6 +43283,69 @@
       </c>
       <c r="D321" s="10" t="s">
         <v>53</v>
+      </c>
+      <c r="E321" s="11">
+        <v>61</v>
+      </c>
+      <c r="F321" s="11">
+        <v>31.3</v>
+      </c>
+      <c r="G321" s="11">
+        <v>46.832999999999998</v>
+      </c>
+      <c r="H321" s="11">
+        <v>25.3</v>
+      </c>
+      <c r="I321" s="11">
+        <v>22.3</v>
+      </c>
+      <c r="J321" s="11">
+        <v>23.3</v>
+      </c>
+      <c r="K321" s="11">
+        <v>93</v>
+      </c>
+      <c r="L321" s="11">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="M321" s="11">
+        <v>74.625</v>
+      </c>
+      <c r="N321" s="11">
+        <v>12</v>
+      </c>
+      <c r="O321" s="11">
+        <v>10.5</v>
+      </c>
+      <c r="P321" s="11">
+        <v>11.625</v>
+      </c>
+      <c r="Q321" s="11">
+        <v>57</v>
+      </c>
+      <c r="R321" s="11">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="S321" s="11">
+        <v>36.1</v>
+      </c>
+      <c r="T321" s="11">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="U321" s="11">
+        <v>3.8</v>
+      </c>
+      <c r="V321" s="11">
+        <v>4.2359999999999998</v>
+      </c>
+      <c r="W321" s="11">
+        <v>16.5</v>
+      </c>
+      <c r="X321" s="11">
+        <v>8</v>
+      </c>
+      <c r="Y321" s="11">
+        <v>12.170999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -43281,21 +43365,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:AK8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="10.77734375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.77734375" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.81640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.08984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.08984375" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.453125" style="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.44140625" style="11" customWidth="1"/>
-    <col min="9" max="9" width="9.77734375" style="11" customWidth="1"/>
-    <col min="10" max="10" width="10.33203125" style="11" customWidth="1"/>
-    <col min="11" max="11" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.453125" style="11" customWidth="1"/>
+    <col min="9" max="9" width="9.81640625" style="11" customWidth="1"/>
+    <col min="10" max="10" width="10.36328125" style="11" customWidth="1"/>
+    <col min="11" max="11" width="9.453125" style="11" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" style="11"/>
-    <col min="13" max="13" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.453125" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -43927,19 +44011,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:Y35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="10.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.08984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.08984375" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="15"/>
-    <col min="7" max="7" width="9.44140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.44140625" style="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.453125" style="17" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.453125" style="15" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="15"/>
-    <col min="10" max="10" width="11.77734375" style="17" customWidth="1"/>
+    <col min="10" max="10" width="11.81640625" style="17" customWidth="1"/>
     <col min="11" max="12" width="9" style="15"/>
-    <col min="13" max="13" width="13.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.36328125" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -45604,13 +45688,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:Y35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.36328125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.08984375" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.08984375" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.453125" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -46968,7 +47052,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <sheetData/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -46981,11 +47065,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="22.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.77734375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="22.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.81640625" style="3" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FD1BE1F-B20D-4DE2-9487-4ED89630B318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2A412D9-38EC-4B8E-B1C7-5ADD83EEDFC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="61">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -417,10 +417,10 @@
     </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Comma" xfId="2" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="백분율" xfId="3" builtinId="5"/>
+    <cellStyle name="쉼표" xfId="2" builtinId="3"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -438,7 +438,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1447,6 +1447,15 @@
                 <c:pt idx="318">
                   <c:v>46204</c:v>
                 </c:pt>
+                <c:pt idx="319">
+                  <c:v>46205</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>46205</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>46205</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2412,6 +2421,12 @@
                 </c:pt>
                 <c:pt idx="318">
                   <c:v>46.832999999999998</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>46.832999999999998</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>46.667000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3415,6 +3430,15 @@
                 <c:pt idx="318">
                   <c:v>46204</c:v>
                 </c:pt>
+                <c:pt idx="319">
+                  <c:v>46205</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>46205</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>46205</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4379,6 +4403,12 @@
                   <c:v>23.3</c:v>
                 </c:pt>
                 <c:pt idx="318">
+                  <c:v>23.3</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>23.3</c:v>
+                </c:pt>
+                <c:pt idx="320">
                   <c:v>23.3</c:v>
                 </c:pt>
               </c:numCache>
@@ -5383,6 +5413,15 @@
                 <c:pt idx="318">
                   <c:v>46204</c:v>
                 </c:pt>
+                <c:pt idx="319">
+                  <c:v>46205</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>46205</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>46205</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6348,6 +6387,12 @@
                 </c:pt>
                 <c:pt idx="318">
                   <c:v>74.625</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>75.375</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>75.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7351,6 +7396,15 @@
                 <c:pt idx="318">
                   <c:v>46204</c:v>
                 </c:pt>
+                <c:pt idx="319">
+                  <c:v>46205</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>46205</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>46205</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8316,6 +8370,12 @@
                 </c:pt>
                 <c:pt idx="318">
                   <c:v>11.625</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>11.6</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>11.6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9319,6 +9379,15 @@
                 <c:pt idx="318">
                   <c:v>46204</c:v>
                 </c:pt>
+                <c:pt idx="319">
+                  <c:v>46205</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>46205</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>46205</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10284,6 +10353,12 @@
                 </c:pt>
                 <c:pt idx="318">
                   <c:v>36.1</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>36.299999999999997</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>36.299999999999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11303,6 +11378,15 @@
                 <c:pt idx="318">
                   <c:v>46204</c:v>
                 </c:pt>
+                <c:pt idx="319">
+                  <c:v>46205</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>46205</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>46205</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -12268,6 +12352,12 @@
                 </c:pt>
                 <c:pt idx="318">
                   <c:v>4.2359999999999998</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>4.2140000000000004</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>4.2039999999999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13273,6 +13363,15 @@
                 <c:pt idx="318">
                   <c:v>46204</c:v>
                 </c:pt>
+                <c:pt idx="319">
+                  <c:v>46205</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>46205</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>46205</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -14238,6 +14337,12 @@
                 </c:pt>
                 <c:pt idx="318">
                   <c:v>12.170999999999999</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>12.340999999999999</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>12.340999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14516,7 +14621,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -15555,7 +15660,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -18332,15 +18437,15 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Z321"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <dimension ref="A1:Z324"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.81640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.08984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.81640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.77734375" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.77734375" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="13" width="9" style="11"/>
-    <col min="14" max="14" width="9.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="15" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -43346,6 +43451,174 @@
       </c>
       <c r="Y321" s="11">
         <v>12.170999999999999</v>
+      </c>
+    </row>
+    <row r="322" spans="1:25">
+      <c r="A322" s="8">
+        <v>46205</v>
+      </c>
+      <c r="B322" s="8">
+        <v>46205</v>
+      </c>
+      <c r="C322" s="9">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D322" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E322" s="11">
+        <v>61</v>
+      </c>
+      <c r="F322" s="11">
+        <v>31</v>
+      </c>
+      <c r="G322" s="11">
+        <v>46.832999999999998</v>
+      </c>
+      <c r="H322" s="11">
+        <v>25.3</v>
+      </c>
+      <c r="I322" s="11">
+        <v>22.3</v>
+      </c>
+      <c r="J322" s="11">
+        <v>23.3</v>
+      </c>
+      <c r="K322" s="11">
+        <v>94</v>
+      </c>
+      <c r="L322" s="11">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="M322" s="11">
+        <v>75.375</v>
+      </c>
+      <c r="N322" s="11">
+        <v>12</v>
+      </c>
+      <c r="O322" s="11">
+        <v>10.5</v>
+      </c>
+      <c r="P322" s="11">
+        <v>11.6</v>
+      </c>
+      <c r="Q322" s="11">
+        <v>59</v>
+      </c>
+      <c r="R322" s="11">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="S322" s="11">
+        <v>36.299999999999997</v>
+      </c>
+      <c r="T322" s="11">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="U322" s="11">
+        <v>3.8</v>
+      </c>
+      <c r="V322" s="11">
+        <v>4.2140000000000004</v>
+      </c>
+      <c r="W322" s="11">
+        <v>16.5</v>
+      </c>
+      <c r="X322" s="11">
+        <v>8</v>
+      </c>
+      <c r="Y322" s="11">
+        <v>12.340999999999999</v>
+      </c>
+    </row>
+    <row r="323" spans="1:25">
+      <c r="A323" s="8">
+        <v>46205</v>
+      </c>
+      <c r="B323" s="8">
+        <v>46205</v>
+      </c>
+      <c r="C323" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D323" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E323" s="11">
+        <v>61</v>
+      </c>
+      <c r="F323" s="11">
+        <v>31</v>
+      </c>
+      <c r="G323" s="11">
+        <v>46.667000000000002</v>
+      </c>
+      <c r="H323" s="11">
+      